--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20165,11 +20165,7 @@
       <c r="I2" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="58" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="J2" s="58" t="n"/>
       <c r="K2" s="58" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -20211,7 +20207,11 @@
       <c r="I3" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="58" t="inlineStr"/>
+      <c r="J3" s="58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="K3" s="58" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -20253,7 +20253,7 @@
       <c r="I4" s="58" t="n">
         <v>0.75</v>
       </c>
-      <c r="J4" s="58" t="inlineStr"/>
+      <c r="J4" s="58" t="n"/>
       <c r="K4" s="58" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -20295,7 +20295,7 @@
       <c r="I5" s="58" t="n">
         <v>0.75</v>
       </c>
-      <c r="J5" s="58" t="inlineStr"/>
+      <c r="J5" s="58" t="n"/>
       <c r="K5" s="58" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -20337,7 +20337,7 @@
       <c r="I6" s="58" t="n">
         <v>0.75</v>
       </c>
-      <c r="J6" s="58" t="inlineStr"/>
+      <c r="J6" s="58" t="n"/>
       <c r="K6" s="58" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -20349,6 +20349,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="52" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20153,17 +20153,25 @@
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="58" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G2" s="58" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H2" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="58" t="n">
-        <v>0</v>
+      <c r="F2" s="58" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="G2" s="58" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="H2" s="58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" s="58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J2" s="58" t="n"/>
       <c r="K2" s="58" t="inlineStr">
@@ -20193,19 +20201,27 @@
           <t>main.png</t>
         </is>
       </c>
-      <c r="D3" s="58" t="inlineStr"/>
-      <c r="E3" s="58" t="inlineStr"/>
-      <c r="F3" s="58" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G3" s="58" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H3" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="58" t="n">
-        <v>0</v>
+      <c r="D3" s="58" t="n"/>
+      <c r="E3" s="58" t="n"/>
+      <c r="F3" s="58" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="G3" s="58" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H3" s="58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I3" s="58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J3" s="58" t="inlineStr">
         <is>
@@ -20239,19 +20255,27 @@
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="58" t="inlineStr"/>
-      <c r="E4" s="58" t="inlineStr"/>
-      <c r="F4" s="58" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G4" s="58" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H4" s="58" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I4" s="58" t="n">
-        <v>0.75</v>
+      <c r="D4" s="58" t="n"/>
+      <c r="E4" s="58" t="n"/>
+      <c r="F4" s="58" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="G4" s="58" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H4" s="58" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="I4" s="58" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
       </c>
       <c r="J4" s="58" t="n"/>
       <c r="K4" s="58" t="inlineStr">
@@ -20281,19 +20305,27 @@
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="58" t="inlineStr"/>
-      <c r="E5" s="58" t="inlineStr"/>
-      <c r="F5" s="58" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G5" s="58" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H5" s="58" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I5" s="58" t="n">
-        <v>0.75</v>
+      <c r="D5" s="58" t="n"/>
+      <c r="E5" s="58" t="n"/>
+      <c r="F5" s="58" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="G5" s="58" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H5" s="58" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I5" s="58" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
       </c>
       <c r="J5" s="58" t="n"/>
       <c r="K5" s="58" t="inlineStr">
@@ -20323,19 +20355,27 @@
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="58" t="inlineStr"/>
-      <c r="E6" s="58" t="inlineStr"/>
-      <c r="F6" s="58" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G6" s="58" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H6" s="58" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I6" s="58" t="n">
-        <v>0.75</v>
+      <c r="D6" s="58" t="n"/>
+      <c r="E6" s="58" t="n"/>
+      <c r="F6" s="58" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="G6" s="58" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H6" s="58" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="I6" s="58" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
       </c>
       <c r="J6" s="58" t="n"/>
       <c r="K6" s="58" t="inlineStr">

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -15,6 +15,7 @@
     <sheet name="参考資料" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="キャラクター" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="読み上げ" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="読み方" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FAQ'!$A$1:$J$18</definedName>
@@ -266,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -424,6 +425,9 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1039,6 +1043,945 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="48" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="B1" s="48" t="inlineStr">
+        <is>
+          <t>読み</t>
+        </is>
+      </c>
+      <c r="C1" s="48" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="D1" s="48" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="60" t="inlineStr">
+        <is>
+          <t>白川郷</t>
+        </is>
+      </c>
+      <c r="B2" s="60" t="inlineStr">
+        <is>
+          <t>シラカワゴウ</t>
+        </is>
+      </c>
+      <c r="C2" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D2" s="46" t="inlineStr">
+        <is>
+          <t>「しらかわきょう」と読まれることがある</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="60" t="inlineStr">
+        <is>
+          <t>白川村</t>
+        </is>
+      </c>
+      <c r="B3" s="60" t="inlineStr">
+        <is>
+          <t>シラカワムラ</t>
+        </is>
+      </c>
+      <c r="C3" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D3" s="46" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="60" t="inlineStr">
+        <is>
+          <t>荻町</t>
+        </is>
+      </c>
+      <c r="B4" s="60" t="inlineStr">
+        <is>
+          <t>オギマチ</t>
+        </is>
+      </c>
+      <c r="C4" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D4" s="46" t="inlineStr">
+        <is>
+          <t>「はぎまち」「おぎちょう」と読まれやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>鳩谷</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="inlineStr">
+        <is>
+          <t>ハトガヤ</t>
+        </is>
+      </c>
+      <c r="C5" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D5" s="46" t="inlineStr">
+        <is>
+          <t>「はとや」と読まれやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr">
+        <is>
+          <t>飯島</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t>イイジマ</t>
+        </is>
+      </c>
+      <c r="C6" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D6" s="46" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>寺尾</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="inlineStr">
+        <is>
+          <t>テラオ</t>
+        </is>
+      </c>
+      <c r="C7" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D7" s="46" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="60" t="inlineStr">
+        <is>
+          <t>和田家</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>ワダケ</t>
+        </is>
+      </c>
+      <c r="C8" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D8" s="46" t="inlineStr">
+        <is>
+          <t>「わだか」「わだいえ」と読まれやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="60" t="inlineStr">
+        <is>
+          <t>城山</t>
+        </is>
+      </c>
+      <c r="B9" s="60" t="inlineStr">
+        <is>
+          <t>シロヤマ</t>
+        </is>
+      </c>
+      <c r="C9" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D9" s="46" t="inlineStr">
+        <is>
+          <t>城山展望台。「じょうざん」と読まれやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="60" t="inlineStr">
+        <is>
+          <t>白山</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>ハクサン</t>
+        </is>
+      </c>
+      <c r="C10" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>「しろやま」と読まれやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="60" t="inlineStr">
+        <is>
+          <t>庄川</t>
+        </is>
+      </c>
+      <c r="B11" s="60" t="inlineStr">
+        <is>
+          <t>ショウガワ</t>
+        </is>
+      </c>
+      <c r="C11" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="60" t="inlineStr">
+        <is>
+          <t>白水湖</t>
+        </is>
+      </c>
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>シラミズコ</t>
+        </is>
+      </c>
+      <c r="C12" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D12" s="46" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="60" t="inlineStr">
+        <is>
+          <t>白水園</t>
+        </is>
+      </c>
+      <c r="B13" s="60" t="inlineStr">
+        <is>
+          <t>シラミズエン</t>
+        </is>
+      </c>
+      <c r="C13" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D13" s="46" t="inlineStr">
+        <is>
+          <t>飲食店。要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="60" t="inlineStr">
+        <is>
+          <t>三方岩岳</t>
+        </is>
+      </c>
+      <c r="B14" s="60" t="inlineStr">
+        <is>
+          <t>サンボウイワダケ</t>
+        </is>
+      </c>
+      <c r="C14" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="60" t="inlineStr">
+        <is>
+          <t>野谷荘司山</t>
+        </is>
+      </c>
+      <c r="B15" s="60" t="inlineStr">
+        <is>
+          <t>ノダニショウジヤマ</t>
+        </is>
+      </c>
+      <c r="C15" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="60" t="inlineStr">
+        <is>
+          <t>猪臥山</t>
+        </is>
+      </c>
+      <c r="B16" s="60" t="inlineStr">
+        <is>
+          <t>イブシヤマ</t>
+        </is>
+      </c>
+      <c r="C16" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D16" s="46" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="60" t="inlineStr">
+        <is>
+          <t>民家園</t>
+        </is>
+      </c>
+      <c r="B17" s="60" t="inlineStr">
+        <is>
+          <t>ミンカエン</t>
+        </is>
+      </c>
+      <c r="C17" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
+        <is>
+          <t>合掌造り民家園</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="60" t="inlineStr">
+        <is>
+          <t>白川八幡神社</t>
+        </is>
+      </c>
+      <c r="B18" s="60" t="inlineStr">
+        <is>
+          <t>シラカワハチマンジンジャ</t>
+        </is>
+      </c>
+      <c r="C18" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D18" s="46" t="inlineStr">
+        <is>
+          <t>社名はひとまとめで読ませる</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="60" t="inlineStr">
+        <is>
+          <t>鳩谷八幡神社</t>
+        </is>
+      </c>
+      <c r="B19" s="60" t="inlineStr">
+        <is>
+          <t>ハトガヤハチマンジンジャ</t>
+        </is>
+      </c>
+      <c r="C19" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D19" s="46" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="60" t="inlineStr">
+        <is>
+          <t>飯島八幡神社</t>
+        </is>
+      </c>
+      <c r="B20" s="60" t="inlineStr">
+        <is>
+          <t>イイジマハチマンジンジャ</t>
+        </is>
+      </c>
+      <c r="C20" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D20" s="46" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="60" t="inlineStr">
+        <is>
+          <t>今藤商店</t>
+        </is>
+      </c>
+      <c r="B21" s="60" t="inlineStr">
+        <is>
+          <t>イマトウショウテン</t>
+        </is>
+      </c>
+      <c r="C21" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D21" s="46" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="60" t="inlineStr">
+        <is>
+          <t>朴葉味噌</t>
+        </is>
+      </c>
+      <c r="B22" s="60" t="inlineStr">
+        <is>
+          <t>ホオバミソ</t>
+        </is>
+      </c>
+      <c r="C22" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D22" s="46" t="inlineStr">
+        <is>
+          <t>「ぼくようみそ」と読まれやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="60" t="inlineStr">
+        <is>
+          <t>岩魚</t>
+        </is>
+      </c>
+      <c r="B23" s="60" t="inlineStr">
+        <is>
+          <t>イワナ</t>
+        </is>
+      </c>
+      <c r="C23" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="inlineStr">
+        <is>
+          <t>「がんぎょ」と読まれやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="60" t="inlineStr">
+        <is>
+          <t>飛騨牛</t>
+        </is>
+      </c>
+      <c r="B24" s="60" t="inlineStr">
+        <is>
+          <t>ヒダギュウ</t>
+        </is>
+      </c>
+      <c r="C24" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D24" s="46" t="inlineStr">
+        <is>
+          <t>「ひだうし」と読まれやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="60" t="inlineStr">
+        <is>
+          <t>石豆腐</t>
+        </is>
+      </c>
+      <c r="B25" s="60" t="inlineStr">
+        <is>
+          <t>イシドウフ</t>
+        </is>
+      </c>
+      <c r="C25" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D25" s="46" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="60" t="inlineStr">
+        <is>
+          <t>合掌造り</t>
+        </is>
+      </c>
+      <c r="B26" s="60" t="inlineStr">
+        <is>
+          <t>ガッショウヅクリ</t>
+        </is>
+      </c>
+      <c r="C26" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="60" t="inlineStr">
+        <is>
+          <t>春駒（はるこま）</t>
+        </is>
+      </c>
+      <c r="B27" s="60" t="inlineStr">
+        <is>
+          <t>ハルコマ</t>
+        </is>
+      </c>
+      <c r="C27" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="inlineStr">
+        <is>
+          <t>読み方が添えてある箇所ごと差し替える</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="60" t="inlineStr">
+        <is>
+          <t>春駒</t>
+        </is>
+      </c>
+      <c r="B28" s="60" t="inlineStr">
+        <is>
+          <t>ハルコマ</t>
+        </is>
+      </c>
+      <c r="C28" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D28" s="46" t="inlineStr">
+        <is>
+          <t>民謡。「しゅんく」と読まれやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="60" t="inlineStr">
+        <is>
+          <t>白川連獅子</t>
+        </is>
+      </c>
+      <c r="B29" s="60" t="inlineStr">
+        <is>
+          <t>シラカワレンジシ</t>
+        </is>
+      </c>
+      <c r="C29" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="60" t="inlineStr">
+        <is>
+          <t>獅子舞</t>
+        </is>
+      </c>
+      <c r="B30" s="60" t="inlineStr">
+        <is>
+          <t>シシマイ</t>
+        </is>
+      </c>
+      <c r="C30" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D30" s="46" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="60" t="inlineStr">
+        <is>
+          <t>神幸祭</t>
+        </is>
+      </c>
+      <c r="B31" s="60" t="inlineStr">
+        <is>
+          <t>シンコウサイ</t>
+        </is>
+      </c>
+      <c r="C31" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="inlineStr">
+        <is>
+          <t>「じんこうさい」の社もある。要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="60" t="inlineStr">
+        <is>
+          <t>還御</t>
+        </is>
+      </c>
+      <c r="B32" s="60" t="inlineStr">
+        <is>
+          <t>カンギョ</t>
+        </is>
+      </c>
+      <c r="C32" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D32" s="46" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="60" t="inlineStr">
+        <is>
+          <t>初穂料</t>
+        </is>
+      </c>
+      <c r="B33" s="60" t="inlineStr">
+        <is>
+          <t>ハツホリョウ</t>
+        </is>
+      </c>
+      <c r="C33" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="60" t="inlineStr">
+        <is>
+          <t>記念盃</t>
+        </is>
+      </c>
+      <c r="B34" s="60" t="inlineStr">
+        <is>
+          <t>キネンハイ</t>
+        </is>
+      </c>
+      <c r="C34" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D34" s="46" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="60" t="inlineStr">
+        <is>
+          <t>志納</t>
+        </is>
+      </c>
+      <c r="B35" s="60" t="inlineStr">
+        <is>
+          <t>シノウ</t>
+        </is>
+      </c>
+      <c r="C35" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D35" s="46" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="60" t="inlineStr">
+        <is>
+          <t>徳利</t>
+        </is>
+      </c>
+      <c r="B36" s="60" t="inlineStr">
+        <is>
+          <t>トックリ</t>
+        </is>
+      </c>
+      <c r="C36" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D36" s="46" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="60" t="inlineStr">
+        <is>
+          <t>五穀豊穣</t>
+        </is>
+      </c>
+      <c r="B37" s="60" t="inlineStr">
+        <is>
+          <t>ゴコクホウジョウ</t>
+        </is>
+      </c>
+      <c r="C37" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D37" s="46" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="60" t="inlineStr">
+        <is>
+          <t>郷土芸能</t>
+        </is>
+      </c>
+      <c r="B38" s="60" t="inlineStr">
+        <is>
+          <t>キョウドゲイノウ</t>
+        </is>
+      </c>
+      <c r="C38" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D38" s="46" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="60" t="inlineStr">
+        <is>
+          <t>入村料</t>
+        </is>
+      </c>
+      <c r="B39" s="60" t="inlineStr">
+        <is>
+          <t>ニュウソンリョウ</t>
+        </is>
+      </c>
+      <c r="C39" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D39" s="46" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="60" t="inlineStr">
+        <is>
+          <t>村内</t>
+        </is>
+      </c>
+      <c r="B40" s="60" t="inlineStr">
+        <is>
+          <t>ソンナイ</t>
+        </is>
+      </c>
+      <c r="C40" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D40" s="46" t="inlineStr">
+        <is>
+          <t>「むらうち」と読まれやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="60" t="inlineStr">
+        <is>
+          <t>当村</t>
+        </is>
+      </c>
+      <c r="B41" s="60" t="inlineStr">
+        <is>
+          <t>トウソン</t>
+        </is>
+      </c>
+      <c r="C41" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D41" s="46" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="60" t="inlineStr">
+        <is>
+          <t>窓口机上</t>
+        </is>
+      </c>
+      <c r="B42" s="60" t="inlineStr">
+        <is>
+          <t>マドグチノツクエノウエ</t>
+        </is>
+      </c>
+      <c r="C42" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D42" s="46" t="inlineStr">
+        <is>
+          <t>回答の文そのものを「窓口の机の上」に直した方が読みやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="60" t="inlineStr">
+        <is>
+          <t>拾得物</t>
+        </is>
+      </c>
+      <c r="B43" s="60" t="inlineStr">
+        <is>
+          <t>シュウトクブツ</t>
+        </is>
+      </c>
+      <c r="C43" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D43" s="46" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="60" t="inlineStr">
+        <is>
+          <t>紙巻</t>
+        </is>
+      </c>
+      <c r="B44" s="60" t="inlineStr">
+        <is>
+          <t>カミマキ</t>
+        </is>
+      </c>
+      <c r="C44" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D44" s="46" t="inlineStr">
+        <is>
+          <t>紙巻きたばこ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="60" t="inlineStr">
+        <is>
+          <t>加熱式</t>
+        </is>
+      </c>
+      <c r="B45" s="60" t="inlineStr">
+        <is>
+          <t>カネツシキ</t>
+        </is>
+      </c>
+      <c r="C45" s="60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D45" s="46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="59" t="inlineStr">
+        <is>
+          <t>※ 読み上げるときだけ「表記」を「読み」に差し替えます。画面に出る文字は変わりません。「読み」はカタカナで書いてください（ひらがなでも動きますが、カタカナの方が安定します）。長い語から先に差し替えるので、「白川八幡神社」と「白川郷」のように重なる語を両方書いても大丈夫です。日本語の読み上げにだけ使います（英語などの読み上げには当てません）。備考に「要確認」と書いた行は、正しい読みを確かめてから使ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A47:D50"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -20389,7 +21332,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="52" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -14,8 +14,9 @@
     <sheet name="音声セット" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="参考資料" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="キャラクター" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="読み上げ" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="読み方" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="画面レイアウト" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="読み上げ" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="読み方" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FAQ'!$A$1:$J$18</definedName>
@@ -267,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -425,6 +426,9 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -1049,6 +1053,184 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="48" t="inlineStr">
+        <is>
+          <t>言語</t>
+        </is>
+      </c>
+      <c r="B1" s="48" t="inlineStr">
+        <is>
+          <t>優先する声</t>
+        </is>
+      </c>
+      <c r="C1" s="48" t="inlineStr">
+        <is>
+          <t>速さ</t>
+        </is>
+      </c>
+      <c r="D1" s="48" t="inlineStr">
+        <is>
+          <t>高さ</t>
+        </is>
+      </c>
+      <c r="E1" s="48" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="61" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="B2" s="46" t="inlineStr">
+        <is>
+          <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
+        </is>
+      </c>
+      <c r="C2" s="61" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D2" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="46" t="inlineStr">
+        <is>
+          <t>Androidアプリで使っていたのと同じ「Google 日本語」を先頭にしている</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="61" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B3" s="46" t="inlineStr">
+        <is>
+          <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
+        </is>
+      </c>
+      <c r="C3" s="61" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D3" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="46" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="61" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
+        </is>
+      </c>
+      <c r="C4" s="61" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D4" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="46" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="61" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="inlineStr">
+        <is>
+          <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
+        </is>
+      </c>
+      <c r="C5" s="61" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D5" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="46" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="61" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="inlineStr">
+        <is>
+          <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
+        </is>
+      </c>
+      <c r="C6" s="61" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D6" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="46" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="61" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="B7" s="46" t="inlineStr">
+        <is>
+          <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
+        </is>
+      </c>
+      <c r="C7" s="61" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D7" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="46" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="59" t="inlineStr">
+        <is>
+          <t>※ 「優先する声」は上から順に探し、その端末に入っている最初の声を使います。名前の一部が合えば採用します（「Microsoft Aria - English (United States)」に「Microsoft Aria」で当たります）。どれも入っていない端末では、その言語の声から自動で選びます。速さは1.0が標準、小さいほどゆっくり。高さは1.0が標準、大きいほど高い声になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A9:E11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1081,17 +1263,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="60" t="inlineStr">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="60" t="inlineStr">
+      <c r="B2" s="61" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="60" t="inlineStr">
+      <c r="C2" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1103,17 +1285,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1121,17 +1303,17 @@
       <c r="D3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="61" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="60" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1143,17 +1325,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="61" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="60" t="inlineStr">
+      <c r="C5" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1165,17 +1347,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="A6" s="61" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="60" t="inlineStr">
+      <c r="C6" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1183,17 +1365,17 @@
       <c r="D6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="61" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="60" t="inlineStr">
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="60" t="inlineStr">
+      <c r="C7" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1201,17 +1383,17 @@
       <c r="D7" s="46" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="60" t="inlineStr">
+      <c r="C8" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1223,17 +1405,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="60" t="inlineStr">
+      <c r="A9" s="61" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="60" t="inlineStr">
+      <c r="C9" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1245,17 +1427,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="60" t="inlineStr">
+      <c r="C10" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1267,17 +1449,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="A11" s="61" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="60" t="inlineStr">
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1285,17 +1467,17 @@
       <c r="D11" s="46" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="A12" s="61" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="60" t="inlineStr">
+      <c r="C12" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1303,17 +1485,17 @@
       <c r="D12" s="46" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="61" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="60" t="inlineStr">
+      <c r="C13" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1325,17 +1507,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="A14" s="61" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
+      <c r="B14" s="61" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="60" t="inlineStr">
+      <c r="C14" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1347,17 +1529,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="61" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="60" t="inlineStr">
+      <c r="C15" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1369,17 +1551,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="61" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="60" t="inlineStr">
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="60" t="inlineStr">
+      <c r="C16" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1391,17 +1573,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="61" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="60" t="inlineStr">
+      <c r="C17" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1413,17 +1595,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="60" t="inlineStr">
+      <c r="A18" s="61" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="60" t="inlineStr">
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="60" t="inlineStr">
+      <c r="C18" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1435,17 +1617,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="61" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="60" t="inlineStr">
+      <c r="C19" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1453,17 +1635,17 @@
       <c r="D19" s="46" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="60" t="inlineStr">
+      <c r="A20" s="61" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="60" t="inlineStr">
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="60" t="inlineStr">
+      <c r="C20" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1471,17 +1653,17 @@
       <c r="D20" s="46" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="60" t="inlineStr">
+      <c r="A21" s="61" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="60" t="inlineStr">
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="60" t="inlineStr">
+      <c r="C21" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1493,17 +1675,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="60" t="inlineStr">
+      <c r="A22" s="61" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="60" t="inlineStr">
+      <c r="B22" s="61" t="inlineStr">
         <is>
           <t>ホオバミソ</t>
         </is>
       </c>
-      <c r="C22" s="60" t="inlineStr">
+      <c r="C22" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1515,17 +1697,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="60" t="inlineStr">
+      <c r="A23" s="61" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="60" t="inlineStr">
+      <c r="B23" s="61" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="60" t="inlineStr">
+      <c r="C23" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1537,17 +1719,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="60" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="60" t="inlineStr">
+      <c r="B24" s="61" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="60" t="inlineStr">
+      <c r="C24" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1559,17 +1741,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="60" t="inlineStr">
+      <c r="A25" s="61" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="60" t="inlineStr">
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="60" t="inlineStr">
+      <c r="C25" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1577,17 +1759,17 @@
       <c r="D25" s="46" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="60" t="inlineStr">
+      <c r="A26" s="61" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="60" t="inlineStr">
+      <c r="B26" s="61" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="60" t="inlineStr">
+      <c r="C26" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1595,17 +1777,17 @@
       <c r="D26" s="46" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="60" t="inlineStr">
+      <c r="A27" s="61" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="60" t="inlineStr">
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="60" t="inlineStr">
+      <c r="C27" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1617,17 +1799,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="60" t="inlineStr">
+      <c r="A28" s="61" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="60" t="inlineStr">
+      <c r="B28" s="61" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="60" t="inlineStr">
+      <c r="C28" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1639,17 +1821,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="60" t="inlineStr">
+      <c r="A29" s="61" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="60" t="inlineStr">
+      <c r="B29" s="61" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="60" t="inlineStr">
+      <c r="C29" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1661,17 +1843,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="60" t="inlineStr">
+      <c r="A30" s="61" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="60" t="inlineStr">
+      <c r="B30" s="61" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="60" t="inlineStr">
+      <c r="C30" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1679,17 +1861,17 @@
       <c r="D30" s="46" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="60" t="inlineStr">
+      <c r="A31" s="61" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="60" t="inlineStr">
+      <c r="B31" s="61" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="60" t="inlineStr">
+      <c r="C31" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1701,17 +1883,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="60" t="inlineStr">
+      <c r="A32" s="61" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="60" t="inlineStr">
+      <c r="B32" s="61" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="60" t="inlineStr">
+      <c r="C32" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1719,17 +1901,17 @@
       <c r="D32" s="46" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="60" t="inlineStr">
+      <c r="A33" s="61" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="60" t="inlineStr">
+      <c r="B33" s="61" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="60" t="inlineStr">
+      <c r="C33" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1737,17 +1919,17 @@
       <c r="D33" s="46" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="60" t="inlineStr">
+      <c r="A34" s="61" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="60" t="inlineStr">
+      <c r="B34" s="61" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="60" t="inlineStr">
+      <c r="C34" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1755,17 +1937,17 @@
       <c r="D34" s="46" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="60" t="inlineStr">
+      <c r="A35" s="61" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="60" t="inlineStr">
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="60" t="inlineStr">
+      <c r="C35" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1773,17 +1955,17 @@
       <c r="D35" s="46" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="60" t="inlineStr">
+      <c r="A36" s="61" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="60" t="inlineStr">
+      <c r="B36" s="61" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="60" t="inlineStr">
+      <c r="C36" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1791,17 +1973,17 @@
       <c r="D36" s="46" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="60" t="inlineStr">
+      <c r="A37" s="61" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="60" t="inlineStr">
+      <c r="B37" s="61" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="60" t="inlineStr">
+      <c r="C37" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1809,17 +1991,17 @@
       <c r="D37" s="46" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="60" t="inlineStr">
+      <c r="A38" s="61" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="60" t="inlineStr">
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="60" t="inlineStr">
+      <c r="C38" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1827,17 +2009,17 @@
       <c r="D38" s="46" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="60" t="inlineStr">
+      <c r="A39" s="61" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="60" t="inlineStr">
+      <c r="B39" s="61" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="60" t="inlineStr">
+      <c r="C39" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1845,17 +2027,17 @@
       <c r="D39" s="46" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="60" t="inlineStr">
+      <c r="A40" s="61" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="60" t="inlineStr">
+      <c r="B40" s="61" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="60" t="inlineStr">
+      <c r="C40" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1867,17 +2049,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="60" t="inlineStr">
+      <c r="A41" s="61" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="60" t="inlineStr">
+      <c r="B41" s="61" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="60" t="inlineStr">
+      <c r="C41" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1885,17 +2067,17 @@
       <c r="D41" s="46" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="60" t="inlineStr">
+      <c r="A42" s="61" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="60" t="inlineStr">
+      <c r="B42" s="61" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="60" t="inlineStr">
+      <c r="C42" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1907,17 +2089,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="60" t="inlineStr">
+      <c r="A43" s="61" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="60" t="inlineStr">
+      <c r="B43" s="61" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="60" t="inlineStr">
+      <c r="C43" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1925,17 +2107,17 @@
       <c r="D43" s="46" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="60" t="inlineStr">
+      <c r="A44" s="61" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="60" t="inlineStr">
+      <c r="B44" s="61" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="60" t="inlineStr">
+      <c r="C44" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1947,17 +2129,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="60" t="inlineStr">
+      <c r="A45" s="61" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="60" t="inlineStr">
+      <c r="B45" s="61" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="60" t="inlineStr">
+      <c r="C45" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -4436,7 +4618,7 @@
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="58" t="n"/>
+      <c r="N43" s="61" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -5625,17 +5807,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="58" t="inlineStr">
+      <c r="A66" s="61" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="58" t="inlineStr">
+      <c r="B66" s="61" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="58" t="inlineStr">
+      <c r="C66" s="61" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -5665,26 +5847,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="58" t="inlineStr">
+      <c r="G66" s="61" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="58" t="n"/>
-      <c r="I66" s="58" t="inlineStr">
+      <c r="H66" s="61" t="n"/>
+      <c r="I66" s="61" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="58" t="inlineStr">
+      <c r="J66" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="58" t="n"/>
-      <c r="L66" s="58" t="n"/>
-      <c r="M66" s="58" t="n"/>
-      <c r="N66" s="58" t="n"/>
+      <c r="K66" s="61" t="n"/>
+      <c r="L66" s="61" t="n"/>
+      <c r="M66" s="61" t="n"/>
+      <c r="N66" s="61" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -6271,11 +6453,7 @@
           <t>The shuttle bus to the observatory leaves from the stop in front of the water-lily pond at Wada House. The fare is 300 yen one way, paid in cash when you get off. Elementary school children pay half price, infants ride free if they do not use a seat, and people with a disability certificate pay half price. Pets are not allowed on the bus. Buses going up run from 9:00 a.m. to 11:40 a.m. and from 1:20 p.m. to 3:40 p.m. Buses coming down run from 9:10 a.m. to 12:10 p.m. and from 1:30 p.m. to 4:10 p.m. All buses run every 20 minutes.</t>
         </is>
       </c>
-      <c r="E2" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E2" s="21" t="n"/>
       <c r="F2" s="23" t="inlineStr">
         <is>
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。</t>
@@ -6307,11 +6485,7 @@
           <t>El autobús lanzadera al mirador sale de la parada situada frente al estanque de nenúfares de la Casa Wada. La tarifa es de 300 yenes por trayecto y se paga en efectivo al bajar. Los niños de primaria pagan la mitad, los niños pequeños viajan gratis si no ocupan asiento y las personas con certificado de discapacidad pagan la mitad. No se admiten mascotas. De subida, funciona de 9:00 a 11:40 por la mañana y de 13:20 a 15:40 por la tarde. De bajada, de 9:10 a 12:10 por la mañana y de 13:30 a 16:10 por la tarde. En todos los casos, sale cada 20 minutos.</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E3" s="21" t="n"/>
       <c r="F3" s="23" t="inlineStr">
         <is>
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。</t>
@@ -6344,11 +6518,7 @@
           <t>La navette pour l'observatoire part de l'arrêt situé devant le bassin aux nénuphars de la maison Wada. Le tarif est de 300 yens l'aller simple, à régler en espèces à la descente. Les élèves de l'école primaire paient demi-tarif, les jeunes enfants voyagent gratuitement s'ils n'occupent pas de siège, et les titulaires d'un certificat de handicap paient demi-tarif. Les animaux ne sont pas admis à bord. À la montée, la navette circule de 9 h à 11 h 40 le matin et de 13 h 20 à 15 h 40 l'après-midi. À la descente, elle circule de 9 h 10 à 12 h 10 le matin et de 13 h 30 à 16 h 10 l'après-midi. Dans tous les cas, il y a un départ toutes les 20 minutes.</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E4" s="21" t="n"/>
       <c r="F4" s="23" t="inlineStr">
         <is>
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。</t>
@@ -6380,11 +6550,7 @@
           <t>전망대행 셔틀버스는 와다 가옥의 수련 연못 앞 승차장에서 출발합니다. 요금은 편도 300엔이며, 내리실 때 현금으로 지불해 주세요. 초등학생은 반값, 유아는 좌석을 사용하지 않는 경우 무료, 장애인 수첩을 소지하신 분은 반값입니다. 반려동물은 탑승할 수 없습니다. 올라가는 편은 오전 9시부터 11시 40분까지, 오후는 1시 20분부터 3시 40분까지 운행합니다. 내려오는 편은 오전 9시 10분부터 12시 10분까지, 오후는 1시 30분부터 4시 10분까지 운행합니다. 모두 20분 간격으로 운행하고 있습니다.</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E5" s="21" t="n"/>
       <c r="F5" s="23" t="inlineStr">
         <is>
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。</t>
@@ -6417,11 +6583,7 @@
           <t>前往观景台的接驳巴士从和田家睡莲池前的乘车处发车。车费单程300日元，请在下车时以现金支付。小学生半价，幼儿不占座位免费，持有残疾人证的乘客半价。宠物不可乘车。上山方向：上午9点至11点40分，下午1点20分至3点40分。下山方向：上午9点10分至12点10分，下午1点30分至4点10分。均为每20分钟一班。</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E6" s="24" t="n"/>
       <c r="F6" s="26" t="inlineStr">
         <is>
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。</t>
@@ -6453,11 +6615,7 @@
           <t>There is only one taxi company in the village, and because it operates the shuttle buses, taxis are usually not available. You can use a taxi only if you call the taxi company directly and are able to make a reservation. To get around the village, please use the local route buses.</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E7" s="27" t="n"/>
       <c r="F7" s="29" t="inlineStr">
         <is>
           <t>村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。</t>
@@ -6489,11 +6647,7 @@
           <t>En el pueblo solo hay una compañía de taxis y, como se encarga del servicio de autobús lanzadera, normalmente no está disponible. Solo podrá utilizarlo si llama directamente a la compañía de taxis y consigue una reserva. Para desplazarse dentro del pueblo, utilice el autobús de línea.</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E8" s="27" t="n"/>
       <c r="F8" s="29" t="inlineStr">
         <is>
           <t>村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。</t>
@@ -6525,11 +6679,7 @@
           <t>Il n'y a qu'une seule compagnie de taxi dans le village, et comme elle assure le service de la navette, elle n'est normalement pas disponible. Vous pouvez l'utiliser uniquement si vous appelez directement la compagnie de taxi et obtenez une réservation. Pour vous déplacer dans le village, veuillez utiliser les bus de ligne.</t>
         </is>
       </c>
-      <c r="E9" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E9" s="27" t="n"/>
       <c r="F9" s="29" t="inlineStr">
         <is>
           <t>村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。</t>
@@ -6561,11 +6711,7 @@
           <t>마을 안의 택시 회사는 1곳뿐이며, 셔틀버스를 운행하고 있어 평소에는 이용하실 수 없습니다. 택시 회사에 직접 전화하셔서 예약이 된 경우에만 이용하실 수 있습니다. 마을 안에서 이동하실 때는 노선버스를 이용해 주세요.</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E10" s="27" t="n"/>
       <c r="F10" s="29" t="inlineStr">
         <is>
           <t>村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。</t>
@@ -6597,11 +6743,7 @@
           <t>村内只有一家出租车公司，由于该公司负责运营接驳巴士，通常无法使用出租车。请直接致电出租车公司，只有在预约成功的情况下才能乘坐。村内移动请乘坐路线巴士。</t>
         </is>
       </c>
-      <c r="E11" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E11" s="30" t="n"/>
       <c r="F11" s="32" t="inlineStr">
         <is>
           <t>村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。</t>
@@ -6633,11 +6775,7 @@
           <t>The shuttle bus to Terao Parking Lot leaves from the same place where you got off. There is no fixed timetable and buses run continuously, so please wait at the place where you got off.</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E12" s="21" t="n"/>
       <c r="F12" s="23" t="inlineStr">
         <is>
           <t>寺尾駐車場行きのシャトルバスは、降りた場所と同じ乗降場所です。時刻は決まっておらず、随時運行しておりますので、降りた場所でお待ちください。</t>
@@ -6670,11 +6808,7 @@
           <t>El autobús lanzadera al Estacionamiento de Terao sale del mismo lugar donde usted se bajó. No tiene horario fijo y circula de forma continua, así que espere en el lugar donde se bajó.</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E13" s="21" t="n"/>
       <c r="F13" s="23" t="inlineStr">
         <is>
           <t>寺尾駐車場行きのシャトルバスは、降りた場所と同じ乗降場所です。時刻は決まっておらず、随時運行しておりますので、降りた場所でお待ちください。</t>
@@ -6707,11 +6841,7 @@
           <t>La navette pour le parking de Terao part du même arrêt que celui où vous êtes descendu. Il n'y a pas d'horaire fixe, elle circule en continu : veuillez l'attendre à l'endroit où vous êtes descendu.</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E14" s="21" t="n"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t>寺尾駐車場行きのシャトルバスは、降りた場所と同じ乗降場所です。時刻は決まっておらず、随時運行しておりますので、降りた場所でお待ちください。</t>
@@ -6743,11 +6873,7 @@
           <t>데라오 주차장행 셔틀버스는 내리신 곳과 같은 승하차장에서 타십니다. 정해진 시간표 없이 수시로 운행하고 있으니, 내리신 곳에서 기다려 주세요.</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E15" s="21" t="n"/>
       <c r="F15" s="23" t="inlineStr">
         <is>
           <t>寺尾駐車場行きのシャトルバスは、降りた場所と同じ乗降場所です。時刻は決まっておらず、随時運行しておりますので、降りた場所でお待ちください。</t>
@@ -6779,11 +6905,7 @@
           <t>前往寺尾停车场的接驳巴士，与您下车的地方是同一个上下车点。没有固定时刻，随时发车，请在您下车的地方等候。</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E16" s="24" t="n"/>
       <c r="F16" s="26" t="inlineStr">
         <is>
           <t>寺尾駐車場行きのシャトルバスは、降りた場所と同じ乗降場所です。時刻は決まっておらず、随時運行しておりますので、降りた場所でお待ちください。</t>
@@ -6815,11 +6937,7 @@
           <t>The shuttle bus to Terao Parking Lot does not use the same stop as the bus to the observatory. It runs continuously, with no fixed timetable, from Seseragi Park Parking Lot. Please wait at the place where you got off on your way here.</t>
         </is>
       </c>
-      <c r="E17" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E17" s="27" t="n"/>
       <c r="F17" s="29" t="inlineStr">
         <is>
           <t>寺尾駐車場行きのシャトルバスは、展望台行き乗降場所とは異なります。せせらぎ公園駐車場からダイヤを定めず、随時運行しております。往路で降車された場所でお待ちください。</t>
@@ -6852,11 +6970,7 @@
           <t>El autobús lanzadera al Estacionamiento de Terao no sale del mismo lugar que el autobús al mirador. Circula de forma continua, sin horario fijo, desde el Estacionamiento del Parque Seseragi. Espere en el lugar donde se bajó a la ida.</t>
         </is>
       </c>
-      <c r="E18" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E18" s="27" t="n"/>
       <c r="F18" s="29" t="inlineStr">
         <is>
           <t>寺尾駐車場行きのシャトルバスは、展望台行き乗降場所とは異なります。せせらぎ公園駐車場からダイヤを定めず、随時運行しております。往路で降車された場所でお待ちください。</t>
@@ -6889,11 +7003,7 @@
           <t>L'arrêt de la navette pour le parking de Terao est différent de celui de la navette pour l'observatoire. Elle part du parking du parc Seseragi, sans horaire fixe, et circule en continu. Veuillez l'attendre à l'endroit où vous êtes descendu à l'aller.</t>
         </is>
       </c>
-      <c r="E19" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E19" s="27" t="n"/>
       <c r="F19" s="29" t="inlineStr">
         <is>
           <t>寺尾駐車場行きのシャトルバスは、展望台行き乗降場所とは異なります。せせらぎ公園駐車場からダイヤを定めず、随時運行しております。往路で降車された場所でお待ちください。</t>
@@ -6925,11 +7035,7 @@
           <t>데라오 주차장행 셔틀버스는 전망대행 승하차장과 다릅니다. 세세라기 공원 주차장에서 정해진 시간표 없이 수시로 운행하고 있습니다. 오실 때 내리신 곳에서 기다려 주세요.</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E20" s="27" t="n"/>
       <c r="F20" s="29" t="inlineStr">
         <is>
           <t>寺尾駐車場行きのシャトルバスは、展望台行き乗降場所とは異なります。せせらぎ公園駐車場からダイヤを定めず、随時運行しております。往路で降車された場所でお待ちください。</t>
@@ -6961,11 +7067,7 @@
           <t>前往寺尾停车场的接驳巴士，与前往观景台的上下车点不同。从Seseragi公园停车场出发，不设固定班次，随时发车。请在去程下车的地方等候。</t>
         </is>
       </c>
-      <c r="E21" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E21" s="30" t="n"/>
       <c r="F21" s="32" t="inlineStr">
         <is>
           <t>寺尾駐車場行きのシャトルバスは、展望台行き乗降場所とは異なります。せせらぎ公園駐車場からダイヤを定めず、随時運行しております。往路で降車された場所でお待ちください。</t>
@@ -6998,11 +7100,7 @@
           <t>Cards issued outside Japan can only be used at the post office ATM. It is about a 20-minute walk: leave this building and turn right. Cards issued in Japan can be used at the JA ATM. It is about a 2-minute walk: leave this building and turn left.</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E22" s="21" t="n"/>
       <c r="F22" s="23" t="inlineStr">
         <is>
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
@@ -7035,11 +7133,7 @@
           <t>Las tarjetas emitidas en el extranjero solo pueden usarse en el cajero automático de la oficina de correos. Está a unos 20 minutos a pie: salga de este edificio y gire a la derecha. Las tarjetas emitidas en Japón pueden usarse en el cajero automático de JA. Está a unos 2 minutos a pie: salga de este edificio y gire a la izquierda.</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E23" s="21" t="n"/>
       <c r="F23" s="23" t="inlineStr">
         <is>
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
@@ -7072,11 +7166,7 @@
           <t>Les cartes émises à l'étranger ne peuvent être utilisées qu'au distributeur du bureau de poste. Il se trouve à environ 20 minutes à pied : en sortant de ce bâtiment, tournez à droite. Les cartes émises au Japon peuvent être utilisées au distributeur de la JA. Il se trouve à environ 2 minutes à pied : en sortant de ce bâtiment, tournez à gauche.</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E24" s="21" t="n"/>
       <c r="F24" s="23" t="inlineStr">
         <is>
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
@@ -7109,11 +7199,7 @@
           <t>해외에서 발급된 카드는 우체국 ATM에서만 이용하실 수 있습니다. 이 건물을 나가서 오른쪽으로 걸어서 20분 정도 거리에 있습니다. 일본에서 발급된 카드는 JA ATM을 이용하실 수 있습니다. 이 건물을 나가서 왼쪽으로 걸어서 2분 정도 거리에 있습니다.</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E25" s="21" t="n"/>
       <c r="F25" s="23" t="inlineStr">
         <is>
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
@@ -7146,11 +7232,7 @@
           <t>海外发行的银行卡只能在邮局的ATM使用。出了这栋建筑向右，步行约20分钟即可到达。日本国内发行的银行卡可以使用JA（日本农业协同组合）的ATM。出了这栋建筑向左，步行约2分钟即可到达。</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E26" s="24" t="n"/>
       <c r="F26" s="26" t="inlineStr">
         <is>
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
@@ -7183,11 +7265,7 @@
           <t>Credit cards issued outside Japan can only be used at the post office ATM. It seems that some cards cannot be used. Please use Hatogaya Post Office, about 5 minutes by car from here. Cash cards and credit cards issued in Japan can be used at the JA ATM. It is in front of Wada House, across from the stop for the shuttle bus to the observatory.</t>
         </is>
       </c>
-      <c r="E27" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E27" s="27" t="n"/>
       <c r="F27" s="29" t="inlineStr">
         <is>
           <t>海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はここから車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
@@ -7220,11 +7298,7 @@
           <t>Las tarjetas de crédito emitidas en el extranjero solo pueden usarse en el cajero automático de la oficina de correos. Al parecer, algunas tarjetas no se pueden utilizar. Utilice la Oficina de Correos de Hatogaya, a unos 5 minutos en coche desde aquí. Las tarjetas bancarias y de crédito emitidas en Japón pueden usarse en el cajero automático de JA, que está delante de la Casa Wada, enfrente de la parada del autobús lanzadera al mirador.</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E28" s="27" t="n"/>
       <c r="F28" s="29" t="inlineStr">
         <is>
           <t>海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はここから車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
@@ -7257,11 +7331,7 @@
           <t>Les cartes de crédit émises à l'étranger ne peuvent être utilisées qu'au distributeur du bureau de poste. Il semble que certaines cartes ne soient pas acceptées. Veuillez vous rendre au bureau de poste de Hatogaya, à environ 5 minutes en voiture d'ici. Les cartes bancaires et cartes de crédit émises au Japon peuvent être utilisées au distributeur de la JA. Il se trouve devant la maison Wada, en face de l'arrêt de la navette pour l'observatoire.</t>
         </is>
       </c>
-      <c r="E29" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E29" s="27" t="n"/>
       <c r="F29" s="29" t="inlineStr">
         <is>
           <t>海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はここから車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
@@ -7294,11 +7364,7 @@
           <t>해외에서 발급된 신용카드는 우체국 ATM에서만 이용하실 수 있습니다. 일부 이용할 수 없는 카드도 있는 것 같습니다. 우체국은 여기서 차로 5분 정도 거리에 있는 하토가야 우체국을 이용해 주세요. 일본에서 발급된 현금카드나 신용카드는 JA ATM을 이용하실 수 있습니다. 와다 가옥 앞, 전망대행 셔틀버스 승차장 맞은편에 있습니다.</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E30" s="27" t="n"/>
       <c r="F30" s="29" t="inlineStr">
         <is>
           <t>海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はここから車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
@@ -7331,11 +7397,7 @@
           <t>海外发行的信用卡只能在邮局的ATM使用，部分银行卡可能无法使用。邮局请前往距此开车约5分钟的鸠谷邮局。日本国内发行的现金卡和信用卡可以使用JA（日本农业协同组合）的ATM，位于和田家前、前往观景台的接驳巴士乘车处对面。</t>
         </is>
       </c>
-      <c r="E31" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E31" s="30" t="n"/>
       <c r="F31" s="32" t="inlineStr">
         <is>
           <t>海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はここから車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
@@ -7368,11 +7430,7 @@
           <t>To return by bus, please take the bus you reserved or an express bus departing today. Same-day tickets can be purchased at the counter.</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E32" s="21" t="n"/>
       <c r="F32" s="23" t="inlineStr">
         <is>
           <t>バスを利用したお帰りの際は予約したバス。または当日の高速バスを利用しておかえりください。窓口にて当日券をお買い求めできます。</t>
@@ -7404,11 +7462,7 @@
           <t>Para regresar en autobús, tome el autobús que haya reservado o un autobús expreso del mismo día. En el mostrador puede comprar billetes para el mismo día.</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E33" s="21" t="n"/>
       <c r="F33" s="23" t="inlineStr">
         <is>
           <t>バスを利用したお帰りの際は予約したバス。または当日の高速バスを利用しておかえりください。窓口にて当日券をお買い求めできます。</t>
@@ -7440,11 +7494,7 @@
           <t>Pour votre retour en bus, veuillez prendre le bus que vous avez réservé, ou un bus express du jour même. Vous pouvez acheter des billets pour le jour même au guichet.</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E34" s="21" t="n"/>
       <c r="F34" s="23" t="inlineStr">
         <is>
           <t>バスを利用したお帰りの際は予約したバス。または当日の高速バスを利用しておかえりください。窓口にて当日券をお買い求めできます。</t>
@@ -7476,11 +7526,7 @@
           <t>버스로 돌아가실 때는 예약하신 버스, 또는 당일 고속버스를 이용해 주세요. 당일 승차권은 창구에서 구입하실 수 있습니다.</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E35" s="21" t="n"/>
       <c r="F35" s="23" t="inlineStr">
         <is>
           <t>バスを利用したお帰りの際は予約したバス。または当日の高速バスを利用しておかえりください。窓口にて当日券をお買い求めできます。</t>
@@ -7512,11 +7558,7 @@
           <t>乘坐巴士返程时，请搭乘您已预约的巴士，或当天的高速巴士。当天的车票可以在窗口购买。</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E36" s="24" t="n"/>
       <c r="F36" s="26" t="inlineStr">
         <is>
           <t>バスを利用したお帰りの際は予約したバス。または当日の高速バスを利用しておかえりください。窓口にて当日券をお買い求めできます。</t>
@@ -7549,11 +7591,7 @@
           <t>To exchange foreign currency, please use the exchange machine near the restrooms. If you need coins for the coin lockers, we can change money for you at the counter.</t>
         </is>
       </c>
-      <c r="E37" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E37" s="27" t="n"/>
       <c r="F37" s="29" t="inlineStr">
         <is>
           <t>外貨の両替は、お手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
@@ -7586,11 +7624,7 @@
           <t>Para cambiar moneda extranjera, utilice la máquina de cambio que está cerca de los baños. En el mostrador cambiamos billetes por monedas para usar en las taquillas.</t>
         </is>
       </c>
-      <c r="E38" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E38" s="27" t="n"/>
       <c r="F38" s="29" t="inlineStr">
         <is>
           <t>外貨の両替は、お手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
@@ -7623,11 +7657,7 @@
           <t>Pour changer des devises étrangères, veuillez utiliser la machine de change située près des toilettes. Pour obtenir de la monnaie à utiliser dans les consignes automatiques, adressez-vous au guichet.</t>
         </is>
       </c>
-      <c r="E39" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E39" s="27" t="n"/>
       <c r="F39" s="29" t="inlineStr">
         <is>
           <t>外貨の両替は、お手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
@@ -7660,11 +7690,7 @@
           <t>외화 환전은 화장실 근처에 있는 환전기를 이용해 주세요. 코인로커에서 사용하실 동전으로 바꾸는 것은 창구에서 해 드립니다.</t>
         </is>
       </c>
-      <c r="E40" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E40" s="27" t="n"/>
       <c r="F40" s="29" t="inlineStr">
         <is>
           <t>外貨の両替は、お手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
@@ -7696,11 +7722,7 @@
           <t>外币兑换请使用洗手间附近的外币兑换机。如需兑换投币储物柜使用的零钱，请到窗口办理。</t>
         </is>
       </c>
-      <c r="E41" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E41" s="30" t="n"/>
       <c r="F41" s="32" t="inlineStr">
         <is>
           <t>外貨の両替は、お手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
@@ -7733,11 +7755,7 @@
           <t>To exchange foreign currency, please use the exchange machine at the Tourist Association in Shirakawa-go Bus Terminal. It accepts banknotes only. If you need coins for the coin lockers, we can change Japanese yen banknotes into Japanese yen coins at the counter.</t>
         </is>
       </c>
-      <c r="E42" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E42" s="21" t="n"/>
       <c r="F42" s="23" t="inlineStr">
         <is>
           <t>紙幣のみ対応ですが、外貨両替は観光協会バスターミナルにある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
@@ -7770,11 +7788,7 @@
           <t>Para cambiar moneda extranjera, utilice la máquina de cambio de la Asociación de Turismo en la Terminal de Autobuses; solo admite billetes. En el mostrador cambiamos billetes de yenes japoneses por monedas de yenes para usar en las taquillas.</t>
         </is>
       </c>
-      <c r="E43" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E43" s="21" t="n"/>
       <c r="F43" s="23" t="inlineStr">
         <is>
           <t>紙幣のみ対応ですが、外貨両替は観光協会バスターミナルにある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
@@ -7807,11 +7821,7 @@
           <t>Pour changer des devises étrangères, veuillez utiliser la machine de change du terminal de bus de Shirakawa-go, au bureau de l'Association touristique ; elle n'accepte que les billets. Pour changer des billets en yens contre des pièces en yens à utiliser dans les consignes automatiques, adressez-vous au guichet.</t>
         </is>
       </c>
-      <c r="E44" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E44" s="21" t="n"/>
       <c r="F44" s="23" t="inlineStr">
         <is>
           <t>紙幣のみ対応ですが、外貨両替は観光協会バスターミナルにある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
@@ -7844,11 +7854,7 @@
           <t>외화 환전은 지폐만 가능하며, 시라카와고 버스터미널의 관광협회에 있는 환전기를 이용해 주세요. 코인로커에서 사용하실 일본 엔 지폐를 일본 엔 동전으로 바꾸는 것은 창구에서 해 드립니다.</t>
         </is>
       </c>
-      <c r="E45" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E45" s="21" t="n"/>
       <c r="F45" s="23" t="inlineStr">
         <is>
           <t>紙幣のみ対応ですが、外貨両替は観光協会バスターミナルにある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
@@ -7880,11 +7886,7 @@
           <t>外币兑换请使用观光协会白川乡巴士总站内的兑换机，仅限纸币。如需将日元纸币兑换成储物柜使用的日元硬币，请到窗口办理。</t>
         </is>
       </c>
-      <c r="E46" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E46" s="24" t="n"/>
       <c r="F46" s="26" t="inlineStr">
         <is>
           <t>紙幣のみ対応ですが、外貨両替は観光協会バスターミナルにある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
@@ -7917,11 +7919,7 @@
           <t>There are coin lockers here. Lockers without a key are in use. If they are full, a nearby home also keeps luggage. If both are full, please ask at the counter and we will keep your luggage temporarily.</t>
         </is>
       </c>
-      <c r="E47" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E47" s="27" t="n"/>
       <c r="F47" s="29" t="inlineStr">
         <is>
           <t>コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、窓口で臨時にお預かりしますのでお声がけください。</t>
@@ -7954,11 +7952,7 @@
           <t>Hay taquillas que funcionan con monedas. Las que no tienen llave están en uso. Si están todas ocupadas, algunas casas particulares cercanas también guardan equipaje. Si ambas opciones están completas, consúltenos en el mostrador y le guardaremos el equipaje temporalmente.</t>
         </is>
       </c>
-      <c r="E48" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E48" s="27" t="n"/>
       <c r="F48" s="29" t="inlineStr">
         <is>
           <t>コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、窓口で臨時にお預かりしますのでお声がけください。</t>
@@ -7991,11 +7985,7 @@
           <t>Des consignes automatiques sont à votre disposition. Celles qui n'ont pas de clé sont déjà utilisées. Si elles sont toutes pleines, des maisons voisines gardent également les bagages. Si tout est complet, nous pouvons garder vos bagages temporairement au guichet : n'hésitez pas à nous le demander.</t>
         </is>
       </c>
-      <c r="E49" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E49" s="27" t="n"/>
       <c r="F49" s="29" t="inlineStr">
         <is>
           <t>コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、窓口で臨時にお預かりしますのでお声がけください。</t>
@@ -8028,11 +8018,7 @@
           <t>코인로커가 있습니다. 열쇠가 꽂혀 있지 않은 로커는 사용 중입니다. 로커가 가득 찬 경우에는 근처 가정에서도 짐을 맡아 드리고 있습니다. 두 곳 모두 가득 찬 경우에는 창구에서 임시로 보관해 드리니 말씀해 주세요.</t>
         </is>
       </c>
-      <c r="E50" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E50" s="27" t="n"/>
       <c r="F50" s="29" t="inlineStr">
         <is>
           <t>コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、窓口で臨時にお預かりしますのでお声がけください。</t>
@@ -8065,11 +8051,7 @@
           <t>这里有投币储物柜。没有插钥匙的柜子表示正在使用中。如果储物柜已满，附近的住户也提供行李寄存服务。如果都满了，窗口可以临时为您保管，请告诉工作人员。</t>
         </is>
       </c>
-      <c r="E51" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E51" s="30" t="n"/>
       <c r="F51" s="32" t="inlineStr">
         <is>
           <t>コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、窓口で臨時にお預かりしますのでお声がけください。</t>
@@ -8102,11 +8084,7 @@
           <t>There are no coin lockers at this parking lot or nearby. There are coin lockers at the Bus Terminal.</t>
         </is>
       </c>
-      <c r="E52" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E52" s="21" t="n"/>
       <c r="F52" s="23" t="inlineStr">
         <is>
           <t>この駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
@@ -8139,11 +8117,7 @@
           <t>No hay taquillas de monedas en este estacionamiento ni en los alrededores. Sí las hay en la Terminal de Autobuses.</t>
         </is>
       </c>
-      <c r="E53" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E53" s="21" t="n"/>
       <c r="F53" s="23" t="inlineStr">
         <is>
           <t>この駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
@@ -8176,11 +8150,7 @@
           <t>Il n'y a pas de consignes automatiques sur ce parking ni aux alentours. Il y en a au terminal de bus.</t>
         </is>
       </c>
-      <c r="E54" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E54" s="21" t="n"/>
       <c r="F54" s="23" t="inlineStr">
         <is>
           <t>この駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
@@ -8213,11 +8183,7 @@
           <t>이 주차장과 주변에는 코인로커가 없습니다. 버스터미널에는 있습니다.</t>
         </is>
       </c>
-      <c r="E55" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E55" s="21" t="n"/>
       <c r="F55" s="23" t="inlineStr">
         <is>
           <t>この駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
@@ -8250,11 +8216,7 @@
           <t>这个停车场及附近没有投币储物柜。巴士总站有储物柜。</t>
         </is>
       </c>
-      <c r="E56" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E56" s="24" t="n"/>
       <c r="F56" s="26" t="inlineStr">
         <is>
           <t>この駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
@@ -8287,11 +8249,7 @@
           <t>Please pay the parking fee at the payment machine when you leave. There are no parking tickets. You can pay in cash, including 10,000-yen bills, as well as by credit card, QR code payment, or transit IC card.</t>
         </is>
       </c>
-      <c r="E57" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E57" s="27" t="n"/>
       <c r="F57" s="29" t="inlineStr">
         <is>
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。</t>
@@ -8324,11 +8282,7 @@
           <t>Pague la tarifa del estacionamiento en la máquina de pago al salir. No hay tique de estacionamiento. Se acepta efectivo, incluidos los billetes de 10000 yenes, así como tarjetas de crédito, pagos con código QR y tarjetas IC de transporte.</t>
         </is>
       </c>
-      <c r="E58" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E58" s="27" t="n"/>
       <c r="F58" s="29" t="inlineStr">
         <is>
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。</t>
@@ -8361,11 +8315,7 @@
           <t>Veuillez régler les frais de stationnement à la machine de paiement en sortant du parking. Il n'y a pas de ticket de stationnement. Vous pouvez payer en espèces, y compris avec des billets de 10 000 yens, mais aussi par carte de crédit, par paiement QR code ou avec une carte de transport IC.</t>
         </is>
       </c>
-      <c r="E59" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E59" s="27" t="n"/>
       <c r="F59" s="29" t="inlineStr">
         <is>
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。</t>
@@ -8398,11 +8348,7 @@
           <t>주차장 이용 요금은 출차하실 때 정산기에서 지불해 주세요. 참고로 주차권은 없습니다. 1만 엔 지폐 등 현금은 물론, 신용카드, QR코드 결제, 교통계 IC카드도 이용하실 수 있습니다.</t>
         </is>
       </c>
-      <c r="E60" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E60" s="27" t="n"/>
       <c r="F60" s="29" t="inlineStr">
         <is>
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。</t>
@@ -8434,11 +8380,7 @@
           <t>停车费请在出场时于自动缴费机支付。停车场不发停车券。除1万日元纸币等现金外，还可以使用信用卡、二维码支付和交通IC卡。</t>
         </is>
       </c>
-      <c r="E61" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E61" s="30" t="n"/>
       <c r="F61" s="32" t="inlineStr">
         <is>
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。</t>
@@ -8470,11 +8412,7 @@
           <t>Souvenir stamps are available on the table. Postage stamps are sold at the counter. We do not offer goshuin temple and shrine seals.</t>
         </is>
       </c>
-      <c r="E62" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E62" s="21" t="n"/>
       <c r="F62" s="23" t="inlineStr">
         <is>
           <t>スタンプは机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
@@ -8507,11 +8445,7 @@
           <t>Los sellos de recuerdo están sobre la mesa. Los sellos postales se venden en el mostrador. No ofrecemos goshuin.</t>
         </is>
       </c>
-      <c r="E63" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E63" s="21" t="n"/>
       <c r="F63" s="23" t="inlineStr">
         <is>
           <t>スタンプは机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
@@ -8544,11 +8478,7 @@
           <t>Les tampons sont à votre disposition sur la table. Les timbres sont vendus au guichet. Nous ne proposons pas de goshuin.</t>
         </is>
       </c>
-      <c r="E64" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E64" s="21" t="n"/>
       <c r="F64" s="23" t="inlineStr">
         <is>
           <t>スタンプは机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
@@ -8581,11 +8511,7 @@
           <t>스탬프는 책상 위에 준비되어 있습니다. 우표는 창구에서 취급하고 있습니다. 고슈인은 해 드리지 않습니다.</t>
         </is>
       </c>
-      <c r="E65" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E65" s="21" t="n"/>
       <c r="F65" s="23" t="inlineStr">
         <is>
           <t>スタンプは机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
@@ -8617,11 +8543,7 @@
           <t>纪念印章放在桌子上。邮票可以在窗口购买。本处不提供御朱印。</t>
         </is>
       </c>
-      <c r="E66" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E66" s="24" t="n"/>
       <c r="F66" s="26" t="inlineStr">
         <is>
           <t>スタンプは机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
@@ -8653,11 +8575,7 @@
           <t>Souvenir stamps are available on the table at the counter. We do not sell postage stamps or offer goshuin temple and shrine seals.</t>
         </is>
       </c>
-      <c r="E67" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E67" s="27" t="n"/>
       <c r="F67" s="29" t="inlineStr">
         <is>
           <t>記念スタンプは窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
@@ -8690,11 +8608,7 @@
           <t>Los sellos de recuerdo están sobre la mesa del mostrador. No vendemos sellos postales ni ofrecemos goshuin.</t>
         </is>
       </c>
-      <c r="E68" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E68" s="27" t="n"/>
       <c r="F68" s="29" t="inlineStr">
         <is>
           <t>記念スタンプは窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
@@ -8727,11 +8641,7 @@
           <t>Le tampon souvenir est à votre disposition sur la table du guichet. Nous ne vendons pas de timbres et ne proposons pas de goshuin.</t>
         </is>
       </c>
-      <c r="E69" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E69" s="27" t="n"/>
       <c r="F69" s="29" t="inlineStr">
         <is>
           <t>記念スタンプは窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
@@ -8764,11 +8674,7 @@
           <t>기념 스탬프는 창구 책상 위에 준비되어 있습니다. 우표와 고슈인은 취급하지 않습니다.</t>
         </is>
       </c>
-      <c r="E70" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E70" s="27" t="n"/>
       <c r="F70" s="29" t="inlineStr">
         <is>
           <t>記念スタンプは窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
@@ -8800,11 +8706,7 @@
           <t>纪念印章放在窗口的桌子上。本处不出售邮票，也不提供御朱印。</t>
         </is>
       </c>
-      <c r="E71" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E71" s="30" t="n"/>
       <c r="F71" s="32" t="inlineStr">
         <is>
           <t>記念スタンプは窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
@@ -8837,11 +8739,7 @@
           <t>There is no fee to enter the village, but part of the parking fee is used to preserve the gassho-style village. When you enter the facilities open to visitors inside the village, please pay each admission fee on site. Each facility is operated separately, and there is no ticket like a free pass.</t>
         </is>
       </c>
-      <c r="E72" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E72" s="21" t="n"/>
       <c r="F72" s="23" t="inlineStr">
         <is>
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。</t>
@@ -8874,11 +8772,7 @@
           <t>No es necesario pagar entrada para acceder al pueblo, pero parte de la tarifa de estacionamiento se destina a la conservación de la aldea de casas gassho-zukuri. Para entrar en las instalaciones visitables de la aldea, se paga la entrada de cada una en el mismo lugar. Cada instalación funciona de forma independiente y no existe ningún pase libre que sirva para todas.</t>
         </is>
       </c>
-      <c r="E73" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E73" s="21" t="n"/>
       <c r="F73" s="23" t="inlineStr">
         <is>
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。</t>
@@ -8911,11 +8805,7 @@
           <t>Il n'y a pas de droit d'entrée à payer pour le village, mais une partie des frais de stationnement sert à la préservation du village aux maisons gassho. Pour visiter les maisons ouvertes au public dans le village, vous payez le droit d'entrée de chacune sur place. Chaque maison est gérée séparément, et il n'existe pas de billet combiné de type pass.</t>
         </is>
       </c>
-      <c r="E74" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E74" s="21" t="n"/>
       <c r="F74" s="23" t="inlineStr">
         <is>
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。</t>
@@ -8948,11 +8838,7 @@
           <t>입촌료를 내실 필요는 없지만, 주차 요금의 일부는 갓쇼 마을 보전에 쓰이고 있습니다. 또한 갓쇼 마을 안의 관람 시설에 들어가실 때는 각 시설의 입장료를 현장에서 지불해 주셔야 합니다. 시설은 각각 따로 운영되고 있으며, 프리패스 같은 티켓은 없습니다.</t>
         </is>
       </c>
-      <c r="E75" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E75" s="21" t="n"/>
       <c r="F75" s="23" t="inlineStr">
         <is>
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。</t>
@@ -8985,11 +8871,7 @@
           <t>不需要支付入村费，但停车费的一部分会用于保护合掌造村落。另外，参观村落内的参观设施时，需要在各设施现场分别支付门票。各设施独立经营，没有通票之类的票券。</t>
         </is>
       </c>
-      <c r="E76" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E76" s="24" t="n"/>
       <c r="F76" s="26" t="inlineStr">
         <is>
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。</t>
@@ -9022,11 +8904,7 @@
           <t>The mountains you can see in front of you include Mt. Sanpoiwa, Mt. Noyashoji, and Mt. Inobuse. From the observatory, you can also see a little of Mt. Hakusan.</t>
         </is>
       </c>
-      <c r="E77" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E77" s="27" t="n"/>
       <c r="F77" s="29" t="inlineStr">
         <is>
           <t>正面に見えるのは三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
@@ -9059,11 +8937,7 @@
           <t>Las montañas que se ven de frente son el monte Sanpoiwa, el monte Noyashoji y el monte Inobuse, entre otras. Desde el mirador también se puede ver un poco el monte Hakusan.</t>
         </is>
       </c>
-      <c r="E78" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E78" s="27" t="n"/>
       <c r="F78" s="29" t="inlineStr">
         <is>
           <t>正面に見えるのは三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
@@ -9096,11 +8970,7 @@
           <t>Les montagnes que vous voyez en face sont notamment le mont Sanpoiwa, le mont Noyashoji et le mont Inobuse. Depuis l'observatoire, on peut aussi apercevoir un peu le mont Hakusan.</t>
         </is>
       </c>
-      <c r="E79" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E79" s="27" t="n"/>
       <c r="F79" s="29" t="inlineStr">
         <is>
           <t>正面に見えるのは三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
@@ -9133,11 +9003,7 @@
           <t>정면에 보이는 산은 산포이와산, 노야쇼지산, 이노부세산 등입니다. 전망대에서는 하쿠산도 조금 보실 수 있습니다.</t>
         </is>
       </c>
-      <c r="E80" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E80" s="27" t="n"/>
       <c r="F80" s="29" t="inlineStr">
         <is>
           <t>正面に見えるのは三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
@@ -9170,11 +9036,7 @@
           <t>正前方看到的是三方岩岳、野谷庄司山、猪卧山等。从观景台还可以稍微看到白山。</t>
         </is>
       </c>
-      <c r="E81" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E81" s="30" t="n"/>
       <c r="F81" s="32" t="inlineStr">
         <is>
           <t>正面に見えるのは三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
@@ -9207,11 +9069,7 @@
           <t>There are 2 ways to get to the observatory: on foot or by shuttle bus. To take the walking path, leave this building and go left for about 2 minutes, then turn left at a restaurant called Shiramizuen. Walk on with Wada House on your right, and at the end of the road there is a path going up to the left. It takes about 20 minutes to get there. To take the mountain trail, leave this building and go right. Just after you enter Route 360, climb the stairs and you will reach the Castle Ruins Observatory. To take the shuttle bus, leave this building and go left for about 2 minutes, and get on at the bus stop in front of the water-lily pond at Wada House.</t>
         </is>
       </c>
-      <c r="E82" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E82" s="21" t="n"/>
       <c r="F82" s="23" t="inlineStr">
         <is>
           <t>展望台へは、歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る道があり、およそ20分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
@@ -9244,11 +9102,7 @@
           <t>Puede ir al mirador a pie o en el autobús lanzadera. Si va por el sendero, salga de este edificio, gire a la izquierda, camine unos 2 minutos y gire a la izquierda en el restaurante Shiramizuen. Siga adelante con la Casa Wada a su derecha; al final encontrará un camino que sube hacia la izquierda y llegará en unos 20 minutos. Si prefiere el camino de montaña, salga de este edificio, vaya hacia la derecha, entre en la Ruta 360 y suba las escaleras que encontrará enseguida; así llegará al Mirador de las Ruinas del Castillo. Si va en autobús lanzadera, salga de este edificio, gire a la izquierda y, a unos 2 minutos, suba en la parada frente al estanque de nenúfares de la Casa Wada.</t>
         </is>
       </c>
-      <c r="E83" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E83" s="21" t="n"/>
       <c r="F83" s="23" t="inlineStr">
         <is>
           <t>展望台へは、歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る道があり、およそ20分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
@@ -9281,11 +9135,7 @@
           <t>Pour aller à l'observatoire, il y a deux possibilités : à pied ou en navette. Si vous prenez le sentier de promenade, sortez de ce bâtiment, tournez à gauche et marchez environ 2 minutes, puis tournez à gauche au restaurant Shiramizuen. Continuez en laissant la maison Wada sur votre droite ; au bout, un chemin monte sur la gauche, et vous arriverez en 20 minutes environ. Si vous prenez le sentier de montagne, sortez de ce bâtiment, tournez à droite, et juste après être entré sur la route 360, montez l'escalier : vous arriverez à l'observatoire des ruines du château. Pour la navette, sortez de ce bâtiment, tournez à gauche, et prenez-la à l'arrêt situé à environ 2 minutes, devant le bassin aux nénuphars de la maison Wada.</t>
         </is>
       </c>
-      <c r="E84" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E84" s="21" t="n"/>
       <c r="F84" s="23" t="inlineStr">
         <is>
           <t>展望台へは、歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る道があり、およそ20分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
@@ -9318,11 +9168,7 @@
           <t>전망대까지는 걸어가는 방법과 셔틀버스를 타는 방법, 2가지가 있습니다. 산책로로 걸어가실 경우, 이 건물을 나가서 왼쪽으로 2분 정도 가신 뒤, 시라미즈엔이라는 음식점에서 왼쪽으로 도세요. 와다 가옥을 오른쪽에 두고 나아가면 막다른 곳에 왼쪽으로 올라가는 길이 있으며, 약 20분이면 도착합니다. 산길로 걸어가실 경우, 이 건물을 나가서 오른쪽으로 가신 뒤 국도 360호선에 들어서자마자 나오는 계단을 오르면 성터 전망대에 도착합니다. 셔틀버스를 이용하실 경우, 이 건물을 나가서 왼쪽으로 2분 정도 거리에 있는 와다 가옥 수련 연못 앞 버스 정류장에서 타 주세요.</t>
         </is>
       </c>
-      <c r="E85" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E85" s="21" t="n"/>
       <c r="F85" s="23" t="inlineStr">
         <is>
           <t>展望台へは、歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る道があり、およそ20分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
@@ -9355,11 +9201,7 @@
           <t>前往观景台有步行和乘坐接驳巴士两种方式。走游步道的话，出了这栋建筑向左走约2分钟，在一家叫白水园的餐厅处左转。经过右手边的和田家继续向前，尽头有一条向左上坡的路，大约20分钟可以到达。走山路的话，出了这栋建筑向右走，进入360号国道后立即登上台阶，即可到达城迹观景台。乘坐接驳巴士的话，请出了这栋建筑向左走约2分钟，在和田家睡莲池前的巴士站上车。</t>
         </is>
       </c>
-      <c r="E86" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E86" s="24" t="n"/>
       <c r="F86" s="26" t="inlineStr">
         <is>
           <t>展望台へは、歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る道があり、およそ20分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
@@ -9392,11 +9234,7 @@
           <t>The paid shuttle bus is a convenient way to get to the observatory. Cross the bridge right in front of this building, go out to the main street, and walk left for about 10 minutes. There is a bus stop in front of Wada House. Please take the shuttle bus from there. There is also a route you can walk up along the foot of the mountain, which takes about 30 to 40 minutes from here.</t>
         </is>
       </c>
-      <c r="E87" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E87" s="27" t="n"/>
       <c r="F87" s="29" t="inlineStr">
         <is>
           <t>展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできるルートもあり、ここから30～40分ほどで行くことができます。</t>
@@ -9429,11 +9267,7 @@
           <t>Para ir al mirador, lo más práctico es el autobús lanzadera de pago. Cruce el puente que está justo delante de este edificio, salga a la calle principal y gire a la izquierda; a unos 10 minutos encontrará la parada delante de la Casa Wada. Suba allí al autobús lanzadera. También hay una ruta a pie que sube por la falda de la montaña, y desde aquí se tarda unos 30 a 40 minutos.</t>
         </is>
       </c>
-      <c r="E88" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E88" s="27" t="n"/>
       <c r="F88" s="29" t="inlineStr">
         <is>
           <t>展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできるルートもあり、ここから30～40分ほどで行くことができます。</t>
@@ -9466,11 +9300,7 @@
           <t>Pour aller à l'observatoire, la navette payante est pratique. Traversez le pont juste en face de ce bâtiment, rejoignez la rue principale et marchez environ 10 minutes vers la gauche : l'arrêt se trouve devant la maison Wada. Prenez la navette à cet arrêt. Il existe aussi un itinéraire à pied qui monte le long du pied de la montagne ; il faut compter 30 à 40 minutes depuis ici.</t>
         </is>
       </c>
-      <c r="E89" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E89" s="27" t="n"/>
       <c r="F89" s="29" t="inlineStr">
         <is>
           <t>展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできるルートもあり、ここから30～40分ほどで行くことができます。</t>
@@ -9503,11 +9333,7 @@
           <t>전망대까지는 유료 셔틀버스가 편리합니다. 이 건물 바로 앞의 다리를 건너 큰길로 나가서 왼쪽으로 10분 정도 가시면 와다 가옥 앞에 버스 정류장이 있습니다. 그곳에서 셔틀버스를 타 주세요. 또는 산자락을 따라 걸어서 올라가는 길도 있으며, 여기서 30분에서 40분 정도면 가실 수 있습니다.</t>
         </is>
       </c>
-      <c r="E90" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E90" s="27" t="n"/>
       <c r="F90" s="29" t="inlineStr">
         <is>
           <t>展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできるルートもあり、ここから30～40分ほどで行くことができます。</t>
@@ -9540,11 +9366,7 @@
           <t>前往观景台，乘坐收费的接驳巴士比较方便。过这栋建筑正前方的桥，走到大路后向左走约10分钟，和田家前面就是巴士站，请在那里乘坐接驳巴士。另外也有沿着山边步行上山的路线，从这里出发约30到40分钟可以到达。</t>
         </is>
       </c>
-      <c r="E91" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E91" s="30" t="n"/>
       <c r="F91" s="32" t="inlineStr">
         <is>
           <t>展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできるルートもあり、ここから30～40分ほどで行くことができます。</t>
@@ -9577,11 +9399,7 @@
           <t>This is a very small village, so you can walk around it. You can see the whole village in 2 to 3 hours, including a meal. Places marked with the eye symbol on the map are facilities open to visitors.</t>
         </is>
       </c>
-      <c r="E92" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E92" s="21" t="n"/>
       <c r="F92" s="23" t="inlineStr">
         <is>
           <t>とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。</t>
@@ -9614,11 +9432,7 @@
           <t>Es una aldea muy pequeña, así que puede recorrerla a pie. Incluyendo la comida, puede verla entera en 2 o 3 horas. Los lugares marcados con el símbolo del ojo en el mapa son las instalaciones visitables.</t>
         </is>
       </c>
-      <c r="E93" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E93" s="21" t="n"/>
       <c r="F93" s="23" t="inlineStr">
         <is>
           <t>とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。</t>
@@ -9651,11 +9465,7 @@
           <t>Le village est très petit, vous pouvez donc le visiter à pied. En comptant un repas, 2 à 3 heures suffisent pour tout voir. Les lieux marqués du symbole de l'œil sur la carte sont les maisons ouvertes à la visite.</t>
         </is>
       </c>
-      <c r="E94" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E94" s="21" t="n"/>
       <c r="F94" s="23" t="inlineStr">
         <is>
           <t>とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。</t>
@@ -9688,11 +9498,7 @@
           <t>아주 작은 마을이라 걸어서 둘러보실 수 있습니다. 식사 시간을 포함해도 2시간에서 3시간이면 전체를 보실 수 있습니다. 눈 모양 표시가 있는 곳이 관람 시설입니다.</t>
         </is>
       </c>
-      <c r="E95" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E95" s="21" t="n"/>
       <c r="F95" s="23" t="inlineStr">
         <is>
           <t>とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。</t>
@@ -9725,11 +9531,7 @@
           <t>这是一个很小的村落，可以步行游览。包括用餐在内，2到3个小时就可以看完全部。地图上标有眼睛标志的地方是参观设施。</t>
         </is>
       </c>
-      <c r="E96" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E96" s="24" t="n"/>
       <c r="F96" s="26" t="inlineStr">
         <is>
           <t>とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。</t>
@@ -9762,11 +9564,7 @@
           <t>Shiramizu Falls and Shiramizu Lake can only be reached by private car. Please note that the road may be closed or restricted due to heavy rain. For details, please see SHIRAKAWA-Going.</t>
         </is>
       </c>
-      <c r="E97" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E97" s="27" t="n"/>
       <c r="F97" s="29" t="inlineStr">
         <is>
           <t>白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
@@ -9799,11 +9597,7 @@
           <t>A la cascada Shiramizu y al lago Shiramizu solo se puede llegar en vehículo propio. Tenga en cuenta también que puede haber restricciones de tráfico por lluvias intensas. Para más información, consulte SHIRAKAWA-Going.</t>
         </is>
       </c>
-      <c r="E98" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E98" s="27" t="n"/>
       <c r="F98" s="29" t="inlineStr">
         <is>
           <t>白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
@@ -9836,11 +9630,7 @@
           <t>Les chutes de Shiramizu et le lac Shiramizu ne sont accessibles qu'en voiture particulière. Attention, la circulation peut être restreinte en cas de fortes pluies. Pour plus de détails, veuillez consulter SHIRAKAWA-Going.</t>
         </is>
       </c>
-      <c r="E99" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E99" s="27" t="n"/>
       <c r="F99" s="29" t="inlineStr">
         <is>
           <t>白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
@@ -9873,11 +9663,7 @@
           <t>시라미즈 폭포와 시라미즈 호수는 자가용이 아니면 가실 수 없습니다. 또한 폭우로 통행이 제한되는 경우가 있으니 주의해 주세요. 자세한 내용은 시라카와 고잉을 확인해 주세요.</t>
         </is>
       </c>
-      <c r="E100" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E100" s="27" t="n"/>
       <c r="F100" s="29" t="inlineStr">
         <is>
           <t>白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
@@ -9909,11 +9695,7 @@
           <t>白水瀑布和白水湖只能自驾前往。另外，因暴雨有时会实施通行限制，请注意。详情请查看SHIRAKAWA-Going。</t>
         </is>
       </c>
-      <c r="E101" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E101" s="30" t="n"/>
       <c r="F101" s="32" t="inlineStr">
         <is>
           <t>白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
@@ -9946,11 +9728,7 @@
           <t>We do not have halal meals. For vegetarians, there are meat-free dishes such as hoba miso, which is miso grilled on a magnolia leaf, iwana char dishes, and tofu dishes.</t>
         </is>
       </c>
-      <c r="E102" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E102" s="21" t="n"/>
       <c r="F102" s="23" t="inlineStr">
         <is>
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。</t>
@@ -9983,11 +9761,7 @@
           <t>No ofrecemos comida halal. Para las personas vegetarianas hay hoba miso sin carne, platos de trucha iwana y platos de tofu.</t>
         </is>
       </c>
-      <c r="E103" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E103" s="21" t="n"/>
       <c r="F103" s="23" t="inlineStr">
         <is>
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。</t>
@@ -10020,11 +9794,7 @@
           <t>Nous ne proposons pas de repas halal. Pour les végétariens, il existe des plats sans viande : le hoba miso, du miso grillé sur une feuille de magnolia, des plats de poisson iwana et des plats de tofu.</t>
         </is>
       </c>
-      <c r="E104" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E104" s="21" t="n"/>
       <c r="F104" s="23" t="inlineStr">
         <is>
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。</t>
@@ -10057,11 +9827,7 @@
           <t>할랄 대응 식사는 준비되어 있지 않습니다. 채식을 하시는 분께는 고기를 사용하지 않은 호바 미소, 곤들매기 요리, 두부 요리가 있습니다.</t>
         </is>
       </c>
-      <c r="E105" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E105" s="21" t="n"/>
       <c r="F105" s="23" t="inlineStr">
         <is>
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。</t>
@@ -10094,11 +9860,7 @@
           <t>本村没有提供清真餐食。素食者可以选择不使用肉类的朴叶味噌（放在朴树叶上烤的味噌）、岩鱼料理和豆腐料理。</t>
         </is>
       </c>
-      <c r="E106" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E106" s="24" t="n"/>
       <c r="F106" s="26" t="inlineStr">
         <is>
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。</t>
@@ -10131,11 +9893,7 @@
           <t>The local specialty is the hoba miso set meal, which is miso grilled on a magnolia leaf. There are also dishes with Hida beef, mountain vegetables, iwana char, rainbow trout, and ishi-dofu, a firm tofu.</t>
         </is>
       </c>
-      <c r="E107" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E107" s="27" t="n"/>
       <c r="F107" s="29" t="inlineStr">
         <is>
           <t>郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。</t>
@@ -10168,11 +9926,7 @@
           <t>El plato típico de la zona es el menú de hoba miso, miso asado sobre hoja de magnolia. También hay platos de carne de res de Hida, verduras de montaña, trucha iwana, trucha arcoíris e ishi-dofu, un tofu muy firme.</t>
         </is>
       </c>
-      <c r="E108" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E108" s="27" t="n"/>
       <c r="F108" s="29" t="inlineStr">
         <is>
           <t>郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。</t>
@@ -10205,11 +9959,7 @@
           <t>La spécialité locale est le menu hoba miso, du miso grillé sur une feuille de magnolia. Il y a aussi des plats de bœuf de Hida, de légumes de montagne, de poisson iwana, de truite arc-en-ciel et de ishi-dofu, un tofu ferme.</t>
         </is>
       </c>
-      <c r="E109" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E109" s="27" t="n"/>
       <c r="F109" s="29" t="inlineStr">
         <is>
           <t>郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。</t>
@@ -10242,11 +9992,7 @@
           <t>향토 요리는 호바 미소 정식입니다. 히다규, 산나물, 곤들매기, 무지개송어, 이시도후 요리도 있습니다.</t>
         </is>
       </c>
-      <c r="E110" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E110" s="27" t="n"/>
       <c r="F110" s="29" t="inlineStr">
         <is>
           <t>郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。</t>
@@ -10279,11 +10025,7 @@
           <t>当地的乡土料理是朴叶味噌（放在朴树叶上烤的味噌）套餐。另外还有飞驒牛、山野菜、岩鱼、虹鳟和石豆腐（质地结实的豆腐）等料理。</t>
         </is>
       </c>
-      <c r="E111" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E111" s="30" t="n"/>
       <c r="F111" s="32" t="inlineStr">
         <is>
           <t>郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。</t>
@@ -10316,11 +10058,7 @@
           <t>There are 2 parking spaces for people with physical disabilities inside Shirakawa-go Bus Terminal. Priority is given to people with a disability certificate, people who have reserved a wheelchair, and people with limited mobility, for example those bringing their own wheelchair. The spaces can be used from 8:00 a.m. to 5:00 p.m. The parking fee is 2000 yen per car, and there is no disability discount. To use them, please come directly to the Tourist Association counter inside Shirakawa-go Bus Terminal. Because there are only a few spaces, we may have to turn you away if they are full.</t>
         </is>
       </c>
-      <c r="E112" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E112" s="21" t="n"/>
       <c r="F112" s="23" t="inlineStr">
         <is>
           <t>身体障害者用の駐車スペースは、白川郷バスターミナル内に2台ございます。障害者手帳をお持ちの方、車椅子をご予約の方、または持参されるなど足の不自由な方を優先しております。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。ご利用の際は、白川郷バスターミナル内の観光協会窓口へ直接お越しください。スペースが少ないため、満車の場合はお断りすることがございます。</t>
@@ -10353,11 +10091,7 @@
           <t>En la Terminal de Autobuses de Shirakawa-go hay 2 plazas de estacionamiento para personas con discapacidad física. Tienen prioridad las personas con certificado de discapacidad, quienes hayan reservado una silla de ruedas o traigan la suya, y otras personas con movilidad reducida. Se pueden usar de 8:00 a 17:00, la tarifa es de 2000 yenes por vehículo y no hay descuento por discapacidad. Para utilizarlas, diríjase directamente al mostrador de la Asociación de Turismo, dentro de la Terminal de Autobuses de Shirakawa-go. Como hay pocas plazas, si están ocupadas es posible que no podamos atenderle.</t>
         </is>
       </c>
-      <c r="E113" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E113" s="21" t="n"/>
       <c r="F113" s="23" t="inlineStr">
         <is>
           <t>身体障害者用の駐車スペースは、白川郷バスターミナル内に2台ございます。障害者手帳をお持ちの方、車椅子をご予約の方、または持参されるなど足の不自由な方を優先しております。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。ご利用の際は、白川郷バスターミナル内の観光協会窓口へ直接お越しください。スペースが少ないため、満車の場合はお断りすることがございます。</t>
@@ -10390,11 +10124,7 @@
           <t>Il y a 2 places de stationnement pour personnes handicapées au terminal de bus de Shirakawa-go. Elles sont réservées en priorité aux titulaires d'un certificat de handicap, aux personnes ayant réservé un fauteuil roulant ou apportant le leur, et aux personnes à mobilité réduite. Elles sont utilisables de 8 h à 17 h, au tarif de 2000 yens par véhicule, sans réduction pour les personnes handicapées. Pour les utiliser, veuillez vous adresser directement au guichet de l'Association touristique, dans le terminal de bus de Shirakawa-go. Le nombre de places étant limité, nous pourrions devoir refuser votre demande si elles sont toutes occupées.</t>
         </is>
       </c>
-      <c r="E114" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E114" s="21" t="n"/>
       <c r="F114" s="23" t="inlineStr">
         <is>
           <t>身体障害者用の駐車スペースは、白川郷バスターミナル内に2台ございます。障害者手帳をお持ちの方、車椅子をご予約の方、または持参されるなど足の不自由な方を優先しております。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。ご利用の際は、白川郷バスターミナル内の観光協会窓口へ直接お越しください。スペースが少ないため、満車の場合はお断りすることがございます。</t>
@@ -10426,11 +10156,7 @@
           <t>신체장애인용 주차 공간은 시라카와고 버스터미널 안에 2대분 있습니다. 장애인 수첩을 소지하신 분, 휠체어를 예약하신 분, 또는 휠체어를 직접 가져오신 분 등 다리가 불편하신 분을 우선으로 하고 있습니다. 이용 시간은 오전 8시부터 오후 5시까지이며, 주차 요금은 1대당 2000엔이고 장애인 할인은 없습니다. 이용하실 때는 시라카와고 버스터미널 안의 관광협회 창구로 직접 와 주세요. 공간이 적기 때문에 만차일 경우에는 이용을 거절할 수 있습니다.</t>
         </is>
       </c>
-      <c r="E115" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E115" s="21" t="n"/>
       <c r="F115" s="23" t="inlineStr">
         <is>
           <t>身体障害者用の駐車スペースは、白川郷バスターミナル内に2台ございます。障害者手帳をお持ちの方、車椅子をご予約の方、または持参されるなど足の不自由な方を優先しております。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。ご利用の際は、白川郷バスターミナル内の観光協会窓口へ直接お越しください。スペースが少ないため、満車の場合はお断りすることがございます。</t>
@@ -10462,11 +10188,7 @@
           <t>白川乡巴士总站内有2个残疾人专用停车位。优先提供给持有残疾人证的人士，以及预约了轮椅或自带轮椅等行动不便的人士。使用时间为上午8点至下午5点，停车费每辆2000日元，没有残疾人折扣。使用时请直接前往白川乡巴士总站内的观光协会窗口。车位较少，停满时可能无法接待，敬请谅解。</t>
         </is>
       </c>
-      <c r="E116" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E116" s="24" t="n"/>
       <c r="F116" s="26" t="inlineStr">
         <is>
           <t>身体障害者用の駐車スペースは、白川郷バスターミナル内に2台ございます。障害者手帳をお持ちの方、車椅子をご予約の方、または持参されるなど足の不自由な方を優先しております。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。ご利用の際は、白川郷バスターミナル内の観光協会窓口へ直接お越しください。スペースが少ないため、満車の場合はお断りすることがございます。</t>
@@ -10499,11 +10221,7 @@
           <t>There are 5 parking spaces for wheelchair users with physical disabilities in Seseragi Park Parking Lot. Priority is given to people who have reserved a wheelchair and people with limited mobility, for example those bringing their own wheelchair. The spaces can be used from 8:00 a.m. to 5:00 p.m. The parking fee is 2000 yen per car, and there is no disability discount. Wheelchair rental is available at the counter on the 1st floor of Deai-no-Yakata, but the number of wheelchairs is limited. Also, we may have to turn you away if the parking spaces are full.</t>
         </is>
       </c>
-      <c r="E117" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E117" s="27" t="n"/>
       <c r="F117" s="29" t="inlineStr">
         <is>
           <t>身体障害者車いす用駐車スペースは、せせらぎ公園駐車場内に５台ございます。車椅子をご予約の方、または持参されるなど足の不自由な方を優先しております。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。車いすはであいの館１階窓口で貸し出しのご案内をしておりますが台数に限りがあります。また駐車スペースも満車の場合はお断りすることがございます。</t>
@@ -10536,11 +10254,7 @@
           <t>En el Estacionamiento del Parque Seseragi hay 5 plazas de estacionamiento para personas con discapacidad física en silla de ruedas. Tienen prioridad quienes hayan reservado una silla de ruedas o traigan la suya, y otras personas con movilidad reducida. Se pueden usar de 8:00 a 17:00, la tarifa es de 2000 yenes por vehículo y no hay descuento por discapacidad. En el mostrador de la planta baja de Deai-no-Yakata informamos sobre el préstamo de sillas de ruedas, pero hay un número limitado. Además, si las plazas de estacionamiento están ocupadas, es posible que no podamos atenderle.</t>
         </is>
       </c>
-      <c r="E118" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E118" s="27" t="n"/>
       <c r="F118" s="29" t="inlineStr">
         <is>
           <t>身体障害者車いす用駐車スペースは、せせらぎ公園駐車場内に５台ございます。車椅子をご予約の方、または持参されるなど足の不自由な方を優先しております。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。車いすはであいの館１階窓口で貸し出しのご案内をしておりますが台数に限りがあります。また駐車スペースも満車の場合はお断りすることがございます。</t>
@@ -10573,11 +10287,7 @@
           <t>Il y a 5 places de stationnement pour personnes handicapées en fauteuil roulant au parking du parc Seseragi. Elles sont réservées en priorité aux personnes ayant réservé un fauteuil roulant ou apportant le leur, et aux personnes à mobilité réduite. Elles sont utilisables de 8 h à 17 h, au tarif de 2000 yens par véhicule, sans réduction pour les personnes handicapées. Le prêt de fauteuils roulants se fait au guichet du rez-de-chaussée du Deai-no-Yakata, mais leur nombre est limité. Si les places de stationnement sont toutes occupées, nous pourrions également devoir refuser votre demande.</t>
         </is>
       </c>
-      <c r="E119" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E119" s="27" t="n"/>
       <c r="F119" s="29" t="inlineStr">
         <is>
           <t>身体障害者車いす用駐車スペースは、せせらぎ公園駐車場内に５台ございます。車椅子をご予約の方、または持参されるなど足の不自由な方を優先しております。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。車いすはであいの館１階窓口で貸し出しのご案内をしておりますが台数に限りがあります。また駐車スペースも満車の場合はお断りすることがございます。</t>
@@ -10609,11 +10319,7 @@
           <t>신체장애인 휠체어용 주차 공간은 세세라기 공원 주차장 안에 5대분 있습니다. 휠체어를 예약하신 분, 또는 휠체어를 직접 가져오신 분 등 다리가 불편하신 분을 우선으로 하고 있습니다. 이용 시간은 오전 8시부터 오후 5시까지이며, 주차 요금은 1대당 2000엔이고 장애인 할인은 없습니다. 휠체어는 데아이노야카타 1층 창구에서 대여 안내를 하고 있지만, 대수가 한정되어 있습니다. 또한 주차 공간도 만차일 경우에는 이용을 거절할 수 있습니다.</t>
         </is>
       </c>
-      <c r="E120" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E120" s="27" t="n"/>
       <c r="F120" s="29" t="inlineStr">
         <is>
           <t>身体障害者車いす用駐車スペースは、せせらぎ公園駐車場内に５台ございます。車椅子をご予約の方、または持参されるなど足の不自由な方を優先しております。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。車いすはであいの館１階窓口で貸し出しのご案内をしておりますが台数に限りがあります。また駐車スペースも満車の場合はお断りすることがございます。</t>
@@ -10645,11 +10351,7 @@
           <t>Seseragi公园停车场内有5个残疾人轮椅专用停车位。优先提供给预约了轮椅或自带轮椅等行动不便的人士。使用时间为上午8点至下午5点，停车费每辆2000日元，没有残疾人折扣。Deai-no-Yakata（出会之馆）1楼窗口提供轮椅租借咨询，但数量有限。另外，停车位停满时也可能无法接待，敬请谅解。</t>
         </is>
       </c>
-      <c r="E121" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E121" s="30" t="n"/>
       <c r="F121" s="32" t="inlineStr">
         <is>
           <t>身体障害者車いす用駐車スペースは、せせらぎ公園駐車場内に５台ございます。車椅子をご予約の方、または持参されるなど足の不自由な方を優先しております。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。車いすはであいの館１階窓口で貸し出しのご案内をしておりますが台数に限りがあります。また駐車スペースも満車の場合はお断りすることがございます。</t>
@@ -10681,11 +10383,7 @@
           <t>We have 2 wheelchairs at Shirakawa-go Bus Terminal and 2 at Seseragi Park Parking Lot. They are available on a first-come, first-served basis, so please ask at either information center. At Seseragi Park Parking Lot, wheelchairs are lent from 9:30 a.m. to 3:30 p.m. During the winter season, from November to the end of March, we do not lend wheelchairs for safety reasons. Please note that the village has many gravel paths and uneven steps and is not a fully accessible tourist facility, so please take care when moving around.</t>
         </is>
       </c>
-      <c r="E122" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E122" s="21" t="n"/>
       <c r="F122" s="23" t="inlineStr">
         <is>
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。</t>
@@ -10717,11 +10415,7 @@
           <t>Tenemos sillas de ruedas: 2 en la Terminal de Autobuses de Shirakawa-go y 2 en el Estacionamiento del Parque Seseragi. Se prestan por orden de llegada, así que pregunte en cualquiera de los centros de información. En el Estacionamiento del Parque Seseragi, el préstamo es de 9:30 a 15:30. Durante el invierno, de noviembre a finales de marzo, no se prestan por motivos de seguridad. Tenga en cuenta que en el pueblo hay muchos caminos de grava y desniveles, y que no es una instalación turística acondicionada, así que tenga cuidado al desplazarse.</t>
         </is>
       </c>
-      <c r="E123" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E123" s="21" t="n"/>
       <c r="F123" s="23" t="inlineStr">
         <is>
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。</t>
@@ -10753,11 +10447,7 @@
           <t>Nous disposons de 2 fauteuils roulants au terminal de bus de Shirakawa-go et de 2 au parking du parc Seseragi. Ils sont prêtés dans l'ordre d'arrivée : adressez-vous au point d'information concerné. Au parking du parc Seseragi, le prêt se fait de 9 h 30 à 15 h 30. Pendant la période hivernale, de novembre à fin mars, il n'y a pas de prêt, pour des raisons de sécurité. Veuillez noter que le village comporte de nombreux chemins de gravier et marches, et qu'il ne s'agit pas d'un site touristique aménagé : soyez prudent lors de vos déplacements.</t>
         </is>
       </c>
-      <c r="E124" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E124" s="21" t="n"/>
       <c r="F124" s="23" t="inlineStr">
         <is>
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。</t>
@@ -10790,11 +10480,7 @@
           <t>휠체어는 시라카와고 버스터미널에 2대, 세세라기 공원 주차장에 2대 준비되어 있습니다. 선착순이므로 각 안내소에 말씀해 주세요. 세세라기 공원 주차장에서의 대여는 오전 9시 30분부터 오후 3시 30분까지입니다. 11월부터 3월 말까지의 겨울철에는 안전을 위해 대여하지 않습니다. 또한 마을 안은 자갈길과 단차가 많고 정비된 관광 시설이 아니므로, 이동하실 때 주의해 주세요.</t>
         </is>
       </c>
-      <c r="E125" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E125" s="21" t="n"/>
       <c r="F125" s="23" t="inlineStr">
         <is>
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。</t>
@@ -10826,11 +10512,7 @@
           <t>白川乡巴士总站和Seseragi公园停车场各备有2台轮椅。先到先得，请向各咨询处提出。Seseragi公园停车场的租借时间为上午9点30分至下午3点30分。11月至3月底的冬季期间，出于安全考虑不提供租借。另外，村内砂石路和台阶较多，并非经过整修的观光设施，移动时请多加小心。</t>
         </is>
       </c>
-      <c r="E126" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E126" s="24" t="n"/>
       <c r="F126" s="26" t="inlineStr">
         <is>
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。</t>
@@ -10862,11 +10544,7 @@
           <t>Please be careful of bears. If you encounter a bear, do not turn your back on it, and back away slowly. If you are attacked, lie face down on the ground and protect your head.</t>
         </is>
       </c>
-      <c r="E127" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E127" s="27" t="n"/>
       <c r="F127" s="29" t="inlineStr">
         <is>
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。
@@ -10899,11 +10577,7 @@
           <t>Tenga cuidado, pueden aparecer osos. Si se encuentra con un oso, retroceda despacio sin darle la espalda. Si llega a ser atacado, póngase boca abajo en el suelo y protéjase la cabeza.</t>
         </is>
       </c>
-      <c r="E128" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E128" s="27" t="n"/>
       <c r="F128" s="29" t="inlineStr">
         <is>
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。
@@ -10936,11 +10610,7 @@
           <t>Attention aux ours. Si vous rencontrez un ours, reculez lentement sans lui tourner le dos. Si vous êtes attaqué, couchez-vous face contre le sol et protégez votre tête.</t>
         </is>
       </c>
-      <c r="E129" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E129" s="27" t="n"/>
       <c r="F129" s="29" t="inlineStr">
         <is>
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。
@@ -10974,11 +10644,7 @@
           <t>곰 출몰에 주의해 주세요. 만약 곰을 만나게 되면 등을 보이지 말고 천천히 뒤로 물러나세요. 만약 공격을 당했을 때는 땅에 엎드려 머리를 보호하세요.</t>
         </is>
       </c>
-      <c r="E130" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E130" s="27" t="n"/>
       <c r="F130" s="29" t="inlineStr">
         <is>
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。
@@ -11011,11 +10677,7 @@
           <t>请注意熊出没。万一遇到熊，请不要背对它，慢慢向后退。万一遭到袭击，请趴在地上保护好头部。</t>
         </is>
       </c>
-      <c r="E131" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E131" s="30" t="n"/>
       <c r="F131" s="32" t="inlineStr">
         <is>
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。
@@ -11048,11 +10710,7 @@
           <t>Even with smokeless electronic cigarettes or heated tobacco products, smoking while walking and using them outside designated areas is prohibited. For heated tobacco, please use the smoking areas at Ogimachi Multipurpose Hall, Ogimachi Park, the Bus Terminal, and Seseragi Park Parking Lot.</t>
         </is>
       </c>
-      <c r="E132" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E132" s="21" t="n"/>
       <c r="F132" s="23" t="inlineStr">
         <is>
           <t>火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。</t>
@@ -11085,11 +10743,7 @@
           <t>Incluso los cigarrillos electrónicos y el tabaco calentado, que no usan fuego, están prohibidos mientras camina y fuera de los lugares designados. Para el tabaco calentado, utilice las zonas de fumadores del Salón Multiusos de Ogimachi, el Parque Ogimachi, la Terminal de Autobuses y el Estacionamiento del Parque Seseragi.</t>
         </is>
       </c>
-      <c r="E133" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E133" s="21" t="n"/>
       <c r="F133" s="23" t="inlineStr">
         <is>
           <t>火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。</t>
@@ -11122,11 +10776,7 @@
           <t>Même pour les cigarettes électroniques et le tabac chauffé, qui n'utilisent pas de flamme, il est interdit de fumer en marchant ou en dehors des emplacements prévus. Pour le tabac chauffé, veuillez utiliser les espaces fumeurs de la salle polyvalente d'Ogimachi, du parc d'Ogimachi, du terminal de bus et du parking du parc Seseragi.</t>
         </is>
       </c>
-      <c r="E134" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E134" s="21" t="n"/>
       <c r="F134" s="23" t="inlineStr">
         <is>
           <t>火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。</t>
@@ -11159,11 +10809,7 @@
           <t>불을 사용하지 않는 전자담배나 가열식 담배라도, 걸으면서 피우거나 지정된 장소 이외에서 사용하는 것은 금지되어 있습니다. 가열식 담배는 오기마치 다목적 집회시설, 오기마치 공원, 버스터미널, 세세라기 공원 주차장의 각 흡연 장소를 이용해 주세요.</t>
         </is>
       </c>
-      <c r="E135" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E135" s="21" t="n"/>
       <c r="F135" s="23" t="inlineStr">
         <is>
           <t>火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。</t>
@@ -11195,11 +10841,7 @@
           <t>即使是不用火的电子烟或加热烟，也禁止边走边吸或在指定地点以外使用。加热烟请在荻町多功能集会设施、荻町公园、巴士总站和Seseragi公园停车场的各吸烟处使用。</t>
         </is>
       </c>
-      <c r="E136" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E136" s="24" t="n"/>
       <c r="F136" s="26" t="inlineStr">
         <is>
           <t>火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。</t>
@@ -11232,11 +10874,7 @@
           <t>People live in this village. It is prohibited to enter private property to take photos or to photograph residents without permission. Because people live here, please do not speak loudly or make noise. Please enjoy your visit quietly.</t>
         </is>
       </c>
-      <c r="E137" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E137" s="27" t="n"/>
       <c r="F137" s="29" t="inlineStr">
         <is>
           <t>集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。</t>
@@ -11269,11 +10907,7 @@
           <t>La aldea es un lugar donde viven sus residentes. Está prohibido entrar en propiedades privadas para tomar fotografías y fotografiar a los residentes sin su permiso. Como es un lugar donde vive gente, no hable en voz alta ni haga ruido. Le pedimos que haga su visita en silencio.</t>
         </is>
       </c>
-      <c r="E138" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E138" s="27" t="n"/>
       <c r="F138" s="29" t="inlineStr">
         <is>
           <t>集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。</t>
@@ -11306,11 +10940,7 @@
           <t>Le village est un lieu où vivent des habitants. Il est interdit d'entrer sur une propriété privée pour prendre des photos, ou de photographier les habitants sans leur permission. Comme des gens y vivent, veuillez ne pas parler fort ni faire de bruit. Merci de visiter le village dans le calme.</t>
         </is>
       </c>
-      <c r="E139" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E139" s="27" t="n"/>
       <c r="F139" s="29" t="inlineStr">
         <is>
           <t>集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。</t>
@@ -11343,11 +10973,7 @@
           <t>마을은 주민분들이 생활하고 계신 곳입니다. 사유지에 들어가서 촬영하거나 주민분들을 허락 없이 촬영하는 것은 금지되어 있습니다. 생활하시는 곳이므로 큰 소리를 내거나 떠드는 것은 삼가 주세요. 조용히 관광해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="E140" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E140" s="27" t="n"/>
       <c r="F140" s="29" t="inlineStr">
         <is>
           <t>集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。</t>
@@ -11380,11 +11006,7 @@
           <t>村落是居民生活的地方。禁止进入私人土地拍摄，也禁止未经允许拍摄居民。因为这里是居民生活的地方，请不要大声喧哗或吵闹，请安静地游览。</t>
         </is>
       </c>
-      <c r="E141" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E141" s="30" t="n"/>
       <c r="F141" s="32" t="inlineStr">
         <is>
           <t>集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。</t>
@@ -11417,11 +11039,7 @@
           <t>Gassho-style houses are very vulnerable to fire, so smoking anywhere other than designated areas, including while walking, is strictly prohibited. For regular cigarettes, please use the smoking areas at Shirakawa-go Bus Terminal and Seseragi Park Parking Lot. The smoking areas at Ogimachi Park and Ogimachi Multipurpose Hall are for heated tobacco only.</t>
         </is>
       </c>
-      <c r="E142" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E142" s="21" t="n"/>
       <c r="F142" s="23" t="inlineStr">
         <is>
           <t>合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。</t>
@@ -11454,11 +11072,7 @@
           <t>Las aldeas de casas gassho-zukuri son muy vulnerables al fuego, por lo que está terminantemente prohibido fumar fuera de los lugares designados, también mientras camina. Para los cigarrillos convencionales, utilice las zonas de fumadores de la Terminal de Autobuses de Shirakawa-go y del Estacionamiento del Parque Seseragi. Las zonas de fumadores del Parque Ogimachi y del Salón Multiusos de Ogimachi son solo para tabaco calentado.</t>
         </is>
       </c>
-      <c r="E143" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E143" s="21" t="n"/>
       <c r="F143" s="23" t="inlineStr">
         <is>
           <t>合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。</t>
@@ -11491,11 +11105,7 @@
           <t>Les maisons gassho sont extrêmement vulnérables au feu : il est donc strictement interdit de fumer en dehors des emplacements prévus, y compris en marchant. Pour les cigarettes classiques, veuillez utiliser les espaces fumeurs du terminal de bus de Shirakawa-go et du parking du parc Seseragi. Les espaces fumeurs du parc d'Ogimachi et de la salle polyvalente d'Ogimachi sont réservés au tabac chauffé.</t>
         </is>
       </c>
-      <c r="E144" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E144" s="21" t="n"/>
       <c r="F144" s="23" t="inlineStr">
         <is>
           <t>合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。</t>
@@ -11528,11 +11138,7 @@
           <t>갓쇼즈쿠리 마을은 화재에 매우 취약하기 때문에, 걸으면서 피우는 것을 포함해 지정된 장소 이외에서의 흡연은 엄격히 금지되어 있습니다. 궐련은 시라카와고 버스터미널과 세세라기 공원 주차장의 흡연 장소를 이용해 주세요. 오기마치 공원과 오기마치 다목적 집회시설의 흡연 장소는 가열식 담배 전용입니다.</t>
         </is>
       </c>
-      <c r="E145" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E145" s="21" t="n"/>
       <c r="F145" s="23" t="inlineStr">
         <is>
           <t>合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。</t>
@@ -11565,11 +11171,7 @@
           <t>合掌造村落非常容易发生火灾，因此严禁在指定地点以外吸烟，包括边走边吸。纸烟请在白川乡巴士总站和Seseragi公园停车场的吸烟处吸。荻町公园和荻町多功能集会设施的吸烟处仅限加热烟。</t>
         </is>
       </c>
-      <c r="E146" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E146" s="24" t="n"/>
       <c r="F146" s="26" t="inlineStr">
         <is>
           <t>合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。</t>
@@ -11602,11 +11204,7 @@
           <t>There is no place where you can play in the snow. Apart from the roads, all land in the village is private property. People live here, so please do not enter private property to play in the snow or make noise.</t>
         </is>
       </c>
-      <c r="E147" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E147" s="27" t="n"/>
       <c r="F147" s="29" t="inlineStr">
         <is>
           <t>雪遊びが出来る場所はありません。集落内は道路以外私有地です。住民の方が生活している場所ですので私有地に入って雪遊びをしたり騒がないで下さい。</t>
@@ -11638,11 +11236,7 @@
           <t>No hay ningún lugar donde se pueda jugar con la nieve. Dentro de la aldea, todo lo que no es carretera es propiedad privada. Es un lugar donde viven sus residentes, así que no entre en propiedades privadas para jugar con la nieve ni haga ruido.</t>
         </is>
       </c>
-      <c r="E148" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E148" s="27" t="n"/>
       <c r="F148" s="29" t="inlineStr">
         <is>
           <t>雪遊びが出来る場所はありません。集落内は道路以外私有地です。住民の方が生活している場所ですので私有地に入って雪遊びをしたり騒がないで下さい。</t>
@@ -11674,11 +11268,7 @@
           <t>Il n'y a pas d'endroit où jouer dans la neige. Dans le village, tout ce qui n'est pas la route est une propriété privée. Des habitants y vivent : veuillez ne pas entrer sur les propriétés privées pour jouer dans la neige et ne pas faire de bruit.</t>
         </is>
       </c>
-      <c r="E149" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E149" s="27" t="n"/>
       <c r="F149" s="29" t="inlineStr">
         <is>
           <t>雪遊びが出来る場所はありません。集落内は道路以外私有地です。住民の方が生活している場所ですので私有地に入って雪遊びをしたり騒がないで下さい。</t>
@@ -11711,11 +11301,7 @@
           <t>눈놀이를 할 수 있는 장소는 없습니다. 마을 안은 도로를 제외하면 모두 사유지입니다. 주민분들이 생활하고 계신 곳이므로 사유지에 들어가서 눈놀이를 하거나 떠들지 말아 주세요.</t>
         </is>
       </c>
-      <c r="E150" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E150" s="27" t="n"/>
       <c r="F150" s="29" t="inlineStr">
         <is>
           <t>雪遊びが出来る場所はありません。集落内は道路以外私有地です。住民の方が生活している場所ですので私有地に入って雪遊びをしたり騒がないで下さい。</t>
@@ -11747,11 +11333,7 @@
           <t>这里没有可以玩雪的地方。村落内除道路以外都是私人土地。这是居民生活的地方，请不要进入私人土地玩雪或吵闹。</t>
         </is>
       </c>
-      <c r="E151" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E151" s="30" t="n"/>
       <c r="F151" s="32" t="inlineStr">
         <is>
           <t>雪遊びが出来る場所はありません。集落内は道路以外私有地です。住民の方が生活している場所ですので私有地に入って雪遊びをしたり騒がないで下さい。</t>
@@ -11784,11 +11366,7 @@
           <t>There are no trash bins in Shirakawa Village. Please take your trash home with you.</t>
         </is>
       </c>
-      <c r="E152" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E152" s="21" t="n"/>
       <c r="F152" s="23" t="inlineStr">
         <is>
           <t>白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。</t>
@@ -11821,11 +11399,7 @@
           <t>En la aldea de Shirakawa no hay papeleras. Le agradecemos que se lleve su basura consigo.</t>
         </is>
       </c>
-      <c r="E153" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E153" s="21" t="n"/>
       <c r="F153" s="23" t="inlineStr">
         <is>
           <t>白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。</t>
@@ -11858,11 +11432,7 @@
           <t>Il n'y a pas de poubelles dans le village de Shirakawa. Merci de bien vouloir remporter vos déchets.</t>
         </is>
       </c>
-      <c r="E154" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E154" s="21" t="n"/>
       <c r="F154" s="23" t="inlineStr">
         <is>
           <t>白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。</t>
@@ -11894,11 +11464,7 @@
           <t>시라카와무라에는 쓰레기통을 설치하지 않았습니다. 쓰레기는 가지고 돌아가 주시도록 협조 부탁드립니다.</t>
         </is>
       </c>
-      <c r="E155" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E155" s="21" t="n"/>
       <c r="F155" s="23" t="inlineStr">
         <is>
           <t>白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。</t>
@@ -11930,11 +11496,7 @@
           <t>白川村没有设置垃圾桶。请配合将垃圾带走。</t>
         </is>
       </c>
-      <c r="E156" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E156" s="24" t="n"/>
       <c r="F156" s="26" t="inlineStr">
         <is>
           <t>白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。</t>
@@ -11967,11 +11529,7 @@
           <t>If you are looking for accommodation you can book for today, please call the accommodation directly. Minshuku guesthouses and similar places do not accept same-day reservations.</t>
         </is>
       </c>
-      <c r="E157" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E157" s="27" t="n"/>
       <c r="F157" s="29" t="inlineStr">
         <is>
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。</t>
@@ -12004,11 +11562,7 @@
           <t>Si busca un alojamiento que acepte reservas para el mismo día, llame directamente por teléfono. Los minshuku y otras casas de huéspedes similares no aceptan reservas para el mismo día.</t>
         </is>
       </c>
-      <c r="E158" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E158" s="27" t="n"/>
       <c r="F158" s="29" t="inlineStr">
         <is>
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。</t>
@@ -12041,11 +11595,7 @@
           <t>Si vous cherchez un hébergement à réserver le jour même, veuillez appeler directement les établissements. Les minshuku, ou chambres d'hôtes, n'acceptent pas les réservations le jour même.</t>
         </is>
       </c>
-      <c r="E159" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E159" s="27" t="n"/>
       <c r="F159" s="29" t="inlineStr">
         <is>
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。</t>
@@ -12078,11 +11628,7 @@
           <t>당일 예약이 가능한 숙소를 찾으실 때는 직접 전화해 주시기 바랍니다. 민박 등은 당일 예약을 받지 않습니다.</t>
         </is>
       </c>
-      <c r="E160" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E160" s="27" t="n"/>
       <c r="F160" s="29" t="inlineStr">
         <is>
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。</t>
@@ -12115,11 +11661,7 @@
           <t>如需寻找可当天预约的住宿，请直接打电话联系。民宿等不接受当天预约。</t>
         </is>
       </c>
-      <c r="E161" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E161" s="30" t="n"/>
       <c r="F161" s="32" t="inlineStr">
         <is>
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。</t>
@@ -12152,11 +11694,7 @@
           <t>Doburoku is served in the grounds of Shirakawa Hachiman Shrine from about 3:30 p.m. to about 5:00 p.m. To receive doburoku, first make an offering, called hatsuhoryo, at the reception in the shrine grounds and receive a special red commemorative sake cup. Take the cup and join the line, and you will be served special doburoku brewed at the shrine. You may have refills, but drinking is only allowed within the shrine grounds, and you cannot take any home.</t>
         </is>
       </c>
-      <c r="E162" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E162" s="21" t="n"/>
       <c r="F162" s="23" t="inlineStr">
         <is>
           <t>どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。</t>
@@ -12189,11 +11727,7 @@
           <t>El doburoku se reparte en el recinto del Santuario Hachiman de Shirakawa aproximadamente de 15:30 a 17:00. Para recibirlo, primero entregue la ofrenda, llamada hatsuhoryo, en la recepción del recinto y reciba la copa conmemorativa roja especial. Con esa copa, póngase en la fila y le servirán el doburoku especial elaborado en el santuario. Puede repetir, pero solo se puede consumir dentro del recinto y no se puede llevar.</t>
         </is>
       </c>
-      <c r="E163" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E163" s="21" t="n"/>
       <c r="F163" s="23" t="inlineStr">
         <is>
           <t>どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。</t>
@@ -12226,11 +11760,7 @@
           <t>La distribution de doburoku, un saké non filtré, a lieu dans l'enceinte du sanctuaire Shirakawa Hachiman, d'environ 15 h 30 à environ 17 h. Pour recevoir du doburoku, présentez d'abord une offrande, appelée hatsuhoryo, à l'accueil du sanctuaire, et recevez la coupe souvenir rouge prévue à cet effet. Faites ensuite la queue avec cette coupe, et l'on vous servira le doburoku spécial brassé par le sanctuaire. Vous pouvez vous resservir, mais il doit être consommé uniquement dans l'enceinte du sanctuaire et ne peut pas être emporté.</t>
         </is>
       </c>
-      <c r="E164" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E164" s="21" t="n"/>
       <c r="F164" s="23" t="inlineStr">
         <is>
           <t>どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。</t>
@@ -12263,11 +11793,7 @@
           <t>도부로쿠 나눔은 시라카와 하치만 신사 경내에서 오후 3시 30분쯤부터 오후 5시쯤까지 진행됩니다. 도부로쿠를 받으시려면 먼저 경내 접수처에서 봉납금인 하쓰호료를 내시고 전용 빨간 기념 잔을 받아 주세요. 그 잔을 들고 줄을 서시면 신사에서 빚은 특제 도부로쿠를 따라 드립니다. 더 받으실 수도 있지만, 경내에서만 드실 수 있으며 가지고 가실 수는 없습니다.</t>
         </is>
       </c>
-      <c r="E165" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E165" s="21" t="n"/>
       <c r="F165" s="23" t="inlineStr">
         <is>
           <t>どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。</t>
@@ -12300,11 +11826,7 @@
           <t>浊酒（doburoku）的免费分发在白川八幡神社院内进行，时间约为下午3点30分至下午5点。想要品尝浊酒，请先在院内的接待处缴纳供奉金（初穗料），领取专用的红色纪念酒杯。拿着酒杯排队，就会为您斟上神社酿造的特制浊酒。可以续杯，但仅限在神社院内饮用，不能带走。</t>
         </is>
       </c>
-      <c r="E166" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E166" s="24" t="n"/>
       <c r="F166" s="26" t="inlineStr">
         <is>
           <t>どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。</t>
@@ -12337,11 +11859,7 @@
           <t>The doburoku served in the shrine grounds is an offering shared from the gods, so taking it home in a flask, plastic bottle, or similar container is strictly prohibited. During the festival, if you make a donation of 2000 yen at the reception in the shrine grounds, you will receive 1 tokkuri, a sake flask. Bottled doburoku for souvenirs can be purchased at liquor stores and souvenir shops in the village. Doburoku has a high alcohol content, so please be careful not to drink too much. Anyone driving a car or riding a bicycle must never drink.</t>
         </is>
       </c>
-      <c r="E167" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E167" s="27" t="n"/>
       <c r="F167" s="29" t="inlineStr">
         <is>
           <t>境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。</t>
@@ -12374,11 +11892,7 @@
           <t>El doburoku que se sirve en el recinto es una ofrenda a los dioses que luego se comparte, por lo que está estrictamente prohibido llevárselo en cantimploras, botellas de plástico u otros recipientes. Durante el festival, si hace una donación de 2000 yenes en la recepción del recinto, recibirá 1 tokkuri, una jarrita de sake. El doburoku embotellado de recuerdo se puede comprar en las licorerías y tiendas de recuerdos del pueblo. Además, el doburoku tiene un contenido alcohólico alto, así que no beba en exceso. Si va a conducir un vehículo o una bicicleta, no beba en absoluto.</t>
         </is>
       </c>
-      <c r="E168" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E168" s="27" t="n"/>
       <c r="F168" s="29" t="inlineStr">
         <is>
           <t>境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。</t>
@@ -12411,11 +11925,7 @@
           <t>Le doburoku servi dans l'enceinte du sanctuaire est une offrande aux divinités que l'on partage ensuite : il est donc strictement interdit de l'emporter dans une gourde, une bouteille en plastique ou tout autre récipient. Pendant la période du festival, en faisant un don de 2000 yens à l'accueil du sanctuaire, vous recevez un tokkuri, un flacon à saké. Le doburoku en bouteille à rapporter en souvenir est en vente chez les marchands de saké et les boutiques de souvenirs du village. Le doburoku est un alcool fort : veillez à ne pas en boire trop. Si vous conduisez une voiture ou un vélo, ne buvez absolument pas d'alcool.</t>
         </is>
       </c>
-      <c r="E169" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E169" s="27" t="n"/>
       <c r="F169" s="29" t="inlineStr">
         <is>
           <t>境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。</t>
@@ -12448,11 +11958,7 @@
           <t>경내에서 나눠 드리는 도부로쿠는 신께 올린 공물을 물려받은 것이므로, 물병이나 페트병 등에 담아 가져가는 것은 엄격히 금지되어 있습니다. 축제 기간 중에는 경내 접수처에서 2000엔을 기부하시면 돗쿠리 술병을 1병 받으실 수 있습니다. 기념품용 병 도부로쿠는 마을 안의 주류 판매점이나 기념품 가게에서 구입하실 수 있습니다. 또한 도부로쿠는 알코올 도수가 높은 술이므로 과음하지 않도록 주의해 주세요. 자동차나 자전거를 운전하시는 분은 절대로 술을 드시지 마세요.</t>
         </is>
       </c>
-      <c r="E170" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E170" s="27" t="n"/>
       <c r="F170" s="29" t="inlineStr">
         <is>
           <t>境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。</t>
@@ -12484,11 +11990,7 @@
           <t>院内分发的浊酒是供奉给神明后撤下的供品，因此严禁装入水壶或塑料瓶等带走。节日期间，在院内接待处捐献2000日元，可以获得1个德利（酒壶）。作为伴手礼的瓶装浊酒，可以在村内的酒铺和土特产店购买。另外，浊酒酒精度数较高，请注意不要饮酒过量。驾驶汽车或自行车的人请绝对不要饮酒。</t>
         </is>
       </c>
-      <c r="E171" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E171" s="30" t="n"/>
       <c r="F171" s="32" t="inlineStr">
         <is>
           <t>境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。</t>
@@ -12521,11 +12023,7 @@
           <t>Minors cannot drink doburoku. You are welcome to watch the festival with your children.</t>
         </is>
       </c>
-      <c r="E172" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E172" s="21" t="n"/>
       <c r="F172" s="23" t="inlineStr">
         <is>
           <t>未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。</t>
@@ -12558,11 +12056,7 @@
           <t>Los menores de edad no pueden tomar doburoku. Las familias con niños sí pueden ver el festival.</t>
         </is>
       </c>
-      <c r="E173" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E173" s="21" t="n"/>
       <c r="F173" s="23" t="inlineStr">
         <is>
           <t>未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。</t>
@@ -12595,11 +12089,7 @@
           <t>Les mineurs ne peuvent pas boire de doburoku. Vous pouvez toutefois assister au festival avec vos enfants.</t>
         </is>
       </c>
-      <c r="E174" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E174" s="21" t="n"/>
       <c r="F174" s="23" t="inlineStr">
         <is>
           <t>未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。</t>
@@ -12632,11 +12122,7 @@
           <t>미성년자는 도부로쿠를 드실 수 없습니다. 아이를 동반하셔도 축제는 관람하실 수 있습니다.</t>
         </is>
       </c>
-      <c r="E175" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E175" s="21" t="n"/>
       <c r="F175" s="23" t="inlineStr">
         <is>
           <t>未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。</t>
@@ -12668,11 +12154,7 @@
           <t>未成年人不能饮用浊酒。带孩子也可以观看节日活动。</t>
         </is>
       </c>
-      <c r="E176" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E176" s="24" t="n"/>
       <c r="F176" s="26" t="inlineStr">
         <is>
           <t>未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。</t>
@@ -12705,11 +12187,7 @@
           <t>The Doburoku Festival of Shirakawa-go is a traditional Shinto ritual held every autumn to pray for a good harvest, the safety of families, and peace in the village. At Shirakawa Hachiman Shrine, it is held over 2 days, on October 14 and 15. After that, it continues at Hatogaya Hachiman Shrine and then Iijima Hachiman Shrine, for 2 days each. There are many highlights, such as the colorful daytime village procession, called Shinkosai, doburoku served in the shrine grounds, and the lion dance and the Shirakawa-go Harukoma folk dance, performed as offerings from the evening.</t>
         </is>
       </c>
-      <c r="E177" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E177" s="27" t="n"/>
       <c r="F177" s="29" t="inlineStr">
         <is>
           <t>白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。</t>
@@ -12742,11 +12220,7 @@
           <t>El Festival Doburoku de Shirakawa-go es un rito sintoísta tradicional que se celebra cada otoño para pedir abundantes cosechas, la seguridad de los hogares y la paz del pueblo. En el Santuario Hachiman de Shirakawa se celebra durante 2 días, el 14 y el 15 de octubre. Después continúa, 2 días en cada uno, en el Santuario Hachiman de Hatogaya y en el Santuario Hachiman de Iijima. Tiene muchos atractivos, como la vistosa procesión por el pueblo, llamada Shinkosai, durante el día, el reparto de doburoku, un sake sin refinar, en el recinto del santuario, y la danza del león y la danza folclórica Harukoma de Shirakawa-go, que se ofrecen a partir del atardecer.</t>
         </is>
       </c>
-      <c r="E178" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E178" s="27" t="n"/>
       <c r="F178" s="29" t="inlineStr">
         <is>
           <t>白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。</t>
@@ -12779,11 +12253,7 @@
           <t>Le Doburoku Festival de Shirakawa-go est une cérémonie shinto traditionnelle organisée chaque automne pour prier pour de bonnes récoltes, la sécurité des foyers et la paix du village. Au sanctuaire Shirakawa Hachiman, il se déroule sur 2 jours, les 14 et 15 octobre. Il se poursuit ensuite au sanctuaire Hatogaya Hachiman puis au sanctuaire Iijima Hachiman, pendant 2 jours chacun. Il y a beaucoup à voir : la procession colorée à travers le village en journée, appelée Shinkosai, la distribution de doburoku dans l'enceinte du sanctuaire, et, à partir de la fin d'après-midi, les offrandes de danse du lion et de danse folklorique Harukoma de Shirakawa-go.</t>
         </is>
       </c>
-      <c r="E179" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E179" s="27" t="n"/>
       <c r="F179" s="29" t="inlineStr">
         <is>
           <t>白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。</t>
@@ -12816,11 +12286,7 @@
           <t>시라카와고의 도부로쿠 축제는 오곡 풍요, 가정의 안녕, 마을의 평화를 기원하며 매년 가을에 열리는 전통 신사 행사입니다. 시라카와 하치만 신사에서는 10월 14일과 15일 이틀에 걸쳐 열립니다. 그 후 이틀씩 하토가야 하치만 신사, 이이지마 하치만 신사로 이어집니다. 낮의 화려한 마을 순회 행렬인 신코사이, 경내에서의 도부로쿠 나눔, 저녁 이후에 봉납되는 사자춤과 민요 시라카와고 하루코마 등 볼거리가 풍부합니다.</t>
         </is>
       </c>
-      <c r="E180" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E180" s="27" t="n"/>
       <c r="F180" s="29" t="inlineStr">
         <is>
           <t>白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。</t>
@@ -12852,11 +12318,7 @@
           <t>白川乡的浊酒节是每年秋季举行的传统祭神活动，祈求五谷丰登、家宅平安和乡里和平。白川八幡神社的祭典在10月14日和15日两天举行。之后依次在鸠谷八幡神社、饭岛八幡神社各举行2天。白天有热闹的村内巡游队伍（神幸祭），神社院内有浊酒分发，傍晚以后还有供奉的狮子舞和民谣白川乡春驹等，看点非常丰富。</t>
         </is>
       </c>
-      <c r="E181" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E181" s="30" t="n"/>
       <c r="F181" s="32" t="inlineStr">
         <is>
           <t>白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。</t>
@@ -12889,11 +12351,7 @@
           <t>Traditional local performing arts are offered on the stage and in front of the worship hall in the shrine grounds. Performances include the powerful Shirakawa Renjishi lion dance and the Harukoma folk dance, which is designated as an Important Intangible Folk Cultural Property of the prefecture. They begin at the same time as the doburoku serving in the daytime session, and after a break, the lion dance and folk songs are performed again in the evening session from about 7:00 p.m.</t>
         </is>
       </c>
-      <c r="E182" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E182" s="21" t="n"/>
       <c r="F182" s="23" t="inlineStr">
         <is>
           <t>神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。</t>
@@ -12926,11 +12384,7 @@
           <t>En el escenario del recinto del santuario y frente al salón de oración se ofrecen artes escénicas tradicionales locales. Se presentan el enérgico Shirakawa Renjishi, una danza del león, y la danza Harukoma, un baile folclórico declarado Bien Cultural Folclórico Inmaterial Importante de la prefectura. Comienzan al mismo tiempo que el reparto de doburoku de la sesión de día y, tras un descanso, la danza del león y los bailes folclóricos se vuelven a presentar en la sesión de noche, a partir de las 19:00 aproximadamente.</t>
         </is>
       </c>
-      <c r="E183" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E183" s="21" t="n"/>
       <c r="F183" s="23" t="inlineStr">
         <is>
           <t>神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。</t>
@@ -12963,11 +12417,7 @@
           <t>Des arts traditionnels locaux sont présentés en offrande sur la scène du sanctuaire, devant le pavillon de culte. On peut notamment voir le spectaculaire Shirakawa Renjishi, une danse du lion, et la danse Harukoma, un chant folklorique classé bien culturel immatériel folklorique important de la préfecture. Les représentations commencent en même temps que la distribution de doburoku de l'après-midi, puis, après une pause, la danse du lion et les chants folkloriques sont de nouveau présentés lors de la séance du soir, à partir d'environ 19 h.</t>
         </is>
       </c>
-      <c r="E184" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E184" s="21" t="n"/>
       <c r="F184" s="23" t="inlineStr">
         <is>
           <t>神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。</t>
@@ -13000,11 +12450,7 @@
           <t>신사 경내의 무대와 배전 앞에서는 전통 향토 예능이 봉납됩니다. 용맹한 사자춤인 시라카와 렌지시와, 현 중요 무형 민속 문화재로 지정된 민요 하루코마 춤 등을 선보입니다. 낮 공연은 도부로쿠 나눔과 동시에 시작되며, 한 번 휴식을 가진 뒤 오후 7시쯤부터 시작되는 밤 공연에서도 사자춤과 민요를 선보입니다.</t>
         </is>
       </c>
-      <c r="E185" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E185" s="21" t="n"/>
       <c r="F185" s="23" t="inlineStr">
         <is>
           <t>神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。</t>
@@ -13037,11 +12483,7 @@
           <t>神社院内的舞台和拜殿前会供奉传统的乡土艺能表演，包括雄壮的白川连狮子（狮子舞），以及被指定为岐阜县重要无形民俗文化遗产的民谣春驹（Harukoma）舞蹈等。表演与白天的浊酒分发同时开始，中间休息一次后，从晚上7点左右开始的夜场也会表演狮子舞和民谣。</t>
         </is>
       </c>
-      <c r="E186" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E186" s="24" t="n"/>
       <c r="F186" s="26" t="inlineStr">
         <is>
           <t>神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。</t>
@@ -13074,11 +12516,7 @@
           <t>On both days, the festival generally follows this schedule: 8:00 a.m., Shinto ritual at the main hall; 9:00 a.m., the village procession departs and parades from the sacred bridge through the village; 3:00 p.m., the procession returns to the shrine; 3:30 p.m. to 5:00 p.m., doburoku is served in the shrine grounds; 3:30 p.m., offering performances of local performing arts such as the lion dance and folk songs begin; 7:00 p.m., evening lion dance and folk song performances. Times may change depending on how things progress and the weather, so please allow plenty of time.</t>
         </is>
       </c>
-      <c r="E187" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E187" s="27" t="n"/>
       <c r="F187" s="29" t="inlineStr">
         <is>
           <t>両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。</t>
@@ -13111,11 +12549,7 @@
           <t>Ambos días, el programa es aproximadamente el siguiente: 08:00, rito sintoísta en el salón principal; 09:00, salida de la procesión por el pueblo, que parte del puente sagrado y recorre la aldea; 15:00, regreso de la procesión al santuario; de 15:30 a 17:00, reparto de doburoku en el recinto; 15:30, comienzo de las artes tradicionales locales, como la danza del león y los bailes folclóricos; 19:00, danza del león y bailes folclóricos de la noche. Los horarios pueden adelantarse o retrasarse según el desarrollo del festival y el tiempo, así que venga con tiempo de sobra.</t>
         </is>
       </c>
-      <c r="E188" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E188" s="27" t="n"/>
       <c r="F188" s="29" t="inlineStr">
         <is>
           <t>両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。</t>
@@ -13148,11 +12582,7 @@
           <t>Les deux jours, le programme se déroule à peu près ainsi : à partir de 8 h, cérémonie shinto au pavillon principal ; à partir de 9 h, départ de la procession à travers le village, depuis le pont du sanctuaire jusque dans le village ; à partir de 15 h, retour de la procession au sanctuaire ; de 15 h 30 à 17 h, distribution de doburoku dans l'enceinte du sanctuaire ; à partir de 15 h 30, début des offrandes d'arts traditionnels locaux, comme la danse du lion et les chants folkloriques ; à partir de 19 h, danse du lion et chants folkloriques du soir. Les horaires peuvent varier selon le déroulement et la météo : prévoyez donc un peu de marge.</t>
         </is>
       </c>
-      <c r="E189" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E189" s="27" t="n"/>
       <c r="F189" s="29" t="inlineStr">
         <is>
           <t>両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。</t>
@@ -13185,11 +12615,7 @@
           <t>이틀 모두 대체로 다음과 같은 순서로 진행됩니다. 오전 8시부터 본전에서 신사 의식, 오전 9시부터 마을 순회 행렬 출발로 신교 다리에서 마을 안을 행진, 오후 3시부터 행렬이 신사로 귀환, 오후 3시 30분부터 5시까지 경내에서 도부로쿠 나눔, 오후 3시 30분부터 사자춤과 민요 등 향토 예능 봉납 시작, 오후 7시부터 밤의 사자춤과 민요 봉납이 있습니다. 진행 상황이나 날씨에 따라 시간이 앞당겨지거나 늦어질 수 있으니, 시간 여유를 두고 와 주세요.</t>
         </is>
       </c>
-      <c r="E190" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E190" s="27" t="n"/>
       <c r="F190" s="29" t="inlineStr">
         <is>
           <t>両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。</t>
@@ -13222,11 +12648,7 @@
           <t>两天的活动大致按以下流程进行：上午8点起，本殿举行祭神仪式；上午9点起，村内巡游队伍出发，从神桥出发在村落内巡游；下午3点起，巡游队伍返回神社；下午3点30分至5点，在神社院内分发浊酒；下午3点30分起，开始供奉乡土艺能表演，如狮子舞、民谣等；晚上7点起，供奉夜场狮子舞和民谣。时间可能因进行情况和天气有所提前或推后，请预留充足的时间前来。</t>
         </is>
       </c>
-      <c r="E191" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E191" s="30" t="n"/>
       <c r="F191" s="32" t="inlineStr">
         <is>
           <t>両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。</t>
@@ -13259,11 +12681,7 @@
           <t>The venue, Shirakawa Hachiman Shrine, is at the southern end of the Ogimachi gassho-style village. From Shirakawa-go Bus Terminal, it is about a 15 to 20 minute walk south, along the main street lined with gassho-style houses.</t>
         </is>
       </c>
-      <c r="E192" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E192" s="21" t="n"/>
       <c r="F192" s="23" t="inlineStr">
         <is>
           <t>会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
@@ -13296,11 +12714,7 @@
           <t>El lugar del festival, el Santuario Hachiman de Shirakawa, está en el extremo sur de la aldea de casas gassho-zukuri de Ogimachi. Desde la Terminal de Autobuses de Shirakawa-go, está a unos 15 a 20 minutos a pie en dirección sur, por la calle principal donde se alinean las casas gassho-zukuri.</t>
         </is>
       </c>
-      <c r="E193" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E193" s="21" t="n"/>
       <c r="F193" s="23" t="inlineStr">
         <is>
           <t>会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
@@ -13333,11 +12747,7 @@
           <t>Le lieu du festival, le sanctuaire Shirakawa Hachiman, se trouve à l'extrémité sud du village aux maisons gassho d'Ogimachi. Depuis le terminal de bus de Shirakawa-go, comptez environ 15 à 20 minutes à pied vers le sud, par la rue principale bordée de maisons gassho.</t>
         </is>
       </c>
-      <c r="E194" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E194" s="21" t="n"/>
       <c r="F194" s="23" t="inlineStr">
         <is>
           <t>会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
@@ -13370,11 +12780,7 @@
           <t>행사장인 시라카와 하치만 신사는 오기마치 갓쇼즈쿠리 마을의 남쪽 끝에 있습니다. 시라카와고 버스터미널에서는 남쪽, 갓쇼즈쿠리 가옥이 늘어선 메인 거리 방향으로 걸어서 약 15분에서 20분 걸립니다.</t>
         </is>
       </c>
-      <c r="E195" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E195" s="21" t="n"/>
       <c r="F195" s="23" t="inlineStr">
         <is>
           <t>会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
@@ -13406,11 +12812,7 @@
           <t>会场白川八幡神社位于荻町合掌造村落的南端。从白川乡巴士总站出发，向南沿着合掌造房屋林立的主街步行约15到20分钟。</t>
         </is>
       </c>
-      <c r="E196" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E196" s="24" t="n"/>
       <c r="F196" s="26" t="inlineStr">
         <is>
           <t>会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
@@ -13443,11 +12845,7 @@
           <t>Shirakawa Hachiman Shrine is at the southern end of the Ogimachi gassho-style village. From Deai-no-Yakata, cross Deai Bridge, go out to the main street, and head right, to the south, and you will arrive there. Look for the torii gate and the large cedar trees.</t>
         </is>
       </c>
-      <c r="E197" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E197" s="27" t="n"/>
       <c r="F197" s="29" t="inlineStr">
         <is>
           <t>「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
@@ -13480,11 +12878,7 @@
           <t>El Santuario Hachiman de Shirakawa está en el extremo sur de la aldea de casas gassho-zukuri de Ogimachi. Desde Deai-no-Yakata, cruce el Puente Deai, salga a la calle principal y siga hacia la derecha, es decir, hacia el sur, hasta llegar. Lo reconocerá por el torii y el gran cedro.</t>
         </is>
       </c>
-      <c r="E198" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E198" s="27" t="n"/>
       <c r="F198" s="29" t="inlineStr">
         <is>
           <t>「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
@@ -13517,11 +12911,7 @@
           <t>Le sanctuaire Shirakawa Hachiman se trouve à l'extrémité sud du village aux maisons gassho d'Ogimachi. Depuis le Deai-no-Yakata, traversez le pont Deai, rejoignez la rue principale et continuez vers la droite, c'est-à-dire vers le sud, pour y arriver. Le torii et le grand cèdre vous serviront de repères.</t>
         </is>
       </c>
-      <c r="E199" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E199" s="27" t="n"/>
       <c r="F199" s="29" t="inlineStr">
         <is>
           <t>「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
@@ -13554,11 +12944,7 @@
           <t>시라카와 하치만 신사는 오기마치 갓쇼즈쿠리 마을의 남쪽 끝에 있습니다. 데아이노야카타 쪽에서는 데아이 다리를 건너 큰길로 나가서 오른쪽, 즉 남쪽으로 가시면 도착합니다. 도리이와 큰 삼나무가 표지입니다.</t>
         </is>
       </c>
-      <c r="E200" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E200" s="27" t="n"/>
       <c r="F200" s="29" t="inlineStr">
         <is>
           <t>「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
@@ -13590,11 +12976,7 @@
           <t>白川八幡神社位于荻町合掌造村落的南端。从Deai-no-Yakata（出会之馆）方向出发，过Deai桥走到大路后，向右（南边）前进即可到达。鸟居和高大的杉树是标志。</t>
         </is>
       </c>
-      <c r="E201" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E201" s="30" t="n"/>
       <c r="F201" s="32" t="inlineStr">
         <is>
           <t>「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
@@ -13633,11 +13015,7 @@
           <t>That building is in the direction of Hatogaya Hachiman Shrine. Please take the road along the river to get there. Leave the building, turn right, and follow Route 156. Then turn left at the bridge that crosses the river and follow the road along the river.</t>
         </is>
       </c>
-      <c r="E202" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E202" s="21" t="n"/>
       <c r="F202" s="23" t="inlineStr">
         <is>
           <t>その建物は鳩谷八幡神社方面にあります。向かわれる際は川沿いの道をお進みください。建物を出て右に行き国道156号線を進み、川を渡る橋を左に曲がり川沿いを進む道です。</t>
@@ -13678,11 +13056,7 @@
           <t>Ese edificio está en dirección al Santuario Hachiman de Hatogaya. Para ir, siga el camino junto al río. Salga del edificio, gire a la derecha y siga por la Ruta 156; en el puente que cruza el río, gire a la izquierda y continúe por el camino junto al río.</t>
         </is>
       </c>
-      <c r="E203" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E203" s="21" t="n"/>
       <c r="F203" s="23" t="inlineStr">
         <is>
           <t>その建物は鳩谷八幡神社方面にあります。向かわれる際は川沿いの道をお進みください。建物を出て右に行き国道156号線を進み、川を渡る橋を左に曲がり川沿いを進む道です。</t>
@@ -13723,11 +13097,7 @@
           <t>Cet établissement se trouve en direction du sanctuaire Hatogaya Hachiman. Pour vous y rendre, veuillez emprunter le chemin qui longe la rivière. En sortant du bâtiment, tournez à droite et suivez la route 156, puis tournez à gauche au pont qui traverse la rivière et continuez le long de la rivière.</t>
         </is>
       </c>
-      <c r="E204" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E204" s="21" t="n"/>
       <c r="F204" s="23" t="inlineStr">
         <is>
           <t>その建物は鳩谷八幡神社方面にあります。向かわれる際は川沿いの道をお進みください。建物を出て右に行き国道156号線を進み、川を渡る橋を左に曲がり川沿いを進む道です。</t>
@@ -13777,11 +13147,7 @@
           <t>그 건물은 하토가야 하치만 신사 방면에 있습니다. 가실 때는 강변 길로 가 주세요. 건물을 나가서 오른쪽으로 가서 국도 156호선을 따라가다가, 강을 건너는 다리에서 왼쪽으로 돌아 강을 따라가는 길입니다.</t>
         </is>
       </c>
-      <c r="E205" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E205" s="21" t="n"/>
       <c r="F205" s="23" t="inlineStr">
         <is>
           <t>その建物は鳩谷八幡神社方面にあります。向かわれる際は川沿いの道をお進みください。建物を出て右に行き国道156号線を進み、川を渡る橋を左に曲がり川沿いを進む道です。</t>
@@ -13824,11 +13190,7 @@
           <t>那栋建筑在鸠谷八幡神社方向。前往时请沿河边的路走。出了建筑向右，沿156号国道前进，在过河的桥处左转，然后沿河边走即可。</t>
         </is>
       </c>
-      <c r="E206" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E206" s="24" t="n"/>
       <c r="F206" s="26" t="inlineStr">
         <is>
           <t>その建物は鳩谷八幡神社方面にあります。向かわれる際は川沿いの道をお進みください。建物を出て右に行き国道156号線を進み、川を渡る橋を左に曲がり川沿いを進む道です。</t>
@@ -13867,11 +13229,7 @@
           <t>That building is in the direction of Hatogaya Hachiman Shrine. Please take the road along the river to get there. Follow Route 156, then turn left at the bridge that crosses the river and follow the road along the river.</t>
         </is>
       </c>
-      <c r="E207" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E207" s="27" t="n"/>
       <c r="F207" s="29" t="inlineStr">
         <is>
           <t>その建物は鳩谷八幡神社方面にあります。向かわれる際は川沿いの道をお進みください。国道156号線を進み、川を渡る橋を左に曲がり川沿いを進む道です。</t>
@@ -13912,11 +13270,7 @@
           <t>Ese edificio está en dirección al Santuario Hachiman de Hatogaya. Para ir, siga el camino junto al río. Siga por la Ruta 156; en el puente que cruza el río, gire a la izquierda y continúe por el camino junto al río.</t>
         </is>
       </c>
-      <c r="E208" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E208" s="27" t="n"/>
       <c r="F208" s="29" t="inlineStr">
         <is>
           <t>その建物は鳩谷八幡神社方面にあります。向かわれる際は川沿いの道をお進みください。国道156号線を進み、川を渡る橋を左に曲がり川沿いを進む道です。</t>
@@ -13957,11 +13311,7 @@
           <t>Cet établissement se trouve en direction du sanctuaire Hatogaya Hachiman. Pour vous y rendre, veuillez emprunter le chemin qui longe la rivière. Suivez la route 156, puis tournez à gauche au pont qui traverse la rivière et continuez le long de la rivière.</t>
         </is>
       </c>
-      <c r="E209" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E209" s="27" t="n"/>
       <c r="F209" s="29" t="inlineStr">
         <is>
           <t>その建物は鳩谷八幡神社方面にあります。向かわれる際は川沿いの道をお進みください。国道156号線を進み、川を渡る橋を左に曲がり川沿いを進む道です。</t>
@@ -14011,11 +13361,7 @@
           <t>그 건물은 하토가야 하치만 신사 방면에 있습니다. 가실 때는 강변 길로 가 주세요. 국도 156호선을 따라가다가, 강을 건너는 다리에서 왼쪽으로 돌아 강을 따라가는 길입니다.</t>
         </is>
       </c>
-      <c r="E210" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E210" s="27" t="n"/>
       <c r="F210" s="29" t="inlineStr">
         <is>
           <t>その建物は鳩谷八幡神社方面にあります。向かわれる際は川沿いの道をお進みください。国道156号線を進み、川を渡る橋を左に曲がり川沿いを進む道です。</t>
@@ -14058,11 +13404,7 @@
           <t>那栋建筑在鸠谷八幡神社方向。前往时请沿河边的路走。沿156号国道前进，在过河的桥处左转，然后沿河边走即可。</t>
         </is>
       </c>
-      <c r="E211" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E211" s="30" t="n"/>
       <c r="F211" s="32" t="inlineStr">
         <is>
           <t>その建物は鳩谷八幡神社方面にあります。向かわれる際は川沿いの道をお進みください。国道156号線を進み、川を渡る橋を左に曲がり川沿いを進む道です。</t>
@@ -14095,11 +13437,7 @@
           <t>For items left on a bus, please contact the bus company. If you tell them where the bus departed from, its departure time, and your seat number, they can check for you. For items lost in the village, we can let you know if they have been handed in as found property. Please send us an email with your name, details of the lost item, and your contact information. Valuables may be taken directly to the police, so please also call the police.</t>
         </is>
       </c>
-      <c r="E212" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E212" s="21" t="n"/>
       <c r="F212" s="23" t="inlineStr">
         <is>
           <t>バス車内でのお忘れ物は、バス会社にお尋ねください。どこから何時発の便か、座席番号などをお知らせいただくと確認ができます。村内での落とし物は、拾得物としての届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえ、メールをお願いいたします。貴重品は警察に直接届けられる場合もありますので、警察にもお電話をお願いいたします。</t>
@@ -14132,11 +13470,7 @@
           <t>Si olvidó algo dentro del autobús, consulte a la compañía de autobuses. Si les indica desde dónde y a qué hora salió el autobús, su número de asiento y otros datos, podrán comprobarlo. En cuanto a los objetos perdidos en el pueblo, podemos informarle si alguien lo ha entregado. Envíenos un correo electrónico indicando su nombre, la descripción del objeto perdido y sus datos de contacto. Como los objetos de valor a veces se entregan directamente a la policía, llame también a la policía.</t>
         </is>
       </c>
-      <c r="E213" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E213" s="21" t="n"/>
       <c r="F213" s="23" t="inlineStr">
         <is>
           <t>バス車内でのお忘れ物は、バス会社にお尋ねください。どこから何時発の便か、座席番号などをお知らせいただくと確認ができます。村内での落とし物は、拾得物としての届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえ、メールをお願いいたします。貴重品は警察に直接届けられる場合もありますので、警察にもお電話をお願いいたします。</t>
@@ -14169,11 +13503,7 @@
           <t>Pour un objet oublié dans un bus, veuillez vous adresser à la compagnie de bus. Elle pourra vérifier si vous lui indiquez d'où et à quelle heure partait le bus, ainsi que votre numéro de siège. Pour un objet perdu dans le village, nous pourrons vous informer s'il a été déposé comme objet trouvé. Veuillez nous envoyer un e-mail en indiquant votre nom, la description de l'objet perdu et vos coordonnées. Les objets de valeur pouvant être remis directement à la police, veuillez également appeler la police.</t>
         </is>
       </c>
-      <c r="E214" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E214" s="21" t="n"/>
       <c r="F214" s="23" t="inlineStr">
         <is>
           <t>バス車内でのお忘れ物は、バス会社にお尋ねください。どこから何時発の便か、座席番号などをお知らせいただくと確認ができます。村内での落とし物は、拾得物としての届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえ、メールをお願いいたします。貴重品は警察に直接届けられる場合もありますので、警察にもお電話をお願いいたします。</t>
@@ -14206,11 +13536,7 @@
           <t>버스 안에서 잃어버린 물건은 버스 회사에 문의해 주세요. 어디에서 몇 시에 출발한 편인지, 좌석 번호 등을 알려 주시면 확인할 수 있습니다. 마을 안에서 잃어버린 물건은 습득물로 신고된 경우 알려 드릴 수 있습니다. 성함, 잃어버린 물건의 자세한 내용, 연락처를 적어서 이메일로 보내 주세요. 귀중품은 경찰에 직접 신고되는 경우도 있으므로 경찰에도 전화해 주세요.</t>
         </is>
       </c>
-      <c r="E215" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E215" s="21" t="n"/>
       <c r="F215" s="23" t="inlineStr">
         <is>
           <t>バス車内でのお忘れ物は、バス会社にお尋ねください。どこから何時発の便か、座席番号などをお知らせいただくと確認ができます。村内での落とし物は、拾得物としての届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえ、メールをお願いいたします。貴重品は警察に直接届けられる場合もありますので、警察にもお電話をお願いいたします。</t>
@@ -14243,11 +13569,7 @@
           <t>在巴士车内遗失的物品，请向巴士公司询问。告知从哪里出发、几点的班次以及座位号等信息，就可以帮您确认。在村内遗失的物品，如果有人作为拾得物上交，我们可以通知您。请写明您的姓名、遗失物品的详细情况和联系方式，发送电子邮件给我们。贵重物品有时会被直接送到警察那里，所以也请致电警察。</t>
         </is>
       </c>
-      <c r="E216" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E216" s="24" t="n"/>
       <c r="F216" s="26" t="inlineStr">
         <is>
           <t>バス車内でのお忘れ物は、バス会社にお尋ねください。どこから何時発の便か、座席番号などをお知らせいただくと確認ができます。村内での落とし物は、拾得物としての届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえ、メールをお願いいたします。貴重品は警察に直接届けられる場合もありますので、警察にもお電話をお願いいたします。</t>
@@ -14280,11 +13602,7 @@
           <t>For items lost in the village, we can let you know if they have been handed in as found property. Please send us an email with your name, details of the lost item, and your contact information. Valuables may be taken directly to the police, so please also call the police.</t>
         </is>
       </c>
-      <c r="E217" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E217" s="27" t="n"/>
       <c r="F217" s="29" t="inlineStr">
         <is>
           <t>村内での落とし物は、拾得物としての届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえ、メールをお願いいたします。貴重品は警察に直接届けられる場合もありますので、警察にもお電話をお願いいたします。</t>
@@ -14317,11 +13635,7 @@
           <t>En cuanto a los objetos perdidos en el pueblo, podemos informarle si alguien lo ha entregado. Envíenos un correo electrónico indicando su nombre, la descripción del objeto perdido y sus datos de contacto. Como los objetos de valor a veces se entregan directamente a la policía, llame también a la policía.</t>
         </is>
       </c>
-      <c r="E218" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E218" s="27" t="n"/>
       <c r="F218" s="29" t="inlineStr">
         <is>
           <t>村内での落とし物は、拾得物としての届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえ、メールをお願いいたします。貴重品は警察に直接届けられる場合もありますので、警察にもお電話をお願いいたします。</t>
@@ -14354,11 +13668,7 @@
           <t>Pour un objet perdu dans le village, nous pourrons vous informer s'il a été déposé comme objet trouvé. Veuillez nous envoyer un e-mail en indiquant votre nom, la description de l'objet perdu et vos coordonnées. Les objets de valeur pouvant être remis directement à la police, veuillez également appeler la police.</t>
         </is>
       </c>
-      <c r="E219" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E219" s="27" t="n"/>
       <c r="F219" s="29" t="inlineStr">
         <is>
           <t>村内での落とし物は、拾得物としての届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえ、メールをお願いいたします。貴重品は警察に直接届けられる場合もありますので、警察にもお電話をお願いいたします。</t>
@@ -14391,11 +13701,7 @@
           <t>마을 안에서 잃어버린 물건은 습득물로 신고된 경우 알려 드릴 수 있습니다. 성함, 잃어버린 물건의 자세한 내용, 연락처를 적어서 이메일로 보내 주세요. 귀중품은 경찰에 직접 신고되는 경우도 있으므로 경찰에도 전화해 주세요.</t>
         </is>
       </c>
-      <c r="E220" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E220" s="27" t="n"/>
       <c r="F220" s="29" t="inlineStr">
         <is>
           <t>村内での落とし物は、拾得物としての届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえ、メールをお願いいたします。貴重品は警察に直接届けられる場合もありますので、警察にもお電話をお願いいたします。</t>
@@ -14428,11 +13734,7 @@
           <t>在村内遗失的物品，如果有人作为拾得物上交，我们可以通知您。请写明您的姓名、遗失物品的详细情况和联系方式，发送电子邮件给我们。贵重物品有时会被直接送到警察那里，所以也请致电警察。</t>
         </is>
       </c>
-      <c r="E221" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E221" s="30" t="n"/>
       <c r="F221" s="32" t="inlineStr">
         <is>
           <t>村内での落とし物は、拾得物としての届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえ、メールをお願いいたします。貴重品は警察に直接届けられる場合もありますので、警察にもお電話をお願いいたします。</t>
@@ -14465,11 +13767,7 @@
           <t>Yuinosho is behind Michi-no-Eki Shirakawa-go, 3.1 km away, and takes about 30 minutes on foot. The main road has heavy traffic, so we recommend the road along the river. Follow Route 156, turn left at the bridge that crosses the river, and follow the road along the river. There are restrooms on the way. The pick-up service starts at 2:30 p.m. For the bus back to the Bus Terminal the next day, please make a reservation at the Yuinosho counter.</t>
         </is>
       </c>
-      <c r="E222" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E222" s="21" t="n"/>
       <c r="F222" s="23" t="inlineStr">
         <is>
           <t>結の庄は道の駅白川郷の裏手、3.1ｋｍ先にあり、歩くとおよそ30分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。国道156号線を進み、川を渡る橋を左に曲がって川沿いに進む道です。途中にお手洗いもございます。送迎は午後2時30分から始まります。翌日バスターミナルに戻るバスは、結の庄のカウンターでご予約ください。</t>
@@ -14501,11 +13799,7 @@
           <t>Yuinosho está detrás de Michi-no-Eki Shirakawa-go, la estación de carretera, a 3,1 km de aquí, y se tarda unos 30 minutos a pie. Como la carretera nacional tiene mucho tráfico, le recomendamos el camino junto al río: siga por la Ruta 156, gire a la izquierda en el puente que cruza el río y continúe junto al río. En el camino también hay baños. El servicio de traslado empieza a las 14:30. Para el autobús de regreso a la Terminal de Autobuses al día siguiente, haga la reserva en el mostrador de Yuinosho.</t>
         </is>
       </c>
-      <c r="E223" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E223" s="21" t="n"/>
       <c r="F223" s="23" t="inlineStr">
         <is>
           <t>結の庄は道の駅白川郷の裏手、3.1ｋｍ先にあり、歩くとおよそ30分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。国道156号線を進み、川を渡る橋を左に曲がって川沿いに進む道です。途中にお手洗いもございます。送迎は午後2時30分から始まります。翌日バスターミナルに戻るバスは、結の庄のカウンターでご予約ください。</t>
@@ -14538,11 +13832,7 @@
           <t>L'hôtel Yuinosho se trouve derrière le Michi-no-Eki Shirakawa-go, l'aire de repos routière, à 3,1 km d'ici ; il faut environ 30 minutes à pied. La route nationale étant très fréquentée, nous vous conseillons le chemin qui longe la rivière : suivez la route 156, tournez à gauche au pont qui traverse la rivière et continuez le long de la rivière. Il y a aussi des toilettes en chemin. Le service de navette commence à 14 h 30. Pour le bus du lendemain qui revient au terminal de bus, veuillez réserver au comptoir du Yuinosho.</t>
         </is>
       </c>
-      <c r="E224" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E224" s="21" t="n"/>
       <c r="F224" s="23" t="inlineStr">
         <is>
           <t>結の庄は道の駅白川郷の裏手、3.1ｋｍ先にあり、歩くとおよそ30分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。国道156号線を進み、川を渡る橋を左に曲がって川沿いに進む道です。途中にお手洗いもございます。送迎は午後2時30分から始まります。翌日バスターミナルに戻るバスは、結の庄のカウンターでご予約ください。</t>
@@ -14574,11 +13864,7 @@
           <t>유이노쇼는 미치노에키 시라카와고 뒤편, 3.1 km 떨어진 곳에 있으며 걸어서 약 30분 걸립니다. 국도는 교통량이 많아서 강변 길을 추천합니다. 국도 156호선을 따라가다가, 강을 건너는 다리에서 왼쪽으로 돌아 강을 따라가는 길입니다. 도중에 화장실도 있습니다. 송영 서비스는 오후 2시 30분부터 시작됩니다. 다음 날 버스터미널로 돌아가는 버스는 유이노쇼 카운터에서 예약해 주세요.</t>
         </is>
       </c>
-      <c r="E225" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E225" s="21" t="n"/>
       <c r="F225" s="23" t="inlineStr">
         <is>
           <t>結の庄は道の駅白川郷の裏手、3.1ｋｍ先にあり、歩くとおよそ30分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。国道156号線を進み、川を渡る橋を左に曲がって川沿いに進む道です。途中にお手洗いもございます。送迎は午後2時30分から始まります。翌日バスターミナルに戻るバスは、結の庄のカウンターでご予約ください。</t>
@@ -14610,11 +13896,7 @@
           <t>结之庄（酒店）位于道之站白川乡（公路休息站）的后面，距离3.1 km，步行大约需要30分钟。国道车流量大，建议走河边的路：沿156号国道前进，在过河的桥处左转，然后沿河边走。途中也有洗手间。接送服务从下午2点30分开始。第二天返回巴士总站的巴士，请在结之庄的前台预约。</t>
         </is>
       </c>
-      <c r="E226" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E226" s="24" t="n"/>
       <c r="F226" s="26" t="inlineStr">
         <is>
           <t>結の庄は道の駅白川郷の裏手、3.1ｋｍ先にあり、歩くとおよそ30分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。国道156号線を進み、川を渡る橋を左に曲がって川沿いに進む道です。途中にお手洗いもございます。送迎は午後2時30分から始まります。翌日バスターミナルに戻るバスは、結の庄のカウンターでご予約ください。</t>
@@ -14647,11 +13929,7 @@
           <t>Yuinosho is behind Michi-no-Eki Shirakawa-go, 3.1 km away, and takes about 40 minutes on foot. The main road has heavy traffic, so we recommend the road along the river. There are restrooms on the way. The pick-up service starts at 2:30 p.m. For the bus back to the Bus Terminal the next day, please make a reservation at the Yuinosho counter.</t>
         </is>
       </c>
-      <c r="E227" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E227" s="27" t="n"/>
       <c r="F227" s="29" t="inlineStr">
         <is>
           <t>結の庄は道の駅白川郷の裏手、3.1ｋｍ先にあり、歩くとおよそ40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。途中にお手洗いもございます。送迎は午後2時30分から始まります。翌日バスターミナルに戻るバスは、結の庄のカウンターでご予約ください。</t>
@@ -14683,11 +13961,7 @@
           <t>Yuinosho está detrás de Michi-no-Eki Shirakawa-go, la estación de carretera, a 3,1 km de aquí, y se tarda unos 40 minutos a pie. Como la carretera nacional tiene mucho tráfico, le recomendamos el camino junto al río. En el camino también hay baños. El servicio de traslado empieza a las 14:30. Para el autobús de regreso a la Terminal de Autobuses al día siguiente, haga la reserva en el mostrador de Yuinosho.</t>
         </is>
       </c>
-      <c r="E228" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E228" s="27" t="n"/>
       <c r="F228" s="29" t="inlineStr">
         <is>
           <t>結の庄は道の駅白川郷の裏手、3.1ｋｍ先にあり、歩くとおよそ40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。途中にお手洗いもございます。送迎は午後2時30分から始まります。翌日バスターミナルに戻るバスは、結の庄のカウンターでご予約ください。</t>
@@ -14720,11 +13994,7 @@
           <t>L'hôtel Yuinosho se trouve derrière le Michi-no-Eki Shirakawa-go, l'aire de repos routière, à 3,1 km d'ici ; il faut environ 40 minutes à pied. La route nationale étant très fréquentée, nous vous conseillons le chemin qui longe la rivière. Il y a aussi des toilettes en chemin. Le service de navette commence à 14 h 30. Pour le bus du lendemain qui revient au terminal de bus, veuillez réserver au comptoir du Yuinosho.</t>
         </is>
       </c>
-      <c r="E229" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E229" s="27" t="n"/>
       <c r="F229" s="29" t="inlineStr">
         <is>
           <t>結の庄は道の駅白川郷の裏手、3.1ｋｍ先にあり、歩くとおよそ40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。途中にお手洗いもございます。送迎は午後2時30分から始まります。翌日バスターミナルに戻るバスは、結の庄のカウンターでご予約ください。</t>
@@ -14756,11 +14026,7 @@
           <t>유이노쇼는 미치노에키 시라카와고 뒤편, 3.1 km 떨어진 곳에 있으며 걸어서 약 40분 걸립니다. 국도는 교통량이 많아서 강변 길을 추천합니다. 도중에 화장실도 있습니다. 송영 서비스는 오후 2시 30분부터 시작됩니다. 다음 날 버스터미널로 돌아가는 버스는 유이노쇼 카운터에서 예약해 주세요.</t>
         </is>
       </c>
-      <c r="E230" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E230" s="27" t="n"/>
       <c r="F230" s="29" t="inlineStr">
         <is>
           <t>結の庄は道の駅白川郷の裏手、3.1ｋｍ先にあり、歩くとおよそ40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。途中にお手洗いもございます。送迎は午後2時30分から始まります。翌日バスターミナルに戻るバスは、結の庄のカウンターでご予約ください。</t>
@@ -14792,11 +14058,7 @@
           <t>结之庄（酒店）位于道之站白川乡（公路休息站）的后面，距离3.1 km，步行大约需要40分钟。国道车流量大，建议走河边的路。途中也有洗手间。接送服务从下午2点30分开始。第二天返回巴士总站的巴士，请在结之庄的前台预约。</t>
         </is>
       </c>
-      <c r="E231" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E231" s="30" t="n"/>
       <c r="F231" s="32" t="inlineStr">
         <is>
           <t>結の庄は道の駅白川郷の裏手、3.1ｋｍ先にあり、歩くとおよそ40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。途中にお手洗いもございます。送迎は午後2時30分から始まります。翌日バスターミナルに戻るバスは、結の庄のカウンターでご予約ください。</t>
@@ -14829,11 +14091,7 @@
           <t>You can check the bus timetable on the notice in front of the information center or at the bus company counter. For details, please ask a staff member.</t>
         </is>
       </c>
-      <c r="E232" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E232" s="21" t="n"/>
       <c r="F232" s="23" t="inlineStr">
         <is>
           <t>バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。</t>
@@ -14865,11 +14123,7 @@
           <t>Puede consultar el horario de autobuses en el tablón frente al centro de información o en la ventanilla de la compañía de autobuses. Para más detalles, pregunte al personal.</t>
         </is>
       </c>
-      <c r="E233" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E233" s="21" t="n"/>
       <c r="F233" s="23" t="inlineStr">
         <is>
           <t>バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。</t>
@@ -14902,11 +14156,7 @@
           <t>Vous pouvez consulter les horaires des bus sur le panneau d'affichage devant le point d'information ou au guichet de la compagnie de bus. Pour plus de détails, veuillez vous adresser au personnel.</t>
         </is>
       </c>
-      <c r="E234" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E234" s="21" t="n"/>
       <c r="F234" s="23" t="inlineStr">
         <is>
           <t>バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。</t>
@@ -14939,11 +14189,7 @@
           <t>버스 시간표는 안내소 앞 게시물 또는 버스 회사 창구에서 확인하실 수 있습니다. 자세한 내용은 직원에게 문의해 주세요.</t>
         </is>
       </c>
-      <c r="E235" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E235" s="21" t="n"/>
       <c r="F235" s="23" t="inlineStr">
         <is>
           <t>バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。</t>
@@ -14976,11 +14222,7 @@
           <t>巴士时刻表可以查看咨询处前的公告，或到巴士公司的窗口确认。详情请询问工作人员。</t>
         </is>
       </c>
-      <c r="E236" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E236" s="24" t="n"/>
       <c r="F236" s="26" t="inlineStr">
         <is>
           <t>バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。</t>
@@ -15013,11 +14255,7 @@
           <t>The village is a small area, so there is no sightseeing loop bus. Please enjoy exploring on foot. However, there is a shuttle bus to the observatory.</t>
         </is>
       </c>
-      <c r="E237" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E237" s="27" t="n"/>
       <c r="F237" s="29" t="inlineStr">
         <is>
           <t>村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。</t>
@@ -15050,11 +14288,7 @@
           <t>El pueblo es una zona pequeña, así que no hay autobús turístico de recorrido. Le invitamos a disfrutar de la visita a pie. Eso sí, hay un autobús lanzadera al mirador.</t>
         </is>
       </c>
-      <c r="E238" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E238" s="27" t="n"/>
       <c r="F238" s="29" t="inlineStr">
         <is>
           <t>村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。</t>
@@ -15086,11 +14320,7 @@
           <t>Le village est petit : il n'y a donc pas de bus touristique qui en fait le tour. Profitez de la visite à pied. Il existe toutefois une navette pour l'observatoire.</t>
         </is>
       </c>
-      <c r="E239" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E239" s="27" t="n"/>
       <c r="F239" s="29" t="inlineStr">
         <is>
           <t>村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。</t>
@@ -15122,11 +14352,7 @@
           <t>마을 안은 작은 지역이라 관광용 순환 버스는 없습니다. 걸어서 관람을 즐겨 주세요. 참고로 전망대행 셔틀버스는 있습니다.</t>
         </is>
       </c>
-      <c r="E240" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E240" s="27" t="n"/>
       <c r="F240" s="29" t="inlineStr">
         <is>
           <t>村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。</t>
@@ -15158,11 +14384,7 @@
           <t>村内区域很小，因此没有观光循环巴士。请享受步行游览的乐趣。另外，有前往观景台的接驳巴士。</t>
         </is>
       </c>
-      <c r="E241" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E241" s="30" t="n"/>
       <c r="F241" s="32" t="inlineStr">
         <is>
           <t>村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。</t>
@@ -15195,11 +14417,7 @@
           <t>Snow boots can be rented inside Shirakawa-go Bus Terminal. Sizes range from 23 cm to 27 cm, with 3 pairs of each size. The number is limited, and reservations are not possible. The rental hours are 8:30 a.m. to 5:00 p.m., and the fee is 1000 yen for same-day return or 1500 yen for 2 days.</t>
         </is>
       </c>
-      <c r="E242" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E242" s="21" t="n"/>
       <c r="F242" s="23" t="inlineStr">
         <is>
           <t>スノーブーツのレンタルは白川郷バスターミナル内にございます。サイズは23センチから27センチまで、各サイズ3足ずつご用意しております。数に限りがあり、ご予約はできません。貸出時間は8時30分から17時、料金は当日返却が1000円、2日間が1500円です。</t>
@@ -15232,11 +14450,7 @@
           <t>El alquiler de botas de nieve está dentro de la Terminal de Autobuses de Shirakawa-go. Hay tallas de 23 a 27 centímetros, con 3 pares de cada talla. El número es limitado y no se aceptan reservas. El horario de alquiler es de 8:30 a 17:00, y la tarifa es de 1000 yenes con devolución el mismo día y de 1500 yenes por 2 días.</t>
         </is>
       </c>
-      <c r="E243" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E243" s="21" t="n"/>
       <c r="F243" s="23" t="inlineStr">
         <is>
           <t>スノーブーツのレンタルは白川郷バスターミナル内にございます。サイズは23センチから27センチまで、各サイズ3足ずつご用意しております。数に限りがあり、ご予約はできません。貸出時間は8時30分から17時、料金は当日返却が1000円、2日間が1500円です。</t>
@@ -15269,11 +14483,7 @@
           <t>La location de bottes de neige se fait au terminal de bus de Shirakawa-go. Les pointures vont de 23 à 27 centimètres, avec 3 paires par taille. Le nombre est limité et il n'est pas possible de réserver. La location est possible de 8 h 30 à 17 h, au tarif de 1000 yens pour un retour le jour même et de 1500 yens pour 2 jours.</t>
         </is>
       </c>
-      <c r="E244" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E244" s="21" t="n"/>
       <c r="F244" s="23" t="inlineStr">
         <is>
           <t>スノーブーツのレンタルは白川郷バスターミナル内にございます。サイズは23センチから27センチまで、各サイズ3足ずつご用意しております。数に限りがあり、ご予約はできません。貸出時間は8時30分から17時、料金は当日返却が1000円、2日間が1500円です。</t>
@@ -15306,11 +14516,7 @@
           <t>스노부츠 대여는 시라카와고 버스터미널 안에서 하고 있습니다. 사이즈는 23센티미터부터 27센티미터까지, 사이즈별로 3켤레씩 준비되어 있습니다. 수량이 한정되어 있으며, 예약은 받지 않습니다. 대여 시간은 오전 8시 30분부터 오후 5시까지이며, 요금은 당일 반납 1000엔, 2일간 1500엔입니다.</t>
         </is>
       </c>
-      <c r="E245" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E245" s="21" t="n"/>
       <c r="F245" s="23" t="inlineStr">
         <is>
           <t>スノーブーツのレンタルは白川郷バスターミナル内にございます。サイズは23センチから27センチまで、各サイズ3足ずつご用意しております。数に限りがあり、ご予約はできません。貸出時間は8時30分から17時、料金は当日返却が1000円、2日間が1500円です。</t>
@@ -15342,11 +14548,7 @@
           <t>雪地靴租借在白川乡巴士总站内。尺码从23厘米到27厘米，每个尺码各备有3双。数量有限，不接受预约。租借时间为上午8点30分至下午5点，费用为当天归还1000日元，2天1500日元。</t>
         </is>
       </c>
-      <c r="E246" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E246" s="24" t="n"/>
       <c r="F246" s="26" t="inlineStr">
         <is>
           <t>スノーブーツのレンタルは白川郷バスターミナル内にございます。サイズは23センチから27センチまで、各サイズ3足ずつご用意しております。数に限りがあり、ご予約はできません。貸出時間は8時30分から17時、料金は当日返却が1000円、2日間が1500円です。</t>
@@ -15379,11 +14581,7 @@
           <t>For the location of restrooms, please see the village map. There are 5 wheelchair-accessible restrooms in the village.</t>
         </is>
       </c>
-      <c r="E247" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E247" s="27" t="n"/>
       <c r="F247" s="29" t="inlineStr">
         <is>
           <t>お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。</t>
@@ -15416,11 +14614,7 @@
           <t>Para ubicar los baños, consulte el mapa del pueblo. En el pueblo hay 5 baños accesibles para sillas de ruedas.</t>
         </is>
       </c>
-      <c r="E248" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E248" s="27" t="n"/>
       <c r="F248" s="29" t="inlineStr">
         <is>
           <t>お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。</t>
@@ -15453,11 +14647,7 @@
           <t>Pour trouver les toilettes, veuillez consulter la carte du village. Il y a 5 toilettes accessibles en fauteuil roulant dans le village.</t>
         </is>
       </c>
-      <c r="E249" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E249" s="27" t="n"/>
       <c r="F249" s="29" t="inlineStr">
         <is>
           <t>お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。</t>
@@ -15489,11 +14679,7 @@
           <t>화장실 안내는 마을 지도를 확인해 주세요. 휠체어로 이용하실 수 있는 화장실은 마을 안에 5곳 있습니다.</t>
         </is>
       </c>
-      <c r="E250" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E250" s="27" t="n"/>
       <c r="F250" s="29" t="inlineStr">
         <is>
           <t>お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。</t>
@@ -15525,11 +14711,7 @@
           <t>洗手间的位置请查看村内地图。村内有5处可供轮椅使用的厕所。</t>
         </is>
       </c>
-      <c r="E251" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E251" s="30" t="n"/>
       <c r="F251" s="32" t="inlineStr">
         <is>
           <t>お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。</t>
@@ -15562,11 +14744,7 @@
           <t>Admission to the gassho-style houses open to visitors is 300 yen to 400 yen per person at each facility, except for Gassho-zukuri Minkaen, which is 800 yen per person.</t>
         </is>
       </c>
-      <c r="E252" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E252" s="21" t="n"/>
       <c r="F252" s="23" t="inlineStr">
         <is>
           <t>合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。</t>
@@ -15599,11 +14777,7 @@
           <t>Las casas gassho-zukuri visitables cuestan de 300 a 400 yenes por persona cada una; solo el Gassho-zukuri Minkaen, un museo al aire libre, cuesta 800 yenes por persona.</t>
         </is>
       </c>
-      <c r="E253" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E253" s="21" t="n"/>
       <c r="F253" s="23" t="inlineStr">
         <is>
           <t>合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。</t>
@@ -15636,11 +14810,7 @@
           <t>Les maisons gassho ouvertes à la visite coûtent de 300 à 400 yens par personne chacune, sauf le Gassho-zukuri Minkaen, un musée en plein air, qui coûte 800 yens par personne.</t>
         </is>
       </c>
-      <c r="E254" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E254" s="21" t="n"/>
       <c r="F254" s="23" t="inlineStr">
         <is>
           <t>合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。</t>
@@ -15673,11 +14843,7 @@
           <t>갓쇼즈쿠리 관람 시설은 각 시설 1인당 300엔에서 400엔이며, 갓쇼즈쿠리 민카엔만 1인당 800엔입니다.</t>
         </is>
       </c>
-      <c r="E255" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E255" s="21" t="n"/>
       <c r="F255" s="23" t="inlineStr">
         <is>
           <t>合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。</t>
@@ -15710,11 +14876,7 @@
           <t>合掌造参观设施的门票为每处每人300日元至400日元，只有合掌造民家园（露天博物馆）为每人800日元。</t>
         </is>
       </c>
-      <c r="E256" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E256" s="24" t="n"/>
       <c r="F256" s="26" t="inlineStr">
         <is>
           <t>合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。</t>
@@ -15747,11 +14909,7 @@
           <t>Here is information about places to eat in the village. Groups need to make reservations early. Many restaurants close on irregular days, so please check in advance. For a detailed list, please see the link on the screen.</t>
         </is>
       </c>
-      <c r="E257" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E257" s="27" t="n"/>
       <c r="F257" s="29" t="inlineStr">
         <is>
           <t>村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
@@ -15784,11 +14942,7 @@
           <t>Le informamos sobre los lugares para comer del pueblo. Los grupos deben reservar con antelación. Muchos establecimientos tienen días de cierre irregulares, así que compruébelo antes. Para ver la lista completa, consulte el enlace en la pantalla.</t>
         </is>
       </c>
-      <c r="E258" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E258" s="27" t="n"/>
       <c r="F258" s="29" t="inlineStr">
         <is>
           <t>村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
@@ -15821,11 +14975,7 @@
           <t>Nous vous présentons les restaurants du village. Les groupes doivent réserver tôt. Beaucoup d'établissements ont des jours de fermeture irréguliers : veuillez vérifier à l'avance. Pour la liste détaillée, veuillez consulter le lien à l'écran.</t>
         </is>
       </c>
-      <c r="E259" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E259" s="27" t="n"/>
       <c r="F259" s="29" t="inlineStr">
         <is>
           <t>村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
@@ -15858,11 +15008,7 @@
           <t>마을 안의 식사 시설을 안내해 드리고 있습니다. 단체 손님은 미리 예약하셔야 합니다. 많은 가게가 부정기 휴무이므로 사전에 확인해 주세요. 자세한 목록은 화면의 링크를 확인해 주세요.</t>
         </is>
       </c>
-      <c r="E260" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E260" s="27" t="n"/>
       <c r="F260" s="29" t="inlineStr">
         <is>
           <t>村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
@@ -15895,11 +15041,7 @@
           <t>我们为您介绍村内的餐饮设施。团体游客需要提前预约。很多店铺不定期休息，请事先确认。详细列表请查看屏幕上的链接。</t>
         </is>
       </c>
-      <c r="E261" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E261" s="30" t="n"/>
       <c r="F261" s="32" t="inlineStr">
         <is>
           <t>村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
@@ -15932,11 +15074,7 @@
           <t>The timing changes every year depending on the temperature, so please be sure to check for yourself. Cherry blossoms usually bloom around April 15. Autumn leaves are usually at their best from the end of October to early November.</t>
         </is>
       </c>
-      <c r="E262" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E262" s="21" t="n"/>
       <c r="F262" s="23" t="inlineStr">
         <is>
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。</t>
@@ -15969,11 +15107,7 @@
           <t>Varía cada año según las temperaturas, así que compruébelo usted mismo. Los cerezos suelen florecer hacia el 15 de abril. Las hojas de otoño suelen estar en su mejor momento desde finales de octubre hasta principios de noviembre.</t>
         </is>
       </c>
-      <c r="E263" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E263" s="21" t="n"/>
       <c r="F263" s="23" t="inlineStr">
         <is>
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。</t>
@@ -16006,11 +15140,7 @@
           <t>Les dates varient chaque année selon les températures : veuillez donc les vérifier vous-même. Les cerisiers fleurissent généralement vers le 15 avril. Les couleurs d'automne sont généralement à leur plus beau de fin octobre à début novembre.</t>
         </is>
       </c>
-      <c r="E264" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E264" s="21" t="n"/>
       <c r="F264" s="23" t="inlineStr">
         <is>
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。</t>
@@ -16043,11 +15173,7 @@
           <t>해마다 기온에 따라 달라지므로 반드시 직접 확인해 주세요. 벚꽃은 예년 4월 15일쯤 개화합니다. 단풍은 예년 10월 말부터 11월 초순이 절정입니다.</t>
         </is>
       </c>
-      <c r="E265" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E265" s="21" t="n"/>
       <c r="F265" s="23" t="inlineStr">
         <is>
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。</t>
@@ -16080,11 +15206,7 @@
           <t>每年会因气温而有所变化，请务必自行确认。樱花通常在4月15日左右开放。红叶通常在10月底到11月初最为美丽。</t>
         </is>
       </c>
-      <c r="E266" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E266" s="24" t="n"/>
       <c r="F266" s="26" t="inlineStr">
         <is>
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。</t>
@@ -16117,11 +15239,7 @@
           <t>Recent trends show that the first snow is observed in early December every year. This village gets very heavy snowfall, so the ground stays covered with snow from late December to late February. Please check the weather forecast before you go out.</t>
         </is>
       </c>
-      <c r="E267" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E267" s="27" t="n"/>
       <c r="F267" s="29" t="inlineStr">
         <is>
           <t>近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。</t>
@@ -16154,11 +15272,7 @@
           <t>Según la tendencia de los últimos años, la primera nevada se registra a principios de diciembre. Este pueblo está en una zona de nevadas muy intensas, por lo que de finales de diciembre a finales de febrero la nieve permanece acumulada. Consulte el pronóstico del tiempo antes de salir.</t>
         </is>
       </c>
-      <c r="E268" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E268" s="27" t="n"/>
       <c r="F268" s="29" t="inlineStr">
         <is>
           <t>近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。</t>
@@ -16191,11 +15305,7 @@
           <t>Ces dernières années, la première neige est observée début décembre. Notre village se trouve dans une région de fortes chutes de neige, et le sol reste enneigé de fin décembre à fin février. Veuillez consulter les prévisions météo avant de partir.</t>
         </is>
       </c>
-      <c r="E269" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E269" s="27" t="n"/>
       <c r="F269" s="29" t="inlineStr">
         <is>
           <t>近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。</t>
@@ -16228,11 +15338,7 @@
           <t>최근 경향으로는 매년 12월 초순에 첫눈이 관측됩니다. 이 마을은 폭설 지대이기 때문에 12월 하순부터 2월 하순까지는 눈이 쌓인 상태가 계속됩니다. 외출하시기 전에 일기예보를 확인해 주세요.</t>
         </is>
       </c>
-      <c r="E270" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E270" s="27" t="n"/>
       <c r="F270" s="29" t="inlineStr">
         <is>
           <t>近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。</t>
@@ -16265,11 +15371,7 @@
           <t>从近年的情况来看，每年12月上旬会迎来初雪。本村是大雪地区，12月下旬到2月下旬会持续积雪。出行前请确认天气预报。</t>
         </is>
       </c>
-      <c r="E271" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E271" s="30" t="n"/>
       <c r="F271" s="32" t="inlineStr">
         <is>
           <t>近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。</t>
@@ -16302,11 +15404,7 @@
           <t>During the snowy season, please be sure to come with studless winter tires fitted on your car. The roads are very slippery.</t>
         </is>
       </c>
-      <c r="E272" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E272" s="21" t="n"/>
       <c r="F272" s="23" t="inlineStr">
         <is>
           <t>雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
@@ -16339,11 +15437,7 @@
           <t>En la temporada de nieve, venga siempre con neumáticos de invierno sin clavos instalados. La calzada está muy resbaladiza.</t>
         </is>
       </c>
-      <c r="E273" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E273" s="21" t="n"/>
       <c r="F273" s="23" t="inlineStr">
         <is>
           <t>雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
@@ -16376,11 +15470,7 @@
           <t>Pendant la saison des neiges, veuillez impérativement venir avec des pneus hiver. Les routes sont très glissantes.</t>
         </is>
       </c>
-      <c r="E274" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E274" s="21" t="n"/>
       <c r="F274" s="23" t="inlineStr">
         <is>
           <t>雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
@@ -16413,11 +15503,7 @@
           <t>눈이 내리는 시기에는 반드시 스터드리스 타이어를 장착하고 오세요. 노면이 매우 미끄럽습니다.</t>
         </is>
       </c>
-      <c r="E275" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E275" s="21" t="n"/>
       <c r="F275" s="23" t="inlineStr">
         <is>
           <t>雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
@@ -16450,11 +15536,7 @@
           <t>下雪的季节，请务必安装雪地轮胎（无钉防滑轮胎）后前来。路面非常湿滑。</t>
         </is>
       </c>
-      <c r="E276" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E276" s="24" t="n"/>
       <c r="F276" s="26" t="inlineStr">
         <is>
           <t>雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
@@ -16486,11 +15568,7 @@
           <t>You may come into the village by bicycle, but we do not recommend it because there are many people walking. Please walk your bicycle, or park it before sightseeing.</t>
         </is>
       </c>
-      <c r="E277" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E277" s="27" t="n"/>
       <c r="F277" s="29" t="inlineStr">
         <is>
           <t>自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。</t>
@@ -16522,11 +15600,7 @@
           <t>Se puede entrar en la aldea en bicicleta, pero no lo recomendamos porque hay mucha gente caminando. Le pedimos que la lleve empujándola a pie o que la estacione antes de hacer la visita.</t>
         </is>
       </c>
-      <c r="E278" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E278" s="27" t="n"/>
       <c r="F278" s="29" t="inlineStr">
         <is>
           <t>自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。</t>
@@ -16558,11 +15632,7 @@
           <t>Il est possible de venir à vélo dans le village, mais nous ne le recommandons pas, car il y a beaucoup de piétons. Veuillez pousser votre vélo à la main, ou le garer avant de visiter.</t>
         </is>
       </c>
-      <c r="E279" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E279" s="27" t="n"/>
       <c r="F279" s="29" t="inlineStr">
         <is>
           <t>自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。</t>
@@ -16594,11 +15664,7 @@
           <t>자전거로 마을 안에 들어오실 수는 있지만, 걸어 다니는 분이 많아 권하지 않습니다. 자전거를 끌고 걸으시거나, 자전거를 세워 두신 후 관람해 주시기 바랍니다.</t>
         </is>
       </c>
-      <c r="E280" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E280" s="27" t="n"/>
       <c r="F280" s="29" t="inlineStr">
         <is>
           <t>自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。</t>
@@ -16630,11 +15696,7 @@
           <t>可以骑自行车进入村落，但因为步行游客很多，我们不太推荐。请推着自行车步行，或停好自行车后再参观。</t>
         </is>
       </c>
-      <c r="E281" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E281" s="30" t="n"/>
       <c r="F281" s="32" t="inlineStr">
         <is>
           <t>自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。</t>
@@ -16667,11 +15729,7 @@
           <t>Please do not enter the mountains or the fields. You could get lost or injured. For walking, please use the roads in the village and the walking path to the observatory.</t>
         </is>
       </c>
-      <c r="E282" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E282" s="21" t="n"/>
       <c r="F282" s="23" t="inlineStr">
         <is>
           <t>山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。</t>
@@ -16704,11 +15762,7 @@
           <t>No entre en las montañas ni en los campos de cultivo. Existe el riesgo de perderse o de sufrir lesiones. Para pasear, utilice los caminos de la aldea y el sendero que lleva al mirador.</t>
         </is>
       </c>
-      <c r="E283" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E283" s="21" t="n"/>
       <c r="F283" s="23" t="inlineStr">
         <is>
           <t>山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。</t>
@@ -16741,11 +15795,7 @@
           <t>Veuillez ne pas entrer dans la montagne ni dans les champs et rizières. Vous risqueriez de vous perdre ou de vous blesser. Pour vous promener, veuillez utiliser les chemins du village et le sentier menant à l'observatoire.</t>
         </is>
       </c>
-      <c r="E284" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E284" s="21" t="n"/>
       <c r="F284" s="23" t="inlineStr">
         <is>
           <t>山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。</t>
@@ -16778,11 +15828,7 @@
           <t>산속이나 논밭에는 들어가지 마세요. 길을 잃거나 다칠 위험이 있습니다. 산책은 마을 안의 길과 전망대까지의 산책로를 이용해 주세요.</t>
         </is>
       </c>
-      <c r="E285" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E285" s="21" t="n"/>
       <c r="F285" s="23" t="inlineStr">
         <is>
           <t>山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。</t>
@@ -16815,11 +15861,7 @@
           <t>请不要进入山林或田地。有迷路或受伤的危险。散步请走村落内的道路和通往观景台的游步道。</t>
         </is>
       </c>
-      <c r="E286" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E286" s="24" t="n"/>
       <c r="F286" s="26" t="inlineStr">
         <is>
           <t>山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。</t>
@@ -16852,11 +15894,7 @@
           <t>You are welcome to walk around the village with your pet. However, most shops do not allow pets inside. Kobiki allows pets if you carry them in your arms. Imafuji Shoten allows pets to accompany you. For other shops, please check with each shop. Please note that pets are not allowed on the shuttle bus to the observatory.</t>
         </is>
       </c>
-      <c r="E287" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E287" s="27" t="n"/>
       <c r="F287" s="29" t="inlineStr">
         <is>
           <t>ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。</t>
@@ -16888,11 +15926,7 @@
           <t>Puede recorrer la aldea con su mascota. Sin embargo, la mayoría de las tiendas no admiten mascotas en su interior. En Kobiki puede entrar si lleva a su mascota en brazos. En Imafuji Shoten se admiten mascotas. Para las demás tiendas, consulte en cada una. Tenga en cuenta que las mascotas no pueden subir al autobús lanzadera del mirador.</t>
         </is>
       </c>
-      <c r="E288" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E288" s="27" t="n"/>
       <c r="F288" s="29" t="inlineStr">
         <is>
           <t>ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。</t>
@@ -16925,11 +15959,7 @@
           <t>Vous pouvez visiter le village avec votre animal de compagnie. Cependant, la plupart des boutiques n'acceptent pas les animaux à l'intérieur. Chez Kobiki, vous pouvez entrer si vous portez votre animal dans les bras. Imafuji Shoten accepte les animaux. Pour les autres boutiques, veuillez vous renseigner auprès de chacune. Veuillez noter que les animaux ne sont pas admis dans la navette pour l'observatoire.</t>
         </is>
       </c>
-      <c r="E289" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E289" s="27" t="n"/>
       <c r="F289" s="29" t="inlineStr">
         <is>
           <t>ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。</t>
@@ -16962,11 +15992,7 @@
           <t>반려동물과 함께 마을 안을 둘러보실 수 있습니다. 다만 대부분의 가게는 반려동물 출입이 불가합니다. 고비키는 안고 계시면 입장하실 수 있습니다. 이마후지 상점은 반려동물 동반이 가능합니다. 그 밖의 가게는 각 가게에 확인해 주세요. 또한 전망대행 셔틀버스에는 반려동물이 탑승할 수 없습니다.</t>
         </is>
       </c>
-      <c r="E290" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E290" s="27" t="n"/>
       <c r="F290" s="29" t="inlineStr">
         <is>
           <t>ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。</t>
@@ -16999,11 +16025,7 @@
           <t>可以带宠物一起在村落内游览。但是大部分店铺不允许宠物进入。Kobiki店内可以抱着宠物进入。今藤商店可以带宠物进入。其他店铺请向各店确认。另外，宠物不能乘坐前往观景台的接驳巴士。</t>
         </is>
       </c>
-      <c r="E291" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E291" s="30" t="n"/>
       <c r="F291" s="32" t="inlineStr">
         <is>
           <t>ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。</t>
@@ -17036,11 +16058,7 @@
           <t>The river is very dangerous because the current is fast and the water is deep. Please do not go into the river.</t>
         </is>
       </c>
-      <c r="E292" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E292" s="21" t="n"/>
       <c r="F292" s="23" t="inlineStr">
         <is>
           <t>川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。</t>
@@ -17073,11 +16091,7 @@
           <t>El río es muy peligroso porque la corriente es rápida y el agua es profunda. No entre en el río.</t>
         </is>
       </c>
-      <c r="E293" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E293" s="21" t="n"/>
       <c r="F293" s="23" t="inlineStr">
         <is>
           <t>川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。</t>
@@ -17110,11 +16124,7 @@
           <t>Le courant de la rivière est rapide et l'eau est profonde : c'est très dangereux. Veuillez ne pas entrer dans la rivière.</t>
         </is>
       </c>
-      <c r="E294" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E294" s="21" t="n"/>
       <c r="F294" s="23" t="inlineStr">
         <is>
           <t>川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。</t>
@@ -17147,11 +16157,7 @@
           <t>강은 물살이 빠르고 수심도 깊어 매우 위험합니다. 강에는 들어가지 마세요.</t>
         </is>
       </c>
-      <c r="E295" s="21" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E295" s="21" t="n"/>
       <c r="F295" s="23" t="inlineStr">
         <is>
           <t>川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。</t>
@@ -17184,11 +16190,7 @@
           <t>河流水流湍急，水也很深，非常危险。请不要进入河中。</t>
         </is>
       </c>
-      <c r="E296" s="24" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E296" s="24" t="n"/>
       <c r="F296" s="26" t="inlineStr">
         <is>
           <t>川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。</t>
@@ -17221,11 +16223,7 @@
           <t>People live in the World Heritage village. For this reason, we ask visitors, except those staying overnight in the village, to visit between 8:00 a.m. and 5:00 p.m. The village parking lots are also open from 8:00 a.m. to 5:00 p.m. This does not apply on days with events such as the light-up.</t>
         </is>
       </c>
-      <c r="E297" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E297" s="27" t="n"/>
       <c r="F297" s="29" t="inlineStr">
         <is>
           <t>世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。</t>
@@ -17258,11 +16256,7 @@
           <t>En la aldea declarada Patrimonio de la Humanidad viven sus residentes. Por eso, salvo quienes se alojan en la aldea, le pedimos que la visite entre las 8:00 y las 17:00. El estacionamiento municipal también funciona de 8:00 a 17:00. Se exceptúan los días con eventos como la iluminación nocturna.</t>
         </is>
       </c>
-      <c r="E298" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E298" s="27" t="n"/>
       <c r="F298" s="29" t="inlineStr">
         <is>
           <t>世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。</t>
@@ -17295,11 +16289,7 @@
           <t>Des habitants vivent dans le village classé au patrimoine mondial. C'est pourquoi, sauf si vous séjournez dans le village, nous vous demandons de le visiter entre 8 h et 17 h. Les parkings municipaux sont également ouverts de 8 h à 17 h. Les jours d'événements comme les illuminations font exception.</t>
         </is>
       </c>
-      <c r="E299" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E299" s="27" t="n"/>
       <c r="F299" s="29" t="inlineStr">
         <is>
           <t>世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。</t>
@@ -17332,11 +16322,7 @@
           <t>세계유산 마을에는 주민분들이 생활하고 계십니다. 그래서 마을 안에 숙박하시는 분 외에는 오전 8시부터 오후 5시 사이에 관람해 주시기를 부탁드리고 있습니다. 마을에서 운영하는 주차장의 운영 시간도 오전 8시부터 오후 5시까지입니다. 라이트업 등 행사가 열리는 날은 제외합니다.</t>
         </is>
       </c>
-      <c r="E300" s="27" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E300" s="27" t="n"/>
       <c r="F300" s="29" t="inlineStr">
         <is>
           <t>世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。</t>
@@ -17369,11 +16355,7 @@
           <t>世界遗产村落里有居民生活。因此，除在村落内住宿的游客外，请在上午8点至下午5点之间参观。村营停车场的营业时间也是上午8点至下午5点。点灯等活动举办日除外。</t>
         </is>
       </c>
-      <c r="E301" s="30" t="inlineStr">
-        <is>
-          <t>自動翻訳（要確認）</t>
-        </is>
-      </c>
+      <c r="E301" s="30" t="n"/>
       <c r="F301" s="32" t="inlineStr">
         <is>
           <t>世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。</t>
@@ -17381,12 +16363,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="58" t="inlineStr">
+      <c r="A302" s="61" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="58" t="inlineStr">
+      <c r="B302" s="61" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17407,17 +16389,17 @@
       </c>
       <c r="E302" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。　人手で修正: Shirakawa‑gō → Shirakawa-go</t>
+          <t>人手で修正: Shirakawa‑gō → Shirakawa-go｜日本語原文: 身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="58" t="inlineStr">
+      <c r="A303" s="61" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="58" t="inlineStr">
+      <c r="B303" s="61" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17438,17 +16420,17 @@
       </c>
       <c r="E303" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
+          <t>日本語原文: 身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="58" t="inlineStr">
+      <c r="A304" s="61" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="58" t="inlineStr">
+      <c r="B304" s="61" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17469,17 +16451,17 @@
       </c>
       <c r="E304" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。　人手で修正: 백화고 → 시라카와고 / 엔です。 → 엔입니다.</t>
+          <t>人手で修正: 백화고 → 시라카와고 / 엔です。 → 엔입니다.｜日本語原文: 身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="58" t="inlineStr">
+      <c r="A305" s="61" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="58" t="inlineStr">
+      <c r="B305" s="61" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17500,17 +16482,17 @@
       </c>
       <c r="E305" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
+          <t>日本語原文: 身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="58" t="inlineStr">
+      <c r="A306" s="61" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="58" t="inlineStr">
+      <c r="B306" s="61" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17531,17 +16513,17 @@
       </c>
       <c r="E306" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
+          <t>日本語原文: 身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="58" t="inlineStr">
+      <c r="A307" s="61" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="58" t="inlineStr">
+      <c r="B307" s="61" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17562,17 +16544,17 @@
       </c>
       <c r="E307" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
+          <t>日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="58" t="inlineStr">
+      <c r="A308" s="61" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="58" t="inlineStr">
+      <c r="B308" s="61" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17593,17 +16575,17 @@
       </c>
       <c r="E308" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
+          <t>日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
         </is>
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="58" t="inlineStr">
+      <c r="A309" s="61" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="58" t="inlineStr">
+      <c r="B309" s="61" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17624,17 +16606,17 @@
       </c>
       <c r="E309" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
+          <t>日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="58" t="inlineStr">
+      <c r="A310" s="61" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="58" t="inlineStr">
+      <c r="B310" s="61" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17655,17 +16637,17 @@
       </c>
       <c r="E310" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
+          <t>日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="58" t="inlineStr">
+      <c r="A311" s="61" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="58" t="inlineStr">
+      <c r="B311" s="61" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17686,17 +16668,17 @@
       </c>
       <c r="E311" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
+          <t>日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="58" t="inlineStr">
+      <c r="A312" s="61" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="58" t="inlineStr">
+      <c r="B312" s="61" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17716,17 +16698,17 @@
       </c>
       <c r="E312" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。　人手で修正: Shirakawa‑gō → Shirakawa-go</t>
+          <t>人手で修正: Shirakawa‑gō → Shirakawa-go｜日本語原文: 高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="58" t="inlineStr">
+      <c r="A313" s="61" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="58" t="inlineStr">
+      <c r="B313" s="61" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17746,17 +16728,17 @@
       </c>
       <c r="E313" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
+          <t>日本語原文: 高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="58" t="inlineStr">
+      <c r="A314" s="61" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="58" t="inlineStr">
+      <c r="B314" s="61" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17776,17 +16758,17 @@
       </c>
       <c r="E314" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。　人手で修正: 백화고 → 시라카와고</t>
+          <t>人手で修正: 백화고 → 시라카와고｜日本語原文: 高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="58" t="inlineStr">
+      <c r="A315" s="61" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="58" t="inlineStr">
+      <c r="B315" s="61" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17806,17 +16788,17 @@
       </c>
       <c r="E315" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
+          <t>日本語原文: 高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="58" t="inlineStr">
+      <c r="A316" s="61" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="58" t="inlineStr">
+      <c r="B316" s="61" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17836,17 +16818,17 @@
       </c>
       <c r="E316" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
+          <t>日本語原文: 高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="58" t="inlineStr">
+      <c r="A317" s="61" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="58" t="inlineStr">
+      <c r="B317" s="61" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17867,17 +16849,17 @@
       </c>
       <c r="E317" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　人手で修正: Shirakawa‑gō → Shirakawa-go</t>
+          <t>人手で修正: Shirakawa‑gō → Shirakawa-go｜日本語原文: 外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="58" t="inlineStr">
+      <c r="A318" s="61" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="58" t="inlineStr">
+      <c r="B318" s="61" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17898,17 +16880,17 @@
       </c>
       <c r="E318" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。</t>
+          <t>日本語原文: 外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="58" t="inlineStr">
+      <c r="A319" s="61" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="58" t="inlineStr">
+      <c r="B319" s="61" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17929,17 +16911,17 @@
       </c>
       <c r="E319" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　人手で修正: 백화고 → 시라카와고</t>
+          <t>人手で修正: 백화고 → 시라카와고｜日本語原文: 外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="58" t="inlineStr">
+      <c r="A320" s="61" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="58" t="inlineStr">
+      <c r="B320" s="61" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17960,17 +16942,17 @@
       </c>
       <c r="E320" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。</t>
+          <t>日本語原文: 外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="58" t="inlineStr">
+      <c r="A321" s="61" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="58" t="inlineStr">
+      <c r="B321" s="61" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17991,17 +16973,17 @@
       </c>
       <c r="E321" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。</t>
+          <t>日本語原文: 外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="58" t="inlineStr">
+      <c r="A322" s="61" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="58" t="inlineStr">
+      <c r="B322" s="61" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18021,17 +17003,17 @@
       </c>
       <c r="E322" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　人手で修正: Shirakawa‑gō → Shirakawa-go</t>
+          <t>人手で修正: Shirakawa‑gō → Shirakawa-go｜日本語原文: 白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="58" t="inlineStr">
+      <c r="A323" s="61" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="58" t="inlineStr">
+      <c r="B323" s="61" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18051,17 +17033,17 @@
       </c>
       <c r="E323" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。</t>
+          <t>日本語原文: 白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="58" t="inlineStr">
+      <c r="A324" s="61" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="58" t="inlineStr">
+      <c r="B324" s="61" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18081,17 +17063,17 @@
       </c>
       <c r="E324" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　人手で修正: 백화고 → 시라카와고</t>
+          <t>人手で修正: 백화고 → 시라카와고｜日本語原文: 白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="58" t="inlineStr">
+      <c r="A325" s="61" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="58" t="inlineStr">
+      <c r="B325" s="61" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18111,17 +17093,17 @@
       </c>
       <c r="E325" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。</t>
+          <t>日本語原文: 白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。</t>
         </is>
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="58" t="inlineStr">
+      <c r="A326" s="61" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="58" t="inlineStr">
+      <c r="B326" s="61" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18141,17 +17123,17 @@
       </c>
       <c r="E326" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。</t>
+          <t>日本語原文: 白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。</t>
         </is>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="58" t="inlineStr">
+      <c r="A327" s="61" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="58" t="inlineStr">
+      <c r="B327" s="61" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18173,17 +17155,17 @@
       </c>
       <c r="E327" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　人手で修正: Shirakawago → Shirakawa-go</t>
+          <t>人手で修正: Shirakawago → Shirakawa-go｜日本語原文: そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。</t>
         </is>
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="58" t="inlineStr">
+      <c r="A328" s="61" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="58" t="inlineStr">
+      <c r="B328" s="61" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18205,17 +17187,17 @@
       </c>
       <c r="E328" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。</t>
+          <t>日本語原文: そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。</t>
         </is>
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="58" t="inlineStr">
+      <c r="A329" s="61" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="58" t="inlineStr">
+      <c r="B329" s="61" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18237,17 +17219,17 @@
       </c>
       <c r="E329" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　人手で修正: すみれ荘 → 스미레소(すみれ荘)</t>
+          <t>人手で修正: すみれ荘 → 스미레소(すみれ荘)｜日本語原文: そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。</t>
         </is>
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="58" t="inlineStr">
+      <c r="A330" s="61" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="58" t="inlineStr">
+      <c r="B330" s="61" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18269,17 +17251,17 @@
       </c>
       <c r="E330" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　人手で修正: Shirakawago → Shirakawa-go</t>
+          <t>人手で修正: Shirakawago → Shirakawa-go｜日本語原文: そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="58" t="inlineStr">
+      <c r="A331" s="61" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="58" t="inlineStr">
+      <c r="B331" s="61" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18301,17 +17283,17 @@
       </c>
       <c r="E331" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　人手で修正: Shirakawago → Shirakawa-go</t>
+          <t>人手で修正: Shirakawago → Shirakawa-go｜日本語原文: そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="58" t="inlineStr">
+      <c r="A332" s="61" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="58" t="inlineStr">
+      <c r="B332" s="61" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18333,17 +17315,17 @@
       </c>
       <c r="E332" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。</t>
+          <t>日本語原文: バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="58" t="inlineStr">
+      <c r="A333" s="61" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="58" t="inlineStr">
+      <c r="B333" s="61" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18365,17 +17347,17 @@
       </c>
       <c r="E333" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。</t>
+          <t>日本語原文: バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="58" t="inlineStr">
+      <c r="A334" s="61" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="58" t="inlineStr">
+      <c r="B334" s="61" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18397,17 +17379,17 @@
       </c>
       <c r="E334" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。</t>
+          <t>日本語原文: バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。</t>
         </is>
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="58" t="inlineStr">
+      <c r="A335" s="61" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="58" t="inlineStr">
+      <c r="B335" s="61" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18429,17 +17411,17 @@
       </c>
       <c r="E335" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。</t>
+          <t>日本語原文: バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。</t>
         </is>
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="58" t="inlineStr">
+      <c r="A336" s="61" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="58" t="inlineStr">
+      <c r="B336" s="61" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18461,17 +17443,17 @@
       </c>
       <c r="E336" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。</t>
+          <t>日本語原文: バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。</t>
         </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="58" t="inlineStr">
+      <c r="A337" s="61" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="58" t="inlineStr">
+      <c r="B337" s="61" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18493,17 +17475,17 @@
       </c>
       <c r="E337" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　人手で修正: Shirakawago → Shirakawa-go</t>
+          <t>人手で修正: Shirakawago → Shirakawa-go｜日本語原文: コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。</t>
         </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="58" t="inlineStr">
+      <c r="A338" s="61" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="58" t="inlineStr">
+      <c r="B338" s="61" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18525,17 +17507,17 @@
       </c>
       <c r="E338" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。</t>
+          <t>日本語原文: コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。</t>
         </is>
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="58" t="inlineStr">
+      <c r="A339" s="61" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="58" t="inlineStr">
+      <c r="B339" s="61" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18557,17 +17539,17 @@
       </c>
       <c r="E339" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　人手で修正: 백가와고 → 시라카와고 / であいの館 → 데아이노야카타</t>
+          <t>人手で修正: 백가와고 → 시라카와고 / であいの館 → 데아이노야카타｜日本語原文: コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。</t>
         </is>
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="58" t="inlineStr">
+      <c r="A340" s="61" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="58" t="inlineStr">
+      <c r="B340" s="61" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18589,17 +17571,17 @@
       </c>
       <c r="E340" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　人手で修正: Shirakawago → Shirakawa-go</t>
+          <t>人手で修正: Shirakawago → Shirakawa-go｜日本語原文: コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。</t>
         </is>
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="58" t="inlineStr">
+      <c r="A341" s="61" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="58" t="inlineStr">
+      <c r="B341" s="61" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18621,17 +17603,17 @@
       </c>
       <c r="E341" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　人手で修正: Shirakawago → Shirakawa-go</t>
+          <t>人手で修正: Shirakawago → Shirakawa-go｜日本語原文: コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。</t>
         </is>
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="58" t="inlineStr">
+      <c r="A342" s="61" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="58" t="inlineStr">
+      <c r="B342" s="61" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18653,17 +17635,17 @@
       </c>
       <c r="E342" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。　人手で修正: Shirakawago → Shirakawa-go / Shiroyama → Mt. Hakusan　※山の名前のローマ字・ハングル表記は要確認（三方岩岳・野谷荘司山・猪臥山）。白山は Hakusan に修正済み</t>
+          <t>人手で修正: Shirakawago → Shirakawa-go / Shiroyama → Mt. Hakusan　※山の名前のローマ字・ハングル表記は要確認（三方岩岳・野谷荘司山・猪臥山）。白山は Hakusan に修正済み｜日本語原文: 白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="58" t="inlineStr">
+      <c r="A343" s="61" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="58" t="inlineStr">
+      <c r="B343" s="61" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18685,17 +17667,17 @@
       </c>
       <c r="E343" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。　※山の名前のローマ字・ハングル表記は要確認（三方岩岳・野谷荘司山・猪臥山）。白山は Hakusan に修正済み</t>
+          <t>※山の名前のローマ字・ハングル表記は要確認（三方岩岳・野谷荘司山・猪臥山）。白山は Hakusan に修正済み｜日本語原文: 白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="58" t="inlineStr">
+      <c r="A344" s="61" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="58" t="inlineStr">
+      <c r="B344" s="61" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18717,17 +17699,17 @@
       </c>
       <c r="E344" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。　人手で修正: 백가와고 → 시라카와고 / 백산 → 하쿠산(白山)　※山の名前のローマ字・ハングル表記は要確認（三方岩岳・野谷荘司山・猪臥山）。白山は Hakusan に修正済み</t>
+          <t>人手で修正: 백가와고 → 시라카와고 / 백산 → 하쿠산(白山)　※山の名前のローマ字・ハングル表記は要確認（三方岩岳・野谷荘司山・猪臥山）。白山は Hakusan に修正済み｜日本語原文: 白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="58" t="inlineStr">
+      <c r="A345" s="61" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="58" t="inlineStr">
+      <c r="B345" s="61" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18749,17 +17731,17 @@
       </c>
       <c r="E345" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。　人手で修正: Shirakawago → Shirakawa-go / Shiroyama → el monte Hakusan　※山の名前のローマ字・ハングル表記は要確認（三方岩岳・野谷荘司山・猪臥山）。白山は Hakusan に修正済み</t>
+          <t>人手で修正: Shirakawago → Shirakawa-go / Shiroyama → el monte Hakusan　※山の名前のローマ字・ハングル表記は要確認（三方岩岳・野谷荘司山・猪臥山）。白山は Hakusan に修正済み｜日本語原文: 白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="58" t="inlineStr">
+      <c r="A346" s="61" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="58" t="inlineStr">
+      <c r="B346" s="61" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18781,17 +17763,17 @@
       </c>
       <c r="E346" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。　人手で修正: Shirakawago → Shirakawa-go / le mont Shiroyama → le mont Hakusan / Shiroyama → Hakusan　※山の名前のローマ字・ハングル表記は要確認（三方岩岳・野谷荘司山・猪臥山）。白山は Hakusan に修正済み</t>
+          <t>人手で修正: Shirakawago → Shirakawa-go / le mont Shiroyama → le mont Hakusan / Shiroyama → Hakusan　※山の名前のローマ字・ハングル表記は要確認（三方岩岳・野谷荘司山・猪臥山）。白山は Hakusan に修正済み｜日本語原文: 白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="58" t="inlineStr">
+      <c r="A347" s="61" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="58" t="inlineStr">
+      <c r="B347" s="61" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18813,17 +17795,17 @@
       </c>
       <c r="E347" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。</t>
+          <t>日本語原文: 展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。</t>
         </is>
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="58" t="inlineStr">
+      <c r="A348" s="61" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="58" t="inlineStr">
+      <c r="B348" s="61" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18845,17 +17827,17 @@
       </c>
       <c r="E348" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。</t>
+          <t>日本語原文: 展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。</t>
         </is>
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="58" t="inlineStr">
+      <c r="A349" s="61" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="58" t="inlineStr">
+      <c r="B349" s="61" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18877,17 +17859,17 @@
       </c>
       <c r="E349" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。</t>
+          <t>日本語原文: 展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="58" t="inlineStr">
+      <c r="A350" s="61" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="58" t="inlineStr">
+      <c r="B350" s="61" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18909,17 +17891,17 @@
       </c>
       <c r="E350" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。</t>
+          <t>日本語原文: 展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。</t>
         </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="58" t="inlineStr">
+      <c r="A351" s="61" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="58" t="inlineStr">
+      <c r="B351" s="61" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18941,17 +17923,17 @@
       </c>
       <c r="E351" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。</t>
+          <t>日本語原文: 展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。</t>
         </is>
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="58" t="inlineStr">
+      <c r="A352" s="61" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="58" t="inlineStr">
+      <c r="B352" s="61" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18972,17 +17954,17 @@
       </c>
       <c r="E352" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
+          <t>日本語原文: 集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="58" t="inlineStr">
+      <c r="A353" s="61" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="58" t="inlineStr">
+      <c r="B353" s="61" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -19003,17 +17985,17 @@
       </c>
       <c r="E353" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
+          <t>日本語原文: 集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="58" t="inlineStr">
+      <c r="A354" s="61" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="58" t="inlineStr">
+      <c r="B354" s="61" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -19034,17 +18016,17 @@
       </c>
       <c r="E354" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
+          <t>日本語原文: 集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="58" t="inlineStr">
+      <c r="A355" s="61" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="58" t="inlineStr">
+      <c r="B355" s="61" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -19065,17 +18047,17 @@
       </c>
       <c r="E355" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
+          <t>日本語原文: 集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="58" t="inlineStr">
+      <c r="A356" s="61" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="58" t="inlineStr">
+      <c r="B356" s="61" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -19096,17 +18078,17 @@
       </c>
       <c r="E356" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
+          <t>日本語原文: 集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="58" t="inlineStr">
+      <c r="A357" s="61" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="58" t="inlineStr">
+      <c r="B357" s="61" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -19127,17 +18109,17 @@
       </c>
       <c r="E357" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　人手で修正: Shirakawa‑gō → Shirakawa-go</t>
+          <t>人手で修正: Shirakawa‑gō → Shirakawa-go｜日本語原文: 記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="58" t="inlineStr">
+      <c r="A358" s="61" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="58" t="inlineStr">
+      <c r="B358" s="61" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -19158,17 +18140,17 @@
       </c>
       <c r="E358" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。</t>
+          <t>日本語原文: 記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。</t>
         </is>
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="58" t="inlineStr">
+      <c r="A359" s="61" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="58" t="inlineStr">
+      <c r="B359" s="61" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -19189,17 +18171,17 @@
       </c>
       <c r="E359" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　人手で修正: 백가고 → 시라카와고 / 데아이노칸 → 데아이노야카타 / 御朱印 → 고슈인(御朱印)</t>
+          <t>人手で修正: 백가고 → 시라카와고 / 데아이노칸 → 데아이노야카타 / 御朱印 → 고슈인(御朱印)｜日本語原文: 記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。</t>
         </is>
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="58" t="inlineStr">
+      <c r="A360" s="61" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="58" t="inlineStr">
+      <c r="B360" s="61" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -19220,17 +18202,17 @@
       </c>
       <c r="E360" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。</t>
+          <t>日本語原文: 記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。</t>
         </is>
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="58" t="inlineStr">
+      <c r="A361" s="61" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="58" t="inlineStr">
+      <c r="B361" s="61" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -19251,17 +18233,17 @@
       </c>
       <c r="E361" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。</t>
+          <t>日本語原文: 記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。</t>
         </is>
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="58" t="inlineStr">
+      <c r="A362" s="61" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="58" t="inlineStr">
+      <c r="B362" s="61" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -19283,17 +18265,17 @@
       </c>
       <c r="E362" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
+          <t>日本語原文: 寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="58" t="inlineStr">
+      <c r="A363" s="61" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="58" t="inlineStr">
+      <c r="B363" s="61" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -19315,17 +18297,17 @@
       </c>
       <c r="E363" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
+          <t>日本語原文: 寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="58" t="inlineStr">
+      <c r="A364" s="61" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="58" t="inlineStr">
+      <c r="B364" s="61" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -19347,17 +18329,17 @@
       </c>
       <c r="E364" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
+          <t>日本語原文: 寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="58" t="inlineStr">
+      <c r="A365" s="61" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="58" t="inlineStr">
+      <c r="B365" s="61" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -19379,17 +18361,17 @@
       </c>
       <c r="E365" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
+          <t>日本語原文: 寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="58" t="inlineStr">
+      <c r="A366" s="61" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="58" t="inlineStr">
+      <c r="B366" s="61" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -19411,17 +18393,17 @@
       </c>
       <c r="E366" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
+          <t>日本語原文: 寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="58" t="inlineStr">
+      <c r="A367" s="61" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="58" t="inlineStr">
+      <c r="B367" s="61" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -19443,17 +18425,17 @@
       </c>
       <c r="E367" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。　人手で修正: Shirakawa‑gō → Shirakawa-go / Roadside Station Shirakawa-go → Michi-no-Eki Shirakawa-go roadside station</t>
+          <t>人手で修正: Shirakawa‑gō → Shirakawa-go / Roadside Station Shirakawa-go → Michi-no-Eki Shirakawa-go roadside station｜日本語原文: 結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="58" t="inlineStr">
+      <c r="A368" s="61" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="58" t="inlineStr">
+      <c r="B368" s="61" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -19475,17 +18457,17 @@
       </c>
       <c r="E368" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
+          <t>日本語原文: 結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="58" t="inlineStr">
+      <c r="A369" s="61" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="58" t="inlineStr">
+      <c r="B369" s="61" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -19507,17 +18489,17 @@
       </c>
       <c r="E369" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。　人手で修正: 백가고 → 시라카와고 / 도로역 → 미치노에키(道の駅)</t>
+          <t>人手で修正: 백가고 → 시라카와고 / 도로역 → 미치노에키(道の駅)｜日本語原文: 結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="58" t="inlineStr">
+      <c r="A370" s="61" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="58" t="inlineStr">
+      <c r="B370" s="61" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -19539,17 +18521,17 @@
       </c>
       <c r="E370" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
+          <t>日本語原文: 結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="58" t="inlineStr">
+      <c r="A371" s="61" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="58" t="inlineStr">
+      <c r="B371" s="61" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -19571,7 +18553,7 @@
       </c>
       <c r="E371" s="46" t="inlineStr">
         <is>
-          <t>自動翻訳（要確認）｜日本語原文: 結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
+          <t>日本語原文: 結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
     </row>
@@ -20707,7 +19689,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -20717,7 +19699,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="58" t="inlineStr">
+      <c r="C2" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20729,7 +19711,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="58" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -20739,7 +19721,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="58" t="inlineStr">
+      <c r="C3" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20751,7 +19733,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="58" t="inlineStr">
+      <c r="A4" s="61" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -20761,7 +19743,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="58" t="inlineStr">
+      <c r="C4" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20773,7 +19755,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="58" t="inlineStr">
+      <c r="A5" s="61" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -20783,7 +19765,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="58" t="inlineStr">
+      <c r="C5" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20795,7 +19777,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="58" t="inlineStr">
+      <c r="A6" s="61" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20805,7 +19787,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="58" t="inlineStr">
+      <c r="C6" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20817,7 +19799,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="58" t="inlineStr">
+      <c r="A7" s="61" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20827,7 +19809,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="58" t="inlineStr">
+      <c r="C7" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20839,7 +19821,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20849,7 +19831,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="58" t="inlineStr">
+      <c r="C8" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20861,7 +19843,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="58" t="inlineStr">
+      <c r="A9" s="61" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20871,7 +19853,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="58" t="inlineStr">
+      <c r="C9" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20883,7 +19865,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="58" t="inlineStr">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20893,7 +19875,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="58" t="inlineStr">
+      <c r="C10" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20905,7 +19887,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="58" t="inlineStr">
+      <c r="A11" s="61" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20915,7 +19897,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="58" t="inlineStr">
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20927,7 +19909,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="58" t="inlineStr">
+      <c r="A12" s="61" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20937,7 +19919,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="58" t="inlineStr">
+      <c r="C12" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20949,7 +19931,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="58" t="inlineStr">
+      <c r="A13" s="61" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20959,7 +19941,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="58" t="inlineStr">
+      <c r="C13" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -21071,53 +20053,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="58" t="inlineStr">
+      <c r="B2" s="61" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="58" t="inlineStr">
+      <c r="C2" s="61" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="58" t="inlineStr">
+      <c r="D2" s="61" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="58" t="inlineStr">
+      <c r="E2" s="61" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="58" t="inlineStr">
+      <c r="F2" s="61" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="58" t="inlineStr">
+      <c r="G2" s="61" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="58" t="inlineStr">
+      <c r="H2" s="61" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="58" t="inlineStr">
+      <c r="I2" s="61" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="58" t="n"/>
-      <c r="K2" s="58" t="inlineStr">
+      <c r="J2" s="61" t="n"/>
+      <c r="K2" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -21129,199 +20111,195 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="58" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="58" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="58" t="inlineStr">
+      <c r="C3" s="61" t="inlineStr">
         <is>
           <t>main.png</t>
         </is>
       </c>
-      <c r="D3" s="58" t="n"/>
-      <c r="E3" s="58" t="n"/>
-      <c r="F3" s="58" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="G3" s="58" t="inlineStr">
+      <c r="D3" s="61" t="n"/>
+      <c r="E3" s="61" t="n"/>
+      <c r="F3" s="61" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G3" s="61" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H3" s="61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I3" s="61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" s="61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K3" s="61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L3" s="46" t="inlineStr">
+        <is>
+          <t>白川郷のメイン。表情差分なし。名前は仮（「結」から）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="61" t="inlineStr">
+        <is>
+          <t>がっしょくん</t>
+        </is>
+      </c>
+      <c r="B4" s="61" t="inlineStr">
+        <is>
+          <t>yuru</t>
+        </is>
+      </c>
+      <c r="C4" s="61" t="inlineStr">
+        <is>
+          <t>yuru.png</t>
+        </is>
+      </c>
+      <c r="D4" s="61" t="n"/>
+      <c r="E4" s="61" t="n"/>
+      <c r="F4" s="61" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="G4" s="61" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H4" s="61" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="I4" s="61" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="J4" s="61" t="n"/>
+      <c r="K4" s="61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L4" s="46" t="inlineStr">
+        <is>
+          <t>ゆるキャラ。表情差分なし。名前は仮</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="61" t="inlineStr">
+        <is>
+          <t>やねくん</t>
+        </is>
+      </c>
+      <c r="B5" s="61" t="inlineStr">
+        <is>
+          <t>yane</t>
+        </is>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>2.png</t>
+        </is>
+      </c>
+      <c r="D5" s="61" t="n"/>
+      <c r="E5" s="61" t="n"/>
+      <c r="F5" s="61" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="G5" s="61" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H5" s="61" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="H3" s="58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" s="58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" s="58" t="inlineStr">
+      <c r="I5" s="61" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="J5" s="61" t="n"/>
+      <c r="K5" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="58" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="L3" s="46" t="inlineStr">
-        <is>
-          <t>白川郷のメイン。表情差分なし。名前は仮（「結」から）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="58" t="inlineStr">
-        <is>
-          <t>がっしょくん</t>
-        </is>
-      </c>
-      <c r="B4" s="58" t="inlineStr">
-        <is>
-          <t>yuru</t>
-        </is>
-      </c>
-      <c r="C4" s="58" t="inlineStr">
-        <is>
-          <t>yuru.png</t>
-        </is>
-      </c>
-      <c r="D4" s="58" t="n"/>
-      <c r="E4" s="58" t="n"/>
-      <c r="F4" s="58" t="inlineStr">
+      <c r="L5" s="46" t="inlineStr">
+        <is>
+          <t>看板風。名前は仮。キャラクターとして使わないなら有効をFALSEに</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="61" t="inlineStr">
+        <is>
+          <t>ごうちゃん</t>
+        </is>
+      </c>
+      <c r="B6" s="61" t="inlineStr">
+        <is>
+          <t>gou</t>
+        </is>
+      </c>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>4.png</t>
+        </is>
+      </c>
+      <c r="D6" s="61" t="n"/>
+      <c r="E6" s="61" t="n"/>
+      <c r="F6" s="61" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="58" t="inlineStr">
+      <c r="G6" s="61" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="58" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="I4" s="58" t="inlineStr">
+      <c r="H6" s="61" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="I6" s="61" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="58" t="n"/>
-      <c r="K4" s="58" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="L4" s="46" t="inlineStr">
-        <is>
-          <t>ゆるキャラ。表情差分なし。名前は仮</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="58" t="inlineStr">
-        <is>
-          <t>やねくん</t>
-        </is>
-      </c>
-      <c r="B5" s="58" t="inlineStr">
-        <is>
-          <t>yane</t>
-        </is>
-      </c>
-      <c r="C5" s="58" t="inlineStr">
-        <is>
-          <t>2.png</t>
-        </is>
-      </c>
-      <c r="D5" s="58" t="n"/>
-      <c r="E5" s="58" t="n"/>
-      <c r="F5" s="58" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="G5" s="58" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H5" s="58" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="I5" s="58" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="J5" s="58" t="n"/>
-      <c r="K5" s="58" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="L5" s="46" t="inlineStr">
-        <is>
-          <t>看板風。名前は仮。キャラクターとして使わないなら有効をFALSEに</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="58" t="inlineStr">
-        <is>
-          <t>ごうちゃん</t>
-        </is>
-      </c>
-      <c r="B6" s="58" t="inlineStr">
-        <is>
-          <t>gou</t>
-        </is>
-      </c>
-      <c r="C6" s="58" t="inlineStr">
-        <is>
-          <t>4.png</t>
-        </is>
-      </c>
-      <c r="D6" s="58" t="n"/>
-      <c r="E6" s="58" t="n"/>
-      <c r="F6" s="58" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="G6" s="58" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H6" s="58" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="I6" s="58" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="J6" s="58" t="n"/>
-      <c r="K6" s="58" t="inlineStr">
+      <c r="J6" s="61" t="n"/>
+      <c r="K6" s="61" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -21350,173 +20328,231 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="48" t="inlineStr">
         <is>
-          <t>言語</t>
+          <t>設置場所</t>
         </is>
       </c>
       <c r="B1" s="48" t="inlineStr">
         <is>
-          <t>優先する声</t>
+          <t>並び順</t>
         </is>
       </c>
       <c r="C1" s="48" t="inlineStr">
         <is>
-          <t>速さ</t>
+          <t>よくある質問の高さ</t>
         </is>
       </c>
       <c r="D1" s="48" t="inlineStr">
         <is>
-          <t>高さ</t>
+          <t>入力欄の高さ</t>
         </is>
       </c>
       <c r="E1" s="48" t="inlineStr">
         <is>
+          <t>話すボタンの高さ</t>
+        </is>
+      </c>
+      <c r="F1" s="48" t="inlineStr">
+        <is>
+          <t>言語の高さ</t>
+        </is>
+      </c>
+      <c r="G1" s="48" t="inlineStr">
+        <is>
+          <t>キャラクターの大きさ</t>
+        </is>
+      </c>
+      <c r="H1" s="48" t="inlineStr">
+        <is>
+          <t>キャラクターの高さ位置</t>
+        </is>
+      </c>
+      <c r="I1" s="48" t="inlineStr">
+        <is>
+          <t>キャラクターの左右位置</t>
+        </is>
+      </c>
+      <c r="J1" s="48" t="inlineStr">
+        <is>
+          <t>吹き出しの幅</t>
+        </is>
+      </c>
+      <c r="K1" s="48" t="inlineStr">
+        <is>
+          <t>文字の大きさ</t>
+        </is>
+      </c>
+      <c r="L1" s="48" t="inlineStr">
+        <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
-        <is>
-          <t>ja</t>
+      <c r="A2" s="61" t="inlineStr">
+        <is>
+          <t>バスターミナル</t>
         </is>
       </c>
       <c r="B2" s="46" t="inlineStr">
         <is>
-          <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
-        </is>
-      </c>
-      <c r="C2" s="58" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D2" s="58" t="n">
+          <t>stage,faq,talk,languages</t>
+        </is>
+      </c>
+      <c r="C2" s="61" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D2" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="61" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F2" s="61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G2" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="46" t="inlineStr">
-        <is>
-          <t>Androidアプリで使っていたのと同じ「Google 日本語」を先頭にしている</t>
+      <c r="H2" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="61" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K2" s="61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L2" s="46" t="inlineStr">
+        <is>
+          <t>据え置きのタブレット。話すボタンを大きく、入力欄は出さない</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="58" t="inlineStr">
-        <is>
-          <t>en</t>
+      <c r="A3" s="61" t="inlineStr">
+        <is>
+          <t>であいの館</t>
         </is>
       </c>
       <c r="B3" s="46" t="inlineStr">
         <is>
-          <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
-        </is>
-      </c>
-      <c r="C3" s="58" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D3" s="58" t="n">
+          <t>stage,faq,talk,languages</t>
+        </is>
+      </c>
+      <c r="C3" s="61" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D3" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="61" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F3" s="61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="46" t="inlineStr"/>
+      <c r="H3" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="61" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K3" s="61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L3" s="46" t="inlineStr">
+        <is>
+          <t>据え置きのタブレット。バスターミナルと同じ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="58" t="inlineStr">
-        <is>
-          <t>zh</t>
+      <c r="A4" s="61" t="inlineStr">
+        <is>
+          <t>観光客</t>
         </is>
       </c>
       <c r="B4" s="46" t="inlineStr">
         <is>
-          <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
-        </is>
-      </c>
-      <c r="C4" s="58" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D4" s="58" t="n">
+          <t>stage,faq,typed,talk,languages</t>
+        </is>
+      </c>
+      <c r="C4" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="46" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="58" t="inlineStr">
-        <is>
-          <t>ko</t>
-        </is>
-      </c>
-      <c r="B5" s="46" t="inlineStr">
-        <is>
-          <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
-        </is>
-      </c>
-      <c r="C5" s="58" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D5" s="58" t="n">
+      <c r="H4" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="46" t="inlineStr"/>
+      <c r="L4" s="46" t="inlineStr">
+        <is>
+          <t>観光客のスマートフォン。0は「決めない」＝中身なりの大きさ</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="58" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
-      <c r="B6" s="46" t="inlineStr">
-        <is>
-          <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
-        </is>
-      </c>
-      <c r="C6" s="58" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D6" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="46" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="58" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="B7" s="46" t="inlineStr">
-        <is>
-          <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
-        </is>
-      </c>
-      <c r="C7" s="58" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D7" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="46" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="59" t="inlineStr">
-        <is>
-          <t>※ 「優先する声」は上から順に探し、その端末に入っている最初の声を使います。名前の一部が合えば採用します（「Microsoft Aria - English (United States)」に「Microsoft Aria」で当たります）。どれも入っていない端末では、その言語の声から自動で選びます。速さは1.0が標準、小さいほどゆっくり。高さは1.0が標準、大きいほど高い声になります。</t>
-        </is>
-      </c>
-    </row>
+      <c r="A6" s="59" t="inlineStr">
+        <is>
+          <t>※ 設置場所は、案内アプリのURLに付ける名前と同じにしてください（?place=バスターミナル なら「バスターミナル」）。観光客の端末は「観光客」です。「共通」と書いた行は、合う行が無いときに使われます。　並び順は、出すブロックをカンマで区切って上から順に書きます（stage=会話領域 / faq=よくある質問 / typed=文字で質問する / talk=話すボタン / languages=言語）。書かなかったブロックは出ません。　高さは画面の高さに対する割合（0.15なら15%）。0は「決めない」で、中身なりの高さになります。　キャラクターの大きさは倍率（1.0が「キャラクター」シートのまま）、高さ位置は0が下端・1が上端、左右位置は0が右端・1が左端です。　この表は管理画面の「画面レイアウト」から、画面を見ながら動かして決められます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10"/>
-    <row r="11"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:E11"/>
+    <mergeCell ref="A6:L10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20415,7 +20415,7 @@
       </c>
       <c r="B2" s="46" t="inlineStr">
         <is>
-          <t>stage,faq,talk,languages</t>
+          <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
       <c r="C2" s="61" t="n">
@@ -20539,6 +20539,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="59" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20415,7 +20415,7 @@
       </c>
       <c r="B2" s="46" t="inlineStr">
         <is>
-          <t>stage,faq,typed,talk,languages</t>
+          <t>stage,faq,talk,languages</t>
         </is>
       </c>
       <c r="C2" s="61" t="n">

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20415,7 +20415,7 @@
       </c>
       <c r="B2" s="46" t="inlineStr">
         <is>
-          <t>stage,faq,talk,languages</t>
+          <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
       <c r="C2" s="61" t="n">

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20463,7 +20463,7 @@
         </is>
       </c>
       <c r="C3" s="61" t="n">
-        <v>0.09</v>
+        <v>0.066</v>
       </c>
       <c r="D3" s="61" t="n">
         <v>0</v>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20440,7 +20440,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="61" t="n">
-        <v>0.46</v>
+        <v>0.664</v>
       </c>
       <c r="K2" s="61" t="n">
         <v>1.1</v>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20484,7 +20484,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="61" t="n">
-        <v>0.46</v>
+        <v>0.738</v>
       </c>
       <c r="K3" s="61" t="n">
         <v>1.1</v>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20481,10 +20481,10 @@
         <v>0</v>
       </c>
       <c r="I3" s="61" t="n">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="J3" s="61" t="n">
-        <v>0.738</v>
+        <v>0.85</v>
       </c>
       <c r="K3" s="61" t="n">
         <v>1.1</v>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20459,7 +20459,7 @@
       </c>
       <c r="B3" s="46" t="inlineStr">
         <is>
-          <t>stage,faq,talk,languages</t>
+          <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
       <c r="C3" s="61" t="n">

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20459,7 +20459,7 @@
       </c>
       <c r="B3" s="46" t="inlineStr">
         <is>
-          <t>stage,faq,typed,talk,languages</t>
+          <t>stage,faq,talk,languages</t>
         </is>
       </c>
       <c r="C3" s="61" t="n">

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -19617,11 +19617,7 @@
           <t>VOICEVOXで作成。設置で使う場合はクレジット表記が必要</t>
         </is>
       </c>
-      <c r="F2" s="57" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="F2" s="57" t="n"/>
     </row>
     <row r="3" ht="32.4" customHeight="1">
       <c r="A3" s="41" t="inlineStr">
@@ -19643,6 +19639,11 @@
       <c r="E3" s="42" t="inlineStr">
         <is>
           <t>VOICEVOXで作成。設置で使う場合はクレジット表記が必要</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20540,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="59" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -19617,7 +19617,11 @@
           <t>VOICEVOXで作成。設置で使う場合はクレジット表記が必要</t>
         </is>
       </c>
-      <c r="F2" s="57" t="n"/>
+      <c r="F2" s="57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="32.4" customHeight="1">
       <c r="A3" s="41" t="inlineStr">
@@ -19639,11 +19643,6 @@
       <c r="E3" s="42" t="inlineStr">
         <is>
           <t>VOICEVOXで作成。設置で使う場合はクレジット表記が必要</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
     </row>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20484,7 +20484,7 @@
         <v>0.145</v>
       </c>
       <c r="J3" s="61" t="n">
-        <v>0.85</v>
+        <v>0.636</v>
       </c>
       <c r="K3" s="61" t="n">
         <v>1.1</v>
@@ -20539,6 +20539,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="59" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20484,7 +20484,7 @@
         <v>0.145</v>
       </c>
       <c r="J3" s="61" t="n">
-        <v>0.636</v>
+        <v>0.303</v>
       </c>
       <c r="K3" s="61" t="n">
         <v>1.1</v>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -19975,7 +19975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19988,6 +19988,11 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20051,6 +20056,31 @@
           <t>備考</t>
         </is>
       </c>
+      <c r="M1" s="48" t="inlineStr">
+        <is>
+          <t>名前（英語）</t>
+        </is>
+      </c>
+      <c r="N1" s="48" t="inlineStr">
+        <is>
+          <t>名前（中国語）</t>
+        </is>
+      </c>
+      <c r="O1" s="48" t="inlineStr">
+        <is>
+          <t>名前（韓国語）</t>
+        </is>
+      </c>
+      <c r="P1" s="48" t="inlineStr">
+        <is>
+          <t>名前（スペイン語）</t>
+        </is>
+      </c>
+      <c r="Q1" s="48" t="inlineStr">
+        <is>
+          <t>名前（フランス語）</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="61" t="inlineStr">
@@ -20107,6 +20137,31 @@
       <c r="L2" s="46" t="inlineStr">
         <is>
           <t>表情が3枚ある案内役。これまで使っていたもの</t>
+        </is>
+      </c>
+      <c r="M2" s="57" t="inlineStr">
+        <is>
+          <t>Navi</t>
+        </is>
+      </c>
+      <c r="N2" s="57" t="inlineStr">
+        <is>
+          <t>小导</t>
+        </is>
+      </c>
+      <c r="O2" s="57" t="inlineStr">
+        <is>
+          <t>나비</t>
+        </is>
+      </c>
+      <c r="P2" s="57" t="inlineStr">
+        <is>
+          <t>Navi</t>
+        </is>
+      </c>
+      <c r="Q2" s="57" t="inlineStr">
+        <is>
+          <t>Navi</t>
         </is>
       </c>
     </row>
@@ -20159,6 +20214,31 @@
           <t>白川郷のメイン。表情差分なし。名前は仮（「結」から）</t>
         </is>
       </c>
+      <c r="M3" s="57" t="inlineStr">
+        <is>
+          <t>Yui</t>
+        </is>
+      </c>
+      <c r="N3" s="57" t="inlineStr">
+        <is>
+          <t>结衣</t>
+        </is>
+      </c>
+      <c r="O3" s="57" t="inlineStr">
+        <is>
+          <t>유이</t>
+        </is>
+      </c>
+      <c r="P3" s="57" t="inlineStr">
+        <is>
+          <t>Yui</t>
+        </is>
+      </c>
+      <c r="Q3" s="57" t="inlineStr">
+        <is>
+          <t>Yui</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="61" t="inlineStr">
@@ -20209,6 +20289,31 @@
           <t>ゆるキャラ。表情差分なし。名前は仮</t>
         </is>
       </c>
+      <c r="M4" s="57" t="inlineStr">
+        <is>
+          <t>Gassho-kun</t>
+        </is>
+      </c>
+      <c r="N4" s="57" t="inlineStr">
+        <is>
+          <t>合掌君</t>
+        </is>
+      </c>
+      <c r="O4" s="57" t="inlineStr">
+        <is>
+          <t>갓쇼 군</t>
+        </is>
+      </c>
+      <c r="P4" s="57" t="inlineStr">
+        <is>
+          <t>Gassho-kun</t>
+        </is>
+      </c>
+      <c r="Q4" s="57" t="inlineStr">
+        <is>
+          <t>Gassho-kun</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="61" t="inlineStr">
@@ -20259,6 +20364,31 @@
           <t>看板風。名前は仮。キャラクターとして使わないなら有効をFALSEに</t>
         </is>
       </c>
+      <c r="M5" s="57" t="inlineStr">
+        <is>
+          <t>Yane-kun</t>
+        </is>
+      </c>
+      <c r="N5" s="57" t="inlineStr">
+        <is>
+          <t>屋顶君</t>
+        </is>
+      </c>
+      <c r="O5" s="57" t="inlineStr">
+        <is>
+          <t>야네 군</t>
+        </is>
+      </c>
+      <c r="P5" s="57" t="inlineStr">
+        <is>
+          <t>Yane-kun</t>
+        </is>
+      </c>
+      <c r="Q5" s="57" t="inlineStr">
+        <is>
+          <t>Yane-kun</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="61" t="inlineStr">
@@ -20309,7 +20439,33 @@
           <t>看板風。名前は仮。キャラクターとして使わないなら有効をFALSEに</t>
         </is>
       </c>
-    </row>
+      <c r="M6" s="57" t="inlineStr">
+        <is>
+          <t>Go-chan</t>
+        </is>
+      </c>
+      <c r="N6" s="57" t="inlineStr">
+        <is>
+          <t>小乡</t>
+        </is>
+      </c>
+      <c r="O6" s="57" t="inlineStr">
+        <is>
+          <t>고 짱</t>
+        </is>
+      </c>
+      <c r="P6" s="57" t="inlineStr">
+        <is>
+          <t>Go-chan</t>
+        </is>
+      </c>
+      <c r="Q6" s="57" t="inlineStr">
+        <is>
+          <t>Go-chan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="52" t="inlineStr">
         <is>
@@ -20539,7 +20695,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="59" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -1300,7 +1300,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D3" s="46" t="inlineStr"/>
+      <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="61" t="inlineStr">
@@ -1362,7 +1362,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D6" s="46" t="inlineStr"/>
+      <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="61" t="inlineStr">
@@ -1380,7 +1380,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D7" s="46" t="inlineStr"/>
+      <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="61" t="inlineStr">
@@ -1464,7 +1464,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr"/>
+      <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="61" t="inlineStr">
@@ -1482,7 +1482,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D12" s="46" t="inlineStr"/>
+      <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="61" t="inlineStr">
@@ -1632,7 +1632,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D19" s="46" t="inlineStr"/>
+      <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="61" t="inlineStr">
@@ -1650,7 +1650,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D20" s="46" t="inlineStr"/>
+      <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="61" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B22" s="61" t="inlineStr">
         <is>
-          <t>ホオバミソ</t>
+          <t>ホウバミソ</t>
         </is>
       </c>
       <c r="C22" s="61" t="inlineStr">
@@ -1756,7 +1756,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D25" s="46" t="inlineStr"/>
+      <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="61" t="inlineStr">
@@ -1774,7 +1774,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D26" s="46" t="inlineStr"/>
+      <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="61" t="inlineStr">
@@ -1858,7 +1858,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D30" s="46" t="inlineStr"/>
+      <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="61" t="inlineStr">
@@ -1898,7 +1898,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D32" s="46" t="inlineStr"/>
+      <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="61" t="inlineStr">
@@ -1916,7 +1916,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D33" s="46" t="inlineStr"/>
+      <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="61" t="inlineStr">
@@ -1934,7 +1934,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D34" s="46" t="inlineStr"/>
+      <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="61" t="inlineStr">
@@ -1952,7 +1952,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D35" s="46" t="inlineStr"/>
+      <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="61" t="inlineStr">
@@ -1970,7 +1970,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D36" s="46" t="inlineStr"/>
+      <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="61" t="inlineStr">
@@ -1988,7 +1988,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D37" s="46" t="inlineStr"/>
+      <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="61" t="inlineStr">
@@ -2006,7 +2006,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D38" s="46" t="inlineStr"/>
+      <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="61" t="inlineStr">
@@ -2024,7 +2024,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D39" s="46" t="inlineStr"/>
+      <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="61" t="inlineStr">
@@ -2064,7 +2064,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D41" s="46" t="inlineStr"/>
+      <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="61" t="inlineStr">
@@ -2104,7 +2104,7 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D43" s="46" t="inlineStr"/>
+      <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="61" t="inlineStr">
@@ -2144,8 +2144,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D45" s="46" t="inlineStr"/>
-    </row>
+      <c r="D45" s="46" t="n"/>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="59" t="inlineStr">
         <is>
@@ -20465,7 +20466,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="52" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -14,9 +14,10 @@
     <sheet name="音声セット" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="参考資料" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="キャラクター" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="画面レイアウト" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="読み上げ" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="読み方" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="会話" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="画面レイアウト" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="読み上げ" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="読み方" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FAQ'!$A$1:$J$18</definedName>
@@ -268,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -426,6 +427,18 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -1053,6 +1066,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="48" t="inlineStr">
+        <is>
+          <t>設置場所</t>
+        </is>
+      </c>
+      <c r="B1" s="48" t="inlineStr">
+        <is>
+          <t>並び順</t>
+        </is>
+      </c>
+      <c r="C1" s="48" t="inlineStr">
+        <is>
+          <t>よくある質問の高さ</t>
+        </is>
+      </c>
+      <c r="D1" s="48" t="inlineStr">
+        <is>
+          <t>入力欄の高さ</t>
+        </is>
+      </c>
+      <c r="E1" s="48" t="inlineStr">
+        <is>
+          <t>話すボタンの高さ</t>
+        </is>
+      </c>
+      <c r="F1" s="48" t="inlineStr">
+        <is>
+          <t>言語の高さ</t>
+        </is>
+      </c>
+      <c r="G1" s="48" t="inlineStr">
+        <is>
+          <t>キャラクターの大きさ</t>
+        </is>
+      </c>
+      <c r="H1" s="48" t="inlineStr">
+        <is>
+          <t>キャラクターの高さ位置</t>
+        </is>
+      </c>
+      <c r="I1" s="48" t="inlineStr">
+        <is>
+          <t>キャラクターの左右位置</t>
+        </is>
+      </c>
+      <c r="J1" s="48" t="inlineStr">
+        <is>
+          <t>吹き出しの幅</t>
+        </is>
+      </c>
+      <c r="K1" s="48" t="inlineStr">
+        <is>
+          <t>文字の大きさ</t>
+        </is>
+      </c>
+      <c r="L1" s="48" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="64" t="inlineStr">
+        <is>
+          <t>バスターミナル</t>
+        </is>
+      </c>
+      <c r="B2" s="46" t="inlineStr">
+        <is>
+          <t>stage,faq,talk,languages</t>
+        </is>
+      </c>
+      <c r="C2" s="64" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D2" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="64" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F2" s="64" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G2" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="64" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="K2" s="64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L2" s="46" t="inlineStr">
+        <is>
+          <t>据え置きのタブレット。話すボタンを大きく、入力欄は出さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="64" t="inlineStr">
+        <is>
+          <t>であいの館</t>
+        </is>
+      </c>
+      <c r="B3" s="46" t="inlineStr">
+        <is>
+          <t>stage,faq,talk,languages</t>
+        </is>
+      </c>
+      <c r="C3" s="64" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="D3" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="64" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F3" s="64" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="64" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="J3" s="64" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="K3" s="64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L3" s="46" t="inlineStr">
+        <is>
+          <t>据え置きのタブレット。バスターミナルと同じ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="64" t="inlineStr">
+        <is>
+          <t>観光客</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>stage,faq,typed,talk,languages</t>
+        </is>
+      </c>
+      <c r="C4" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="46" t="inlineStr">
+        <is>
+          <t>観光客のスマートフォン。0は「決めない」＝中身なりの大きさ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="59" t="inlineStr">
+        <is>
+          <t>※ 設置場所は、案内アプリのURLに付ける名前と同じにしてください（?place=バスターミナル なら「バスターミナル」）。観光客の端末は「観光客」です。「共通」と書いた行は、合う行が無いときに使われます。　並び順は、出すブロックをカンマで区切って上から順に書きます（stage=会話領域 / faq=よくある質問 / typed=文字で質問する / talk=話すボタン / languages=言語）。書かなかったブロックは出ません。　高さは画面の高さに対する割合（0.15なら15%）。0は「決めない」で、中身なりの高さになります。　キャラクターの大きさは倍率（1.0が「キャラクター」シートのまま）、高さ位置は0が下端・1が上端、左右位置は0が右端・1が左端です。　この表は管理画面の「画面レイアウト」から、画面を見ながら動かして決められます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:L10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1091,7 +1340,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="61" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1101,10 +1350,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="61" t="n">
+      <c r="C2" s="64" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="61" t="n">
+      <c r="D2" s="64" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1114,7 +1363,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1124,16 +1373,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="61" t="n">
+      <c r="C3" s="64" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="61" t="n">
+      <c r="D3" s="64" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="61" t="inlineStr">
+      <c r="A4" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1143,16 +1392,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="61" t="n">
+      <c r="C4" s="64" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="61" t="n">
+      <c r="D4" s="64" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="61" t="inlineStr">
+      <c r="A5" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1162,16 +1411,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="61" t="n">
+      <c r="C5" s="64" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="61" t="n">
+      <c r="D5" s="64" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1181,16 +1430,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="61" t="n">
+      <c r="C6" s="64" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="61" t="n">
+      <c r="D6" s="64" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="61" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1200,10 +1449,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="61" t="n">
+      <c r="C7" s="64" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="61" t="n">
+      <c r="D7" s="64" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1225,7 +1474,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1263,17 +1512,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="61" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="61" t="inlineStr">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="61" t="inlineStr">
+      <c r="C2" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1285,17 +1534,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="61" t="inlineStr">
+      <c r="B3" s="64" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="61" t="inlineStr">
+      <c r="C3" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1303,17 +1552,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="61" t="inlineStr">
+      <c r="A4" s="64" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="61" t="inlineStr">
+      <c r="B4" s="64" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="61" t="inlineStr">
+      <c r="C4" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1325,17 +1574,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="61" t="inlineStr">
+      <c r="A5" s="64" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="64" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="61" t="inlineStr">
+      <c r="C5" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1347,17 +1596,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="64" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="61" t="inlineStr">
+      <c r="C6" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1365,17 +1614,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="61" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="61" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1383,17 +1632,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="64" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="64" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="61" t="inlineStr">
+      <c r="C8" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1405,17 +1654,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="61" t="inlineStr">
+      <c r="A9" s="64" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="61" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="61" t="inlineStr">
+      <c r="C9" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1427,17 +1676,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="61" t="inlineStr">
+      <c r="A10" s="64" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="64" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="61" t="inlineStr">
+      <c r="C10" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1449,17 +1698,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="61" t="inlineStr">
+      <c r="A11" s="64" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="B11" s="64" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="61" t="inlineStr">
+      <c r="C11" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1467,17 +1716,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="61" t="inlineStr">
+      <c r="A12" s="64" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="64" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="61" t="inlineStr">
+      <c r="C12" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1485,17 +1734,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="61" t="inlineStr">
+      <c r="A13" s="64" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="B13" s="64" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="61" t="inlineStr">
+      <c r="C13" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1507,17 +1756,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="61" t="inlineStr">
+      <c r="A14" s="64" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="61" t="inlineStr">
+      <c r="B14" s="64" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="61" t="inlineStr">
+      <c r="C14" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1529,17 +1778,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="61" t="inlineStr">
+      <c r="A15" s="64" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="61" t="inlineStr">
+      <c r="B15" s="64" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="61" t="inlineStr">
+      <c r="C15" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1551,17 +1800,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="61" t="inlineStr">
+      <c r="A16" s="64" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="61" t="inlineStr">
+      <c r="B16" s="64" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="61" t="inlineStr">
+      <c r="C16" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1573,17 +1822,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="61" t="inlineStr">
+      <c r="A17" s="64" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="61" t="inlineStr">
+      <c r="B17" s="64" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="61" t="inlineStr">
+      <c r="C17" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1595,17 +1844,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="61" t="inlineStr">
+      <c r="A18" s="64" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="61" t="inlineStr">
+      <c r="B18" s="64" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="61" t="inlineStr">
+      <c r="C18" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1617,17 +1866,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="61" t="inlineStr">
+      <c r="A19" s="64" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="B19" s="64" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="61" t="inlineStr">
+      <c r="C19" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1635,17 +1884,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="61" t="inlineStr">
+      <c r="A20" s="64" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="61" t="inlineStr">
+      <c r="B20" s="64" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="61" t="inlineStr">
+      <c r="C20" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1653,17 +1902,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="61" t="inlineStr">
+      <c r="A21" s="64" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="61" t="inlineStr">
+      <c r="B21" s="64" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="61" t="inlineStr">
+      <c r="C21" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1675,17 +1924,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="61" t="inlineStr">
+      <c r="A22" s="64" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="61" t="inlineStr">
+      <c r="B22" s="64" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="61" t="inlineStr">
+      <c r="C22" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1697,17 +1946,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="64" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="61" t="inlineStr">
+      <c r="B23" s="64" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="61" t="inlineStr">
+      <c r="C23" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1719,17 +1968,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="61" t="inlineStr">
+      <c r="A24" s="64" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="61" t="inlineStr">
+      <c r="B24" s="64" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="61" t="inlineStr">
+      <c r="C24" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1741,17 +1990,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="61" t="inlineStr">
+      <c r="A25" s="64" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="61" t="inlineStr">
+      <c r="B25" s="64" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="61" t="inlineStr">
+      <c r="C25" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1759,17 +2008,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="61" t="inlineStr">
+      <c r="A26" s="64" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="61" t="inlineStr">
+      <c r="B26" s="64" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="61" t="inlineStr">
+      <c r="C26" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1777,17 +2026,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="61" t="inlineStr">
+      <c r="A27" s="64" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="61" t="inlineStr">
+      <c r="B27" s="64" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="61" t="inlineStr">
+      <c r="C27" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1799,17 +2048,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="61" t="inlineStr">
+      <c r="A28" s="64" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="61" t="inlineStr">
+      <c r="B28" s="64" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="61" t="inlineStr">
+      <c r="C28" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1821,17 +2070,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="61" t="inlineStr">
+      <c r="A29" s="64" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="61" t="inlineStr">
+      <c r="B29" s="64" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="61" t="inlineStr">
+      <c r="C29" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1843,17 +2092,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="61" t="inlineStr">
+      <c r="A30" s="64" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="61" t="inlineStr">
+      <c r="B30" s="64" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="61" t="inlineStr">
+      <c r="C30" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1861,17 +2110,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="61" t="inlineStr">
+      <c r="A31" s="64" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="61" t="inlineStr">
+      <c r="B31" s="64" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="61" t="inlineStr">
+      <c r="C31" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1883,17 +2132,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="61" t="inlineStr">
+      <c r="A32" s="64" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="61" t="inlineStr">
+      <c r="B32" s="64" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="61" t="inlineStr">
+      <c r="C32" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1901,17 +2150,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="61" t="inlineStr">
+      <c r="A33" s="64" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="61" t="inlineStr">
+      <c r="B33" s="64" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="61" t="inlineStr">
+      <c r="C33" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1919,17 +2168,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="61" t="inlineStr">
+      <c r="A34" s="64" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="61" t="inlineStr">
+      <c r="B34" s="64" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="61" t="inlineStr">
+      <c r="C34" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1937,17 +2186,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="61" t="inlineStr">
+      <c r="A35" s="64" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="61" t="inlineStr">
+      <c r="B35" s="64" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="61" t="inlineStr">
+      <c r="C35" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1955,17 +2204,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="61" t="inlineStr">
+      <c r="A36" s="64" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="61" t="inlineStr">
+      <c r="B36" s="64" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="61" t="inlineStr">
+      <c r="C36" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1973,17 +2222,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="61" t="inlineStr">
+      <c r="A37" s="64" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="61" t="inlineStr">
+      <c r="B37" s="64" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="61" t="inlineStr">
+      <c r="C37" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1991,17 +2240,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="61" t="inlineStr">
+      <c r="A38" s="64" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="61" t="inlineStr">
+      <c r="B38" s="64" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="61" t="inlineStr">
+      <c r="C38" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2009,17 +2258,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="61" t="inlineStr">
+      <c r="A39" s="64" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="61" t="inlineStr">
+      <c r="B39" s="64" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="61" t="inlineStr">
+      <c r="C39" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2027,17 +2276,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="61" t="inlineStr">
+      <c r="A40" s="64" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="61" t="inlineStr">
+      <c r="B40" s="64" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="61" t="inlineStr">
+      <c r="C40" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2049,17 +2298,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="61" t="inlineStr">
+      <c r="A41" s="64" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="61" t="inlineStr">
+      <c r="B41" s="64" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="61" t="inlineStr">
+      <c r="C41" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2067,17 +2316,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="61" t="inlineStr">
+      <c r="A42" s="64" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="61" t="inlineStr">
+      <c r="B42" s="64" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="61" t="inlineStr">
+      <c r="C42" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2089,17 +2338,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="61" t="inlineStr">
+      <c r="A43" s="64" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="61" t="inlineStr">
+      <c r="B43" s="64" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="61" t="inlineStr">
+      <c r="C43" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2107,17 +2356,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="61" t="inlineStr">
+      <c r="A44" s="64" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="61" t="inlineStr">
+      <c r="B44" s="64" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="61" t="inlineStr">
+      <c r="C44" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2129,24 +2378,23 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="61" t="inlineStr">
+      <c r="A45" s="64" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="61" t="inlineStr">
+      <c r="B45" s="64" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="61" t="inlineStr">
+      <c r="C45" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
       <c r="D45" s="46" t="n"/>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="59" t="inlineStr">
         <is>
@@ -4619,7 +4867,7 @@
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="61" t="n"/>
+      <c r="N43" s="64" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -5808,17 +6056,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="61" t="inlineStr">
+      <c r="A66" s="64" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="61" t="inlineStr">
+      <c r="B66" s="64" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="61" t="inlineStr">
+      <c r="C66" s="64" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -5848,26 +6096,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="61" t="inlineStr">
+      <c r="G66" s="64" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="61" t="n"/>
-      <c r="I66" s="61" t="inlineStr">
+      <c r="H66" s="64" t="n"/>
+      <c r="I66" s="64" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="61" t="inlineStr">
+      <c r="J66" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="61" t="n"/>
-      <c r="L66" s="61" t="n"/>
-      <c r="M66" s="61" t="n"/>
-      <c r="N66" s="61" t="n"/>
+      <c r="K66" s="64" t="n"/>
+      <c r="L66" s="64" t="n"/>
+      <c r="M66" s="64" t="n"/>
+      <c r="N66" s="64" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -16364,12 +16612,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="61" t="inlineStr">
+      <c r="A302" s="64" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="61" t="inlineStr">
+      <c r="B302" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16395,12 +16643,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="61" t="inlineStr">
+      <c r="A303" s="64" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="61" t="inlineStr">
+      <c r="B303" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16426,12 +16674,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="61" t="inlineStr">
+      <c r="A304" s="64" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="61" t="inlineStr">
+      <c r="B304" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16457,12 +16705,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="61" t="inlineStr">
+      <c r="A305" s="64" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="61" t="inlineStr">
+      <c r="B305" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16488,12 +16736,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="61" t="inlineStr">
+      <c r="A306" s="64" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="61" t="inlineStr">
+      <c r="B306" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -16519,12 +16767,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="61" t="inlineStr">
+      <c r="A307" s="64" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="61" t="inlineStr">
+      <c r="B307" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16550,12 +16798,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="61" t="inlineStr">
+      <c r="A308" s="64" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="61" t="inlineStr">
+      <c r="B308" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16581,12 +16829,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="61" t="inlineStr">
+      <c r="A309" s="64" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="61" t="inlineStr">
+      <c r="B309" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16612,12 +16860,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="61" t="inlineStr">
+      <c r="A310" s="64" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="61" t="inlineStr">
+      <c r="B310" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16643,12 +16891,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="61" t="inlineStr">
+      <c r="A311" s="64" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="61" t="inlineStr">
+      <c r="B311" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -16674,12 +16922,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="61" t="inlineStr">
+      <c r="A312" s="64" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="61" t="inlineStr">
+      <c r="B312" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16704,12 +16952,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="61" t="inlineStr">
+      <c r="A313" s="64" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="61" t="inlineStr">
+      <c r="B313" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16734,12 +16982,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="61" t="inlineStr">
+      <c r="A314" s="64" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="61" t="inlineStr">
+      <c r="B314" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16764,12 +17012,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="61" t="inlineStr">
+      <c r="A315" s="64" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="61" t="inlineStr">
+      <c r="B315" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16794,12 +17042,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="61" t="inlineStr">
+      <c r="A316" s="64" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="61" t="inlineStr">
+      <c r="B316" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -16824,12 +17072,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="61" t="inlineStr">
+      <c r="A317" s="64" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="61" t="inlineStr">
+      <c r="B317" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16855,12 +17103,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="61" t="inlineStr">
+      <c r="A318" s="64" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="61" t="inlineStr">
+      <c r="B318" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16886,12 +17134,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="61" t="inlineStr">
+      <c r="A319" s="64" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="61" t="inlineStr">
+      <c r="B319" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16917,12 +17165,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="61" t="inlineStr">
+      <c r="A320" s="64" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="61" t="inlineStr">
+      <c r="B320" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16948,12 +17196,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="61" t="inlineStr">
+      <c r="A321" s="64" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="61" t="inlineStr">
+      <c r="B321" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -16979,12 +17227,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="61" t="inlineStr">
+      <c r="A322" s="64" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="61" t="inlineStr">
+      <c r="B322" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17009,12 +17257,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="61" t="inlineStr">
+      <c r="A323" s="64" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="61" t="inlineStr">
+      <c r="B323" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17039,12 +17287,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="61" t="inlineStr">
+      <c r="A324" s="64" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="61" t="inlineStr">
+      <c r="B324" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17069,12 +17317,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="61" t="inlineStr">
+      <c r="A325" s="64" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="61" t="inlineStr">
+      <c r="B325" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17099,12 +17347,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="61" t="inlineStr">
+      <c r="A326" s="64" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="61" t="inlineStr">
+      <c r="B326" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17129,12 +17377,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="61" t="inlineStr">
+      <c r="A327" s="64" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="61" t="inlineStr">
+      <c r="B327" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17161,12 +17409,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="61" t="inlineStr">
+      <c r="A328" s="64" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="61" t="inlineStr">
+      <c r="B328" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17193,12 +17441,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="61" t="inlineStr">
+      <c r="A329" s="64" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="61" t="inlineStr">
+      <c r="B329" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17225,12 +17473,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="61" t="inlineStr">
+      <c r="A330" s="64" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="61" t="inlineStr">
+      <c r="B330" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17257,12 +17505,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="61" t="inlineStr">
+      <c r="A331" s="64" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="61" t="inlineStr">
+      <c r="B331" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17289,12 +17537,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="61" t="inlineStr">
+      <c r="A332" s="64" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="61" t="inlineStr">
+      <c r="B332" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17321,12 +17569,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="61" t="inlineStr">
+      <c r="A333" s="64" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="61" t="inlineStr">
+      <c r="B333" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17353,12 +17601,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="61" t="inlineStr">
+      <c r="A334" s="64" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="61" t="inlineStr">
+      <c r="B334" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17385,12 +17633,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="61" t="inlineStr">
+      <c r="A335" s="64" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="61" t="inlineStr">
+      <c r="B335" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17417,12 +17665,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="61" t="inlineStr">
+      <c r="A336" s="64" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="61" t="inlineStr">
+      <c r="B336" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17449,12 +17697,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="61" t="inlineStr">
+      <c r="A337" s="64" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="61" t="inlineStr">
+      <c r="B337" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17481,12 +17729,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="61" t="inlineStr">
+      <c r="A338" s="64" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="61" t="inlineStr">
+      <c r="B338" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17513,12 +17761,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="61" t="inlineStr">
+      <c r="A339" s="64" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="61" t="inlineStr">
+      <c r="B339" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17545,12 +17793,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="61" t="inlineStr">
+      <c r="A340" s="64" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="61" t="inlineStr">
+      <c r="B340" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17577,12 +17825,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="61" t="inlineStr">
+      <c r="A341" s="64" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="61" t="inlineStr">
+      <c r="B341" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17609,12 +17857,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="61" t="inlineStr">
+      <c r="A342" s="64" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="61" t="inlineStr">
+      <c r="B342" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17641,12 +17889,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="61" t="inlineStr">
+      <c r="A343" s="64" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="61" t="inlineStr">
+      <c r="B343" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17673,12 +17921,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="61" t="inlineStr">
+      <c r="A344" s="64" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="61" t="inlineStr">
+      <c r="B344" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17705,12 +17953,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="61" t="inlineStr">
+      <c r="A345" s="64" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="61" t="inlineStr">
+      <c r="B345" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17737,12 +17985,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="61" t="inlineStr">
+      <c r="A346" s="64" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="61" t="inlineStr">
+      <c r="B346" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17769,12 +18017,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="61" t="inlineStr">
+      <c r="A347" s="64" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="61" t="inlineStr">
+      <c r="B347" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17801,12 +18049,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="61" t="inlineStr">
+      <c r="A348" s="64" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="61" t="inlineStr">
+      <c r="B348" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17833,12 +18081,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="61" t="inlineStr">
+      <c r="A349" s="64" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="61" t="inlineStr">
+      <c r="B349" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17865,12 +18113,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="61" t="inlineStr">
+      <c r="A350" s="64" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="61" t="inlineStr">
+      <c r="B350" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17897,12 +18145,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="61" t="inlineStr">
+      <c r="A351" s="64" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="61" t="inlineStr">
+      <c r="B351" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17929,12 +18177,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="61" t="inlineStr">
+      <c r="A352" s="64" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="61" t="inlineStr">
+      <c r="B352" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17960,12 +18208,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="61" t="inlineStr">
+      <c r="A353" s="64" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="61" t="inlineStr">
+      <c r="B353" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17991,12 +18239,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="61" t="inlineStr">
+      <c r="A354" s="64" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="61" t="inlineStr">
+      <c r="B354" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18022,12 +18270,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="61" t="inlineStr">
+      <c r="A355" s="64" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="61" t="inlineStr">
+      <c r="B355" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18053,12 +18301,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="61" t="inlineStr">
+      <c r="A356" s="64" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="61" t="inlineStr">
+      <c r="B356" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18084,12 +18332,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="61" t="inlineStr">
+      <c r="A357" s="64" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="61" t="inlineStr">
+      <c r="B357" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18115,12 +18363,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="61" t="inlineStr">
+      <c r="A358" s="64" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="61" t="inlineStr">
+      <c r="B358" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18146,12 +18394,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="61" t="inlineStr">
+      <c r="A359" s="64" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="61" t="inlineStr">
+      <c r="B359" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18177,12 +18425,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="61" t="inlineStr">
+      <c r="A360" s="64" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="61" t="inlineStr">
+      <c r="B360" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18208,12 +18456,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="61" t="inlineStr">
+      <c r="A361" s="64" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="61" t="inlineStr">
+      <c r="B361" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18239,12 +18487,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="61" t="inlineStr">
+      <c r="A362" s="64" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="61" t="inlineStr">
+      <c r="B362" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18271,12 +18519,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="61" t="inlineStr">
+      <c r="A363" s="64" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="61" t="inlineStr">
+      <c r="B363" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18303,12 +18551,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="61" t="inlineStr">
+      <c r="A364" s="64" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="61" t="inlineStr">
+      <c r="B364" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18335,12 +18583,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="61" t="inlineStr">
+      <c r="A365" s="64" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="61" t="inlineStr">
+      <c r="B365" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18367,12 +18615,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="61" t="inlineStr">
+      <c r="A366" s="64" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="61" t="inlineStr">
+      <c r="B366" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18399,12 +18647,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="61" t="inlineStr">
+      <c r="A367" s="64" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="61" t="inlineStr">
+      <c r="B367" s="64" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18431,12 +18679,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="61" t="inlineStr">
+      <c r="A368" s="64" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="61" t="inlineStr">
+      <c r="B368" s="64" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18463,12 +18711,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="61" t="inlineStr">
+      <c r="A369" s="64" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="61" t="inlineStr">
+      <c r="B369" s="64" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18495,12 +18743,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="61" t="inlineStr">
+      <c r="A370" s="64" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="61" t="inlineStr">
+      <c r="B370" s="64" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18527,12 +18775,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="61" t="inlineStr">
+      <c r="A371" s="64" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="61" t="inlineStr">
+      <c r="B371" s="64" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -19557,7 +19805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -19603,19 +19851,19 @@
     <row r="2" ht="32.4" customHeight="1">
       <c r="A2" s="41" t="inlineStr">
         <is>
-          <t>いま入っている音声（VOICEVOX）</t>
+          <t>春日部つむぎ</t>
         </is>
       </c>
       <c r="B2" s="41" t="n"/>
       <c r="C2" s="41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D2" s="41" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="42" t="inlineStr">
         <is>
-          <t>VOICEVOXで作成。設置で使う場合はクレジット表記が必要</t>
+          <t>VOICEVOX:春日部つむぎ で作成。設置で使う場合はクレジット表記が必要</t>
         </is>
       </c>
       <c r="F2" s="57" t="inlineStr">
@@ -19624,29 +19872,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="32.4" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
-        <is>
-          <t>ずんだもん</t>
-        </is>
-      </c>
-      <c r="B3" s="41" t="inlineStr">
-        <is>
-          <t>zundamon</t>
-        </is>
-      </c>
-      <c r="C3" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="D3" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="42" t="inlineStr">
-        <is>
-          <t>VOICEVOXで作成。設置で使う場合はクレジット表記が必要</t>
-        </is>
-      </c>
-    </row>
+    <row r="3" ht="32.4" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19690,7 +19916,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="61" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -19700,7 +19926,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="61" t="inlineStr">
+      <c r="C2" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19712,7 +19938,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -19722,7 +19948,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="61" t="inlineStr">
+      <c r="C3" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19734,7 +19960,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="61" t="inlineStr">
+      <c r="A4" s="64" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -19744,7 +19970,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="61" t="inlineStr">
+      <c r="C4" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19756,7 +19982,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="61" t="inlineStr">
+      <c r="A5" s="64" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -19766,7 +19992,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="61" t="inlineStr">
+      <c r="C5" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19778,7 +20004,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -19788,7 +20014,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="61" t="inlineStr">
+      <c r="C6" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19800,7 +20026,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="61" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -19810,7 +20036,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="61" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19822,7 +20048,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="64" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -19832,7 +20058,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="61" t="inlineStr">
+      <c r="C8" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19844,7 +20070,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="61" t="inlineStr">
+      <c r="A9" s="64" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -19854,7 +20080,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="61" t="inlineStr">
+      <c r="C9" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19866,7 +20092,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="61" t="inlineStr">
+      <c r="A10" s="64" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -19876,7 +20102,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="61" t="inlineStr">
+      <c r="C10" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19888,7 +20114,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="61" t="inlineStr">
+      <c r="A11" s="64" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -19898,7 +20124,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="61" t="inlineStr">
+      <c r="C11" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19910,7 +20136,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="61" t="inlineStr">
+      <c r="A12" s="64" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -19920,7 +20146,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="61" t="inlineStr">
+      <c r="C12" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19932,7 +20158,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="61" t="inlineStr">
+      <c r="A13" s="64" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -19942,7 +20168,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="61" t="inlineStr">
+      <c r="C13" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20084,53 +20310,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="61" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="61" t="inlineStr">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="61" t="inlineStr">
+      <c r="C2" s="64" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="61" t="inlineStr">
+      <c r="D2" s="64" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="61" t="inlineStr">
+      <c r="E2" s="64" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="61" t="inlineStr">
+      <c r="F2" s="64" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="61" t="inlineStr">
+      <c r="G2" s="64" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="61" t="inlineStr">
+      <c r="H2" s="64" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="61" t="inlineStr">
+      <c r="I2" s="64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="61" t="n"/>
-      <c r="K2" s="61" t="inlineStr">
+      <c r="J2" s="64" t="n"/>
+      <c r="K2" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20167,45 +20393,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="61" t="inlineStr">
+      <c r="B3" s="64" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="61" t="inlineStr">
+      <c r="C3" s="64" t="inlineStr">
         <is>
           <t>main.png</t>
         </is>
       </c>
-      <c r="D3" s="61" t="n"/>
-      <c r="E3" s="61" t="n"/>
-      <c r="F3" s="61" t="n">
+      <c r="D3" s="64" t="n"/>
+      <c r="E3" s="64" t="n"/>
+      <c r="F3" s="64" t="n">
         <v>0.16</v>
       </c>
-      <c r="G3" s="61" t="n">
+      <c r="G3" s="64" t="n">
         <v>0.3</v>
       </c>
-      <c r="H3" s="61" t="inlineStr">
+      <c r="H3" s="64" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="61" t="inlineStr">
+      <c r="I3" s="64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="61" t="inlineStr">
+      <c r="J3" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="61" t="inlineStr">
+      <c r="K3" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20242,45 +20468,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="61" t="inlineStr">
+      <c r="A4" s="64" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="61" t="inlineStr">
+      <c r="B4" s="64" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="61" t="inlineStr">
+      <c r="C4" s="64" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="61" t="n"/>
-      <c r="E4" s="61" t="n"/>
-      <c r="F4" s="61" t="inlineStr">
+      <c r="D4" s="64" t="n"/>
+      <c r="E4" s="64" t="n"/>
+      <c r="F4" s="64" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="61" t="inlineStr">
+      <c r="G4" s="64" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="61" t="inlineStr">
+      <c r="H4" s="64" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="61" t="inlineStr">
+      <c r="I4" s="64" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="61" t="n"/>
-      <c r="K4" s="61" t="inlineStr">
+      <c r="J4" s="64" t="n"/>
+      <c r="K4" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20317,45 +20543,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="61" t="inlineStr">
+      <c r="A5" s="64" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="64" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="61" t="inlineStr">
+      <c r="C5" s="64" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="61" t="n"/>
-      <c r="E5" s="61" t="n"/>
-      <c r="F5" s="61" t="inlineStr">
+      <c r="D5" s="64" t="n"/>
+      <c r="E5" s="64" t="n"/>
+      <c r="F5" s="64" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="61" t="inlineStr">
+      <c r="G5" s="64" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="61" t="inlineStr">
+      <c r="H5" s="64" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="61" t="inlineStr">
+      <c r="I5" s="64" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="61" t="n"/>
-      <c r="K5" s="61" t="inlineStr">
+      <c r="J5" s="64" t="n"/>
+      <c r="K5" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20392,45 +20618,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="64" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="61" t="inlineStr">
+      <c r="C6" s="64" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="61" t="n"/>
-      <c r="E6" s="61" t="n"/>
-      <c r="F6" s="61" t="inlineStr">
+      <c r="D6" s="64" t="n"/>
+      <c r="E6" s="64" t="n"/>
+      <c r="F6" s="64" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="61" t="inlineStr">
+      <c r="G6" s="64" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="61" t="inlineStr">
+      <c r="H6" s="64" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="61" t="inlineStr">
+      <c r="I6" s="64" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="61" t="n"/>
-      <c r="K6" s="61" t="inlineStr">
+      <c r="J6" s="64" t="n"/>
+      <c r="K6" s="64" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20484,231 +20710,892 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="48" t="inlineStr">
         <is>
-          <t>設置場所</t>
+          <t>種類</t>
         </is>
       </c>
       <c r="B1" s="48" t="inlineStr">
         <is>
-          <t>並び順</t>
+          <t>キャラクター</t>
         </is>
       </c>
       <c r="C1" s="48" t="inlineStr">
         <is>
-          <t>よくある質問の高さ</t>
+          <t>聞き方</t>
         </is>
       </c>
       <c r="D1" s="48" t="inlineStr">
         <is>
-          <t>入力欄の高さ</t>
+          <t>返事</t>
         </is>
       </c>
       <c r="E1" s="48" t="inlineStr">
         <is>
-          <t>話すボタンの高さ</t>
+          <t>返事（英語）</t>
         </is>
       </c>
       <c r="F1" s="48" t="inlineStr">
         <is>
-          <t>言語の高さ</t>
+          <t>返事（中国語）</t>
         </is>
       </c>
       <c r="G1" s="48" t="inlineStr">
         <is>
-          <t>キャラクターの大きさ</t>
+          <t>返事（韓国語）</t>
         </is>
       </c>
       <c r="H1" s="48" t="inlineStr">
         <is>
-          <t>キャラクターの高さ位置</t>
+          <t>返事（スペイン語）</t>
         </is>
       </c>
       <c r="I1" s="48" t="inlineStr">
         <is>
-          <t>キャラクターの左右位置</t>
+          <t>返事（フランス語）</t>
         </is>
       </c>
       <c r="J1" s="48" t="inlineStr">
         <is>
-          <t>吹き出しの幅</t>
-        </is>
-      </c>
-      <c r="K1" s="48" t="inlineStr">
-        <is>
-          <t>文字の大きさ</t>
-        </is>
-      </c>
-      <c r="L1" s="48" t="inlineStr">
-        <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="61" t="inlineStr">
-        <is>
-          <t>バスターミナル</t>
-        </is>
-      </c>
-      <c r="B2" s="46" t="inlineStr">
-        <is>
-          <t>stage,faq,talk,languages</t>
-        </is>
-      </c>
-      <c r="C2" s="61" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="D2" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="61" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F2" s="61" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G2" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="61" t="n">
-        <v>0.664</v>
-      </c>
-      <c r="K2" s="61" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L2" s="46" t="inlineStr">
-        <is>
-          <t>据え置きのタブレット。話すボタンを大きく、入力欄は出さない</t>
-        </is>
-      </c>
+      <c r="A2" s="65" t="inlineStr">
+        <is>
+          <t>あいさつ</t>
+        </is>
+      </c>
+      <c r="B2" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C2" s="46" t="inlineStr"/>
+      <c r="D2" s="46" t="inlineStr">
+        <is>
+          <t>こんにちは！白川郷へようこそ。わたしは{名前}です。知りたいことを聞いてくださいね。</t>
+        </is>
+      </c>
+      <c r="E2" s="46" t="inlineStr">
+        <is>
+          <t>Hello! Welcome to Shirakawa-go. I'm {名前}. Feel free to ask me anything.</t>
+        </is>
+      </c>
+      <c r="F2" s="46" t="inlineStr">
+        <is>
+          <t>你好！欢迎来到白川乡。我是{名前}，有什么想知道的请问我吧。</t>
+        </is>
+      </c>
+      <c r="G2" s="46" t="inlineStr">
+        <is>
+          <t>안녕하세요! 시라카와고에 오신 것을 환영합니다. 저는 {名前}입니다. 궁금한 것을 물어보세요.</t>
+        </is>
+      </c>
+      <c r="H2" s="46" t="inlineStr">
+        <is>
+          <t>¡Hola! Bienvenido a Shirakawa-go. Soy {名前}. Pregúntame lo que quieras.</t>
+        </is>
+      </c>
+      <c r="I2" s="46" t="inlineStr">
+        <is>
+          <t>Bonjour ! Bienvenue à Shirakawa-go. Je suis {名前}. N'hésitez pas à me poser vos questions.</t>
+        </is>
+      </c>
+      <c r="J2" s="46" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="61" t="inlineStr">
-        <is>
-          <t>であいの館</t>
-        </is>
-      </c>
-      <c r="B3" s="46" t="inlineStr">
-        <is>
-          <t>stage,faq,talk,languages</t>
-        </is>
-      </c>
-      <c r="C3" s="61" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="D3" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="61" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F3" s="61" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G3" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="61" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="J3" s="61" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="K3" s="61" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L3" s="46" t="inlineStr">
-        <is>
-          <t>据え置きのタブレット。バスターミナルと同じ</t>
-        </is>
-      </c>
+      <c r="A3" s="65" t="inlineStr">
+        <is>
+          <t>あいさつ</t>
+        </is>
+      </c>
+      <c r="B3" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C3" s="46" t="inlineStr"/>
+      <c r="D3" s="46" t="inlineStr">
+        <is>
+          <t>こんにちは！{名前}です。白川郷のことなら、なんでも聞いてください。</t>
+        </is>
+      </c>
+      <c r="E3" s="46" t="inlineStr">
+        <is>
+          <t>Hi there! I'm {名前}. Ask me anything about Shirakawa-go.</t>
+        </is>
+      </c>
+      <c r="F3" s="46" t="inlineStr">
+        <is>
+          <t>你好！我是{名前}。关于白川乡的事情，尽管问我吧。</t>
+        </is>
+      </c>
+      <c r="G3" s="46" t="inlineStr">
+        <is>
+          <t>안녕하세요! {名前}입니다. 시라카와고에 대해 무엇이든 물어보세요.</t>
+        </is>
+      </c>
+      <c r="H3" s="46" t="inlineStr">
+        <is>
+          <t>¡Hola! Soy {名前}. Pregúntame lo que quieras sobre Shirakawa-go.</t>
+        </is>
+      </c>
+      <c r="I3" s="46" t="inlineStr">
+        <is>
+          <t>Salut ! Je suis {名前}. Posez-moi toutes vos questions sur Shirakawa-go.</t>
+        </is>
+      </c>
+      <c r="J3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="61" t="inlineStr">
-        <is>
-          <t>観光客</t>
-        </is>
-      </c>
-      <c r="B4" s="46" t="inlineStr">
-        <is>
-          <t>stage,faq,typed,talk,languages</t>
-        </is>
-      </c>
-      <c r="C4" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="46" t="inlineStr">
-        <is>
-          <t>観光客のスマートフォン。0は「決めない」＝中身なりの大きさ</t>
-        </is>
-      </c>
+      <c r="A4" s="65" t="inlineStr">
+        <is>
+          <t>あいさつ</t>
+        </is>
+      </c>
+      <c r="B4" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="inlineStr"/>
+      <c r="D4" s="46" t="inlineStr">
+        <is>
+          <t>ようこそ、白川郷へ！合掌造りの里を、ゆっくり楽しんでいってくださいね。</t>
+        </is>
+      </c>
+      <c r="E4" s="46" t="inlineStr">
+        <is>
+          <t>Welcome to Shirakawa-go! Take your time and enjoy the gassho-style village.</t>
+        </is>
+      </c>
+      <c r="F4" s="46" t="inlineStr">
+        <is>
+          <t>欢迎来到白川乡！请慢慢欣赏合掌造村落吧。</t>
+        </is>
+      </c>
+      <c r="G4" s="46" t="inlineStr">
+        <is>
+          <t>시라카와고에 오신 것을 환영해요! 갓쇼즈쿠리 마을을 천천히 즐겨 주세요.</t>
+        </is>
+      </c>
+      <c r="H4" s="46" t="inlineStr">
+        <is>
+          <t>¡Bienvenido a Shirakawa-go! Disfrute con calma del pueblo de casas gassho.</t>
+        </is>
+      </c>
+      <c r="I4" s="46" t="inlineStr">
+        <is>
+          <t>Bienvenue à Shirakawa-go ! Prenez le temps de profiter du village aux maisons gassho.</t>
+        </is>
+      </c>
+      <c r="J4" s="46" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="65" t="inlineStr">
+        <is>
+          <t>お礼</t>
+        </is>
+      </c>
+      <c r="B5" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C5" s="46" t="inlineStr"/>
+      <c r="D5" s="46" t="inlineStr">
+        <is>
+          <t>どういたしまして。白川郷を楽しんでくださいね。</t>
+        </is>
+      </c>
+      <c r="E5" s="46" t="inlineStr">
+        <is>
+          <t>You're welcome! Enjoy your time in Shirakawa-go.</t>
+        </is>
+      </c>
+      <c r="F5" s="46" t="inlineStr">
+        <is>
+          <t>不客气！祝您在白川乡玩得愉快。</t>
+        </is>
+      </c>
+      <c r="G5" s="46" t="inlineStr">
+        <is>
+          <t>천만에요! 시라카와고에서 즐거운 시간 보내세요.</t>
+        </is>
+      </c>
+      <c r="H5" s="46" t="inlineStr">
+        <is>
+          <t>¡De nada! Disfrute de Shirakawa-go.</t>
+        </is>
+      </c>
+      <c r="I5" s="46" t="inlineStr">
+        <is>
+          <t>Je vous en prie ! Profitez bien de Shirakawa-go.</t>
+        </is>
+      </c>
+      <c r="J5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr">
-        <is>
-          <t>※ 設置場所は、案内アプリのURLに付ける名前と同じにしてください（?place=バスターミナル なら「バスターミナル」）。観光客の端末は「観光客」です。「共通」と書いた行は、合う行が無いときに使われます。　並び順は、出すブロックをカンマで区切って上から順に書きます（stage=会話領域 / faq=よくある質問 / typed=文字で質問する / talk=話すボタン / languages=言語）。書かなかったブロックは出ません。　高さは画面の高さに対する割合（0.15なら15%）。0は「決めない」で、中身なりの高さになります。　キャラクターの大きさは倍率（1.0が「キャラクター」シートのまま）、高さ位置は0が下端・1が上端、左右位置は0が右端・1が左端です。　この表は管理画面の「画面レイアウト」から、画面を見ながら動かして決められます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
+      <c r="A6" s="65" t="inlineStr">
+        <is>
+          <t>お礼</t>
+        </is>
+      </c>
+      <c r="B6" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C6" s="46" t="inlineStr"/>
+      <c r="D6" s="46" t="inlineStr">
+        <is>
+          <t>お役に立ててうれしいです。ほかにも気になることがあれば、聞いてくださいね。</t>
+        </is>
+      </c>
+      <c r="E6" s="46" t="inlineStr">
+        <is>
+          <t>I'm glad I could help. Let me know if there's anything else you'd like to know.</t>
+        </is>
+      </c>
+      <c r="F6" s="46" t="inlineStr">
+        <is>
+          <t>很高兴能帮上忙。如果还有其他想知道的，请随时问我。</t>
+        </is>
+      </c>
+      <c r="G6" s="46" t="inlineStr">
+        <is>
+          <t>도움이 되어 기뻐요. 더 궁금한 것이 있으면 물어보세요.</t>
+        </is>
+      </c>
+      <c r="H6" s="46" t="inlineStr">
+        <is>
+          <t>Me alegra haber ayudado. Si tiene otra pregunta, no dude en hacerla.</t>
+        </is>
+      </c>
+      <c r="I6" s="46" t="inlineStr">
+        <is>
+          <t>Je suis ravie d'avoir pu aider. N'hésitez pas si vous avez d'autres questions.</t>
+        </is>
+      </c>
+      <c r="J6" s="46" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="65" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="B7" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C7" s="46" t="inlineStr"/>
+      <c r="D7" s="46" t="inlineStr">
+        <is>
+          <t>わたしは{名前}です。白川郷の案内をしています。</t>
+        </is>
+      </c>
+      <c r="E7" s="46" t="inlineStr">
+        <is>
+          <t>I'm {名前}, your guide to Shirakawa-go.</t>
+        </is>
+      </c>
+      <c r="F7" s="46" t="inlineStr">
+        <is>
+          <t>我是{名前}，负责介绍白川乡。</t>
+        </is>
+      </c>
+      <c r="G7" s="46" t="inlineStr">
+        <is>
+          <t>저는 {名前}입니다. 시라카와고를 안내하고 있어요.</t>
+        </is>
+      </c>
+      <c r="H7" s="46" t="inlineStr">
+        <is>
+          <t>Soy {名前}, su guía de Shirakawa-go.</t>
+        </is>
+      </c>
+      <c r="I7" s="46" t="inlineStr">
+        <is>
+          <t>Je suis {名前}, votre guide à Shirakawa-go.</t>
+        </is>
+      </c>
+      <c r="J7" s="46" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="B8" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C8" s="46" t="inlineStr"/>
+      <c r="D8" s="46" t="inlineStr">
+        <is>
+          <t>{名前}といいます。どうぞよろしくお願いします！</t>
+        </is>
+      </c>
+      <c r="E8" s="46" t="inlineStr">
+        <is>
+          <t>My name is {名前}. Nice to meet you!</t>
+        </is>
+      </c>
+      <c r="F8" s="46" t="inlineStr">
+        <is>
+          <t>我叫{名前}，请多关照！</t>
+        </is>
+      </c>
+      <c r="G8" s="46" t="inlineStr">
+        <is>
+          <t>{名前}라고 해요. 잘 부탁드려요!</t>
+        </is>
+      </c>
+      <c r="H8" s="46" t="inlineStr">
+        <is>
+          <t>Me llamo {名前}. ¡Encantada de conocerle!</t>
+        </is>
+      </c>
+      <c r="I8" s="46" t="inlineStr">
+        <is>
+          <t>Je m'appelle {名前}. Enchantée !</t>
+        </is>
+      </c>
+      <c r="J8" s="46" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="65" t="inlineStr">
+        <is>
+          <t>元気</t>
+        </is>
+      </c>
+      <c r="B9" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C9" s="46" t="inlineStr"/>
+      <c r="D9" s="46" t="inlineStr">
+        <is>
+          <t>はい、元気です！何かお手伝いできることはありますか。</t>
+        </is>
+      </c>
+      <c r="E9" s="46" t="inlineStr">
+        <is>
+          <t>I'm doing great, thank you! How can I help you?</t>
+        </is>
+      </c>
+      <c r="F9" s="46" t="inlineStr">
+        <is>
+          <t>我很好，谢谢！有什么可以帮您的吗？</t>
+        </is>
+      </c>
+      <c r="G9" s="46" t="inlineStr">
+        <is>
+          <t>네, 잘 지내요! 무엇을 도와드릴까요?</t>
+        </is>
+      </c>
+      <c r="H9" s="46" t="inlineStr">
+        <is>
+          <t>¡Muy bien, gracias! ¿En qué puedo ayudarle?</t>
+        </is>
+      </c>
+      <c r="I9" s="46" t="inlineStr">
+        <is>
+          <t>Très bien, merci ! Comment puis-je vous aider ?</t>
+        </is>
+      </c>
+      <c r="J9" s="46" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="65" t="inlineStr">
+        <is>
+          <t>元気</t>
+        </is>
+      </c>
+      <c r="B10" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C10" s="46" t="inlineStr"/>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>とっても元気です！今日も白川郷はいいところですよ。</t>
+        </is>
+      </c>
+      <c r="E10" s="46" t="inlineStr">
+        <is>
+          <t>I'm full of energy! Shirakawa-go is lovely today, too.</t>
+        </is>
+      </c>
+      <c r="F10" s="46" t="inlineStr">
+        <is>
+          <t>我精神很好！今天的白川乡也很美哦。</t>
+        </is>
+      </c>
+      <c r="G10" s="46" t="inlineStr">
+        <is>
+          <t>아주 잘 지내요! 오늘도 시라카와고는 정말 좋은 곳이에요.</t>
+        </is>
+      </c>
+      <c r="H10" s="46" t="inlineStr">
+        <is>
+          <t>¡Con mucha energía! Shirakawa-go también está precioso hoy.</t>
+        </is>
+      </c>
+      <c r="I10" s="46" t="inlineStr">
+        <is>
+          <t>En pleine forme ! Shirakawa-go est magnifique aujourd'hui aussi.</t>
+        </is>
+      </c>
+      <c r="J10" s="46" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="65" t="inlineStr">
+        <is>
+          <t>さようなら</t>
+        </is>
+      </c>
+      <c r="B11" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C11" s="46" t="inlineStr"/>
+      <c r="D11" s="46" t="inlineStr">
+        <is>
+          <t>ありがとうございました。どうぞお気をつけて、白川郷を楽しんでください。</t>
+        </is>
+      </c>
+      <c r="E11" s="46" t="inlineStr">
+        <is>
+          <t>Thank you for visiting! Take care and enjoy Shirakawa-go.</t>
+        </is>
+      </c>
+      <c r="F11" s="46" t="inlineStr">
+        <is>
+          <t>谢谢您！路上小心，祝您在白川乡玩得开心。</t>
+        </is>
+      </c>
+      <c r="G11" s="46" t="inlineStr">
+        <is>
+          <t>감사합니다! 조심히 다니시고 시라카와고를 즐기세요.</t>
+        </is>
+      </c>
+      <c r="H11" s="46" t="inlineStr">
+        <is>
+          <t>¡Gracias! Cuídese y disfrute de Shirakawa-go.</t>
+        </is>
+      </c>
+      <c r="I11" s="46" t="inlineStr">
+        <is>
+          <t>Merci ! Prenez soin de vous et profitez de Shirakawa-go.</t>
+        </is>
+      </c>
+      <c r="J11" s="46" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="65" t="inlineStr">
+        <is>
+          <t>さようなら</t>
+        </is>
+      </c>
+      <c r="B12" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C12" s="46" t="inlineStr"/>
+      <c r="D12" s="46" t="inlineStr">
+        <is>
+          <t>またいつでも来てくださいね。いってらっしゃい！</t>
+        </is>
+      </c>
+      <c r="E12" s="46" t="inlineStr">
+        <is>
+          <t>Please come back anytime. Have a great trip!</t>
+        </is>
+      </c>
+      <c r="F12" s="46" t="inlineStr">
+        <is>
+          <t>欢迎随时再来。一路顺风！</t>
+        </is>
+      </c>
+      <c r="G12" s="46" t="inlineStr">
+        <is>
+          <t>언제든지 또 오세요. 좋은 여행 되세요!</t>
+        </is>
+      </c>
+      <c r="H12" s="46" t="inlineStr">
+        <is>
+          <t>Vuelva cuando quiera. ¡Buen viaje!</t>
+        </is>
+      </c>
+      <c r="I12" s="46" t="inlineStr">
+        <is>
+          <t>Revenez quand vous voulez. Bon voyage !</t>
+        </is>
+      </c>
+      <c r="J12" s="46" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="65" t="inlineStr">
+        <is>
+          <t>好きな食べ物</t>
+        </is>
+      </c>
+      <c r="B13" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C13" s="46" t="inlineStr">
+        <is>
+          <t>好きな食べ物
+何が好き
+好物
+なに食べたい
+favorite food
+what's your favorite food
+what is your favorite food
+what do you like to eat
+喜欢吃什么
+最喜欢的食物
+좋아하는 음식
+좋아하는 음식이 뭐예요
+comida favorita
+cuál es tu comida favorita
+plat préféré
+quel est ton plat préféré</t>
+        </is>
+      </c>
+      <c r="D13" s="46" t="inlineStr">
+        <is>
+          <t>わたしは朴葉味噌が大好きです。香ばしくて、ご飯がすすみますよ。</t>
+        </is>
+      </c>
+      <c r="E13" s="46" t="inlineStr">
+        <is>
+          <t>I love hoba miso! It's fragrant and goes perfectly with rice.</t>
+        </is>
+      </c>
+      <c r="F13" s="46" t="inlineStr">
+        <is>
+          <t>我最喜欢朴叶味噌了！香喷喷的，特别下饭。</t>
+        </is>
+      </c>
+      <c r="G13" s="46" t="inlineStr">
+        <is>
+          <t>저는 호바미소를 정말 좋아해요. 고소해서 밥이 술술 넘어가요.</t>
+        </is>
+      </c>
+      <c r="H13" s="46" t="inlineStr">
+        <is>
+          <t>¡Me encanta el hoba miso! Es aromático y va perfecto con arroz.</t>
+        </is>
+      </c>
+      <c r="I13" s="46" t="inlineStr">
+        <is>
+          <t>J'adore le hoba miso ! Il est parfumé et se marie parfaitement avec le riz.</t>
+        </is>
+      </c>
+      <c r="J13" s="46" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="65" t="inlineStr">
+        <is>
+          <t>好きな食べ物</t>
+        </is>
+      </c>
+      <c r="B14" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C14" s="46" t="inlineStr">
+        <is>
+          <t>好きな食べ物
+何が好き
+好物
+なに食べたい
+favorite food
+what's your favorite food
+what is your favorite food
+what do you like to eat
+喜欢吃什么
+最喜欢的食物
+좋아하는 음식
+좋아하는 음식이 뭐예요
+comida favorita
+cuál es tu comida favorita
+plat préféré
+quel est ton plat préféré</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t>五平餅が好きです！甘いたれの香りがたまりません。</t>
+        </is>
+      </c>
+      <c r="E14" s="46" t="inlineStr">
+        <is>
+          <t>I like gohei-mochi! The sweet sauce smells wonderful.</t>
+        </is>
+      </c>
+      <c r="F14" s="46" t="inlineStr">
+        <is>
+          <t>我喜欢五平饼！甜甜的酱汁香气真让人受不了。</t>
+        </is>
+      </c>
+      <c r="G14" s="46" t="inlineStr">
+        <is>
+          <t>고헤이모치를 좋아해요! 달콤한 소스 향이 최고예요.</t>
+        </is>
+      </c>
+      <c r="H14" s="46" t="inlineStr">
+        <is>
+          <t>¡Me gusta el gohei-mochi! La salsa dulce huele de maravilla.</t>
+        </is>
+      </c>
+      <c r="I14" s="46" t="inlineStr">
+        <is>
+          <t>J'aime le gohei-mochi ! La sauce sucrée sent délicieusement bon.</t>
+        </is>
+      </c>
+      <c r="J14" s="46" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="65" t="inlineStr">
+        <is>
+          <t>趣味</t>
+        </is>
+      </c>
+      <c r="B15" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C15" s="46" t="inlineStr">
+        <is>
+          <t>趣味
+趣味は何
+休みの日は何してる
+好きなこと
+hobby
+hobbies
+what's your hobby
+what are your hobbies
+what do you do for fun
+爱好
+你的爱好是什么
+兴趣
+취미
+취미가 뭐예요
+pasatiempo
+cuál es tu pasatiempo
+passe-temps
+loisirs
+quel est ton passe-temps</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="inlineStr">
+        <is>
+          <t>合掌造りの屋根をながめるのが好きです。季節ごとに表情が変わるんですよ。</t>
+        </is>
+      </c>
+      <c r="E15" s="46" t="inlineStr">
+        <is>
+          <t>I love looking at the thatched gassho roofs. They change with every season.</t>
+        </is>
+      </c>
+      <c r="F15" s="46" t="inlineStr">
+        <is>
+          <t>我喜欢眺望合掌造的茅草屋顶，每个季节的样子都不一样哦。</t>
+        </is>
+      </c>
+      <c r="G15" s="46" t="inlineStr">
+        <is>
+          <t>갓쇼즈쿠리 지붕을 바라보는 걸 좋아해요. 계절마다 모습이 달라져요.</t>
+        </is>
+      </c>
+      <c r="H15" s="46" t="inlineStr">
+        <is>
+          <t>Me encanta mirar los techos de paja de las casas gassho. Cambian con cada estación.</t>
+        </is>
+      </c>
+      <c r="I15" s="46" t="inlineStr">
+        <is>
+          <t>J'adore contempler les toits de chaume des maisons gassho. Ils changent à chaque saison.</t>
+        </is>
+      </c>
+      <c r="J15" s="46" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="65" t="inlineStr">
+        <is>
+          <t>ほめられた</t>
+        </is>
+      </c>
+      <c r="B16" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="inlineStr">
+        <is>
+          <t>かわいい
+かわいいね
+かわいいですね
+すごいね
+賢いね
+cute
+you are cute
+so cute
+smart
+可爱
+好可爱
+귀여워
+귀엽다
+귀여워요
+linda
+qué linda
+mignonne
+trop mignon</t>
+        </is>
+      </c>
+      <c r="D16" s="46" t="inlineStr">
+        <is>
+          <t>ありがとうございます！そう言ってもらえるとうれしいです。</t>
+        </is>
+      </c>
+      <c r="E16" s="46" t="inlineStr">
+        <is>
+          <t>Thank you! That makes me happy.</t>
+        </is>
+      </c>
+      <c r="F16" s="46" t="inlineStr">
+        <is>
+          <t>谢谢！听您这么说我很开心。</t>
+        </is>
+      </c>
+      <c r="G16" s="46" t="inlineStr">
+        <is>
+          <t>고마워요! 그렇게 말해 주시니 기뻐요.</t>
+        </is>
+      </c>
+      <c r="H16" s="46" t="inlineStr">
+        <is>
+          <t>¡Gracias! Me alegra mucho oír eso.</t>
+        </is>
+      </c>
+      <c r="I16" s="46" t="inlineStr">
+        <is>
+          <t>Merci ! Ça me fait très plaisir.</t>
+        </is>
+      </c>
+      <c r="J16" s="46" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="65" t="inlineStr">
+        <is>
+          <t>ほめられた</t>
+        </is>
+      </c>
+      <c r="B17" s="65" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>かわいい
+かわいいね
+かわいいですね
+すごいね
+賢いね
+cute
+you are cute
+so cute
+smart
+可爱
+好可爱
+귀여워
+귀엽다
+귀여워요
+linda
+qué linda
+mignonne
+trop mignon</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
+        <is>
+          <t>えへへ、照れちゃいます。白川郷も素敵なところですよ！</t>
+        </is>
+      </c>
+      <c r="E17" s="46" t="inlineStr">
+        <is>
+          <t>Hehe, you're making me blush. Shirakawa-go is lovely too!</t>
+        </is>
+      </c>
+      <c r="F17" s="46" t="inlineStr">
+        <is>
+          <t>嘿嘿，有点不好意思呢。白川乡也是个很棒的地方哦！</t>
+        </is>
+      </c>
+      <c r="G17" s="46" t="inlineStr">
+        <is>
+          <t>헤헤, 쑥스러워요. 시라카와고도 멋진 곳이에요!</t>
+        </is>
+      </c>
+      <c r="H17" s="46" t="inlineStr">
+        <is>
+          <t>Jeje, me da vergüenza. ¡Shirakawa-go también es precioso!</t>
+        </is>
+      </c>
+      <c r="I17" s="46" t="inlineStr">
+        <is>
+          <t>Hihi, vous me faites rougir. Shirakawa-go est aussi un endroit merveilleux !</t>
+        </is>
+      </c>
+      <c r="J17" s="46" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="59" t="inlineStr">
+        <is>
+          <t>※ 「こんにちは」「ありがとう」などへの返事です。質問回答集で見つからなかったときに使います。　種類は あいさつ／お礼／名前／元気／さようなら のほか、自分で名前を付けて足せます（「聞き方」に言い方を1行に1つ）。　キャラクターには ID（main など）か「共通」を書きます。そのキャラクターの行が無い種類は「共通」の返事になります。　同じ種類の行を何行か書くと、その中から選んで答えます。{名前} は、そのキャラクターの名前に置き換わります。　管理画面の「キャラクター」から書けます（保存すると自動で翻訳されます）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:L10"/>
+    <mergeCell ref="A19:J22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -1146,7 +1146,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="64" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1156,31 +1156,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="64" t="n">
+      <c r="C2" s="65" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="64" t="n">
+      <c r="D2" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="64" t="n">
+      <c r="E2" s="65" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="64" t="n">
+      <c r="F2" s="65" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="64" t="n">
+      <c r="G2" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="64" t="n">
+      <c r="H2" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="64" t="n">
+      <c r="I2" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="64" t="n">
+      <c r="J2" s="65" t="n">
         <v>0.664</v>
       </c>
-      <c r="K2" s="64" t="n">
+      <c r="K2" s="65" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="64" t="inlineStr">
+      <c r="A3" s="65" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1200,31 +1200,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="64" t="n">
+      <c r="C3" s="65" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="64" t="n">
+      <c r="D3" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="64" t="n">
+      <c r="E3" s="65" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="64" t="n">
+      <c r="F3" s="65" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="64" t="n">
+      <c r="G3" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="64" t="n">
+      <c r="H3" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="64" t="n">
+      <c r="I3" s="65" t="n">
         <v>0.145</v>
       </c>
-      <c r="J3" s="64" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="K3" s="64" t="n">
+      <c r="J3" s="65" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="K3" s="65" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="64" t="inlineStr">
+      <c r="A4" s="65" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1244,31 +1244,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="64" t="n">
+      <c r="C4" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="64" t="n">
+      <c r="D4" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="64" t="n">
+      <c r="E4" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="64" t="n">
+      <c r="F4" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="64" t="n">
+      <c r="G4" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="64" t="n">
+      <c r="H4" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="64" t="n">
+      <c r="I4" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="64" t="n">
+      <c r="J4" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="64" t="n">
+      <c r="K4" s="65" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1277,6 +1277,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="59" t="inlineStr">
         <is>
@@ -1340,7 +1341,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="64" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1350,10 +1351,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="64" t="n">
+      <c r="C2" s="65" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="64" t="n">
+      <c r="D2" s="65" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1363,7 +1364,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="64" t="inlineStr">
+      <c r="A3" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1373,16 +1374,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="64" t="n">
+      <c r="C3" s="65" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="64" t="n">
+      <c r="D3" s="65" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="64" t="inlineStr">
+      <c r="A4" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1392,16 +1393,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="64" t="n">
+      <c r="C4" s="65" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="64" t="n">
+      <c r="D4" s="65" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="64" t="inlineStr">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1411,16 +1412,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="64" t="n">
+      <c r="C5" s="65" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="64" t="n">
+      <c r="D5" s="65" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="64" t="inlineStr">
+      <c r="A6" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1430,16 +1431,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="64" t="n">
+      <c r="C6" s="65" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="64" t="n">
+      <c r="D6" s="65" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1449,10 +1450,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="64" t="n">
+      <c r="C7" s="65" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="64" t="n">
+      <c r="D7" s="65" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1512,17 +1513,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="64" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="64" t="inlineStr">
+      <c r="B2" s="65" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="64" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1534,17 +1535,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="64" t="inlineStr">
+      <c r="A3" s="65" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="64" t="inlineStr">
+      <c r="B3" s="65" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="64" t="inlineStr">
+      <c r="C3" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1552,17 +1553,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="64" t="inlineStr">
+      <c r="A4" s="65" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="64" t="inlineStr">
+      <c r="B4" s="65" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="64" t="inlineStr">
+      <c r="C4" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1574,17 +1575,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="64" t="inlineStr">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="64" t="inlineStr">
+      <c r="B5" s="65" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="64" t="inlineStr">
+      <c r="C5" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1596,17 +1597,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="64" t="inlineStr">
+      <c r="A6" s="65" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="64" t="inlineStr">
+      <c r="B6" s="65" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="64" t="inlineStr">
+      <c r="C6" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1614,17 +1615,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="64" t="inlineStr">
+      <c r="B7" s="65" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="64" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1632,17 +1633,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="64" t="inlineStr">
+      <c r="A8" s="65" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="64" t="inlineStr">
+      <c r="B8" s="65" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="64" t="inlineStr">
+      <c r="C8" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1654,17 +1655,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="64" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="64" t="inlineStr">
+      <c r="B9" s="65" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="64" t="inlineStr">
+      <c r="C9" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1676,17 +1677,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="64" t="inlineStr">
+      <c r="A10" s="65" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="64" t="inlineStr">
+      <c r="B10" s="65" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="64" t="inlineStr">
+      <c r="C10" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1698,17 +1699,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="64" t="inlineStr">
+      <c r="A11" s="65" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="64" t="inlineStr">
+      <c r="B11" s="65" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="64" t="inlineStr">
+      <c r="C11" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1716,17 +1717,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="64" t="inlineStr">
+      <c r="A12" s="65" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="64" t="inlineStr">
+      <c r="B12" s="65" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="64" t="inlineStr">
+      <c r="C12" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1734,17 +1735,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="64" t="inlineStr">
+      <c r="A13" s="65" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="64" t="inlineStr">
+      <c r="B13" s="65" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="64" t="inlineStr">
+      <c r="C13" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1756,17 +1757,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="64" t="inlineStr">
+      <c r="A14" s="65" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="64" t="inlineStr">
+      <c r="B14" s="65" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="64" t="inlineStr">
+      <c r="C14" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1778,17 +1779,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="64" t="inlineStr">
+      <c r="A15" s="65" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="64" t="inlineStr">
+      <c r="B15" s="65" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="64" t="inlineStr">
+      <c r="C15" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1800,17 +1801,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="64" t="inlineStr">
+      <c r="A16" s="65" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="64" t="inlineStr">
+      <c r="B16" s="65" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="64" t="inlineStr">
+      <c r="C16" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1822,17 +1823,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="64" t="inlineStr">
+      <c r="A17" s="65" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="64" t="inlineStr">
+      <c r="B17" s="65" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="64" t="inlineStr">
+      <c r="C17" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1844,17 +1845,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="64" t="inlineStr">
+      <c r="A18" s="65" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="64" t="inlineStr">
+      <c r="B18" s="65" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="64" t="inlineStr">
+      <c r="C18" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1866,17 +1867,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="64" t="inlineStr">
+      <c r="A19" s="65" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="64" t="inlineStr">
+      <c r="B19" s="65" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="64" t="inlineStr">
+      <c r="C19" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1884,17 +1885,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="64" t="inlineStr">
+      <c r="A20" s="65" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="64" t="inlineStr">
+      <c r="B20" s="65" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="64" t="inlineStr">
+      <c r="C20" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1902,17 +1903,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="64" t="inlineStr">
+      <c r="A21" s="65" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="64" t="inlineStr">
+      <c r="B21" s="65" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="64" t="inlineStr">
+      <c r="C21" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1924,17 +1925,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="64" t="inlineStr">
+      <c r="A22" s="65" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="64" t="inlineStr">
+      <c r="B22" s="65" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="64" t="inlineStr">
+      <c r="C22" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1946,17 +1947,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="64" t="inlineStr">
+      <c r="A23" s="65" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="64" t="inlineStr">
+      <c r="B23" s="65" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="64" t="inlineStr">
+      <c r="C23" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1968,17 +1969,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="64" t="inlineStr">
+      <c r="A24" s="65" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="64" t="inlineStr">
+      <c r="B24" s="65" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="64" t="inlineStr">
+      <c r="C24" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1990,17 +1991,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="65" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="64" t="inlineStr">
+      <c r="B25" s="65" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="64" t="inlineStr">
+      <c r="C25" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2008,17 +2009,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="A26" s="65" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="64" t="inlineStr">
+      <c r="B26" s="65" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="64" t="inlineStr">
+      <c r="C26" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2026,17 +2027,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="65" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="64" t="inlineStr">
+      <c r="B27" s="65" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="64" t="inlineStr">
+      <c r="C27" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2048,17 +2049,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="64" t="inlineStr">
+      <c r="A28" s="65" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="64" t="inlineStr">
+      <c r="B28" s="65" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="64" t="inlineStr">
+      <c r="C28" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2070,17 +2071,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="64" t="inlineStr">
+      <c r="A29" s="65" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="64" t="inlineStr">
+      <c r="B29" s="65" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="64" t="inlineStr">
+      <c r="C29" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2092,17 +2093,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="64" t="inlineStr">
+      <c r="A30" s="65" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="64" t="inlineStr">
+      <c r="B30" s="65" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="64" t="inlineStr">
+      <c r="C30" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2110,17 +2111,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="64" t="inlineStr">
+      <c r="A31" s="65" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="64" t="inlineStr">
+      <c r="B31" s="65" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="64" t="inlineStr">
+      <c r="C31" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2132,17 +2133,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="64" t="inlineStr">
+      <c r="A32" s="65" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="64" t="inlineStr">
+      <c r="B32" s="65" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="64" t="inlineStr">
+      <c r="C32" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2150,17 +2151,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="64" t="inlineStr">
+      <c r="A33" s="65" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="64" t="inlineStr">
+      <c r="B33" s="65" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="64" t="inlineStr">
+      <c r="C33" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2168,17 +2169,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="64" t="inlineStr">
+      <c r="A34" s="65" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="64" t="inlineStr">
+      <c r="B34" s="65" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="64" t="inlineStr">
+      <c r="C34" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2186,17 +2187,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="64" t="inlineStr">
+      <c r="A35" s="65" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="64" t="inlineStr">
+      <c r="B35" s="65" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="64" t="inlineStr">
+      <c r="C35" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2204,17 +2205,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="64" t="inlineStr">
+      <c r="A36" s="65" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="64" t="inlineStr">
+      <c r="B36" s="65" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="64" t="inlineStr">
+      <c r="C36" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2222,17 +2223,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="64" t="inlineStr">
+      <c r="A37" s="65" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="64" t="inlineStr">
+      <c r="B37" s="65" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="64" t="inlineStr">
+      <c r="C37" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2240,17 +2241,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="64" t="inlineStr">
+      <c r="A38" s="65" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="64" t="inlineStr">
+      <c r="B38" s="65" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="64" t="inlineStr">
+      <c r="C38" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2258,17 +2259,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="64" t="inlineStr">
+      <c r="A39" s="65" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="64" t="inlineStr">
+      <c r="B39" s="65" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="64" t="inlineStr">
+      <c r="C39" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2276,17 +2277,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="64" t="inlineStr">
+      <c r="A40" s="65" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="64" t="inlineStr">
+      <c r="B40" s="65" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="64" t="inlineStr">
+      <c r="C40" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2298,17 +2299,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="64" t="inlineStr">
+      <c r="A41" s="65" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="64" t="inlineStr">
+      <c r="B41" s="65" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="64" t="inlineStr">
+      <c r="C41" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2316,17 +2317,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="64" t="inlineStr">
+      <c r="A42" s="65" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="64" t="inlineStr">
+      <c r="B42" s="65" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="64" t="inlineStr">
+      <c r="C42" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2338,17 +2339,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="64" t="inlineStr">
+      <c r="A43" s="65" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="64" t="inlineStr">
+      <c r="B43" s="65" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="64" t="inlineStr">
+      <c r="C43" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2356,17 +2357,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="64" t="inlineStr">
+      <c r="A44" s="65" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="64" t="inlineStr">
+      <c r="B44" s="65" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="64" t="inlineStr">
+      <c r="C44" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2378,17 +2379,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="64" t="inlineStr">
+      <c r="A45" s="65" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="64" t="inlineStr">
+      <c r="B45" s="65" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="64" t="inlineStr">
+      <c r="C45" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -4867,7 +4868,7 @@
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="64" t="n"/>
+      <c r="N43" s="65" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -6056,17 +6057,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="64" t="inlineStr">
+      <c r="A66" s="65" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="64" t="inlineStr">
+      <c r="B66" s="65" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="64" t="inlineStr">
+      <c r="C66" s="65" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -6096,26 +6097,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="64" t="inlineStr">
+      <c r="G66" s="65" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="64" t="n"/>
-      <c r="I66" s="64" t="inlineStr">
+      <c r="H66" s="65" t="n"/>
+      <c r="I66" s="65" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="64" t="inlineStr">
+      <c r="J66" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="64" t="n"/>
-      <c r="L66" s="64" t="n"/>
-      <c r="M66" s="64" t="n"/>
-      <c r="N66" s="64" t="n"/>
+      <c r="K66" s="65" t="n"/>
+      <c r="L66" s="65" t="n"/>
+      <c r="M66" s="65" t="n"/>
+      <c r="N66" s="65" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -16612,12 +16613,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="64" t="inlineStr">
+      <c r="A302" s="65" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="64" t="inlineStr">
+      <c r="B302" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16643,12 +16644,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="64" t="inlineStr">
+      <c r="A303" s="65" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="64" t="inlineStr">
+      <c r="B303" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16674,12 +16675,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="64" t="inlineStr">
+      <c r="A304" s="65" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="64" t="inlineStr">
+      <c r="B304" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16705,12 +16706,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="64" t="inlineStr">
+      <c r="A305" s="65" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="64" t="inlineStr">
+      <c r="B305" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16736,12 +16737,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="64" t="inlineStr">
+      <c r="A306" s="65" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="64" t="inlineStr">
+      <c r="B306" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -16767,12 +16768,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="64" t="inlineStr">
+      <c r="A307" s="65" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="64" t="inlineStr">
+      <c r="B307" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16798,12 +16799,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="64" t="inlineStr">
+      <c r="A308" s="65" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="64" t="inlineStr">
+      <c r="B308" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16829,12 +16830,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="64" t="inlineStr">
+      <c r="A309" s="65" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="64" t="inlineStr">
+      <c r="B309" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16860,12 +16861,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="64" t="inlineStr">
+      <c r="A310" s="65" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="64" t="inlineStr">
+      <c r="B310" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16891,12 +16892,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="64" t="inlineStr">
+      <c r="A311" s="65" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="64" t="inlineStr">
+      <c r="B311" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -16922,12 +16923,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="64" t="inlineStr">
+      <c r="A312" s="65" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="64" t="inlineStr">
+      <c r="B312" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16952,12 +16953,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="64" t="inlineStr">
+      <c r="A313" s="65" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="64" t="inlineStr">
+      <c r="B313" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16982,12 +16983,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="64" t="inlineStr">
+      <c r="A314" s="65" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="64" t="inlineStr">
+      <c r="B314" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17012,12 +17013,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="64" t="inlineStr">
+      <c r="A315" s="65" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="64" t="inlineStr">
+      <c r="B315" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17042,12 +17043,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="64" t="inlineStr">
+      <c r="A316" s="65" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="64" t="inlineStr">
+      <c r="B316" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17072,12 +17073,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="64" t="inlineStr">
+      <c r="A317" s="65" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="64" t="inlineStr">
+      <c r="B317" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17103,12 +17104,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="64" t="inlineStr">
+      <c r="A318" s="65" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="64" t="inlineStr">
+      <c r="B318" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17134,12 +17135,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="64" t="inlineStr">
+      <c r="A319" s="65" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="64" t="inlineStr">
+      <c r="B319" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17165,12 +17166,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="64" t="inlineStr">
+      <c r="A320" s="65" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="64" t="inlineStr">
+      <c r="B320" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17196,12 +17197,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="64" t="inlineStr">
+      <c r="A321" s="65" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="64" t="inlineStr">
+      <c r="B321" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17227,12 +17228,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="64" t="inlineStr">
+      <c r="A322" s="65" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="64" t="inlineStr">
+      <c r="B322" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17257,12 +17258,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="64" t="inlineStr">
+      <c r="A323" s="65" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="64" t="inlineStr">
+      <c r="B323" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17287,12 +17288,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="64" t="inlineStr">
+      <c r="A324" s="65" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="64" t="inlineStr">
+      <c r="B324" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17317,12 +17318,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="64" t="inlineStr">
+      <c r="A325" s="65" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="64" t="inlineStr">
+      <c r="B325" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17347,12 +17348,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="64" t="inlineStr">
+      <c r="A326" s="65" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="64" t="inlineStr">
+      <c r="B326" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17377,12 +17378,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="64" t="inlineStr">
+      <c r="A327" s="65" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="64" t="inlineStr">
+      <c r="B327" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17409,12 +17410,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="64" t="inlineStr">
+      <c r="A328" s="65" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="64" t="inlineStr">
+      <c r="B328" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17441,12 +17442,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="64" t="inlineStr">
+      <c r="A329" s="65" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="64" t="inlineStr">
+      <c r="B329" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17473,12 +17474,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="64" t="inlineStr">
+      <c r="A330" s="65" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="64" t="inlineStr">
+      <c r="B330" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17505,12 +17506,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="64" t="inlineStr">
+      <c r="A331" s="65" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="64" t="inlineStr">
+      <c r="B331" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17537,12 +17538,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="64" t="inlineStr">
+      <c r="A332" s="65" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="64" t="inlineStr">
+      <c r="B332" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17569,12 +17570,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="64" t="inlineStr">
+      <c r="A333" s="65" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="64" t="inlineStr">
+      <c r="B333" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17601,12 +17602,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="64" t="inlineStr">
+      <c r="A334" s="65" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="64" t="inlineStr">
+      <c r="B334" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17633,12 +17634,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="64" t="inlineStr">
+      <c r="A335" s="65" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="64" t="inlineStr">
+      <c r="B335" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17665,12 +17666,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="64" t="inlineStr">
+      <c r="A336" s="65" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="64" t="inlineStr">
+      <c r="B336" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17697,12 +17698,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="64" t="inlineStr">
+      <c r="A337" s="65" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="64" t="inlineStr">
+      <c r="B337" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17729,12 +17730,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="64" t="inlineStr">
+      <c r="A338" s="65" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="64" t="inlineStr">
+      <c r="B338" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17761,12 +17762,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="64" t="inlineStr">
+      <c r="A339" s="65" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="64" t="inlineStr">
+      <c r="B339" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17793,12 +17794,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="64" t="inlineStr">
+      <c r="A340" s="65" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="64" t="inlineStr">
+      <c r="B340" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17825,12 +17826,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="64" t="inlineStr">
+      <c r="A341" s="65" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="64" t="inlineStr">
+      <c r="B341" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17857,12 +17858,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="64" t="inlineStr">
+      <c r="A342" s="65" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="64" t="inlineStr">
+      <c r="B342" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17889,12 +17890,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="64" t="inlineStr">
+      <c r="A343" s="65" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="64" t="inlineStr">
+      <c r="B343" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17921,12 +17922,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="64" t="inlineStr">
+      <c r="A344" s="65" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="64" t="inlineStr">
+      <c r="B344" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17953,12 +17954,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="64" t="inlineStr">
+      <c r="A345" s="65" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="64" t="inlineStr">
+      <c r="B345" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17985,12 +17986,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="64" t="inlineStr">
+      <c r="A346" s="65" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="64" t="inlineStr">
+      <c r="B346" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18017,12 +18018,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="64" t="inlineStr">
+      <c r="A347" s="65" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="64" t="inlineStr">
+      <c r="B347" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18049,12 +18050,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="64" t="inlineStr">
+      <c r="A348" s="65" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="64" t="inlineStr">
+      <c r="B348" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18081,12 +18082,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="64" t="inlineStr">
+      <c r="A349" s="65" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="64" t="inlineStr">
+      <c r="B349" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18113,12 +18114,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="64" t="inlineStr">
+      <c r="A350" s="65" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="64" t="inlineStr">
+      <c r="B350" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18145,12 +18146,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="64" t="inlineStr">
+      <c r="A351" s="65" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="64" t="inlineStr">
+      <c r="B351" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18177,12 +18178,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="64" t="inlineStr">
+      <c r="A352" s="65" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="64" t="inlineStr">
+      <c r="B352" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18208,12 +18209,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="64" t="inlineStr">
+      <c r="A353" s="65" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="64" t="inlineStr">
+      <c r="B353" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18239,12 +18240,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="64" t="inlineStr">
+      <c r="A354" s="65" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="64" t="inlineStr">
+      <c r="B354" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18270,12 +18271,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="64" t="inlineStr">
+      <c r="A355" s="65" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="64" t="inlineStr">
+      <c r="B355" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18301,12 +18302,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="64" t="inlineStr">
+      <c r="A356" s="65" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="64" t="inlineStr">
+      <c r="B356" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18332,12 +18333,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="64" t="inlineStr">
+      <c r="A357" s="65" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="64" t="inlineStr">
+      <c r="B357" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18363,12 +18364,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="64" t="inlineStr">
+      <c r="A358" s="65" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="64" t="inlineStr">
+      <c r="B358" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18394,12 +18395,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="64" t="inlineStr">
+      <c r="A359" s="65" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="64" t="inlineStr">
+      <c r="B359" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18425,12 +18426,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="64" t="inlineStr">
+      <c r="A360" s="65" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="64" t="inlineStr">
+      <c r="B360" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18456,12 +18457,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="64" t="inlineStr">
+      <c r="A361" s="65" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="64" t="inlineStr">
+      <c r="B361" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18487,12 +18488,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="64" t="inlineStr">
+      <c r="A362" s="65" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="64" t="inlineStr">
+      <c r="B362" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18519,12 +18520,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="64" t="inlineStr">
+      <c r="A363" s="65" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="64" t="inlineStr">
+      <c r="B363" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18551,12 +18552,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="64" t="inlineStr">
+      <c r="A364" s="65" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="64" t="inlineStr">
+      <c r="B364" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18583,12 +18584,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="64" t="inlineStr">
+      <c r="A365" s="65" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="64" t="inlineStr">
+      <c r="B365" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18615,12 +18616,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="64" t="inlineStr">
+      <c r="A366" s="65" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="64" t="inlineStr">
+      <c r="B366" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18647,12 +18648,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="64" t="inlineStr">
+      <c r="A367" s="65" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="64" t="inlineStr">
+      <c r="B367" s="65" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18679,12 +18680,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="64" t="inlineStr">
+      <c r="A368" s="65" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="64" t="inlineStr">
+      <c r="B368" s="65" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18711,12 +18712,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="64" t="inlineStr">
+      <c r="A369" s="65" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="64" t="inlineStr">
+      <c r="B369" s="65" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18743,12 +18744,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="64" t="inlineStr">
+      <c r="A370" s="65" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="64" t="inlineStr">
+      <c r="B370" s="65" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18775,12 +18776,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="64" t="inlineStr">
+      <c r="A371" s="65" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="64" t="inlineStr">
+      <c r="B371" s="65" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -19916,7 +19917,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="64" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -19926,7 +19927,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="64" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19938,7 +19939,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="64" t="inlineStr">
+      <c r="A3" s="65" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -19948,7 +19949,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="64" t="inlineStr">
+      <c r="C3" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19960,7 +19961,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="64" t="inlineStr">
+      <c r="A4" s="65" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -19970,7 +19971,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="64" t="inlineStr">
+      <c r="C4" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19982,7 +19983,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="64" t="inlineStr">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -19992,7 +19993,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="64" t="inlineStr">
+      <c r="C5" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20004,7 +20005,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="64" t="inlineStr">
+      <c r="A6" s="65" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20014,7 +20015,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="64" t="inlineStr">
+      <c r="C6" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20026,7 +20027,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20036,7 +20037,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="64" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20048,7 +20049,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="64" t="inlineStr">
+      <c r="A8" s="65" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20058,7 +20059,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="64" t="inlineStr">
+      <c r="C8" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20070,7 +20071,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="64" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20080,7 +20081,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="64" t="inlineStr">
+      <c r="C9" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20092,7 +20093,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="64" t="inlineStr">
+      <c r="A10" s="65" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20102,7 +20103,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="64" t="inlineStr">
+      <c r="C10" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20114,7 +20115,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="64" t="inlineStr">
+      <c r="A11" s="65" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20124,7 +20125,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="64" t="inlineStr">
+      <c r="C11" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20136,7 +20137,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="64" t="inlineStr">
+      <c r="A12" s="65" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20146,7 +20147,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="64" t="inlineStr">
+      <c r="C12" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20158,7 +20159,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="64" t="inlineStr">
+      <c r="A13" s="65" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20168,7 +20169,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="64" t="inlineStr">
+      <c r="C13" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20310,53 +20311,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="64" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="64" t="inlineStr">
+      <c r="B2" s="65" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="64" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="64" t="inlineStr">
+      <c r="D2" s="65" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="64" t="inlineStr">
+      <c r="E2" s="65" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="64" t="inlineStr">
+      <c r="F2" s="65" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="64" t="inlineStr">
+      <c r="G2" s="65" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="64" t="inlineStr">
+      <c r="H2" s="65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="64" t="inlineStr">
+      <c r="I2" s="65" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="64" t="n"/>
-      <c r="K2" s="64" t="inlineStr">
+      <c r="J2" s="65" t="n"/>
+      <c r="K2" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20393,45 +20394,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="64" t="inlineStr">
+      <c r="A3" s="65" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="64" t="inlineStr">
+      <c r="B3" s="65" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="64" t="inlineStr">
+      <c r="C3" s="65" t="inlineStr">
         <is>
           <t>main.png</t>
         </is>
       </c>
-      <c r="D3" s="64" t="n"/>
-      <c r="E3" s="64" t="n"/>
-      <c r="F3" s="64" t="n">
+      <c r="D3" s="65" t="n"/>
+      <c r="E3" s="65" t="n"/>
+      <c r="F3" s="65" t="n">
         <v>0.16</v>
       </c>
-      <c r="G3" s="64" t="n">
+      <c r="G3" s="65" t="n">
         <v>0.3</v>
       </c>
-      <c r="H3" s="64" t="inlineStr">
+      <c r="H3" s="65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="64" t="inlineStr">
+      <c r="I3" s="65" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="64" t="inlineStr">
+      <c r="J3" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="64" t="inlineStr">
+      <c r="K3" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20468,45 +20469,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="64" t="inlineStr">
+      <c r="A4" s="65" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="64" t="inlineStr">
+      <c r="B4" s="65" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="64" t="inlineStr">
+      <c r="C4" s="65" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="64" t="n"/>
-      <c r="E4" s="64" t="n"/>
-      <c r="F4" s="64" t="inlineStr">
+      <c r="D4" s="65" t="n"/>
+      <c r="E4" s="65" t="n"/>
+      <c r="F4" s="65" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="64" t="inlineStr">
+      <c r="G4" s="65" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="64" t="inlineStr">
+      <c r="H4" s="65" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="64" t="inlineStr">
+      <c r="I4" s="65" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="64" t="n"/>
-      <c r="K4" s="64" t="inlineStr">
+      <c r="J4" s="65" t="n"/>
+      <c r="K4" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20543,45 +20544,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="64" t="inlineStr">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="64" t="inlineStr">
+      <c r="B5" s="65" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="64" t="inlineStr">
+      <c r="C5" s="65" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="64" t="n"/>
-      <c r="E5" s="64" t="n"/>
-      <c r="F5" s="64" t="inlineStr">
+      <c r="D5" s="65" t="n"/>
+      <c r="E5" s="65" t="n"/>
+      <c r="F5" s="65" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="64" t="inlineStr">
+      <c r="G5" s="65" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="64" t="inlineStr">
+      <c r="H5" s="65" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="64" t="inlineStr">
+      <c r="I5" s="65" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="64" t="n"/>
-      <c r="K5" s="64" t="inlineStr">
+      <c r="J5" s="65" t="n"/>
+      <c r="K5" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20618,45 +20619,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="64" t="inlineStr">
+      <c r="A6" s="65" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="64" t="inlineStr">
+      <c r="B6" s="65" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="64" t="inlineStr">
+      <c r="C6" s="65" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="64" t="n"/>
-      <c r="E6" s="64" t="n"/>
-      <c r="F6" s="64" t="inlineStr">
+      <c r="D6" s="65" t="n"/>
+      <c r="E6" s="65" t="n"/>
+      <c r="F6" s="65" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="64" t="inlineStr">
+      <c r="G6" s="65" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="64" t="inlineStr">
+      <c r="H6" s="65" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="64" t="inlineStr">
+      <c r="I6" s="65" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="64" t="n"/>
-      <c r="K6" s="64" t="inlineStr">
+      <c r="J6" s="65" t="n"/>
+      <c r="K6" s="65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -1169,7 +1169,7 @@
         <v>0.1</v>
       </c>
       <c r="G2" s="65" t="n">
-        <v>1</v>
+        <v>0.864</v>
       </c>
       <c r="H2" s="65" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="65" t="n">
-        <v>0.664</v>
+        <v>0.864</v>
       </c>
       <c r="K2" s="65" t="n">
         <v>1.1</v>
@@ -20415,7 +20415,7 @@
         <v>0.16</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>0.3</v>
+        <v>0.253</v>
       </c>
       <c r="H3" s="65" t="inlineStr">
         <is>
@@ -20693,6 +20693,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="52" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -1277,7 +1277,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="59" t="inlineStr">
         <is>
@@ -20406,7 +20405,7 @@
       </c>
       <c r="C3" s="65" t="inlineStr">
         <is>
-          <t>main.png</t>
+          <t>main_idle_20261013041339.png</t>
         </is>
       </c>
       <c r="D3" s="65" t="n"/>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20405,7 +20405,7 @@
       </c>
       <c r="C3" s="65" t="inlineStr">
         <is>
-          <t>main_idle_20261013041339.png</t>
+          <t>main_idle_20261013041354.png</t>
         </is>
       </c>
       <c r="D3" s="65" t="n"/>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="65" t="n">
-        <v>1</v>
+        <v>0.728</v>
       </c>
       <c r="H4" s="65" t="n">
         <v>0</v>
@@ -1277,6 +1277,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="59" t="inlineStr">
         <is>
@@ -20411,10 +20412,10 @@
       <c r="D3" s="65" t="n"/>
       <c r="E3" s="65" t="n"/>
       <c r="F3" s="65" t="n">
-        <v>0.16</v>
+        <v>0.175</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>0.253</v>
+        <v>0.569</v>
       </c>
       <c r="H3" s="65" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20415,7 +20415,7 @@
         <v>0.175</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>0.569</v>
+        <v>0.343</v>
       </c>
       <c r="H3" s="65" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20415,7 +20415,7 @@
         <v>0.175</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>0.343</v>
+        <v>0.172</v>
       </c>
       <c r="H3" s="65" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20415,7 +20415,7 @@
         <v>0.175</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>0.172</v>
+        <v>0.344</v>
       </c>
       <c r="H3" s="65" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -1216,10 +1216,10 @@
         <v>1</v>
       </c>
       <c r="H3" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="65" t="n">
         <v>0</v>
-      </c>
-      <c r="I3" s="65" t="n">
-        <v>0.145</v>
       </c>
       <c r="J3" s="65" t="n">
         <v>0.753</v>
@@ -20693,7 +20693,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="52" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -1213,10 +1213,10 @@
         <v>0.1</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H3" s="65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="65" t="n">
         <v>0</v>
@@ -20415,7 +20415,7 @@
         <v>0.175</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>0.344</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H3" s="65" t="inlineStr">
         <is>
@@ -20693,6 +20693,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="52" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="65" t="n">
-        <v>0.728</v>
+        <v>0.681</v>
       </c>
       <c r="H4" s="65" t="n">
         <v>0</v>
@@ -20412,10 +20412,10 @@
       <c r="D3" s="65" t="n"/>
       <c r="E3" s="65" t="n"/>
       <c r="F3" s="65" t="n">
-        <v>0.175</v>
+        <v>0.235</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="H3" s="65" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -20415,7 +20415,7 @@
         <v>0.235</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>0.607</v>
+        <v>0.365</v>
       </c>
       <c r="H3" s="65" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -1213,7 +1213,7 @@
         <v>0.1</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>0.75</v>
+        <v>0.929</v>
       </c>
       <c r="H3" s="65" t="n">
         <v>0</v>
@@ -20415,7 +20415,7 @@
         <v>0.235</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>0.365</v>
+        <v>0.346</v>
       </c>
       <c r="H3" s="65" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -1169,7 +1169,7 @@
         <v>0.1</v>
       </c>
       <c r="G2" s="65" t="n">
-        <v>0.864</v>
+        <v>0.957</v>
       </c>
       <c r="H2" s="65" t="n">
         <v>0</v>
@@ -20415,7 +20415,7 @@
         <v>0.235</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>0.346</v>
+        <v>0.313</v>
       </c>
       <c r="H3" s="65" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="65" t="n">
-        <v>0.681</v>
+        <v>0.981</v>
       </c>
       <c r="H4" s="65" t="n">
         <v>0</v>
@@ -20415,7 +20415,7 @@
         <v>0.235</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>0.313</v>
+        <v>0.338</v>
       </c>
       <c r="H3" s="65" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="65" t="n">
-        <v>0.981</v>
+        <v>0.788</v>
       </c>
       <c r="H4" s="65" t="n">
         <v>0</v>
@@ -20415,7 +20415,7 @@
         <v>0.235</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>0.338</v>
+        <v>0.552</v>
       </c>
       <c r="H3" s="65" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="65" t="n">
-        <v>0.788</v>
+        <v>0.92</v>
       </c>
       <c r="H4" s="65" t="n">
         <v>0</v>
@@ -20406,16 +20406,16 @@
       </c>
       <c r="C3" s="65" t="inlineStr">
         <is>
-          <t>main_idle_20261013041354.png</t>
+          <t>main_idle_20261013044809.png</t>
         </is>
       </c>
       <c r="D3" s="65" t="n"/>
       <c r="E3" s="65" t="n"/>
       <c r="F3" s="65" t="n">
-        <v>0.235</v>
+        <v>0.179</v>
       </c>
       <c r="G3" s="65" t="n">
-        <v>0.552</v>
+        <v>0.23</v>
       </c>
       <c r="H3" s="65" t="inlineStr">
         <is>
@@ -20693,7 +20693,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="52" t="inlineStr">
         <is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -1266,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="65" t="n">
-        <v>0</v>
+        <v>0.884</v>
       </c>
       <c r="K4" s="65" t="n">
         <v>1</v>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -445,6 +445,18 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1277,7 +1289,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="59" t="inlineStr">
         <is>
@@ -2420,7 +2431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:P75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.2"/>
   <cols>
     <col width="16" customWidth="1" style="6" min="1" max="1"/>
@@ -2435,6 +2446,7 @@
     <col width="24" customWidth="1" style="8" min="10" max="10"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2511,6 +2523,11 @@
       <c r="O1" s="48" t="inlineStr">
         <is>
           <t>備考</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>最終更新</t>
         </is>
       </c>
     </row>
@@ -2732,22 +2749,22 @@
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="66" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="66" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="44" t="inlineStr">
         <is>
           <t>atm
 お金 おろ
@@ -2757,34 +2774,44 @@
 お金 引き出</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="44" t="inlineStr">
+        <is>
+          <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。白川郷バスターミナルを出て右へ、約2㎞歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。外貨の両替だけの場合は、白川郷バスターミナル内のお手洗い近くのエクスチェンジマシンをご利用ください。</t>
+        </is>
+      </c>
+      <c r="F6" s="44" t="inlineStr">
         <is>
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
         </is>
       </c>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="G6" s="66" t="n"/>
+      <c r="H6" s="66" t="n"/>
+      <c r="I6" s="66" t="inlineStr">
         <is>
           <t>atm_bt.mp3</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="66" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="14" t="inlineStr">
+      <c r="K6" s="66" t="n"/>
+      <c r="L6" s="66" t="n"/>
+      <c r="M6" s="66" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N6" s="35" t="inlineStr">
+      <c r="N6" s="67" t="inlineStr">
         <is>
           <t>ATMはどこ</t>
+        </is>
+      </c>
+      <c r="O6" s="67" t="n"/>
+      <c r="P6" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:14</t>
         </is>
       </c>
     </row>
@@ -7325,32 +7352,35 @@
       </c>
     </row>
     <row r="22" ht="64.8" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="67" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>ATM
-withdraw cash
+      <c r="C22" s="46" t="inlineStr">
+        <is>
+          <t>ATM cash machine
 withdraw money
 post office
-cash machine
-get cash</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>Cards issued outside Japan can only be used at the post office ATM. It is about a 20-minute walk: leave this building and turn right. Cards issued in Japan can be used at the JA ATM. It is about a 2-minute walk: leave this building and turn left.</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="n"/>
+foreign card
+currency exchange</t>
+        </is>
+      </c>
+      <c r="D22" s="46" t="inlineStr">
+        <is>
+          <t>If you have a card issued overseas, you can only use the ATM at the post office. Exit Shirakawa-go Bus Terminal, turn right, and walk for about twenty minutes, which is approximately two kilometers away. If you have a card issued in Japan, you can use the ATM at JA. Exit this building, turn left, and it is about two minutes walk away. If you only need to exchange foreign currency, please use the exchange machine near the restrooms inside Shirakawa-go Bus Terminal.</t>
+        </is>
+      </c>
+      <c r="E22" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。白川郷バスターミナルを出て右へ、約2㎞歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。外貨の両替だけの場合は、白川郷バスターミナル内のお手洗い近くのエクスチェンジマシンをご利用ください。</t>
+        </is>
+      </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
@@ -7358,32 +7388,35 @@
       </c>
     </row>
     <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="67" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>cajero
-atm
-sacar dinero
-sacar efectivo
-retirar efectivo
-oficina correos</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>Las tarjetas emitidas en el extranjero solo pueden usarse en el cajero automático de la oficina de correos. Está a unos 20 minutos a pie: salga de este edificio y gire a la derecha. Las tarjetas emitidas en Japón pueden usarse en el cajero automático de JA. Está a unos 2 minutos a pie: salga de este edificio y gire a la izquierda.</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="n"/>
+      <c r="C23" s="46" t="inlineStr">
+        <is>
+          <t>cajero automático
+retirar dinero
+oficina de correos
+tarjeta extranjera
+cambio de divisas</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="inlineStr">
+        <is>
+          <t>Si tiene una tarjeta emitida en el extranjero, solo puede utilizar el cajero automático en la oficina de correos. Salga de la Terminal de Autobús de Shirakawa-go, gire a la derecha y camine aproximadamente dos kilómetros, lo que le llevará unos veinte minutos. Si tiene una tarjeta emitida en Japón, puede utilizar el cajero automático de JA. Salga de este edificio, gire a la izquierda y está a aproximadamente dos minutos a pie. Si solo necesita cambiar moneda extranjera, utilice la máquina de cambio cerca de los aseos dentro de la Terminal de Autobús de Shirakawa-go.</t>
+        </is>
+      </c>
+      <c r="E23" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。白川郷バスターミナルを出て右へ、約2㎞歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。外貨の両替だけの場合は、白川郷バスターミナル内のお手洗い近くのエクスチェンジマシンをご利用ください。</t>
+        </is>
+      </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
@@ -7391,32 +7424,35 @@
       </c>
     </row>
     <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="67" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>atm
-distributeur
+      <c r="C24" s="46" t="inlineStr">
+        <is>
+          <t>distributeur automatique
 retirer argent
-retrait espèces
-bureau poste
-billets banque retirer</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>Les cartes émises à l'étranger ne peuvent être utilisées qu'au distributeur du bureau de poste. Il se trouve à environ 20 minutes à pied : en sortant de ce bâtiment, tournez à droite. Les cartes émises au Japon peuvent être utilisées au distributeur de la JA. Il se trouve à environ 2 minutes à pied : en sortant de ce bâtiment, tournez à gauche.</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="n"/>
+bureau de poste
+carte étrangère
+change devises</t>
+        </is>
+      </c>
+      <c r="D24" s="46" t="inlineStr">
+        <is>
+          <t>Si vous avez une carte émise à l'étranger, vous ne pouvez utiliser que le distributeur automatique de la poste. En sortant de la gare routière de Shirakawa-go, tournez à droite et marchez environ deux kilomètres, ce qui prend environ vingt minutes. Si vous avez une carte émise au Japon, vous pouvez utiliser le distributeur automatique de la JA. En sortant de ce bâtiment, tournez à gauche et c'est à environ deux minutes à pied. Si vous avez besoin uniquement de changer des devises étrangères, veuillez utiliser le distributeur de change situé près des toilettes à l'intérieur de la gare routière de Shirakawa-go.</t>
+        </is>
+      </c>
+      <c r="E24" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。白川郷バスターミナルを出て右へ、約2㎞歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。外貨の両替だけの場合は、白川郷バスターミナル内のお手洗い近くのエクスチェンジマシンをご利用ください。</t>
+        </is>
+      </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
@@ -7424,32 +7460,35 @@
       </c>
     </row>
     <row r="25" ht="81" customHeight="1">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="67" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>atm
-에이티엠
-현금 인출
-돈 인출
-현금 뽑
-우체국</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>해외에서 발급된 카드는 우체국 ATM에서만 이용하실 수 있습니다. 이 건물을 나가서 오른쪽으로 걸어서 20분 정도 거리에 있습니다. 일본에서 발급된 카드는 JA ATM을 이용하실 수 있습니다. 이 건물을 나가서 왼쪽으로 걸어서 2분 정도 거리에 있습니다.</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="n"/>
+      <c r="C25" s="46" t="inlineStr">
+        <is>
+          <t>ATM 현금인출기
+돈 빼다 인출
+우체국
+외국카드
+환전 환전하다</t>
+        </is>
+      </c>
+      <c r="D25" s="46" t="inlineStr">
+        <is>
+          <t>해외에서 발급한 카드는 우체국의 ATM만 이용할 수 있습니다. 시라카와고 버스터미널을 나와 오른쪽으로 약 2킬로미터, 걸어서 약 20분 정도 떨어진 곳에 있습니다. 일본에서 발급한 카드는 JA의 ATM을 이용할 수 있습니다. 이 건물을 나와 왼쪽으로 걸어서 약 2분 정도의 거리에 있습니다. 외화 환전만 필요하신 경우에는 시라카와고 버스터미널 내 화장실 근처의 환전기를 이용해주세요.</t>
+        </is>
+      </c>
+      <c r="E25" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。白川郷バスターミナルを出て右へ、約2㎞歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。外貨の両替だけの場合は、白川郷バスターミナル内のお手洗い近くのエクスチェンジマシンをご利用ください。</t>
+        </is>
+      </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
@@ -7457,32 +7496,35 @@
       </c>
     </row>
     <row r="26" ht="64.8" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="68" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="68" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
-        <is>
-          <t>ATM
-取钱
-取现
-提款
+      <c r="C26" s="69" t="inlineStr">
+        <is>
+          <t>自动提款机
+取款 现金
 邮局
-现金 不够</t>
-        </is>
-      </c>
-      <c r="D26" s="25" t="inlineStr">
-        <is>
-          <t>海外发行的银行卡只能在邮局的ATM使用。出了这栋建筑向右，步行约20分钟即可到达。日本国内发行的银行卡可以使用JA（日本农业协同组合）的ATM。出了这栋建筑向左，步行约2分钟即可到达。</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="n"/>
+外币兑换
+国外银行卡</t>
+        </is>
+      </c>
+      <c r="D26" s="69" t="inlineStr">
+        <is>
+          <t>如果您持有海外发行的银行卡，只能使用邮局的自动提款机。从白川乡巴士总站出口向右走，约需二十分钟左右，距离约两公里。如果您持有在日本发行的银行卡，可以使用JA的自动提款机。从本建筑物出口向左走，约二分钟即可到达。如果您仅需要兑换外币，请使用白川乡巴士总站内洗手间附近的兑换机。</t>
+        </is>
+      </c>
+      <c r="E26" s="69" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたカードは、郵便局のATMのみご利用いただけます。白川郷バスターミナルを出て右へ、約2㎞歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。外貨の両替だけの場合は、白川郷バスターミナル内のお手洗い近くのエクスチェンジマシンをご利用ください。</t>
+        </is>
+      </c>
       <c r="F26" s="26" t="inlineStr">
         <is>
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -456,6 +456,24 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1158,7 +1176,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="65" t="inlineStr">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1168,31 +1186,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="65" t="n">
+      <c r="C2" s="67" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="65" t="n">
+      <c r="D2" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="65" t="n">
+      <c r="E2" s="67" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="65" t="n">
+      <c r="F2" s="67" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="65" t="n">
+      <c r="G2" s="67" t="n">
         <v>0.957</v>
       </c>
-      <c r="H2" s="65" t="n">
+      <c r="H2" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="65" t="n">
+      <c r="I2" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="65" t="n">
+      <c r="J2" s="67" t="n">
         <v>0.864</v>
       </c>
-      <c r="K2" s="65" t="n">
+      <c r="K2" s="67" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1202,7 +1220,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="65" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1212,31 +1230,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="65" t="n">
+      <c r="C3" s="67" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="65" t="n">
+      <c r="D3" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="65" t="n">
+      <c r="E3" s="67" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="65" t="n">
+      <c r="F3" s="67" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="65" t="n">
+      <c r="G3" s="67" t="n">
         <v>0.929</v>
       </c>
-      <c r="H3" s="65" t="n">
+      <c r="H3" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="65" t="n">
+      <c r="I3" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="65" t="n">
+      <c r="J3" s="67" t="n">
         <v>0.753</v>
       </c>
-      <c r="K3" s="65" t="n">
+      <c r="K3" s="67" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1246,7 +1264,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="65" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1256,31 +1274,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="65" t="n">
+      <c r="C4" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="65" t="n">
+      <c r="D4" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="65" t="n">
+      <c r="E4" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="65" t="n">
+      <c r="F4" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="65" t="n">
+      <c r="G4" s="67" t="n">
         <v>0.92</v>
       </c>
-      <c r="H4" s="65" t="n">
+      <c r="H4" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="65" t="n">
+      <c r="I4" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="65" t="n">
+      <c r="J4" s="67" t="n">
         <v>0.884</v>
       </c>
-      <c r="K4" s="65" t="n">
+      <c r="K4" s="67" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1352,7 +1370,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="65" t="inlineStr">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1362,10 +1380,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="65" t="n">
+      <c r="C2" s="67" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="65" t="n">
+      <c r="D2" s="67" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1375,7 +1393,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="65" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1385,16 +1403,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="65" t="n">
+      <c r="C3" s="67" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="65" t="n">
+      <c r="D3" s="67" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="65" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1404,16 +1422,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="65" t="n">
+      <c r="C4" s="67" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="65" t="n">
+      <c r="D4" s="67" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="65" t="inlineStr">
+      <c r="A5" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1423,16 +1441,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="65" t="n">
+      <c r="C5" s="67" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="65" t="n">
+      <c r="D5" s="67" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="65" t="inlineStr">
+      <c r="A6" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1442,16 +1460,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="65" t="n">
+      <c r="C6" s="67" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="65" t="n">
+      <c r="D6" s="67" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr">
+      <c r="A7" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1461,10 +1479,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="65" t="n">
+      <c r="C7" s="67" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="65" t="n">
+      <c r="D7" s="67" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1524,17 +1542,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="65" t="inlineStr">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="65" t="inlineStr">
+      <c r="B2" s="67" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="65" t="inlineStr">
+      <c r="C2" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1546,17 +1564,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="65" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="65" t="inlineStr">
+      <c r="B3" s="67" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="65" t="inlineStr">
+      <c r="C3" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1564,17 +1582,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="65" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="65" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="65" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1586,17 +1604,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="65" t="inlineStr">
+      <c r="A5" s="67" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="65" t="inlineStr">
+      <c r="B5" s="67" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="65" t="inlineStr">
+      <c r="C5" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1608,17 +1626,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="65" t="inlineStr">
+      <c r="A6" s="67" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="65" t="inlineStr">
+      <c r="B6" s="67" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="65" t="inlineStr">
+      <c r="C6" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1626,17 +1644,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr">
+      <c r="A7" s="67" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="65" t="inlineStr">
+      <c r="B7" s="67" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="65" t="inlineStr">
+      <c r="C7" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1644,17 +1662,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="65" t="inlineStr">
+      <c r="A8" s="67" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="65" t="inlineStr">
+      <c r="B8" s="67" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="65" t="inlineStr">
+      <c r="C8" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1666,17 +1684,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="65" t="inlineStr">
+      <c r="A9" s="67" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="65" t="inlineStr">
+      <c r="B9" s="67" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="65" t="inlineStr">
+      <c r="C9" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1688,17 +1706,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="65" t="inlineStr">
+      <c r="A10" s="67" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="65" t="inlineStr">
+      <c r="B10" s="67" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="65" t="inlineStr">
+      <c r="C10" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1710,17 +1728,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="65" t="inlineStr">
+      <c r="A11" s="67" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="65" t="inlineStr">
+      <c r="B11" s="67" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="65" t="inlineStr">
+      <c r="C11" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1728,17 +1746,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="65" t="inlineStr">
+      <c r="A12" s="67" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="65" t="inlineStr">
+      <c r="B12" s="67" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="65" t="inlineStr">
+      <c r="C12" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1746,17 +1764,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="65" t="inlineStr">
+      <c r="A13" s="67" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="65" t="inlineStr">
+      <c r="B13" s="67" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="65" t="inlineStr">
+      <c r="C13" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1768,17 +1786,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="65" t="inlineStr">
+      <c r="A14" s="67" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="65" t="inlineStr">
+      <c r="B14" s="67" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="65" t="inlineStr">
+      <c r="C14" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1790,17 +1808,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="65" t="inlineStr">
+      <c r="A15" s="67" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="65" t="inlineStr">
+      <c r="B15" s="67" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="65" t="inlineStr">
+      <c r="C15" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1812,17 +1830,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="65" t="inlineStr">
+      <c r="A16" s="67" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="65" t="inlineStr">
+      <c r="B16" s="67" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="65" t="inlineStr">
+      <c r="C16" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1834,17 +1852,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="65" t="inlineStr">
+      <c r="A17" s="67" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="65" t="inlineStr">
+      <c r="B17" s="67" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="65" t="inlineStr">
+      <c r="C17" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1856,17 +1874,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="65" t="inlineStr">
+      <c r="A18" s="67" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="65" t="inlineStr">
+      <c r="B18" s="67" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="65" t="inlineStr">
+      <c r="C18" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1878,17 +1896,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="65" t="inlineStr">
+      <c r="A19" s="67" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="65" t="inlineStr">
+      <c r="B19" s="67" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="65" t="inlineStr">
+      <c r="C19" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1896,17 +1914,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="65" t="inlineStr">
+      <c r="A20" s="67" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="65" t="inlineStr">
+      <c r="B20" s="67" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="65" t="inlineStr">
+      <c r="C20" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1914,17 +1932,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="65" t="inlineStr">
+      <c r="A21" s="67" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="65" t="inlineStr">
+      <c r="B21" s="67" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="65" t="inlineStr">
+      <c r="C21" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1936,17 +1954,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="65" t="inlineStr">
+      <c r="A22" s="67" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="65" t="inlineStr">
+      <c r="B22" s="67" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="65" t="inlineStr">
+      <c r="C22" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1958,17 +1976,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="65" t="inlineStr">
+      <c r="A23" s="67" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="65" t="inlineStr">
+      <c r="B23" s="67" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="65" t="inlineStr">
+      <c r="C23" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1980,17 +1998,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="65" t="inlineStr">
+      <c r="A24" s="67" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="65" t="inlineStr">
+      <c r="B24" s="67" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="65" t="inlineStr">
+      <c r="C24" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2002,17 +2020,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="65" t="inlineStr">
+      <c r="A25" s="67" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="65" t="inlineStr">
+      <c r="B25" s="67" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="65" t="inlineStr">
+      <c r="C25" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2020,17 +2038,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="65" t="inlineStr">
+      <c r="A26" s="67" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="65" t="inlineStr">
+      <c r="B26" s="67" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="65" t="inlineStr">
+      <c r="C26" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2038,17 +2056,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="65" t="inlineStr">
+      <c r="A27" s="67" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="65" t="inlineStr">
+      <c r="B27" s="67" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="65" t="inlineStr">
+      <c r="C27" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2060,17 +2078,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="65" t="inlineStr">
+      <c r="A28" s="67" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="65" t="inlineStr">
+      <c r="B28" s="67" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="65" t="inlineStr">
+      <c r="C28" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2082,17 +2100,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="65" t="inlineStr">
+      <c r="A29" s="67" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="65" t="inlineStr">
+      <c r="B29" s="67" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="65" t="inlineStr">
+      <c r="C29" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2104,17 +2122,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="65" t="inlineStr">
+      <c r="A30" s="67" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="65" t="inlineStr">
+      <c r="B30" s="67" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="65" t="inlineStr">
+      <c r="C30" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2122,17 +2140,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="65" t="inlineStr">
+      <c r="A31" s="67" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="65" t="inlineStr">
+      <c r="B31" s="67" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="65" t="inlineStr">
+      <c r="C31" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2144,17 +2162,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="65" t="inlineStr">
+      <c r="A32" s="67" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="65" t="inlineStr">
+      <c r="B32" s="67" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="65" t="inlineStr">
+      <c r="C32" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2162,17 +2180,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="65" t="inlineStr">
+      <c r="A33" s="67" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="65" t="inlineStr">
+      <c r="B33" s="67" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="65" t="inlineStr">
+      <c r="C33" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2180,17 +2198,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="65" t="inlineStr">
+      <c r="A34" s="67" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="65" t="inlineStr">
+      <c r="B34" s="67" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="65" t="inlineStr">
+      <c r="C34" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2198,17 +2216,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="65" t="inlineStr">
+      <c r="A35" s="67" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="65" t="inlineStr">
+      <c r="B35" s="67" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="65" t="inlineStr">
+      <c r="C35" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2216,17 +2234,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="65" t="inlineStr">
+      <c r="A36" s="67" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="65" t="inlineStr">
+      <c r="B36" s="67" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="65" t="inlineStr">
+      <c r="C36" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2234,17 +2252,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="65" t="inlineStr">
+      <c r="A37" s="67" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="65" t="inlineStr">
+      <c r="B37" s="67" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="65" t="inlineStr">
+      <c r="C37" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2252,17 +2270,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="65" t="inlineStr">
+      <c r="A38" s="67" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="65" t="inlineStr">
+      <c r="B38" s="67" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="65" t="inlineStr">
+      <c r="C38" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2270,17 +2288,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="65" t="inlineStr">
+      <c r="A39" s="67" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="65" t="inlineStr">
+      <c r="B39" s="67" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="65" t="inlineStr">
+      <c r="C39" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2288,17 +2306,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="65" t="inlineStr">
+      <c r="A40" s="67" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="65" t="inlineStr">
+      <c r="B40" s="67" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="65" t="inlineStr">
+      <c r="C40" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2310,17 +2328,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="65" t="inlineStr">
+      <c r="A41" s="67" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="65" t="inlineStr">
+      <c r="B41" s="67" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="65" t="inlineStr">
+      <c r="C41" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2328,17 +2346,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="65" t="inlineStr">
+      <c r="A42" s="67" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="65" t="inlineStr">
+      <c r="B42" s="67" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="65" t="inlineStr">
+      <c r="C42" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2350,17 +2368,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="65" t="inlineStr">
+      <c r="A43" s="67" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="65" t="inlineStr">
+      <c r="B43" s="67" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="65" t="inlineStr">
+      <c r="C43" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2368,17 +2386,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="65" t="inlineStr">
+      <c r="A44" s="67" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="65" t="inlineStr">
+      <c r="B44" s="67" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="65" t="inlineStr">
+      <c r="C44" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2390,17 +2408,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="65" t="inlineStr">
+      <c r="A45" s="67" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="65" t="inlineStr">
+      <c r="B45" s="67" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="65" t="inlineStr">
+      <c r="C45" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2816,22 +2834,22 @@
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="70" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="70" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="70" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="44" t="inlineStr">
         <is>
           <t>atm
 お金 おろ
@@ -2841,33 +2859,40 @@
 お金 引き出</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はここから車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="E7" s="44" t="inlineStr">
+        <is>
+          <t>海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はであいの館から約2.2㎞車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
+        </is>
+      </c>
+      <c r="F7" s="44" t="inlineStr">
         <is>
           <t>海外のカードは鳩谷郵便局のATM、日本のカードは和田家前のJAのATMをご利用ください。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="G7" s="70" t="n"/>
+      <c r="H7" s="70" t="n"/>
+      <c r="I7" s="70" t="inlineStr">
         <is>
           <t>atm_deai.mp3</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="70" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K7" s="11" t="n"/>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="14" t="inlineStr">
+      <c r="K7" s="70" t="n"/>
+      <c r="L7" s="70" t="n"/>
+      <c r="M7" s="70" t="inlineStr">
         <is>
           <t>atm</t>
+        </is>
+      </c>
+      <c r="N7" s="71" t="n"/>
+      <c r="O7" s="71" t="n"/>
+      <c r="P7" s="71" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:15</t>
         </is>
       </c>
     </row>
@@ -4828,17 +4853,17 @@
       </c>
     </row>
     <row r="43" ht="249.6" customHeight="1">
-      <c r="A43" s="43" t="inlineStr">
+      <c r="A43" s="66" t="inlineStr">
         <is>
           <t>guesthouse_access_deai</t>
         </is>
       </c>
-      <c r="B43" s="43" t="inlineStr">
+      <c r="B43" s="66" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C43" s="43" t="inlineStr">
+      <c r="C43" s="66" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -4872,30 +4897,30 @@
           <t>その建物は鳩谷八幡神社方面にあります。国道は交通量が多いため、川沿いの道をおすすめしております。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G43" s="43" t="inlineStr">
+      <c r="G43" s="66" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H43" s="43" t="n"/>
-      <c r="I43" s="43" t="inlineStr">
+      <c r="H43" s="66" t="n"/>
+      <c r="I43" s="66" t="inlineStr">
         <is>
           <t>guesthouse_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J43" s="43" t="inlineStr">
+      <c r="J43" s="66" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K43" s="43" t="n"/>
-      <c r="L43" s="43" t="n"/>
-      <c r="M43" s="43" t="inlineStr">
+      <c r="K43" s="66" t="n"/>
+      <c r="L43" s="66" t="n"/>
+      <c r="M43" s="66" t="inlineStr">
         <is>
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="65" t="n"/>
+      <c r="N43" s="67" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -6084,17 +6109,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="65" t="inlineStr">
+      <c r="A66" s="67" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="65" t="inlineStr">
+      <c r="B66" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="65" t="inlineStr">
+      <c r="C66" s="67" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -6124,26 +6149,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="65" t="inlineStr">
+      <c r="G66" s="67" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="65" t="n"/>
-      <c r="I66" s="65" t="inlineStr">
+      <c r="H66" s="67" t="n"/>
+      <c r="I66" s="67" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="65" t="inlineStr">
+      <c r="J66" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="65" t="n"/>
-      <c r="L66" s="65" t="n"/>
-      <c r="M66" s="65" t="n"/>
-      <c r="N66" s="65" t="n"/>
+      <c r="K66" s="67" t="n"/>
+      <c r="L66" s="67" t="n"/>
+      <c r="M66" s="67" t="n"/>
+      <c r="N66" s="67" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -7532,32 +7557,35 @@
       </c>
     </row>
     <row r="27" ht="64.8" customHeight="1">
-      <c r="A27" s="27" t="inlineStr">
+      <c r="A27" s="72" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B27" s="72" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="C27" s="28" t="inlineStr">
+      <c r="C27" s="73" t="inlineStr">
         <is>
           <t>ATM
 withdraw cash
-withdraw money
-post office
 cash machine
-get cash</t>
-        </is>
-      </c>
-      <c r="D27" s="28" t="inlineStr">
-        <is>
-          <t>Credit cards issued outside Japan can only be used at the post office ATM. It seems that some cards cannot be used. Please use Hatogaya Post Office, about 5 minutes by car from here. Cash cards and credit cards issued in Japan can be used at the JA ATM. It is in front of Wada House, across from the stop for the shuttle bus to the observatory.</t>
-        </is>
-      </c>
-      <c r="E27" s="27" t="n"/>
+credit card ATM
+where to get money</t>
+        </is>
+      </c>
+      <c r="D27" s="73" t="inlineStr">
+        <is>
+          <t>Foreign-issued credit cards can only be used at post office ATMs. Please note that some cards may not be accepted. The nearest post office is Hatoya Post Office, approximately two point two kilometers away, about five minutes by car from Deai no Mori. For Japanese-issued cash cards and credit cards, you can use JA ATMs. There is one located across from Wada House, near the shuttle bus stop to the observation deck.</t>
+        </is>
+      </c>
+      <c r="E27" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はであいの館から約2.2㎞車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
+        </is>
+      </c>
       <c r="F27" s="29" t="inlineStr">
         <is>
           <t>海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はここから車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
@@ -7565,32 +7593,35 @@
       </c>
     </row>
     <row r="28" ht="64.8" customHeight="1">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="72" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B28" s="72" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="C28" s="28" t="inlineStr">
-        <is>
-          <t>cajero
-atm
+      <c r="C28" s="73" t="inlineStr">
+        <is>
+          <t>cajero automático
 sacar dinero
-sacar efectivo
-retirar efectivo
-oficina correos</t>
-        </is>
-      </c>
-      <c r="D28" s="28" t="inlineStr">
-        <is>
-          <t>Las tarjetas de crédito emitidas en el extranjero solo pueden usarse en el cajero automático de la oficina de correos. Al parecer, algunas tarjetas no se pueden utilizar. Utilice la Oficina de Correos de Hatogaya, a unos 5 minutos en coche desde aquí. Las tarjetas bancarias y de crédito emitidas en Japón pueden usarse en el cajero automático de JA, que está delante de la Casa Wada, enfrente de la parada del autobús lanzadera al mirador.</t>
-        </is>
-      </c>
-      <c r="E28" s="27" t="n"/>
+retiro de efectivo
+tarjeta de crédito
+dónde obtener dinero</t>
+        </is>
+      </c>
+      <c r="D28" s="73" t="inlineStr">
+        <is>
+          <t>Los cajeros automáticos de la oficina de correos solo aceptan tarjetas de crédito emitidas en el extranjero. Tenga en cuenta que algunas tarjetas pueden no ser aceptadas. La oficina de correos más cercana es la Oficina de Correos de Hatoya, aproximadamente a dos punto dos kilómetros de Deai no Mori, a unos cinco minutos en coche. Para tarjetas de débito y tarjetas de crédito emitidas en Japón, puede utilizar los cajeros automáticos de JA. Hay uno ubicado frente a la Casa Wada, cerca de la parada del autobús lanzadera hacia el mirador.</t>
+        </is>
+      </c>
+      <c r="E28" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はであいの館から約2.2㎞車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
+        </is>
+      </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
           <t>海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はここから車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
@@ -7598,32 +7629,35 @@
       </c>
     </row>
     <row r="29" ht="64.8" customHeight="1">
-      <c r="A29" s="27" t="inlineStr">
+      <c r="A29" s="72" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B29" s="27" t="inlineStr">
+      <c r="B29" s="72" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="C29" s="28" t="inlineStr">
-        <is>
-          <t>atm
-distributeur
-retirer argent
-retrait espèces
-bureau poste
-billets banque retirer</t>
-        </is>
-      </c>
-      <c r="D29" s="28" t="inlineStr">
-        <is>
-          <t>Les cartes de crédit émises à l'étranger ne peuvent être utilisées qu'au distributeur du bureau de poste. Il semble que certaines cartes ne soient pas acceptées. Veuillez vous rendre au bureau de poste de Hatogaya, à environ 5 minutes en voiture d'ici. Les cartes bancaires et cartes de crédit émises au Japon peuvent être utilisées au distributeur de la JA. Il se trouve devant la maison Wada, en face de l'arrêt de la navette pour l'observatoire.</t>
-        </is>
-      </c>
-      <c r="E29" s="27" t="n"/>
+      <c r="C29" s="73" t="inlineStr">
+        <is>
+          <t>distributeur automatique
+retrait d'argent
+guichet automatique
+carte de crédit
+où retirer de l'argent</t>
+        </is>
+      </c>
+      <c r="D29" s="73" t="inlineStr">
+        <is>
+          <t>Les cartes de crédit émises à l'étranger ne peuvent être utilisées que aux distributeurs automatiques de la poste. Veuillez noter que certaines cartes pourraient ne pas être acceptées. Le bureau de poste le plus proche est le Bureau de Poste de Hatoya, situé à environ deux point deux kilomètres de Deai no Mori, à environ cinq minutes en voiture. Pour les cartes de débit et les cartes de crédit émises au Japon, vous pouvez utiliser les distributeurs automatiques de JA. Il y en a un situé en face de la Maison Wada, près de l'arrêt de la navette vers le belvédère.</t>
+        </is>
+      </c>
+      <c r="E29" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はであいの館から約2.2㎞車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
+        </is>
+      </c>
       <c r="F29" s="29" t="inlineStr">
         <is>
           <t>海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はここから車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
@@ -7631,32 +7665,35 @@
       </c>
     </row>
     <row r="30" ht="81" customHeight="1">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="72" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B30" s="27" t="inlineStr">
+      <c r="B30" s="72" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="C30" s="28" t="inlineStr">
-        <is>
-          <t>atm
-에이티엠
+      <c r="C30" s="73" t="inlineStr">
+        <is>
+          <t>ATM
 현금 인출
-돈 인출
-현금 뽑
-우체국</t>
-        </is>
-      </c>
-      <c r="D30" s="28" t="inlineStr">
-        <is>
-          <t>해외에서 발급된 신용카드는 우체국 ATM에서만 이용하실 수 있습니다. 일부 이용할 수 없는 카드도 있는 것 같습니다. 우체국은 여기서 차로 5분 정도 거리에 있는 하토가야 우체국을 이용해 주세요. 일본에서 발급된 현금카드나 신용카드는 JA ATM을 이용하실 수 있습니다. 와다 가옥 앞, 전망대행 셔틀버스 승차장 맞은편에 있습니다.</t>
-        </is>
-      </c>
-      <c r="E30" s="27" t="n"/>
+돈 찾
+신용카드
+현금 뽑</t>
+        </is>
+      </c>
+      <c r="D30" s="73" t="inlineStr">
+        <is>
+          <t>해외에서 발행된 신용카드는 우체국 ATM에서만 이용 가능합니다. 일부 카드는 이용하지 못할 수 있습니다. 가장 가까운 우체국은 데아이노모리에서 약 2.2킬로미터 거리의 하토야 우체국입니다. 자동차로 약 5분 소요됩니다. 일본에서 발행된 현금카드와 신용카드는 JA ATM에서 이용 가능합니다. 와다 가 맞은편, 전망대 셔틀버스 승차장 근처에 위치하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="E30" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はであいの館から約2.2㎞車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
+        </is>
+      </c>
       <c r="F30" s="29" t="inlineStr">
         <is>
           <t>海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はここから車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
@@ -7664,32 +7701,35 @@
       </c>
     </row>
     <row r="31" ht="64.8" customHeight="1">
-      <c r="A31" s="30" t="inlineStr">
+      <c r="A31" s="74" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B31" s="30" t="inlineStr">
+      <c r="B31" s="74" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C31" s="31" t="inlineStr">
-        <is>
-          <t>ATM
+      <c r="C31" s="75" t="inlineStr">
+        <is>
+          <t>自动取款机
 取钱
-取现
-提款
-邮局
-现金 不够</t>
-        </is>
-      </c>
-      <c r="D31" s="31" t="inlineStr">
-        <is>
-          <t>海外发行的信用卡只能在邮局的ATM使用，部分银行卡可能无法使用。邮局请前往距此开车约5分钟的鸠谷邮局。日本国内发行的现金卡和信用卡可以使用JA（日本农业协同组合）的ATM，位于和田家前、前往观景台的接驳巴士乘车处对面。</t>
-        </is>
-      </c>
-      <c r="E31" s="30" t="n"/>
+提现
+信用卡
+取款</t>
+        </is>
+      </c>
+      <c r="D31" s="75" t="inlineStr">
+        <is>
+          <t>在邮局自动取款机可以使用外国发行的信用卡。但请注意，部分信用卡可能无法使用。最近的邮局是鸠谷邮局，距离相逢之馆约2.2公里，开车约需5分钟。对于日本发行的现金卡和信用卡，可以使用JA自动取款机。该自动取款机位于和田家对面，观景台班车乘车点附近。</t>
+        </is>
+      </c>
+      <c r="E31" s="75" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はであいの館から約2.2㎞車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
+        </is>
+      </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
           <t>海外で発行されたクレジットカードは、郵便局のATMのみご利用いただけます。一部ご利用になれないカードもあるようです。郵便局はここから車で5分ほどの「鳩谷郵便局」をご利用ください。日本で発行されたキャッシュカードやクレジットカードは、JAのATMをご利用いただけます。和田家前、展望台行きシャトルバス乗り場の向かいにございます。</t>
@@ -16655,12 +16695,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="65" t="inlineStr">
+      <c r="A302" s="67" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="65" t="inlineStr">
+      <c r="B302" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16686,12 +16726,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="65" t="inlineStr">
+      <c r="A303" s="67" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="65" t="inlineStr">
+      <c r="B303" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16717,12 +16757,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="65" t="inlineStr">
+      <c r="A304" s="67" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="65" t="inlineStr">
+      <c r="B304" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16748,12 +16788,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="65" t="inlineStr">
+      <c r="A305" s="67" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="65" t="inlineStr">
+      <c r="B305" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16779,12 +16819,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="65" t="inlineStr">
+      <c r="A306" s="67" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="65" t="inlineStr">
+      <c r="B306" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -16810,12 +16850,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="65" t="inlineStr">
+      <c r="A307" s="67" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="65" t="inlineStr">
+      <c r="B307" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16841,12 +16881,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="65" t="inlineStr">
+      <c r="A308" s="67" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="65" t="inlineStr">
+      <c r="B308" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16872,12 +16912,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="65" t="inlineStr">
+      <c r="A309" s="67" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="65" t="inlineStr">
+      <c r="B309" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16903,12 +16943,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="65" t="inlineStr">
+      <c r="A310" s="67" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="65" t="inlineStr">
+      <c r="B310" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16934,12 +16974,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="65" t="inlineStr">
+      <c r="A311" s="67" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="65" t="inlineStr">
+      <c r="B311" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -16965,12 +17005,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="65" t="inlineStr">
+      <c r="A312" s="67" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="65" t="inlineStr">
+      <c r="B312" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16995,12 +17035,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="65" t="inlineStr">
+      <c r="A313" s="67" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="65" t="inlineStr">
+      <c r="B313" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17025,12 +17065,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="65" t="inlineStr">
+      <c r="A314" s="67" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="65" t="inlineStr">
+      <c r="B314" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17055,12 +17095,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="65" t="inlineStr">
+      <c r="A315" s="67" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="65" t="inlineStr">
+      <c r="B315" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17085,12 +17125,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="65" t="inlineStr">
+      <c r="A316" s="67" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="65" t="inlineStr">
+      <c r="B316" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17115,12 +17155,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="65" t="inlineStr">
+      <c r="A317" s="67" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="65" t="inlineStr">
+      <c r="B317" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17146,12 +17186,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="65" t="inlineStr">
+      <c r="A318" s="67" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="65" t="inlineStr">
+      <c r="B318" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17177,12 +17217,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="65" t="inlineStr">
+      <c r="A319" s="67" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="65" t="inlineStr">
+      <c r="B319" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17208,12 +17248,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="65" t="inlineStr">
+      <c r="A320" s="67" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="65" t="inlineStr">
+      <c r="B320" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17239,12 +17279,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="65" t="inlineStr">
+      <c r="A321" s="67" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="65" t="inlineStr">
+      <c r="B321" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17270,12 +17310,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="65" t="inlineStr">
+      <c r="A322" s="67" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="65" t="inlineStr">
+      <c r="B322" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17300,12 +17340,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="65" t="inlineStr">
+      <c r="A323" s="67" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="65" t="inlineStr">
+      <c r="B323" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17330,12 +17370,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="65" t="inlineStr">
+      <c r="A324" s="67" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="65" t="inlineStr">
+      <c r="B324" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17360,12 +17400,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="65" t="inlineStr">
+      <c r="A325" s="67" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="65" t="inlineStr">
+      <c r="B325" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17390,12 +17430,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="65" t="inlineStr">
+      <c r="A326" s="67" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="65" t="inlineStr">
+      <c r="B326" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17420,12 +17460,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="65" t="inlineStr">
+      <c r="A327" s="67" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="65" t="inlineStr">
+      <c r="B327" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17452,12 +17492,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="65" t="inlineStr">
+      <c r="A328" s="67" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="65" t="inlineStr">
+      <c r="B328" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17484,12 +17524,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="65" t="inlineStr">
+      <c r="A329" s="67" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="65" t="inlineStr">
+      <c r="B329" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17516,12 +17556,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="65" t="inlineStr">
+      <c r="A330" s="67" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="65" t="inlineStr">
+      <c r="B330" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17548,12 +17588,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="65" t="inlineStr">
+      <c r="A331" s="67" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="65" t="inlineStr">
+      <c r="B331" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17580,12 +17620,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="65" t="inlineStr">
+      <c r="A332" s="67" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="65" t="inlineStr">
+      <c r="B332" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17612,12 +17652,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="65" t="inlineStr">
+      <c r="A333" s="67" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="65" t="inlineStr">
+      <c r="B333" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17644,12 +17684,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="65" t="inlineStr">
+      <c r="A334" s="67" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="65" t="inlineStr">
+      <c r="B334" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17676,12 +17716,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="65" t="inlineStr">
+      <c r="A335" s="67" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="65" t="inlineStr">
+      <c r="B335" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17708,12 +17748,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="65" t="inlineStr">
+      <c r="A336" s="67" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="65" t="inlineStr">
+      <c r="B336" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17740,12 +17780,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="65" t="inlineStr">
+      <c r="A337" s="67" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="65" t="inlineStr">
+      <c r="B337" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17772,12 +17812,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="65" t="inlineStr">
+      <c r="A338" s="67" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="65" t="inlineStr">
+      <c r="B338" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17804,12 +17844,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="65" t="inlineStr">
+      <c r="A339" s="67" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="65" t="inlineStr">
+      <c r="B339" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17836,12 +17876,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="65" t="inlineStr">
+      <c r="A340" s="67" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="65" t="inlineStr">
+      <c r="B340" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17868,12 +17908,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="65" t="inlineStr">
+      <c r="A341" s="67" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="65" t="inlineStr">
+      <c r="B341" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17900,12 +17940,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="65" t="inlineStr">
+      <c r="A342" s="67" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="65" t="inlineStr">
+      <c r="B342" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17932,12 +17972,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="65" t="inlineStr">
+      <c r="A343" s="67" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="65" t="inlineStr">
+      <c r="B343" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17964,12 +18004,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="65" t="inlineStr">
+      <c r="A344" s="67" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="65" t="inlineStr">
+      <c r="B344" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17996,12 +18036,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="65" t="inlineStr">
+      <c r="A345" s="67" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="65" t="inlineStr">
+      <c r="B345" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18028,12 +18068,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="65" t="inlineStr">
+      <c r="A346" s="67" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="65" t="inlineStr">
+      <c r="B346" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18060,12 +18100,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="65" t="inlineStr">
+      <c r="A347" s="67" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="65" t="inlineStr">
+      <c r="B347" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18092,12 +18132,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="65" t="inlineStr">
+      <c r="A348" s="67" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="65" t="inlineStr">
+      <c r="B348" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18124,12 +18164,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="65" t="inlineStr">
+      <c r="A349" s="67" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="65" t="inlineStr">
+      <c r="B349" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18156,12 +18196,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="65" t="inlineStr">
+      <c r="A350" s="67" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="65" t="inlineStr">
+      <c r="B350" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18188,12 +18228,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="65" t="inlineStr">
+      <c r="A351" s="67" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="65" t="inlineStr">
+      <c r="B351" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18220,12 +18260,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="65" t="inlineStr">
+      <c r="A352" s="67" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="65" t="inlineStr">
+      <c r="B352" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18251,12 +18291,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="65" t="inlineStr">
+      <c r="A353" s="67" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="65" t="inlineStr">
+      <c r="B353" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18282,12 +18322,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="65" t="inlineStr">
+      <c r="A354" s="67" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="65" t="inlineStr">
+      <c r="B354" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18313,12 +18353,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="65" t="inlineStr">
+      <c r="A355" s="67" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="65" t="inlineStr">
+      <c r="B355" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18344,12 +18384,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="65" t="inlineStr">
+      <c r="A356" s="67" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="65" t="inlineStr">
+      <c r="B356" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18375,12 +18415,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="65" t="inlineStr">
+      <c r="A357" s="67" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="65" t="inlineStr">
+      <c r="B357" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18406,12 +18446,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="65" t="inlineStr">
+      <c r="A358" s="67" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="65" t="inlineStr">
+      <c r="B358" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18437,12 +18477,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="65" t="inlineStr">
+      <c r="A359" s="67" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="65" t="inlineStr">
+      <c r="B359" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18468,12 +18508,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="65" t="inlineStr">
+      <c r="A360" s="67" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="65" t="inlineStr">
+      <c r="B360" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18499,12 +18539,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="65" t="inlineStr">
+      <c r="A361" s="67" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="65" t="inlineStr">
+      <c r="B361" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18530,12 +18570,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="65" t="inlineStr">
+      <c r="A362" s="67" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="65" t="inlineStr">
+      <c r="B362" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18562,12 +18602,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="65" t="inlineStr">
+      <c r="A363" s="67" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="65" t="inlineStr">
+      <c r="B363" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18594,12 +18634,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="65" t="inlineStr">
+      <c r="A364" s="67" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="65" t="inlineStr">
+      <c r="B364" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18626,12 +18666,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="65" t="inlineStr">
+      <c r="A365" s="67" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="65" t="inlineStr">
+      <c r="B365" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18658,12 +18698,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="65" t="inlineStr">
+      <c r="A366" s="67" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="65" t="inlineStr">
+      <c r="B366" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18690,12 +18730,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="65" t="inlineStr">
+      <c r="A367" s="67" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="65" t="inlineStr">
+      <c r="B367" s="67" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18722,12 +18762,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="65" t="inlineStr">
+      <c r="A368" s="67" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="65" t="inlineStr">
+      <c r="B368" s="67" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18754,12 +18794,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="65" t="inlineStr">
+      <c r="A369" s="67" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="65" t="inlineStr">
+      <c r="B369" s="67" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18786,12 +18826,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="65" t="inlineStr">
+      <c r="A370" s="67" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="65" t="inlineStr">
+      <c r="B370" s="67" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18818,12 +18858,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="65" t="inlineStr">
+      <c r="A371" s="67" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="65" t="inlineStr">
+      <c r="B371" s="67" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -19959,7 +19999,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="65" t="inlineStr">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -19969,7 +20009,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="65" t="inlineStr">
+      <c r="C2" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -19981,7 +20021,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="65" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -19991,7 +20031,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="65" t="inlineStr">
+      <c r="C3" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20003,7 +20043,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="65" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -20013,7 +20053,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="65" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20025,7 +20065,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="65" t="inlineStr">
+      <c r="A5" s="67" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -20035,7 +20075,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="65" t="inlineStr">
+      <c r="C5" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20047,7 +20087,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="65" t="inlineStr">
+      <c r="A6" s="67" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20057,7 +20097,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="65" t="inlineStr">
+      <c r="C6" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20069,7 +20109,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr">
+      <c r="A7" s="67" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20079,7 +20119,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="65" t="inlineStr">
+      <c r="C7" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20091,7 +20131,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="65" t="inlineStr">
+      <c r="A8" s="67" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20101,7 +20141,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="65" t="inlineStr">
+      <c r="C8" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20113,7 +20153,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="65" t="inlineStr">
+      <c r="A9" s="67" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20123,7 +20163,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="65" t="inlineStr">
+      <c r="C9" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20135,7 +20175,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="65" t="inlineStr">
+      <c r="A10" s="67" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20145,7 +20185,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="65" t="inlineStr">
+      <c r="C10" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20157,7 +20197,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="65" t="inlineStr">
+      <c r="A11" s="67" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20167,7 +20207,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="65" t="inlineStr">
+      <c r="C11" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20179,7 +20219,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="65" t="inlineStr">
+      <c r="A12" s="67" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20189,7 +20229,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="65" t="inlineStr">
+      <c r="C12" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20201,7 +20241,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="65" t="inlineStr">
+      <c r="A13" s="67" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20211,7 +20251,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="65" t="inlineStr">
+      <c r="C13" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20353,53 +20393,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="65" t="inlineStr">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="65" t="inlineStr">
+      <c r="B2" s="67" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="65" t="inlineStr">
+      <c r="C2" s="67" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="65" t="inlineStr">
+      <c r="D2" s="67" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="65" t="inlineStr">
+      <c r="E2" s="67" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="65" t="inlineStr">
+      <c r="F2" s="67" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="65" t="inlineStr">
+      <c r="G2" s="67" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="65" t="inlineStr">
+      <c r="H2" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="65" t="inlineStr">
+      <c r="I2" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="65" t="n"/>
-      <c r="K2" s="65" t="inlineStr">
+      <c r="J2" s="67" t="n"/>
+      <c r="K2" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20436,45 +20476,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="65" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="65" t="inlineStr">
+      <c r="B3" s="67" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="65" t="inlineStr">
+      <c r="C3" s="67" t="inlineStr">
         <is>
           <t>main_idle_20261013044809.png</t>
         </is>
       </c>
-      <c r="D3" s="65" t="n"/>
-      <c r="E3" s="65" t="n"/>
-      <c r="F3" s="65" t="n">
+      <c r="D3" s="67" t="n"/>
+      <c r="E3" s="67" t="n"/>
+      <c r="F3" s="67" t="n">
         <v>0.179</v>
       </c>
-      <c r="G3" s="65" t="n">
+      <c r="G3" s="67" t="n">
         <v>0.23</v>
       </c>
-      <c r="H3" s="65" t="inlineStr">
+      <c r="H3" s="67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="65" t="inlineStr">
+      <c r="I3" s="67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="65" t="inlineStr">
+      <c r="J3" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="65" t="inlineStr">
+      <c r="K3" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20511,45 +20551,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="65" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="65" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="65" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="65" t="n"/>
-      <c r="E4" s="65" t="n"/>
-      <c r="F4" s="65" t="inlineStr">
+      <c r="D4" s="67" t="n"/>
+      <c r="E4" s="67" t="n"/>
+      <c r="F4" s="67" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="65" t="inlineStr">
+      <c r="G4" s="67" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="65" t="inlineStr">
+      <c r="H4" s="67" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="65" t="inlineStr">
+      <c r="I4" s="67" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="65" t="n"/>
-      <c r="K4" s="65" t="inlineStr">
+      <c r="J4" s="67" t="n"/>
+      <c r="K4" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20586,45 +20626,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="65" t="inlineStr">
+      <c r="A5" s="67" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="65" t="inlineStr">
+      <c r="B5" s="67" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="65" t="inlineStr">
+      <c r="C5" s="67" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="65" t="n"/>
-      <c r="E5" s="65" t="n"/>
-      <c r="F5" s="65" t="inlineStr">
+      <c r="D5" s="67" t="n"/>
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="65" t="inlineStr">
+      <c r="G5" s="67" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="65" t="inlineStr">
+      <c r="H5" s="67" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="65" t="inlineStr">
+      <c r="I5" s="67" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="65" t="n"/>
-      <c r="K5" s="65" t="inlineStr">
+      <c r="J5" s="67" t="n"/>
+      <c r="K5" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20661,45 +20701,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="65" t="inlineStr">
+      <c r="A6" s="67" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="65" t="inlineStr">
+      <c r="B6" s="67" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="65" t="inlineStr">
+      <c r="C6" s="67" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="65" t="n"/>
-      <c r="E6" s="65" t="n"/>
-      <c r="F6" s="65" t="inlineStr">
+      <c r="D6" s="67" t="n"/>
+      <c r="E6" s="67" t="n"/>
+      <c r="F6" s="67" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="65" t="inlineStr">
+      <c r="G6" s="67" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="65" t="inlineStr">
+      <c r="H6" s="67" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="65" t="inlineStr">
+      <c r="I6" s="67" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="65" t="n"/>
-      <c r="K6" s="65" t="inlineStr">
+      <c r="J6" s="67" t="n"/>
+      <c r="K6" s="67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20821,12 +20861,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="65" t="inlineStr">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B2" s="65" t="inlineStr">
+      <c r="B2" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -20865,12 +20905,12 @@
       <c r="J2" s="46" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="65" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B3" s="65" t="inlineStr">
+      <c r="B3" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -20909,12 +20949,12 @@
       <c r="J3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="65" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B4" s="65" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -20953,12 +20993,12 @@
       <c r="J4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="65" t="inlineStr">
+      <c r="A5" s="67" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B5" s="65" t="inlineStr">
+      <c r="B5" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -20997,12 +21037,12 @@
       <c r="J5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="65" t="inlineStr">
+      <c r="A6" s="67" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B6" s="65" t="inlineStr">
+      <c r="B6" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21041,12 +21081,12 @@
       <c r="J6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr">
+      <c r="A7" s="67" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B7" s="65" t="inlineStr">
+      <c r="B7" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21085,12 +21125,12 @@
       <c r="J7" s="46" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="65" t="inlineStr">
+      <c r="A8" s="67" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B8" s="65" t="inlineStr">
+      <c r="B8" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21129,12 +21169,12 @@
       <c r="J8" s="46" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="65" t="inlineStr">
+      <c r="A9" s="67" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B9" s="65" t="inlineStr">
+      <c r="B9" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21173,12 +21213,12 @@
       <c r="J9" s="46" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="65" t="inlineStr">
+      <c r="A10" s="67" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B10" s="65" t="inlineStr">
+      <c r="B10" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21217,12 +21257,12 @@
       <c r="J10" s="46" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="65" t="inlineStr">
+      <c r="A11" s="67" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B11" s="65" t="inlineStr">
+      <c r="B11" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21261,12 +21301,12 @@
       <c r="J11" s="46" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="65" t="inlineStr">
+      <c r="A12" s="67" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B12" s="65" t="inlineStr">
+      <c r="B12" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21305,12 +21345,12 @@
       <c r="J12" s="46" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="65" t="inlineStr">
+      <c r="A13" s="67" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B13" s="65" t="inlineStr">
+      <c r="B13" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21368,12 +21408,12 @@
       <c r="J13" s="46" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="65" t="inlineStr">
+      <c r="A14" s="67" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B14" s="65" t="inlineStr">
+      <c r="B14" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21431,12 +21471,12 @@
       <c r="J14" s="46" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="65" t="inlineStr">
+      <c r="A15" s="67" t="inlineStr">
         <is>
           <t>趣味</t>
         </is>
       </c>
-      <c r="B15" s="65" t="inlineStr">
+      <c r="B15" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21497,12 +21537,12 @@
       <c r="J15" s="46" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="65" t="inlineStr">
+      <c r="A16" s="67" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B16" s="65" t="inlineStr">
+      <c r="B16" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21562,12 +21602,12 @@
       <c r="J16" s="46" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="65" t="inlineStr">
+      <c r="A17" s="67" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B17" s="65" t="inlineStr">
+      <c r="B17" s="67" t="inlineStr">
         <is>
           <t>共通</t>
         </is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -475,6 +475,18 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1176,7 +1188,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="inlineStr">
+      <c r="A2" s="71" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1186,31 +1198,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="67" t="n">
+      <c r="C2" s="71" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="67" t="n">
+      <c r="D2" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="67" t="n">
+      <c r="E2" s="71" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="67" t="n">
+      <c r="F2" s="71" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="67" t="n">
+      <c r="G2" s="71" t="n">
         <v>0.957</v>
       </c>
-      <c r="H2" s="67" t="n">
+      <c r="H2" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="67" t="n">
+      <c r="I2" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="67" t="n">
+      <c r="J2" s="71" t="n">
         <v>0.864</v>
       </c>
-      <c r="K2" s="67" t="n">
+      <c r="K2" s="71" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1220,7 +1232,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="67" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1230,31 +1242,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="67" t="n">
+      <c r="C3" s="71" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="67" t="n">
+      <c r="D3" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="67" t="n">
+      <c r="E3" s="71" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="67" t="n">
+      <c r="F3" s="71" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="67" t="n">
+      <c r="G3" s="71" t="n">
         <v>0.929</v>
       </c>
-      <c r="H3" s="67" t="n">
+      <c r="H3" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="67" t="n">
+      <c r="I3" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="67" t="n">
+      <c r="J3" s="71" t="n">
         <v>0.753</v>
       </c>
-      <c r="K3" s="67" t="n">
+      <c r="K3" s="71" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1264,7 +1276,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="67" t="inlineStr">
+      <c r="A4" s="71" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1274,31 +1286,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="67" t="n">
+      <c r="C4" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="67" t="n">
+      <c r="D4" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="67" t="n">
+      <c r="E4" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="67" t="n">
+      <c r="F4" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="67" t="n">
+      <c r="G4" s="71" t="n">
         <v>0.92</v>
       </c>
-      <c r="H4" s="67" t="n">
+      <c r="H4" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="67" t="n">
+      <c r="I4" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="67" t="n">
+      <c r="J4" s="71" t="n">
         <v>0.884</v>
       </c>
-      <c r="K4" s="67" t="n">
+      <c r="K4" s="71" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1370,7 +1382,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="inlineStr">
+      <c r="A2" s="71" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1380,10 +1392,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="67" t="n">
+      <c r="C2" s="71" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="67" t="n">
+      <c r="D2" s="71" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1393,7 +1405,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="67" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1403,16 +1415,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="67" t="n">
+      <c r="C3" s="71" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="67" t="n">
+      <c r="D3" s="71" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="67" t="inlineStr">
+      <c r="A4" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1422,16 +1434,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="67" t="n">
+      <c r="C4" s="71" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="67" t="n">
+      <c r="D4" s="71" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="67" t="inlineStr">
+      <c r="A5" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1441,16 +1453,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="67" t="n">
+      <c r="C5" s="71" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="67" t="n">
+      <c r="D5" s="71" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="67" t="inlineStr">
+      <c r="A6" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1460,16 +1472,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="67" t="n">
+      <c r="C6" s="71" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="67" t="n">
+      <c r="D6" s="71" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="67" t="inlineStr">
+      <c r="A7" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1479,10 +1491,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="67" t="n">
+      <c r="C7" s="71" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="67" t="n">
+      <c r="D7" s="71" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1542,17 +1554,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="inlineStr">
+      <c r="A2" s="71" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="67" t="inlineStr">
+      <c r="B2" s="71" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="67" t="inlineStr">
+      <c r="C2" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1564,17 +1576,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="67" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="67" t="inlineStr">
+      <c r="B3" s="71" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="67" t="inlineStr">
+      <c r="C3" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1582,17 +1594,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="67" t="inlineStr">
+      <c r="A4" s="71" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="67" t="inlineStr">
+      <c r="B4" s="71" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="67" t="inlineStr">
+      <c r="C4" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1604,17 +1616,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="67" t="inlineStr">
+      <c r="A5" s="71" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="67" t="inlineStr">
+      <c r="B5" s="71" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="67" t="inlineStr">
+      <c r="C5" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1626,17 +1638,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="67" t="inlineStr">
+      <c r="A6" s="71" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="67" t="inlineStr">
+      <c r="B6" s="71" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="67" t="inlineStr">
+      <c r="C6" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1644,17 +1656,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="67" t="inlineStr">
+      <c r="A7" s="71" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="67" t="inlineStr">
+      <c r="B7" s="71" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="67" t="inlineStr">
+      <c r="C7" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1662,17 +1674,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="67" t="inlineStr">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="67" t="inlineStr">
+      <c r="B8" s="71" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="67" t="inlineStr">
+      <c r="C8" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1684,17 +1696,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="67" t="inlineStr">
+      <c r="A9" s="71" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="67" t="inlineStr">
+      <c r="B9" s="71" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="67" t="inlineStr">
+      <c r="C9" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1706,17 +1718,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="67" t="inlineStr">
+      <c r="A10" s="71" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="67" t="inlineStr">
+      <c r="B10" s="71" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="67" t="inlineStr">
+      <c r="C10" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1728,17 +1740,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="67" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="67" t="inlineStr">
+      <c r="B11" s="71" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="67" t="inlineStr">
+      <c r="C11" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1746,17 +1758,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="67" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="67" t="inlineStr">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="67" t="inlineStr">
+      <c r="C12" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1764,17 +1776,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="67" t="inlineStr">
+      <c r="A13" s="71" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="67" t="inlineStr">
+      <c r="B13" s="71" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="67" t="inlineStr">
+      <c r="C13" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1786,17 +1798,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="71" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="67" t="inlineStr">
+      <c r="B14" s="71" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="67" t="inlineStr">
+      <c r="C14" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1808,17 +1820,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="67" t="inlineStr">
+      <c r="A15" s="71" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="67" t="inlineStr">
+      <c r="B15" s="71" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="67" t="inlineStr">
+      <c r="C15" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1830,17 +1842,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="67" t="inlineStr">
+      <c r="A16" s="71" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="67" t="inlineStr">
+      <c r="B16" s="71" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="67" t="inlineStr">
+      <c r="C16" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1852,17 +1864,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="67" t="inlineStr">
+      <c r="A17" s="71" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="67" t="inlineStr">
+      <c r="B17" s="71" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="67" t="inlineStr">
+      <c r="C17" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1874,17 +1886,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="67" t="inlineStr">
+      <c r="A18" s="71" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="67" t="inlineStr">
+      <c r="B18" s="71" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="67" t="inlineStr">
+      <c r="C18" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1896,17 +1908,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="67" t="inlineStr">
+      <c r="A19" s="71" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="67" t="inlineStr">
+      <c r="B19" s="71" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="67" t="inlineStr">
+      <c r="C19" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1914,17 +1926,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="67" t="inlineStr">
+      <c r="A20" s="71" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="67" t="inlineStr">
+      <c r="B20" s="71" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="67" t="inlineStr">
+      <c r="C20" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1932,17 +1944,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="67" t="inlineStr">
+      <c r="A21" s="71" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="67" t="inlineStr">
+      <c r="B21" s="71" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="67" t="inlineStr">
+      <c r="C21" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1954,17 +1966,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="67" t="inlineStr">
+      <c r="A22" s="71" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="67" t="inlineStr">
+      <c r="B22" s="71" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="67" t="inlineStr">
+      <c r="C22" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1976,17 +1988,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="67" t="inlineStr">
+      <c r="A23" s="71" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="67" t="inlineStr">
+      <c r="B23" s="71" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="67" t="inlineStr">
+      <c r="C23" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1998,17 +2010,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="67" t="inlineStr">
+      <c r="A24" s="71" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="67" t="inlineStr">
+      <c r="B24" s="71" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="67" t="inlineStr">
+      <c r="C24" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2020,17 +2032,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="67" t="inlineStr">
+      <c r="A25" s="71" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="67" t="inlineStr">
+      <c r="B25" s="71" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="67" t="inlineStr">
+      <c r="C25" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2038,17 +2050,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="67" t="inlineStr">
+      <c r="A26" s="71" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="67" t="inlineStr">
+      <c r="B26" s="71" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="67" t="inlineStr">
+      <c r="C26" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2056,17 +2068,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="67" t="inlineStr">
+      <c r="A27" s="71" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="67" t="inlineStr">
+      <c r="B27" s="71" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="67" t="inlineStr">
+      <c r="C27" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2078,17 +2090,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="67" t="inlineStr">
+      <c r="A28" s="71" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="67" t="inlineStr">
+      <c r="B28" s="71" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="67" t="inlineStr">
+      <c r="C28" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2100,17 +2112,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="67" t="inlineStr">
+      <c r="A29" s="71" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="67" t="inlineStr">
+      <c r="B29" s="71" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="67" t="inlineStr">
+      <c r="C29" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2122,17 +2134,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="67" t="inlineStr">
+      <c r="A30" s="71" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="67" t="inlineStr">
+      <c r="B30" s="71" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="67" t="inlineStr">
+      <c r="C30" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2140,17 +2152,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="67" t="inlineStr">
+      <c r="A31" s="71" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="67" t="inlineStr">
+      <c r="B31" s="71" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="67" t="inlineStr">
+      <c r="C31" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2162,17 +2174,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="67" t="inlineStr">
+      <c r="A32" s="71" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="67" t="inlineStr">
+      <c r="B32" s="71" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="67" t="inlineStr">
+      <c r="C32" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2180,17 +2192,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="67" t="inlineStr">
+      <c r="A33" s="71" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="67" t="inlineStr">
+      <c r="B33" s="71" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="67" t="inlineStr">
+      <c r="C33" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2198,17 +2210,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="67" t="inlineStr">
+      <c r="A34" s="71" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="67" t="inlineStr">
+      <c r="B34" s="71" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="67" t="inlineStr">
+      <c r="C34" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2216,17 +2228,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="67" t="inlineStr">
+      <c r="A35" s="71" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="67" t="inlineStr">
+      <c r="B35" s="71" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="67" t="inlineStr">
+      <c r="C35" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2234,17 +2246,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="67" t="inlineStr">
+      <c r="A36" s="71" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="67" t="inlineStr">
+      <c r="B36" s="71" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="67" t="inlineStr">
+      <c r="C36" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2252,17 +2264,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="67" t="inlineStr">
+      <c r="A37" s="71" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="67" t="inlineStr">
+      <c r="B37" s="71" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="67" t="inlineStr">
+      <c r="C37" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2270,17 +2282,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="67" t="inlineStr">
+      <c r="A38" s="71" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="67" t="inlineStr">
+      <c r="B38" s="71" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="67" t="inlineStr">
+      <c r="C38" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2288,17 +2300,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="67" t="inlineStr">
+      <c r="A39" s="71" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="67" t="inlineStr">
+      <c r="B39" s="71" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="67" t="inlineStr">
+      <c r="C39" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2306,17 +2318,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="67" t="inlineStr">
+      <c r="A40" s="71" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="67" t="inlineStr">
+      <c r="B40" s="71" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="67" t="inlineStr">
+      <c r="C40" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2328,17 +2340,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="67" t="inlineStr">
+      <c r="A41" s="71" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="67" t="inlineStr">
+      <c r="B41" s="71" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="67" t="inlineStr">
+      <c r="C41" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2346,17 +2358,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="67" t="inlineStr">
+      <c r="A42" s="71" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="67" t="inlineStr">
+      <c r="B42" s="71" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="67" t="inlineStr">
+      <c r="C42" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2368,17 +2380,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="67" t="inlineStr">
+      <c r="A43" s="71" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="67" t="inlineStr">
+      <c r="B43" s="71" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="67" t="inlineStr">
+      <c r="C43" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2386,17 +2398,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="67" t="inlineStr">
+      <c r="A44" s="71" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="67" t="inlineStr">
+      <c r="B44" s="71" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="67" t="inlineStr">
+      <c r="C44" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2408,17 +2420,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="67" t="inlineStr">
+      <c r="A45" s="71" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="67" t="inlineStr">
+      <c r="B45" s="71" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="67" t="inlineStr">
+      <c r="C45" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2767,17 +2779,17 @@
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="66" t="inlineStr">
+      <c r="A6" s="70" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B6" s="66" t="inlineStr">
+      <c r="B6" s="70" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C6" s="66" t="inlineStr">
+      <c r="C6" s="70" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2802,32 +2814,32 @@
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
         </is>
       </c>
-      <c r="G6" s="66" t="n"/>
-      <c r="H6" s="66" t="n"/>
-      <c r="I6" s="66" t="inlineStr">
+      <c r="G6" s="70" t="n"/>
+      <c r="H6" s="70" t="n"/>
+      <c r="I6" s="70" t="inlineStr">
         <is>
           <t>atm_bt.mp3</t>
         </is>
       </c>
-      <c r="J6" s="66" t="inlineStr">
+      <c r="J6" s="70" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K6" s="66" t="n"/>
-      <c r="L6" s="66" t="n"/>
-      <c r="M6" s="66" t="inlineStr">
+      <c r="K6" s="70" t="n"/>
+      <c r="L6" s="70" t="n"/>
+      <c r="M6" s="70" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N6" s="67" t="inlineStr">
+      <c r="N6" s="71" t="inlineStr">
         <is>
           <t>ATMはどこ</t>
         </is>
       </c>
-      <c r="O6" s="67" t="n"/>
-      <c r="P6" s="67" t="inlineStr">
+      <c r="O6" s="71" t="n"/>
+      <c r="P6" s="71" t="inlineStr">
         <is>
           <t>2026-10-13 17:14</t>
         </is>
@@ -2946,22 +2958,22 @@
       </c>
     </row>
     <row r="9" ht="58.05" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="76" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="76" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="76" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="44" t="inlineStr">
         <is>
           <t>両替
 外貨
@@ -2970,29 +2982,36 @@
 両替 ロッカー</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>外貨の両替は、お手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>外貨の両替は、白川郷バスターミナル内のお手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
+        </is>
+      </c>
+      <c r="F9" s="44" t="n"/>
+      <c r="G9" s="76" t="n"/>
+      <c r="H9" s="76" t="n"/>
+      <c r="I9" s="76" t="inlineStr">
         <is>
           <t>currency_exchange_bt.mp3</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J9" s="76" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="14" t="inlineStr">
+      <c r="K9" s="76" t="n"/>
+      <c r="L9" s="76" t="n"/>
+      <c r="M9" s="76" t="inlineStr">
         <is>
           <t>currency_exchange</t>
+        </is>
+      </c>
+      <c r="N9" s="77" t="n"/>
+      <c r="O9" s="77" t="n"/>
+      <c r="P9" s="77" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:18</t>
         </is>
       </c>
     </row>
@@ -4853,17 +4872,17 @@
       </c>
     </row>
     <row r="43" ht="249.6" customHeight="1">
-      <c r="A43" s="66" t="inlineStr">
+      <c r="A43" s="70" t="inlineStr">
         <is>
           <t>guesthouse_access_deai</t>
         </is>
       </c>
-      <c r="B43" s="66" t="inlineStr">
+      <c r="B43" s="70" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C43" s="66" t="inlineStr">
+      <c r="C43" s="70" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -4897,30 +4916,30 @@
           <t>その建物は鳩谷八幡神社方面にあります。国道は交通量が多いため、川沿いの道をおすすめしております。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G43" s="66" t="inlineStr">
+      <c r="G43" s="70" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H43" s="66" t="n"/>
-      <c r="I43" s="66" t="inlineStr">
+      <c r="H43" s="70" t="n"/>
+      <c r="I43" s="70" t="inlineStr">
         <is>
           <t>guesthouse_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J43" s="66" t="inlineStr">
+      <c r="J43" s="70" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K43" s="66" t="n"/>
-      <c r="L43" s="66" t="n"/>
-      <c r="M43" s="66" t="inlineStr">
+      <c r="K43" s="70" t="n"/>
+      <c r="L43" s="70" t="n"/>
+      <c r="M43" s="70" t="inlineStr">
         <is>
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="67" t="n"/>
+      <c r="N43" s="71" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -6109,17 +6128,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="67" t="inlineStr">
+      <c r="A66" s="71" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="67" t="inlineStr">
+      <c r="B66" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="67" t="inlineStr">
+      <c r="C66" s="71" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -6149,26 +6168,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="67" t="inlineStr">
+      <c r="G66" s="71" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="67" t="n"/>
-      <c r="I66" s="67" t="inlineStr">
+      <c r="H66" s="71" t="n"/>
+      <c r="I66" s="71" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="67" t="inlineStr">
+      <c r="J66" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="67" t="n"/>
-      <c r="L66" s="67" t="n"/>
-      <c r="M66" s="67" t="n"/>
-      <c r="N66" s="67" t="n"/>
+      <c r="K66" s="71" t="n"/>
+      <c r="L66" s="71" t="n"/>
+      <c r="M66" s="71" t="n"/>
+      <c r="N66" s="71" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -7377,12 +7396,12 @@
       </c>
     </row>
     <row r="22" ht="64.8" customHeight="1">
-      <c r="A22" s="67" t="inlineStr">
+      <c r="A22" s="71" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B22" s="67" t="inlineStr">
+      <c r="B22" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7413,12 +7432,12 @@
       </c>
     </row>
     <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="67" t="inlineStr">
+      <c r="A23" s="71" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B23" s="67" t="inlineStr">
+      <c r="B23" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7449,12 +7468,12 @@
       </c>
     </row>
     <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="67" t="inlineStr">
+      <c r="A24" s="71" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B24" s="67" t="inlineStr">
+      <c r="B24" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7485,12 +7504,12 @@
       </c>
     </row>
     <row r="25" ht="81" customHeight="1">
-      <c r="A25" s="67" t="inlineStr">
+      <c r="A25" s="71" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B25" s="67" t="inlineStr">
+      <c r="B25" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7898,32 +7917,35 @@
       </c>
     </row>
     <row r="37" ht="64.8" customHeight="1">
-      <c r="A37" s="27" t="inlineStr">
+      <c r="A37" s="78" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B37" s="27" t="inlineStr">
+      <c r="B37" s="78" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="C37" s="28" t="inlineStr">
+      <c r="C37" s="73" t="inlineStr">
         <is>
           <t>currency exchange
 exchange money
-foreign currency
-change money
-small change
-coin locker change</t>
-        </is>
-      </c>
-      <c r="D37" s="28" t="inlineStr">
-        <is>
-          <t>To exchange foreign currency, please use the exchange machine near the restrooms. If you need coins for the coin lockers, we can change money for you at the counter.</t>
-        </is>
-      </c>
-      <c r="E37" s="27" t="n"/>
+change foreign currency
+coin exchange locker
+where exchange</t>
+        </is>
+      </c>
+      <c r="D37" s="73" t="inlineStr">
+        <is>
+          <t>For currency exchange, please use the exchange machine located near the restrooms inside Shirakawa-go Bus Terminal. If you need small coins for coin lockers, our staff at the counter can help you exchange them.</t>
+        </is>
+      </c>
+      <c r="E37" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 外貨の両替は、白川郷バスターミナル内のお手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
+        </is>
+      </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
           <t>外貨の両替は、お手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
@@ -7931,32 +7953,35 @@
       </c>
     </row>
     <row r="38" ht="64.8" customHeight="1">
-      <c r="A38" s="27" t="inlineStr">
+      <c r="A38" s="78" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B38" s="27" t="inlineStr">
+      <c r="B38" s="78" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="C38" s="28" t="inlineStr">
-        <is>
-          <t>cambiar dinero
-cambio moneda
-divisa
-moneda extranjera
-monedas taquilla
-monedas locker</t>
-        </is>
-      </c>
-      <c r="D38" s="28" t="inlineStr">
-        <is>
-          <t>Para cambiar moneda extranjera, utilice la máquina de cambio que está cerca de los baños. En el mostrador cambiamos billetes por monedas para usar en las taquillas.</t>
-        </is>
-      </c>
-      <c r="E38" s="27" t="n"/>
+      <c r="C38" s="73" t="inlineStr">
+        <is>
+          <t>cambio de dinero
+cambio de moneda extranjera
+cambio de monedas
+monedas para taquilla
+dónde cambiar dinero</t>
+        </is>
+      </c>
+      <c r="D38" s="73" t="inlineStr">
+        <is>
+          <t>Para cambiar moneda extranjera, utilice la máquina de cambio ubicada cerca de los aseos dentro de la Terminal de Autobuses de Shirakawa-go. Si necesita cambiar monedas para los casilleros, nuestro personal en la ventanilla le puede ayudar.</t>
+        </is>
+      </c>
+      <c r="E38" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 外貨の両替は、白川郷バスターミナル内のお手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
+        </is>
+      </c>
       <c r="F38" s="29" t="inlineStr">
         <is>
           <t>外貨の両替は、お手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
@@ -7964,32 +7989,35 @@
       </c>
     </row>
     <row r="39" ht="64.8" customHeight="1">
-      <c r="A39" s="27" t="inlineStr">
+      <c r="A39" s="78" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B39" s="27" t="inlineStr">
+      <c r="B39" s="78" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="C39" s="28" t="inlineStr">
-        <is>
-          <t>change
-changer argent
-devise
-monnaie
-pièces
-change casier</t>
-        </is>
-      </c>
-      <c r="D39" s="28" t="inlineStr">
-        <is>
-          <t>Pour changer des devises étrangères, veuillez utiliser la machine de change située près des toilettes. Pour obtenir de la monnaie à utiliser dans les consignes automatiques, adressez-vous au guichet.</t>
-        </is>
-      </c>
-      <c r="E39" s="27" t="n"/>
+      <c r="C39" s="73" t="inlineStr">
+        <is>
+          <t>change de devises
+changer de l'argent
+échange monnaie étrangère
+pièces monnaie consigne
+où changer argent</t>
+        </is>
+      </c>
+      <c r="D39" s="73" t="inlineStr">
+        <is>
+          <t>Pour échanger des devises étrangères, veuillez utiliser la machine d'échange située près des toilettes à l'intérieur de la Gare Routière de Shirakawa-go. Si vous avez besoin de petite monnaie pour les casiers, notre personnel au guichet peut vous aider.</t>
+        </is>
+      </c>
+      <c r="E39" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 外貨の両替は、白川郷バスターミナル内のお手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
+        </is>
+      </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
           <t>外貨の両替は、お手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
@@ -7997,32 +8025,35 @@
       </c>
     </row>
     <row r="40" ht="113.4" customHeight="1">
-      <c r="A40" s="27" t="inlineStr">
+      <c r="A40" s="78" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B40" s="27" t="inlineStr">
+      <c r="B40" s="78" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="C40" s="28" t="inlineStr">
+      <c r="C40" s="73" t="inlineStr">
         <is>
           <t>환전
-외화
-잔돈
-동전 교환
-동전 바꾸
-환전 로커</t>
-        </is>
-      </c>
-      <c r="D40" s="28" t="inlineStr">
-        <is>
-          <t>외화 환전은 화장실 근처에 있는 환전기를 이용해 주세요. 코인로커에서 사용하실 동전으로 바꾸는 것은 창구에서 해 드립니다.</t>
-        </is>
-      </c>
-      <c r="E40" s="27" t="n"/>
+외화 환전
+동전 환전
+보관함 동전
+어디서 환전하다</t>
+        </is>
+      </c>
+      <c r="D40" s="73" t="inlineStr">
+        <is>
+          <t>외화 환전은 시라카와고 버스 터미널 내 화장실 근처의 환전 기계를 이용하시기 바랍니다. 동전 보관함용 잔돈 환전이 필요하신 경우, 창구에서 도와드립니다.</t>
+        </is>
+      </c>
+      <c r="E40" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 外貨の両替は、白川郷バスターミナル内のお手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
+        </is>
+      </c>
       <c r="F40" s="29" t="inlineStr">
         <is>
           <t>外貨の両替は、お手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
@@ -8030,31 +8061,35 @@
       </c>
     </row>
     <row r="41" ht="97.2" customHeight="1">
-      <c r="A41" s="30" t="inlineStr">
+      <c r="A41" s="79" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B41" s="30" t="inlineStr">
+      <c r="B41" s="79" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C41" s="31" t="inlineStr">
-        <is>
-          <t>兑换
+      <c r="C41" s="75" t="inlineStr">
+        <is>
+          <t>兑换 外币
 换钱
-外币
-零钱
-硬币 储物柜</t>
-        </is>
-      </c>
-      <c r="D41" s="31" t="inlineStr">
-        <is>
-          <t>外币兑换请使用洗手间附近的外币兑换机。如需兑换投币储物柜使用的零钱，请到窗口办理。</t>
-        </is>
-      </c>
-      <c r="E41" s="30" t="n"/>
+兑换 硬币
+投币柜 硬币
+在哪里 兑换</t>
+        </is>
+      </c>
+      <c r="D41" s="75" t="inlineStr">
+        <is>
+          <t>外币兑换请使用白川乡巴士总站内靠近卫生间的自动兑换机。如需为投币柜兑换零钱，请到窗口咨询工作人员。</t>
+        </is>
+      </c>
+      <c r="E41" s="75" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 外貨の両替は、白川郷バスターミナル内のお手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
+        </is>
+      </c>
       <c r="F41" s="32" t="inlineStr">
         <is>
           <t>外貨の両替は、お手洗い近くのエクスチェンジマシンをご利用ください。コインロッカーでお使いになる小銭への両替は、窓口で承ります。</t>
@@ -16695,12 +16730,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="67" t="inlineStr">
+      <c r="A302" s="71" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="67" t="inlineStr">
+      <c r="B302" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16726,12 +16761,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="67" t="inlineStr">
+      <c r="A303" s="71" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="67" t="inlineStr">
+      <c r="B303" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16757,12 +16792,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="67" t="inlineStr">
+      <c r="A304" s="71" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="67" t="inlineStr">
+      <c r="B304" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16788,12 +16823,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="67" t="inlineStr">
+      <c r="A305" s="71" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="67" t="inlineStr">
+      <c r="B305" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16819,12 +16854,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="67" t="inlineStr">
+      <c r="A306" s="71" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="67" t="inlineStr">
+      <c r="B306" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -16850,12 +16885,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="67" t="inlineStr">
+      <c r="A307" s="71" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="67" t="inlineStr">
+      <c r="B307" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16881,12 +16916,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="67" t="inlineStr">
+      <c r="A308" s="71" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="67" t="inlineStr">
+      <c r="B308" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16912,12 +16947,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="67" t="inlineStr">
+      <c r="A309" s="71" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="67" t="inlineStr">
+      <c r="B309" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16943,12 +16978,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="67" t="inlineStr">
+      <c r="A310" s="71" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="67" t="inlineStr">
+      <c r="B310" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16974,12 +17009,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="67" t="inlineStr">
+      <c r="A311" s="71" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="67" t="inlineStr">
+      <c r="B311" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17005,12 +17040,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="67" t="inlineStr">
+      <c r="A312" s="71" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="67" t="inlineStr">
+      <c r="B312" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17035,12 +17070,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="67" t="inlineStr">
+      <c r="A313" s="71" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="67" t="inlineStr">
+      <c r="B313" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17065,12 +17100,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="67" t="inlineStr">
+      <c r="A314" s="71" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="67" t="inlineStr">
+      <c r="B314" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17095,12 +17130,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="67" t="inlineStr">
+      <c r="A315" s="71" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="67" t="inlineStr">
+      <c r="B315" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17125,12 +17160,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="67" t="inlineStr">
+      <c r="A316" s="71" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="67" t="inlineStr">
+      <c r="B316" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17155,12 +17190,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="67" t="inlineStr">
+      <c r="A317" s="71" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="67" t="inlineStr">
+      <c r="B317" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17186,12 +17221,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="67" t="inlineStr">
+      <c r="A318" s="71" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="67" t="inlineStr">
+      <c r="B318" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17217,12 +17252,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="67" t="inlineStr">
+      <c r="A319" s="71" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="67" t="inlineStr">
+      <c r="B319" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17248,12 +17283,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="67" t="inlineStr">
+      <c r="A320" s="71" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="67" t="inlineStr">
+      <c r="B320" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17279,12 +17314,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="67" t="inlineStr">
+      <c r="A321" s="71" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="67" t="inlineStr">
+      <c r="B321" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17310,12 +17345,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="67" t="inlineStr">
+      <c r="A322" s="71" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="67" t="inlineStr">
+      <c r="B322" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17340,12 +17375,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="67" t="inlineStr">
+      <c r="A323" s="71" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="67" t="inlineStr">
+      <c r="B323" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17370,12 +17405,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="67" t="inlineStr">
+      <c r="A324" s="71" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="67" t="inlineStr">
+      <c r="B324" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17400,12 +17435,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="67" t="inlineStr">
+      <c r="A325" s="71" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="67" t="inlineStr">
+      <c r="B325" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17430,12 +17465,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="67" t="inlineStr">
+      <c r="A326" s="71" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="67" t="inlineStr">
+      <c r="B326" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17460,12 +17495,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="67" t="inlineStr">
+      <c r="A327" s="71" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="67" t="inlineStr">
+      <c r="B327" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17492,12 +17527,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="67" t="inlineStr">
+      <c r="A328" s="71" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="67" t="inlineStr">
+      <c r="B328" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17524,12 +17559,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="67" t="inlineStr">
+      <c r="A329" s="71" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="67" t="inlineStr">
+      <c r="B329" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17556,12 +17591,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="67" t="inlineStr">
+      <c r="A330" s="71" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="67" t="inlineStr">
+      <c r="B330" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17588,12 +17623,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="67" t="inlineStr">
+      <c r="A331" s="71" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="67" t="inlineStr">
+      <c r="B331" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17620,12 +17655,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="67" t="inlineStr">
+      <c r="A332" s="71" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="67" t="inlineStr">
+      <c r="B332" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17652,12 +17687,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="67" t="inlineStr">
+      <c r="A333" s="71" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="67" t="inlineStr">
+      <c r="B333" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17684,12 +17719,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="67" t="inlineStr">
+      <c r="A334" s="71" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="67" t="inlineStr">
+      <c r="B334" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17716,12 +17751,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="67" t="inlineStr">
+      <c r="A335" s="71" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="67" t="inlineStr">
+      <c r="B335" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17748,12 +17783,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="67" t="inlineStr">
+      <c r="A336" s="71" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="67" t="inlineStr">
+      <c r="B336" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17780,12 +17815,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="67" t="inlineStr">
+      <c r="A337" s="71" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="67" t="inlineStr">
+      <c r="B337" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17812,12 +17847,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="67" t="inlineStr">
+      <c r="A338" s="71" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="67" t="inlineStr">
+      <c r="B338" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17844,12 +17879,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="67" t="inlineStr">
+      <c r="A339" s="71" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="67" t="inlineStr">
+      <c r="B339" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17876,12 +17911,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="67" t="inlineStr">
+      <c r="A340" s="71" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="67" t="inlineStr">
+      <c r="B340" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17908,12 +17943,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="67" t="inlineStr">
+      <c r="A341" s="71" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="67" t="inlineStr">
+      <c r="B341" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17940,12 +17975,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="67" t="inlineStr">
+      <c r="A342" s="71" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="67" t="inlineStr">
+      <c r="B342" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17972,12 +18007,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="67" t="inlineStr">
+      <c r="A343" s="71" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="67" t="inlineStr">
+      <c r="B343" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18004,12 +18039,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="67" t="inlineStr">
+      <c r="A344" s="71" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="67" t="inlineStr">
+      <c r="B344" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18036,12 +18071,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="67" t="inlineStr">
+      <c r="A345" s="71" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="67" t="inlineStr">
+      <c r="B345" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18068,12 +18103,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="67" t="inlineStr">
+      <c r="A346" s="71" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="67" t="inlineStr">
+      <c r="B346" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18100,12 +18135,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="67" t="inlineStr">
+      <c r="A347" s="71" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="67" t="inlineStr">
+      <c r="B347" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18132,12 +18167,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="67" t="inlineStr">
+      <c r="A348" s="71" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="67" t="inlineStr">
+      <c r="B348" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18164,12 +18199,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="67" t="inlineStr">
+      <c r="A349" s="71" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="67" t="inlineStr">
+      <c r="B349" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18196,12 +18231,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="67" t="inlineStr">
+      <c r="A350" s="71" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="67" t="inlineStr">
+      <c r="B350" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18228,12 +18263,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="67" t="inlineStr">
+      <c r="A351" s="71" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="67" t="inlineStr">
+      <c r="B351" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18260,12 +18295,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="67" t="inlineStr">
+      <c r="A352" s="71" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="67" t="inlineStr">
+      <c r="B352" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18291,12 +18326,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="67" t="inlineStr">
+      <c r="A353" s="71" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="67" t="inlineStr">
+      <c r="B353" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18322,12 +18357,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="67" t="inlineStr">
+      <c r="A354" s="71" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="67" t="inlineStr">
+      <c r="B354" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18353,12 +18388,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="67" t="inlineStr">
+      <c r="A355" s="71" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="67" t="inlineStr">
+      <c r="B355" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18384,12 +18419,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="67" t="inlineStr">
+      <c r="A356" s="71" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="67" t="inlineStr">
+      <c r="B356" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18415,12 +18450,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="67" t="inlineStr">
+      <c r="A357" s="71" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="67" t="inlineStr">
+      <c r="B357" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18446,12 +18481,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="67" t="inlineStr">
+      <c r="A358" s="71" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="67" t="inlineStr">
+      <c r="B358" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18477,12 +18512,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="67" t="inlineStr">
+      <c r="A359" s="71" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="67" t="inlineStr">
+      <c r="B359" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18508,12 +18543,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="67" t="inlineStr">
+      <c r="A360" s="71" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="67" t="inlineStr">
+      <c r="B360" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18539,12 +18574,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="67" t="inlineStr">
+      <c r="A361" s="71" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="67" t="inlineStr">
+      <c r="B361" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18570,12 +18605,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="67" t="inlineStr">
+      <c r="A362" s="71" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="67" t="inlineStr">
+      <c r="B362" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18602,12 +18637,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="67" t="inlineStr">
+      <c r="A363" s="71" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="67" t="inlineStr">
+      <c r="B363" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18634,12 +18669,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="67" t="inlineStr">
+      <c r="A364" s="71" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="67" t="inlineStr">
+      <c r="B364" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18666,12 +18701,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="67" t="inlineStr">
+      <c r="A365" s="71" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="67" t="inlineStr">
+      <c r="B365" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18698,12 +18733,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="67" t="inlineStr">
+      <c r="A366" s="71" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="67" t="inlineStr">
+      <c r="B366" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18730,12 +18765,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="67" t="inlineStr">
+      <c r="A367" s="71" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="67" t="inlineStr">
+      <c r="B367" s="71" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18762,12 +18797,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="67" t="inlineStr">
+      <c r="A368" s="71" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="67" t="inlineStr">
+      <c r="B368" s="71" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18794,12 +18829,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="67" t="inlineStr">
+      <c r="A369" s="71" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="67" t="inlineStr">
+      <c r="B369" s="71" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18826,12 +18861,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="67" t="inlineStr">
+      <c r="A370" s="71" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="67" t="inlineStr">
+      <c r="B370" s="71" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18858,12 +18893,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="67" t="inlineStr">
+      <c r="A371" s="71" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="67" t="inlineStr">
+      <c r="B371" s="71" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -19999,7 +20034,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="inlineStr">
+      <c r="A2" s="71" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -20009,7 +20044,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="67" t="inlineStr">
+      <c r="C2" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20021,7 +20056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="67" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -20031,7 +20066,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="67" t="inlineStr">
+      <c r="C3" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20043,7 +20078,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="67" t="inlineStr">
+      <c r="A4" s="71" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -20053,7 +20088,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="67" t="inlineStr">
+      <c r="C4" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20065,7 +20100,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="67" t="inlineStr">
+      <c r="A5" s="71" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -20075,7 +20110,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="67" t="inlineStr">
+      <c r="C5" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20087,7 +20122,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="67" t="inlineStr">
+      <c r="A6" s="71" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20097,7 +20132,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="67" t="inlineStr">
+      <c r="C6" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20109,7 +20144,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="67" t="inlineStr">
+      <c r="A7" s="71" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20119,7 +20154,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="67" t="inlineStr">
+      <c r="C7" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20131,7 +20166,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="67" t="inlineStr">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20141,7 +20176,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="67" t="inlineStr">
+      <c r="C8" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20153,7 +20188,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="67" t="inlineStr">
+      <c r="A9" s="71" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20163,7 +20198,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="67" t="inlineStr">
+      <c r="C9" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20175,7 +20210,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="67" t="inlineStr">
+      <c r="A10" s="71" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20185,7 +20220,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="67" t="inlineStr">
+      <c r="C10" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20197,7 +20232,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="67" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20207,7 +20242,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="67" t="inlineStr">
+      <c r="C11" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20219,7 +20254,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="67" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20229,7 +20264,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="67" t="inlineStr">
+      <c r="C12" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20241,7 +20276,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="67" t="inlineStr">
+      <c r="A13" s="71" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20251,7 +20286,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="67" t="inlineStr">
+      <c r="C13" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20393,53 +20428,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="inlineStr">
+      <c r="A2" s="71" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="67" t="inlineStr">
+      <c r="B2" s="71" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="67" t="inlineStr">
+      <c r="C2" s="71" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="67" t="inlineStr">
+      <c r="D2" s="71" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="67" t="inlineStr">
+      <c r="E2" s="71" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="67" t="inlineStr">
+      <c r="F2" s="71" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="67" t="inlineStr">
+      <c r="G2" s="71" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="67" t="inlineStr">
+      <c r="H2" s="71" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="67" t="inlineStr">
+      <c r="I2" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="67" t="n"/>
-      <c r="K2" s="67" t="inlineStr">
+      <c r="J2" s="71" t="n"/>
+      <c r="K2" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20476,45 +20511,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="67" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="67" t="inlineStr">
+      <c r="B3" s="71" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="67" t="inlineStr">
+      <c r="C3" s="71" t="inlineStr">
         <is>
           <t>main_idle_20261013044809.png</t>
         </is>
       </c>
-      <c r="D3" s="67" t="n"/>
-      <c r="E3" s="67" t="n"/>
-      <c r="F3" s="67" t="n">
+      <c r="D3" s="71" t="n"/>
+      <c r="E3" s="71" t="n"/>
+      <c r="F3" s="71" t="n">
         <v>0.179</v>
       </c>
-      <c r="G3" s="67" t="n">
+      <c r="G3" s="71" t="n">
         <v>0.23</v>
       </c>
-      <c r="H3" s="67" t="inlineStr">
+      <c r="H3" s="71" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="67" t="inlineStr">
+      <c r="I3" s="71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="67" t="inlineStr">
+      <c r="J3" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="67" t="inlineStr">
+      <c r="K3" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20551,45 +20586,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="67" t="inlineStr">
+      <c r="A4" s="71" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="67" t="inlineStr">
+      <c r="B4" s="71" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="67" t="inlineStr">
+      <c r="C4" s="71" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="67" t="n"/>
-      <c r="E4" s="67" t="n"/>
-      <c r="F4" s="67" t="inlineStr">
+      <c r="D4" s="71" t="n"/>
+      <c r="E4" s="71" t="n"/>
+      <c r="F4" s="71" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="67" t="inlineStr">
+      <c r="G4" s="71" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="67" t="inlineStr">
+      <c r="H4" s="71" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="67" t="inlineStr">
+      <c r="I4" s="71" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="67" t="n"/>
-      <c r="K4" s="67" t="inlineStr">
+      <c r="J4" s="71" t="n"/>
+      <c r="K4" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20626,45 +20661,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="67" t="inlineStr">
+      <c r="A5" s="71" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="67" t="inlineStr">
+      <c r="B5" s="71" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="67" t="inlineStr">
+      <c r="C5" s="71" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="67" t="n"/>
-      <c r="E5" s="67" t="n"/>
-      <c r="F5" s="67" t="inlineStr">
+      <c r="D5" s="71" t="n"/>
+      <c r="E5" s="71" t="n"/>
+      <c r="F5" s="71" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="67" t="inlineStr">
+      <c r="G5" s="71" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="67" t="inlineStr">
+      <c r="H5" s="71" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="67" t="inlineStr">
+      <c r="I5" s="71" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="67" t="n"/>
-      <c r="K5" s="67" t="inlineStr">
+      <c r="J5" s="71" t="n"/>
+      <c r="K5" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20701,45 +20736,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="67" t="inlineStr">
+      <c r="A6" s="71" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="67" t="inlineStr">
+      <c r="B6" s="71" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="67" t="inlineStr">
+      <c r="C6" s="71" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="67" t="n"/>
-      <c r="E6" s="67" t="n"/>
-      <c r="F6" s="67" t="inlineStr">
+      <c r="D6" s="71" t="n"/>
+      <c r="E6" s="71" t="n"/>
+      <c r="F6" s="71" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="67" t="inlineStr">
+      <c r="G6" s="71" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="67" t="inlineStr">
+      <c r="H6" s="71" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="67" t="inlineStr">
+      <c r="I6" s="71" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="67" t="n"/>
-      <c r="K6" s="67" t="inlineStr">
+      <c r="J6" s="71" t="n"/>
+      <c r="K6" s="71" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20861,12 +20896,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="inlineStr">
+      <c r="A2" s="71" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B2" s="67" t="inlineStr">
+      <c r="B2" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -20905,12 +20940,12 @@
       <c r="J2" s="46" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="67" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B3" s="67" t="inlineStr">
+      <c r="B3" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -20949,12 +20984,12 @@
       <c r="J3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="67" t="inlineStr">
+      <c r="A4" s="71" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B4" s="67" t="inlineStr">
+      <c r="B4" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -20993,12 +21028,12 @@
       <c r="J4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="67" t="inlineStr">
+      <c r="A5" s="71" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B5" s="67" t="inlineStr">
+      <c r="B5" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21037,12 +21072,12 @@
       <c r="J5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="67" t="inlineStr">
+      <c r="A6" s="71" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B6" s="67" t="inlineStr">
+      <c r="B6" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21081,12 +21116,12 @@
       <c r="J6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="67" t="inlineStr">
+      <c r="A7" s="71" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B7" s="67" t="inlineStr">
+      <c r="B7" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21125,12 +21160,12 @@
       <c r="J7" s="46" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="67" t="inlineStr">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B8" s="67" t="inlineStr">
+      <c r="B8" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21169,12 +21204,12 @@
       <c r="J8" s="46" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="67" t="inlineStr">
+      <c r="A9" s="71" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B9" s="67" t="inlineStr">
+      <c r="B9" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21213,12 +21248,12 @@
       <c r="J9" s="46" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="67" t="inlineStr">
+      <c r="A10" s="71" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B10" s="67" t="inlineStr">
+      <c r="B10" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21257,12 +21292,12 @@
       <c r="J10" s="46" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="67" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B11" s="67" t="inlineStr">
+      <c r="B11" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21301,12 +21336,12 @@
       <c r="J11" s="46" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="67" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B12" s="67" t="inlineStr">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21345,12 +21380,12 @@
       <c r="J12" s="46" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="67" t="inlineStr">
+      <c r="A13" s="71" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B13" s="67" t="inlineStr">
+      <c r="B13" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21408,12 +21443,12 @@
       <c r="J13" s="46" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="71" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B14" s="67" t="inlineStr">
+      <c r="B14" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21471,12 +21506,12 @@
       <c r="J14" s="46" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="67" t="inlineStr">
+      <c r="A15" s="71" t="inlineStr">
         <is>
           <t>趣味</t>
         </is>
       </c>
-      <c r="B15" s="67" t="inlineStr">
+      <c r="B15" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21537,12 +21572,12 @@
       <c r="J15" s="46" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="67" t="inlineStr">
+      <c r="A16" s="71" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B16" s="67" t="inlineStr">
+      <c r="B16" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21602,12 +21637,12 @@
       <c r="J16" s="46" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="67" t="inlineStr">
+      <c r="A17" s="71" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B17" s="67" t="inlineStr">
+      <c r="B17" s="71" t="inlineStr">
         <is>
           <t>共通</t>
         </is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -486,6 +486,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1188,7 +1197,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1198,31 +1207,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="71" t="n">
+      <c r="C2" s="77" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="71" t="n">
+      <c r="D2" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="71" t="n">
+      <c r="E2" s="77" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="71" t="n">
+      <c r="F2" s="77" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="71" t="n">
+      <c r="G2" s="77" t="n">
         <v>0.957</v>
       </c>
-      <c r="H2" s="71" t="n">
+      <c r="H2" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="71" t="n">
+      <c r="I2" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="71" t="n">
+      <c r="J2" s="77" t="n">
         <v>0.864</v>
       </c>
-      <c r="K2" s="71" t="n">
+      <c r="K2" s="77" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1232,7 +1241,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="71" t="inlineStr">
+      <c r="A3" s="77" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1242,31 +1251,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="71" t="n">
+      <c r="C3" s="77" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="71" t="n">
+      <c r="D3" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="71" t="n">
+      <c r="E3" s="77" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="71" t="n">
+      <c r="F3" s="77" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="71" t="n">
+      <c r="G3" s="77" t="n">
         <v>0.929</v>
       </c>
-      <c r="H3" s="71" t="n">
+      <c r="H3" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="71" t="n">
+      <c r="I3" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="71" t="n">
+      <c r="J3" s="77" t="n">
         <v>0.753</v>
       </c>
-      <c r="K3" s="71" t="n">
+      <c r="K3" s="77" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1276,7 +1285,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="71" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1286,31 +1295,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="71" t="n">
+      <c r="C4" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="71" t="n">
+      <c r="D4" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="71" t="n">
+      <c r="E4" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="71" t="n">
+      <c r="F4" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="71" t="n">
+      <c r="G4" s="77" t="n">
         <v>0.92</v>
       </c>
-      <c r="H4" s="71" t="n">
+      <c r="H4" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="71" t="n">
+      <c r="I4" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="71" t="n">
+      <c r="J4" s="77" t="n">
         <v>0.884</v>
       </c>
-      <c r="K4" s="71" t="n">
+      <c r="K4" s="77" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1382,7 +1391,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1392,10 +1401,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="71" t="n">
+      <c r="C2" s="77" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="71" t="n">
+      <c r="D2" s="77" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1405,7 +1414,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="71" t="inlineStr">
+      <c r="A3" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1415,16 +1424,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="71" t="n">
+      <c r="C3" s="77" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="71" t="n">
+      <c r="D3" s="77" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="71" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1434,16 +1443,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="71" t="n">
+      <c r="C4" s="77" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="71" t="n">
+      <c r="D4" s="77" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="71" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1453,16 +1462,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="71" t="n">
+      <c r="C5" s="77" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="71" t="n">
+      <c r="D5" s="77" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="71" t="inlineStr">
+      <c r="A6" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1472,16 +1481,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="71" t="n">
+      <c r="C6" s="77" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="71" t="n">
+      <c r="D6" s="77" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="71" t="inlineStr">
+      <c r="A7" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1491,10 +1500,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="71" t="n">
+      <c r="C7" s="77" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="71" t="n">
+      <c r="D7" s="77" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1554,17 +1563,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="71" t="inlineStr">
+      <c r="B2" s="77" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="71" t="inlineStr">
+      <c r="C2" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1576,17 +1585,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="71" t="inlineStr">
+      <c r="A3" s="77" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="71" t="inlineStr">
+      <c r="B3" s="77" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="71" t="inlineStr">
+      <c r="C3" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1594,17 +1603,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="71" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="71" t="inlineStr">
+      <c r="B4" s="77" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="71" t="inlineStr">
+      <c r="C4" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1616,17 +1625,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="71" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="71" t="inlineStr">
+      <c r="B5" s="77" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="71" t="inlineStr">
+      <c r="C5" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1638,17 +1647,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="71" t="inlineStr">
+      <c r="A6" s="77" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="71" t="inlineStr">
+      <c r="B6" s="77" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="71" t="inlineStr">
+      <c r="C6" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1656,17 +1665,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="71" t="inlineStr">
+      <c r="A7" s="77" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="71" t="inlineStr">
+      <c r="B7" s="77" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="71" t="inlineStr">
+      <c r="C7" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1674,17 +1683,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="71" t="inlineStr">
+      <c r="A8" s="77" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="71" t="inlineStr">
+      <c r="B8" s="77" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="71" t="inlineStr">
+      <c r="C8" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1696,17 +1705,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="71" t="inlineStr">
+      <c r="A9" s="77" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="71" t="inlineStr">
+      <c r="B9" s="77" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="71" t="inlineStr">
+      <c r="C9" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1718,17 +1727,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="71" t="inlineStr">
+      <c r="A10" s="77" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="71" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="71" t="inlineStr">
+      <c r="C10" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1740,17 +1749,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="71" t="inlineStr">
+      <c r="A11" s="77" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="71" t="inlineStr">
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="71" t="inlineStr">
+      <c r="C11" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1758,17 +1767,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="71" t="inlineStr">
+      <c r="A12" s="77" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="71" t="inlineStr">
+      <c r="B12" s="77" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="71" t="inlineStr">
+      <c r="C12" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1776,17 +1785,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="71" t="inlineStr">
+      <c r="A13" s="77" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="71" t="inlineStr">
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="71" t="inlineStr">
+      <c r="C13" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1798,17 +1807,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="71" t="inlineStr">
+      <c r="A14" s="77" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="71" t="inlineStr">
+      <c r="B14" s="77" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="71" t="inlineStr">
+      <c r="C14" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1820,17 +1829,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="71" t="inlineStr">
+      <c r="A15" s="77" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="71" t="inlineStr">
+      <c r="B15" s="77" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="71" t="inlineStr">
+      <c r="C15" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1842,17 +1851,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="71" t="inlineStr">
+      <c r="A16" s="77" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="71" t="inlineStr">
+      <c r="B16" s="77" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="71" t="inlineStr">
+      <c r="C16" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1864,17 +1873,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="71" t="inlineStr">
+      <c r="A17" s="77" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="71" t="inlineStr">
+      <c r="B17" s="77" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="71" t="inlineStr">
+      <c r="C17" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1886,17 +1895,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="71" t="inlineStr">
+      <c r="A18" s="77" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="71" t="inlineStr">
+      <c r="B18" s="77" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="71" t="inlineStr">
+      <c r="C18" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1908,17 +1917,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="71" t="inlineStr">
+      <c r="A19" s="77" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="71" t="inlineStr">
+      <c r="B19" s="77" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="71" t="inlineStr">
+      <c r="C19" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1926,17 +1935,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="71" t="inlineStr">
+      <c r="A20" s="77" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="71" t="inlineStr">
+      <c r="B20" s="77" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="71" t="inlineStr">
+      <c r="C20" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1944,17 +1953,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="71" t="inlineStr">
+      <c r="A21" s="77" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="71" t="inlineStr">
+      <c r="B21" s="77" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="71" t="inlineStr">
+      <c r="C21" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1966,17 +1975,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="71" t="inlineStr">
+      <c r="A22" s="77" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="71" t="inlineStr">
+      <c r="B22" s="77" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="71" t="inlineStr">
+      <c r="C22" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1988,17 +1997,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="71" t="inlineStr">
+      <c r="A23" s="77" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="71" t="inlineStr">
+      <c r="B23" s="77" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="71" t="inlineStr">
+      <c r="C23" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2010,17 +2019,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="71" t="inlineStr">
+      <c r="A24" s="77" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="71" t="inlineStr">
+      <c r="B24" s="77" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="71" t="inlineStr">
+      <c r="C24" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2032,17 +2041,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="71" t="inlineStr">
+      <c r="A25" s="77" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="71" t="inlineStr">
+      <c r="B25" s="77" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="71" t="inlineStr">
+      <c r="C25" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2050,17 +2059,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="71" t="inlineStr">
+      <c r="A26" s="77" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="71" t="inlineStr">
+      <c r="B26" s="77" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="71" t="inlineStr">
+      <c r="C26" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2068,17 +2077,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="71" t="inlineStr">
+      <c r="A27" s="77" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="71" t="inlineStr">
+      <c r="B27" s="77" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="71" t="inlineStr">
+      <c r="C27" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2090,17 +2099,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="71" t="inlineStr">
+      <c r="A28" s="77" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="71" t="inlineStr">
+      <c r="B28" s="77" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="71" t="inlineStr">
+      <c r="C28" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2112,17 +2121,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="71" t="inlineStr">
+      <c r="A29" s="77" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="71" t="inlineStr">
+      <c r="B29" s="77" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="71" t="inlineStr">
+      <c r="C29" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2134,17 +2143,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="71" t="inlineStr">
+      <c r="A30" s="77" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="71" t="inlineStr">
+      <c r="B30" s="77" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="71" t="inlineStr">
+      <c r="C30" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2152,17 +2161,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="71" t="inlineStr">
+      <c r="A31" s="77" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="71" t="inlineStr">
+      <c r="B31" s="77" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="71" t="inlineStr">
+      <c r="C31" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2174,17 +2183,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="71" t="inlineStr">
+      <c r="A32" s="77" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="71" t="inlineStr">
+      <c r="B32" s="77" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="71" t="inlineStr">
+      <c r="C32" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2192,17 +2201,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="71" t="inlineStr">
+      <c r="A33" s="77" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="71" t="inlineStr">
+      <c r="B33" s="77" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="71" t="inlineStr">
+      <c r="C33" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2210,17 +2219,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="71" t="inlineStr">
+      <c r="A34" s="77" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="71" t="inlineStr">
+      <c r="B34" s="77" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="71" t="inlineStr">
+      <c r="C34" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2228,17 +2237,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="71" t="inlineStr">
+      <c r="A35" s="77" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="71" t="inlineStr">
+      <c r="B35" s="77" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="71" t="inlineStr">
+      <c r="C35" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2246,17 +2255,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="71" t="inlineStr">
+      <c r="A36" s="77" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="71" t="inlineStr">
+      <c r="B36" s="77" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="71" t="inlineStr">
+      <c r="C36" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2264,17 +2273,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="71" t="inlineStr">
+      <c r="A37" s="77" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="71" t="inlineStr">
+      <c r="B37" s="77" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="71" t="inlineStr">
+      <c r="C37" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2282,17 +2291,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="71" t="inlineStr">
+      <c r="A38" s="77" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="71" t="inlineStr">
+      <c r="B38" s="77" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="71" t="inlineStr">
+      <c r="C38" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2300,17 +2309,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="71" t="inlineStr">
+      <c r="A39" s="77" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="71" t="inlineStr">
+      <c r="B39" s="77" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="71" t="inlineStr">
+      <c r="C39" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2318,17 +2327,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="71" t="inlineStr">
+      <c r="A40" s="77" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="71" t="inlineStr">
+      <c r="B40" s="77" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="71" t="inlineStr">
+      <c r="C40" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2340,17 +2349,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="71" t="inlineStr">
+      <c r="A41" s="77" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="71" t="inlineStr">
+      <c r="B41" s="77" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="71" t="inlineStr">
+      <c r="C41" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2358,17 +2367,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="71" t="inlineStr">
+      <c r="A42" s="77" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="71" t="inlineStr">
+      <c r="B42" s="77" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="71" t="inlineStr">
+      <c r="C42" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2380,17 +2389,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="71" t="inlineStr">
+      <c r="A43" s="77" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="71" t="inlineStr">
+      <c r="B43" s="77" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="71" t="inlineStr">
+      <c r="C43" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2398,17 +2407,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="71" t="inlineStr">
+      <c r="A44" s="77" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="71" t="inlineStr">
+      <c r="B44" s="77" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="71" t="inlineStr">
+      <c r="C44" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2420,17 +2429,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="71" t="inlineStr">
+      <c r="A45" s="77" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="71" t="inlineStr">
+      <c r="B45" s="77" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="71" t="inlineStr">
+      <c r="C45" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2779,17 +2788,17 @@
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="70" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B6" s="70" t="inlineStr">
+      <c r="B6" s="76" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C6" s="70" t="inlineStr">
+      <c r="C6" s="76" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2814,49 +2823,49 @@
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
         </is>
       </c>
-      <c r="G6" s="70" t="n"/>
-      <c r="H6" s="70" t="n"/>
-      <c r="I6" s="70" t="inlineStr">
+      <c r="G6" s="76" t="n"/>
+      <c r="H6" s="76" t="n"/>
+      <c r="I6" s="76" t="inlineStr">
         <is>
           <t>atm_bt.mp3</t>
         </is>
       </c>
-      <c r="J6" s="70" t="inlineStr">
+      <c r="J6" s="76" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K6" s="70" t="n"/>
-      <c r="L6" s="70" t="n"/>
-      <c r="M6" s="70" t="inlineStr">
+      <c r="K6" s="76" t="n"/>
+      <c r="L6" s="76" t="n"/>
+      <c r="M6" s="76" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N6" s="71" t="inlineStr">
+      <c r="N6" s="77" t="inlineStr">
         <is>
           <t>ATMはどこ</t>
         </is>
       </c>
-      <c r="O6" s="71" t="n"/>
-      <c r="P6" s="71" t="inlineStr">
+      <c r="O6" s="77" t="n"/>
+      <c r="P6" s="77" t="inlineStr">
         <is>
           <t>2026-10-13 17:14</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="70" t="inlineStr">
+      <c r="A7" s="76" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B7" s="70" t="inlineStr">
+      <c r="B7" s="76" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C7" s="70" t="inlineStr">
+      <c r="C7" s="76" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2881,28 +2890,28 @@
           <t>海外のカードは鳩谷郵便局のATM、日本のカードは和田家前のJAのATMをご利用ください。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G7" s="70" t="n"/>
-      <c r="H7" s="70" t="n"/>
-      <c r="I7" s="70" t="inlineStr">
+      <c r="G7" s="76" t="n"/>
+      <c r="H7" s="76" t="n"/>
+      <c r="I7" s="76" t="inlineStr">
         <is>
           <t>atm_deai.mp3</t>
         </is>
       </c>
-      <c r="J7" s="70" t="inlineStr">
+      <c r="J7" s="76" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K7" s="70" t="n"/>
-      <c r="L7" s="70" t="n"/>
-      <c r="M7" s="70" t="inlineStr">
+      <c r="K7" s="76" t="n"/>
+      <c r="L7" s="76" t="n"/>
+      <c r="M7" s="76" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N7" s="71" t="n"/>
-      <c r="O7" s="71" t="n"/>
-      <c r="P7" s="71" t="inlineStr">
+      <c r="N7" s="77" t="n"/>
+      <c r="O7" s="77" t="n"/>
+      <c r="P7" s="77" t="inlineStr">
         <is>
           <t>2026-10-13 17:15</t>
         </is>
@@ -3016,22 +3025,22 @@
       </c>
     </row>
     <row r="10" ht="58.05" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="80" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="80" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="80" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="44" t="inlineStr">
         <is>
           <t>両替
 外貨
@@ -3040,29 +3049,36 @@
 両替 ロッカー</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>紙幣のみ対応ですが、外貨両替は観光協会バスターミナルにある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="E10" s="44" t="inlineStr">
+        <is>
+          <t>紙幣のみ対応ですが、外貨両替は白川郷バスターミナル内にある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
+        </is>
+      </c>
+      <c r="F10" s="44" t="n"/>
+      <c r="G10" s="80" t="n"/>
+      <c r="H10" s="80" t="n"/>
+      <c r="I10" s="80" t="inlineStr">
         <is>
           <t>currency_exchange_deai.mp3</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="80" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="11" t="n"/>
-      <c r="M10" s="14" t="inlineStr">
+      <c r="K10" s="80" t="n"/>
+      <c r="L10" s="80" t="n"/>
+      <c r="M10" s="80" t="inlineStr">
         <is>
           <t>currency_exchange</t>
+        </is>
+      </c>
+      <c r="N10" s="81" t="n"/>
+      <c r="O10" s="81" t="n"/>
+      <c r="P10" s="81" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:19</t>
         </is>
       </c>
     </row>
@@ -4872,17 +4888,17 @@
       </c>
     </row>
     <row r="43" ht="249.6" customHeight="1">
-      <c r="A43" s="70" t="inlineStr">
+      <c r="A43" s="76" t="inlineStr">
         <is>
           <t>guesthouse_access_deai</t>
         </is>
       </c>
-      <c r="B43" s="70" t="inlineStr">
+      <c r="B43" s="76" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C43" s="70" t="inlineStr">
+      <c r="C43" s="76" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -4916,30 +4932,30 @@
           <t>その建物は鳩谷八幡神社方面にあります。国道は交通量が多いため、川沿いの道をおすすめしております。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G43" s="70" t="inlineStr">
+      <c r="G43" s="76" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H43" s="70" t="n"/>
-      <c r="I43" s="70" t="inlineStr">
+      <c r="H43" s="76" t="n"/>
+      <c r="I43" s="76" t="inlineStr">
         <is>
           <t>guesthouse_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J43" s="70" t="inlineStr">
+      <c r="J43" s="76" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K43" s="70" t="n"/>
-      <c r="L43" s="70" t="n"/>
-      <c r="M43" s="70" t="inlineStr">
+      <c r="K43" s="76" t="n"/>
+      <c r="L43" s="76" t="n"/>
+      <c r="M43" s="76" t="inlineStr">
         <is>
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="71" t="n"/>
+      <c r="N43" s="77" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -6128,17 +6144,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="71" t="inlineStr">
+      <c r="A66" s="77" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="71" t="inlineStr">
+      <c r="B66" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="71" t="inlineStr">
+      <c r="C66" s="77" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -6168,26 +6184,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="71" t="inlineStr">
+      <c r="G66" s="77" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="71" t="n"/>
-      <c r="I66" s="71" t="inlineStr">
+      <c r="H66" s="77" t="n"/>
+      <c r="I66" s="77" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="71" t="inlineStr">
+      <c r="J66" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="71" t="n"/>
-      <c r="L66" s="71" t="n"/>
-      <c r="M66" s="71" t="n"/>
-      <c r="N66" s="71" t="n"/>
+      <c r="K66" s="77" t="n"/>
+      <c r="L66" s="77" t="n"/>
+      <c r="M66" s="77" t="n"/>
+      <c r="N66" s="77" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -7396,12 +7412,12 @@
       </c>
     </row>
     <row r="22" ht="64.8" customHeight="1">
-      <c r="A22" s="71" t="inlineStr">
+      <c r="A22" s="77" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B22" s="71" t="inlineStr">
+      <c r="B22" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7432,12 +7448,12 @@
       </c>
     </row>
     <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="71" t="inlineStr">
+      <c r="A23" s="77" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B23" s="71" t="inlineStr">
+      <c r="B23" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7468,12 +7484,12 @@
       </c>
     </row>
     <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="71" t="inlineStr">
+      <c r="A24" s="77" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B24" s="71" t="inlineStr">
+      <c r="B24" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7504,12 +7520,12 @@
       </c>
     </row>
     <row r="25" ht="81" customHeight="1">
-      <c r="A25" s="71" t="inlineStr">
+      <c r="A25" s="77" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B25" s="71" t="inlineStr">
+      <c r="B25" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7576,12 +7592,12 @@
       </c>
     </row>
     <row r="27" ht="64.8" customHeight="1">
-      <c r="A27" s="72" t="inlineStr">
+      <c r="A27" s="78" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B27" s="72" t="inlineStr">
+      <c r="B27" s="78" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7612,12 +7628,12 @@
       </c>
     </row>
     <row r="28" ht="64.8" customHeight="1">
-      <c r="A28" s="72" t="inlineStr">
+      <c r="A28" s="78" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B28" s="72" t="inlineStr">
+      <c r="B28" s="78" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7648,12 +7664,12 @@
       </c>
     </row>
     <row r="29" ht="64.8" customHeight="1">
-      <c r="A29" s="72" t="inlineStr">
+      <c r="A29" s="78" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B29" s="72" t="inlineStr">
+      <c r="B29" s="78" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7684,12 +7700,12 @@
       </c>
     </row>
     <row r="30" ht="81" customHeight="1">
-      <c r="A30" s="72" t="inlineStr">
+      <c r="A30" s="78" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B30" s="72" t="inlineStr">
+      <c r="B30" s="78" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7720,12 +7736,12 @@
       </c>
     </row>
     <row r="31" ht="64.8" customHeight="1">
-      <c r="A31" s="74" t="inlineStr">
+      <c r="A31" s="79" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B31" s="74" t="inlineStr">
+      <c r="B31" s="79" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8097,32 +8113,35 @@
       </c>
     </row>
     <row r="42" ht="64.8" customHeight="1">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="81" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B42" s="21" t="inlineStr">
+      <c r="B42" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="C42" s="22" t="inlineStr">
+      <c r="C42" s="46" t="inlineStr">
         <is>
           <t>currency exchange
-exchange money
-foreign currency
-change money
-small change
-coin locker change</t>
-        </is>
-      </c>
-      <c r="D42" s="22" t="inlineStr">
-        <is>
-          <t>To exchange foreign currency, please use the exchange machine at the Tourist Association in Shirakawa-go Bus Terminal. It accepts banknotes only. If you need coins for the coin lockers, we can change Japanese yen banknotes into Japanese yen coins at the counter.</t>
-        </is>
-      </c>
-      <c r="E42" s="21" t="n"/>
+exchange foreign money
+change coins
+coin locker yen
+where exchange</t>
+        </is>
+      </c>
+      <c r="D42" s="46" t="inlineStr">
+        <is>
+          <t>We can exchange banknotes only. For foreign currency exchange, please use the exchange machine located inside Shirakawa-go Bus Terminal. For exchanging Japanese banknotes to Japanese coins for use with coin lockers, we can assist you at our counter.</t>
+        </is>
+      </c>
+      <c r="E42" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 紙幣のみ対応ですが、外貨両替は白川郷バスターミナル内にある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
+        </is>
+      </c>
       <c r="F42" s="23" t="inlineStr">
         <is>
           <t>紙幣のみ対応ですが、外貨両替は観光協会バスターミナルにある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
@@ -8130,32 +8149,35 @@
       </c>
     </row>
     <row r="43" ht="64.8" customHeight="1">
-      <c r="A43" s="21" t="inlineStr">
+      <c r="A43" s="81" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B43" s="21" t="inlineStr">
+      <c r="B43" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="C43" s="22" t="inlineStr">
-        <is>
-          <t>cambiar dinero
-cambio moneda
-divisa
-moneda extranjera
-monedas taquilla
-monedas locker</t>
-        </is>
-      </c>
-      <c r="D43" s="22" t="inlineStr">
-        <is>
-          <t>Para cambiar moneda extranjera, utilice la máquina de cambio de la Asociación de Turismo en la Terminal de Autobuses; solo admite billetes. En el mostrador cambiamos billetes de yenes japoneses por monedas de yenes para usar en las taquillas.</t>
-        </is>
-      </c>
-      <c r="E43" s="21" t="n"/>
+      <c r="C43" s="46" t="inlineStr">
+        <is>
+          <t>cambio de moneda extranjera
+cambiar dinero
+cambio de monedas
+cambio de billetes
+taquilla monedas</t>
+        </is>
+      </c>
+      <c r="D43" s="46" t="inlineStr">
+        <is>
+          <t>Solo podemos cambiar billetes. Para cambiar moneda extranjera, por favor use la máquina de cambio ubicada dentro de la Terminal de Autobuses Shirakawa-go. Si necesita cambiar billetes de yen japonés por monedas de yen japonés para usar en las taquillas de almacenamiento, nuestro personal en la ventanilla puede ayudarle.</t>
+        </is>
+      </c>
+      <c r="E43" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 紙幣のみ対応ですが、外貨両替は白川郷バスターミナル内にある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
+        </is>
+      </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
           <t>紙幣のみ対応ですが、外貨両替は観光協会バスターミナルにある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
@@ -8163,32 +8185,35 @@
       </c>
     </row>
     <row r="44" ht="81" customHeight="1">
-      <c r="A44" s="21" t="inlineStr">
+      <c r="A44" s="81" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B44" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="C44" s="22" t="inlineStr">
-        <is>
-          <t>change
+      <c r="C44" s="46" t="inlineStr">
+        <is>
+          <t>change devises étrangères
 changer argent
-devise
-monnaie
-pièces
-change casier</t>
-        </is>
-      </c>
-      <c r="D44" s="22" t="inlineStr">
-        <is>
-          <t>Pour changer des devises étrangères, veuillez utiliser la machine de change du terminal de bus de Shirakawa-go, au bureau de l'Association touristique ; elle n'accepte que les billets. Pour changer des billets en yens contre des pièces en yens à utiliser dans les consignes automatiques, adressez-vous au guichet.</t>
-        </is>
-      </c>
-      <c r="E44" s="21" t="n"/>
+change pièces
+change billets
+casier pièces</t>
+        </is>
+      </c>
+      <c r="D44" s="46" t="inlineStr">
+        <is>
+          <t>Nous ne pouvons changer que les billets. Pour l'échange de devises étrangères, veuillez utiliser le distributeur de change situé à l'intérieur de la gare routière de Shirakawa-go. Pour échanger des billets en yen japonais contre des pièces en yen japonais pour utiliser les casiers de rangement, notre personnel au guichet peut vous aider.</t>
+        </is>
+      </c>
+      <c r="E44" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 紙幣のみ対応ですが、外貨両替は白川郷バスターミナル内にある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
+        </is>
+      </c>
       <c r="F44" s="23" t="inlineStr">
         <is>
           <t>紙幣のみ対応ですが、外貨両替は観光協会バスターミナルにある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
@@ -8196,32 +8221,35 @@
       </c>
     </row>
     <row r="45" ht="64.8" customHeight="1">
-      <c r="A45" s="21" t="inlineStr">
+      <c r="A45" s="81" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B45" s="21" t="inlineStr">
+      <c r="B45" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="C45" s="22" t="inlineStr">
-        <is>
-          <t>환전
-외화
-잔돈
-동전 교환
-동전 바꾸
-환전 로커</t>
-        </is>
-      </c>
-      <c r="D45" s="22" t="inlineStr">
-        <is>
-          <t>외화 환전은 지폐만 가능하며, 시라카와고 버스터미널의 관광협회에 있는 환전기를 이용해 주세요. 코인로커에서 사용하실 일본 엔 지폐를 일본 엔 동전으로 바꾸는 것은 창구에서 해 드립니다.</t>
-        </is>
-      </c>
-      <c r="E45" s="21" t="n"/>
+      <c r="C45" s="46" t="inlineStr">
+        <is>
+          <t>환전 외화
+돈 바꾸기
+동전 환전
+지폐 환전
+보관함 동전</t>
+        </is>
+      </c>
+      <c r="D45" s="46" t="inlineStr">
+        <is>
+          <t>지폐만 환전 가능합니다. 외화 환전이 필요하신 경우, 시라카와고 버스 터미널 내에 있는 환전기를 이용해주세요. 짐보관함 사용을 위해 일본 엔 지폐를 일본 엔 동전으로 바꾸고 싶으시다면, 창구에서 도와드립니다.</t>
+        </is>
+      </c>
+      <c r="E45" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 紙幣のみ対応ですが、外貨両替は白川郷バスターミナル内にある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
+        </is>
+      </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
           <t>紙幣のみ対応ですが、外貨両替は観光協会バスターミナルにある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
@@ -8229,31 +8257,35 @@
       </c>
     </row>
     <row r="46" ht="64.8" customHeight="1">
-      <c r="A46" s="24" t="inlineStr">
+      <c r="A46" s="82" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B46" s="24" t="inlineStr">
+      <c r="B46" s="82" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C46" s="25" t="inlineStr">
-        <is>
-          <t>兑换
+      <c r="C46" s="69" t="inlineStr">
+        <is>
+          <t>兑换外币
 换钱
-外币
-零钱
-硬币 储物柜</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="inlineStr">
-        <is>
-          <t>外币兑换请使用观光协会白川乡巴士总站内的兑换机，仅限纸币。如需将日元纸币兑换成储物柜使用的日元硬币，请到窗口办理。</t>
-        </is>
-      </c>
-      <c r="E46" s="24" t="n"/>
+硬币兑换
+纸币兑换
+投币柜兑换</t>
+        </is>
+      </c>
+      <c r="D46" s="69" t="inlineStr">
+        <is>
+          <t>我们只支持纸币兑换。如需兑换外币，请使用位于白川乡巴士站内的自动兑换机。如需将日元纸币兑换为日元硬币以供投币柜使用，我们可以在窗口为您提供帮助。</t>
+        </is>
+      </c>
+      <c r="E46" s="69" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 紙幣のみ対応ですが、外貨両替は白川郷バスターミナル内にある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
+        </is>
+      </c>
       <c r="F46" s="26" t="inlineStr">
         <is>
           <t>紙幣のみ対応ですが、外貨両替は観光協会バスターミナルにある両替機をご利用ください。（コインロッカーでお使いになる日本円紙幣から日本円通貨への両替は、窓口で承ります）</t>
@@ -16730,12 +16762,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="71" t="inlineStr">
+      <c r="A302" s="77" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="71" t="inlineStr">
+      <c r="B302" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16761,12 +16793,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="71" t="inlineStr">
+      <c r="A303" s="77" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="71" t="inlineStr">
+      <c r="B303" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16792,12 +16824,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="71" t="inlineStr">
+      <c r="A304" s="77" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="71" t="inlineStr">
+      <c r="B304" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16823,12 +16855,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="71" t="inlineStr">
+      <c r="A305" s="77" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="71" t="inlineStr">
+      <c r="B305" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16854,12 +16886,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="71" t="inlineStr">
+      <c r="A306" s="77" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="71" t="inlineStr">
+      <c r="B306" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -16885,12 +16917,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="71" t="inlineStr">
+      <c r="A307" s="77" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="71" t="inlineStr">
+      <c r="B307" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16916,12 +16948,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="71" t="inlineStr">
+      <c r="A308" s="77" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="71" t="inlineStr">
+      <c r="B308" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16947,12 +16979,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="71" t="inlineStr">
+      <c r="A309" s="77" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="71" t="inlineStr">
+      <c r="B309" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16978,12 +17010,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="71" t="inlineStr">
+      <c r="A310" s="77" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="71" t="inlineStr">
+      <c r="B310" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17009,12 +17041,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="71" t="inlineStr">
+      <c r="A311" s="77" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="71" t="inlineStr">
+      <c r="B311" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17040,12 +17072,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="71" t="inlineStr">
+      <c r="A312" s="77" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="71" t="inlineStr">
+      <c r="B312" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17070,12 +17102,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="71" t="inlineStr">
+      <c r="A313" s="77" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="71" t="inlineStr">
+      <c r="B313" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17100,12 +17132,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="71" t="inlineStr">
+      <c r="A314" s="77" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="71" t="inlineStr">
+      <c r="B314" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17130,12 +17162,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="71" t="inlineStr">
+      <c r="A315" s="77" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="71" t="inlineStr">
+      <c r="B315" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17160,12 +17192,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="71" t="inlineStr">
+      <c r="A316" s="77" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="71" t="inlineStr">
+      <c r="B316" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17190,12 +17222,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="71" t="inlineStr">
+      <c r="A317" s="77" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="71" t="inlineStr">
+      <c r="B317" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17221,12 +17253,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="71" t="inlineStr">
+      <c r="A318" s="77" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="71" t="inlineStr">
+      <c r="B318" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17252,12 +17284,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="71" t="inlineStr">
+      <c r="A319" s="77" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="71" t="inlineStr">
+      <c r="B319" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17283,12 +17315,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="71" t="inlineStr">
+      <c r="A320" s="77" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="71" t="inlineStr">
+      <c r="B320" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17314,12 +17346,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="71" t="inlineStr">
+      <c r="A321" s="77" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="71" t="inlineStr">
+      <c r="B321" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17345,12 +17377,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="71" t="inlineStr">
+      <c r="A322" s="77" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="71" t="inlineStr">
+      <c r="B322" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17375,12 +17407,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="71" t="inlineStr">
+      <c r="A323" s="77" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="71" t="inlineStr">
+      <c r="B323" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17405,12 +17437,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="71" t="inlineStr">
+      <c r="A324" s="77" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="71" t="inlineStr">
+      <c r="B324" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17435,12 +17467,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="71" t="inlineStr">
+      <c r="A325" s="77" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="71" t="inlineStr">
+      <c r="B325" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17465,12 +17497,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="71" t="inlineStr">
+      <c r="A326" s="77" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="71" t="inlineStr">
+      <c r="B326" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17495,12 +17527,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="71" t="inlineStr">
+      <c r="A327" s="77" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="71" t="inlineStr">
+      <c r="B327" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17527,12 +17559,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="71" t="inlineStr">
+      <c r="A328" s="77" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="71" t="inlineStr">
+      <c r="B328" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17559,12 +17591,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="71" t="inlineStr">
+      <c r="A329" s="77" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="71" t="inlineStr">
+      <c r="B329" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17591,12 +17623,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="71" t="inlineStr">
+      <c r="A330" s="77" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="71" t="inlineStr">
+      <c r="B330" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17623,12 +17655,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="71" t="inlineStr">
+      <c r="A331" s="77" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="71" t="inlineStr">
+      <c r="B331" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17655,12 +17687,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="71" t="inlineStr">
+      <c r="A332" s="77" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="71" t="inlineStr">
+      <c r="B332" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17687,12 +17719,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="71" t="inlineStr">
+      <c r="A333" s="77" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="71" t="inlineStr">
+      <c r="B333" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17719,12 +17751,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="71" t="inlineStr">
+      <c r="A334" s="77" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="71" t="inlineStr">
+      <c r="B334" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17751,12 +17783,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="71" t="inlineStr">
+      <c r="A335" s="77" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="71" t="inlineStr">
+      <c r="B335" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17783,12 +17815,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="71" t="inlineStr">
+      <c r="A336" s="77" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="71" t="inlineStr">
+      <c r="B336" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17815,12 +17847,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="71" t="inlineStr">
+      <c r="A337" s="77" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="71" t="inlineStr">
+      <c r="B337" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17847,12 +17879,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="71" t="inlineStr">
+      <c r="A338" s="77" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="71" t="inlineStr">
+      <c r="B338" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17879,12 +17911,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="71" t="inlineStr">
+      <c r="A339" s="77" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="71" t="inlineStr">
+      <c r="B339" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17911,12 +17943,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="71" t="inlineStr">
+      <c r="A340" s="77" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="71" t="inlineStr">
+      <c r="B340" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17943,12 +17975,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="71" t="inlineStr">
+      <c r="A341" s="77" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="71" t="inlineStr">
+      <c r="B341" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17975,12 +18007,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="71" t="inlineStr">
+      <c r="A342" s="77" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="71" t="inlineStr">
+      <c r="B342" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18007,12 +18039,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="71" t="inlineStr">
+      <c r="A343" s="77" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="71" t="inlineStr">
+      <c r="B343" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18039,12 +18071,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="71" t="inlineStr">
+      <c r="A344" s="77" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="71" t="inlineStr">
+      <c r="B344" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18071,12 +18103,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="71" t="inlineStr">
+      <c r="A345" s="77" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="71" t="inlineStr">
+      <c r="B345" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18103,12 +18135,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="71" t="inlineStr">
+      <c r="A346" s="77" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="71" t="inlineStr">
+      <c r="B346" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18135,12 +18167,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="71" t="inlineStr">
+      <c r="A347" s="77" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="71" t="inlineStr">
+      <c r="B347" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18167,12 +18199,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="71" t="inlineStr">
+      <c r="A348" s="77" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="71" t="inlineStr">
+      <c r="B348" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18199,12 +18231,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="71" t="inlineStr">
+      <c r="A349" s="77" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="71" t="inlineStr">
+      <c r="B349" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18231,12 +18263,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="71" t="inlineStr">
+      <c r="A350" s="77" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="71" t="inlineStr">
+      <c r="B350" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18263,12 +18295,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="71" t="inlineStr">
+      <c r="A351" s="77" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="71" t="inlineStr">
+      <c r="B351" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18295,12 +18327,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="71" t="inlineStr">
+      <c r="A352" s="77" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="71" t="inlineStr">
+      <c r="B352" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18326,12 +18358,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="71" t="inlineStr">
+      <c r="A353" s="77" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="71" t="inlineStr">
+      <c r="B353" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18357,12 +18389,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="71" t="inlineStr">
+      <c r="A354" s="77" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="71" t="inlineStr">
+      <c r="B354" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18388,12 +18420,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="71" t="inlineStr">
+      <c r="A355" s="77" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="71" t="inlineStr">
+      <c r="B355" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18419,12 +18451,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="71" t="inlineStr">
+      <c r="A356" s="77" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="71" t="inlineStr">
+      <c r="B356" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18450,12 +18482,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="71" t="inlineStr">
+      <c r="A357" s="77" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="71" t="inlineStr">
+      <c r="B357" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18481,12 +18513,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="71" t="inlineStr">
+      <c r="A358" s="77" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="71" t="inlineStr">
+      <c r="B358" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18512,12 +18544,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="71" t="inlineStr">
+      <c r="A359" s="77" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="71" t="inlineStr">
+      <c r="B359" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18543,12 +18575,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="71" t="inlineStr">
+      <c r="A360" s="77" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="71" t="inlineStr">
+      <c r="B360" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18574,12 +18606,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="71" t="inlineStr">
+      <c r="A361" s="77" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="71" t="inlineStr">
+      <c r="B361" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18605,12 +18637,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="71" t="inlineStr">
+      <c r="A362" s="77" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="71" t="inlineStr">
+      <c r="B362" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18637,12 +18669,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="71" t="inlineStr">
+      <c r="A363" s="77" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="71" t="inlineStr">
+      <c r="B363" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18669,12 +18701,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="71" t="inlineStr">
+      <c r="A364" s="77" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="71" t="inlineStr">
+      <c r="B364" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18701,12 +18733,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="71" t="inlineStr">
+      <c r="A365" s="77" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="71" t="inlineStr">
+      <c r="B365" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18733,12 +18765,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="71" t="inlineStr">
+      <c r="A366" s="77" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="71" t="inlineStr">
+      <c r="B366" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18765,12 +18797,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="71" t="inlineStr">
+      <c r="A367" s="77" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="71" t="inlineStr">
+      <c r="B367" s="77" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18797,12 +18829,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="71" t="inlineStr">
+      <c r="A368" s="77" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="71" t="inlineStr">
+      <c r="B368" s="77" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18829,12 +18861,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="71" t="inlineStr">
+      <c r="A369" s="77" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="71" t="inlineStr">
+      <c r="B369" s="77" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18861,12 +18893,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="71" t="inlineStr">
+      <c r="A370" s="77" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="71" t="inlineStr">
+      <c r="B370" s="77" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18893,12 +18925,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="71" t="inlineStr">
+      <c r="A371" s="77" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="71" t="inlineStr">
+      <c r="B371" s="77" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -20034,7 +20066,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -20044,7 +20076,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="71" t="inlineStr">
+      <c r="C2" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20056,7 +20088,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="71" t="inlineStr">
+      <c r="A3" s="77" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -20066,7 +20098,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="71" t="inlineStr">
+      <c r="C3" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20078,7 +20110,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="71" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -20088,7 +20120,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="71" t="inlineStr">
+      <c r="C4" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20100,7 +20132,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="71" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -20110,7 +20142,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="71" t="inlineStr">
+      <c r="C5" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20122,7 +20154,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="71" t="inlineStr">
+      <c r="A6" s="77" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20132,7 +20164,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="71" t="inlineStr">
+      <c r="C6" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20144,7 +20176,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="71" t="inlineStr">
+      <c r="A7" s="77" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20154,7 +20186,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="71" t="inlineStr">
+      <c r="C7" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20166,7 +20198,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="71" t="inlineStr">
+      <c r="A8" s="77" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20176,7 +20208,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="71" t="inlineStr">
+      <c r="C8" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20188,7 +20220,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="71" t="inlineStr">
+      <c r="A9" s="77" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20198,7 +20230,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="71" t="inlineStr">
+      <c r="C9" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20210,7 +20242,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="71" t="inlineStr">
+      <c r="A10" s="77" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20220,7 +20252,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="71" t="inlineStr">
+      <c r="C10" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20232,7 +20264,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="71" t="inlineStr">
+      <c r="A11" s="77" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20242,7 +20274,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="71" t="inlineStr">
+      <c r="C11" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20254,7 +20286,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="71" t="inlineStr">
+      <c r="A12" s="77" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20264,7 +20296,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="71" t="inlineStr">
+      <c r="C12" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20276,7 +20308,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="71" t="inlineStr">
+      <c r="A13" s="77" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20286,7 +20318,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="71" t="inlineStr">
+      <c r="C13" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20428,53 +20460,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="71" t="inlineStr">
+      <c r="B2" s="77" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="71" t="inlineStr">
+      <c r="C2" s="77" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="71" t="inlineStr">
+      <c r="D2" s="77" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="71" t="inlineStr">
+      <c r="E2" s="77" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="71" t="inlineStr">
+      <c r="F2" s="77" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="71" t="inlineStr">
+      <c r="G2" s="77" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="71" t="inlineStr">
+      <c r="H2" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="71" t="inlineStr">
+      <c r="I2" s="77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="71" t="n"/>
-      <c r="K2" s="71" t="inlineStr">
+      <c r="J2" s="77" t="n"/>
+      <c r="K2" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20511,45 +20543,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="71" t="inlineStr">
+      <c r="A3" s="77" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="71" t="inlineStr">
+      <c r="B3" s="77" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="71" t="inlineStr">
+      <c r="C3" s="77" t="inlineStr">
         <is>
           <t>main_idle_20261013044809.png</t>
         </is>
       </c>
-      <c r="D3" s="71" t="n"/>
-      <c r="E3" s="71" t="n"/>
-      <c r="F3" s="71" t="n">
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n">
         <v>0.179</v>
       </c>
-      <c r="G3" s="71" t="n">
+      <c r="G3" s="77" t="n">
         <v>0.23</v>
       </c>
-      <c r="H3" s="71" t="inlineStr">
+      <c r="H3" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="71" t="inlineStr">
+      <c r="I3" s="77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="71" t="inlineStr">
+      <c r="J3" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="71" t="inlineStr">
+      <c r="K3" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20586,45 +20618,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="71" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="71" t="inlineStr">
+      <c r="B4" s="77" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="71" t="inlineStr">
+      <c r="C4" s="77" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="71" t="n"/>
-      <c r="E4" s="71" t="n"/>
-      <c r="F4" s="71" t="inlineStr">
+      <c r="D4" s="77" t="n"/>
+      <c r="E4" s="77" t="n"/>
+      <c r="F4" s="77" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="71" t="inlineStr">
+      <c r="G4" s="77" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="71" t="inlineStr">
+      <c r="H4" s="77" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="71" t="inlineStr">
+      <c r="I4" s="77" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="71" t="n"/>
-      <c r="K4" s="71" t="inlineStr">
+      <c r="J4" s="77" t="n"/>
+      <c r="K4" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20661,45 +20693,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="71" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="71" t="inlineStr">
+      <c r="B5" s="77" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="71" t="inlineStr">
+      <c r="C5" s="77" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="71" t="n"/>
-      <c r="E5" s="71" t="n"/>
-      <c r="F5" s="71" t="inlineStr">
+      <c r="D5" s="77" t="n"/>
+      <c r="E5" s="77" t="n"/>
+      <c r="F5" s="77" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="71" t="inlineStr">
+      <c r="G5" s="77" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="71" t="inlineStr">
+      <c r="H5" s="77" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="71" t="inlineStr">
+      <c r="I5" s="77" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="71" t="n"/>
-      <c r="K5" s="71" t="inlineStr">
+      <c r="J5" s="77" t="n"/>
+      <c r="K5" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20736,45 +20768,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="71" t="inlineStr">
+      <c r="A6" s="77" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="71" t="inlineStr">
+      <c r="B6" s="77" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="71" t="inlineStr">
+      <c r="C6" s="77" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="71" t="n"/>
-      <c r="E6" s="71" t="n"/>
-      <c r="F6" s="71" t="inlineStr">
+      <c r="D6" s="77" t="n"/>
+      <c r="E6" s="77" t="n"/>
+      <c r="F6" s="77" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="71" t="inlineStr">
+      <c r="G6" s="77" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="71" t="inlineStr">
+      <c r="H6" s="77" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="71" t="inlineStr">
+      <c r="I6" s="77" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="71" t="n"/>
-      <c r="K6" s="71" t="inlineStr">
+      <c r="J6" s="77" t="n"/>
+      <c r="K6" s="77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20896,12 +20928,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B2" s="71" t="inlineStr">
+      <c r="B2" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -20940,12 +20972,12 @@
       <c r="J2" s="46" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="71" t="inlineStr">
+      <c r="A3" s="77" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B3" s="71" t="inlineStr">
+      <c r="B3" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -20984,12 +21016,12 @@
       <c r="J3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="71" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B4" s="71" t="inlineStr">
+      <c r="B4" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21028,12 +21060,12 @@
       <c r="J4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="71" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B5" s="71" t="inlineStr">
+      <c r="B5" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21072,12 +21104,12 @@
       <c r="J5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="71" t="inlineStr">
+      <c r="A6" s="77" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B6" s="71" t="inlineStr">
+      <c r="B6" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21116,12 +21148,12 @@
       <c r="J6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="71" t="inlineStr">
+      <c r="A7" s="77" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B7" s="71" t="inlineStr">
+      <c r="B7" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21160,12 +21192,12 @@
       <c r="J7" s="46" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="71" t="inlineStr">
+      <c r="A8" s="77" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B8" s="71" t="inlineStr">
+      <c r="B8" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21204,12 +21236,12 @@
       <c r="J8" s="46" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="71" t="inlineStr">
+      <c r="A9" s="77" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B9" s="71" t="inlineStr">
+      <c r="B9" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21248,12 +21280,12 @@
       <c r="J9" s="46" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="71" t="inlineStr">
+      <c r="A10" s="77" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B10" s="71" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21292,12 +21324,12 @@
       <c r="J10" s="46" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="71" t="inlineStr">
+      <c r="A11" s="77" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B11" s="71" t="inlineStr">
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21336,12 +21368,12 @@
       <c r="J11" s="46" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="71" t="inlineStr">
+      <c r="A12" s="77" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B12" s="71" t="inlineStr">
+      <c r="B12" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21380,12 +21412,12 @@
       <c r="J12" s="46" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="71" t="inlineStr">
+      <c r="A13" s="77" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B13" s="71" t="inlineStr">
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21443,12 +21475,12 @@
       <c r="J13" s="46" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="71" t="inlineStr">
+      <c r="A14" s="77" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B14" s="71" t="inlineStr">
+      <c r="B14" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21506,12 +21538,12 @@
       <c r="J14" s="46" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="71" t="inlineStr">
+      <c r="A15" s="77" t="inlineStr">
         <is>
           <t>趣味</t>
         </is>
       </c>
-      <c r="B15" s="71" t="inlineStr">
+      <c r="B15" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21572,12 +21604,12 @@
       <c r="J15" s="46" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="71" t="inlineStr">
+      <c r="A16" s="77" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B16" s="71" t="inlineStr">
+      <c r="B16" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21637,12 +21669,12 @@
       <c r="J16" s="46" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="71" t="inlineStr">
+      <c r="A17" s="77" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B17" s="71" t="inlineStr">
+      <c r="B17" s="77" t="inlineStr">
         <is>
           <t>共通</t>
         </is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -495,6 +495,18 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1197,7 +1209,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="77" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1207,31 +1219,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="77" t="n">
+      <c r="C2" s="81" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="77" t="n">
+      <c r="D2" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="77" t="n">
+      <c r="E2" s="81" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="77" t="n">
+      <c r="F2" s="81" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="77" t="n">
+      <c r="G2" s="81" t="n">
         <v>0.957</v>
       </c>
-      <c r="H2" s="77" t="n">
+      <c r="H2" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="77" t="n">
+      <c r="I2" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="77" t="n">
+      <c r="J2" s="81" t="n">
         <v>0.864</v>
       </c>
-      <c r="K2" s="77" t="n">
+      <c r="K2" s="81" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1241,7 +1253,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="77" t="inlineStr">
+      <c r="A3" s="81" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1251,31 +1263,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="77" t="n">
+      <c r="C3" s="81" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="77" t="n">
+      <c r="D3" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="77" t="n">
+      <c r="E3" s="81" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="77" t="n">
+      <c r="F3" s="81" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="77" t="n">
+      <c r="G3" s="81" t="n">
         <v>0.929</v>
       </c>
-      <c r="H3" s="77" t="n">
+      <c r="H3" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="77" t="n">
+      <c r="I3" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="77" t="n">
+      <c r="J3" s="81" t="n">
         <v>0.753</v>
       </c>
-      <c r="K3" s="77" t="n">
+      <c r="K3" s="81" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1285,7 +1297,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="77" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1295,31 +1307,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="77" t="n">
+      <c r="C4" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="77" t="n">
+      <c r="D4" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="77" t="n">
+      <c r="E4" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="77" t="n">
+      <c r="F4" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="77" t="n">
+      <c r="G4" s="81" t="n">
         <v>0.92</v>
       </c>
-      <c r="H4" s="77" t="n">
+      <c r="H4" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="77" t="n">
+      <c r="I4" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="77" t="n">
+      <c r="J4" s="81" t="n">
         <v>0.884</v>
       </c>
-      <c r="K4" s="77" t="n">
+      <c r="K4" s="81" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1391,7 +1403,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="77" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1401,10 +1413,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="77" t="n">
+      <c r="C2" s="81" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="77" t="n">
+      <c r="D2" s="81" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1414,7 +1426,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="77" t="inlineStr">
+      <c r="A3" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1424,16 +1436,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="77" t="n">
+      <c r="C3" s="81" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="77" t="n">
+      <c r="D3" s="81" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="77" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1443,16 +1455,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="77" t="n">
+      <c r="C4" s="81" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="77" t="n">
+      <c r="D4" s="81" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1462,16 +1474,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="77" t="n">
+      <c r="C5" s="81" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="77" t="n">
+      <c r="D5" s="81" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="77" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1481,16 +1493,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="77" t="n">
+      <c r="C6" s="81" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="77" t="n">
+      <c r="D6" s="81" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="77" t="inlineStr">
+      <c r="A7" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1500,10 +1512,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="77" t="n">
+      <c r="C7" s="81" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="77" t="n">
+      <c r="D7" s="81" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1563,17 +1575,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="77" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="77" t="inlineStr">
+      <c r="B2" s="81" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="77" t="inlineStr">
+      <c r="C2" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1585,17 +1597,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="77" t="inlineStr">
+      <c r="A3" s="81" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="77" t="inlineStr">
+      <c r="B3" s="81" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="77" t="inlineStr">
+      <c r="C3" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1603,17 +1615,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="77" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="77" t="inlineStr">
+      <c r="B4" s="81" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="77" t="inlineStr">
+      <c r="C4" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1625,17 +1637,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="77" t="inlineStr">
+      <c r="B5" s="81" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="77" t="inlineStr">
+      <c r="C5" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1647,17 +1659,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="77" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="77" t="inlineStr">
+      <c r="B6" s="81" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="77" t="inlineStr">
+      <c r="C6" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1665,17 +1677,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="77" t="inlineStr">
+      <c r="A7" s="81" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="77" t="inlineStr">
+      <c r="B7" s="81" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="77" t="inlineStr">
+      <c r="C7" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1683,17 +1695,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="77" t="inlineStr">
+      <c r="A8" s="81" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="77" t="inlineStr">
+      <c r="B8" s="81" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="77" t="inlineStr">
+      <c r="C8" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1705,17 +1717,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="77" t="inlineStr">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="77" t="inlineStr">
+      <c r="B9" s="81" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="77" t="inlineStr">
+      <c r="C9" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1727,17 +1739,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="77" t="inlineStr">
+      <c r="A10" s="81" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="77" t="inlineStr">
+      <c r="B10" s="81" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="77" t="inlineStr">
+      <c r="C10" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1749,17 +1761,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="77" t="inlineStr">
+      <c r="A11" s="81" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="77" t="inlineStr">
+      <c r="B11" s="81" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="77" t="inlineStr">
+      <c r="C11" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1767,17 +1779,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="77" t="inlineStr">
+      <c r="A12" s="81" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="77" t="inlineStr">
+      <c r="B12" s="81" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="77" t="inlineStr">
+      <c r="C12" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1785,17 +1797,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="77" t="inlineStr">
+      <c r="A13" s="81" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="77" t="inlineStr">
+      <c r="B13" s="81" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="77" t="inlineStr">
+      <c r="C13" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1807,17 +1819,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="77" t="inlineStr">
+      <c r="A14" s="81" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="77" t="inlineStr">
+      <c r="B14" s="81" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="77" t="inlineStr">
+      <c r="C14" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1829,17 +1841,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="77" t="inlineStr">
+      <c r="A15" s="81" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="77" t="inlineStr">
+      <c r="B15" s="81" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="77" t="inlineStr">
+      <c r="C15" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1851,17 +1863,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="77" t="inlineStr">
+      <c r="A16" s="81" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="77" t="inlineStr">
+      <c r="B16" s="81" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="77" t="inlineStr">
+      <c r="C16" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1873,17 +1885,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="77" t="inlineStr">
+      <c r="A17" s="81" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="77" t="inlineStr">
+      <c r="B17" s="81" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="77" t="inlineStr">
+      <c r="C17" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1895,17 +1907,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="77" t="inlineStr">
+      <c r="A18" s="81" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="77" t="inlineStr">
+      <c r="B18" s="81" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="77" t="inlineStr">
+      <c r="C18" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1917,17 +1929,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="77" t="inlineStr">
+      <c r="A19" s="81" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="77" t="inlineStr">
+      <c r="B19" s="81" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="77" t="inlineStr">
+      <c r="C19" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1935,17 +1947,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="77" t="inlineStr">
+      <c r="A20" s="81" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="77" t="inlineStr">
+      <c r="B20" s="81" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="77" t="inlineStr">
+      <c r="C20" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1953,17 +1965,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="77" t="inlineStr">
+      <c r="A21" s="81" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="77" t="inlineStr">
+      <c r="B21" s="81" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="77" t="inlineStr">
+      <c r="C21" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1975,17 +1987,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="77" t="inlineStr">
+      <c r="A22" s="81" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="77" t="inlineStr">
+      <c r="B22" s="81" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="77" t="inlineStr">
+      <c r="C22" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1997,17 +2009,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="77" t="inlineStr">
+      <c r="A23" s="81" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="77" t="inlineStr">
+      <c r="B23" s="81" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="77" t="inlineStr">
+      <c r="C23" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2019,17 +2031,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="77" t="inlineStr">
+      <c r="A24" s="81" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="77" t="inlineStr">
+      <c r="B24" s="81" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="77" t="inlineStr">
+      <c r="C24" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2041,17 +2053,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="77" t="inlineStr">
+      <c r="A25" s="81" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="77" t="inlineStr">
+      <c r="B25" s="81" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="77" t="inlineStr">
+      <c r="C25" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2059,17 +2071,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="77" t="inlineStr">
+      <c r="A26" s="81" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="77" t="inlineStr">
+      <c r="B26" s="81" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="77" t="inlineStr">
+      <c r="C26" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2077,17 +2089,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="77" t="inlineStr">
+      <c r="A27" s="81" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="77" t="inlineStr">
+      <c r="B27" s="81" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="77" t="inlineStr">
+      <c r="C27" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2099,17 +2111,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="77" t="inlineStr">
+      <c r="A28" s="81" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="77" t="inlineStr">
+      <c r="B28" s="81" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="77" t="inlineStr">
+      <c r="C28" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2121,17 +2133,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="77" t="inlineStr">
+      <c r="A29" s="81" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="77" t="inlineStr">
+      <c r="B29" s="81" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="77" t="inlineStr">
+      <c r="C29" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2143,17 +2155,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="77" t="inlineStr">
+      <c r="A30" s="81" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="77" t="inlineStr">
+      <c r="B30" s="81" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="77" t="inlineStr">
+      <c r="C30" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2161,17 +2173,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="77" t="inlineStr">
+      <c r="A31" s="81" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="77" t="inlineStr">
+      <c r="B31" s="81" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="77" t="inlineStr">
+      <c r="C31" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2183,17 +2195,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="77" t="inlineStr">
+      <c r="A32" s="81" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="77" t="inlineStr">
+      <c r="B32" s="81" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="77" t="inlineStr">
+      <c r="C32" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2201,17 +2213,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="77" t="inlineStr">
+      <c r="A33" s="81" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="77" t="inlineStr">
+      <c r="B33" s="81" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="77" t="inlineStr">
+      <c r="C33" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2219,17 +2231,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="77" t="inlineStr">
+      <c r="A34" s="81" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="77" t="inlineStr">
+      <c r="B34" s="81" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="77" t="inlineStr">
+      <c r="C34" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2237,17 +2249,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="77" t="inlineStr">
+      <c r="A35" s="81" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="77" t="inlineStr">
+      <c r="B35" s="81" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="77" t="inlineStr">
+      <c r="C35" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2255,17 +2267,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="77" t="inlineStr">
+      <c r="A36" s="81" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="77" t="inlineStr">
+      <c r="B36" s="81" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="77" t="inlineStr">
+      <c r="C36" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2273,17 +2285,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="77" t="inlineStr">
+      <c r="A37" s="81" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="77" t="inlineStr">
+      <c r="B37" s="81" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="77" t="inlineStr">
+      <c r="C37" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2291,17 +2303,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="77" t="inlineStr">
+      <c r="A38" s="81" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="77" t="inlineStr">
+      <c r="B38" s="81" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="77" t="inlineStr">
+      <c r="C38" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2309,17 +2321,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="77" t="inlineStr">
+      <c r="A39" s="81" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="77" t="inlineStr">
+      <c r="B39" s="81" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="77" t="inlineStr">
+      <c r="C39" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2327,17 +2339,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="77" t="inlineStr">
+      <c r="A40" s="81" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="77" t="inlineStr">
+      <c r="B40" s="81" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="77" t="inlineStr">
+      <c r="C40" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2349,17 +2361,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="77" t="inlineStr">
+      <c r="A41" s="81" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="77" t="inlineStr">
+      <c r="B41" s="81" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="77" t="inlineStr">
+      <c r="C41" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2367,17 +2379,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="77" t="inlineStr">
+      <c r="A42" s="81" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="77" t="inlineStr">
+      <c r="B42" s="81" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="77" t="inlineStr">
+      <c r="C42" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2389,17 +2401,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="77" t="inlineStr">
+      <c r="A43" s="81" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="77" t="inlineStr">
+      <c r="B43" s="81" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="77" t="inlineStr">
+      <c r="C43" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2407,17 +2419,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="77" t="inlineStr">
+      <c r="A44" s="81" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="77" t="inlineStr">
+      <c r="B44" s="81" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="77" t="inlineStr">
+      <c r="C44" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2429,17 +2441,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="77" t="inlineStr">
+      <c r="A45" s="81" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="77" t="inlineStr">
+      <c r="B45" s="81" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="77" t="inlineStr">
+      <c r="C45" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2788,17 +2800,17 @@
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="76" t="inlineStr">
+      <c r="A6" s="80" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B6" s="76" t="inlineStr">
+      <c r="B6" s="80" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C6" s="76" t="inlineStr">
+      <c r="C6" s="80" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2823,49 +2835,49 @@
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
         </is>
       </c>
-      <c r="G6" s="76" t="n"/>
-      <c r="H6" s="76" t="n"/>
-      <c r="I6" s="76" t="inlineStr">
+      <c r="G6" s="80" t="n"/>
+      <c r="H6" s="80" t="n"/>
+      <c r="I6" s="80" t="inlineStr">
         <is>
           <t>atm_bt.mp3</t>
         </is>
       </c>
-      <c r="J6" s="76" t="inlineStr">
+      <c r="J6" s="80" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K6" s="76" t="n"/>
-      <c r="L6" s="76" t="n"/>
-      <c r="M6" s="76" t="inlineStr">
+      <c r="K6" s="80" t="n"/>
+      <c r="L6" s="80" t="n"/>
+      <c r="M6" s="80" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N6" s="77" t="inlineStr">
+      <c r="N6" s="81" t="inlineStr">
         <is>
           <t>ATMはどこ</t>
         </is>
       </c>
-      <c r="O6" s="77" t="n"/>
-      <c r="P6" s="77" t="inlineStr">
+      <c r="O6" s="81" t="n"/>
+      <c r="P6" s="81" t="inlineStr">
         <is>
           <t>2026-10-13 17:14</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="76" t="inlineStr">
+      <c r="A7" s="80" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B7" s="76" t="inlineStr">
+      <c r="B7" s="80" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C7" s="76" t="inlineStr">
+      <c r="C7" s="80" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2890,28 +2902,28 @@
           <t>海外のカードは鳩谷郵便局のATM、日本のカードは和田家前のJAのATMをご利用ください。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G7" s="76" t="n"/>
-      <c r="H7" s="76" t="n"/>
-      <c r="I7" s="76" t="inlineStr">
+      <c r="G7" s="80" t="n"/>
+      <c r="H7" s="80" t="n"/>
+      <c r="I7" s="80" t="inlineStr">
         <is>
           <t>atm_deai.mp3</t>
         </is>
       </c>
-      <c r="J7" s="76" t="inlineStr">
+      <c r="J7" s="80" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K7" s="76" t="n"/>
-      <c r="L7" s="76" t="n"/>
-      <c r="M7" s="76" t="inlineStr">
+      <c r="K7" s="80" t="n"/>
+      <c r="L7" s="80" t="n"/>
+      <c r="M7" s="80" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N7" s="77" t="n"/>
-      <c r="O7" s="77" t="n"/>
-      <c r="P7" s="77" t="inlineStr">
+      <c r="N7" s="81" t="n"/>
+      <c r="O7" s="81" t="n"/>
+      <c r="P7" s="81" t="inlineStr">
         <is>
           <t>2026-10-13 17:15</t>
         </is>
@@ -2967,17 +2979,17 @@
       </c>
     </row>
     <row r="9" ht="58.05" customHeight="1">
-      <c r="A9" s="76" t="inlineStr">
+      <c r="A9" s="80" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B9" s="76" t="inlineStr">
+      <c r="B9" s="80" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C9" s="76" t="inlineStr">
+      <c r="C9" s="80" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2997,28 +3009,28 @@
         </is>
       </c>
       <c r="F9" s="44" t="n"/>
-      <c r="G9" s="76" t="n"/>
-      <c r="H9" s="76" t="n"/>
-      <c r="I9" s="76" t="inlineStr">
+      <c r="G9" s="80" t="n"/>
+      <c r="H9" s="80" t="n"/>
+      <c r="I9" s="80" t="inlineStr">
         <is>
           <t>currency_exchange_bt.mp3</t>
         </is>
       </c>
-      <c r="J9" s="76" t="inlineStr">
+      <c r="J9" s="80" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K9" s="76" t="n"/>
-      <c r="L9" s="76" t="n"/>
-      <c r="M9" s="76" t="inlineStr">
+      <c r="K9" s="80" t="n"/>
+      <c r="L9" s="80" t="n"/>
+      <c r="M9" s="80" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N9" s="77" t="n"/>
-      <c r="O9" s="77" t="n"/>
-      <c r="P9" s="77" t="inlineStr">
+      <c r="N9" s="81" t="n"/>
+      <c r="O9" s="81" t="n"/>
+      <c r="P9" s="81" t="inlineStr">
         <is>
           <t>2026-10-13 17:18</t>
         </is>
@@ -3083,22 +3095,22 @@
       </c>
     </row>
     <row r="11" ht="58.05" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="83" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="83" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="83" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="44" t="inlineStr">
         <is>
           <t>荷物 預け
 コインロッカー
@@ -3108,34 +3120,40 @@
 荷物 置き</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、窓口で臨時にお預かりしますのでお声がけください。</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="E11" s="44" t="inlineStr">
+        <is>
+          <t>コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、白川郷バスターミナル内の観光協会窓口窓口で臨時にお預かりしますのでお声がけください。</t>
+        </is>
+      </c>
+      <c r="F11" s="44" t="n"/>
+      <c r="G11" s="83" t="n"/>
+      <c r="H11" s="83" t="n"/>
+      <c r="I11" s="83" t="inlineStr">
         <is>
           <t>luggage_bt.mp3</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J11" s="83" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="14" t="inlineStr">
+      <c r="K11" s="83" t="n"/>
+      <c r="L11" s="83" t="n"/>
+      <c r="M11" s="83" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N11" s="35" t="inlineStr">
+      <c r="N11" s="84" t="inlineStr">
         <is>
           <t>荷物を預けたい</t>
+        </is>
+      </c>
+      <c r="O11" s="84" t="n"/>
+      <c r="P11" s="84" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:21</t>
         </is>
       </c>
     </row>
@@ -4888,17 +4906,17 @@
       </c>
     </row>
     <row r="43" ht="249.6" customHeight="1">
-      <c r="A43" s="76" t="inlineStr">
+      <c r="A43" s="80" t="inlineStr">
         <is>
           <t>guesthouse_access_deai</t>
         </is>
       </c>
-      <c r="B43" s="76" t="inlineStr">
+      <c r="B43" s="80" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C43" s="76" t="inlineStr">
+      <c r="C43" s="80" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -4932,30 +4950,30 @@
           <t>その建物は鳩谷八幡神社方面にあります。国道は交通量が多いため、川沿いの道をおすすめしております。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G43" s="76" t="inlineStr">
+      <c r="G43" s="80" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H43" s="76" t="n"/>
-      <c r="I43" s="76" t="inlineStr">
+      <c r="H43" s="80" t="n"/>
+      <c r="I43" s="80" t="inlineStr">
         <is>
           <t>guesthouse_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J43" s="76" t="inlineStr">
+      <c r="J43" s="80" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K43" s="76" t="n"/>
-      <c r="L43" s="76" t="n"/>
-      <c r="M43" s="76" t="inlineStr">
+      <c r="K43" s="80" t="n"/>
+      <c r="L43" s="80" t="n"/>
+      <c r="M43" s="80" t="inlineStr">
         <is>
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="77" t="n"/>
+      <c r="N43" s="81" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -6144,17 +6162,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="77" t="inlineStr">
+      <c r="A66" s="81" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="77" t="inlineStr">
+      <c r="B66" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="77" t="inlineStr">
+      <c r="C66" s="81" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -6184,26 +6202,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="77" t="inlineStr">
+      <c r="G66" s="81" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="77" t="n"/>
-      <c r="I66" s="77" t="inlineStr">
+      <c r="H66" s="81" t="n"/>
+      <c r="I66" s="81" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="77" t="inlineStr">
+      <c r="J66" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="77" t="n"/>
-      <c r="L66" s="77" t="n"/>
-      <c r="M66" s="77" t="n"/>
-      <c r="N66" s="77" t="n"/>
+      <c r="K66" s="81" t="n"/>
+      <c r="L66" s="81" t="n"/>
+      <c r="M66" s="81" t="n"/>
+      <c r="N66" s="81" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -7412,12 +7430,12 @@
       </c>
     </row>
     <row r="22" ht="64.8" customHeight="1">
-      <c r="A22" s="77" t="inlineStr">
+      <c r="A22" s="81" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B22" s="77" t="inlineStr">
+      <c r="B22" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7448,12 +7466,12 @@
       </c>
     </row>
     <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="77" t="inlineStr">
+      <c r="A23" s="81" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B23" s="77" t="inlineStr">
+      <c r="B23" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7484,12 +7502,12 @@
       </c>
     </row>
     <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="77" t="inlineStr">
+      <c r="A24" s="81" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B24" s="77" t="inlineStr">
+      <c r="B24" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7520,12 +7538,12 @@
       </c>
     </row>
     <row r="25" ht="81" customHeight="1">
-      <c r="A25" s="77" t="inlineStr">
+      <c r="A25" s="81" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B25" s="77" t="inlineStr">
+      <c r="B25" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7556,12 +7574,12 @@
       </c>
     </row>
     <row r="26" ht="64.8" customHeight="1">
-      <c r="A26" s="68" t="inlineStr">
+      <c r="A26" s="82" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B26" s="68" t="inlineStr">
+      <c r="B26" s="82" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8293,32 +8311,35 @@
       </c>
     </row>
     <row r="47" ht="81" customHeight="1">
-      <c r="A47" s="27" t="inlineStr">
+      <c r="A47" s="85" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B47" s="27" t="inlineStr">
+      <c r="B47" s="85" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="C47" s="28" t="inlineStr">
-        <is>
-          <t>luggage
-baggage
+      <c r="C47" s="73" t="inlineStr">
+        <is>
+          <t>luggage storage
 coin locker
-locker
-suitcase
-leave bag</t>
-        </is>
-      </c>
-      <c r="D47" s="28" t="inlineStr">
-        <is>
-          <t>There are coin lockers here. Lockers without a key are in use. If they are full, a nearby home also keeps luggage. If both are full, please ask at the counter and we will keep your luggage temporarily.</t>
-        </is>
-      </c>
-      <c r="E47" s="27" t="n"/>
+suitcase storage
+where can I leave my bag
+baggage storage locker</t>
+        </is>
+      </c>
+      <c r="D47" s="73" t="inlineStr">
+        <is>
+          <t>We have coin lockers available. If a locker doesn't have a key, it's currently in use. When the lockers are full, some nearby houses also offer luggage storage. If both are full, please ask at the Tourist Information Center window inside Shirakawa-go Bus Terminal, and we can store your luggage temporarily.</t>
+        </is>
+      </c>
+      <c r="E47" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、白川郷バスターミナル内の観光協会窓口窓口で臨時にお預かりしますのでお声がけください。</t>
+        </is>
+      </c>
       <c r="F47" s="29" t="inlineStr">
         <is>
           <t>コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、窓口で臨時にお預かりしますのでお声がけください。</t>
@@ -8326,32 +8347,35 @@
       </c>
     </row>
     <row r="48" ht="64.8" customHeight="1">
-      <c r="A48" s="27" t="inlineStr">
+      <c r="A48" s="85" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B48" s="27" t="inlineStr">
+      <c r="B48" s="85" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="C48" s="28" t="inlineStr">
-        <is>
-          <t>taquilla
-consigna
-equipaje
-maleta
-dejar bolsa
-locker</t>
-        </is>
-      </c>
-      <c r="D48" s="28" t="inlineStr">
-        <is>
-          <t>Hay taquillas que funcionan con monedas. Las que no tienen llave están en uso. Si están todas ocupadas, algunas casas particulares cercanas también guardan equipaje. Si ambas opciones están completas, consúltenos en el mostrador y le guardaremos el equipaje temporalmente.</t>
-        </is>
-      </c>
-      <c r="E48" s="27" t="n"/>
+      <c r="C48" s="73" t="inlineStr">
+        <is>
+          <t>guardar equipaje
+casillero de monedas
+almacenamiento de maletas
+dónde dejar mi bolsa
+guardarropa</t>
+        </is>
+      </c>
+      <c r="D48" s="73" t="inlineStr">
+        <is>
+          <t>Disponemos de casilleros de monedas. Si un casillero no tiene llave, significa que está en uso. Cuando los casilleros están llenos, algunas casas cercanas también pueden guardar su equipaje. Si ambos están llenos, diríjase a la ventanilla del Centro de Información Turística dentro de la Terminal de Autobuses de Shirakawa-go y podremos guardar su equipaje de forma temporal.</t>
+        </is>
+      </c>
+      <c r="E48" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、白川郷バスターミナル内の観光協会窓口窓口で臨時にお預かりしますのでお声がけください。</t>
+        </is>
+      </c>
       <c r="F48" s="29" t="inlineStr">
         <is>
           <t>コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、窓口で臨時にお預かりしますのでお声がけください。</t>
@@ -8359,32 +8383,35 @@
       </c>
     </row>
     <row r="49" ht="64.8" customHeight="1">
-      <c r="A49" s="27" t="inlineStr">
+      <c r="A49" s="85" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B49" s="27" t="inlineStr">
+      <c r="B49" s="85" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="C49" s="28" t="inlineStr">
-        <is>
-          <t>consigne
-casier
-bagage
-valise
-déposer bagage
-laisser valise</t>
-        </is>
-      </c>
-      <c r="D49" s="28" t="inlineStr">
-        <is>
-          <t>Des consignes automatiques sont à votre disposition. Celles qui n'ont pas de clé sont déjà utilisées. Si elles sont toutes pleines, des maisons voisines gardent également les bagages. Si tout est complet, nous pouvons garder vos bagages temporairement au guichet : n'hésitez pas à nous le demander.</t>
-        </is>
-      </c>
-      <c r="E49" s="27" t="n"/>
+      <c r="C49" s="73" t="inlineStr">
+        <is>
+          <t>consigne à bagages
+casier à pièces
+rangement valises
+où laisser mon sac
+stockage de bagages</t>
+        </is>
+      </c>
+      <c r="D49" s="73" t="inlineStr">
+        <is>
+          <t>Nous mettons à votre disposition des casiers à pièces. Si un casier n'a pas de clé, c'est qu'il est actuellement utilisé. Quand les casiers sont pleins, certaines maisons voisines proposent également un service de garde de bagages. Si les deux sont pleins, veuillez vous présenter au guichet du Centre d'Information Touristique à l'intérieur de la Gare Routière de Shirakawa-go, et nous pourrons garder vos bagages temporairement.</t>
+        </is>
+      </c>
+      <c r="E49" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、白川郷バスターミナル内の観光協会窓口窓口で臨時にお預かりしますのでお声がけください。</t>
+        </is>
+      </c>
       <c r="F49" s="29" t="inlineStr">
         <is>
           <t>コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、窓口で臨時にお預かりしますのでお声がけください。</t>
@@ -8392,32 +8419,35 @@
       </c>
     </row>
     <row r="50" ht="64.8" customHeight="1">
-      <c r="A50" s="27" t="inlineStr">
+      <c r="A50" s="85" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B50" s="27" t="inlineStr">
+      <c r="B50" s="85" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="C50" s="28" t="inlineStr">
-        <is>
-          <t>짐 맡기
-짐 맡길
-짐 보관
-코인로커
-사물함
-캐리어</t>
-        </is>
-      </c>
-      <c r="D50" s="28" t="inlineStr">
-        <is>
-          <t>코인로커가 있습니다. 열쇠가 꽂혀 있지 않은 로커는 사용 중입니다. 로커가 가득 찬 경우에는 근처 가정에서도 짐을 맡아 드리고 있습니다. 두 곳 모두 가득 찬 경우에는 창구에서 임시로 보관해 드리니 말씀해 주세요.</t>
-        </is>
-      </c>
-      <c r="E50" s="27" t="n"/>
+      <c r="C50" s="73" t="inlineStr">
+        <is>
+          <t>짐 보관
+동전 락커
+수하물 보관
+짐을 두다
+짐을 맡기다</t>
+        </is>
+      </c>
+      <c r="D50" s="73" t="inlineStr">
+        <is>
+          <t>동전 락커를 이용할 수 있습니다. 락커에 열쇠가 없으면 사용 중입니다. 락커가 가득 찼을 때는 근처 주택에서도 짐을 보관해 드립니다. 둘 다 가득 차 있으면 시라카와고 버스 터미널 내 관광협회 안내소 창구에 말씀해 주시면 임시로 보관해 드리겠습니다.</t>
+        </is>
+      </c>
+      <c r="E50" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、白川郷バスターミナル内の観光協会窓口窓口で臨時にお預かりしますのでお声がけください。</t>
+        </is>
+      </c>
       <c r="F50" s="29" t="inlineStr">
         <is>
           <t>コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、窓口で臨時にお預かりしますのでお声がけください。</t>
@@ -8425,32 +8455,35 @@
       </c>
     </row>
     <row r="51" ht="48.6" customHeight="1">
-      <c r="A51" s="30" t="inlineStr">
+      <c r="A51" s="86" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B51" s="30" t="inlineStr">
+      <c r="B51" s="86" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C51" s="31" t="inlineStr">
-        <is>
-          <t>寄存 行李
+      <c r="C51" s="75" t="inlineStr">
+        <is>
+          <t>行李寄存
+投币柜
 储物柜
-寄存柜
-行李箱
-行李 放哪
-存包</t>
-        </is>
-      </c>
-      <c r="D51" s="31" t="inlineStr">
-        <is>
-          <t>这里有投币储物柜。没有插钥匙的柜子表示正在使用中。如果储物柜已满，附近的住户也提供行李寄存服务。如果都满了，窗口可以临时为您保管，请告诉工作人员。</t>
-        </is>
-      </c>
-      <c r="E51" s="30" t="n"/>
+放行李
+箱子存放</t>
+        </is>
+      </c>
+      <c r="D51" s="75" t="inlineStr">
+        <is>
+          <t>我们提供投币式储物柜。如果储物柜上没有钥匙，表示正在使用中。当储物柜满了的时候，附近的民居也可以帮您保管行李。如果两处都满了，请到白川乡巴士终点站内的观光协会窗口告诉我们，我们会临时为您保管行李。</t>
+        </is>
+      </c>
+      <c r="E51" s="75" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、白川郷バスターミナル内の観光協会窓口窓口で臨時にお預かりしますのでお声がけください。</t>
+        </is>
+      </c>
       <c r="F51" s="32" t="inlineStr">
         <is>
           <t>コインロッカーがございます。鍵が付いていないものは使用中です。満杯の場合は、近くのお宅でもお荷物をお預かりしております。どちらもいっぱいの場合は、窓口で臨時にお預かりしますのでお声がけください。</t>
@@ -16762,12 +16795,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="77" t="inlineStr">
+      <c r="A302" s="81" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="77" t="inlineStr">
+      <c r="B302" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16793,12 +16826,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="77" t="inlineStr">
+      <c r="A303" s="81" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="77" t="inlineStr">
+      <c r="B303" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16824,12 +16857,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="77" t="inlineStr">
+      <c r="A304" s="81" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="77" t="inlineStr">
+      <c r="B304" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16855,12 +16888,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="77" t="inlineStr">
+      <c r="A305" s="81" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="77" t="inlineStr">
+      <c r="B305" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16886,12 +16919,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="77" t="inlineStr">
+      <c r="A306" s="81" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="77" t="inlineStr">
+      <c r="B306" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -16917,12 +16950,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="77" t="inlineStr">
+      <c r="A307" s="81" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="77" t="inlineStr">
+      <c r="B307" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16948,12 +16981,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="77" t="inlineStr">
+      <c r="A308" s="81" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="77" t="inlineStr">
+      <c r="B308" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16979,12 +17012,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="77" t="inlineStr">
+      <c r="A309" s="81" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="77" t="inlineStr">
+      <c r="B309" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17010,12 +17043,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="77" t="inlineStr">
+      <c r="A310" s="81" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="77" t="inlineStr">
+      <c r="B310" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17041,12 +17074,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="77" t="inlineStr">
+      <c r="A311" s="81" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="77" t="inlineStr">
+      <c r="B311" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17072,12 +17105,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="77" t="inlineStr">
+      <c r="A312" s="81" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="77" t="inlineStr">
+      <c r="B312" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17102,12 +17135,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="77" t="inlineStr">
+      <c r="A313" s="81" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="77" t="inlineStr">
+      <c r="B313" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17132,12 +17165,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="77" t="inlineStr">
+      <c r="A314" s="81" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="77" t="inlineStr">
+      <c r="B314" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17162,12 +17195,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="77" t="inlineStr">
+      <c r="A315" s="81" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="77" t="inlineStr">
+      <c r="B315" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17192,12 +17225,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="77" t="inlineStr">
+      <c r="A316" s="81" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="77" t="inlineStr">
+      <c r="B316" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17222,12 +17255,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="77" t="inlineStr">
+      <c r="A317" s="81" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="77" t="inlineStr">
+      <c r="B317" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17253,12 +17286,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="77" t="inlineStr">
+      <c r="A318" s="81" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="77" t="inlineStr">
+      <c r="B318" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17284,12 +17317,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="77" t="inlineStr">
+      <c r="A319" s="81" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="77" t="inlineStr">
+      <c r="B319" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17315,12 +17348,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="77" t="inlineStr">
+      <c r="A320" s="81" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="77" t="inlineStr">
+      <c r="B320" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17346,12 +17379,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="77" t="inlineStr">
+      <c r="A321" s="81" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="77" t="inlineStr">
+      <c r="B321" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17377,12 +17410,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="77" t="inlineStr">
+      <c r="A322" s="81" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="77" t="inlineStr">
+      <c r="B322" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17407,12 +17440,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="77" t="inlineStr">
+      <c r="A323" s="81" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="77" t="inlineStr">
+      <c r="B323" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17437,12 +17470,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="77" t="inlineStr">
+      <c r="A324" s="81" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="77" t="inlineStr">
+      <c r="B324" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17467,12 +17500,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="77" t="inlineStr">
+      <c r="A325" s="81" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="77" t="inlineStr">
+      <c r="B325" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17497,12 +17530,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="77" t="inlineStr">
+      <c r="A326" s="81" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="77" t="inlineStr">
+      <c r="B326" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17527,12 +17560,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="77" t="inlineStr">
+      <c r="A327" s="81" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="77" t="inlineStr">
+      <c r="B327" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17559,12 +17592,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="77" t="inlineStr">
+      <c r="A328" s="81" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="77" t="inlineStr">
+      <c r="B328" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17591,12 +17624,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="77" t="inlineStr">
+      <c r="A329" s="81" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="77" t="inlineStr">
+      <c r="B329" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17623,12 +17656,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="77" t="inlineStr">
+      <c r="A330" s="81" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="77" t="inlineStr">
+      <c r="B330" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17655,12 +17688,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="77" t="inlineStr">
+      <c r="A331" s="81" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="77" t="inlineStr">
+      <c r="B331" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17687,12 +17720,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="77" t="inlineStr">
+      <c r="A332" s="81" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="77" t="inlineStr">
+      <c r="B332" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17719,12 +17752,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="77" t="inlineStr">
+      <c r="A333" s="81" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="77" t="inlineStr">
+      <c r="B333" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17751,12 +17784,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="77" t="inlineStr">
+      <c r="A334" s="81" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="77" t="inlineStr">
+      <c r="B334" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17783,12 +17816,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="77" t="inlineStr">
+      <c r="A335" s="81" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="77" t="inlineStr">
+      <c r="B335" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17815,12 +17848,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="77" t="inlineStr">
+      <c r="A336" s="81" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="77" t="inlineStr">
+      <c r="B336" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17847,12 +17880,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="77" t="inlineStr">
+      <c r="A337" s="81" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="77" t="inlineStr">
+      <c r="B337" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17879,12 +17912,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="77" t="inlineStr">
+      <c r="A338" s="81" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="77" t="inlineStr">
+      <c r="B338" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17911,12 +17944,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="77" t="inlineStr">
+      <c r="A339" s="81" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="77" t="inlineStr">
+      <c r="B339" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17943,12 +17976,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="77" t="inlineStr">
+      <c r="A340" s="81" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="77" t="inlineStr">
+      <c r="B340" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17975,12 +18008,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="77" t="inlineStr">
+      <c r="A341" s="81" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="77" t="inlineStr">
+      <c r="B341" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18007,12 +18040,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="77" t="inlineStr">
+      <c r="A342" s="81" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="77" t="inlineStr">
+      <c r="B342" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18039,12 +18072,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="77" t="inlineStr">
+      <c r="A343" s="81" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="77" t="inlineStr">
+      <c r="B343" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18071,12 +18104,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="77" t="inlineStr">
+      <c r="A344" s="81" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="77" t="inlineStr">
+      <c r="B344" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18103,12 +18136,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="77" t="inlineStr">
+      <c r="A345" s="81" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="77" t="inlineStr">
+      <c r="B345" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18135,12 +18168,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="77" t="inlineStr">
+      <c r="A346" s="81" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="77" t="inlineStr">
+      <c r="B346" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18167,12 +18200,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="77" t="inlineStr">
+      <c r="A347" s="81" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="77" t="inlineStr">
+      <c r="B347" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18199,12 +18232,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="77" t="inlineStr">
+      <c r="A348" s="81" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="77" t="inlineStr">
+      <c r="B348" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18231,12 +18264,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="77" t="inlineStr">
+      <c r="A349" s="81" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="77" t="inlineStr">
+      <c r="B349" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18263,12 +18296,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="77" t="inlineStr">
+      <c r="A350" s="81" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="77" t="inlineStr">
+      <c r="B350" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18295,12 +18328,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="77" t="inlineStr">
+      <c r="A351" s="81" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="77" t="inlineStr">
+      <c r="B351" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18327,12 +18360,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="77" t="inlineStr">
+      <c r="A352" s="81" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="77" t="inlineStr">
+      <c r="B352" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18358,12 +18391,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="77" t="inlineStr">
+      <c r="A353" s="81" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="77" t="inlineStr">
+      <c r="B353" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18389,12 +18422,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="77" t="inlineStr">
+      <c r="A354" s="81" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="77" t="inlineStr">
+      <c r="B354" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18420,12 +18453,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="77" t="inlineStr">
+      <c r="A355" s="81" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="77" t="inlineStr">
+      <c r="B355" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18451,12 +18484,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="77" t="inlineStr">
+      <c r="A356" s="81" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="77" t="inlineStr">
+      <c r="B356" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18482,12 +18515,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="77" t="inlineStr">
+      <c r="A357" s="81" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="77" t="inlineStr">
+      <c r="B357" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18513,12 +18546,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="77" t="inlineStr">
+      <c r="A358" s="81" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="77" t="inlineStr">
+      <c r="B358" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18544,12 +18577,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="77" t="inlineStr">
+      <c r="A359" s="81" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="77" t="inlineStr">
+      <c r="B359" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18575,12 +18608,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="77" t="inlineStr">
+      <c r="A360" s="81" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="77" t="inlineStr">
+      <c r="B360" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18606,12 +18639,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="77" t="inlineStr">
+      <c r="A361" s="81" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="77" t="inlineStr">
+      <c r="B361" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18637,12 +18670,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="77" t="inlineStr">
+      <c r="A362" s="81" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="77" t="inlineStr">
+      <c r="B362" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18669,12 +18702,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="77" t="inlineStr">
+      <c r="A363" s="81" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="77" t="inlineStr">
+      <c r="B363" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18701,12 +18734,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="77" t="inlineStr">
+      <c r="A364" s="81" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="77" t="inlineStr">
+      <c r="B364" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18733,12 +18766,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="77" t="inlineStr">
+      <c r="A365" s="81" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="77" t="inlineStr">
+      <c r="B365" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18765,12 +18798,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="77" t="inlineStr">
+      <c r="A366" s="81" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="77" t="inlineStr">
+      <c r="B366" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18797,12 +18830,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="77" t="inlineStr">
+      <c r="A367" s="81" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="77" t="inlineStr">
+      <c r="B367" s="81" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18829,12 +18862,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="77" t="inlineStr">
+      <c r="A368" s="81" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="77" t="inlineStr">
+      <c r="B368" s="81" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18861,12 +18894,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="77" t="inlineStr">
+      <c r="A369" s="81" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="77" t="inlineStr">
+      <c r="B369" s="81" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18893,12 +18926,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="77" t="inlineStr">
+      <c r="A370" s="81" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="77" t="inlineStr">
+      <c r="B370" s="81" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18925,12 +18958,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="77" t="inlineStr">
+      <c r="A371" s="81" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="77" t="inlineStr">
+      <c r="B371" s="81" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -20066,7 +20099,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="77" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -20076,7 +20109,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="77" t="inlineStr">
+      <c r="C2" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20088,7 +20121,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="77" t="inlineStr">
+      <c r="A3" s="81" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -20098,7 +20131,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="77" t="inlineStr">
+      <c r="C3" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20110,7 +20143,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="77" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -20120,7 +20153,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="77" t="inlineStr">
+      <c r="C4" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20132,7 +20165,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -20142,7 +20175,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="77" t="inlineStr">
+      <c r="C5" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20154,7 +20187,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="77" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20164,7 +20197,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="77" t="inlineStr">
+      <c r="C6" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20176,7 +20209,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="77" t="inlineStr">
+      <c r="A7" s="81" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20186,7 +20219,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="77" t="inlineStr">
+      <c r="C7" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20198,7 +20231,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="77" t="inlineStr">
+      <c r="A8" s="81" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20208,7 +20241,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="77" t="inlineStr">
+      <c r="C8" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20220,7 +20253,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="77" t="inlineStr">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20230,7 +20263,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="77" t="inlineStr">
+      <c r="C9" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20242,7 +20275,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="77" t="inlineStr">
+      <c r="A10" s="81" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20252,7 +20285,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="77" t="inlineStr">
+      <c r="C10" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20264,7 +20297,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="77" t="inlineStr">
+      <c r="A11" s="81" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20274,7 +20307,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="77" t="inlineStr">
+      <c r="C11" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20286,7 +20319,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="77" t="inlineStr">
+      <c r="A12" s="81" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20296,7 +20329,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="77" t="inlineStr">
+      <c r="C12" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20308,7 +20341,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="77" t="inlineStr">
+      <c r="A13" s="81" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20318,7 +20351,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="77" t="inlineStr">
+      <c r="C13" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20460,53 +20493,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="77" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="77" t="inlineStr">
+      <c r="B2" s="81" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="77" t="inlineStr">
+      <c r="C2" s="81" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="77" t="inlineStr">
+      <c r="D2" s="81" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="77" t="inlineStr">
+      <c r="E2" s="81" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="77" t="inlineStr">
+      <c r="F2" s="81" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="77" t="inlineStr">
+      <c r="G2" s="81" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="77" t="inlineStr">
+      <c r="H2" s="81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="77" t="inlineStr">
+      <c r="I2" s="81" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="77" t="n"/>
-      <c r="K2" s="77" t="inlineStr">
+      <c r="J2" s="81" t="n"/>
+      <c r="K2" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20543,45 +20576,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="77" t="inlineStr">
+      <c r="A3" s="81" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="77" t="inlineStr">
+      <c r="B3" s="81" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="77" t="inlineStr">
+      <c r="C3" s="81" t="inlineStr">
         <is>
           <t>main_idle_20261013044809.png</t>
         </is>
       </c>
-      <c r="D3" s="77" t="n"/>
-      <c r="E3" s="77" t="n"/>
-      <c r="F3" s="77" t="n">
+      <c r="D3" s="81" t="n"/>
+      <c r="E3" s="81" t="n"/>
+      <c r="F3" s="81" t="n">
         <v>0.179</v>
       </c>
-      <c r="G3" s="77" t="n">
+      <c r="G3" s="81" t="n">
         <v>0.23</v>
       </c>
-      <c r="H3" s="77" t="inlineStr">
+      <c r="H3" s="81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="77" t="inlineStr">
+      <c r="I3" s="81" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="77" t="inlineStr">
+      <c r="J3" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="77" t="inlineStr">
+      <c r="K3" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20618,45 +20651,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="77" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="77" t="inlineStr">
+      <c r="B4" s="81" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="77" t="inlineStr">
+      <c r="C4" s="81" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="77" t="n"/>
-      <c r="E4" s="77" t="n"/>
-      <c r="F4" s="77" t="inlineStr">
+      <c r="D4" s="81" t="n"/>
+      <c r="E4" s="81" t="n"/>
+      <c r="F4" s="81" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="77" t="inlineStr">
+      <c r="G4" s="81" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="77" t="inlineStr">
+      <c r="H4" s="81" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="77" t="inlineStr">
+      <c r="I4" s="81" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="77" t="n"/>
-      <c r="K4" s="77" t="inlineStr">
+      <c r="J4" s="81" t="n"/>
+      <c r="K4" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20693,45 +20726,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="77" t="inlineStr">
+      <c r="B5" s="81" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="77" t="inlineStr">
+      <c r="C5" s="81" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="77" t="n"/>
-      <c r="E5" s="77" t="n"/>
-      <c r="F5" s="77" t="inlineStr">
+      <c r="D5" s="81" t="n"/>
+      <c r="E5" s="81" t="n"/>
+      <c r="F5" s="81" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="77" t="inlineStr">
+      <c r="G5" s="81" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="77" t="inlineStr">
+      <c r="H5" s="81" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="77" t="inlineStr">
+      <c r="I5" s="81" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="77" t="n"/>
-      <c r="K5" s="77" t="inlineStr">
+      <c r="J5" s="81" t="n"/>
+      <c r="K5" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20768,45 +20801,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="77" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="77" t="inlineStr">
+      <c r="B6" s="81" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="77" t="inlineStr">
+      <c r="C6" s="81" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="77" t="n"/>
-      <c r="E6" s="77" t="n"/>
-      <c r="F6" s="77" t="inlineStr">
+      <c r="D6" s="81" t="n"/>
+      <c r="E6" s="81" t="n"/>
+      <c r="F6" s="81" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="77" t="inlineStr">
+      <c r="G6" s="81" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="77" t="inlineStr">
+      <c r="H6" s="81" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="77" t="inlineStr">
+      <c r="I6" s="81" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="77" t="n"/>
-      <c r="K6" s="77" t="inlineStr">
+      <c r="J6" s="81" t="n"/>
+      <c r="K6" s="81" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20928,12 +20961,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="77" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B2" s="77" t="inlineStr">
+      <c r="B2" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -20972,12 +21005,12 @@
       <c r="J2" s="46" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="77" t="inlineStr">
+      <c r="A3" s="81" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B3" s="77" t="inlineStr">
+      <c r="B3" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21016,12 +21049,12 @@
       <c r="J3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="77" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B4" s="77" t="inlineStr">
+      <c r="B4" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21060,12 +21093,12 @@
       <c r="J4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B5" s="77" t="inlineStr">
+      <c r="B5" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21104,12 +21137,12 @@
       <c r="J5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="77" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B6" s="77" t="inlineStr">
+      <c r="B6" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21148,12 +21181,12 @@
       <c r="J6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="77" t="inlineStr">
+      <c r="A7" s="81" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B7" s="77" t="inlineStr">
+      <c r="B7" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21192,12 +21225,12 @@
       <c r="J7" s="46" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="77" t="inlineStr">
+      <c r="A8" s="81" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B8" s="77" t="inlineStr">
+      <c r="B8" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21236,12 +21269,12 @@
       <c r="J8" s="46" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="77" t="inlineStr">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B9" s="77" t="inlineStr">
+      <c r="B9" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21280,12 +21313,12 @@
       <c r="J9" s="46" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="77" t="inlineStr">
+      <c r="A10" s="81" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B10" s="77" t="inlineStr">
+      <c r="B10" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21324,12 +21357,12 @@
       <c r="J10" s="46" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="77" t="inlineStr">
+      <c r="A11" s="81" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B11" s="77" t="inlineStr">
+      <c r="B11" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21368,12 +21401,12 @@
       <c r="J11" s="46" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="77" t="inlineStr">
+      <c r="A12" s="81" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B12" s="77" t="inlineStr">
+      <c r="B12" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21412,12 +21445,12 @@
       <c r="J12" s="46" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="77" t="inlineStr">
+      <c r="A13" s="81" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B13" s="77" t="inlineStr">
+      <c r="B13" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21475,12 +21508,12 @@
       <c r="J13" s="46" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="77" t="inlineStr">
+      <c r="A14" s="81" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B14" s="77" t="inlineStr">
+      <c r="B14" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21538,12 +21571,12 @@
       <c r="J14" s="46" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="77" t="inlineStr">
+      <c r="A15" s="81" t="inlineStr">
         <is>
           <t>趣味</t>
         </is>
       </c>
-      <c r="B15" s="77" t="inlineStr">
+      <c r="B15" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21604,12 +21637,12 @@
       <c r="J15" s="46" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="77" t="inlineStr">
+      <c r="A16" s="81" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B16" s="77" t="inlineStr">
+      <c r="B16" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21669,12 +21702,12 @@
       <c r="J16" s="46" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="77" t="inlineStr">
+      <c r="A17" s="81" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B17" s="77" t="inlineStr">
+      <c r="B17" s="81" t="inlineStr">
         <is>
           <t>共通</t>
         </is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -507,6 +507,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1209,7 +1218,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="81" t="inlineStr">
+      <c r="A2" s="84" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1219,31 +1228,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="81" t="n">
+      <c r="C2" s="84" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="81" t="n">
+      <c r="D2" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="81" t="n">
+      <c r="E2" s="84" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="81" t="n">
+      <c r="F2" s="84" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="81" t="n">
+      <c r="G2" s="84" t="n">
         <v>0.957</v>
       </c>
-      <c r="H2" s="81" t="n">
+      <c r="H2" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="81" t="n">
+      <c r="I2" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="81" t="n">
+      <c r="J2" s="84" t="n">
         <v>0.864</v>
       </c>
-      <c r="K2" s="81" t="n">
+      <c r="K2" s="84" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1253,7 +1262,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="81" t="inlineStr">
+      <c r="A3" s="84" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1263,31 +1272,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="81" t="n">
+      <c r="C3" s="84" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="81" t="n">
+      <c r="D3" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="81" t="n">
+      <c r="E3" s="84" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="81" t="n">
+      <c r="F3" s="84" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="81" t="n">
+      <c r="G3" s="84" t="n">
         <v>0.929</v>
       </c>
-      <c r="H3" s="81" t="n">
+      <c r="H3" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="81" t="n">
+      <c r="I3" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="81" t="n">
+      <c r="J3" s="84" t="n">
         <v>0.753</v>
       </c>
-      <c r="K3" s="81" t="n">
+      <c r="K3" s="84" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1297,7 +1306,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="81" t="inlineStr">
+      <c r="A4" s="84" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1307,31 +1316,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="81" t="n">
+      <c r="C4" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="81" t="n">
+      <c r="D4" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="81" t="n">
+      <c r="E4" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="81" t="n">
+      <c r="F4" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="81" t="n">
+      <c r="G4" s="84" t="n">
         <v>0.92</v>
       </c>
-      <c r="H4" s="81" t="n">
+      <c r="H4" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="81" t="n">
+      <c r="I4" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="81" t="n">
+      <c r="J4" s="84" t="n">
         <v>0.884</v>
       </c>
-      <c r="K4" s="81" t="n">
+      <c r="K4" s="84" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1403,7 +1412,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="81" t="inlineStr">
+      <c r="A2" s="84" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1413,10 +1422,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="81" t="n">
+      <c r="C2" s="84" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="81" t="n">
+      <c r="D2" s="84" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1426,7 +1435,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="81" t="inlineStr">
+      <c r="A3" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1436,16 +1445,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="81" t="n">
+      <c r="C3" s="84" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="81" t="n">
+      <c r="D3" s="84" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="81" t="inlineStr">
+      <c r="A4" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1455,16 +1464,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="81" t="n">
+      <c r="C4" s="84" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="81" t="n">
+      <c r="D4" s="84" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="81" t="inlineStr">
+      <c r="A5" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1474,16 +1483,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="81" t="n">
+      <c r="C5" s="84" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="81" t="n">
+      <c r="D5" s="84" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="81" t="inlineStr">
+      <c r="A6" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1493,16 +1502,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="81" t="n">
+      <c r="C6" s="84" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="81" t="n">
+      <c r="D6" s="84" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="81" t="inlineStr">
+      <c r="A7" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1512,10 +1521,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="81" t="n">
+      <c r="C7" s="84" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="81" t="n">
+      <c r="D7" s="84" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1575,17 +1584,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="81" t="inlineStr">
+      <c r="A2" s="84" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="81" t="inlineStr">
+      <c r="B2" s="84" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="81" t="inlineStr">
+      <c r="C2" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1597,17 +1606,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="81" t="inlineStr">
+      <c r="A3" s="84" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="81" t="inlineStr">
+      <c r="B3" s="84" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="81" t="inlineStr">
+      <c r="C3" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1615,17 +1624,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="81" t="inlineStr">
+      <c r="A4" s="84" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="81" t="inlineStr">
+      <c r="B4" s="84" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="81" t="inlineStr">
+      <c r="C4" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1637,17 +1646,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="81" t="inlineStr">
+      <c r="A5" s="84" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="81" t="inlineStr">
+      <c r="B5" s="84" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="81" t="inlineStr">
+      <c r="C5" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1659,17 +1668,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="81" t="inlineStr">
+      <c r="A6" s="84" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="81" t="inlineStr">
+      <c r="B6" s="84" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="81" t="inlineStr">
+      <c r="C6" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1677,17 +1686,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="81" t="inlineStr">
+      <c r="A7" s="84" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="81" t="inlineStr">
+      <c r="B7" s="84" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="81" t="inlineStr">
+      <c r="C7" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1695,17 +1704,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="81" t="inlineStr">
+      <c r="A8" s="84" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="81" t="inlineStr">
+      <c r="B8" s="84" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="81" t="inlineStr">
+      <c r="C8" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1717,17 +1726,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="81" t="inlineStr">
+      <c r="A9" s="84" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="81" t="inlineStr">
+      <c r="B9" s="84" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="81" t="inlineStr">
+      <c r="C9" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1739,17 +1748,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="81" t="inlineStr">
+      <c r="A10" s="84" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="81" t="inlineStr">
+      <c r="B10" s="84" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="81" t="inlineStr">
+      <c r="C10" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1761,17 +1770,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="81" t="inlineStr">
+      <c r="A11" s="84" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="81" t="inlineStr">
+      <c r="B11" s="84" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="81" t="inlineStr">
+      <c r="C11" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1779,17 +1788,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="81" t="inlineStr">
+      <c r="A12" s="84" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="81" t="inlineStr">
+      <c r="B12" s="84" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="81" t="inlineStr">
+      <c r="C12" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1797,17 +1806,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="81" t="inlineStr">
+      <c r="A13" s="84" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="81" t="inlineStr">
+      <c r="B13" s="84" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="81" t="inlineStr">
+      <c r="C13" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1819,17 +1828,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="81" t="inlineStr">
+      <c r="A14" s="84" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="81" t="inlineStr">
+      <c r="B14" s="84" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="81" t="inlineStr">
+      <c r="C14" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1841,17 +1850,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="81" t="inlineStr">
+      <c r="A15" s="84" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="81" t="inlineStr">
+      <c r="B15" s="84" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="81" t="inlineStr">
+      <c r="C15" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1863,17 +1872,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="81" t="inlineStr">
+      <c r="A16" s="84" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="81" t="inlineStr">
+      <c r="B16" s="84" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="81" t="inlineStr">
+      <c r="C16" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1885,17 +1894,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="81" t="inlineStr">
+      <c r="A17" s="84" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="81" t="inlineStr">
+      <c r="B17" s="84" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="81" t="inlineStr">
+      <c r="C17" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1907,17 +1916,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="81" t="inlineStr">
+      <c r="A18" s="84" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="81" t="inlineStr">
+      <c r="B18" s="84" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="81" t="inlineStr">
+      <c r="C18" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1929,17 +1938,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="81" t="inlineStr">
+      <c r="A19" s="84" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="81" t="inlineStr">
+      <c r="B19" s="84" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="81" t="inlineStr">
+      <c r="C19" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1947,17 +1956,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="81" t="inlineStr">
+      <c r="A20" s="84" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="81" t="inlineStr">
+      <c r="B20" s="84" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="81" t="inlineStr">
+      <c r="C20" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1965,17 +1974,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="81" t="inlineStr">
+      <c r="A21" s="84" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="81" t="inlineStr">
+      <c r="B21" s="84" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="81" t="inlineStr">
+      <c r="C21" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1987,17 +1996,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="81" t="inlineStr">
+      <c r="A22" s="84" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="81" t="inlineStr">
+      <c r="B22" s="84" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="81" t="inlineStr">
+      <c r="C22" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2009,17 +2018,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="81" t="inlineStr">
+      <c r="A23" s="84" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="81" t="inlineStr">
+      <c r="B23" s="84" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="81" t="inlineStr">
+      <c r="C23" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2031,17 +2040,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="81" t="inlineStr">
+      <c r="A24" s="84" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="81" t="inlineStr">
+      <c r="B24" s="84" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="81" t="inlineStr">
+      <c r="C24" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2053,17 +2062,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="81" t="inlineStr">
+      <c r="A25" s="84" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="81" t="inlineStr">
+      <c r="B25" s="84" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="81" t="inlineStr">
+      <c r="C25" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2071,17 +2080,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="81" t="inlineStr">
+      <c r="A26" s="84" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="81" t="inlineStr">
+      <c r="B26" s="84" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="81" t="inlineStr">
+      <c r="C26" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2089,17 +2098,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="81" t="inlineStr">
+      <c r="A27" s="84" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="81" t="inlineStr">
+      <c r="B27" s="84" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="81" t="inlineStr">
+      <c r="C27" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2111,17 +2120,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="81" t="inlineStr">
+      <c r="A28" s="84" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="81" t="inlineStr">
+      <c r="B28" s="84" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="81" t="inlineStr">
+      <c r="C28" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2133,17 +2142,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="81" t="inlineStr">
+      <c r="A29" s="84" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="81" t="inlineStr">
+      <c r="B29" s="84" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="81" t="inlineStr">
+      <c r="C29" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2155,17 +2164,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="81" t="inlineStr">
+      <c r="A30" s="84" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="81" t="inlineStr">
+      <c r="B30" s="84" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="81" t="inlineStr">
+      <c r="C30" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2173,17 +2182,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="81" t="inlineStr">
+      <c r="A31" s="84" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="81" t="inlineStr">
+      <c r="B31" s="84" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="81" t="inlineStr">
+      <c r="C31" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2195,17 +2204,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="81" t="inlineStr">
+      <c r="A32" s="84" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="81" t="inlineStr">
+      <c r="B32" s="84" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="81" t="inlineStr">
+      <c r="C32" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2213,17 +2222,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="81" t="inlineStr">
+      <c r="A33" s="84" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="81" t="inlineStr">
+      <c r="B33" s="84" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="81" t="inlineStr">
+      <c r="C33" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2231,17 +2240,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="81" t="inlineStr">
+      <c r="A34" s="84" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="81" t="inlineStr">
+      <c r="B34" s="84" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="81" t="inlineStr">
+      <c r="C34" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2249,17 +2258,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="81" t="inlineStr">
+      <c r="A35" s="84" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="81" t="inlineStr">
+      <c r="B35" s="84" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="81" t="inlineStr">
+      <c r="C35" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2267,17 +2276,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="81" t="inlineStr">
+      <c r="A36" s="84" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="81" t="inlineStr">
+      <c r="B36" s="84" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="81" t="inlineStr">
+      <c r="C36" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2285,17 +2294,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="81" t="inlineStr">
+      <c r="A37" s="84" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="81" t="inlineStr">
+      <c r="B37" s="84" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="81" t="inlineStr">
+      <c r="C37" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2303,17 +2312,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="81" t="inlineStr">
+      <c r="A38" s="84" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="81" t="inlineStr">
+      <c r="B38" s="84" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="81" t="inlineStr">
+      <c r="C38" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2321,17 +2330,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="81" t="inlineStr">
+      <c r="A39" s="84" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="81" t="inlineStr">
+      <c r="B39" s="84" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="81" t="inlineStr">
+      <c r="C39" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2339,17 +2348,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="81" t="inlineStr">
+      <c r="A40" s="84" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="81" t="inlineStr">
+      <c r="B40" s="84" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="81" t="inlineStr">
+      <c r="C40" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2361,17 +2370,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="81" t="inlineStr">
+      <c r="A41" s="84" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="81" t="inlineStr">
+      <c r="B41" s="84" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="81" t="inlineStr">
+      <c r="C41" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2379,17 +2388,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="81" t="inlineStr">
+      <c r="A42" s="84" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="81" t="inlineStr">
+      <c r="B42" s="84" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="81" t="inlineStr">
+      <c r="C42" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2401,17 +2410,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="81" t="inlineStr">
+      <c r="A43" s="84" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="81" t="inlineStr">
+      <c r="B43" s="84" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="81" t="inlineStr">
+      <c r="C43" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2419,17 +2428,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="81" t="inlineStr">
+      <c r="A44" s="84" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="81" t="inlineStr">
+      <c r="B44" s="84" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="81" t="inlineStr">
+      <c r="C44" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2441,17 +2450,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="81" t="inlineStr">
+      <c r="A45" s="84" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="81" t="inlineStr">
+      <c r="B45" s="84" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="81" t="inlineStr">
+      <c r="C45" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2800,17 +2809,17 @@
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="80" t="inlineStr">
+      <c r="A6" s="83" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B6" s="80" t="inlineStr">
+      <c r="B6" s="83" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C6" s="80" t="inlineStr">
+      <c r="C6" s="83" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2835,49 +2844,49 @@
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
         </is>
       </c>
-      <c r="G6" s="80" t="n"/>
-      <c r="H6" s="80" t="n"/>
-      <c r="I6" s="80" t="inlineStr">
+      <c r="G6" s="83" t="n"/>
+      <c r="H6" s="83" t="n"/>
+      <c r="I6" s="83" t="inlineStr">
         <is>
           <t>atm_bt.mp3</t>
         </is>
       </c>
-      <c r="J6" s="80" t="inlineStr">
+      <c r="J6" s="83" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K6" s="80" t="n"/>
-      <c r="L6" s="80" t="n"/>
-      <c r="M6" s="80" t="inlineStr">
+      <c r="K6" s="83" t="n"/>
+      <c r="L6" s="83" t="n"/>
+      <c r="M6" s="83" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N6" s="81" t="inlineStr">
+      <c r="N6" s="84" t="inlineStr">
         <is>
           <t>ATMはどこ</t>
         </is>
       </c>
-      <c r="O6" s="81" t="n"/>
-      <c r="P6" s="81" t="inlineStr">
+      <c r="O6" s="84" t="n"/>
+      <c r="P6" s="84" t="inlineStr">
         <is>
           <t>2026-10-13 17:14</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="80" t="inlineStr">
+      <c r="A7" s="83" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B7" s="80" t="inlineStr">
+      <c r="B7" s="83" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C7" s="80" t="inlineStr">
+      <c r="C7" s="83" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2902,28 +2911,28 @@
           <t>海外のカードは鳩谷郵便局のATM、日本のカードは和田家前のJAのATMをご利用ください。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G7" s="80" t="n"/>
-      <c r="H7" s="80" t="n"/>
-      <c r="I7" s="80" t="inlineStr">
+      <c r="G7" s="83" t="n"/>
+      <c r="H7" s="83" t="n"/>
+      <c r="I7" s="83" t="inlineStr">
         <is>
           <t>atm_deai.mp3</t>
         </is>
       </c>
-      <c r="J7" s="80" t="inlineStr">
+      <c r="J7" s="83" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K7" s="80" t="n"/>
-      <c r="L7" s="80" t="n"/>
-      <c r="M7" s="80" t="inlineStr">
+      <c r="K7" s="83" t="n"/>
+      <c r="L7" s="83" t="n"/>
+      <c r="M7" s="83" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N7" s="81" t="n"/>
-      <c r="O7" s="81" t="n"/>
-      <c r="P7" s="81" t="inlineStr">
+      <c r="N7" s="84" t="n"/>
+      <c r="O7" s="84" t="n"/>
+      <c r="P7" s="84" t="inlineStr">
         <is>
           <t>2026-10-13 17:15</t>
         </is>
@@ -2979,17 +2988,17 @@
       </c>
     </row>
     <row r="9" ht="58.05" customHeight="1">
-      <c r="A9" s="80" t="inlineStr">
+      <c r="A9" s="83" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B9" s="80" t="inlineStr">
+      <c r="B9" s="83" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C9" s="80" t="inlineStr">
+      <c r="C9" s="83" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3009,45 +3018,45 @@
         </is>
       </c>
       <c r="F9" s="44" t="n"/>
-      <c r="G9" s="80" t="n"/>
-      <c r="H9" s="80" t="n"/>
-      <c r="I9" s="80" t="inlineStr">
+      <c r="G9" s="83" t="n"/>
+      <c r="H9" s="83" t="n"/>
+      <c r="I9" s="83" t="inlineStr">
         <is>
           <t>currency_exchange_bt.mp3</t>
         </is>
       </c>
-      <c r="J9" s="80" t="inlineStr">
+      <c r="J9" s="83" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K9" s="80" t="n"/>
-      <c r="L9" s="80" t="n"/>
-      <c r="M9" s="80" t="inlineStr">
+      <c r="K9" s="83" t="n"/>
+      <c r="L9" s="83" t="n"/>
+      <c r="M9" s="83" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N9" s="81" t="n"/>
-      <c r="O9" s="81" t="n"/>
-      <c r="P9" s="81" t="inlineStr">
+      <c r="N9" s="84" t="n"/>
+      <c r="O9" s="84" t="n"/>
+      <c r="P9" s="84" t="inlineStr">
         <is>
           <t>2026-10-13 17:18</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58.05" customHeight="1">
-      <c r="A10" s="80" t="inlineStr">
+      <c r="A10" s="83" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B10" s="80" t="inlineStr">
+      <c r="B10" s="83" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C10" s="80" t="inlineStr">
+      <c r="C10" s="83" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3067,28 +3076,28 @@
         </is>
       </c>
       <c r="F10" s="44" t="n"/>
-      <c r="G10" s="80" t="n"/>
-      <c r="H10" s="80" t="n"/>
-      <c r="I10" s="80" t="inlineStr">
+      <c r="G10" s="83" t="n"/>
+      <c r="H10" s="83" t="n"/>
+      <c r="I10" s="83" t="inlineStr">
         <is>
           <t>currency_exchange_deai.mp3</t>
         </is>
       </c>
-      <c r="J10" s="80" t="inlineStr">
+      <c r="J10" s="83" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K10" s="80" t="n"/>
-      <c r="L10" s="80" t="n"/>
-      <c r="M10" s="80" t="inlineStr">
+      <c r="K10" s="83" t="n"/>
+      <c r="L10" s="83" t="n"/>
+      <c r="M10" s="83" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N10" s="81" t="n"/>
-      <c r="O10" s="81" t="n"/>
-      <c r="P10" s="81" t="inlineStr">
+      <c r="N10" s="84" t="n"/>
+      <c r="O10" s="84" t="n"/>
+      <c r="P10" s="84" t="inlineStr">
         <is>
           <t>2026-10-13 17:19</t>
         </is>
@@ -3158,22 +3167,22 @@
       </c>
     </row>
     <row r="12" ht="58.05" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="87" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="87" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="87" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="44" t="inlineStr">
         <is>
           <t>荷物 預け
 コインロッカー
@@ -3183,29 +3192,36 @@
 荷物 置き</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>この駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>せせらぎ公園駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
+        </is>
+      </c>
+      <c r="F12" s="44" t="n"/>
+      <c r="G12" s="87" t="n"/>
+      <c r="H12" s="87" t="n"/>
+      <c r="I12" s="87" t="inlineStr">
         <is>
           <t>luggage_deai.mp3</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="87" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K12" s="11" t="n"/>
-      <c r="L12" s="11" t="n"/>
-      <c r="M12" s="14" t="inlineStr">
+      <c r="K12" s="87" t="n"/>
+      <c r="L12" s="87" t="n"/>
+      <c r="M12" s="87" t="inlineStr">
         <is>
           <t>luggage</t>
+        </is>
+      </c>
+      <c r="N12" s="88" t="n"/>
+      <c r="O12" s="88" t="n"/>
+      <c r="P12" s="88" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:21</t>
         </is>
       </c>
     </row>
@@ -4906,17 +4922,17 @@
       </c>
     </row>
     <row r="43" ht="249.6" customHeight="1">
-      <c r="A43" s="80" t="inlineStr">
+      <c r="A43" s="83" t="inlineStr">
         <is>
           <t>guesthouse_access_deai</t>
         </is>
       </c>
-      <c r="B43" s="80" t="inlineStr">
+      <c r="B43" s="83" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C43" s="80" t="inlineStr">
+      <c r="C43" s="83" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -4950,30 +4966,30 @@
           <t>その建物は鳩谷八幡神社方面にあります。国道は交通量が多いため、川沿いの道をおすすめしております。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G43" s="80" t="inlineStr">
+      <c r="G43" s="83" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H43" s="80" t="n"/>
-      <c r="I43" s="80" t="inlineStr">
+      <c r="H43" s="83" t="n"/>
+      <c r="I43" s="83" t="inlineStr">
         <is>
           <t>guesthouse_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J43" s="80" t="inlineStr">
+      <c r="J43" s="83" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K43" s="80" t="n"/>
-      <c r="L43" s="80" t="n"/>
-      <c r="M43" s="80" t="inlineStr">
+      <c r="K43" s="83" t="n"/>
+      <c r="L43" s="83" t="n"/>
+      <c r="M43" s="83" t="inlineStr">
         <is>
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="81" t="n"/>
+      <c r="N43" s="84" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -6162,17 +6178,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="81" t="inlineStr">
+      <c r="A66" s="84" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="81" t="inlineStr">
+      <c r="B66" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="81" t="inlineStr">
+      <c r="C66" s="84" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -6202,26 +6218,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="81" t="inlineStr">
+      <c r="G66" s="84" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="81" t="n"/>
-      <c r="I66" s="81" t="inlineStr">
+      <c r="H66" s="84" t="n"/>
+      <c r="I66" s="84" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="81" t="inlineStr">
+      <c r="J66" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="81" t="n"/>
-      <c r="L66" s="81" t="n"/>
-      <c r="M66" s="81" t="n"/>
-      <c r="N66" s="81" t="n"/>
+      <c r="K66" s="84" t="n"/>
+      <c r="L66" s="84" t="n"/>
+      <c r="M66" s="84" t="n"/>
+      <c r="N66" s="84" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -7430,12 +7446,12 @@
       </c>
     </row>
     <row r="22" ht="64.8" customHeight="1">
-      <c r="A22" s="81" t="inlineStr">
+      <c r="A22" s="84" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B22" s="81" t="inlineStr">
+      <c r="B22" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7466,12 +7482,12 @@
       </c>
     </row>
     <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="81" t="inlineStr">
+      <c r="A23" s="84" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B23" s="81" t="inlineStr">
+      <c r="B23" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7502,12 +7518,12 @@
       </c>
     </row>
     <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="81" t="inlineStr">
+      <c r="A24" s="84" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B24" s="81" t="inlineStr">
+      <c r="B24" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7538,12 +7554,12 @@
       </c>
     </row>
     <row r="25" ht="81" customHeight="1">
-      <c r="A25" s="81" t="inlineStr">
+      <c r="A25" s="84" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B25" s="81" t="inlineStr">
+      <c r="B25" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7610,12 +7626,12 @@
       </c>
     </row>
     <row r="27" ht="64.8" customHeight="1">
-      <c r="A27" s="78" t="inlineStr">
+      <c r="A27" s="85" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B27" s="78" t="inlineStr">
+      <c r="B27" s="85" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7646,12 +7662,12 @@
       </c>
     </row>
     <row r="28" ht="64.8" customHeight="1">
-      <c r="A28" s="78" t="inlineStr">
+      <c r="A28" s="85" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B28" s="78" t="inlineStr">
+      <c r="B28" s="85" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7682,12 +7698,12 @@
       </c>
     </row>
     <row r="29" ht="64.8" customHeight="1">
-      <c r="A29" s="78" t="inlineStr">
+      <c r="A29" s="85" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B29" s="78" t="inlineStr">
+      <c r="B29" s="85" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7718,12 +7734,12 @@
       </c>
     </row>
     <row r="30" ht="81" customHeight="1">
-      <c r="A30" s="78" t="inlineStr">
+      <c r="A30" s="85" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B30" s="78" t="inlineStr">
+      <c r="B30" s="85" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7754,12 +7770,12 @@
       </c>
     </row>
     <row r="31" ht="64.8" customHeight="1">
-      <c r="A31" s="79" t="inlineStr">
+      <c r="A31" s="86" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B31" s="79" t="inlineStr">
+      <c r="B31" s="86" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -7951,12 +7967,12 @@
       </c>
     </row>
     <row r="37" ht="64.8" customHeight="1">
-      <c r="A37" s="78" t="inlineStr">
+      <c r="A37" s="85" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B37" s="78" t="inlineStr">
+      <c r="B37" s="85" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7987,12 +8003,12 @@
       </c>
     </row>
     <row r="38" ht="64.8" customHeight="1">
-      <c r="A38" s="78" t="inlineStr">
+      <c r="A38" s="85" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B38" s="78" t="inlineStr">
+      <c r="B38" s="85" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8023,12 +8039,12 @@
       </c>
     </row>
     <row r="39" ht="64.8" customHeight="1">
-      <c r="A39" s="78" t="inlineStr">
+      <c r="A39" s="85" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B39" s="78" t="inlineStr">
+      <c r="B39" s="85" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8059,12 +8075,12 @@
       </c>
     </row>
     <row r="40" ht="113.4" customHeight="1">
-      <c r="A40" s="78" t="inlineStr">
+      <c r="A40" s="85" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B40" s="78" t="inlineStr">
+      <c r="B40" s="85" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8095,12 +8111,12 @@
       </c>
     </row>
     <row r="41" ht="97.2" customHeight="1">
-      <c r="A41" s="79" t="inlineStr">
+      <c r="A41" s="86" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B41" s="79" t="inlineStr">
+      <c r="B41" s="86" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8131,12 +8147,12 @@
       </c>
     </row>
     <row r="42" ht="64.8" customHeight="1">
-      <c r="A42" s="81" t="inlineStr">
+      <c r="A42" s="84" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B42" s="81" t="inlineStr">
+      <c r="B42" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8167,12 +8183,12 @@
       </c>
     </row>
     <row r="43" ht="64.8" customHeight="1">
-      <c r="A43" s="81" t="inlineStr">
+      <c r="A43" s="84" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B43" s="81" t="inlineStr">
+      <c r="B43" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8203,12 +8219,12 @@
       </c>
     </row>
     <row r="44" ht="81" customHeight="1">
-      <c r="A44" s="81" t="inlineStr">
+      <c r="A44" s="84" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B44" s="81" t="inlineStr">
+      <c r="B44" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8239,12 +8255,12 @@
       </c>
     </row>
     <row r="45" ht="64.8" customHeight="1">
-      <c r="A45" s="81" t="inlineStr">
+      <c r="A45" s="84" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B45" s="81" t="inlineStr">
+      <c r="B45" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8491,32 +8507,35 @@
       </c>
     </row>
     <row r="52" ht="48.6" customHeight="1">
-      <c r="A52" s="21" t="inlineStr">
+      <c r="A52" s="88" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B52" s="21" t="inlineStr">
+      <c r="B52" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="C52" s="22" t="inlineStr">
-        <is>
-          <t>luggage
-baggage
-coin locker
-locker
-suitcase
-leave bag</t>
-        </is>
-      </c>
-      <c r="D52" s="22" t="inlineStr">
-        <is>
-          <t>There are no coin lockers at this parking lot or nearby. There are coin lockers at the Bus Terminal.</t>
-        </is>
-      </c>
-      <c r="E52" s="21" t="n"/>
+      <c r="C52" s="46" t="inlineStr">
+        <is>
+          <t>luggage storage locker
+coin locker baggage
+where suitcase storage
+left luggage facility
+store bag backpack</t>
+        </is>
+      </c>
+      <c r="D52" s="46" t="inlineStr">
+        <is>
+          <t>There are no coin lockers at Seseragi Park Car Park or in the nearby area. However, coin lockers are available at the bus terminal.</t>
+        </is>
+      </c>
+      <c r="E52" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: せせらぎ公園駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
+        </is>
+      </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
           <t>この駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
@@ -8524,32 +8543,35 @@
       </c>
     </row>
     <row r="53" ht="97.2" customHeight="1">
-      <c r="A53" s="21" t="inlineStr">
+      <c r="A53" s="88" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B53" s="21" t="inlineStr">
+      <c r="B53" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="C53" s="22" t="inlineStr">
-        <is>
-          <t>taquilla
-consigna
-equipaje
-maleta
-dejar bolsa
-locker</t>
-        </is>
-      </c>
-      <c r="D53" s="22" t="inlineStr">
-        <is>
-          <t>No hay taquillas de monedas en este estacionamiento ni en los alrededores. Sí las hay en la Terminal de Autobuses.</t>
-        </is>
-      </c>
-      <c r="E53" s="21" t="n"/>
+      <c r="C53" s="46" t="inlineStr">
+        <is>
+          <t>almacenamiento equipaje
+taquilla moneda
+guardar maleta
+consigna equipaje
+dejar mochila</t>
+        </is>
+      </c>
+      <c r="D53" s="46" t="inlineStr">
+        <is>
+          <t>No hay taquillas de monedas en el aparcamiento de Seseragi Park ni en las áreas cercanas. Sin embargo, las taquillas de monedas están disponibles en la terminal de autobuses.</t>
+        </is>
+      </c>
+      <c r="E53" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: せせらぎ公園駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
+        </is>
+      </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
           <t>この駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
@@ -8557,32 +8579,35 @@
       </c>
     </row>
     <row r="54" ht="97.2" customHeight="1">
-      <c r="A54" s="21" t="inlineStr">
+      <c r="A54" s="88" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B54" s="21" t="inlineStr">
+      <c r="B54" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="C54" s="22" t="inlineStr">
-        <is>
-          <t>consigne
-casier
-bagage
-valise
-déposer bagage
-laisser valise</t>
-        </is>
-      </c>
-      <c r="D54" s="22" t="inlineStr">
-        <is>
-          <t>Il n'y a pas de consignes automatiques sur ce parking ni aux alentours. Il y en a au terminal de bus.</t>
-        </is>
-      </c>
-      <c r="E54" s="21" t="n"/>
+      <c r="C54" s="46" t="inlineStr">
+        <is>
+          <t>rangement bagages
+casier à pièces
+consigne valise
+stockage bagage
+laisser sac</t>
+        </is>
+      </c>
+      <c r="D54" s="46" t="inlineStr">
+        <is>
+          <t>Il n'y a pas de casiers à pièces au parking de Seseragi Park ni dans les zones environnantes. Cependant, des casiers à pièces sont disponibles à la gare routière.</t>
+        </is>
+      </c>
+      <c r="E54" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: せせらぎ公園駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
+        </is>
+      </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
           <t>この駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
@@ -8590,32 +8615,35 @@
       </c>
     </row>
     <row r="55" ht="97.2" customHeight="1">
-      <c r="A55" s="21" t="inlineStr">
+      <c r="A55" s="88" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B55" s="21" t="inlineStr">
+      <c r="B55" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="C55" s="22" t="inlineStr">
-        <is>
-          <t>짐 맡기
-짐 맡길
-짐 보관
-코인로커
-사물함
-캐리어</t>
-        </is>
-      </c>
-      <c r="D55" s="22" t="inlineStr">
-        <is>
-          <t>이 주차장과 주변에는 코인로커가 없습니다. 버스터미널에는 있습니다.</t>
-        </is>
-      </c>
-      <c r="E55" s="21" t="n"/>
+      <c r="C55" s="46" t="inlineStr">
+        <is>
+          <t>짐 보관
+동전 보관함
+짐 맡기
+수하물 보관
+짐 두기</t>
+        </is>
+      </c>
+      <c r="D55" s="46" t="inlineStr">
+        <is>
+          <t>세세라기 공원 주차장 및 인근 지역에는 동전 보관함이 없습니다. 다만 버스 터미널에는 동전 보관함이 있습니다.</t>
+        </is>
+      </c>
+      <c r="E55" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: せせらぎ公園駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
+        </is>
+      </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
           <t>この駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
@@ -8623,32 +8651,35 @@
       </c>
     </row>
     <row r="56" ht="97.2" customHeight="1">
-      <c r="A56" s="24" t="inlineStr">
+      <c r="A56" s="89" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B56" s="24" t="inlineStr">
+      <c r="B56" s="89" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C56" s="25" t="inlineStr">
-        <is>
-          <t>寄存 行李
+      <c r="C56" s="69" t="inlineStr">
+        <is>
+          <t>行李 存放
+投币柜
 储物柜
-寄存柜
 行李箱
-行李 放哪
-存包</t>
-        </is>
-      </c>
-      <c r="D56" s="25" t="inlineStr">
-        <is>
-          <t>这个停车场及附近没有投币储物柜。巴士总站有储物柜。</t>
-        </is>
-      </c>
-      <c r="E56" s="24" t="n"/>
+放 包</t>
+        </is>
+      </c>
+      <c r="D56" s="69" t="inlineStr">
+        <is>
+          <t>在瀬瀬らぎ公园停车场及周边地区没有投币柜。不过，巴士总站有投币柜可供使用。</t>
+        </is>
+      </c>
+      <c r="E56" s="69" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: せせらぎ公園駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
+        </is>
+      </c>
       <c r="F56" s="26" t="inlineStr">
         <is>
           <t>この駐車場や近隣にコインロッカーはございません。バスターミナルにはございます。</t>
@@ -16795,12 +16826,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="81" t="inlineStr">
+      <c r="A302" s="84" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="81" t="inlineStr">
+      <c r="B302" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16826,12 +16857,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="81" t="inlineStr">
+      <c r="A303" s="84" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="81" t="inlineStr">
+      <c r="B303" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16857,12 +16888,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="81" t="inlineStr">
+      <c r="A304" s="84" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="81" t="inlineStr">
+      <c r="B304" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16888,12 +16919,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="81" t="inlineStr">
+      <c r="A305" s="84" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="81" t="inlineStr">
+      <c r="B305" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16919,12 +16950,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="81" t="inlineStr">
+      <c r="A306" s="84" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="81" t="inlineStr">
+      <c r="B306" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -16950,12 +16981,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="81" t="inlineStr">
+      <c r="A307" s="84" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="81" t="inlineStr">
+      <c r="B307" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16981,12 +17012,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="81" t="inlineStr">
+      <c r="A308" s="84" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="81" t="inlineStr">
+      <c r="B308" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17012,12 +17043,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="81" t="inlineStr">
+      <c r="A309" s="84" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="81" t="inlineStr">
+      <c r="B309" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17043,12 +17074,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="81" t="inlineStr">
+      <c r="A310" s="84" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="81" t="inlineStr">
+      <c r="B310" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17074,12 +17105,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="81" t="inlineStr">
+      <c r="A311" s="84" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="81" t="inlineStr">
+      <c r="B311" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17105,12 +17136,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="81" t="inlineStr">
+      <c r="A312" s="84" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="81" t="inlineStr">
+      <c r="B312" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17135,12 +17166,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="81" t="inlineStr">
+      <c r="A313" s="84" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="81" t="inlineStr">
+      <c r="B313" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17165,12 +17196,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="81" t="inlineStr">
+      <c r="A314" s="84" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="81" t="inlineStr">
+      <c r="B314" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17195,12 +17226,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="81" t="inlineStr">
+      <c r="A315" s="84" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="81" t="inlineStr">
+      <c r="B315" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17225,12 +17256,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="81" t="inlineStr">
+      <c r="A316" s="84" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="81" t="inlineStr">
+      <c r="B316" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17255,12 +17286,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="81" t="inlineStr">
+      <c r="A317" s="84" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="81" t="inlineStr">
+      <c r="B317" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17286,12 +17317,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="81" t="inlineStr">
+      <c r="A318" s="84" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="81" t="inlineStr">
+      <c r="B318" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17317,12 +17348,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="81" t="inlineStr">
+      <c r="A319" s="84" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="81" t="inlineStr">
+      <c r="B319" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17348,12 +17379,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="81" t="inlineStr">
+      <c r="A320" s="84" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="81" t="inlineStr">
+      <c r="B320" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17379,12 +17410,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="81" t="inlineStr">
+      <c r="A321" s="84" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="81" t="inlineStr">
+      <c r="B321" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17410,12 +17441,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="81" t="inlineStr">
+      <c r="A322" s="84" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="81" t="inlineStr">
+      <c r="B322" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17440,12 +17471,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="81" t="inlineStr">
+      <c r="A323" s="84" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="81" t="inlineStr">
+      <c r="B323" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17470,12 +17501,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="81" t="inlineStr">
+      <c r="A324" s="84" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="81" t="inlineStr">
+      <c r="B324" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17500,12 +17531,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="81" t="inlineStr">
+      <c r="A325" s="84" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="81" t="inlineStr">
+      <c r="B325" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17530,12 +17561,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="81" t="inlineStr">
+      <c r="A326" s="84" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="81" t="inlineStr">
+      <c r="B326" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17560,12 +17591,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="81" t="inlineStr">
+      <c r="A327" s="84" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="81" t="inlineStr">
+      <c r="B327" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17592,12 +17623,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="81" t="inlineStr">
+      <c r="A328" s="84" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="81" t="inlineStr">
+      <c r="B328" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17624,12 +17655,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="81" t="inlineStr">
+      <c r="A329" s="84" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="81" t="inlineStr">
+      <c r="B329" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17656,12 +17687,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="81" t="inlineStr">
+      <c r="A330" s="84" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="81" t="inlineStr">
+      <c r="B330" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17688,12 +17719,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="81" t="inlineStr">
+      <c r="A331" s="84" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="81" t="inlineStr">
+      <c r="B331" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17720,12 +17751,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="81" t="inlineStr">
+      <c r="A332" s="84" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="81" t="inlineStr">
+      <c r="B332" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17752,12 +17783,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="81" t="inlineStr">
+      <c r="A333" s="84" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="81" t="inlineStr">
+      <c r="B333" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17784,12 +17815,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="81" t="inlineStr">
+      <c r="A334" s="84" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="81" t="inlineStr">
+      <c r="B334" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17816,12 +17847,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="81" t="inlineStr">
+      <c r="A335" s="84" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="81" t="inlineStr">
+      <c r="B335" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17848,12 +17879,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="81" t="inlineStr">
+      <c r="A336" s="84" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="81" t="inlineStr">
+      <c r="B336" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17880,12 +17911,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="81" t="inlineStr">
+      <c r="A337" s="84" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="81" t="inlineStr">
+      <c r="B337" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17912,12 +17943,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="81" t="inlineStr">
+      <c r="A338" s="84" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="81" t="inlineStr">
+      <c r="B338" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17944,12 +17975,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="81" t="inlineStr">
+      <c r="A339" s="84" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="81" t="inlineStr">
+      <c r="B339" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17976,12 +18007,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="81" t="inlineStr">
+      <c r="A340" s="84" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="81" t="inlineStr">
+      <c r="B340" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18008,12 +18039,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="81" t="inlineStr">
+      <c r="A341" s="84" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="81" t="inlineStr">
+      <c r="B341" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18040,12 +18071,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="81" t="inlineStr">
+      <c r="A342" s="84" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="81" t="inlineStr">
+      <c r="B342" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18072,12 +18103,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="81" t="inlineStr">
+      <c r="A343" s="84" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="81" t="inlineStr">
+      <c r="B343" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18104,12 +18135,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="81" t="inlineStr">
+      <c r="A344" s="84" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="81" t="inlineStr">
+      <c r="B344" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18136,12 +18167,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="81" t="inlineStr">
+      <c r="A345" s="84" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="81" t="inlineStr">
+      <c r="B345" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18168,12 +18199,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="81" t="inlineStr">
+      <c r="A346" s="84" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="81" t="inlineStr">
+      <c r="B346" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18200,12 +18231,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="81" t="inlineStr">
+      <c r="A347" s="84" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="81" t="inlineStr">
+      <c r="B347" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18232,12 +18263,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="81" t="inlineStr">
+      <c r="A348" s="84" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="81" t="inlineStr">
+      <c r="B348" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18264,12 +18295,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="81" t="inlineStr">
+      <c r="A349" s="84" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="81" t="inlineStr">
+      <c r="B349" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18296,12 +18327,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="81" t="inlineStr">
+      <c r="A350" s="84" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="81" t="inlineStr">
+      <c r="B350" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18328,12 +18359,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="81" t="inlineStr">
+      <c r="A351" s="84" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="81" t="inlineStr">
+      <c r="B351" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18360,12 +18391,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="81" t="inlineStr">
+      <c r="A352" s="84" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="81" t="inlineStr">
+      <c r="B352" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18391,12 +18422,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="81" t="inlineStr">
+      <c r="A353" s="84" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="81" t="inlineStr">
+      <c r="B353" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18422,12 +18453,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="81" t="inlineStr">
+      <c r="A354" s="84" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="81" t="inlineStr">
+      <c r="B354" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18453,12 +18484,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="81" t="inlineStr">
+      <c r="A355" s="84" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="81" t="inlineStr">
+      <c r="B355" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18484,12 +18515,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="81" t="inlineStr">
+      <c r="A356" s="84" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="81" t="inlineStr">
+      <c r="B356" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18515,12 +18546,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="81" t="inlineStr">
+      <c r="A357" s="84" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="81" t="inlineStr">
+      <c r="B357" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18546,12 +18577,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="81" t="inlineStr">
+      <c r="A358" s="84" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="81" t="inlineStr">
+      <c r="B358" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18577,12 +18608,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="81" t="inlineStr">
+      <c r="A359" s="84" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="81" t="inlineStr">
+      <c r="B359" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18608,12 +18639,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="81" t="inlineStr">
+      <c r="A360" s="84" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="81" t="inlineStr">
+      <c r="B360" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18639,12 +18670,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="81" t="inlineStr">
+      <c r="A361" s="84" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="81" t="inlineStr">
+      <c r="B361" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18670,12 +18701,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="81" t="inlineStr">
+      <c r="A362" s="84" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="81" t="inlineStr">
+      <c r="B362" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18702,12 +18733,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="81" t="inlineStr">
+      <c r="A363" s="84" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="81" t="inlineStr">
+      <c r="B363" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18734,12 +18765,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="81" t="inlineStr">
+      <c r="A364" s="84" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="81" t="inlineStr">
+      <c r="B364" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18766,12 +18797,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="81" t="inlineStr">
+      <c r="A365" s="84" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="81" t="inlineStr">
+      <c r="B365" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18798,12 +18829,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="81" t="inlineStr">
+      <c r="A366" s="84" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="81" t="inlineStr">
+      <c r="B366" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18830,12 +18861,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="81" t="inlineStr">
+      <c r="A367" s="84" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="81" t="inlineStr">
+      <c r="B367" s="84" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18862,12 +18893,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="81" t="inlineStr">
+      <c r="A368" s="84" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="81" t="inlineStr">
+      <c r="B368" s="84" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18894,12 +18925,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="81" t="inlineStr">
+      <c r="A369" s="84" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="81" t="inlineStr">
+      <c r="B369" s="84" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18926,12 +18957,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="81" t="inlineStr">
+      <c r="A370" s="84" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="81" t="inlineStr">
+      <c r="B370" s="84" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18958,12 +18989,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="81" t="inlineStr">
+      <c r="A371" s="84" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="81" t="inlineStr">
+      <c r="B371" s="84" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -20099,7 +20130,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="81" t="inlineStr">
+      <c r="A2" s="84" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -20109,7 +20140,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="81" t="inlineStr">
+      <c r="C2" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20121,7 +20152,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="81" t="inlineStr">
+      <c r="A3" s="84" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -20131,7 +20162,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="81" t="inlineStr">
+      <c r="C3" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20143,7 +20174,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="81" t="inlineStr">
+      <c r="A4" s="84" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -20153,7 +20184,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="81" t="inlineStr">
+      <c r="C4" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20165,7 +20196,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="81" t="inlineStr">
+      <c r="A5" s="84" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -20175,7 +20206,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="81" t="inlineStr">
+      <c r="C5" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20187,7 +20218,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="81" t="inlineStr">
+      <c r="A6" s="84" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20197,7 +20228,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="81" t="inlineStr">
+      <c r="C6" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20209,7 +20240,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="81" t="inlineStr">
+      <c r="A7" s="84" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20219,7 +20250,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="81" t="inlineStr">
+      <c r="C7" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20231,7 +20262,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="81" t="inlineStr">
+      <c r="A8" s="84" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20241,7 +20272,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="81" t="inlineStr">
+      <c r="C8" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20253,7 +20284,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="81" t="inlineStr">
+      <c r="A9" s="84" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20263,7 +20294,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="81" t="inlineStr">
+      <c r="C9" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20275,7 +20306,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="81" t="inlineStr">
+      <c r="A10" s="84" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20285,7 +20316,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="81" t="inlineStr">
+      <c r="C10" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20297,7 +20328,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="81" t="inlineStr">
+      <c r="A11" s="84" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20307,7 +20338,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="81" t="inlineStr">
+      <c r="C11" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20319,7 +20350,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="81" t="inlineStr">
+      <c r="A12" s="84" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20329,7 +20360,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="81" t="inlineStr">
+      <c r="C12" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20341,7 +20372,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="81" t="inlineStr">
+      <c r="A13" s="84" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20351,7 +20382,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="81" t="inlineStr">
+      <c r="C13" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20493,53 +20524,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="81" t="inlineStr">
+      <c r="A2" s="84" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="81" t="inlineStr">
+      <c r="B2" s="84" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="81" t="inlineStr">
+      <c r="C2" s="84" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="81" t="inlineStr">
+      <c r="D2" s="84" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="81" t="inlineStr">
+      <c r="E2" s="84" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="81" t="inlineStr">
+      <c r="F2" s="84" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="81" t="inlineStr">
+      <c r="G2" s="84" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="81" t="inlineStr">
+      <c r="H2" s="84" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="81" t="inlineStr">
+      <c r="I2" s="84" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="81" t="n"/>
-      <c r="K2" s="81" t="inlineStr">
+      <c r="J2" s="84" t="n"/>
+      <c r="K2" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20576,45 +20607,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="81" t="inlineStr">
+      <c r="A3" s="84" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="81" t="inlineStr">
+      <c r="B3" s="84" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="81" t="inlineStr">
+      <c r="C3" s="84" t="inlineStr">
         <is>
           <t>main_idle_20261013044809.png</t>
         </is>
       </c>
-      <c r="D3" s="81" t="n"/>
-      <c r="E3" s="81" t="n"/>
-      <c r="F3" s="81" t="n">
+      <c r="D3" s="84" t="n"/>
+      <c r="E3" s="84" t="n"/>
+      <c r="F3" s="84" t="n">
         <v>0.179</v>
       </c>
-      <c r="G3" s="81" t="n">
+      <c r="G3" s="84" t="n">
         <v>0.23</v>
       </c>
-      <c r="H3" s="81" t="inlineStr">
+      <c r="H3" s="84" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="81" t="inlineStr">
+      <c r="I3" s="84" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="81" t="inlineStr">
+      <c r="J3" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="81" t="inlineStr">
+      <c r="K3" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20651,45 +20682,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="81" t="inlineStr">
+      <c r="A4" s="84" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="81" t="inlineStr">
+      <c r="B4" s="84" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="81" t="inlineStr">
+      <c r="C4" s="84" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="81" t="n"/>
-      <c r="E4" s="81" t="n"/>
-      <c r="F4" s="81" t="inlineStr">
+      <c r="D4" s="84" t="n"/>
+      <c r="E4" s="84" t="n"/>
+      <c r="F4" s="84" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="81" t="inlineStr">
+      <c r="G4" s="84" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="81" t="inlineStr">
+      <c r="H4" s="84" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="81" t="inlineStr">
+      <c r="I4" s="84" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="81" t="n"/>
-      <c r="K4" s="81" t="inlineStr">
+      <c r="J4" s="84" t="n"/>
+      <c r="K4" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20726,45 +20757,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="81" t="inlineStr">
+      <c r="A5" s="84" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="81" t="inlineStr">
+      <c r="B5" s="84" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="81" t="inlineStr">
+      <c r="C5" s="84" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="81" t="n"/>
-      <c r="E5" s="81" t="n"/>
-      <c r="F5" s="81" t="inlineStr">
+      <c r="D5" s="84" t="n"/>
+      <c r="E5" s="84" t="n"/>
+      <c r="F5" s="84" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="81" t="inlineStr">
+      <c r="G5" s="84" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="81" t="inlineStr">
+      <c r="H5" s="84" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="81" t="inlineStr">
+      <c r="I5" s="84" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="81" t="n"/>
-      <c r="K5" s="81" t="inlineStr">
+      <c r="J5" s="84" t="n"/>
+      <c r="K5" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20801,45 +20832,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="81" t="inlineStr">
+      <c r="A6" s="84" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="81" t="inlineStr">
+      <c r="B6" s="84" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="81" t="inlineStr">
+      <c r="C6" s="84" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="81" t="n"/>
-      <c r="E6" s="81" t="n"/>
-      <c r="F6" s="81" t="inlineStr">
+      <c r="D6" s="84" t="n"/>
+      <c r="E6" s="84" t="n"/>
+      <c r="F6" s="84" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="81" t="inlineStr">
+      <c r="G6" s="84" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="81" t="inlineStr">
+      <c r="H6" s="84" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="81" t="inlineStr">
+      <c r="I6" s="84" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="81" t="n"/>
-      <c r="K6" s="81" t="inlineStr">
+      <c r="J6" s="84" t="n"/>
+      <c r="K6" s="84" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20961,12 +20992,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="81" t="inlineStr">
+      <c r="A2" s="84" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B2" s="81" t="inlineStr">
+      <c r="B2" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21005,12 +21036,12 @@
       <c r="J2" s="46" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="81" t="inlineStr">
+      <c r="A3" s="84" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B3" s="81" t="inlineStr">
+      <c r="B3" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21049,12 +21080,12 @@
       <c r="J3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="81" t="inlineStr">
+      <c r="A4" s="84" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B4" s="81" t="inlineStr">
+      <c r="B4" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21093,12 +21124,12 @@
       <c r="J4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="81" t="inlineStr">
+      <c r="A5" s="84" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B5" s="81" t="inlineStr">
+      <c r="B5" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21137,12 +21168,12 @@
       <c r="J5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="81" t="inlineStr">
+      <c r="A6" s="84" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B6" s="81" t="inlineStr">
+      <c r="B6" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21181,12 +21212,12 @@
       <c r="J6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="81" t="inlineStr">
+      <c r="A7" s="84" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B7" s="81" t="inlineStr">
+      <c r="B7" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21225,12 +21256,12 @@
       <c r="J7" s="46" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="81" t="inlineStr">
+      <c r="A8" s="84" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B8" s="81" t="inlineStr">
+      <c r="B8" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21269,12 +21300,12 @@
       <c r="J8" s="46" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="81" t="inlineStr">
+      <c r="A9" s="84" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B9" s="81" t="inlineStr">
+      <c r="B9" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21313,12 +21344,12 @@
       <c r="J9" s="46" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="81" t="inlineStr">
+      <c r="A10" s="84" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B10" s="81" t="inlineStr">
+      <c r="B10" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21357,12 +21388,12 @@
       <c r="J10" s="46" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="81" t="inlineStr">
+      <c r="A11" s="84" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B11" s="81" t="inlineStr">
+      <c r="B11" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21401,12 +21432,12 @@
       <c r="J11" s="46" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="81" t="inlineStr">
+      <c r="A12" s="84" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B12" s="81" t="inlineStr">
+      <c r="B12" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21445,12 +21476,12 @@
       <c r="J12" s="46" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="81" t="inlineStr">
+      <c r="A13" s="84" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B13" s="81" t="inlineStr">
+      <c r="B13" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21508,12 +21539,12 @@
       <c r="J13" s="46" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="81" t="inlineStr">
+      <c r="A14" s="84" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B14" s="81" t="inlineStr">
+      <c r="B14" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21571,12 +21602,12 @@
       <c r="J14" s="46" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="81" t="inlineStr">
+      <c r="A15" s="84" t="inlineStr">
         <is>
           <t>趣味</t>
         </is>
       </c>
-      <c r="B15" s="81" t="inlineStr">
+      <c r="B15" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21637,12 +21668,12 @@
       <c r="J15" s="46" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="81" t="inlineStr">
+      <c r="A16" s="84" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B16" s="81" t="inlineStr">
+      <c r="B16" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21702,12 +21733,12 @@
       <c r="J16" s="46" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="81" t="inlineStr">
+      <c r="A17" s="84" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B17" s="81" t="inlineStr">
+      <c r="B17" s="84" t="inlineStr">
         <is>
           <t>共通</t>
         </is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -507,6 +507,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1218,7 +1227,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="84" t="inlineStr">
+      <c r="A2" s="88" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1228,31 +1237,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="84" t="n">
+      <c r="C2" s="88" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="84" t="n">
+      <c r="D2" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="84" t="n">
+      <c r="E2" s="88" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="84" t="n">
+      <c r="F2" s="88" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="84" t="n">
+      <c r="G2" s="88" t="n">
         <v>0.957</v>
       </c>
-      <c r="H2" s="84" t="n">
+      <c r="H2" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="84" t="n">
+      <c r="I2" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="84" t="n">
+      <c r="J2" s="88" t="n">
         <v>0.864</v>
       </c>
-      <c r="K2" s="84" t="n">
+      <c r="K2" s="88" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1262,7 +1271,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="84" t="inlineStr">
+      <c r="A3" s="88" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1272,31 +1281,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="84" t="n">
+      <c r="C3" s="88" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="84" t="n">
+      <c r="D3" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="84" t="n">
+      <c r="E3" s="88" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="84" t="n">
+      <c r="F3" s="88" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="84" t="n">
+      <c r="G3" s="88" t="n">
         <v>0.929</v>
       </c>
-      <c r="H3" s="84" t="n">
+      <c r="H3" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="84" t="n">
+      <c r="I3" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="84" t="n">
+      <c r="J3" s="88" t="n">
         <v>0.753</v>
       </c>
-      <c r="K3" s="84" t="n">
+      <c r="K3" s="88" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1306,7 +1315,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="84" t="inlineStr">
+      <c r="A4" s="88" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1316,31 +1325,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="84" t="n">
+      <c r="C4" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="84" t="n">
+      <c r="D4" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="84" t="n">
+      <c r="E4" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="84" t="n">
+      <c r="F4" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="84" t="n">
+      <c r="G4" s="88" t="n">
         <v>0.92</v>
       </c>
-      <c r="H4" s="84" t="n">
+      <c r="H4" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="84" t="n">
+      <c r="I4" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="84" t="n">
+      <c r="J4" s="88" t="n">
         <v>0.884</v>
       </c>
-      <c r="K4" s="84" t="n">
+      <c r="K4" s="88" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1412,7 +1421,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="84" t="inlineStr">
+      <c r="A2" s="88" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1422,10 +1431,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="84" t="n">
+      <c r="C2" s="88" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="84" t="n">
+      <c r="D2" s="88" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1435,7 +1444,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="84" t="inlineStr">
+      <c r="A3" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1445,16 +1454,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="84" t="n">
+      <c r="C3" s="88" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="84" t="n">
+      <c r="D3" s="88" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="84" t="inlineStr">
+      <c r="A4" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1464,16 +1473,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="84" t="n">
+      <c r="C4" s="88" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="84" t="n">
+      <c r="D4" s="88" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="84" t="inlineStr">
+      <c r="A5" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1483,16 +1492,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="84" t="n">
+      <c r="C5" s="88" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="84" t="n">
+      <c r="D5" s="88" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="84" t="inlineStr">
+      <c r="A6" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1502,16 +1511,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="84" t="n">
+      <c r="C6" s="88" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="84" t="n">
+      <c r="D6" s="88" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="84" t="inlineStr">
+      <c r="A7" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1521,10 +1530,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="84" t="n">
+      <c r="C7" s="88" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="84" t="n">
+      <c r="D7" s="88" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1584,17 +1593,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="84" t="inlineStr">
+      <c r="A2" s="88" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="84" t="inlineStr">
+      <c r="B2" s="88" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="84" t="inlineStr">
+      <c r="C2" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1606,17 +1615,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="84" t="inlineStr">
+      <c r="A3" s="88" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="84" t="inlineStr">
+      <c r="B3" s="88" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="84" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1624,17 +1633,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="84" t="inlineStr">
+      <c r="A4" s="88" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="84" t="inlineStr">
+      <c r="B4" s="88" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="84" t="inlineStr">
+      <c r="C4" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1646,17 +1655,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="84" t="inlineStr">
+      <c r="A5" s="88" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="84" t="inlineStr">
+      <c r="B5" s="88" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="84" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1668,17 +1677,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="84" t="inlineStr">
+      <c r="A6" s="88" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="84" t="inlineStr">
+      <c r="B6" s="88" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="84" t="inlineStr">
+      <c r="C6" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1686,17 +1695,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="84" t="inlineStr">
+      <c r="A7" s="88" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="84" t="inlineStr">
+      <c r="B7" s="88" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="84" t="inlineStr">
+      <c r="C7" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1704,17 +1713,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="84" t="inlineStr">
+      <c r="A8" s="88" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="84" t="inlineStr">
+      <c r="B8" s="88" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="84" t="inlineStr">
+      <c r="C8" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1726,17 +1735,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="84" t="inlineStr">
+      <c r="A9" s="88" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="84" t="inlineStr">
+      <c r="B9" s="88" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="84" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1748,17 +1757,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="84" t="inlineStr">
+      <c r="A10" s="88" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="84" t="inlineStr">
+      <c r="B10" s="88" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="84" t="inlineStr">
+      <c r="C10" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1770,17 +1779,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="84" t="inlineStr">
+      <c r="A11" s="88" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="84" t="inlineStr">
+      <c r="B11" s="88" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="84" t="inlineStr">
+      <c r="C11" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1788,17 +1797,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="84" t="inlineStr">
+      <c r="A12" s="88" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="84" t="inlineStr">
+      <c r="B12" s="88" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="84" t="inlineStr">
+      <c r="C12" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1806,17 +1815,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="84" t="inlineStr">
+      <c r="A13" s="88" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="84" t="inlineStr">
+      <c r="B13" s="88" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="84" t="inlineStr">
+      <c r="C13" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1828,17 +1837,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="84" t="inlineStr">
+      <c r="A14" s="88" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="84" t="inlineStr">
+      <c r="B14" s="88" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="84" t="inlineStr">
+      <c r="C14" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1850,17 +1859,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="84" t="inlineStr">
+      <c r="A15" s="88" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="84" t="inlineStr">
+      <c r="B15" s="88" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="84" t="inlineStr">
+      <c r="C15" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1872,17 +1881,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="84" t="inlineStr">
+      <c r="A16" s="88" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="84" t="inlineStr">
+      <c r="B16" s="88" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="84" t="inlineStr">
+      <c r="C16" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1894,17 +1903,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="84" t="inlineStr">
+      <c r="A17" s="88" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="84" t="inlineStr">
+      <c r="B17" s="88" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="84" t="inlineStr">
+      <c r="C17" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1916,17 +1925,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="84" t="inlineStr">
+      <c r="A18" s="88" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="84" t="inlineStr">
+      <c r="B18" s="88" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="84" t="inlineStr">
+      <c r="C18" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1938,17 +1947,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="84" t="inlineStr">
+      <c r="A19" s="88" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="84" t="inlineStr">
+      <c r="B19" s="88" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="84" t="inlineStr">
+      <c r="C19" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1956,17 +1965,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="84" t="inlineStr">
+      <c r="A20" s="88" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="84" t="inlineStr">
+      <c r="B20" s="88" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="84" t="inlineStr">
+      <c r="C20" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1974,17 +1983,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="84" t="inlineStr">
+      <c r="A21" s="88" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="84" t="inlineStr">
+      <c r="B21" s="88" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="84" t="inlineStr">
+      <c r="C21" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1996,17 +2005,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="84" t="inlineStr">
+      <c r="A22" s="88" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="84" t="inlineStr">
+      <c r="B22" s="88" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="84" t="inlineStr">
+      <c r="C22" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2018,17 +2027,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="84" t="inlineStr">
+      <c r="A23" s="88" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="84" t="inlineStr">
+      <c r="B23" s="88" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="84" t="inlineStr">
+      <c r="C23" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2040,17 +2049,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="84" t="inlineStr">
+      <c r="A24" s="88" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="84" t="inlineStr">
+      <c r="B24" s="88" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="84" t="inlineStr">
+      <c r="C24" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2062,17 +2071,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="84" t="inlineStr">
+      <c r="A25" s="88" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="84" t="inlineStr">
+      <c r="B25" s="88" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="84" t="inlineStr">
+      <c r="C25" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2080,17 +2089,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="84" t="inlineStr">
+      <c r="A26" s="88" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="84" t="inlineStr">
+      <c r="B26" s="88" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="84" t="inlineStr">
+      <c r="C26" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2098,17 +2107,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="84" t="inlineStr">
+      <c r="A27" s="88" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="84" t="inlineStr">
+      <c r="B27" s="88" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="84" t="inlineStr">
+      <c r="C27" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2120,17 +2129,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="84" t="inlineStr">
+      <c r="A28" s="88" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="84" t="inlineStr">
+      <c r="B28" s="88" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="84" t="inlineStr">
+      <c r="C28" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2142,17 +2151,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="84" t="inlineStr">
+      <c r="A29" s="88" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="84" t="inlineStr">
+      <c r="B29" s="88" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="84" t="inlineStr">
+      <c r="C29" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2164,17 +2173,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="84" t="inlineStr">
+      <c r="A30" s="88" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="84" t="inlineStr">
+      <c r="B30" s="88" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="84" t="inlineStr">
+      <c r="C30" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2182,17 +2191,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="84" t="inlineStr">
+      <c r="A31" s="88" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="84" t="inlineStr">
+      <c r="B31" s="88" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="84" t="inlineStr">
+      <c r="C31" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2204,17 +2213,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="84" t="inlineStr">
+      <c r="A32" s="88" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="84" t="inlineStr">
+      <c r="B32" s="88" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="84" t="inlineStr">
+      <c r="C32" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2222,17 +2231,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="84" t="inlineStr">
+      <c r="A33" s="88" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="84" t="inlineStr">
+      <c r="B33" s="88" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="84" t="inlineStr">
+      <c r="C33" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2240,17 +2249,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="84" t="inlineStr">
+      <c r="A34" s="88" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="84" t="inlineStr">
+      <c r="B34" s="88" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="84" t="inlineStr">
+      <c r="C34" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2258,17 +2267,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="84" t="inlineStr">
+      <c r="A35" s="88" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="84" t="inlineStr">
+      <c r="B35" s="88" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="84" t="inlineStr">
+      <c r="C35" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2276,17 +2285,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="84" t="inlineStr">
+      <c r="A36" s="88" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="84" t="inlineStr">
+      <c r="B36" s="88" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="84" t="inlineStr">
+      <c r="C36" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2294,17 +2303,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="84" t="inlineStr">
+      <c r="A37" s="88" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="84" t="inlineStr">
+      <c r="B37" s="88" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="84" t="inlineStr">
+      <c r="C37" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2312,17 +2321,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="84" t="inlineStr">
+      <c r="A38" s="88" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="84" t="inlineStr">
+      <c r="B38" s="88" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="84" t="inlineStr">
+      <c r="C38" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2330,17 +2339,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="84" t="inlineStr">
+      <c r="A39" s="88" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="84" t="inlineStr">
+      <c r="B39" s="88" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="84" t="inlineStr">
+      <c r="C39" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2348,17 +2357,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="84" t="inlineStr">
+      <c r="A40" s="88" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="84" t="inlineStr">
+      <c r="B40" s="88" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="84" t="inlineStr">
+      <c r="C40" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2370,17 +2379,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="84" t="inlineStr">
+      <c r="A41" s="88" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="84" t="inlineStr">
+      <c r="B41" s="88" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="84" t="inlineStr">
+      <c r="C41" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2388,17 +2397,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="84" t="inlineStr">
+      <c r="A42" s="88" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="84" t="inlineStr">
+      <c r="B42" s="88" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="84" t="inlineStr">
+      <c r="C42" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2410,17 +2419,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="84" t="inlineStr">
+      <c r="A43" s="88" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="84" t="inlineStr">
+      <c r="B43" s="88" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="84" t="inlineStr">
+      <c r="C43" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2428,17 +2437,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="84" t="inlineStr">
+      <c r="A44" s="88" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="84" t="inlineStr">
+      <c r="B44" s="88" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="84" t="inlineStr">
+      <c r="C44" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2450,17 +2459,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="84" t="inlineStr">
+      <c r="A45" s="88" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="84" t="inlineStr">
+      <c r="B45" s="88" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="84" t="inlineStr">
+      <c r="C45" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2809,17 +2818,17 @@
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="83" t="inlineStr">
+      <c r="A6" s="87" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B6" s="83" t="inlineStr">
+      <c r="B6" s="87" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C6" s="83" t="inlineStr">
+      <c r="C6" s="87" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2844,49 +2853,49 @@
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
         </is>
       </c>
-      <c r="G6" s="83" t="n"/>
-      <c r="H6" s="83" t="n"/>
-      <c r="I6" s="83" t="inlineStr">
+      <c r="G6" s="87" t="n"/>
+      <c r="H6" s="87" t="n"/>
+      <c r="I6" s="87" t="inlineStr">
         <is>
           <t>atm_bt.mp3</t>
         </is>
       </c>
-      <c r="J6" s="83" t="inlineStr">
+      <c r="J6" s="87" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K6" s="83" t="n"/>
-      <c r="L6" s="83" t="n"/>
-      <c r="M6" s="83" t="inlineStr">
+      <c r="K6" s="87" t="n"/>
+      <c r="L6" s="87" t="n"/>
+      <c r="M6" s="87" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N6" s="84" t="inlineStr">
+      <c r="N6" s="88" t="inlineStr">
         <is>
           <t>ATMはどこ</t>
         </is>
       </c>
-      <c r="O6" s="84" t="n"/>
-      <c r="P6" s="84" t="inlineStr">
+      <c r="O6" s="88" t="n"/>
+      <c r="P6" s="88" t="inlineStr">
         <is>
           <t>2026-10-13 17:14</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="83" t="inlineStr">
+      <c r="A7" s="87" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B7" s="83" t="inlineStr">
+      <c r="B7" s="87" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C7" s="83" t="inlineStr">
+      <c r="C7" s="87" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2911,28 +2920,28 @@
           <t>海外のカードは鳩谷郵便局のATM、日本のカードは和田家前のJAのATMをご利用ください。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G7" s="83" t="n"/>
-      <c r="H7" s="83" t="n"/>
-      <c r="I7" s="83" t="inlineStr">
+      <c r="G7" s="87" t="n"/>
+      <c r="H7" s="87" t="n"/>
+      <c r="I7" s="87" t="inlineStr">
         <is>
           <t>atm_deai.mp3</t>
         </is>
       </c>
-      <c r="J7" s="83" t="inlineStr">
+      <c r="J7" s="87" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K7" s="83" t="n"/>
-      <c r="L7" s="83" t="n"/>
-      <c r="M7" s="83" t="inlineStr">
+      <c r="K7" s="87" t="n"/>
+      <c r="L7" s="87" t="n"/>
+      <c r="M7" s="87" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N7" s="84" t="n"/>
-      <c r="O7" s="84" t="n"/>
-      <c r="P7" s="84" t="inlineStr">
+      <c r="N7" s="88" t="n"/>
+      <c r="O7" s="88" t="n"/>
+      <c r="P7" s="88" t="inlineStr">
         <is>
           <t>2026-10-13 17:15</t>
         </is>
@@ -2988,17 +2997,17 @@
       </c>
     </row>
     <row r="9" ht="58.05" customHeight="1">
-      <c r="A9" s="83" t="inlineStr">
+      <c r="A9" s="87" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B9" s="83" t="inlineStr">
+      <c r="B9" s="87" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C9" s="83" t="inlineStr">
+      <c r="C9" s="87" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3018,45 +3027,45 @@
         </is>
       </c>
       <c r="F9" s="44" t="n"/>
-      <c r="G9" s="83" t="n"/>
-      <c r="H9" s="83" t="n"/>
-      <c r="I9" s="83" t="inlineStr">
+      <c r="G9" s="87" t="n"/>
+      <c r="H9" s="87" t="n"/>
+      <c r="I9" s="87" t="inlineStr">
         <is>
           <t>currency_exchange_bt.mp3</t>
         </is>
       </c>
-      <c r="J9" s="83" t="inlineStr">
+      <c r="J9" s="87" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K9" s="83" t="n"/>
-      <c r="L9" s="83" t="n"/>
-      <c r="M9" s="83" t="inlineStr">
+      <c r="K9" s="87" t="n"/>
+      <c r="L9" s="87" t="n"/>
+      <c r="M9" s="87" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N9" s="84" t="n"/>
-      <c r="O9" s="84" t="n"/>
-      <c r="P9" s="84" t="inlineStr">
+      <c r="N9" s="88" t="n"/>
+      <c r="O9" s="88" t="n"/>
+      <c r="P9" s="88" t="inlineStr">
         <is>
           <t>2026-10-13 17:18</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58.05" customHeight="1">
-      <c r="A10" s="83" t="inlineStr">
+      <c r="A10" s="87" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B10" s="83" t="inlineStr">
+      <c r="B10" s="87" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C10" s="83" t="inlineStr">
+      <c r="C10" s="87" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3076,45 +3085,45 @@
         </is>
       </c>
       <c r="F10" s="44" t="n"/>
-      <c r="G10" s="83" t="n"/>
-      <c r="H10" s="83" t="n"/>
-      <c r="I10" s="83" t="inlineStr">
+      <c r="G10" s="87" t="n"/>
+      <c r="H10" s="87" t="n"/>
+      <c r="I10" s="87" t="inlineStr">
         <is>
           <t>currency_exchange_deai.mp3</t>
         </is>
       </c>
-      <c r="J10" s="83" t="inlineStr">
+      <c r="J10" s="87" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K10" s="83" t="n"/>
-      <c r="L10" s="83" t="n"/>
-      <c r="M10" s="83" t="inlineStr">
+      <c r="K10" s="87" t="n"/>
+      <c r="L10" s="87" t="n"/>
+      <c r="M10" s="87" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N10" s="84" t="n"/>
-      <c r="O10" s="84" t="n"/>
-      <c r="P10" s="84" t="inlineStr">
+      <c r="N10" s="88" t="n"/>
+      <c r="O10" s="88" t="n"/>
+      <c r="P10" s="88" t="inlineStr">
         <is>
           <t>2026-10-13 17:19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58.05" customHeight="1">
-      <c r="A11" s="83" t="inlineStr">
+      <c r="A11" s="87" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B11" s="83" t="inlineStr">
+      <c r="B11" s="87" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C11" s="83" t="inlineStr">
+      <c r="C11" s="87" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3135,32 +3144,32 @@
         </is>
       </c>
       <c r="F11" s="44" t="n"/>
-      <c r="G11" s="83" t="n"/>
-      <c r="H11" s="83" t="n"/>
-      <c r="I11" s="83" t="inlineStr">
+      <c r="G11" s="87" t="n"/>
+      <c r="H11" s="87" t="n"/>
+      <c r="I11" s="87" t="inlineStr">
         <is>
           <t>luggage_bt.mp3</t>
         </is>
       </c>
-      <c r="J11" s="83" t="inlineStr">
+      <c r="J11" s="87" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K11" s="83" t="n"/>
-      <c r="L11" s="83" t="n"/>
-      <c r="M11" s="83" t="inlineStr">
+      <c r="K11" s="87" t="n"/>
+      <c r="L11" s="87" t="n"/>
+      <c r="M11" s="87" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N11" s="84" t="inlineStr">
+      <c r="N11" s="88" t="inlineStr">
         <is>
           <t>荷物を預けたい</t>
         </is>
       </c>
-      <c r="O11" s="84" t="n"/>
-      <c r="P11" s="84" t="inlineStr">
+      <c r="O11" s="88" t="n"/>
+      <c r="P11" s="88" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
@@ -3282,22 +3291,22 @@
       </c>
     </row>
     <row r="14" ht="58.05" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="90" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="90" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="90" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="44" t="inlineStr">
         <is>
           <t>スタンプ
 記念 スタンプ
@@ -3306,29 +3315,36 @@
 スタンプ ある</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>スタンプは机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="E14" s="44" t="inlineStr">
+        <is>
+          <t>スタンプは白川郷バスターミナル内の机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
+        </is>
+      </c>
+      <c r="F14" s="44" t="n"/>
+      <c r="G14" s="90" t="n"/>
+      <c r="H14" s="90" t="n"/>
+      <c r="I14" s="90" t="inlineStr">
         <is>
           <t>stamp_bt.mp3</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J14" s="90" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K14" s="11" t="n"/>
-      <c r="L14" s="11" t="n"/>
-      <c r="M14" s="14" t="inlineStr">
+      <c r="K14" s="90" t="n"/>
+      <c r="L14" s="90" t="n"/>
+      <c r="M14" s="90" t="inlineStr">
         <is>
           <t>stamp</t>
+        </is>
+      </c>
+      <c r="N14" s="91" t="n"/>
+      <c r="O14" s="91" t="n"/>
+      <c r="P14" s="91" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:22</t>
         </is>
       </c>
     </row>
@@ -4922,17 +4938,17 @@
       </c>
     </row>
     <row r="43" ht="249.6" customHeight="1">
-      <c r="A43" s="83" t="inlineStr">
+      <c r="A43" s="87" t="inlineStr">
         <is>
           <t>guesthouse_access_deai</t>
         </is>
       </c>
-      <c r="B43" s="83" t="inlineStr">
+      <c r="B43" s="87" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C43" s="83" t="inlineStr">
+      <c r="C43" s="87" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -4966,30 +4982,30 @@
           <t>その建物は鳩谷八幡神社方面にあります。国道は交通量が多いため、川沿いの道をおすすめしております。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G43" s="83" t="inlineStr">
+      <c r="G43" s="87" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H43" s="83" t="n"/>
-      <c r="I43" s="83" t="inlineStr">
+      <c r="H43" s="87" t="n"/>
+      <c r="I43" s="87" t="inlineStr">
         <is>
           <t>guesthouse_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J43" s="83" t="inlineStr">
+      <c r="J43" s="87" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K43" s="83" t="n"/>
-      <c r="L43" s="83" t="n"/>
-      <c r="M43" s="83" t="inlineStr">
+      <c r="K43" s="87" t="n"/>
+      <c r="L43" s="87" t="n"/>
+      <c r="M43" s="87" t="inlineStr">
         <is>
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="84" t="n"/>
+      <c r="N43" s="88" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -6178,17 +6194,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="84" t="inlineStr">
+      <c r="A66" s="88" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="84" t="inlineStr">
+      <c r="B66" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="84" t="inlineStr">
+      <c r="C66" s="88" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -6218,26 +6234,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="84" t="inlineStr">
+      <c r="G66" s="88" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="84" t="n"/>
-      <c r="I66" s="84" t="inlineStr">
+      <c r="H66" s="88" t="n"/>
+      <c r="I66" s="88" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="84" t="inlineStr">
+      <c r="J66" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="84" t="n"/>
-      <c r="L66" s="84" t="n"/>
-      <c r="M66" s="84" t="n"/>
-      <c r="N66" s="84" t="n"/>
+      <c r="K66" s="88" t="n"/>
+      <c r="L66" s="88" t="n"/>
+      <c r="M66" s="88" t="n"/>
+      <c r="N66" s="88" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -7446,12 +7462,12 @@
       </c>
     </row>
     <row r="22" ht="64.8" customHeight="1">
-      <c r="A22" s="84" t="inlineStr">
+      <c r="A22" s="88" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B22" s="84" t="inlineStr">
+      <c r="B22" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7482,12 +7498,12 @@
       </c>
     </row>
     <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="84" t="inlineStr">
+      <c r="A23" s="88" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B23" s="84" t="inlineStr">
+      <c r="B23" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7518,12 +7534,12 @@
       </c>
     </row>
     <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="84" t="inlineStr">
+      <c r="A24" s="88" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B24" s="84" t="inlineStr">
+      <c r="B24" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7554,12 +7570,12 @@
       </c>
     </row>
     <row r="25" ht="81" customHeight="1">
-      <c r="A25" s="84" t="inlineStr">
+      <c r="A25" s="88" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B25" s="84" t="inlineStr">
+      <c r="B25" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7590,12 +7606,12 @@
       </c>
     </row>
     <row r="26" ht="64.8" customHeight="1">
-      <c r="A26" s="82" t="inlineStr">
+      <c r="A26" s="89" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B26" s="82" t="inlineStr">
+      <c r="B26" s="89" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8147,12 +8163,12 @@
       </c>
     </row>
     <row r="42" ht="64.8" customHeight="1">
-      <c r="A42" s="84" t="inlineStr">
+      <c r="A42" s="88" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B42" s="84" t="inlineStr">
+      <c r="B42" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8183,12 +8199,12 @@
       </c>
     </row>
     <row r="43" ht="64.8" customHeight="1">
-      <c r="A43" s="84" t="inlineStr">
+      <c r="A43" s="88" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B43" s="84" t="inlineStr">
+      <c r="B43" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8219,12 +8235,12 @@
       </c>
     </row>
     <row r="44" ht="81" customHeight="1">
-      <c r="A44" s="84" t="inlineStr">
+      <c r="A44" s="88" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B44" s="84" t="inlineStr">
+      <c r="B44" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8255,12 +8271,12 @@
       </c>
     </row>
     <row r="45" ht="64.8" customHeight="1">
-      <c r="A45" s="84" t="inlineStr">
+      <c r="A45" s="88" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B45" s="84" t="inlineStr">
+      <c r="B45" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8291,12 +8307,12 @@
       </c>
     </row>
     <row r="46" ht="64.8" customHeight="1">
-      <c r="A46" s="82" t="inlineStr">
+      <c r="A46" s="89" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B46" s="82" t="inlineStr">
+      <c r="B46" s="89" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8851,31 +8867,35 @@
       </c>
     </row>
     <row r="62" ht="81" customHeight="1">
-      <c r="A62" s="21" t="inlineStr">
+      <c r="A62" s="91" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B62" s="21" t="inlineStr">
+      <c r="B62" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="C62" s="22" t="inlineStr">
+      <c r="C62" s="46" t="inlineStr">
         <is>
           <t>stamp
 souvenir stamp
-goshuin
 postage stamp
-stamp book</t>
-        </is>
-      </c>
-      <c r="D62" s="22" t="inlineStr">
-        <is>
-          <t>Souvenir stamps are available on the table. Postage stamps are sold at the counter. We do not offer goshuin temple and shrine seals.</t>
-        </is>
-      </c>
-      <c r="E62" s="21" t="n"/>
+stamp available
+where stamp</t>
+        </is>
+      </c>
+      <c r="D62" s="46" t="inlineStr">
+        <is>
+          <t>Stamps are available on the desk inside Shirakawa-go Bus Terminal. Postage stamps are sold at the information desk. We do not offer religious seal stamps.</t>
+        </is>
+      </c>
+      <c r="E62" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: スタンプは白川郷バスターミナル内の机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
+        </is>
+      </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
           <t>スタンプは机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
@@ -8883,32 +8903,35 @@
       </c>
     </row>
     <row r="63" ht="97.2" customHeight="1">
-      <c r="A63" s="21" t="inlineStr">
+      <c r="A63" s="91" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B63" s="21" t="inlineStr">
+      <c r="B63" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="C63" s="22" t="inlineStr">
+      <c r="C63" s="46" t="inlineStr">
         <is>
           <t>sello
-sello recuerdo
-goshuin
+sello conmemorativo
 estampilla
-sello postal
-timbre</t>
-        </is>
-      </c>
-      <c r="D63" s="22" t="inlineStr">
-        <is>
-          <t>Los sellos de recuerdo están sobre la mesa. Los sellos postales se venden en el mostrador. No ofrecemos goshuin.</t>
-        </is>
-      </c>
-      <c r="E63" s="21" t="n"/>
+hay sellos
+dónde obtener sello</t>
+        </is>
+      </c>
+      <c r="D63" s="46" t="inlineStr">
+        <is>
+          <t>Los sellos conmemorativos están disponibles en la mesa dentro de la Terminal de Autobuses de Shirakawa-go. Las estampillas postales se venden en la ventanilla de información. No ofrecemos sellos religiosos.</t>
+        </is>
+      </c>
+      <c r="E63" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: スタンプは白川郷バスターミナル内の机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
+        </is>
+      </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
           <t>スタンプは机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
@@ -8916,32 +8939,35 @@
       </c>
     </row>
     <row r="64" ht="97.2" customHeight="1">
-      <c r="A64" s="21" t="inlineStr">
+      <c r="A64" s="91" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B64" s="21" t="inlineStr">
+      <c r="B64" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="C64" s="22" t="inlineStr">
-        <is>
-          <t>tampon
-tampon souvenir
-goshuin
-timbre
+      <c r="C64" s="46" t="inlineStr">
+        <is>
+          <t>timbre
+timbre souvenir
 cachet
-timbre poste</t>
-        </is>
-      </c>
-      <c r="D64" s="22" t="inlineStr">
-        <is>
-          <t>Les tampons sont à votre disposition sur la table. Les timbres sont vendus au guichet. Nous ne proposons pas de goshuin.</t>
-        </is>
-      </c>
-      <c r="E64" s="21" t="n"/>
+timbre disponible
+où trouver timbre</t>
+        </is>
+      </c>
+      <c r="D64" s="46" t="inlineStr">
+        <is>
+          <t>Les timbres de commémoration sont disponibles sur le bureau à l'intérieur de la gare routière de Shirakawa-go. Les timbres-poste sont vendus au guichet d'information. Nous n'offrons pas de cachets religieux.</t>
+        </is>
+      </c>
+      <c r="E64" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: スタンプは白川郷バスターミナル内の机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
+        </is>
+      </c>
       <c r="F64" s="23" t="inlineStr">
         <is>
           <t>スタンプは机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
@@ -8949,32 +8975,35 @@
       </c>
     </row>
     <row r="65" ht="97.2" customHeight="1">
-      <c r="A65" s="21" t="inlineStr">
+      <c r="A65" s="91" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B65" s="21" t="inlineStr">
+      <c r="B65" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="C65" s="22" t="inlineStr">
+      <c r="C65" s="46" t="inlineStr">
         <is>
           <t>스탬프
 기념 스탬프
-도장
 우표
-고슈인
-주인장</t>
-        </is>
-      </c>
-      <c r="D65" s="22" t="inlineStr">
-        <is>
-          <t>스탬프는 책상 위에 준비되어 있습니다. 우표는 창구에서 취급하고 있습니다. 고슈인은 해 드리지 않습니다.</t>
-        </is>
-      </c>
-      <c r="E65" s="21" t="n"/>
+스탬프 있다
+스탬프 구할 수 있다</t>
+        </is>
+      </c>
+      <c r="D65" s="46" t="inlineStr">
+        <is>
+          <t>스탬프는 白川郷 버스 터미널 내부의 책상 위에 준비되어 있습니다. 우표는 창구에서 판매하고 있습니다. 종교적 인장 서비스는 제공하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="E65" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: スタンプは白川郷バスターミナル内の机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
+        </is>
+      </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
           <t>スタンプは机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
@@ -8982,31 +9011,35 @@
       </c>
     </row>
     <row r="66" ht="81" customHeight="1">
-      <c r="A66" s="24" t="inlineStr">
+      <c r="A66" s="92" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B66" s="24" t="inlineStr">
+      <c r="B66" s="92" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C66" s="25" t="inlineStr">
-        <is>
-          <t>印章
-纪念章
-盖章
-御朱印
-邮票</t>
-        </is>
-      </c>
-      <c r="D66" s="25" t="inlineStr">
-        <is>
-          <t>纪念印章放在桌子上。邮票可以在窗口购买。本处不提供御朱印。</t>
-        </is>
-      </c>
-      <c r="E66" s="24" t="n"/>
+      <c r="C66" s="69" t="inlineStr">
+        <is>
+          <t>邮票
+纪念邮票
+印章
+有没有邮票
+邮票在哪里</t>
+        </is>
+      </c>
+      <c r="D66" s="69" t="inlineStr">
+        <is>
+          <t>纪念邮票放在白川乡巴士总站内的桌子上。邮票可以在窗口购买。我们不提供宗教印章服务。</t>
+        </is>
+      </c>
+      <c r="E66" s="69" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: スタンプは白川郷バスターミナル内の机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
+        </is>
+      </c>
       <c r="F66" s="26" t="inlineStr">
         <is>
           <t>スタンプは机の上にご用意しております。切手は窓口で取り扱っております。御朱印は行っておりません。</t>
@@ -16826,12 +16859,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="84" t="inlineStr">
+      <c r="A302" s="88" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="84" t="inlineStr">
+      <c r="B302" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16857,12 +16890,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="84" t="inlineStr">
+      <c r="A303" s="88" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="84" t="inlineStr">
+      <c r="B303" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16888,12 +16921,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="84" t="inlineStr">
+      <c r="A304" s="88" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="84" t="inlineStr">
+      <c r="B304" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16919,12 +16952,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="84" t="inlineStr">
+      <c r="A305" s="88" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="84" t="inlineStr">
+      <c r="B305" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16950,12 +16983,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="84" t="inlineStr">
+      <c r="A306" s="88" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="84" t="inlineStr">
+      <c r="B306" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -16981,12 +17014,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="84" t="inlineStr">
+      <c r="A307" s="88" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="84" t="inlineStr">
+      <c r="B307" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17012,12 +17045,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="84" t="inlineStr">
+      <c r="A308" s="88" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="84" t="inlineStr">
+      <c r="B308" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17043,12 +17076,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="84" t="inlineStr">
+      <c r="A309" s="88" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="84" t="inlineStr">
+      <c r="B309" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17074,12 +17107,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="84" t="inlineStr">
+      <c r="A310" s="88" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="84" t="inlineStr">
+      <c r="B310" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17105,12 +17138,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="84" t="inlineStr">
+      <c r="A311" s="88" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="84" t="inlineStr">
+      <c r="B311" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17136,12 +17169,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="84" t="inlineStr">
+      <c r="A312" s="88" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="84" t="inlineStr">
+      <c r="B312" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17166,12 +17199,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="84" t="inlineStr">
+      <c r="A313" s="88" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="84" t="inlineStr">
+      <c r="B313" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17196,12 +17229,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="84" t="inlineStr">
+      <c r="A314" s="88" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="84" t="inlineStr">
+      <c r="B314" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17226,12 +17259,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="84" t="inlineStr">
+      <c r="A315" s="88" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="84" t="inlineStr">
+      <c r="B315" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17256,12 +17289,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="84" t="inlineStr">
+      <c r="A316" s="88" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="84" t="inlineStr">
+      <c r="B316" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17286,12 +17319,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="84" t="inlineStr">
+      <c r="A317" s="88" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="84" t="inlineStr">
+      <c r="B317" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17317,12 +17350,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="84" t="inlineStr">
+      <c r="A318" s="88" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="84" t="inlineStr">
+      <c r="B318" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17348,12 +17381,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="84" t="inlineStr">
+      <c r="A319" s="88" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="84" t="inlineStr">
+      <c r="B319" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17379,12 +17412,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="84" t="inlineStr">
+      <c r="A320" s="88" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="84" t="inlineStr">
+      <c r="B320" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17410,12 +17443,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="84" t="inlineStr">
+      <c r="A321" s="88" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="84" t="inlineStr">
+      <c r="B321" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17441,12 +17474,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="84" t="inlineStr">
+      <c r="A322" s="88" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="84" t="inlineStr">
+      <c r="B322" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17471,12 +17504,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="84" t="inlineStr">
+      <c r="A323" s="88" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="84" t="inlineStr">
+      <c r="B323" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17501,12 +17534,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="84" t="inlineStr">
+      <c r="A324" s="88" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="84" t="inlineStr">
+      <c r="B324" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17531,12 +17564,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="84" t="inlineStr">
+      <c r="A325" s="88" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="84" t="inlineStr">
+      <c r="B325" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17561,12 +17594,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="84" t="inlineStr">
+      <c r="A326" s="88" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="84" t="inlineStr">
+      <c r="B326" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17591,12 +17624,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="84" t="inlineStr">
+      <c r="A327" s="88" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="84" t="inlineStr">
+      <c r="B327" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17623,12 +17656,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="84" t="inlineStr">
+      <c r="A328" s="88" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="84" t="inlineStr">
+      <c r="B328" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17655,12 +17688,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="84" t="inlineStr">
+      <c r="A329" s="88" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="84" t="inlineStr">
+      <c r="B329" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17687,12 +17720,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="84" t="inlineStr">
+      <c r="A330" s="88" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="84" t="inlineStr">
+      <c r="B330" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17719,12 +17752,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="84" t="inlineStr">
+      <c r="A331" s="88" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="84" t="inlineStr">
+      <c r="B331" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17751,12 +17784,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="84" t="inlineStr">
+      <c r="A332" s="88" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="84" t="inlineStr">
+      <c r="B332" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17783,12 +17816,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="84" t="inlineStr">
+      <c r="A333" s="88" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="84" t="inlineStr">
+      <c r="B333" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17815,12 +17848,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="84" t="inlineStr">
+      <c r="A334" s="88" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="84" t="inlineStr">
+      <c r="B334" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17847,12 +17880,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="84" t="inlineStr">
+      <c r="A335" s="88" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="84" t="inlineStr">
+      <c r="B335" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17879,12 +17912,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="84" t="inlineStr">
+      <c r="A336" s="88" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="84" t="inlineStr">
+      <c r="B336" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17911,12 +17944,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="84" t="inlineStr">
+      <c r="A337" s="88" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="84" t="inlineStr">
+      <c r="B337" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17943,12 +17976,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="84" t="inlineStr">
+      <c r="A338" s="88" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="84" t="inlineStr">
+      <c r="B338" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17975,12 +18008,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="84" t="inlineStr">
+      <c r="A339" s="88" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="84" t="inlineStr">
+      <c r="B339" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18007,12 +18040,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="84" t="inlineStr">
+      <c r="A340" s="88" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="84" t="inlineStr">
+      <c r="B340" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18039,12 +18072,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="84" t="inlineStr">
+      <c r="A341" s="88" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="84" t="inlineStr">
+      <c r="B341" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18071,12 +18104,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="84" t="inlineStr">
+      <c r="A342" s="88" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="84" t="inlineStr">
+      <c r="B342" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18103,12 +18136,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="84" t="inlineStr">
+      <c r="A343" s="88" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="84" t="inlineStr">
+      <c r="B343" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18135,12 +18168,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="84" t="inlineStr">
+      <c r="A344" s="88" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="84" t="inlineStr">
+      <c r="B344" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18167,12 +18200,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="84" t="inlineStr">
+      <c r="A345" s="88" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="84" t="inlineStr">
+      <c r="B345" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18199,12 +18232,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="84" t="inlineStr">
+      <c r="A346" s="88" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="84" t="inlineStr">
+      <c r="B346" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18231,12 +18264,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="84" t="inlineStr">
+      <c r="A347" s="88" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="84" t="inlineStr">
+      <c r="B347" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18263,12 +18296,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="84" t="inlineStr">
+      <c r="A348" s="88" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="84" t="inlineStr">
+      <c r="B348" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18295,12 +18328,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="84" t="inlineStr">
+      <c r="A349" s="88" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="84" t="inlineStr">
+      <c r="B349" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18327,12 +18360,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="84" t="inlineStr">
+      <c r="A350" s="88" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="84" t="inlineStr">
+      <c r="B350" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18359,12 +18392,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="84" t="inlineStr">
+      <c r="A351" s="88" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="84" t="inlineStr">
+      <c r="B351" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18391,12 +18424,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="84" t="inlineStr">
+      <c r="A352" s="88" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="84" t="inlineStr">
+      <c r="B352" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18422,12 +18455,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="84" t="inlineStr">
+      <c r="A353" s="88" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="84" t="inlineStr">
+      <c r="B353" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18453,12 +18486,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="84" t="inlineStr">
+      <c r="A354" s="88" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="84" t="inlineStr">
+      <c r="B354" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18484,12 +18517,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="84" t="inlineStr">
+      <c r="A355" s="88" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="84" t="inlineStr">
+      <c r="B355" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18515,12 +18548,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="84" t="inlineStr">
+      <c r="A356" s="88" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="84" t="inlineStr">
+      <c r="B356" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18546,12 +18579,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="84" t="inlineStr">
+      <c r="A357" s="88" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="84" t="inlineStr">
+      <c r="B357" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18577,12 +18610,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="84" t="inlineStr">
+      <c r="A358" s="88" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="84" t="inlineStr">
+      <c r="B358" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18608,12 +18641,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="84" t="inlineStr">
+      <c r="A359" s="88" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="84" t="inlineStr">
+      <c r="B359" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18639,12 +18672,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="84" t="inlineStr">
+      <c r="A360" s="88" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="84" t="inlineStr">
+      <c r="B360" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18670,12 +18703,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="84" t="inlineStr">
+      <c r="A361" s="88" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="84" t="inlineStr">
+      <c r="B361" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18701,12 +18734,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="84" t="inlineStr">
+      <c r="A362" s="88" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="84" t="inlineStr">
+      <c r="B362" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18733,12 +18766,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="84" t="inlineStr">
+      <c r="A363" s="88" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="84" t="inlineStr">
+      <c r="B363" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18765,12 +18798,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="84" t="inlineStr">
+      <c r="A364" s="88" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="84" t="inlineStr">
+      <c r="B364" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18797,12 +18830,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="84" t="inlineStr">
+      <c r="A365" s="88" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="84" t="inlineStr">
+      <c r="B365" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18829,12 +18862,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="84" t="inlineStr">
+      <c r="A366" s="88" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="84" t="inlineStr">
+      <c r="B366" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18861,12 +18894,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="84" t="inlineStr">
+      <c r="A367" s="88" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="84" t="inlineStr">
+      <c r="B367" s="88" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18893,12 +18926,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="84" t="inlineStr">
+      <c r="A368" s="88" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="84" t="inlineStr">
+      <c r="B368" s="88" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18925,12 +18958,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="84" t="inlineStr">
+      <c r="A369" s="88" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="84" t="inlineStr">
+      <c r="B369" s="88" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18957,12 +18990,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="84" t="inlineStr">
+      <c r="A370" s="88" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="84" t="inlineStr">
+      <c r="B370" s="88" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18989,12 +19022,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="84" t="inlineStr">
+      <c r="A371" s="88" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="84" t="inlineStr">
+      <c r="B371" s="88" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -20130,7 +20163,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="84" t="inlineStr">
+      <c r="A2" s="88" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -20140,7 +20173,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="84" t="inlineStr">
+      <c r="C2" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20152,7 +20185,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="84" t="inlineStr">
+      <c r="A3" s="88" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -20162,7 +20195,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="84" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20174,7 +20207,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="84" t="inlineStr">
+      <c r="A4" s="88" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -20184,7 +20217,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="84" t="inlineStr">
+      <c r="C4" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20196,7 +20229,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="84" t="inlineStr">
+      <c r="A5" s="88" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -20206,7 +20239,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="84" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20218,7 +20251,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="84" t="inlineStr">
+      <c r="A6" s="88" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20228,7 +20261,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="84" t="inlineStr">
+      <c r="C6" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20240,7 +20273,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="84" t="inlineStr">
+      <c r="A7" s="88" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20250,7 +20283,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="84" t="inlineStr">
+      <c r="C7" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20262,7 +20295,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="84" t="inlineStr">
+      <c r="A8" s="88" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20272,7 +20305,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="84" t="inlineStr">
+      <c r="C8" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20284,7 +20317,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="84" t="inlineStr">
+      <c r="A9" s="88" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20294,7 +20327,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="84" t="inlineStr">
+      <c r="C9" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20306,7 +20339,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="84" t="inlineStr">
+      <c r="A10" s="88" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20316,7 +20349,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="84" t="inlineStr">
+      <c r="C10" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20328,7 +20361,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="84" t="inlineStr">
+      <c r="A11" s="88" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20338,7 +20371,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="84" t="inlineStr">
+      <c r="C11" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20350,7 +20383,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="84" t="inlineStr">
+      <c r="A12" s="88" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20360,7 +20393,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="84" t="inlineStr">
+      <c r="C12" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20372,7 +20405,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="84" t="inlineStr">
+      <c r="A13" s="88" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20382,7 +20415,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="84" t="inlineStr">
+      <c r="C13" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20524,53 +20557,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="84" t="inlineStr">
+      <c r="A2" s="88" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="84" t="inlineStr">
+      <c r="B2" s="88" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="84" t="inlineStr">
+      <c r="C2" s="88" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="84" t="inlineStr">
+      <c r="D2" s="88" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="84" t="inlineStr">
+      <c r="E2" s="88" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="84" t="inlineStr">
+      <c r="F2" s="88" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="84" t="inlineStr">
+      <c r="G2" s="88" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="84" t="inlineStr">
+      <c r="H2" s="88" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="84" t="inlineStr">
+      <c r="I2" s="88" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="84" t="n"/>
-      <c r="K2" s="84" t="inlineStr">
+      <c r="J2" s="88" t="n"/>
+      <c r="K2" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20607,45 +20640,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="84" t="inlineStr">
+      <c r="A3" s="88" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="84" t="inlineStr">
+      <c r="B3" s="88" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="84" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
         <is>
           <t>main_idle_20261013044809.png</t>
         </is>
       </c>
-      <c r="D3" s="84" t="n"/>
-      <c r="E3" s="84" t="n"/>
-      <c r="F3" s="84" t="n">
+      <c r="D3" s="88" t="n"/>
+      <c r="E3" s="88" t="n"/>
+      <c r="F3" s="88" t="n">
         <v>0.179</v>
       </c>
-      <c r="G3" s="84" t="n">
+      <c r="G3" s="88" t="n">
         <v>0.23</v>
       </c>
-      <c r="H3" s="84" t="inlineStr">
+      <c r="H3" s="88" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="84" t="inlineStr">
+      <c r="I3" s="88" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="84" t="inlineStr">
+      <c r="J3" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="84" t="inlineStr">
+      <c r="K3" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20682,45 +20715,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="84" t="inlineStr">
+      <c r="A4" s="88" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="84" t="inlineStr">
+      <c r="B4" s="88" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="84" t="inlineStr">
+      <c r="C4" s="88" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="84" t="n"/>
-      <c r="E4" s="84" t="n"/>
-      <c r="F4" s="84" t="inlineStr">
+      <c r="D4" s="88" t="n"/>
+      <c r="E4" s="88" t="n"/>
+      <c r="F4" s="88" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="84" t="inlineStr">
+      <c r="G4" s="88" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="84" t="inlineStr">
+      <c r="H4" s="88" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="84" t="inlineStr">
+      <c r="I4" s="88" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="84" t="n"/>
-      <c r="K4" s="84" t="inlineStr">
+      <c r="J4" s="88" t="n"/>
+      <c r="K4" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20757,45 +20790,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="84" t="inlineStr">
+      <c r="A5" s="88" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="84" t="inlineStr">
+      <c r="B5" s="88" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="84" t="inlineStr">
+      <c r="C5" s="88" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="84" t="n"/>
-      <c r="E5" s="84" t="n"/>
-      <c r="F5" s="84" t="inlineStr">
+      <c r="D5" s="88" t="n"/>
+      <c r="E5" s="88" t="n"/>
+      <c r="F5" s="88" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="84" t="inlineStr">
+      <c r="G5" s="88" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="84" t="inlineStr">
+      <c r="H5" s="88" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="84" t="inlineStr">
+      <c r="I5" s="88" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="84" t="n"/>
-      <c r="K5" s="84" t="inlineStr">
+      <c r="J5" s="88" t="n"/>
+      <c r="K5" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20832,45 +20865,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="84" t="inlineStr">
+      <c r="A6" s="88" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="84" t="inlineStr">
+      <c r="B6" s="88" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="84" t="inlineStr">
+      <c r="C6" s="88" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="84" t="n"/>
-      <c r="E6" s="84" t="n"/>
-      <c r="F6" s="84" t="inlineStr">
+      <c r="D6" s="88" t="n"/>
+      <c r="E6" s="88" t="n"/>
+      <c r="F6" s="88" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="84" t="inlineStr">
+      <c r="G6" s="88" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="84" t="inlineStr">
+      <c r="H6" s="88" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="84" t="inlineStr">
+      <c r="I6" s="88" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="84" t="n"/>
-      <c r="K6" s="84" t="inlineStr">
+      <c r="J6" s="88" t="n"/>
+      <c r="K6" s="88" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20992,12 +21025,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="84" t="inlineStr">
+      <c r="A2" s="88" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B2" s="84" t="inlineStr">
+      <c r="B2" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21036,12 +21069,12 @@
       <c r="J2" s="46" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="84" t="inlineStr">
+      <c r="A3" s="88" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B3" s="84" t="inlineStr">
+      <c r="B3" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21080,12 +21113,12 @@
       <c r="J3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="84" t="inlineStr">
+      <c r="A4" s="88" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B4" s="84" t="inlineStr">
+      <c r="B4" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21124,12 +21157,12 @@
       <c r="J4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="84" t="inlineStr">
+      <c r="A5" s="88" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B5" s="84" t="inlineStr">
+      <c r="B5" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21168,12 +21201,12 @@
       <c r="J5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="84" t="inlineStr">
+      <c r="A6" s="88" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B6" s="84" t="inlineStr">
+      <c r="B6" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21212,12 +21245,12 @@
       <c r="J6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="84" t="inlineStr">
+      <c r="A7" s="88" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B7" s="84" t="inlineStr">
+      <c r="B7" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21256,12 +21289,12 @@
       <c r="J7" s="46" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="84" t="inlineStr">
+      <c r="A8" s="88" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B8" s="84" t="inlineStr">
+      <c r="B8" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21300,12 +21333,12 @@
       <c r="J8" s="46" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="84" t="inlineStr">
+      <c r="A9" s="88" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B9" s="84" t="inlineStr">
+      <c r="B9" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21344,12 +21377,12 @@
       <c r="J9" s="46" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="84" t="inlineStr">
+      <c r="A10" s="88" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B10" s="84" t="inlineStr">
+      <c r="B10" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21388,12 +21421,12 @@
       <c r="J10" s="46" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="84" t="inlineStr">
+      <c r="A11" s="88" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B11" s="84" t="inlineStr">
+      <c r="B11" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21432,12 +21465,12 @@
       <c r="J11" s="46" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="84" t="inlineStr">
+      <c r="A12" s="88" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B12" s="84" t="inlineStr">
+      <c r="B12" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21476,12 +21509,12 @@
       <c r="J12" s="46" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="84" t="inlineStr">
+      <c r="A13" s="88" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B13" s="84" t="inlineStr">
+      <c r="B13" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21539,12 +21572,12 @@
       <c r="J13" s="46" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="84" t="inlineStr">
+      <c r="A14" s="88" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B14" s="84" t="inlineStr">
+      <c r="B14" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21602,12 +21635,12 @@
       <c r="J14" s="46" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="84" t="inlineStr">
+      <c r="A15" s="88" t="inlineStr">
         <is>
           <t>趣味</t>
         </is>
       </c>
-      <c r="B15" s="84" t="inlineStr">
+      <c r="B15" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21668,12 +21701,12 @@
       <c r="J15" s="46" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="84" t="inlineStr">
+      <c r="A16" s="88" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B16" s="84" t="inlineStr">
+      <c r="B16" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21733,12 +21766,12 @@
       <c r="J16" s="46" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="84" t="inlineStr">
+      <c r="A17" s="88" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B17" s="84" t="inlineStr">
+      <c r="B17" s="88" t="inlineStr">
         <is>
           <t>共通</t>
         </is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -525,6 +525,18 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1227,7 +1239,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="88" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1237,31 +1249,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="88" t="n">
+      <c r="C2" s="91" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="88" t="n">
+      <c r="D2" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="88" t="n">
+      <c r="E2" s="91" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="88" t="n">
+      <c r="F2" s="91" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="88" t="n">
+      <c r="G2" s="91" t="n">
         <v>0.957</v>
       </c>
-      <c r="H2" s="88" t="n">
+      <c r="H2" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="88" t="n">
+      <c r="I2" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="88" t="n">
+      <c r="J2" s="91" t="n">
         <v>0.864</v>
       </c>
-      <c r="K2" s="88" t="n">
+      <c r="K2" s="91" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1271,7 +1283,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="88" t="inlineStr">
+      <c r="A3" s="91" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1281,31 +1293,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="88" t="n">
+      <c r="C3" s="91" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="88" t="n">
+      <c r="D3" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="88" t="n">
+      <c r="E3" s="91" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="88" t="n">
+      <c r="F3" s="91" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="88" t="n">
+      <c r="G3" s="91" t="n">
         <v>0.929</v>
       </c>
-      <c r="H3" s="88" t="n">
+      <c r="H3" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="88" t="n">
+      <c r="I3" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="88" t="n">
+      <c r="J3" s="91" t="n">
         <v>0.753</v>
       </c>
-      <c r="K3" s="88" t="n">
+      <c r="K3" s="91" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1315,7 +1327,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="88" t="inlineStr">
+      <c r="A4" s="91" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1325,31 +1337,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="88" t="n">
+      <c r="C4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="88" t="n">
+      <c r="D4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="88" t="n">
+      <c r="E4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="88" t="n">
+      <c r="F4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="88" t="n">
+      <c r="G4" s="91" t="n">
         <v>0.92</v>
       </c>
-      <c r="H4" s="88" t="n">
+      <c r="H4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="88" t="n">
+      <c r="I4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="88" t="n">
+      <c r="J4" s="91" t="n">
         <v>0.884</v>
       </c>
-      <c r="K4" s="88" t="n">
+      <c r="K4" s="91" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1421,7 +1433,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="88" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1431,10 +1443,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="88" t="n">
+      <c r="C2" s="91" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="88" t="n">
+      <c r="D2" s="91" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1444,7 +1456,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="88" t="inlineStr">
+      <c r="A3" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1454,16 +1466,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="88" t="n">
+      <c r="C3" s="91" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="88" t="n">
+      <c r="D3" s="91" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="88" t="inlineStr">
+      <c r="A4" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1473,16 +1485,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="88" t="n">
+      <c r="C4" s="91" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="88" t="n">
+      <c r="D4" s="91" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="88" t="inlineStr">
+      <c r="A5" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1492,16 +1504,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="88" t="n">
+      <c r="C5" s="91" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="88" t="n">
+      <c r="D5" s="91" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="88" t="inlineStr">
+      <c r="A6" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1511,16 +1523,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="88" t="n">
+      <c r="C6" s="91" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="88" t="n">
+      <c r="D6" s="91" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="88" t="inlineStr">
+      <c r="A7" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1530,10 +1542,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="88" t="n">
+      <c r="C7" s="91" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="88" t="n">
+      <c r="D7" s="91" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1593,17 +1605,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="88" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="88" t="inlineStr">
+      <c r="B2" s="91" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="88" t="inlineStr">
+      <c r="C2" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1615,17 +1627,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="88" t="inlineStr">
+      <c r="A3" s="91" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="88" t="inlineStr">
+      <c r="B3" s="91" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="88" t="inlineStr">
+      <c r="C3" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1633,17 +1645,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="88" t="inlineStr">
+      <c r="A4" s="91" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="88" t="inlineStr">
+      <c r="B4" s="91" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="88" t="inlineStr">
+      <c r="C4" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1655,17 +1667,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="88" t="inlineStr">
+      <c r="A5" s="91" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="88" t="inlineStr">
+      <c r="B5" s="91" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="88" t="inlineStr">
+      <c r="C5" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1677,17 +1689,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="88" t="inlineStr">
+      <c r="A6" s="91" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="88" t="inlineStr">
+      <c r="B6" s="91" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="88" t="inlineStr">
+      <c r="C6" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1695,17 +1707,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="88" t="inlineStr">
+      <c r="A7" s="91" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="88" t="inlineStr">
+      <c r="B7" s="91" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="88" t="inlineStr">
+      <c r="C7" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1713,17 +1725,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="88" t="inlineStr">
+      <c r="A8" s="91" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="88" t="inlineStr">
+      <c r="B8" s="91" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="88" t="inlineStr">
+      <c r="C8" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1735,17 +1747,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="88" t="inlineStr">
+      <c r="A9" s="91" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="88" t="inlineStr">
+      <c r="B9" s="91" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="88" t="inlineStr">
+      <c r="C9" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1757,17 +1769,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="88" t="inlineStr">
+      <c r="A10" s="91" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="88" t="inlineStr">
+      <c r="B10" s="91" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="88" t="inlineStr">
+      <c r="C10" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1779,17 +1791,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="88" t="inlineStr">
+      <c r="A11" s="91" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="88" t="inlineStr">
+      <c r="B11" s="91" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="88" t="inlineStr">
+      <c r="C11" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1797,17 +1809,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="88" t="inlineStr">
+      <c r="A12" s="91" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="88" t="inlineStr">
+      <c r="B12" s="91" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="88" t="inlineStr">
+      <c r="C12" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1815,17 +1827,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="88" t="inlineStr">
+      <c r="A13" s="91" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="88" t="inlineStr">
+      <c r="B13" s="91" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="88" t="inlineStr">
+      <c r="C13" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1837,17 +1849,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="88" t="inlineStr">
+      <c r="A14" s="91" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="88" t="inlineStr">
+      <c r="B14" s="91" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="88" t="inlineStr">
+      <c r="C14" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1859,17 +1871,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="88" t="inlineStr">
+      <c r="A15" s="91" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="88" t="inlineStr">
+      <c r="B15" s="91" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="88" t="inlineStr">
+      <c r="C15" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1881,17 +1893,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="88" t="inlineStr">
+      <c r="A16" s="91" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="88" t="inlineStr">
+      <c r="B16" s="91" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="88" t="inlineStr">
+      <c r="C16" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1903,17 +1915,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="88" t="inlineStr">
+      <c r="A17" s="91" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="88" t="inlineStr">
+      <c r="B17" s="91" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="88" t="inlineStr">
+      <c r="C17" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1925,17 +1937,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="88" t="inlineStr">
+      <c r="A18" s="91" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="88" t="inlineStr">
+      <c r="B18" s="91" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="88" t="inlineStr">
+      <c r="C18" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1947,17 +1959,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="88" t="inlineStr">
+      <c r="A19" s="91" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="88" t="inlineStr">
+      <c r="B19" s="91" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="88" t="inlineStr">
+      <c r="C19" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1965,17 +1977,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="88" t="inlineStr">
+      <c r="A20" s="91" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="88" t="inlineStr">
+      <c r="B20" s="91" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="88" t="inlineStr">
+      <c r="C20" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1983,17 +1995,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="88" t="inlineStr">
+      <c r="A21" s="91" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="88" t="inlineStr">
+      <c r="B21" s="91" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="88" t="inlineStr">
+      <c r="C21" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2005,17 +2017,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="88" t="inlineStr">
+      <c r="A22" s="91" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="88" t="inlineStr">
+      <c r="B22" s="91" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="88" t="inlineStr">
+      <c r="C22" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2027,17 +2039,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="88" t="inlineStr">
+      <c r="A23" s="91" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="88" t="inlineStr">
+      <c r="B23" s="91" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="88" t="inlineStr">
+      <c r="C23" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2049,17 +2061,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="88" t="inlineStr">
+      <c r="A24" s="91" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="88" t="inlineStr">
+      <c r="B24" s="91" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="88" t="inlineStr">
+      <c r="C24" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2071,17 +2083,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="88" t="inlineStr">
+      <c r="A25" s="91" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="88" t="inlineStr">
+      <c r="B25" s="91" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="88" t="inlineStr">
+      <c r="C25" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2089,17 +2101,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="88" t="inlineStr">
+      <c r="A26" s="91" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="88" t="inlineStr">
+      <c r="B26" s="91" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="88" t="inlineStr">
+      <c r="C26" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2107,17 +2119,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="88" t="inlineStr">
+      <c r="A27" s="91" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="88" t="inlineStr">
+      <c r="B27" s="91" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="88" t="inlineStr">
+      <c r="C27" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2129,17 +2141,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="88" t="inlineStr">
+      <c r="A28" s="91" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="88" t="inlineStr">
+      <c r="B28" s="91" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="88" t="inlineStr">
+      <c r="C28" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2151,17 +2163,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="88" t="inlineStr">
+      <c r="A29" s="91" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="88" t="inlineStr">
+      <c r="B29" s="91" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="88" t="inlineStr">
+      <c r="C29" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2173,17 +2185,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="88" t="inlineStr">
+      <c r="A30" s="91" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="88" t="inlineStr">
+      <c r="B30" s="91" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="88" t="inlineStr">
+      <c r="C30" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2191,17 +2203,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="88" t="inlineStr">
+      <c r="A31" s="91" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="88" t="inlineStr">
+      <c r="B31" s="91" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="88" t="inlineStr">
+      <c r="C31" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2213,17 +2225,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="88" t="inlineStr">
+      <c r="A32" s="91" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="88" t="inlineStr">
+      <c r="B32" s="91" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="88" t="inlineStr">
+      <c r="C32" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2231,17 +2243,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="88" t="inlineStr">
+      <c r="A33" s="91" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="88" t="inlineStr">
+      <c r="B33" s="91" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="88" t="inlineStr">
+      <c r="C33" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2249,17 +2261,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="88" t="inlineStr">
+      <c r="A34" s="91" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="88" t="inlineStr">
+      <c r="B34" s="91" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="88" t="inlineStr">
+      <c r="C34" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2267,17 +2279,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="88" t="inlineStr">
+      <c r="A35" s="91" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="88" t="inlineStr">
+      <c r="B35" s="91" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="88" t="inlineStr">
+      <c r="C35" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2285,17 +2297,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="88" t="inlineStr">
+      <c r="A36" s="91" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="88" t="inlineStr">
+      <c r="B36" s="91" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="88" t="inlineStr">
+      <c r="C36" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2303,17 +2315,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="88" t="inlineStr">
+      <c r="A37" s="91" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="88" t="inlineStr">
+      <c r="B37" s="91" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="88" t="inlineStr">
+      <c r="C37" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2321,17 +2333,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="88" t="inlineStr">
+      <c r="A38" s="91" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="88" t="inlineStr">
+      <c r="B38" s="91" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="88" t="inlineStr">
+      <c r="C38" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2339,17 +2351,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="88" t="inlineStr">
+      <c r="A39" s="91" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="88" t="inlineStr">
+      <c r="B39" s="91" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="88" t="inlineStr">
+      <c r="C39" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2357,17 +2369,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="88" t="inlineStr">
+      <c r="A40" s="91" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="88" t="inlineStr">
+      <c r="B40" s="91" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="88" t="inlineStr">
+      <c r="C40" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2379,17 +2391,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="88" t="inlineStr">
+      <c r="A41" s="91" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="88" t="inlineStr">
+      <c r="B41" s="91" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="88" t="inlineStr">
+      <c r="C41" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2397,17 +2409,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="88" t="inlineStr">
+      <c r="A42" s="91" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="88" t="inlineStr">
+      <c r="B42" s="91" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="88" t="inlineStr">
+      <c r="C42" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2419,17 +2431,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="88" t="inlineStr">
+      <c r="A43" s="91" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="88" t="inlineStr">
+      <c r="B43" s="91" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="88" t="inlineStr">
+      <c r="C43" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2437,17 +2449,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="88" t="inlineStr">
+      <c r="A44" s="91" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="88" t="inlineStr">
+      <c r="B44" s="91" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="88" t="inlineStr">
+      <c r="C44" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2459,17 +2471,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="88" t="inlineStr">
+      <c r="A45" s="91" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="88" t="inlineStr">
+      <c r="B45" s="91" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="88" t="inlineStr">
+      <c r="C45" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2818,17 +2830,17 @@
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="87" t="inlineStr">
+      <c r="A6" s="90" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B6" s="87" t="inlineStr">
+      <c r="B6" s="90" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C6" s="87" t="inlineStr">
+      <c r="C6" s="90" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2853,49 +2865,49 @@
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
         </is>
       </c>
-      <c r="G6" s="87" t="n"/>
-      <c r="H6" s="87" t="n"/>
-      <c r="I6" s="87" t="inlineStr">
+      <c r="G6" s="90" t="n"/>
+      <c r="H6" s="90" t="n"/>
+      <c r="I6" s="90" t="inlineStr">
         <is>
           <t>atm_bt.mp3</t>
         </is>
       </c>
-      <c r="J6" s="87" t="inlineStr">
+      <c r="J6" s="90" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K6" s="87" t="n"/>
-      <c r="L6" s="87" t="n"/>
-      <c r="M6" s="87" t="inlineStr">
+      <c r="K6" s="90" t="n"/>
+      <c r="L6" s="90" t="n"/>
+      <c r="M6" s="90" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N6" s="88" t="inlineStr">
+      <c r="N6" s="91" t="inlineStr">
         <is>
           <t>ATMはどこ</t>
         </is>
       </c>
-      <c r="O6" s="88" t="n"/>
-      <c r="P6" s="88" t="inlineStr">
+      <c r="O6" s="91" t="n"/>
+      <c r="P6" s="91" t="inlineStr">
         <is>
           <t>2026-10-13 17:14</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="87" t="inlineStr">
+      <c r="A7" s="90" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B7" s="87" t="inlineStr">
+      <c r="B7" s="90" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C7" s="87" t="inlineStr">
+      <c r="C7" s="90" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2920,28 +2932,28 @@
           <t>海外のカードは鳩谷郵便局のATM、日本のカードは和田家前のJAのATMをご利用ください。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G7" s="87" t="n"/>
-      <c r="H7" s="87" t="n"/>
-      <c r="I7" s="87" t="inlineStr">
+      <c r="G7" s="90" t="n"/>
+      <c r="H7" s="90" t="n"/>
+      <c r="I7" s="90" t="inlineStr">
         <is>
           <t>atm_deai.mp3</t>
         </is>
       </c>
-      <c r="J7" s="87" t="inlineStr">
+      <c r="J7" s="90" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K7" s="87" t="n"/>
-      <c r="L7" s="87" t="n"/>
-      <c r="M7" s="87" t="inlineStr">
+      <c r="K7" s="90" t="n"/>
+      <c r="L7" s="90" t="n"/>
+      <c r="M7" s="90" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N7" s="88" t="n"/>
-      <c r="O7" s="88" t="n"/>
-      <c r="P7" s="88" t="inlineStr">
+      <c r="N7" s="91" t="n"/>
+      <c r="O7" s="91" t="n"/>
+      <c r="P7" s="91" t="inlineStr">
         <is>
           <t>2026-10-13 17:15</t>
         </is>
@@ -2997,17 +3009,17 @@
       </c>
     </row>
     <row r="9" ht="58.05" customHeight="1">
-      <c r="A9" s="87" t="inlineStr">
+      <c r="A9" s="90" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B9" s="87" t="inlineStr">
+      <c r="B9" s="90" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C9" s="87" t="inlineStr">
+      <c r="C9" s="90" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3027,45 +3039,45 @@
         </is>
       </c>
       <c r="F9" s="44" t="n"/>
-      <c r="G9" s="87" t="n"/>
-      <c r="H9" s="87" t="n"/>
-      <c r="I9" s="87" t="inlineStr">
+      <c r="G9" s="90" t="n"/>
+      <c r="H9" s="90" t="n"/>
+      <c r="I9" s="90" t="inlineStr">
         <is>
           <t>currency_exchange_bt.mp3</t>
         </is>
       </c>
-      <c r="J9" s="87" t="inlineStr">
+      <c r="J9" s="90" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K9" s="87" t="n"/>
-      <c r="L9" s="87" t="n"/>
-      <c r="M9" s="87" t="inlineStr">
+      <c r="K9" s="90" t="n"/>
+      <c r="L9" s="90" t="n"/>
+      <c r="M9" s="90" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N9" s="88" t="n"/>
-      <c r="O9" s="88" t="n"/>
-      <c r="P9" s="88" t="inlineStr">
+      <c r="N9" s="91" t="n"/>
+      <c r="O9" s="91" t="n"/>
+      <c r="P9" s="91" t="inlineStr">
         <is>
           <t>2026-10-13 17:18</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58.05" customHeight="1">
-      <c r="A10" s="87" t="inlineStr">
+      <c r="A10" s="90" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B10" s="87" t="inlineStr">
+      <c r="B10" s="90" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C10" s="87" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3085,45 +3097,45 @@
         </is>
       </c>
       <c r="F10" s="44" t="n"/>
-      <c r="G10" s="87" t="n"/>
-      <c r="H10" s="87" t="n"/>
-      <c r="I10" s="87" t="inlineStr">
+      <c r="G10" s="90" t="n"/>
+      <c r="H10" s="90" t="n"/>
+      <c r="I10" s="90" t="inlineStr">
         <is>
           <t>currency_exchange_deai.mp3</t>
         </is>
       </c>
-      <c r="J10" s="87" t="inlineStr">
+      <c r="J10" s="90" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K10" s="87" t="n"/>
-      <c r="L10" s="87" t="n"/>
-      <c r="M10" s="87" t="inlineStr">
+      <c r="K10" s="90" t="n"/>
+      <c r="L10" s="90" t="n"/>
+      <c r="M10" s="90" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N10" s="88" t="n"/>
-      <c r="O10" s="88" t="n"/>
-      <c r="P10" s="88" t="inlineStr">
+      <c r="N10" s="91" t="n"/>
+      <c r="O10" s="91" t="n"/>
+      <c r="P10" s="91" t="inlineStr">
         <is>
           <t>2026-10-13 17:19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58.05" customHeight="1">
-      <c r="A11" s="87" t="inlineStr">
+      <c r="A11" s="90" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B11" s="87" t="inlineStr">
+      <c r="B11" s="90" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C11" s="87" t="inlineStr">
+      <c r="C11" s="90" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3144,49 +3156,49 @@
         </is>
       </c>
       <c r="F11" s="44" t="n"/>
-      <c r="G11" s="87" t="n"/>
-      <c r="H11" s="87" t="n"/>
-      <c r="I11" s="87" t="inlineStr">
+      <c r="G11" s="90" t="n"/>
+      <c r="H11" s="90" t="n"/>
+      <c r="I11" s="90" t="inlineStr">
         <is>
           <t>luggage_bt.mp3</t>
         </is>
       </c>
-      <c r="J11" s="87" t="inlineStr">
+      <c r="J11" s="90" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K11" s="87" t="n"/>
-      <c r="L11" s="87" t="n"/>
-      <c r="M11" s="87" t="inlineStr">
+      <c r="K11" s="90" t="n"/>
+      <c r="L11" s="90" t="n"/>
+      <c r="M11" s="90" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N11" s="88" t="inlineStr">
+      <c r="N11" s="91" t="inlineStr">
         <is>
           <t>荷物を預けたい</t>
         </is>
       </c>
-      <c r="O11" s="88" t="n"/>
-      <c r="P11" s="88" t="inlineStr">
+      <c r="O11" s="91" t="n"/>
+      <c r="P11" s="91" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58.05" customHeight="1">
-      <c r="A12" s="87" t="inlineStr">
+      <c r="A12" s="90" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B12" s="87" t="inlineStr">
+      <c r="B12" s="90" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C12" s="87" t="inlineStr">
+      <c r="C12" s="90" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3207,28 +3219,28 @@
         </is>
       </c>
       <c r="F12" s="44" t="n"/>
-      <c r="G12" s="87" t="n"/>
-      <c r="H12" s="87" t="n"/>
-      <c r="I12" s="87" t="inlineStr">
+      <c r="G12" s="90" t="n"/>
+      <c r="H12" s="90" t="n"/>
+      <c r="I12" s="90" t="inlineStr">
         <is>
           <t>luggage_deai.mp3</t>
         </is>
       </c>
-      <c r="J12" s="87" t="inlineStr">
+      <c r="J12" s="90" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K12" s="87" t="n"/>
-      <c r="L12" s="87" t="n"/>
-      <c r="M12" s="87" t="inlineStr">
+      <c r="K12" s="90" t="n"/>
+      <c r="L12" s="90" t="n"/>
+      <c r="M12" s="90" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N12" s="88" t="n"/>
-      <c r="O12" s="88" t="n"/>
-      <c r="P12" s="88" t="inlineStr">
+      <c r="N12" s="91" t="n"/>
+      <c r="O12" s="91" t="n"/>
+      <c r="P12" s="91" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
@@ -3349,22 +3361,22 @@
       </c>
     </row>
     <row r="15" ht="58.05" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="93" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="93" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="93" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="44" t="inlineStr">
         <is>
           <t>スタンプ
 記念 スタンプ
@@ -3373,29 +3385,36 @@
 スタンプ ある</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>記念スタンプは窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="E15" s="44" t="inlineStr">
+        <is>
+          <t>記念スタンプはであいの館の窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
+        </is>
+      </c>
+      <c r="F15" s="44" t="n"/>
+      <c r="G15" s="93" t="n"/>
+      <c r="H15" s="93" t="n"/>
+      <c r="I15" s="93" t="inlineStr">
         <is>
           <t>stamp_deai.mp3</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J15" s="93" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="14" t="inlineStr">
+      <c r="K15" s="93" t="n"/>
+      <c r="L15" s="93" t="n"/>
+      <c r="M15" s="93" t="inlineStr">
         <is>
           <t>stamp</t>
+        </is>
+      </c>
+      <c r="N15" s="94" t="n"/>
+      <c r="O15" s="94" t="n"/>
+      <c r="P15" s="94" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:23</t>
         </is>
       </c>
     </row>
@@ -4938,17 +4957,17 @@
       </c>
     </row>
     <row r="43" ht="249.6" customHeight="1">
-      <c r="A43" s="87" t="inlineStr">
+      <c r="A43" s="90" t="inlineStr">
         <is>
           <t>guesthouse_access_deai</t>
         </is>
       </c>
-      <c r="B43" s="87" t="inlineStr">
+      <c r="B43" s="90" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C43" s="87" t="inlineStr">
+      <c r="C43" s="90" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -4982,30 +5001,30 @@
           <t>その建物は鳩谷八幡神社方面にあります。国道は交通量が多いため、川沿いの道をおすすめしております。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G43" s="87" t="inlineStr">
+      <c r="G43" s="90" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H43" s="87" t="n"/>
-      <c r="I43" s="87" t="inlineStr">
+      <c r="H43" s="90" t="n"/>
+      <c r="I43" s="90" t="inlineStr">
         <is>
           <t>guesthouse_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J43" s="87" t="inlineStr">
+      <c r="J43" s="90" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K43" s="87" t="n"/>
-      <c r="L43" s="87" t="n"/>
-      <c r="M43" s="87" t="inlineStr">
+      <c r="K43" s="90" t="n"/>
+      <c r="L43" s="90" t="n"/>
+      <c r="M43" s="90" t="inlineStr">
         <is>
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="88" t="n"/>
+      <c r="N43" s="91" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -6194,17 +6213,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="88" t="inlineStr">
+      <c r="A66" s="91" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="88" t="inlineStr">
+      <c r="B66" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="88" t="inlineStr">
+      <c r="C66" s="91" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -6234,26 +6253,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="88" t="inlineStr">
+      <c r="G66" s="91" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="88" t="n"/>
-      <c r="I66" s="88" t="inlineStr">
+      <c r="H66" s="91" t="n"/>
+      <c r="I66" s="91" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="88" t="inlineStr">
+      <c r="J66" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="88" t="n"/>
-      <c r="L66" s="88" t="n"/>
-      <c r="M66" s="88" t="n"/>
-      <c r="N66" s="88" t="n"/>
+      <c r="K66" s="91" t="n"/>
+      <c r="L66" s="91" t="n"/>
+      <c r="M66" s="91" t="n"/>
+      <c r="N66" s="91" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -7462,12 +7481,12 @@
       </c>
     </row>
     <row r="22" ht="64.8" customHeight="1">
-      <c r="A22" s="88" t="inlineStr">
+      <c r="A22" s="91" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B22" s="88" t="inlineStr">
+      <c r="B22" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7498,12 +7517,12 @@
       </c>
     </row>
     <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="88" t="inlineStr">
+      <c r="A23" s="91" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B23" s="88" t="inlineStr">
+      <c r="B23" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7534,12 +7553,12 @@
       </c>
     </row>
     <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="88" t="inlineStr">
+      <c r="A24" s="91" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B24" s="88" t="inlineStr">
+      <c r="B24" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7570,12 +7589,12 @@
       </c>
     </row>
     <row r="25" ht="81" customHeight="1">
-      <c r="A25" s="88" t="inlineStr">
+      <c r="A25" s="91" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B25" s="88" t="inlineStr">
+      <c r="B25" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7606,12 +7625,12 @@
       </c>
     </row>
     <row r="26" ht="64.8" customHeight="1">
-      <c r="A26" s="89" t="inlineStr">
+      <c r="A26" s="92" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B26" s="89" t="inlineStr">
+      <c r="B26" s="92" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8163,12 +8182,12 @@
       </c>
     </row>
     <row r="42" ht="64.8" customHeight="1">
-      <c r="A42" s="88" t="inlineStr">
+      <c r="A42" s="91" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B42" s="88" t="inlineStr">
+      <c r="B42" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8199,12 +8218,12 @@
       </c>
     </row>
     <row r="43" ht="64.8" customHeight="1">
-      <c r="A43" s="88" t="inlineStr">
+      <c r="A43" s="91" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B43" s="88" t="inlineStr">
+      <c r="B43" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8235,12 +8254,12 @@
       </c>
     </row>
     <row r="44" ht="81" customHeight="1">
-      <c r="A44" s="88" t="inlineStr">
+      <c r="A44" s="91" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B44" s="88" t="inlineStr">
+      <c r="B44" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8271,12 +8290,12 @@
       </c>
     </row>
     <row r="45" ht="64.8" customHeight="1">
-      <c r="A45" s="88" t="inlineStr">
+      <c r="A45" s="91" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B45" s="88" t="inlineStr">
+      <c r="B45" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8307,12 +8326,12 @@
       </c>
     </row>
     <row r="46" ht="64.8" customHeight="1">
-      <c r="A46" s="89" t="inlineStr">
+      <c r="A46" s="92" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B46" s="89" t="inlineStr">
+      <c r="B46" s="92" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8523,12 +8542,12 @@
       </c>
     </row>
     <row r="52" ht="48.6" customHeight="1">
-      <c r="A52" s="88" t="inlineStr">
+      <c r="A52" s="91" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B52" s="88" t="inlineStr">
+      <c r="B52" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8559,12 +8578,12 @@
       </c>
     </row>
     <row r="53" ht="97.2" customHeight="1">
-      <c r="A53" s="88" t="inlineStr">
+      <c r="A53" s="91" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B53" s="88" t="inlineStr">
+      <c r="B53" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8595,12 +8614,12 @@
       </c>
     </row>
     <row r="54" ht="97.2" customHeight="1">
-      <c r="A54" s="88" t="inlineStr">
+      <c r="A54" s="91" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B54" s="88" t="inlineStr">
+      <c r="B54" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8631,12 +8650,12 @@
       </c>
     </row>
     <row r="55" ht="97.2" customHeight="1">
-      <c r="A55" s="88" t="inlineStr">
+      <c r="A55" s="91" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B55" s="88" t="inlineStr">
+      <c r="B55" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8667,12 +8686,12 @@
       </c>
     </row>
     <row r="56" ht="97.2" customHeight="1">
-      <c r="A56" s="89" t="inlineStr">
+      <c r="A56" s="92" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B56" s="89" t="inlineStr">
+      <c r="B56" s="92" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -9047,31 +9066,35 @@
       </c>
     </row>
     <row r="67" ht="81" customHeight="1">
-      <c r="A67" s="27" t="inlineStr">
+      <c r="A67" s="95" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B67" s="27" t="inlineStr">
+      <c r="B67" s="95" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="C67" s="28" t="inlineStr">
+      <c r="C67" s="73" t="inlineStr">
         <is>
           <t>stamp
 souvenir stamp
-goshuin
-postage stamp
-stamp book</t>
-        </is>
-      </c>
-      <c r="D67" s="28" t="inlineStr">
-        <is>
-          <t>Souvenir stamps are available on the table at the counter. We do not sell postage stamps or offer goshuin temple and shrine seals.</t>
-        </is>
-      </c>
-      <c r="E67" s="27" t="n"/>
+memorial stamp
+stamp available
+where stamp</t>
+        </is>
+      </c>
+      <c r="D67" s="73" t="inlineStr">
+        <is>
+          <t>Souvenir stamps are available at the counter of Deai no Yakata. We do not handle postage stamps or temple seals.</t>
+        </is>
+      </c>
+      <c r="E67" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 記念スタンプはであいの館の窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
+        </is>
+      </c>
       <c r="F67" s="29" t="inlineStr">
         <is>
           <t>記念スタンプは窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
@@ -9079,32 +9102,35 @@
       </c>
     </row>
     <row r="68" ht="97.2" customHeight="1">
-      <c r="A68" s="27" t="inlineStr">
+      <c r="A68" s="95" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B68" s="27" t="inlineStr">
+      <c r="B68" s="95" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="C68" s="28" t="inlineStr">
+      <c r="C68" s="73" t="inlineStr">
         <is>
           <t>sello
-sello recuerdo
-goshuin
+sello conmemorativo
 estampilla
-sello postal
-timbre</t>
-        </is>
-      </c>
-      <c r="D68" s="28" t="inlineStr">
-        <is>
-          <t>Los sellos de recuerdo están sobre la mesa del mostrador. No vendemos sellos postales ni ofrecemos goshuin.</t>
-        </is>
-      </c>
-      <c r="E68" s="27" t="n"/>
+sello disponible
+dónde sello</t>
+        </is>
+      </c>
+      <c r="D68" s="73" t="inlineStr">
+        <is>
+          <t>Los sellos conmemorativos están disponibles en el mostrador de Deai no Yakata. No vendemos sellos postales ni talismanes de templo.</t>
+        </is>
+      </c>
+      <c r="E68" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 記念スタンプはであいの館の窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
+        </is>
+      </c>
       <c r="F68" s="29" t="inlineStr">
         <is>
           <t>記念スタンプは窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
@@ -9112,32 +9138,35 @@
       </c>
     </row>
     <row r="69" ht="97.2" customHeight="1">
-      <c r="A69" s="27" t="inlineStr">
+      <c r="A69" s="95" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B69" s="27" t="inlineStr">
+      <c r="B69" s="95" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="C69" s="28" t="inlineStr">
+      <c r="C69" s="73" t="inlineStr">
         <is>
           <t>tampon
 tampon souvenir
-goshuin
 timbre
-cachet
-timbre poste</t>
-        </is>
-      </c>
-      <c r="D69" s="28" t="inlineStr">
-        <is>
-          <t>Le tampon souvenir est à votre disposition sur la table du guichet. Nous ne vendons pas de timbres et ne proposons pas de goshuin.</t>
-        </is>
-      </c>
-      <c r="E69" s="27" t="n"/>
+tampon disponible
+où tampon</t>
+        </is>
+      </c>
+      <c r="D69" s="73" t="inlineStr">
+        <is>
+          <t>Les tampons commémoratifs sont disponibles au comptoir de Deai no Yakata. Nous ne vendons pas de timbres-poste ni de sceaux de temple.</t>
+        </is>
+      </c>
+      <c r="E69" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 記念スタンプはであいの館の窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
+        </is>
+      </c>
       <c r="F69" s="29" t="inlineStr">
         <is>
           <t>記念スタンプは窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
@@ -9145,32 +9174,35 @@
       </c>
     </row>
     <row r="70" ht="97.2" customHeight="1">
-      <c r="A70" s="27" t="inlineStr">
+      <c r="A70" s="95" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B70" s="27" t="inlineStr">
+      <c r="B70" s="95" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="C70" s="28" t="inlineStr">
+      <c r="C70" s="73" t="inlineStr">
         <is>
           <t>스탬프
 기념 스탬프
-도장
 우표
-고슈인
-주인장</t>
-        </is>
-      </c>
-      <c r="D70" s="28" t="inlineStr">
-        <is>
-          <t>기념 스탬프는 창구 책상 위에 준비되어 있습니다. 우표와 고슈인은 취급하지 않습니다.</t>
-        </is>
-      </c>
-      <c r="E70" s="27" t="n"/>
+스탬프 있습니다
+스탐프 있나</t>
+        </is>
+      </c>
+      <c r="D70" s="73" t="inlineStr">
+        <is>
+          <t>기념 스탬프는 데아이노야카타의 창구 책상 위에 준비되어 있습니다. 우표와 어새(사찰 인장)는 취급하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="E70" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 記念スタンプはであいの館の窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
+        </is>
+      </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
           <t>記念スタンプは窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
@@ -9178,31 +9210,35 @@
       </c>
     </row>
     <row r="71" ht="81" customHeight="1">
-      <c r="A71" s="30" t="inlineStr">
+      <c r="A71" s="96" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B71" s="30" t="inlineStr">
+      <c r="B71" s="96" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C71" s="31" t="inlineStr">
-        <is>
-          <t>印章
-纪念章
-盖章
-御朱印
-邮票</t>
-        </is>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>纪念印章放在窗口的桌子上。本处不出售邮票，也不提供御朱印。</t>
-        </is>
-      </c>
-      <c r="E71" s="30" t="n"/>
+      <c r="C71" s="75" t="inlineStr">
+        <is>
+          <t>纪念章
+邮票
+印章
+有纪念章吗
+哪里纪念章</t>
+        </is>
+      </c>
+      <c r="D71" s="75" t="inlineStr">
+        <is>
+          <t>纪念章在相逢馆的窗口柜台上提供。我们不出售邮票或寺庙印章。</t>
+        </is>
+      </c>
+      <c r="E71" s="75" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 記念スタンプはであいの館の窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
+        </is>
+      </c>
       <c r="F71" s="32" t="inlineStr">
         <is>
           <t>記念スタンプは窓口机上にご用意しております。切手や御朱印の取扱いはございません。</t>
@@ -16859,12 +16895,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="88" t="inlineStr">
+      <c r="A302" s="91" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="88" t="inlineStr">
+      <c r="B302" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16890,12 +16926,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="88" t="inlineStr">
+      <c r="A303" s="91" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="88" t="inlineStr">
+      <c r="B303" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16921,12 +16957,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="88" t="inlineStr">
+      <c r="A304" s="91" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="88" t="inlineStr">
+      <c r="B304" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16952,12 +16988,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="88" t="inlineStr">
+      <c r="A305" s="91" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="88" t="inlineStr">
+      <c r="B305" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -16983,12 +17019,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="88" t="inlineStr">
+      <c r="A306" s="91" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="88" t="inlineStr">
+      <c r="B306" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17014,12 +17050,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="88" t="inlineStr">
+      <c r="A307" s="91" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="88" t="inlineStr">
+      <c r="B307" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17045,12 +17081,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="88" t="inlineStr">
+      <c r="A308" s="91" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="88" t="inlineStr">
+      <c r="B308" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17076,12 +17112,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="88" t="inlineStr">
+      <c r="A309" s="91" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="88" t="inlineStr">
+      <c r="B309" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17107,12 +17143,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="88" t="inlineStr">
+      <c r="A310" s="91" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="88" t="inlineStr">
+      <c r="B310" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17138,12 +17174,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="88" t="inlineStr">
+      <c r="A311" s="91" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="88" t="inlineStr">
+      <c r="B311" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17169,12 +17205,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="88" t="inlineStr">
+      <c r="A312" s="91" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="88" t="inlineStr">
+      <c r="B312" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17199,12 +17235,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="88" t="inlineStr">
+      <c r="A313" s="91" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="88" t="inlineStr">
+      <c r="B313" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17229,12 +17265,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="88" t="inlineStr">
+      <c r="A314" s="91" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="88" t="inlineStr">
+      <c r="B314" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17259,12 +17295,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="88" t="inlineStr">
+      <c r="A315" s="91" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="88" t="inlineStr">
+      <c r="B315" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17289,12 +17325,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="88" t="inlineStr">
+      <c r="A316" s="91" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="88" t="inlineStr">
+      <c r="B316" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17319,12 +17355,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="88" t="inlineStr">
+      <c r="A317" s="91" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="88" t="inlineStr">
+      <c r="B317" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17350,12 +17386,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="88" t="inlineStr">
+      <c r="A318" s="91" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="88" t="inlineStr">
+      <c r="B318" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17381,12 +17417,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="88" t="inlineStr">
+      <c r="A319" s="91" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="88" t="inlineStr">
+      <c r="B319" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17412,12 +17448,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="88" t="inlineStr">
+      <c r="A320" s="91" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="88" t="inlineStr">
+      <c r="B320" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17443,12 +17479,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="88" t="inlineStr">
+      <c r="A321" s="91" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="88" t="inlineStr">
+      <c r="B321" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17474,12 +17510,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="88" t="inlineStr">
+      <c r="A322" s="91" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="88" t="inlineStr">
+      <c r="B322" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17504,12 +17540,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="88" t="inlineStr">
+      <c r="A323" s="91" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="88" t="inlineStr">
+      <c r="B323" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17534,12 +17570,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="88" t="inlineStr">
+      <c r="A324" s="91" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="88" t="inlineStr">
+      <c r="B324" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17564,12 +17600,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="88" t="inlineStr">
+      <c r="A325" s="91" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="88" t="inlineStr">
+      <c r="B325" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17594,12 +17630,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="88" t="inlineStr">
+      <c r="A326" s="91" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="88" t="inlineStr">
+      <c r="B326" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17624,12 +17660,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="88" t="inlineStr">
+      <c r="A327" s="91" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="88" t="inlineStr">
+      <c r="B327" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17656,12 +17692,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="88" t="inlineStr">
+      <c r="A328" s="91" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="88" t="inlineStr">
+      <c r="B328" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17688,12 +17724,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="88" t="inlineStr">
+      <c r="A329" s="91" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="88" t="inlineStr">
+      <c r="B329" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17720,12 +17756,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="88" t="inlineStr">
+      <c r="A330" s="91" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="88" t="inlineStr">
+      <c r="B330" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17752,12 +17788,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="88" t="inlineStr">
+      <c r="A331" s="91" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="88" t="inlineStr">
+      <c r="B331" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17784,12 +17820,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="88" t="inlineStr">
+      <c r="A332" s="91" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="88" t="inlineStr">
+      <c r="B332" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17816,12 +17852,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="88" t="inlineStr">
+      <c r="A333" s="91" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="88" t="inlineStr">
+      <c r="B333" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17848,12 +17884,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="88" t="inlineStr">
+      <c r="A334" s="91" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="88" t="inlineStr">
+      <c r="B334" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17880,12 +17916,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="88" t="inlineStr">
+      <c r="A335" s="91" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="88" t="inlineStr">
+      <c r="B335" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17912,12 +17948,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="88" t="inlineStr">
+      <c r="A336" s="91" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="88" t="inlineStr">
+      <c r="B336" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17944,12 +17980,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="88" t="inlineStr">
+      <c r="A337" s="91" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="88" t="inlineStr">
+      <c r="B337" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17976,12 +18012,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="88" t="inlineStr">
+      <c r="A338" s="91" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="88" t="inlineStr">
+      <c r="B338" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18008,12 +18044,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="88" t="inlineStr">
+      <c r="A339" s="91" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="88" t="inlineStr">
+      <c r="B339" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18040,12 +18076,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="88" t="inlineStr">
+      <c r="A340" s="91" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="88" t="inlineStr">
+      <c r="B340" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18072,12 +18108,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="88" t="inlineStr">
+      <c r="A341" s="91" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="88" t="inlineStr">
+      <c r="B341" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18104,12 +18140,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="88" t="inlineStr">
+      <c r="A342" s="91" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="88" t="inlineStr">
+      <c r="B342" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18136,12 +18172,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="88" t="inlineStr">
+      <c r="A343" s="91" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="88" t="inlineStr">
+      <c r="B343" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18168,12 +18204,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="88" t="inlineStr">
+      <c r="A344" s="91" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="88" t="inlineStr">
+      <c r="B344" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18200,12 +18236,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="88" t="inlineStr">
+      <c r="A345" s="91" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="88" t="inlineStr">
+      <c r="B345" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18232,12 +18268,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="88" t="inlineStr">
+      <c r="A346" s="91" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="88" t="inlineStr">
+      <c r="B346" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18264,12 +18300,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="88" t="inlineStr">
+      <c r="A347" s="91" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="88" t="inlineStr">
+      <c r="B347" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18296,12 +18332,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="88" t="inlineStr">
+      <c r="A348" s="91" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="88" t="inlineStr">
+      <c r="B348" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18328,12 +18364,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="88" t="inlineStr">
+      <c r="A349" s="91" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="88" t="inlineStr">
+      <c r="B349" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18360,12 +18396,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="88" t="inlineStr">
+      <c r="A350" s="91" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="88" t="inlineStr">
+      <c r="B350" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18392,12 +18428,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="88" t="inlineStr">
+      <c r="A351" s="91" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="88" t="inlineStr">
+      <c r="B351" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18424,12 +18460,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="88" t="inlineStr">
+      <c r="A352" s="91" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="88" t="inlineStr">
+      <c r="B352" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18455,12 +18491,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="88" t="inlineStr">
+      <c r="A353" s="91" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="88" t="inlineStr">
+      <c r="B353" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18486,12 +18522,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="88" t="inlineStr">
+      <c r="A354" s="91" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="88" t="inlineStr">
+      <c r="B354" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18517,12 +18553,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="88" t="inlineStr">
+      <c r="A355" s="91" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="88" t="inlineStr">
+      <c r="B355" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18548,12 +18584,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="88" t="inlineStr">
+      <c r="A356" s="91" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="88" t="inlineStr">
+      <c r="B356" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18579,12 +18615,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="88" t="inlineStr">
+      <c r="A357" s="91" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="88" t="inlineStr">
+      <c r="B357" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18610,12 +18646,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="88" t="inlineStr">
+      <c r="A358" s="91" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="88" t="inlineStr">
+      <c r="B358" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18641,12 +18677,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="88" t="inlineStr">
+      <c r="A359" s="91" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="88" t="inlineStr">
+      <c r="B359" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18672,12 +18708,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="88" t="inlineStr">
+      <c r="A360" s="91" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="88" t="inlineStr">
+      <c r="B360" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18703,12 +18739,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="88" t="inlineStr">
+      <c r="A361" s="91" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="88" t="inlineStr">
+      <c r="B361" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18734,12 +18770,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="88" t="inlineStr">
+      <c r="A362" s="91" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="88" t="inlineStr">
+      <c r="B362" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18766,12 +18802,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="88" t="inlineStr">
+      <c r="A363" s="91" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="88" t="inlineStr">
+      <c r="B363" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18798,12 +18834,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="88" t="inlineStr">
+      <c r="A364" s="91" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="88" t="inlineStr">
+      <c r="B364" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18830,12 +18866,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="88" t="inlineStr">
+      <c r="A365" s="91" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="88" t="inlineStr">
+      <c r="B365" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18862,12 +18898,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="88" t="inlineStr">
+      <c r="A366" s="91" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="88" t="inlineStr">
+      <c r="B366" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18894,12 +18930,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="88" t="inlineStr">
+      <c r="A367" s="91" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="88" t="inlineStr">
+      <c r="B367" s="91" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18926,12 +18962,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="88" t="inlineStr">
+      <c r="A368" s="91" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="88" t="inlineStr">
+      <c r="B368" s="91" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18958,12 +18994,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="88" t="inlineStr">
+      <c r="A369" s="91" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="88" t="inlineStr">
+      <c r="B369" s="91" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18990,12 +19026,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="88" t="inlineStr">
+      <c r="A370" s="91" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="88" t="inlineStr">
+      <c r="B370" s="91" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -19022,12 +19058,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="88" t="inlineStr">
+      <c r="A371" s="91" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="88" t="inlineStr">
+      <c r="B371" s="91" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -20163,7 +20199,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="88" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -20173,7 +20209,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="88" t="inlineStr">
+      <c r="C2" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20185,7 +20221,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="88" t="inlineStr">
+      <c r="A3" s="91" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -20195,7 +20231,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="88" t="inlineStr">
+      <c r="C3" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20207,7 +20243,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="88" t="inlineStr">
+      <c r="A4" s="91" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -20217,7 +20253,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="88" t="inlineStr">
+      <c r="C4" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20229,7 +20265,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="88" t="inlineStr">
+      <c r="A5" s="91" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -20239,7 +20275,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="88" t="inlineStr">
+      <c r="C5" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20251,7 +20287,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="88" t="inlineStr">
+      <c r="A6" s="91" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20261,7 +20297,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="88" t="inlineStr">
+      <c r="C6" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20273,7 +20309,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="88" t="inlineStr">
+      <c r="A7" s="91" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20283,7 +20319,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="88" t="inlineStr">
+      <c r="C7" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20295,7 +20331,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="88" t="inlineStr">
+      <c r="A8" s="91" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20305,7 +20341,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="88" t="inlineStr">
+      <c r="C8" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20317,7 +20353,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="88" t="inlineStr">
+      <c r="A9" s="91" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20327,7 +20363,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="88" t="inlineStr">
+      <c r="C9" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20339,7 +20375,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="88" t="inlineStr">
+      <c r="A10" s="91" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20349,7 +20385,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="88" t="inlineStr">
+      <c r="C10" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20361,7 +20397,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="88" t="inlineStr">
+      <c r="A11" s="91" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20371,7 +20407,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="88" t="inlineStr">
+      <c r="C11" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20383,7 +20419,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="88" t="inlineStr">
+      <c r="A12" s="91" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20393,7 +20429,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="88" t="inlineStr">
+      <c r="C12" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20405,7 +20441,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="88" t="inlineStr">
+      <c r="A13" s="91" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20415,7 +20451,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="88" t="inlineStr">
+      <c r="C13" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20557,53 +20593,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="88" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="88" t="inlineStr">
+      <c r="B2" s="91" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="88" t="inlineStr">
+      <c r="C2" s="91" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="88" t="inlineStr">
+      <c r="D2" s="91" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="88" t="inlineStr">
+      <c r="E2" s="91" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="88" t="inlineStr">
+      <c r="F2" s="91" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="88" t="inlineStr">
+      <c r="G2" s="91" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="88" t="inlineStr">
+      <c r="H2" s="91" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="88" t="inlineStr">
+      <c r="I2" s="91" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="88" t="n"/>
-      <c r="K2" s="88" t="inlineStr">
+      <c r="J2" s="91" t="n"/>
+      <c r="K2" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20640,45 +20676,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="88" t="inlineStr">
+      <c r="A3" s="91" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="88" t="inlineStr">
+      <c r="B3" s="91" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="88" t="inlineStr">
+      <c r="C3" s="91" t="inlineStr">
         <is>
           <t>main_idle_20261013044809.png</t>
         </is>
       </c>
-      <c r="D3" s="88" t="n"/>
-      <c r="E3" s="88" t="n"/>
-      <c r="F3" s="88" t="n">
+      <c r="D3" s="91" t="n"/>
+      <c r="E3" s="91" t="n"/>
+      <c r="F3" s="91" t="n">
         <v>0.179</v>
       </c>
-      <c r="G3" s="88" t="n">
+      <c r="G3" s="91" t="n">
         <v>0.23</v>
       </c>
-      <c r="H3" s="88" t="inlineStr">
+      <c r="H3" s="91" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="88" t="inlineStr">
+      <c r="I3" s="91" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="88" t="inlineStr">
+      <c r="J3" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="88" t="inlineStr">
+      <c r="K3" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20715,45 +20751,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="88" t="inlineStr">
+      <c r="A4" s="91" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="88" t="inlineStr">
+      <c r="B4" s="91" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="88" t="inlineStr">
+      <c r="C4" s="91" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="88" t="n"/>
-      <c r="E4" s="88" t="n"/>
-      <c r="F4" s="88" t="inlineStr">
+      <c r="D4" s="91" t="n"/>
+      <c r="E4" s="91" t="n"/>
+      <c r="F4" s="91" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="88" t="inlineStr">
+      <c r="G4" s="91" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="88" t="inlineStr">
+      <c r="H4" s="91" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="88" t="inlineStr">
+      <c r="I4" s="91" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="88" t="n"/>
-      <c r="K4" s="88" t="inlineStr">
+      <c r="J4" s="91" t="n"/>
+      <c r="K4" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20790,45 +20826,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="88" t="inlineStr">
+      <c r="A5" s="91" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="88" t="inlineStr">
+      <c r="B5" s="91" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="88" t="inlineStr">
+      <c r="C5" s="91" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="88" t="n"/>
-      <c r="E5" s="88" t="n"/>
-      <c r="F5" s="88" t="inlineStr">
+      <c r="D5" s="91" t="n"/>
+      <c r="E5" s="91" t="n"/>
+      <c r="F5" s="91" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="88" t="inlineStr">
+      <c r="G5" s="91" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="88" t="inlineStr">
+      <c r="H5" s="91" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="88" t="inlineStr">
+      <c r="I5" s="91" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="88" t="n"/>
-      <c r="K5" s="88" t="inlineStr">
+      <c r="J5" s="91" t="n"/>
+      <c r="K5" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20865,45 +20901,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="88" t="inlineStr">
+      <c r="A6" s="91" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="88" t="inlineStr">
+      <c r="B6" s="91" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="88" t="inlineStr">
+      <c r="C6" s="91" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="88" t="n"/>
-      <c r="E6" s="88" t="n"/>
-      <c r="F6" s="88" t="inlineStr">
+      <c r="D6" s="91" t="n"/>
+      <c r="E6" s="91" t="n"/>
+      <c r="F6" s="91" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="88" t="inlineStr">
+      <c r="G6" s="91" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="88" t="inlineStr">
+      <c r="H6" s="91" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="88" t="inlineStr">
+      <c r="I6" s="91" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="88" t="n"/>
-      <c r="K6" s="88" t="inlineStr">
+      <c r="J6" s="91" t="n"/>
+      <c r="K6" s="91" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -21025,12 +21061,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="88" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B2" s="88" t="inlineStr">
+      <c r="B2" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21069,12 +21105,12 @@
       <c r="J2" s="46" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="88" t="inlineStr">
+      <c r="A3" s="91" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B3" s="88" t="inlineStr">
+      <c r="B3" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21113,12 +21149,12 @@
       <c r="J3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="88" t="inlineStr">
+      <c r="A4" s="91" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B4" s="88" t="inlineStr">
+      <c r="B4" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21157,12 +21193,12 @@
       <c r="J4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="88" t="inlineStr">
+      <c r="A5" s="91" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B5" s="88" t="inlineStr">
+      <c r="B5" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21201,12 +21237,12 @@
       <c r="J5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="88" t="inlineStr">
+      <c r="A6" s="91" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B6" s="88" t="inlineStr">
+      <c r="B6" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21245,12 +21281,12 @@
       <c r="J6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="88" t="inlineStr">
+      <c r="A7" s="91" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B7" s="88" t="inlineStr">
+      <c r="B7" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21289,12 +21325,12 @@
       <c r="J7" s="46" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="88" t="inlineStr">
+      <c r="A8" s="91" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B8" s="88" t="inlineStr">
+      <c r="B8" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21333,12 +21369,12 @@
       <c r="J8" s="46" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="88" t="inlineStr">
+      <c r="A9" s="91" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B9" s="88" t="inlineStr">
+      <c r="B9" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21377,12 +21413,12 @@
       <c r="J9" s="46" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="88" t="inlineStr">
+      <c r="A10" s="91" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B10" s="88" t="inlineStr">
+      <c r="B10" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21421,12 +21457,12 @@
       <c r="J10" s="46" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="88" t="inlineStr">
+      <c r="A11" s="91" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B11" s="88" t="inlineStr">
+      <c r="B11" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21465,12 +21501,12 @@
       <c r="J11" s="46" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="88" t="inlineStr">
+      <c r="A12" s="91" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B12" s="88" t="inlineStr">
+      <c r="B12" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21509,12 +21545,12 @@
       <c r="J12" s="46" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="88" t="inlineStr">
+      <c r="A13" s="91" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B13" s="88" t="inlineStr">
+      <c r="B13" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21572,12 +21608,12 @@
       <c r="J13" s="46" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="88" t="inlineStr">
+      <c r="A14" s="91" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B14" s="88" t="inlineStr">
+      <c r="B14" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21635,12 +21671,12 @@
       <c r="J14" s="46" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="88" t="inlineStr">
+      <c r="A15" s="91" t="inlineStr">
         <is>
           <t>趣味</t>
         </is>
       </c>
-      <c r="B15" s="88" t="inlineStr">
+      <c r="B15" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21701,12 +21737,12 @@
       <c r="J15" s="46" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="88" t="inlineStr">
+      <c r="A16" s="91" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B16" s="88" t="inlineStr">
+      <c r="B16" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21766,12 +21802,12 @@
       <c r="J16" s="46" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="88" t="inlineStr">
+      <c r="A17" s="91" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B17" s="88" t="inlineStr">
+      <c r="B17" s="91" t="inlineStr">
         <is>
           <t>共通</t>
         </is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -537,6 +537,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1239,7 +1248,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="91" t="inlineStr">
+      <c r="A2" s="94" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1249,31 +1258,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="91" t="n">
+      <c r="C2" s="94" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="91" t="n">
+      <c r="D2" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="91" t="n">
+      <c r="E2" s="94" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="91" t="n">
+      <c r="F2" s="94" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="91" t="n">
+      <c r="G2" s="94" t="n">
         <v>0.957</v>
       </c>
-      <c r="H2" s="91" t="n">
+      <c r="H2" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="91" t="n">
+      <c r="I2" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="91" t="n">
+      <c r="J2" s="94" t="n">
         <v>0.864</v>
       </c>
-      <c r="K2" s="91" t="n">
+      <c r="K2" s="94" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1283,7 +1292,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="91" t="inlineStr">
+      <c r="A3" s="94" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1293,31 +1302,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="91" t="n">
+      <c r="C3" s="94" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="91" t="n">
+      <c r="D3" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="91" t="n">
+      <c r="E3" s="94" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="91" t="n">
+      <c r="F3" s="94" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="91" t="n">
+      <c r="G3" s="94" t="n">
         <v>0.929</v>
       </c>
-      <c r="H3" s="91" t="n">
+      <c r="H3" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="91" t="n">
+      <c r="I3" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="91" t="n">
+      <c r="J3" s="94" t="n">
         <v>0.753</v>
       </c>
-      <c r="K3" s="91" t="n">
+      <c r="K3" s="94" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1327,7 +1336,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="91" t="inlineStr">
+      <c r="A4" s="94" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1337,31 +1346,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="91" t="n">
+      <c r="C4" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="91" t="n">
+      <c r="D4" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="91" t="n">
+      <c r="E4" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="91" t="n">
+      <c r="F4" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="91" t="n">
+      <c r="G4" s="94" t="n">
         <v>0.92</v>
       </c>
-      <c r="H4" s="91" t="n">
+      <c r="H4" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="91" t="n">
+      <c r="I4" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="91" t="n">
+      <c r="J4" s="94" t="n">
         <v>0.884</v>
       </c>
-      <c r="K4" s="91" t="n">
+      <c r="K4" s="94" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1433,7 +1442,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="91" t="inlineStr">
+      <c r="A2" s="94" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1443,10 +1452,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="91" t="n">
+      <c r="C2" s="94" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="91" t="n">
+      <c r="D2" s="94" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1456,7 +1465,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="91" t="inlineStr">
+      <c r="A3" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1466,16 +1475,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="91" t="n">
+      <c r="C3" s="94" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="91" t="n">
+      <c r="D3" s="94" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="91" t="inlineStr">
+      <c r="A4" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1485,16 +1494,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="91" t="n">
+      <c r="C4" s="94" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="91" t="n">
+      <c r="D4" s="94" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="91" t="inlineStr">
+      <c r="A5" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1504,16 +1513,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="91" t="n">
+      <c r="C5" s="94" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="91" t="n">
+      <c r="D5" s="94" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="91" t="inlineStr">
+      <c r="A6" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1523,16 +1532,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="91" t="n">
+      <c r="C6" s="94" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="91" t="n">
+      <c r="D6" s="94" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="91" t="inlineStr">
+      <c r="A7" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1542,10 +1551,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="91" t="n">
+      <c r="C7" s="94" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="91" t="n">
+      <c r="D7" s="94" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1605,17 +1614,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="91" t="inlineStr">
+      <c r="A2" s="94" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="91" t="inlineStr">
+      <c r="B2" s="94" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="91" t="inlineStr">
+      <c r="C2" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1627,17 +1636,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="91" t="inlineStr">
+      <c r="A3" s="94" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="91" t="inlineStr">
+      <c r="B3" s="94" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="91" t="inlineStr">
+      <c r="C3" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1645,17 +1654,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="91" t="inlineStr">
+      <c r="A4" s="94" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="91" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="91" t="inlineStr">
+      <c r="C4" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1667,17 +1676,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="91" t="inlineStr">
+      <c r="A5" s="94" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="91" t="inlineStr">
+      <c r="B5" s="94" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="91" t="inlineStr">
+      <c r="C5" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1689,17 +1698,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="91" t="inlineStr">
+      <c r="A6" s="94" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="91" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="91" t="inlineStr">
+      <c r="C6" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1707,17 +1716,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="91" t="inlineStr">
+      <c r="A7" s="94" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="91" t="inlineStr">
+      <c r="B7" s="94" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="91" t="inlineStr">
+      <c r="C7" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1725,17 +1734,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="91" t="inlineStr">
+      <c r="A8" s="94" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="91" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="91" t="inlineStr">
+      <c r="C8" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1747,17 +1756,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="91" t="inlineStr">
+      <c r="A9" s="94" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="91" t="inlineStr">
+      <c r="B9" s="94" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="91" t="inlineStr">
+      <c r="C9" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1769,17 +1778,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="91" t="inlineStr">
+      <c r="A10" s="94" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="91" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="91" t="inlineStr">
+      <c r="C10" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1791,17 +1800,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="91" t="inlineStr">
+      <c r="A11" s="94" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="91" t="inlineStr">
+      <c r="B11" s="94" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="91" t="inlineStr">
+      <c r="C11" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1809,17 +1818,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="91" t="inlineStr">
+      <c r="A12" s="94" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="91" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="91" t="inlineStr">
+      <c r="C12" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1827,17 +1836,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="91" t="inlineStr">
+      <c r="A13" s="94" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="91" t="inlineStr">
+      <c r="B13" s="94" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="91" t="inlineStr">
+      <c r="C13" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1849,17 +1858,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="91" t="inlineStr">
+      <c r="A14" s="94" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="91" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="91" t="inlineStr">
+      <c r="C14" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1871,17 +1880,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="91" t="inlineStr">
+      <c r="A15" s="94" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="91" t="inlineStr">
+      <c r="B15" s="94" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="91" t="inlineStr">
+      <c r="C15" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1893,17 +1902,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="91" t="inlineStr">
+      <c r="A16" s="94" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="91" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="91" t="inlineStr">
+      <c r="C16" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1915,17 +1924,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="91" t="inlineStr">
+      <c r="A17" s="94" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="91" t="inlineStr">
+      <c r="B17" s="94" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="91" t="inlineStr">
+      <c r="C17" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1937,17 +1946,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="91" t="inlineStr">
+      <c r="A18" s="94" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="91" t="inlineStr">
+      <c r="B18" s="94" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="91" t="inlineStr">
+      <c r="C18" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1959,17 +1968,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="91" t="inlineStr">
+      <c r="A19" s="94" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="91" t="inlineStr">
+      <c r="B19" s="94" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="91" t="inlineStr">
+      <c r="C19" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1977,17 +1986,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="91" t="inlineStr">
+      <c r="A20" s="94" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="91" t="inlineStr">
+      <c r="B20" s="94" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="91" t="inlineStr">
+      <c r="C20" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1995,17 +2004,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="91" t="inlineStr">
+      <c r="A21" s="94" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="91" t="inlineStr">
+      <c r="B21" s="94" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="91" t="inlineStr">
+      <c r="C21" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2017,17 +2026,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="91" t="inlineStr">
+      <c r="A22" s="94" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="91" t="inlineStr">
+      <c r="B22" s="94" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="91" t="inlineStr">
+      <c r="C22" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2039,17 +2048,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="91" t="inlineStr">
+      <c r="A23" s="94" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="91" t="inlineStr">
+      <c r="B23" s="94" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="91" t="inlineStr">
+      <c r="C23" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2061,17 +2070,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="91" t="inlineStr">
+      <c r="A24" s="94" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="91" t="inlineStr">
+      <c r="B24" s="94" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="91" t="inlineStr">
+      <c r="C24" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2083,17 +2092,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="91" t="inlineStr">
+      <c r="A25" s="94" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="91" t="inlineStr">
+      <c r="B25" s="94" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="91" t="inlineStr">
+      <c r="C25" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2101,17 +2110,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="91" t="inlineStr">
+      <c r="A26" s="94" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="91" t="inlineStr">
+      <c r="B26" s="94" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="91" t="inlineStr">
+      <c r="C26" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2119,17 +2128,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="91" t="inlineStr">
+      <c r="A27" s="94" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="91" t="inlineStr">
+      <c r="B27" s="94" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="91" t="inlineStr">
+      <c r="C27" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2141,17 +2150,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="91" t="inlineStr">
+      <c r="A28" s="94" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="91" t="inlineStr">
+      <c r="B28" s="94" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="91" t="inlineStr">
+      <c r="C28" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2163,17 +2172,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="91" t="inlineStr">
+      <c r="A29" s="94" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="91" t="inlineStr">
+      <c r="B29" s="94" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="91" t="inlineStr">
+      <c r="C29" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2185,17 +2194,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="91" t="inlineStr">
+      <c r="A30" s="94" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="91" t="inlineStr">
+      <c r="B30" s="94" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="91" t="inlineStr">
+      <c r="C30" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2203,17 +2212,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="91" t="inlineStr">
+      <c r="A31" s="94" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="91" t="inlineStr">
+      <c r="B31" s="94" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="91" t="inlineStr">
+      <c r="C31" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2225,17 +2234,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="91" t="inlineStr">
+      <c r="A32" s="94" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="91" t="inlineStr">
+      <c r="B32" s="94" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="91" t="inlineStr">
+      <c r="C32" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2243,17 +2252,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="91" t="inlineStr">
+      <c r="A33" s="94" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="91" t="inlineStr">
+      <c r="B33" s="94" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="91" t="inlineStr">
+      <c r="C33" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2261,17 +2270,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="91" t="inlineStr">
+      <c r="A34" s="94" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="91" t="inlineStr">
+      <c r="B34" s="94" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="91" t="inlineStr">
+      <c r="C34" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2279,17 +2288,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="91" t="inlineStr">
+      <c r="A35" s="94" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="91" t="inlineStr">
+      <c r="B35" s="94" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="91" t="inlineStr">
+      <c r="C35" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2297,17 +2306,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="91" t="inlineStr">
+      <c r="A36" s="94" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="91" t="inlineStr">
+      <c r="B36" s="94" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="91" t="inlineStr">
+      <c r="C36" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2315,17 +2324,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="91" t="inlineStr">
+      <c r="A37" s="94" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="91" t="inlineStr">
+      <c r="B37" s="94" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="91" t="inlineStr">
+      <c r="C37" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2333,17 +2342,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="91" t="inlineStr">
+      <c r="A38" s="94" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="91" t="inlineStr">
+      <c r="B38" s="94" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="91" t="inlineStr">
+      <c r="C38" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2351,17 +2360,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="91" t="inlineStr">
+      <c r="A39" s="94" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="91" t="inlineStr">
+      <c r="B39" s="94" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="91" t="inlineStr">
+      <c r="C39" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2369,17 +2378,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="91" t="inlineStr">
+      <c r="A40" s="94" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="91" t="inlineStr">
+      <c r="B40" s="94" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="91" t="inlineStr">
+      <c r="C40" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2391,17 +2400,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="91" t="inlineStr">
+      <c r="A41" s="94" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="91" t="inlineStr">
+      <c r="B41" s="94" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="91" t="inlineStr">
+      <c r="C41" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2409,17 +2418,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="91" t="inlineStr">
+      <c r="A42" s="94" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="91" t="inlineStr">
+      <c r="B42" s="94" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="91" t="inlineStr">
+      <c r="C42" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2431,17 +2440,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="91" t="inlineStr">
+      <c r="A43" s="94" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="91" t="inlineStr">
+      <c r="B43" s="94" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="91" t="inlineStr">
+      <c r="C43" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2449,17 +2458,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="91" t="inlineStr">
+      <c r="A44" s="94" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="91" t="inlineStr">
+      <c r="B44" s="94" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="91" t="inlineStr">
+      <c r="C44" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2471,17 +2480,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="91" t="inlineStr">
+      <c r="A45" s="94" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="91" t="inlineStr">
+      <c r="B45" s="94" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="91" t="inlineStr">
+      <c r="C45" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2830,17 +2839,17 @@
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="90" t="inlineStr">
+      <c r="A6" s="93" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B6" s="90" t="inlineStr">
+      <c r="B6" s="93" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C6" s="90" t="inlineStr">
+      <c r="C6" s="93" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2865,49 +2874,49 @@
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
         </is>
       </c>
-      <c r="G6" s="90" t="n"/>
-      <c r="H6" s="90" t="n"/>
-      <c r="I6" s="90" t="inlineStr">
+      <c r="G6" s="93" t="n"/>
+      <c r="H6" s="93" t="n"/>
+      <c r="I6" s="93" t="inlineStr">
         <is>
           <t>atm_bt.mp3</t>
         </is>
       </c>
-      <c r="J6" s="90" t="inlineStr">
+      <c r="J6" s="93" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K6" s="90" t="n"/>
-      <c r="L6" s="90" t="n"/>
-      <c r="M6" s="90" t="inlineStr">
+      <c r="K6" s="93" t="n"/>
+      <c r="L6" s="93" t="n"/>
+      <c r="M6" s="93" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N6" s="91" t="inlineStr">
+      <c r="N6" s="94" t="inlineStr">
         <is>
           <t>ATMはどこ</t>
         </is>
       </c>
-      <c r="O6" s="91" t="n"/>
-      <c r="P6" s="91" t="inlineStr">
+      <c r="O6" s="94" t="n"/>
+      <c r="P6" s="94" t="inlineStr">
         <is>
           <t>2026-10-13 17:14</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="90" t="inlineStr">
+      <c r="A7" s="93" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B7" s="90" t="inlineStr">
+      <c r="B7" s="93" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C7" s="90" t="inlineStr">
+      <c r="C7" s="93" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2932,28 +2941,28 @@
           <t>海外のカードは鳩谷郵便局のATM、日本のカードは和田家前のJAのATMをご利用ください。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G7" s="90" t="n"/>
-      <c r="H7" s="90" t="n"/>
-      <c r="I7" s="90" t="inlineStr">
+      <c r="G7" s="93" t="n"/>
+      <c r="H7" s="93" t="n"/>
+      <c r="I7" s="93" t="inlineStr">
         <is>
           <t>atm_deai.mp3</t>
         </is>
       </c>
-      <c r="J7" s="90" t="inlineStr">
+      <c r="J7" s="93" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K7" s="90" t="n"/>
-      <c r="L7" s="90" t="n"/>
-      <c r="M7" s="90" t="inlineStr">
+      <c r="K7" s="93" t="n"/>
+      <c r="L7" s="93" t="n"/>
+      <c r="M7" s="93" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N7" s="91" t="n"/>
-      <c r="O7" s="91" t="n"/>
-      <c r="P7" s="91" t="inlineStr">
+      <c r="N7" s="94" t="n"/>
+      <c r="O7" s="94" t="n"/>
+      <c r="P7" s="94" t="inlineStr">
         <is>
           <t>2026-10-13 17:15</t>
         </is>
@@ -3009,17 +3018,17 @@
       </c>
     </row>
     <row r="9" ht="58.05" customHeight="1">
-      <c r="A9" s="90" t="inlineStr">
+      <c r="A9" s="93" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B9" s="90" t="inlineStr">
+      <c r="B9" s="93" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C9" s="90" t="inlineStr">
+      <c r="C9" s="93" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3039,45 +3048,45 @@
         </is>
       </c>
       <c r="F9" s="44" t="n"/>
-      <c r="G9" s="90" t="n"/>
-      <c r="H9" s="90" t="n"/>
-      <c r="I9" s="90" t="inlineStr">
+      <c r="G9" s="93" t="n"/>
+      <c r="H9" s="93" t="n"/>
+      <c r="I9" s="93" t="inlineStr">
         <is>
           <t>currency_exchange_bt.mp3</t>
         </is>
       </c>
-      <c r="J9" s="90" t="inlineStr">
+      <c r="J9" s="93" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K9" s="90" t="n"/>
-      <c r="L9" s="90" t="n"/>
-      <c r="M9" s="90" t="inlineStr">
+      <c r="K9" s="93" t="n"/>
+      <c r="L9" s="93" t="n"/>
+      <c r="M9" s="93" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N9" s="91" t="n"/>
-      <c r="O9" s="91" t="n"/>
-      <c r="P9" s="91" t="inlineStr">
+      <c r="N9" s="94" t="n"/>
+      <c r="O9" s="94" t="n"/>
+      <c r="P9" s="94" t="inlineStr">
         <is>
           <t>2026-10-13 17:18</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58.05" customHeight="1">
-      <c r="A10" s="90" t="inlineStr">
+      <c r="A10" s="93" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B10" s="90" t="inlineStr">
+      <c r="B10" s="93" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C10" s="90" t="inlineStr">
+      <c r="C10" s="93" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3097,45 +3106,45 @@
         </is>
       </c>
       <c r="F10" s="44" t="n"/>
-      <c r="G10" s="90" t="n"/>
-      <c r="H10" s="90" t="n"/>
-      <c r="I10" s="90" t="inlineStr">
+      <c r="G10" s="93" t="n"/>
+      <c r="H10" s="93" t="n"/>
+      <c r="I10" s="93" t="inlineStr">
         <is>
           <t>currency_exchange_deai.mp3</t>
         </is>
       </c>
-      <c r="J10" s="90" t="inlineStr">
+      <c r="J10" s="93" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K10" s="90" t="n"/>
-      <c r="L10" s="90" t="n"/>
-      <c r="M10" s="90" t="inlineStr">
+      <c r="K10" s="93" t="n"/>
+      <c r="L10" s="93" t="n"/>
+      <c r="M10" s="93" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N10" s="91" t="n"/>
-      <c r="O10" s="91" t="n"/>
-      <c r="P10" s="91" t="inlineStr">
+      <c r="N10" s="94" t="n"/>
+      <c r="O10" s="94" t="n"/>
+      <c r="P10" s="94" t="inlineStr">
         <is>
           <t>2026-10-13 17:19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58.05" customHeight="1">
-      <c r="A11" s="90" t="inlineStr">
+      <c r="A11" s="93" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B11" s="90" t="inlineStr">
+      <c r="B11" s="93" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C11" s="90" t="inlineStr">
+      <c r="C11" s="93" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3156,49 +3165,49 @@
         </is>
       </c>
       <c r="F11" s="44" t="n"/>
-      <c r="G11" s="90" t="n"/>
-      <c r="H11" s="90" t="n"/>
-      <c r="I11" s="90" t="inlineStr">
+      <c r="G11" s="93" t="n"/>
+      <c r="H11" s="93" t="n"/>
+      <c r="I11" s="93" t="inlineStr">
         <is>
           <t>luggage_bt.mp3</t>
         </is>
       </c>
-      <c r="J11" s="90" t="inlineStr">
+      <c r="J11" s="93" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K11" s="90" t="n"/>
-      <c r="L11" s="90" t="n"/>
-      <c r="M11" s="90" t="inlineStr">
+      <c r="K11" s="93" t="n"/>
+      <c r="L11" s="93" t="n"/>
+      <c r="M11" s="93" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N11" s="91" t="inlineStr">
+      <c r="N11" s="94" t="inlineStr">
         <is>
           <t>荷物を預けたい</t>
         </is>
       </c>
-      <c r="O11" s="91" t="n"/>
-      <c r="P11" s="91" t="inlineStr">
+      <c r="O11" s="94" t="n"/>
+      <c r="P11" s="94" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58.05" customHeight="1">
-      <c r="A12" s="90" t="inlineStr">
+      <c r="A12" s="93" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B12" s="90" t="inlineStr">
+      <c r="B12" s="93" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C12" s="90" t="inlineStr">
+      <c r="C12" s="93" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3219,28 +3228,28 @@
         </is>
       </c>
       <c r="F12" s="44" t="n"/>
-      <c r="G12" s="90" t="n"/>
-      <c r="H12" s="90" t="n"/>
-      <c r="I12" s="90" t="inlineStr">
+      <c r="G12" s="93" t="n"/>
+      <c r="H12" s="93" t="n"/>
+      <c r="I12" s="93" t="inlineStr">
         <is>
           <t>luggage_deai.mp3</t>
         </is>
       </c>
-      <c r="J12" s="90" t="inlineStr">
+      <c r="J12" s="93" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K12" s="90" t="n"/>
-      <c r="L12" s="90" t="n"/>
-      <c r="M12" s="90" t="inlineStr">
+      <c r="K12" s="93" t="n"/>
+      <c r="L12" s="93" t="n"/>
+      <c r="M12" s="93" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N12" s="91" t="n"/>
-      <c r="O12" s="91" t="n"/>
-      <c r="P12" s="91" t="inlineStr">
+      <c r="N12" s="94" t="n"/>
+      <c r="O12" s="94" t="n"/>
+      <c r="P12" s="94" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
@@ -3303,17 +3312,17 @@
       </c>
     </row>
     <row r="14" ht="58.05" customHeight="1">
-      <c r="A14" s="90" t="inlineStr">
+      <c r="A14" s="93" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B14" s="90" t="inlineStr">
+      <c r="B14" s="93" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C14" s="90" t="inlineStr">
+      <c r="C14" s="93" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3333,28 +3342,28 @@
         </is>
       </c>
       <c r="F14" s="44" t="n"/>
-      <c r="G14" s="90" t="n"/>
-      <c r="H14" s="90" t="n"/>
-      <c r="I14" s="90" t="inlineStr">
+      <c r="G14" s="93" t="n"/>
+      <c r="H14" s="93" t="n"/>
+      <c r="I14" s="93" t="inlineStr">
         <is>
           <t>stamp_bt.mp3</t>
         </is>
       </c>
-      <c r="J14" s="90" t="inlineStr">
+      <c r="J14" s="93" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K14" s="90" t="n"/>
-      <c r="L14" s="90" t="n"/>
-      <c r="M14" s="90" t="inlineStr">
+      <c r="K14" s="93" t="n"/>
+      <c r="L14" s="93" t="n"/>
+      <c r="M14" s="93" t="inlineStr">
         <is>
           <t>stamp</t>
         </is>
       </c>
-      <c r="N14" s="91" t="n"/>
-      <c r="O14" s="91" t="n"/>
-      <c r="P14" s="91" t="inlineStr">
+      <c r="N14" s="94" t="n"/>
+      <c r="O14" s="94" t="n"/>
+      <c r="P14" s="94" t="inlineStr">
         <is>
           <t>2026-10-13 17:22</t>
         </is>
@@ -3532,62 +3541,69 @@
       </c>
     </row>
     <row r="18" ht="58.05" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="97" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="97" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="97" t="inlineStr">
         <is>
           <t>sightseeing</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="44" t="inlineStr">
         <is>
           <t>展望台 行き方
 展望台 どうやって
 展望台 歩い
 城山 展望台
-展望台 行く</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>展望台へは、歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る道があり、およそ20分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>展望台へは、歩いておよそ20分、またはシャトルバスでお越しいただけます。詳しい道順は画面をご覧ください。</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="11" t="inlineStr">
+展望台 行く
+展望台 車で</t>
+        </is>
+      </c>
+      <c r="E18" s="44" t="inlineStr">
+        <is>
+          <t>展望台へは自家用車で行くことはできません。歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る約500mの坂道があり、およそ15分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
+        </is>
+      </c>
+      <c r="F18" s="44" t="inlineStr">
+        <is>
+          <t>展望台へは、自家用車で行くことはできません。歩いておよそ15分、またはシャトルバスでお越しいただけます。詳しい道順は画面をご覧ください。</t>
+        </is>
+      </c>
+      <c r="G18" s="97" t="n"/>
+      <c r="H18" s="97" t="n"/>
+      <c r="I18" s="97" t="inlineStr">
         <is>
           <t>observatory_access_bt.mp3</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J18" s="97" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K18" s="11" t="n"/>
-      <c r="L18" s="11" t="n"/>
-      <c r="M18" s="14" t="inlineStr">
+      <c r="K18" s="97" t="n"/>
+      <c r="L18" s="97" t="n"/>
+      <c r="M18" s="97" t="inlineStr">
         <is>
           <t>observatory_access</t>
         </is>
       </c>
-      <c r="N18" s="35" t="inlineStr">
+      <c r="N18" s="98" t="inlineStr">
         <is>
           <t>展望台への行き方</t>
+        </is>
+      </c>
+      <c r="O18" s="98" t="n"/>
+      <c r="P18" s="98" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:26</t>
         </is>
       </c>
     </row>
@@ -4957,17 +4973,17 @@
       </c>
     </row>
     <row r="43" ht="249.6" customHeight="1">
-      <c r="A43" s="90" t="inlineStr">
+      <c r="A43" s="93" t="inlineStr">
         <is>
           <t>guesthouse_access_deai</t>
         </is>
       </c>
-      <c r="B43" s="90" t="inlineStr">
+      <c r="B43" s="93" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C43" s="90" t="inlineStr">
+      <c r="C43" s="93" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -5001,30 +5017,30 @@
           <t>その建物は鳩谷八幡神社方面にあります。国道は交通量が多いため、川沿いの道をおすすめしております。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G43" s="90" t="inlineStr">
+      <c r="G43" s="93" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H43" s="90" t="n"/>
-      <c r="I43" s="90" t="inlineStr">
+      <c r="H43" s="93" t="n"/>
+      <c r="I43" s="93" t="inlineStr">
         <is>
           <t>guesthouse_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J43" s="90" t="inlineStr">
+      <c r="J43" s="93" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K43" s="90" t="n"/>
-      <c r="L43" s="90" t="n"/>
-      <c r="M43" s="90" t="inlineStr">
+      <c r="K43" s="93" t="n"/>
+      <c r="L43" s="93" t="n"/>
+      <c r="M43" s="93" t="inlineStr">
         <is>
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="91" t="n"/>
+      <c r="N43" s="94" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -6213,17 +6229,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="91" t="inlineStr">
+      <c r="A66" s="94" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="91" t="inlineStr">
+      <c r="B66" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="91" t="inlineStr">
+      <c r="C66" s="94" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -6253,26 +6269,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="91" t="inlineStr">
+      <c r="G66" s="94" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="91" t="n"/>
-      <c r="I66" s="91" t="inlineStr">
+      <c r="H66" s="94" t="n"/>
+      <c r="I66" s="94" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="91" t="inlineStr">
+      <c r="J66" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="91" t="n"/>
-      <c r="L66" s="91" t="n"/>
-      <c r="M66" s="91" t="n"/>
-      <c r="N66" s="91" t="n"/>
+      <c r="K66" s="94" t="n"/>
+      <c r="L66" s="94" t="n"/>
+      <c r="M66" s="94" t="n"/>
+      <c r="N66" s="94" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -7481,12 +7497,12 @@
       </c>
     </row>
     <row r="22" ht="64.8" customHeight="1">
-      <c r="A22" s="91" t="inlineStr">
+      <c r="A22" s="94" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B22" s="91" t="inlineStr">
+      <c r="B22" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7517,12 +7533,12 @@
       </c>
     </row>
     <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="91" t="inlineStr">
+      <c r="A23" s="94" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B23" s="91" t="inlineStr">
+      <c r="B23" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7553,12 +7569,12 @@
       </c>
     </row>
     <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="91" t="inlineStr">
+      <c r="A24" s="94" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B24" s="91" t="inlineStr">
+      <c r="B24" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7589,12 +7605,12 @@
       </c>
     </row>
     <row r="25" ht="81" customHeight="1">
-      <c r="A25" s="91" t="inlineStr">
+      <c r="A25" s="94" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B25" s="91" t="inlineStr">
+      <c r="B25" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7661,12 +7677,12 @@
       </c>
     </row>
     <row r="27" ht="64.8" customHeight="1">
-      <c r="A27" s="85" t="inlineStr">
+      <c r="A27" s="95" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B27" s="85" t="inlineStr">
+      <c r="B27" s="95" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7697,12 +7713,12 @@
       </c>
     </row>
     <row r="28" ht="64.8" customHeight="1">
-      <c r="A28" s="85" t="inlineStr">
+      <c r="A28" s="95" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B28" s="85" t="inlineStr">
+      <c r="B28" s="95" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7733,12 +7749,12 @@
       </c>
     </row>
     <row r="29" ht="64.8" customHeight="1">
-      <c r="A29" s="85" t="inlineStr">
+      <c r="A29" s="95" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B29" s="85" t="inlineStr">
+      <c r="B29" s="95" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7769,12 +7785,12 @@
       </c>
     </row>
     <row r="30" ht="81" customHeight="1">
-      <c r="A30" s="85" t="inlineStr">
+      <c r="A30" s="95" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B30" s="85" t="inlineStr">
+      <c r="B30" s="95" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7805,12 +7821,12 @@
       </c>
     </row>
     <row r="31" ht="64.8" customHeight="1">
-      <c r="A31" s="86" t="inlineStr">
+      <c r="A31" s="96" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B31" s="86" t="inlineStr">
+      <c r="B31" s="96" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8002,12 +8018,12 @@
       </c>
     </row>
     <row r="37" ht="64.8" customHeight="1">
-      <c r="A37" s="85" t="inlineStr">
+      <c r="A37" s="95" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B37" s="85" t="inlineStr">
+      <c r="B37" s="95" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8038,12 +8054,12 @@
       </c>
     </row>
     <row r="38" ht="64.8" customHeight="1">
-      <c r="A38" s="85" t="inlineStr">
+      <c r="A38" s="95" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B38" s="85" t="inlineStr">
+      <c r="B38" s="95" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8074,12 +8090,12 @@
       </c>
     </row>
     <row r="39" ht="64.8" customHeight="1">
-      <c r="A39" s="85" t="inlineStr">
+      <c r="A39" s="95" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B39" s="85" t="inlineStr">
+      <c r="B39" s="95" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8110,12 +8126,12 @@
       </c>
     </row>
     <row r="40" ht="113.4" customHeight="1">
-      <c r="A40" s="85" t="inlineStr">
+      <c r="A40" s="95" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B40" s="85" t="inlineStr">
+      <c r="B40" s="95" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8146,12 +8162,12 @@
       </c>
     </row>
     <row r="41" ht="97.2" customHeight="1">
-      <c r="A41" s="86" t="inlineStr">
+      <c r="A41" s="96" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B41" s="86" t="inlineStr">
+      <c r="B41" s="96" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8182,12 +8198,12 @@
       </c>
     </row>
     <row r="42" ht="64.8" customHeight="1">
-      <c r="A42" s="91" t="inlineStr">
+      <c r="A42" s="94" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B42" s="91" t="inlineStr">
+      <c r="B42" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8218,12 +8234,12 @@
       </c>
     </row>
     <row r="43" ht="64.8" customHeight="1">
-      <c r="A43" s="91" t="inlineStr">
+      <c r="A43" s="94" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B43" s="91" t="inlineStr">
+      <c r="B43" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8254,12 +8270,12 @@
       </c>
     </row>
     <row r="44" ht="81" customHeight="1">
-      <c r="A44" s="91" t="inlineStr">
+      <c r="A44" s="94" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B44" s="91" t="inlineStr">
+      <c r="B44" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8290,12 +8306,12 @@
       </c>
     </row>
     <row r="45" ht="64.8" customHeight="1">
-      <c r="A45" s="91" t="inlineStr">
+      <c r="A45" s="94" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B45" s="91" t="inlineStr">
+      <c r="B45" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8362,12 +8378,12 @@
       </c>
     </row>
     <row r="47" ht="81" customHeight="1">
-      <c r="A47" s="85" t="inlineStr">
+      <c r="A47" s="95" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B47" s="85" t="inlineStr">
+      <c r="B47" s="95" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8398,12 +8414,12 @@
       </c>
     </row>
     <row r="48" ht="64.8" customHeight="1">
-      <c r="A48" s="85" t="inlineStr">
+      <c r="A48" s="95" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B48" s="85" t="inlineStr">
+      <c r="B48" s="95" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8434,12 +8450,12 @@
       </c>
     </row>
     <row r="49" ht="64.8" customHeight="1">
-      <c r="A49" s="85" t="inlineStr">
+      <c r="A49" s="95" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B49" s="85" t="inlineStr">
+      <c r="B49" s="95" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8470,12 +8486,12 @@
       </c>
     </row>
     <row r="50" ht="64.8" customHeight="1">
-      <c r="A50" s="85" t="inlineStr">
+      <c r="A50" s="95" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B50" s="85" t="inlineStr">
+      <c r="B50" s="95" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8506,12 +8522,12 @@
       </c>
     </row>
     <row r="51" ht="48.6" customHeight="1">
-      <c r="A51" s="86" t="inlineStr">
+      <c r="A51" s="96" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B51" s="86" t="inlineStr">
+      <c r="B51" s="96" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8542,12 +8558,12 @@
       </c>
     </row>
     <row r="52" ht="48.6" customHeight="1">
-      <c r="A52" s="91" t="inlineStr">
+      <c r="A52" s="94" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B52" s="91" t="inlineStr">
+      <c r="B52" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8578,12 +8594,12 @@
       </c>
     </row>
     <row r="53" ht="97.2" customHeight="1">
-      <c r="A53" s="91" t="inlineStr">
+      <c r="A53" s="94" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B53" s="91" t="inlineStr">
+      <c r="B53" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8614,12 +8630,12 @@
       </c>
     </row>
     <row r="54" ht="97.2" customHeight="1">
-      <c r="A54" s="91" t="inlineStr">
+      <c r="A54" s="94" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B54" s="91" t="inlineStr">
+      <c r="B54" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8650,12 +8666,12 @@
       </c>
     </row>
     <row r="55" ht="97.2" customHeight="1">
-      <c r="A55" s="91" t="inlineStr">
+      <c r="A55" s="94" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B55" s="91" t="inlineStr">
+      <c r="B55" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8886,12 +8902,12 @@
       </c>
     </row>
     <row r="62" ht="81" customHeight="1">
-      <c r="A62" s="91" t="inlineStr">
+      <c r="A62" s="94" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B62" s="91" t="inlineStr">
+      <c r="B62" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8922,12 +8938,12 @@
       </c>
     </row>
     <row r="63" ht="97.2" customHeight="1">
-      <c r="A63" s="91" t="inlineStr">
+      <c r="A63" s="94" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B63" s="91" t="inlineStr">
+      <c r="B63" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8958,12 +8974,12 @@
       </c>
     </row>
     <row r="64" ht="97.2" customHeight="1">
-      <c r="A64" s="91" t="inlineStr">
+      <c r="A64" s="94" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B64" s="91" t="inlineStr">
+      <c r="B64" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8994,12 +9010,12 @@
       </c>
     </row>
     <row r="65" ht="97.2" customHeight="1">
-      <c r="A65" s="91" t="inlineStr">
+      <c r="A65" s="94" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B65" s="91" t="inlineStr">
+      <c r="B65" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -9576,32 +9592,36 @@
       </c>
     </row>
     <row r="82" ht="145.8" customHeight="1">
-      <c r="A82" s="21" t="inlineStr">
+      <c r="A82" s="98" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B82" s="21" t="inlineStr">
+      <c r="B82" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="C82" s="22" t="inlineStr">
-        <is>
-          <t>observatory get
-observatory walk
-observatory how
-viewpoint walk
-castle observatory
-go observatory</t>
-        </is>
-      </c>
-      <c r="D82" s="22" t="inlineStr">
-        <is>
-          <t>There are 2 ways to get to the observatory: on foot or by shuttle bus. To take the walking path, leave this building and go left for about 2 minutes, then turn left at a restaurant called Shiramizuen. Walk on with Wada House on your right, and at the end of the road there is a path going up to the left. It takes about 20 minutes to get there. To take the mountain trail, leave this building and go right. Just after you enter Route 360, climb the stairs and you will reach the Castle Ruins Observatory. To take the shuttle bus, leave this building and go left for about 2 minutes, and get on at the bus stop in front of the water-lily pond at Wada House.</t>
-        </is>
-      </c>
-      <c r="E82" s="21" t="n"/>
+      <c r="C82" s="46" t="inlineStr">
+        <is>
+          <t>How to get to the observation platform
+How do I reach the observation platform
+Walking to the observation platform
+Shiroyama observation platform
+Can I drive to the observation platform
+Shuttle bus observation platform</t>
+        </is>
+      </c>
+      <c r="D82" s="46" t="inlineStr">
+        <is>
+          <t>You cannot drive to the observation platform by private vehicle. There are two ways to reach it: walking or by shuttle bus. If you walk via the pedestrian path, exit this building and turn left. After about two minutes, you will see Hakusui-en restaurant. Turn left there. Continue with Wada-ke house on your right. At the end, there is a slope heading uphill to your left, approximately five hundred meters long. It will take about fifteen minutes to reach the top. If you prefer to walk via the mountain trail, exit this building and turn right. Enter National Route three hundred sixty. You will see stairs right away. Climb them and you will reach Shiroyama Castle observation platform. For the shuttle bus, exit this building and turn left. After about two minutes, you will find the bus stop in front of Wada-ke house Suiren Pond. Please board there.</t>
+        </is>
+      </c>
+      <c r="E82" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 展望台へは自家用車で行くことはできません。歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る約500mの坂道があり、およそ15分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
+        </is>
+      </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
           <t>展望台へは、歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る道があり、およそ20分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
@@ -9609,32 +9629,36 @@
       </c>
     </row>
     <row r="83" ht="145.8" customHeight="1">
-      <c r="A83" s="21" t="inlineStr">
+      <c r="A83" s="98" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B83" s="21" t="inlineStr">
+      <c r="B83" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="C83" s="22" t="inlineStr">
-        <is>
-          <t>mirador llegar
-mirador camin
-mirador pie
-mirador subir
-castillo mirador
-observatorio llegar</t>
-        </is>
-      </c>
-      <c r="D83" s="22" t="inlineStr">
-        <is>
-          <t>Puede ir al mirador a pie o en el autobús lanzadera. Si va por el sendero, salga de este edificio, gire a la izquierda, camine unos 2 minutos y gire a la izquierda en el restaurante Shiramizuen. Siga adelante con la Casa Wada a su derecha; al final encontrará un camino que sube hacia la izquierda y llegará en unos 20 minutos. Si prefiere el camino de montaña, salga de este edificio, vaya hacia la derecha, entre en la Ruta 360 y suba las escaleras que encontrará enseguida; así llegará al Mirador de las Ruinas del Castillo. Si va en autobús lanzadera, salga de este edificio, gire a la izquierda y, a unos 2 minutos, suba en la parada frente al estanque de nenúfares de la Casa Wada.</t>
-        </is>
-      </c>
-      <c r="E83" s="21" t="n"/>
+      <c r="C83" s="46" t="inlineStr">
+        <is>
+          <t>Cómo llegar al mirador
+Cómo ir al mirador
+Camino al mirador
+Mirador Shiroyama
+Puedo conducir al mirador
+Autobús lanzadera mirador</t>
+        </is>
+      </c>
+      <c r="D83" s="46" t="inlineStr">
+        <is>
+          <t>No puede acceder al mirador en vehículo privado. Hay dos formas de llegar: caminando o en autobús lanzadera. Si elige la ruta peatonal, salga de este edificio y gire a la izquierda. Después de aproximadamente dos minutos, verá un restaurante llamado Hakusui-en. Gire a la izquierda allí. Continúe con la casa Wada-ke a su derecha. Al final, hay una pendiente hacia arriba a su izquierda, de aproximadamente quinientos metros de largo. Tardará unos quince minutos en llegar a la cima. Si prefiere la ruta de montaña, salga de este edificio y gire a la derecha. Ingrese a la Ruta Nacional trescientos sesenta. Verá escaleras inmediatamente. Suba y llegará al mirador del castillo Shiroyama. Para el autobús lanzadera, salga de este edificio y gire a la izquierda. Después de aproximadamente dos minutos, encontrará la parada de autobús frente al estanque Suiren de la casa Wada-ke. Por favor, suba allí.</t>
+        </is>
+      </c>
+      <c r="E83" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 展望台へは自家用車で行くことはできません。歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る約500mの坂道があり、およそ15分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
+        </is>
+      </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
           <t>展望台へは、歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る道があり、およそ20分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
@@ -9642,32 +9666,36 @@
       </c>
     </row>
     <row r="84" ht="162" customHeight="1">
-      <c r="A84" s="21" t="inlineStr">
+      <c r="A84" s="98" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B84" s="21" t="inlineStr">
+      <c r="B84" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="C84" s="22" t="inlineStr">
-        <is>
-          <t>observatoire aller
-observatoire chemin
-observatoire pied
-château observatoire
-belvédère aller
-point de vue aller</t>
-        </is>
-      </c>
-      <c r="D84" s="22" t="inlineStr">
-        <is>
-          <t>Pour aller à l'observatoire, il y a deux possibilités : à pied ou en navette. Si vous prenez le sentier de promenade, sortez de ce bâtiment, tournez à gauche et marchez environ 2 minutes, puis tournez à gauche au restaurant Shiramizuen. Continuez en laissant la maison Wada sur votre droite ; au bout, un chemin monte sur la gauche, et vous arriverez en 20 minutes environ. Si vous prenez le sentier de montagne, sortez de ce bâtiment, tournez à droite, et juste après être entré sur la route 360, montez l'escalier : vous arriverez à l'observatoire des ruines du château. Pour la navette, sortez de ce bâtiment, tournez à gauche, et prenez-la à l'arrêt situé à environ 2 minutes, devant le bassin aux nénuphars de la maison Wada.</t>
-        </is>
-      </c>
-      <c r="E84" s="21" t="n"/>
+      <c r="C84" s="46" t="inlineStr">
+        <is>
+          <t>Comment aller au belvédère
+Accès au belvédère
+Chemin vers le belvédère
+Belvédère Shiroyama
+Voiture jusqu'au belvédère
+Bus navette belvédère</t>
+        </is>
+      </c>
+      <c r="D84" s="46" t="inlineStr">
+        <is>
+          <t>Vous ne pouvez pas accéder au belvédère en véhicule privé. Il y a deux façons de le rejoindre : à pied ou en bus navette. Si vous choisissez la route pédestre, sortez de ce bâtiment et tournez à gauche. Après environ deux minutes, vous verrez un restaurant appelé Hakusui-en. Tournez à gauche là-bas. Continuez avec la maison Wada-ke à votre droite. À la fin, il y a une pente ascendante à votre gauche, d'environ cinq cents mètres de long. Il faudra environ quinze minutes pour arriver au sommet. Si vous préférez l'itinéraire de montagne, sortez de ce bâtiment et tournez à droite. Entrez dans la Route nationale trois cent soixante. Vous verrez immédiatement des escaliers. Montez et vous arriverez au belvédère du château Shiroyama. Pour le bus navette, sortez de ce bâtiment et tournez à gauche. Après environ deux minutes, vous trouverez l'arrêt de bus devant l'étang Suiren de la maison Wada-ke. Veuillez monter à bord là-bas.</t>
+        </is>
+      </c>
+      <c r="E84" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 展望台へは自家用車で行くことはできません。歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る約500mの坂道があり、およそ15分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
+        </is>
+      </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
           <t>展望台へは、歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る道があり、およそ20分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
@@ -9675,32 +9703,36 @@
       </c>
     </row>
     <row r="85" ht="145.8" customHeight="1">
-      <c r="A85" s="21" t="inlineStr">
+      <c r="A85" s="98" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B85" s="21" t="inlineStr">
+      <c r="B85" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="C85" s="22" t="inlineStr">
-        <is>
-          <t>전망대 가는
-전망대 가려면
-전망대 어떻게
-전망대 걸어
-전망대 길
-성터 전망대</t>
-        </is>
-      </c>
-      <c r="D85" s="22" t="inlineStr">
-        <is>
-          <t>전망대까지는 걸어가는 방법과 셔틀버스를 타는 방법, 2가지가 있습니다. 산책로로 걸어가실 경우, 이 건물을 나가서 왼쪽으로 2분 정도 가신 뒤, 시라미즈엔이라는 음식점에서 왼쪽으로 도세요. 와다 가옥을 오른쪽에 두고 나아가면 막다른 곳에 왼쪽으로 올라가는 길이 있으며, 약 20분이면 도착합니다. 산길로 걸어가실 경우, 이 건물을 나가서 오른쪽으로 가신 뒤 국도 360호선에 들어서자마자 나오는 계단을 오르면 성터 전망대에 도착합니다. 셔틀버스를 이용하실 경우, 이 건물을 나가서 왼쪽으로 2분 정도 거리에 있는 와다 가옥 수련 연못 앞 버스 정류장에서 타 주세요.</t>
-        </is>
-      </c>
-      <c r="E85" s="21" t="n"/>
+      <c r="C85" s="46" t="inlineStr">
+        <is>
+          <t>전망대 가는 길
+전망대 어떻게 가
+전망대 걸어서
+성산 전망대
+전망대 자동차
+셔틀버스 전망대</t>
+        </is>
+      </c>
+      <c r="D85" s="46" t="inlineStr">
+        <is>
+          <t>전망대는 승용차로 갈 수 없습니다. 도보 또는 셔틀버스 두 가지 방법이 있습니다. 산책로를 걸어가시는 경우, 이 건물을 나가셔서 왼쪽으로 약 2분 정도 진행하시면 하쿠스이엔이라는 음식점이 있습니다. 그곳에서 왼쪽으로 꺾으세요. 와다케 집을 오른쪽에 두고 계속 진행하면, 끝에서 왼쪽으로 올라가는 약 5백 미터의 경사로가 있습니다. 약 15분이 소요됩니다. 산길로 걸어가시는 경우, 이 건물을 나가셔서 오른쪽으로 진행하고 국도 360호선에 들어가세요. 바로 계단이 보입니다. 계단을 올라가시면 시로야마 성터 전망대에 도착합니다. 셔틀버스를 이용하시는 경우, 이 건물을 나가셔서 왼쪽으로 약 2분 진행하면 와다케 집 수이렌 연못 앞의 버스 정류장이 있습니다. 그곳에서 탑승하세요.</t>
+        </is>
+      </c>
+      <c r="E85" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 展望台へは自家用車で行くことはできません。歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る約500mの坂道があり、およそ15分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
+        </is>
+      </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
           <t>展望台へは、歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る道があり、およそ20分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
@@ -9708,32 +9740,36 @@
       </c>
     </row>
     <row r="86" ht="145.8" customHeight="1">
-      <c r="A86" s="24" t="inlineStr">
+      <c r="A86" s="99" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B86" s="24" t="inlineStr">
+      <c r="B86" s="99" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C86" s="25" t="inlineStr">
-        <is>
-          <t>观景台 怎么去
-观景台 怎么走
-观景台 步行
-城山 观景台
-去观景台
-展望台</t>
-        </is>
-      </c>
-      <c r="D86" s="25" t="inlineStr">
-        <is>
-          <t>前往观景台有步行和乘坐接驳巴士两种方式。走游步道的话，出了这栋建筑向左走约2分钟，在一家叫白水园的餐厅处左转。经过右手边的和田家继续向前，尽头有一条向左上坡的路，大约20分钟可以到达。走山路的话，出了这栋建筑向右走，进入360号国道后立即登上台阶，即可到达城迹观景台。乘坐接驳巴士的话，请出了这栋建筑向左走约2分钟，在和田家睡莲池前的巴士站上车。</t>
-        </is>
-      </c>
-      <c r="E86" s="24" t="n"/>
+      <c r="C86" s="69" t="inlineStr">
+        <is>
+          <t>观景台怎么去
+观景台怎么走
+去观景台的路
+城山观景台
+观景台有车吗
+观景台巴士</t>
+        </is>
+      </c>
+      <c r="D86" s="69" t="inlineStr">
+        <is>
+          <t>您不能开私家车前往观景台。有两种方式可以到达：步行或乘坐接驳巴士。如果您选择沿着步道行走，请从本建筑物出口向左走，约两分钟后，您会看到一家名叫白水园的餐厅。在那里向左转。继续前进，右手边会看到和田家。走到尽头后，您会看到一条向左上坡的小路，约五百米长。大约需要十五分钟才能到达观景台。如果您想通过山道行走，从本建筑物出口向右走，进入国道三百六十号线。您会立即看到楼梯。爬上去后，您会到达城山城跡观景台。乘坐接驳巴士的话，从本建筑物出口向左走，约两分钟后，您会在和田家睡莲池前的公交车站找到车站。请在那里上车。</t>
+        </is>
+      </c>
+      <c r="E86" s="69" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 展望台へは自家用車で行くことはできません。歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る約500mの坂道があり、およそ15分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
+        </is>
+      </c>
       <c r="F86" s="26" t="inlineStr">
         <is>
           <t>展望台へは、歩きとシャトルバスの2通りがあります。遊歩道を歩く場合は、この建物を出て左へ2分ほど進み、白水園という飲食店のところを左に曲がります。和田家を右手に進むと、突き当りに左へ上る道があり、およそ20分で着きます。山道を歩く場合は、この建物を出て右へ進み、国道360号線に入ってすぐの階段を登ると城跡展望台に着きます。シャトルバスの場合は、この建物を出て左へ2分ほどの、和田家のすいれん池前のバス停からご乗車ください。</t>
@@ -16895,12 +16931,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="91" t="inlineStr">
+      <c r="A302" s="94" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="91" t="inlineStr">
+      <c r="B302" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16926,12 +16962,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="91" t="inlineStr">
+      <c r="A303" s="94" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="91" t="inlineStr">
+      <c r="B303" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16957,12 +16993,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="91" t="inlineStr">
+      <c r="A304" s="94" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="91" t="inlineStr">
+      <c r="B304" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -16988,12 +17024,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="91" t="inlineStr">
+      <c r="A305" s="94" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="91" t="inlineStr">
+      <c r="B305" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17019,12 +17055,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="91" t="inlineStr">
+      <c r="A306" s="94" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="91" t="inlineStr">
+      <c r="B306" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17050,12 +17086,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="91" t="inlineStr">
+      <c r="A307" s="94" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="91" t="inlineStr">
+      <c r="B307" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17081,12 +17117,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="91" t="inlineStr">
+      <c r="A308" s="94" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="91" t="inlineStr">
+      <c r="B308" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17112,12 +17148,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="91" t="inlineStr">
+      <c r="A309" s="94" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="91" t="inlineStr">
+      <c r="B309" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17143,12 +17179,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="91" t="inlineStr">
+      <c r="A310" s="94" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="91" t="inlineStr">
+      <c r="B310" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17174,12 +17210,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="91" t="inlineStr">
+      <c r="A311" s="94" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="91" t="inlineStr">
+      <c r="B311" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17205,12 +17241,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="91" t="inlineStr">
+      <c r="A312" s="94" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="91" t="inlineStr">
+      <c r="B312" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17235,12 +17271,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="91" t="inlineStr">
+      <c r="A313" s="94" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="91" t="inlineStr">
+      <c r="B313" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17265,12 +17301,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="91" t="inlineStr">
+      <c r="A314" s="94" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="91" t="inlineStr">
+      <c r="B314" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17295,12 +17331,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="91" t="inlineStr">
+      <c r="A315" s="94" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="91" t="inlineStr">
+      <c r="B315" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17325,12 +17361,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="91" t="inlineStr">
+      <c r="A316" s="94" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="91" t="inlineStr">
+      <c r="B316" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17355,12 +17391,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="91" t="inlineStr">
+      <c r="A317" s="94" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="91" t="inlineStr">
+      <c r="B317" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17386,12 +17422,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="91" t="inlineStr">
+      <c r="A318" s="94" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="91" t="inlineStr">
+      <c r="B318" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17417,12 +17453,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="91" t="inlineStr">
+      <c r="A319" s="94" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="91" t="inlineStr">
+      <c r="B319" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17448,12 +17484,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="91" t="inlineStr">
+      <c r="A320" s="94" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="91" t="inlineStr">
+      <c r="B320" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17479,12 +17515,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="91" t="inlineStr">
+      <c r="A321" s="94" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="91" t="inlineStr">
+      <c r="B321" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17510,12 +17546,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="91" t="inlineStr">
+      <c r="A322" s="94" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="91" t="inlineStr">
+      <c r="B322" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17540,12 +17576,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="91" t="inlineStr">
+      <c r="A323" s="94" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="91" t="inlineStr">
+      <c r="B323" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17570,12 +17606,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="91" t="inlineStr">
+      <c r="A324" s="94" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="91" t="inlineStr">
+      <c r="B324" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17600,12 +17636,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="91" t="inlineStr">
+      <c r="A325" s="94" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="91" t="inlineStr">
+      <c r="B325" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17630,12 +17666,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="91" t="inlineStr">
+      <c r="A326" s="94" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="91" t="inlineStr">
+      <c r="B326" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17660,12 +17696,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="91" t="inlineStr">
+      <c r="A327" s="94" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="91" t="inlineStr">
+      <c r="B327" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17692,12 +17728,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="91" t="inlineStr">
+      <c r="A328" s="94" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="91" t="inlineStr">
+      <c r="B328" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17724,12 +17760,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="91" t="inlineStr">
+      <c r="A329" s="94" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="91" t="inlineStr">
+      <c r="B329" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17756,12 +17792,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="91" t="inlineStr">
+      <c r="A330" s="94" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="91" t="inlineStr">
+      <c r="B330" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17788,12 +17824,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="91" t="inlineStr">
+      <c r="A331" s="94" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="91" t="inlineStr">
+      <c r="B331" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17820,12 +17856,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="91" t="inlineStr">
+      <c r="A332" s="94" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="91" t="inlineStr">
+      <c r="B332" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17852,12 +17888,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="91" t="inlineStr">
+      <c r="A333" s="94" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="91" t="inlineStr">
+      <c r="B333" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17884,12 +17920,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="91" t="inlineStr">
+      <c r="A334" s="94" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="91" t="inlineStr">
+      <c r="B334" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17916,12 +17952,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="91" t="inlineStr">
+      <c r="A335" s="94" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="91" t="inlineStr">
+      <c r="B335" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17948,12 +17984,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="91" t="inlineStr">
+      <c r="A336" s="94" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="91" t="inlineStr">
+      <c r="B336" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17980,12 +18016,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="91" t="inlineStr">
+      <c r="A337" s="94" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="91" t="inlineStr">
+      <c r="B337" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18012,12 +18048,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="91" t="inlineStr">
+      <c r="A338" s="94" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="91" t="inlineStr">
+      <c r="B338" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18044,12 +18080,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="91" t="inlineStr">
+      <c r="A339" s="94" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="91" t="inlineStr">
+      <c r="B339" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18076,12 +18112,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="91" t="inlineStr">
+      <c r="A340" s="94" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="91" t="inlineStr">
+      <c r="B340" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18108,12 +18144,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="91" t="inlineStr">
+      <c r="A341" s="94" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="91" t="inlineStr">
+      <c r="B341" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18140,12 +18176,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="91" t="inlineStr">
+      <c r="A342" s="94" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="91" t="inlineStr">
+      <c r="B342" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18172,12 +18208,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="91" t="inlineStr">
+      <c r="A343" s="94" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="91" t="inlineStr">
+      <c r="B343" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18204,12 +18240,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="91" t="inlineStr">
+      <c r="A344" s="94" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="91" t="inlineStr">
+      <c r="B344" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18236,12 +18272,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="91" t="inlineStr">
+      <c r="A345" s="94" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="91" t="inlineStr">
+      <c r="B345" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18268,12 +18304,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="91" t="inlineStr">
+      <c r="A346" s="94" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="91" t="inlineStr">
+      <c r="B346" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18300,12 +18336,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="91" t="inlineStr">
+      <c r="A347" s="94" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="91" t="inlineStr">
+      <c r="B347" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18332,12 +18368,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="91" t="inlineStr">
+      <c r="A348" s="94" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="91" t="inlineStr">
+      <c r="B348" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18364,12 +18400,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="91" t="inlineStr">
+      <c r="A349" s="94" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="91" t="inlineStr">
+      <c r="B349" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18396,12 +18432,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="91" t="inlineStr">
+      <c r="A350" s="94" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="91" t="inlineStr">
+      <c r="B350" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18428,12 +18464,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="91" t="inlineStr">
+      <c r="A351" s="94" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="91" t="inlineStr">
+      <c r="B351" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18460,12 +18496,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="91" t="inlineStr">
+      <c r="A352" s="94" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="91" t="inlineStr">
+      <c r="B352" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18491,12 +18527,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="91" t="inlineStr">
+      <c r="A353" s="94" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="91" t="inlineStr">
+      <c r="B353" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18522,12 +18558,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="91" t="inlineStr">
+      <c r="A354" s="94" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="91" t="inlineStr">
+      <c r="B354" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18553,12 +18589,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="91" t="inlineStr">
+      <c r="A355" s="94" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="91" t="inlineStr">
+      <c r="B355" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18584,12 +18620,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="91" t="inlineStr">
+      <c r="A356" s="94" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="91" t="inlineStr">
+      <c r="B356" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18615,12 +18651,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="91" t="inlineStr">
+      <c r="A357" s="94" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="91" t="inlineStr">
+      <c r="B357" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18646,12 +18682,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="91" t="inlineStr">
+      <c r="A358" s="94" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="91" t="inlineStr">
+      <c r="B358" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18677,12 +18713,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="91" t="inlineStr">
+      <c r="A359" s="94" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="91" t="inlineStr">
+      <c r="B359" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18708,12 +18744,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="91" t="inlineStr">
+      <c r="A360" s="94" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="91" t="inlineStr">
+      <c r="B360" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18739,12 +18775,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="91" t="inlineStr">
+      <c r="A361" s="94" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="91" t="inlineStr">
+      <c r="B361" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18770,12 +18806,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="91" t="inlineStr">
+      <c r="A362" s="94" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="91" t="inlineStr">
+      <c r="B362" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18802,12 +18838,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="91" t="inlineStr">
+      <c r="A363" s="94" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="91" t="inlineStr">
+      <c r="B363" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18834,12 +18870,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="91" t="inlineStr">
+      <c r="A364" s="94" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="91" t="inlineStr">
+      <c r="B364" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18866,12 +18902,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="91" t="inlineStr">
+      <c r="A365" s="94" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="91" t="inlineStr">
+      <c r="B365" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18898,12 +18934,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="91" t="inlineStr">
+      <c r="A366" s="94" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="91" t="inlineStr">
+      <c r="B366" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18930,12 +18966,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="91" t="inlineStr">
+      <c r="A367" s="94" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="91" t="inlineStr">
+      <c r="B367" s="94" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18962,12 +18998,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="91" t="inlineStr">
+      <c r="A368" s="94" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="91" t="inlineStr">
+      <c r="B368" s="94" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18994,12 +19030,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="91" t="inlineStr">
+      <c r="A369" s="94" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="91" t="inlineStr">
+      <c r="B369" s="94" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -19026,12 +19062,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="91" t="inlineStr">
+      <c r="A370" s="94" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="91" t="inlineStr">
+      <c r="B370" s="94" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -19058,12 +19094,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="91" t="inlineStr">
+      <c r="A371" s="94" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="91" t="inlineStr">
+      <c r="B371" s="94" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -20199,7 +20235,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="91" t="inlineStr">
+      <c r="A2" s="94" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -20209,7 +20245,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="91" t="inlineStr">
+      <c r="C2" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20221,7 +20257,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="91" t="inlineStr">
+      <c r="A3" s="94" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -20231,7 +20267,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="91" t="inlineStr">
+      <c r="C3" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20243,7 +20279,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="91" t="inlineStr">
+      <c r="A4" s="94" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -20253,7 +20289,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="91" t="inlineStr">
+      <c r="C4" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20265,7 +20301,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="91" t="inlineStr">
+      <c r="A5" s="94" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -20275,7 +20311,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="91" t="inlineStr">
+      <c r="C5" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20287,7 +20323,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="91" t="inlineStr">
+      <c r="A6" s="94" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20297,7 +20333,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="91" t="inlineStr">
+      <c r="C6" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20309,7 +20345,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="91" t="inlineStr">
+      <c r="A7" s="94" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20319,7 +20355,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="91" t="inlineStr">
+      <c r="C7" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20331,7 +20367,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="91" t="inlineStr">
+      <c r="A8" s="94" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20341,7 +20377,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="91" t="inlineStr">
+      <c r="C8" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20353,7 +20389,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="91" t="inlineStr">
+      <c r="A9" s="94" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20363,7 +20399,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="91" t="inlineStr">
+      <c r="C9" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20375,7 +20411,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="91" t="inlineStr">
+      <c r="A10" s="94" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20385,7 +20421,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="91" t="inlineStr">
+      <c r="C10" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20397,7 +20433,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="91" t="inlineStr">
+      <c r="A11" s="94" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20407,7 +20443,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="91" t="inlineStr">
+      <c r="C11" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20419,7 +20455,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="91" t="inlineStr">
+      <c r="A12" s="94" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20429,7 +20465,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="91" t="inlineStr">
+      <c r="C12" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20441,7 +20477,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="91" t="inlineStr">
+      <c r="A13" s="94" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20451,7 +20487,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="91" t="inlineStr">
+      <c r="C13" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20593,53 +20629,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="91" t="inlineStr">
+      <c r="A2" s="94" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="91" t="inlineStr">
+      <c r="B2" s="94" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="91" t="inlineStr">
+      <c r="C2" s="94" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="91" t="inlineStr">
+      <c r="D2" s="94" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="91" t="inlineStr">
+      <c r="E2" s="94" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="91" t="inlineStr">
+      <c r="F2" s="94" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="91" t="inlineStr">
+      <c r="G2" s="94" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="91" t="inlineStr">
+      <c r="H2" s="94" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="91" t="inlineStr">
+      <c r="I2" s="94" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="91" t="n"/>
-      <c r="K2" s="91" t="inlineStr">
+      <c r="J2" s="94" t="n"/>
+      <c r="K2" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20676,45 +20712,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="91" t="inlineStr">
+      <c r="A3" s="94" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="91" t="inlineStr">
+      <c r="B3" s="94" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="91" t="inlineStr">
+      <c r="C3" s="94" t="inlineStr">
         <is>
           <t>main_idle_20261013044809.png</t>
         </is>
       </c>
-      <c r="D3" s="91" t="n"/>
-      <c r="E3" s="91" t="n"/>
-      <c r="F3" s="91" t="n">
+      <c r="D3" s="94" t="n"/>
+      <c r="E3" s="94" t="n"/>
+      <c r="F3" s="94" t="n">
         <v>0.179</v>
       </c>
-      <c r="G3" s="91" t="n">
+      <c r="G3" s="94" t="n">
         <v>0.23</v>
       </c>
-      <c r="H3" s="91" t="inlineStr">
+      <c r="H3" s="94" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="91" t="inlineStr">
+      <c r="I3" s="94" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="91" t="inlineStr">
+      <c r="J3" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="91" t="inlineStr">
+      <c r="K3" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20751,45 +20787,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="91" t="inlineStr">
+      <c r="A4" s="94" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="91" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="91" t="inlineStr">
+      <c r="C4" s="94" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="91" t="n"/>
-      <c r="E4" s="91" t="n"/>
-      <c r="F4" s="91" t="inlineStr">
+      <c r="D4" s="94" t="n"/>
+      <c r="E4" s="94" t="n"/>
+      <c r="F4" s="94" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="91" t="inlineStr">
+      <c r="G4" s="94" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="91" t="inlineStr">
+      <c r="H4" s="94" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="91" t="inlineStr">
+      <c r="I4" s="94" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="91" t="n"/>
-      <c r="K4" s="91" t="inlineStr">
+      <c r="J4" s="94" t="n"/>
+      <c r="K4" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20826,45 +20862,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="91" t="inlineStr">
+      <c r="A5" s="94" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="91" t="inlineStr">
+      <c r="B5" s="94" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="91" t="inlineStr">
+      <c r="C5" s="94" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="91" t="n"/>
-      <c r="E5" s="91" t="n"/>
-      <c r="F5" s="91" t="inlineStr">
+      <c r="D5" s="94" t="n"/>
+      <c r="E5" s="94" t="n"/>
+      <c r="F5" s="94" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="91" t="inlineStr">
+      <c r="G5" s="94" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="91" t="inlineStr">
+      <c r="H5" s="94" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="91" t="inlineStr">
+      <c r="I5" s="94" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="91" t="n"/>
-      <c r="K5" s="91" t="inlineStr">
+      <c r="J5" s="94" t="n"/>
+      <c r="K5" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20901,45 +20937,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="91" t="inlineStr">
+      <c r="A6" s="94" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="91" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="91" t="inlineStr">
+      <c r="C6" s="94" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="91" t="n"/>
-      <c r="E6" s="91" t="n"/>
-      <c r="F6" s="91" t="inlineStr">
+      <c r="D6" s="94" t="n"/>
+      <c r="E6" s="94" t="n"/>
+      <c r="F6" s="94" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="91" t="inlineStr">
+      <c r="G6" s="94" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="91" t="inlineStr">
+      <c r="H6" s="94" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="91" t="inlineStr">
+      <c r="I6" s="94" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="91" t="n"/>
-      <c r="K6" s="91" t="inlineStr">
+      <c r="J6" s="94" t="n"/>
+      <c r="K6" s="94" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -21061,12 +21097,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="91" t="inlineStr">
+      <c r="A2" s="94" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B2" s="91" t="inlineStr">
+      <c r="B2" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21105,12 +21141,12 @@
       <c r="J2" s="46" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="91" t="inlineStr">
+      <c r="A3" s="94" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B3" s="91" t="inlineStr">
+      <c r="B3" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21149,12 +21185,12 @@
       <c r="J3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="91" t="inlineStr">
+      <c r="A4" s="94" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B4" s="91" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21193,12 +21229,12 @@
       <c r="J4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="91" t="inlineStr">
+      <c r="A5" s="94" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B5" s="91" t="inlineStr">
+      <c r="B5" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21237,12 +21273,12 @@
       <c r="J5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="91" t="inlineStr">
+      <c r="A6" s="94" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B6" s="91" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21281,12 +21317,12 @@
       <c r="J6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="91" t="inlineStr">
+      <c r="A7" s="94" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B7" s="91" t="inlineStr">
+      <c r="B7" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21325,12 +21361,12 @@
       <c r="J7" s="46" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="91" t="inlineStr">
+      <c r="A8" s="94" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B8" s="91" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21369,12 +21405,12 @@
       <c r="J8" s="46" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="91" t="inlineStr">
+      <c r="A9" s="94" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B9" s="91" t="inlineStr">
+      <c r="B9" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21413,12 +21449,12 @@
       <c r="J9" s="46" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="91" t="inlineStr">
+      <c r="A10" s="94" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B10" s="91" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21457,12 +21493,12 @@
       <c r="J10" s="46" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="91" t="inlineStr">
+      <c r="A11" s="94" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B11" s="91" t="inlineStr">
+      <c r="B11" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21501,12 +21537,12 @@
       <c r="J11" s="46" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="91" t="inlineStr">
+      <c r="A12" s="94" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B12" s="91" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21545,12 +21581,12 @@
       <c r="J12" s="46" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="91" t="inlineStr">
+      <c r="A13" s="94" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B13" s="91" t="inlineStr">
+      <c r="B13" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21608,12 +21644,12 @@
       <c r="J13" s="46" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="91" t="inlineStr">
+      <c r="A14" s="94" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B14" s="91" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21671,12 +21707,12 @@
       <c r="J14" s="46" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="91" t="inlineStr">
+      <c r="A15" s="94" t="inlineStr">
         <is>
           <t>趣味</t>
         </is>
       </c>
-      <c r="B15" s="91" t="inlineStr">
+      <c r="B15" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21737,12 +21773,12 @@
       <c r="J15" s="46" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="91" t="inlineStr">
+      <c r="A16" s="94" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B16" s="91" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21802,12 +21838,12 @@
       <c r="J16" s="46" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="91" t="inlineStr">
+      <c r="A17" s="94" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B17" s="91" t="inlineStr">
+      <c r="B17" s="94" t="inlineStr">
         <is>
           <t>共通</t>
         </is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -546,6 +546,18 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1248,7 +1260,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="94" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1258,31 +1270,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="94" t="n">
+      <c r="C2" s="98" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="94" t="n">
+      <c r="D2" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="94" t="n">
+      <c r="E2" s="98" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="94" t="n">
+      <c r="F2" s="98" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="94" t="n">
+      <c r="G2" s="98" t="n">
         <v>0.957</v>
       </c>
-      <c r="H2" s="94" t="n">
+      <c r="H2" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="94" t="n">
+      <c r="I2" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="94" t="n">
+      <c r="J2" s="98" t="n">
         <v>0.864</v>
       </c>
-      <c r="K2" s="94" t="n">
+      <c r="K2" s="98" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1292,7 +1304,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="94" t="inlineStr">
+      <c r="A3" s="98" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1302,31 +1314,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="94" t="n">
+      <c r="C3" s="98" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="94" t="n">
+      <c r="D3" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="94" t="n">
+      <c r="E3" s="98" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="94" t="n">
+      <c r="F3" s="98" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="94" t="n">
+      <c r="G3" s="98" t="n">
         <v>0.929</v>
       </c>
-      <c r="H3" s="94" t="n">
+      <c r="H3" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="94" t="n">
+      <c r="I3" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="94" t="n">
+      <c r="J3" s="98" t="n">
         <v>0.753</v>
       </c>
-      <c r="K3" s="94" t="n">
+      <c r="K3" s="98" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1336,7 +1348,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="94" t="inlineStr">
+      <c r="A4" s="98" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1346,31 +1358,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="94" t="n">
+      <c r="C4" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="94" t="n">
+      <c r="D4" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="94" t="n">
+      <c r="E4" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="94" t="n">
+      <c r="F4" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="94" t="n">
+      <c r="G4" s="98" t="n">
         <v>0.92</v>
       </c>
-      <c r="H4" s="94" t="n">
+      <c r="H4" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="94" t="n">
+      <c r="I4" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="94" t="n">
+      <c r="J4" s="98" t="n">
         <v>0.884</v>
       </c>
-      <c r="K4" s="94" t="n">
+      <c r="K4" s="98" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1442,7 +1454,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="94" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1452,10 +1464,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="94" t="n">
+      <c r="C2" s="98" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="94" t="n">
+      <c r="D2" s="98" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1465,7 +1477,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="94" t="inlineStr">
+      <c r="A3" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1475,16 +1487,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="94" t="n">
+      <c r="C3" s="98" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="94" t="n">
+      <c r="D3" s="98" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="94" t="inlineStr">
+      <c r="A4" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1494,16 +1506,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="94" t="n">
+      <c r="C4" s="98" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="94" t="n">
+      <c r="D4" s="98" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="94" t="inlineStr">
+      <c r="A5" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1513,16 +1525,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="94" t="n">
+      <c r="C5" s="98" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="94" t="n">
+      <c r="D5" s="98" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="94" t="inlineStr">
+      <c r="A6" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1532,16 +1544,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="94" t="n">
+      <c r="C6" s="98" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="94" t="n">
+      <c r="D6" s="98" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="94" t="inlineStr">
+      <c r="A7" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1551,10 +1563,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="94" t="n">
+      <c r="C7" s="98" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="94" t="n">
+      <c r="D7" s="98" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1614,17 +1626,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="94" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="94" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="94" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1636,17 +1648,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="94" t="inlineStr">
+      <c r="A3" s="98" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="94" t="inlineStr">
+      <c r="B3" s="98" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="94" t="inlineStr">
+      <c r="C3" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1654,17 +1666,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="94" t="inlineStr">
+      <c r="A4" s="98" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="94" t="inlineStr">
+      <c r="B4" s="98" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1676,17 +1688,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="94" t="inlineStr">
+      <c r="A5" s="98" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="94" t="inlineStr">
+      <c r="B5" s="98" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="94" t="inlineStr">
+      <c r="C5" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1698,17 +1710,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="94" t="inlineStr">
+      <c r="A6" s="98" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="94" t="inlineStr">
+      <c r="B6" s="98" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1716,17 +1728,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="94" t="inlineStr">
+      <c r="A7" s="98" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="94" t="inlineStr">
+      <c r="B7" s="98" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="94" t="inlineStr">
+      <c r="C7" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1734,17 +1746,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="94" t="inlineStr">
+      <c r="A8" s="98" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="94" t="inlineStr">
+      <c r="B8" s="98" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1756,17 +1768,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="94" t="inlineStr">
+      <c r="A9" s="98" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="94" t="inlineStr">
+      <c r="B9" s="98" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="94" t="inlineStr">
+      <c r="C9" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1778,17 +1790,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="94" t="inlineStr">
+      <c r="A10" s="98" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="94" t="inlineStr">
+      <c r="B10" s="98" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1800,17 +1812,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="94" t="inlineStr">
+      <c r="A11" s="98" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="94" t="inlineStr">
+      <c r="B11" s="98" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="94" t="inlineStr">
+      <c r="C11" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1818,17 +1830,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="94" t="inlineStr">
+      <c r="A12" s="98" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="94" t="inlineStr">
+      <c r="B12" s="98" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1836,17 +1848,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="94" t="inlineStr">
+      <c r="A13" s="98" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="94" t="inlineStr">
+      <c r="B13" s="98" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="94" t="inlineStr">
+      <c r="C13" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1858,17 +1870,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="94" t="inlineStr">
+      <c r="A14" s="98" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="94" t="inlineStr">
+      <c r="B14" s="98" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1880,17 +1892,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="94" t="inlineStr">
+      <c r="A15" s="98" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="94" t="inlineStr">
+      <c r="B15" s="98" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="94" t="inlineStr">
+      <c r="C15" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1902,17 +1914,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="94" t="inlineStr">
+      <c r="A16" s="98" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="94" t="inlineStr">
+      <c r="B16" s="98" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1924,17 +1936,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="94" t="inlineStr">
+      <c r="A17" s="98" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="94" t="inlineStr">
+      <c r="B17" s="98" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="94" t="inlineStr">
+      <c r="C17" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1946,17 +1958,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="94" t="inlineStr">
+      <c r="A18" s="98" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="94" t="inlineStr">
+      <c r="B18" s="98" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C18" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1968,17 +1980,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="94" t="inlineStr">
+      <c r="A19" s="98" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="94" t="inlineStr">
+      <c r="B19" s="98" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="94" t="inlineStr">
+      <c r="C19" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1986,17 +1998,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="94" t="inlineStr">
+      <c r="A20" s="98" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="94" t="inlineStr">
+      <c r="B20" s="98" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="94" t="inlineStr">
+      <c r="C20" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2004,17 +2016,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="94" t="inlineStr">
+      <c r="A21" s="98" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="94" t="inlineStr">
+      <c r="B21" s="98" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="94" t="inlineStr">
+      <c r="C21" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2026,17 +2038,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="94" t="inlineStr">
+      <c r="A22" s="98" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="94" t="inlineStr">
+      <c r="B22" s="98" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="94" t="inlineStr">
+      <c r="C22" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2048,17 +2060,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="94" t="inlineStr">
+      <c r="A23" s="98" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="94" t="inlineStr">
+      <c r="B23" s="98" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="94" t="inlineStr">
+      <c r="C23" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2070,17 +2082,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="94" t="inlineStr">
+      <c r="A24" s="98" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="94" t="inlineStr">
+      <c r="B24" s="98" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="94" t="inlineStr">
+      <c r="C24" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2092,17 +2104,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="94" t="inlineStr">
+      <c r="A25" s="98" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="94" t="inlineStr">
+      <c r="B25" s="98" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="94" t="inlineStr">
+      <c r="C25" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2110,17 +2122,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="94" t="inlineStr">
+      <c r="A26" s="98" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="94" t="inlineStr">
+      <c r="B26" s="98" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="94" t="inlineStr">
+      <c r="C26" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2128,17 +2140,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="94" t="inlineStr">
+      <c r="A27" s="98" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="94" t="inlineStr">
+      <c r="B27" s="98" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="94" t="inlineStr">
+      <c r="C27" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2150,17 +2162,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="94" t="inlineStr">
+      <c r="A28" s="98" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="94" t="inlineStr">
+      <c r="B28" s="98" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="94" t="inlineStr">
+      <c r="C28" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2172,17 +2184,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="94" t="inlineStr">
+      <c r="A29" s="98" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="94" t="inlineStr">
+      <c r="B29" s="98" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="94" t="inlineStr">
+      <c r="C29" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2194,17 +2206,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="94" t="inlineStr">
+      <c r="A30" s="98" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="94" t="inlineStr">
+      <c r="B30" s="98" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="94" t="inlineStr">
+      <c r="C30" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2212,17 +2224,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="94" t="inlineStr">
+      <c r="A31" s="98" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="94" t="inlineStr">
+      <c r="B31" s="98" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="94" t="inlineStr">
+      <c r="C31" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2234,17 +2246,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="94" t="inlineStr">
+      <c r="A32" s="98" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="94" t="inlineStr">
+      <c r="B32" s="98" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="94" t="inlineStr">
+      <c r="C32" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2252,17 +2264,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="94" t="inlineStr">
+      <c r="A33" s="98" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="94" t="inlineStr">
+      <c r="B33" s="98" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="94" t="inlineStr">
+      <c r="C33" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2270,17 +2282,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="94" t="inlineStr">
+      <c r="A34" s="98" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="94" t="inlineStr">
+      <c r="B34" s="98" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="94" t="inlineStr">
+      <c r="C34" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2288,17 +2300,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="94" t="inlineStr">
+      <c r="A35" s="98" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="94" t="inlineStr">
+      <c r="B35" s="98" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="94" t="inlineStr">
+      <c r="C35" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2306,17 +2318,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="94" t="inlineStr">
+      <c r="A36" s="98" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="94" t="inlineStr">
+      <c r="B36" s="98" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="94" t="inlineStr">
+      <c r="C36" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2324,17 +2336,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="94" t="inlineStr">
+      <c r="A37" s="98" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="94" t="inlineStr">
+      <c r="B37" s="98" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="94" t="inlineStr">
+      <c r="C37" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2342,17 +2354,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="94" t="inlineStr">
+      <c r="A38" s="98" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="94" t="inlineStr">
+      <c r="B38" s="98" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="94" t="inlineStr">
+      <c r="C38" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2360,17 +2372,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="94" t="inlineStr">
+      <c r="A39" s="98" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="94" t="inlineStr">
+      <c r="B39" s="98" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="94" t="inlineStr">
+      <c r="C39" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2378,17 +2390,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="94" t="inlineStr">
+      <c r="A40" s="98" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="94" t="inlineStr">
+      <c r="B40" s="98" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="94" t="inlineStr">
+      <c r="C40" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2400,17 +2412,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="94" t="inlineStr">
+      <c r="A41" s="98" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="94" t="inlineStr">
+      <c r="B41" s="98" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="94" t="inlineStr">
+      <c r="C41" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2418,17 +2430,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="94" t="inlineStr">
+      <c r="A42" s="98" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="94" t="inlineStr">
+      <c r="B42" s="98" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="94" t="inlineStr">
+      <c r="C42" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2440,17 +2452,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="94" t="inlineStr">
+      <c r="A43" s="98" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="94" t="inlineStr">
+      <c r="B43" s="98" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="94" t="inlineStr">
+      <c r="C43" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2458,17 +2470,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="94" t="inlineStr">
+      <c r="A44" s="98" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="94" t="inlineStr">
+      <c r="B44" s="98" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="94" t="inlineStr">
+      <c r="C44" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2480,17 +2492,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="94" t="inlineStr">
+      <c r="A45" s="98" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="94" t="inlineStr">
+      <c r="B45" s="98" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="94" t="inlineStr">
+      <c r="C45" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2839,17 +2851,17 @@
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="93" t="inlineStr">
+      <c r="A6" s="97" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B6" s="93" t="inlineStr">
+      <c r="B6" s="97" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C6" s="93" t="inlineStr">
+      <c r="C6" s="97" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2874,49 +2886,49 @@
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
         </is>
       </c>
-      <c r="G6" s="93" t="n"/>
-      <c r="H6" s="93" t="n"/>
-      <c r="I6" s="93" t="inlineStr">
+      <c r="G6" s="97" t="n"/>
+      <c r="H6" s="97" t="n"/>
+      <c r="I6" s="97" t="inlineStr">
         <is>
           <t>atm_bt.mp3</t>
         </is>
       </c>
-      <c r="J6" s="93" t="inlineStr">
+      <c r="J6" s="97" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K6" s="93" t="n"/>
-      <c r="L6" s="93" t="n"/>
-      <c r="M6" s="93" t="inlineStr">
+      <c r="K6" s="97" t="n"/>
+      <c r="L6" s="97" t="n"/>
+      <c r="M6" s="97" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N6" s="94" t="inlineStr">
+      <c r="N6" s="98" t="inlineStr">
         <is>
           <t>ATMはどこ</t>
         </is>
       </c>
-      <c r="O6" s="94" t="n"/>
-      <c r="P6" s="94" t="inlineStr">
+      <c r="O6" s="98" t="n"/>
+      <c r="P6" s="98" t="inlineStr">
         <is>
           <t>2026-10-13 17:14</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="93" t="inlineStr">
+      <c r="A7" s="97" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C7" s="93" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2941,28 +2953,28 @@
           <t>海外のカードは鳩谷郵便局のATM、日本のカードは和田家前のJAのATMをご利用ください。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G7" s="93" t="n"/>
-      <c r="H7" s="93" t="n"/>
-      <c r="I7" s="93" t="inlineStr">
+      <c r="G7" s="97" t="n"/>
+      <c r="H7" s="97" t="n"/>
+      <c r="I7" s="97" t="inlineStr">
         <is>
           <t>atm_deai.mp3</t>
         </is>
       </c>
-      <c r="J7" s="93" t="inlineStr">
+      <c r="J7" s="97" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K7" s="93" t="n"/>
-      <c r="L7" s="93" t="n"/>
-      <c r="M7" s="93" t="inlineStr">
+      <c r="K7" s="97" t="n"/>
+      <c r="L7" s="97" t="n"/>
+      <c r="M7" s="97" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N7" s="94" t="n"/>
-      <c r="O7" s="94" t="n"/>
-      <c r="P7" s="94" t="inlineStr">
+      <c r="N7" s="98" t="n"/>
+      <c r="O7" s="98" t="n"/>
+      <c r="P7" s="98" t="inlineStr">
         <is>
           <t>2026-10-13 17:15</t>
         </is>
@@ -3018,17 +3030,17 @@
       </c>
     </row>
     <row r="9" ht="58.05" customHeight="1">
-      <c r="A9" s="93" t="inlineStr">
+      <c r="A9" s="97" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C9" s="93" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3048,45 +3060,45 @@
         </is>
       </c>
       <c r="F9" s="44" t="n"/>
-      <c r="G9" s="93" t="n"/>
-      <c r="H9" s="93" t="n"/>
-      <c r="I9" s="93" t="inlineStr">
+      <c r="G9" s="97" t="n"/>
+      <c r="H9" s="97" t="n"/>
+      <c r="I9" s="97" t="inlineStr">
         <is>
           <t>currency_exchange_bt.mp3</t>
         </is>
       </c>
-      <c r="J9" s="93" t="inlineStr">
+      <c r="J9" s="97" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K9" s="93" t="n"/>
-      <c r="L9" s="93" t="n"/>
-      <c r="M9" s="93" t="inlineStr">
+      <c r="K9" s="97" t="n"/>
+      <c r="L9" s="97" t="n"/>
+      <c r="M9" s="97" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N9" s="94" t="n"/>
-      <c r="O9" s="94" t="n"/>
-      <c r="P9" s="94" t="inlineStr">
+      <c r="N9" s="98" t="n"/>
+      <c r="O9" s="98" t="n"/>
+      <c r="P9" s="98" t="inlineStr">
         <is>
           <t>2026-10-13 17:18</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58.05" customHeight="1">
-      <c r="A10" s="93" t="inlineStr">
+      <c r="A10" s="97" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B10" s="93" t="inlineStr">
+      <c r="B10" s="97" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C10" s="93" t="inlineStr">
+      <c r="C10" s="97" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3106,45 +3118,45 @@
         </is>
       </c>
       <c r="F10" s="44" t="n"/>
-      <c r="G10" s="93" t="n"/>
-      <c r="H10" s="93" t="n"/>
-      <c r="I10" s="93" t="inlineStr">
+      <c r="G10" s="97" t="n"/>
+      <c r="H10" s="97" t="n"/>
+      <c r="I10" s="97" t="inlineStr">
         <is>
           <t>currency_exchange_deai.mp3</t>
         </is>
       </c>
-      <c r="J10" s="93" t="inlineStr">
+      <c r="J10" s="97" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K10" s="93" t="n"/>
-      <c r="L10" s="93" t="n"/>
-      <c r="M10" s="93" t="inlineStr">
+      <c r="K10" s="97" t="n"/>
+      <c r="L10" s="97" t="n"/>
+      <c r="M10" s="97" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N10" s="94" t="n"/>
-      <c r="O10" s="94" t="n"/>
-      <c r="P10" s="94" t="inlineStr">
+      <c r="N10" s="98" t="n"/>
+      <c r="O10" s="98" t="n"/>
+      <c r="P10" s="98" t="inlineStr">
         <is>
           <t>2026-10-13 17:19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58.05" customHeight="1">
-      <c r="A11" s="93" t="inlineStr">
+      <c r="A11" s="97" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C11" s="93" t="inlineStr">
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3165,49 +3177,49 @@
         </is>
       </c>
       <c r="F11" s="44" t="n"/>
-      <c r="G11" s="93" t="n"/>
-      <c r="H11" s="93" t="n"/>
-      <c r="I11" s="93" t="inlineStr">
+      <c r="G11" s="97" t="n"/>
+      <c r="H11" s="97" t="n"/>
+      <c r="I11" s="97" t="inlineStr">
         <is>
           <t>luggage_bt.mp3</t>
         </is>
       </c>
-      <c r="J11" s="93" t="inlineStr">
+      <c r="J11" s="97" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K11" s="93" t="n"/>
-      <c r="L11" s="93" t="n"/>
-      <c r="M11" s="93" t="inlineStr">
+      <c r="K11" s="97" t="n"/>
+      <c r="L11" s="97" t="n"/>
+      <c r="M11" s="97" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N11" s="94" t="inlineStr">
+      <c r="N11" s="98" t="inlineStr">
         <is>
           <t>荷物を預けたい</t>
         </is>
       </c>
-      <c r="O11" s="94" t="n"/>
-      <c r="P11" s="94" t="inlineStr">
+      <c r="O11" s="98" t="n"/>
+      <c r="P11" s="98" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58.05" customHeight="1">
-      <c r="A12" s="93" t="inlineStr">
+      <c r="A12" s="97" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B12" s="93" t="inlineStr">
+      <c r="B12" s="97" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C12" s="93" t="inlineStr">
+      <c r="C12" s="97" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3228,28 +3240,28 @@
         </is>
       </c>
       <c r="F12" s="44" t="n"/>
-      <c r="G12" s="93" t="n"/>
-      <c r="H12" s="93" t="n"/>
-      <c r="I12" s="93" t="inlineStr">
+      <c r="G12" s="97" t="n"/>
+      <c r="H12" s="97" t="n"/>
+      <c r="I12" s="97" t="inlineStr">
         <is>
           <t>luggage_deai.mp3</t>
         </is>
       </c>
-      <c r="J12" s="93" t="inlineStr">
+      <c r="J12" s="97" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K12" s="93" t="n"/>
-      <c r="L12" s="93" t="n"/>
-      <c r="M12" s="93" t="inlineStr">
+      <c r="K12" s="97" t="n"/>
+      <c r="L12" s="97" t="n"/>
+      <c r="M12" s="97" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N12" s="94" t="n"/>
-      <c r="O12" s="94" t="n"/>
-      <c r="P12" s="94" t="inlineStr">
+      <c r="N12" s="98" t="n"/>
+      <c r="O12" s="98" t="n"/>
+      <c r="P12" s="98" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
@@ -3312,17 +3324,17 @@
       </c>
     </row>
     <row r="14" ht="58.05" customHeight="1">
-      <c r="A14" s="93" t="inlineStr">
+      <c r="A14" s="97" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B14" s="93" t="inlineStr">
+      <c r="B14" s="97" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C14" s="93" t="inlineStr">
+      <c r="C14" s="97" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3342,45 +3354,45 @@
         </is>
       </c>
       <c r="F14" s="44" t="n"/>
-      <c r="G14" s="93" t="n"/>
-      <c r="H14" s="93" t="n"/>
-      <c r="I14" s="93" t="inlineStr">
+      <c r="G14" s="97" t="n"/>
+      <c r="H14" s="97" t="n"/>
+      <c r="I14" s="97" t="inlineStr">
         <is>
           <t>stamp_bt.mp3</t>
         </is>
       </c>
-      <c r="J14" s="93" t="inlineStr">
+      <c r="J14" s="97" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K14" s="93" t="n"/>
-      <c r="L14" s="93" t="n"/>
-      <c r="M14" s="93" t="inlineStr">
+      <c r="K14" s="97" t="n"/>
+      <c r="L14" s="97" t="n"/>
+      <c r="M14" s="97" t="inlineStr">
         <is>
           <t>stamp</t>
         </is>
       </c>
-      <c r="N14" s="94" t="n"/>
-      <c r="O14" s="94" t="n"/>
-      <c r="P14" s="94" t="inlineStr">
+      <c r="N14" s="98" t="n"/>
+      <c r="O14" s="98" t="n"/>
+      <c r="P14" s="98" t="inlineStr">
         <is>
           <t>2026-10-13 17:22</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58.05" customHeight="1">
-      <c r="A15" s="93" t="inlineStr">
+      <c r="A15" s="97" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B15" s="93" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C15" s="93" t="inlineStr">
+      <c r="C15" s="97" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3400,28 +3412,28 @@
         </is>
       </c>
       <c r="F15" s="44" t="n"/>
-      <c r="G15" s="93" t="n"/>
-      <c r="H15" s="93" t="n"/>
-      <c r="I15" s="93" t="inlineStr">
+      <c r="G15" s="97" t="n"/>
+      <c r="H15" s="97" t="n"/>
+      <c r="I15" s="97" t="inlineStr">
         <is>
           <t>stamp_deai.mp3</t>
         </is>
       </c>
-      <c r="J15" s="93" t="inlineStr">
+      <c r="J15" s="97" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K15" s="93" t="n"/>
-      <c r="L15" s="93" t="n"/>
-      <c r="M15" s="93" t="inlineStr">
+      <c r="K15" s="97" t="n"/>
+      <c r="L15" s="97" t="n"/>
+      <c r="M15" s="97" t="inlineStr">
         <is>
           <t>stamp</t>
         </is>
       </c>
-      <c r="N15" s="94" t="n"/>
-      <c r="O15" s="94" t="n"/>
-      <c r="P15" s="94" t="inlineStr">
+      <c r="N15" s="98" t="n"/>
+      <c r="O15" s="98" t="n"/>
+      <c r="P15" s="98" t="inlineStr">
         <is>
           <t>2026-10-13 17:23</t>
         </is>
@@ -3608,22 +3620,22 @@
       </c>
     </row>
     <row r="19" ht="79.2" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="100" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="100" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="100" t="inlineStr">
         <is>
           <t>sightseeing</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="44" t="inlineStr">
         <is>
           <t>展望台 行き方
 展望台 どうやって
@@ -3632,33 +3644,40 @@
 展望台 行く</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできるルートもあり、ここから30～40分ほどで行くことができます。</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>展望台へは、目の前の橋を渡り、大通りを左へ15分ほど進んだ池の前のバス停から、シャトルバスが出ています。</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="E19" s="44" t="inlineStr">
+        <is>
+          <t>展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできる約500mの歩道もあり、であいの館から30～40分ほどで行くことができます。</t>
+        </is>
+      </c>
+      <c r="F19" s="44" t="inlineStr">
+        <is>
+          <t>展望台へは、目の前の橋を渡り、大通りを左へ10分ほど進んだ池の前のバス停から、シャトルバスが出ています。遊歩道もございます。詳しくは画面をご覧ください。</t>
+        </is>
+      </c>
+      <c r="G19" s="100" t="n"/>
+      <c r="H19" s="100" t="n"/>
+      <c r="I19" s="100" t="inlineStr">
         <is>
           <t>observatory_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J19" s="100" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K19" s="11" t="n"/>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="14" t="inlineStr">
+      <c r="K19" s="100" t="n"/>
+      <c r="L19" s="100" t="n"/>
+      <c r="M19" s="100" t="inlineStr">
         <is>
           <t>observatory_access</t>
+        </is>
+      </c>
+      <c r="N19" s="101" t="n"/>
+      <c r="O19" s="101" t="n"/>
+      <c r="P19" s="101" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:27</t>
         </is>
       </c>
     </row>
@@ -4973,17 +4992,17 @@
       </c>
     </row>
     <row r="43" ht="249.6" customHeight="1">
-      <c r="A43" s="93" t="inlineStr">
+      <c r="A43" s="97" t="inlineStr">
         <is>
           <t>guesthouse_access_deai</t>
         </is>
       </c>
-      <c r="B43" s="93" t="inlineStr">
+      <c r="B43" s="97" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C43" s="93" t="inlineStr">
+      <c r="C43" s="97" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -5017,30 +5036,30 @@
           <t>その建物は鳩谷八幡神社方面にあります。国道は交通量が多いため、川沿いの道をおすすめしております。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G43" s="93" t="inlineStr">
+      <c r="G43" s="97" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H43" s="93" t="n"/>
-      <c r="I43" s="93" t="inlineStr">
+      <c r="H43" s="97" t="n"/>
+      <c r="I43" s="97" t="inlineStr">
         <is>
           <t>guesthouse_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J43" s="93" t="inlineStr">
+      <c r="J43" s="97" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K43" s="93" t="n"/>
-      <c r="L43" s="93" t="n"/>
-      <c r="M43" s="93" t="inlineStr">
+      <c r="K43" s="97" t="n"/>
+      <c r="L43" s="97" t="n"/>
+      <c r="M43" s="97" t="inlineStr">
         <is>
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="94" t="n"/>
+      <c r="N43" s="98" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -6229,17 +6248,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="94" t="inlineStr">
+      <c r="A66" s="98" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="94" t="inlineStr">
+      <c r="B66" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="94" t="inlineStr">
+      <c r="C66" s="98" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -6269,26 +6288,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="94" t="inlineStr">
+      <c r="G66" s="98" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="94" t="n"/>
-      <c r="I66" s="94" t="inlineStr">
+      <c r="H66" s="98" t="n"/>
+      <c r="I66" s="98" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="94" t="inlineStr">
+      <c r="J66" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="94" t="n"/>
-      <c r="L66" s="94" t="n"/>
-      <c r="M66" s="94" t="n"/>
-      <c r="N66" s="94" t="n"/>
+      <c r="K66" s="98" t="n"/>
+      <c r="L66" s="98" t="n"/>
+      <c r="M66" s="98" t="n"/>
+      <c r="N66" s="98" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -7497,12 +7516,12 @@
       </c>
     </row>
     <row r="22" ht="64.8" customHeight="1">
-      <c r="A22" s="94" t="inlineStr">
+      <c r="A22" s="98" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B22" s="94" t="inlineStr">
+      <c r="B22" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7533,12 +7552,12 @@
       </c>
     </row>
     <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="94" t="inlineStr">
+      <c r="A23" s="98" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B23" s="94" t="inlineStr">
+      <c r="B23" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7569,12 +7588,12 @@
       </c>
     </row>
     <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="94" t="inlineStr">
+      <c r="A24" s="98" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B24" s="94" t="inlineStr">
+      <c r="B24" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7605,12 +7624,12 @@
       </c>
     </row>
     <row r="25" ht="81" customHeight="1">
-      <c r="A25" s="94" t="inlineStr">
+      <c r="A25" s="98" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B25" s="94" t="inlineStr">
+      <c r="B25" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7641,12 +7660,12 @@
       </c>
     </row>
     <row r="26" ht="64.8" customHeight="1">
-      <c r="A26" s="92" t="inlineStr">
+      <c r="A26" s="99" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
+      <c r="B26" s="99" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8198,12 +8217,12 @@
       </c>
     </row>
     <row r="42" ht="64.8" customHeight="1">
-      <c r="A42" s="94" t="inlineStr">
+      <c r="A42" s="98" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B42" s="94" t="inlineStr">
+      <c r="B42" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8234,12 +8253,12 @@
       </c>
     </row>
     <row r="43" ht="64.8" customHeight="1">
-      <c r="A43" s="94" t="inlineStr">
+      <c r="A43" s="98" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B43" s="94" t="inlineStr">
+      <c r="B43" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8270,12 +8289,12 @@
       </c>
     </row>
     <row r="44" ht="81" customHeight="1">
-      <c r="A44" s="94" t="inlineStr">
+      <c r="A44" s="98" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B44" s="94" t="inlineStr">
+      <c r="B44" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8306,12 +8325,12 @@
       </c>
     </row>
     <row r="45" ht="64.8" customHeight="1">
-      <c r="A45" s="94" t="inlineStr">
+      <c r="A45" s="98" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B45" s="94" t="inlineStr">
+      <c r="B45" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8342,12 +8361,12 @@
       </c>
     </row>
     <row r="46" ht="64.8" customHeight="1">
-      <c r="A46" s="92" t="inlineStr">
+      <c r="A46" s="99" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B46" s="92" t="inlineStr">
+      <c r="B46" s="99" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8558,12 +8577,12 @@
       </c>
     </row>
     <row r="52" ht="48.6" customHeight="1">
-      <c r="A52" s="94" t="inlineStr">
+      <c r="A52" s="98" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B52" s="94" t="inlineStr">
+      <c r="B52" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8594,12 +8613,12 @@
       </c>
     </row>
     <row r="53" ht="97.2" customHeight="1">
-      <c r="A53" s="94" t="inlineStr">
+      <c r="A53" s="98" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B53" s="94" t="inlineStr">
+      <c r="B53" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8630,12 +8649,12 @@
       </c>
     </row>
     <row r="54" ht="97.2" customHeight="1">
-      <c r="A54" s="94" t="inlineStr">
+      <c r="A54" s="98" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B54" s="94" t="inlineStr">
+      <c r="B54" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8666,12 +8685,12 @@
       </c>
     </row>
     <row r="55" ht="97.2" customHeight="1">
-      <c r="A55" s="94" t="inlineStr">
+      <c r="A55" s="98" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B55" s="94" t="inlineStr">
+      <c r="B55" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8702,12 +8721,12 @@
       </c>
     </row>
     <row r="56" ht="97.2" customHeight="1">
-      <c r="A56" s="92" t="inlineStr">
+      <c r="A56" s="99" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B56" s="92" t="inlineStr">
+      <c r="B56" s="99" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8902,12 +8921,12 @@
       </c>
     </row>
     <row r="62" ht="81" customHeight="1">
-      <c r="A62" s="94" t="inlineStr">
+      <c r="A62" s="98" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B62" s="94" t="inlineStr">
+      <c r="B62" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8938,12 +8957,12 @@
       </c>
     </row>
     <row r="63" ht="97.2" customHeight="1">
-      <c r="A63" s="94" t="inlineStr">
+      <c r="A63" s="98" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B63" s="94" t="inlineStr">
+      <c r="B63" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8974,12 +8993,12 @@
       </c>
     </row>
     <row r="64" ht="97.2" customHeight="1">
-      <c r="A64" s="94" t="inlineStr">
+      <c r="A64" s="98" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B64" s="94" t="inlineStr">
+      <c r="B64" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -9010,12 +9029,12 @@
       </c>
     </row>
     <row r="65" ht="97.2" customHeight="1">
-      <c r="A65" s="94" t="inlineStr">
+      <c r="A65" s="98" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B65" s="94" t="inlineStr">
+      <c r="B65" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -9046,12 +9065,12 @@
       </c>
     </row>
     <row r="66" ht="81" customHeight="1">
-      <c r="A66" s="92" t="inlineStr">
+      <c r="A66" s="99" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B66" s="92" t="inlineStr">
+      <c r="B66" s="99" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -9777,32 +9796,35 @@
       </c>
     </row>
     <row r="87" ht="97.2" customHeight="1">
-      <c r="A87" s="27" t="inlineStr">
+      <c r="A87" s="102" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B87" s="27" t="inlineStr">
+      <c r="B87" s="102" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="C87" s="28" t="inlineStr">
-        <is>
-          <t>observatory get
-observatory walk
-observatory how
-viewpoint walk
-castle observatory
-go observatory</t>
-        </is>
-      </c>
-      <c r="D87" s="28" t="inlineStr">
-        <is>
-          <t>The paid shuttle bus is a convenient way to get to the observatory. Cross the bridge right in front of this building, go out to the main street, and walk left for about 10 minutes. There is a bus stop in front of Wada House. Please take the shuttle bus from there. There is also a route you can walk up along the foot of the mountain, which takes about 30 to 40 minutes from here.</t>
-        </is>
-      </c>
-      <c r="E87" s="27" t="n"/>
+      <c r="C87" s="73" t="inlineStr">
+        <is>
+          <t>how to get to observation point
+way to viewpoint
+shuttle bus observatory
+walking trail to observatory
+Shiroyama observation deck</t>
+        </is>
+      </c>
+      <c r="D87" s="73" t="inlineStr">
+        <is>
+          <t>To reach the observation point, we recommend taking our paid shuttle bus. Cross the bridge in front of this building, turn left onto the main street, and walk for about ten minutes. You will find the bus stop in front of Wada House. Board the shuttle bus from there. Alternatively, there is a walking trail of about five hundred meters along the base of the mountain. It takes approximately thirty to forty minutes to reach the observation point on foot from this building, the Deai Hall.</t>
+        </is>
+      </c>
+      <c r="E87" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできる約500mの歩道もあり、であいの館から30～40分ほどで行くことができます。</t>
+        </is>
+      </c>
       <c r="F87" s="29" t="inlineStr">
         <is>
           <t>展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできるルートもあり、ここから30～40分ほどで行くことができます。</t>
@@ -9810,32 +9832,35 @@
       </c>
     </row>
     <row r="88" ht="97.2" customHeight="1">
-      <c r="A88" s="27" t="inlineStr">
+      <c r="A88" s="102" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B88" s="27" t="inlineStr">
+      <c r="B88" s="102" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="C88" s="28" t="inlineStr">
-        <is>
-          <t>mirador llegar
-mirador camin
-mirador pie
-mirador subir
-castillo mirador
-observatorio llegar</t>
-        </is>
-      </c>
-      <c r="D88" s="28" t="inlineStr">
-        <is>
-          <t>Para ir al mirador, lo más práctico es el autobús lanzadera de pago. Cruce el puente que está justo delante de este edificio, salga a la calle principal y gire a la izquierda; a unos 10 minutos encontrará la parada delante de la Casa Wada. Suba allí al autobús lanzadera. También hay una ruta a pie que sube por la falda de la montaña, y desde aquí se tarda unos 30 a 40 minutos.</t>
-        </is>
-      </c>
-      <c r="E88" s="27" t="n"/>
+      <c r="C88" s="73" t="inlineStr">
+        <is>
+          <t>cómo llegar al mirador
+autobús lanzadera observatorio
+sendero a la plataforma de observación
+ruta hacia el punto de vista
+camino hacia el Shiroyama</t>
+        </is>
+      </c>
+      <c r="D88" s="73" t="inlineStr">
+        <is>
+          <t>Para llegar al mirador, le recomendamos tomar nuestro autobús lanzadera de pago. Cruce el puente frente a este edificio, gire a la izquierda en la calle principal y camine durante aproximadamente diez minutos. Encontrará la parada de autobús frente a la casa Wada. Aborde el autobús lanzadera desde allí. También hay un sendero a pie de aproximadamente quinientos metros a lo largo de la base de la montaña. Se tarda aproximadamente treinta a cuarenta minutos en llegar a pie desde este edificio, la Sala Deai.</t>
+        </is>
+      </c>
+      <c r="E88" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできる約500mの歩道もあり、であいの館から30～40分ほどで行くことができます。</t>
+        </is>
+      </c>
       <c r="F88" s="29" t="inlineStr">
         <is>
           <t>展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできるルートもあり、ここから30～40分ほどで行くことができます。</t>
@@ -9843,32 +9868,35 @@
       </c>
     </row>
     <row r="89" ht="97.2" customHeight="1">
-      <c r="A89" s="27" t="inlineStr">
+      <c r="A89" s="102" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B89" s="27" t="inlineStr">
+      <c r="B89" s="102" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="C89" s="28" t="inlineStr">
-        <is>
-          <t>observatoire aller
-observatoire chemin
-observatoire pied
-château observatoire
-belvédère aller
-point de vue aller</t>
-        </is>
-      </c>
-      <c r="D89" s="28" t="inlineStr">
-        <is>
-          <t>Pour aller à l'observatoire, la navette payante est pratique. Traversez le pont juste en face de ce bâtiment, rejoignez la rue principale et marchez environ 10 minutes vers la gauche : l'arrêt se trouve devant la maison Wada. Prenez la navette à cet arrêt. Il existe aussi un itinéraire à pied qui monte le long du pied de la montagne ; il faut compter 30 à 40 minutes depuis ici.</t>
-        </is>
-      </c>
-      <c r="E89" s="27" t="n"/>
+      <c r="C89" s="73" t="inlineStr">
+        <is>
+          <t>comment accéder au belvédère
+itinéraire vers le point de vue
+navette vers l'observatoire
+sentier pédestre observatoire
+accès plate-forme observation</t>
+        </is>
+      </c>
+      <c r="D89" s="73" t="inlineStr">
+        <is>
+          <t>Pour accéder au belvédère, nous vous recommandons de prendre notre navette payante. Traversez le pont devant ce bâtiment, tournez à gauche sur l'avenue principale et marchez pendant environ dix minutes. Vous trouverez l'arrêt de bus devant la maison Wada. Montez à bord de la navette à partir de là. Il y a aussi un sentier pédestre d'environ cinq cents mètres le long de la base de la montagne. Il faut environ trente à quarante minutes pour y arriver à pied en partant de ce bâtiment, le Deai Hall.</t>
+        </is>
+      </c>
+      <c r="E89" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできる約500mの歩道もあり、であいの館から30～40分ほどで行くことができます。</t>
+        </is>
+      </c>
       <c r="F89" s="29" t="inlineStr">
         <is>
           <t>展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできるルートもあり、ここから30～40分ほどで行くことができます。</t>
@@ -9876,32 +9904,35 @@
       </c>
     </row>
     <row r="90" ht="97.2" customHeight="1">
-      <c r="A90" s="27" t="inlineStr">
+      <c r="A90" s="102" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B90" s="27" t="inlineStr">
+      <c r="B90" s="102" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="C90" s="28" t="inlineStr">
-        <is>
-          <t>전망대 가는
-전망대 가려면
-전망대 어떻게
-전망대 걸어
-전망대 길
-성터 전망대</t>
-        </is>
-      </c>
-      <c r="D90" s="28" t="inlineStr">
-        <is>
-          <t>전망대까지는 유료 셔틀버스가 편리합니다. 이 건물 바로 앞의 다리를 건너 큰길로 나가서 왼쪽으로 10분 정도 가시면 와다 가옥 앞에 버스 정류장이 있습니다. 그곳에서 셔틀버스를 타 주세요. 또는 산자락을 따라 걸어서 올라가는 길도 있으며, 여기서 30분에서 40분 정도면 가실 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="E90" s="27" t="n"/>
+      <c r="C90" s="73" t="inlineStr">
+        <is>
+          <t>전망대 가는 방법
+관측소 어떻게 가
+셔틀버스 전망대
+등산로 전망대
+시로야마 전망대 가다</t>
+        </is>
+      </c>
+      <c r="D90" s="73" t="inlineStr">
+        <is>
+          <t>전망대에 가시려면 유료 셔틀버스를 이용하시는 것이 편리합니다. 이 건물 앞의 다리를 건너서 큰 길로 나가 왼쪽으로 약십 분 정도 진행하시면 와다 가 앞에 버스 정류장이 있습니다. 그곳에서 셔틀버스에 타시기 바랍니다. 또는 산 기슭을 따라 걸을 수 있는 약오백 미터의 산책로가 있으며, 이 건물인 데아이 관에서 출발하면 약삼십 분에서 사십 분 정도면 도착할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E90" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできる約500mの歩道もあり、であいの館から30～40分ほどで行くことができます。</t>
+        </is>
+      </c>
       <c r="F90" s="29" t="inlineStr">
         <is>
           <t>展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできるルートもあり、ここから30～40分ほどで行くことができます。</t>
@@ -9909,32 +9940,35 @@
       </c>
     </row>
     <row r="91" ht="97.2" customHeight="1">
-      <c r="A91" s="30" t="inlineStr">
+      <c r="A91" s="103" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B91" s="30" t="inlineStr">
+      <c r="B91" s="103" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C91" s="31" t="inlineStr">
+      <c r="C91" s="75" t="inlineStr">
         <is>
           <t>观景台 怎么去
-观景台 怎么走
-观景台 步行
+观景台 走法
 城山 观景台
-去观景台
-展望台</t>
-        </is>
-      </c>
-      <c r="D91" s="31" t="inlineStr">
-        <is>
-          <t>前往观景台，乘坐收费的接驳巴士比较方便。过这栋建筑正前方的桥，走到大路后向左走约10分钟，和田家前面就是巴士站，请在那里乘坐接驳巴士。另外也有沿着山边步行上山的路线，从这里出发约30到40分钟可以到达。</t>
-        </is>
-      </c>
-      <c r="E91" s="30" t="n"/>
+登山道 观景台
+穿梭巴士 观景台</t>
+        </is>
+      </c>
+      <c r="D91" s="75" t="inlineStr">
+        <is>
+          <t>前往观景台最方便的方式是乘坐付费穿梭巴士。请从本建筑前方的桥走过去，来到大街上向左走约十分钟，您会看到和田家前的公交车站。从那里乘坐穿梭巴士即可。另外，山脚边还有一条约五百米长的步行道，从本建筑出发步行前往观景台需要约三十至四十分钟。</t>
+        </is>
+      </c>
+      <c r="E91" s="75" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできる約500mの歩道もあり、であいの館から30～40分ほどで行くことができます。</t>
+        </is>
+      </c>
       <c r="F91" s="32" t="inlineStr">
         <is>
           <t>展望台へは、有料シャトルバスが便利です。この建物の目の前の橋を渡り、大通りに出て左へ10分ほど進むと、和田家の前にバス停がございます。そちらからシャトルバスにご乗車ください。または山際沿いに歩いて登ることのできるルートもあり、ここから30～40分ほどで行くことができます。</t>
@@ -16931,12 +16965,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="94" t="inlineStr">
+      <c r="A302" s="98" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="94" t="inlineStr">
+      <c r="B302" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16962,12 +16996,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="94" t="inlineStr">
+      <c r="A303" s="98" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="94" t="inlineStr">
+      <c r="B303" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -16993,12 +17027,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="94" t="inlineStr">
+      <c r="A304" s="98" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="94" t="inlineStr">
+      <c r="B304" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17024,12 +17058,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="94" t="inlineStr">
+      <c r="A305" s="98" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="94" t="inlineStr">
+      <c r="B305" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17055,12 +17089,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="94" t="inlineStr">
+      <c r="A306" s="98" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="94" t="inlineStr">
+      <c r="B306" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17086,12 +17120,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="94" t="inlineStr">
+      <c r="A307" s="98" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="94" t="inlineStr">
+      <c r="B307" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17117,12 +17151,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="94" t="inlineStr">
+      <c r="A308" s="98" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="94" t="inlineStr">
+      <c r="B308" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17148,12 +17182,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="94" t="inlineStr">
+      <c r="A309" s="98" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="94" t="inlineStr">
+      <c r="B309" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17179,12 +17213,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="94" t="inlineStr">
+      <c r="A310" s="98" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="94" t="inlineStr">
+      <c r="B310" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17210,12 +17244,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="94" t="inlineStr">
+      <c r="A311" s="98" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="94" t="inlineStr">
+      <c r="B311" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17241,12 +17275,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="94" t="inlineStr">
+      <c r="A312" s="98" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="94" t="inlineStr">
+      <c r="B312" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17271,12 +17305,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="94" t="inlineStr">
+      <c r="A313" s="98" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="94" t="inlineStr">
+      <c r="B313" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17301,12 +17335,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="94" t="inlineStr">
+      <c r="A314" s="98" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="94" t="inlineStr">
+      <c r="B314" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17331,12 +17365,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="94" t="inlineStr">
+      <c r="A315" s="98" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="94" t="inlineStr">
+      <c r="B315" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17361,12 +17395,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="94" t="inlineStr">
+      <c r="A316" s="98" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="94" t="inlineStr">
+      <c r="B316" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17391,12 +17425,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="94" t="inlineStr">
+      <c r="A317" s="98" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="94" t="inlineStr">
+      <c r="B317" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17422,12 +17456,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="94" t="inlineStr">
+      <c r="A318" s="98" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="94" t="inlineStr">
+      <c r="B318" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17453,12 +17487,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="94" t="inlineStr">
+      <c r="A319" s="98" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="94" t="inlineStr">
+      <c r="B319" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17484,12 +17518,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="94" t="inlineStr">
+      <c r="A320" s="98" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="94" t="inlineStr">
+      <c r="B320" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17515,12 +17549,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="94" t="inlineStr">
+      <c r="A321" s="98" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="94" t="inlineStr">
+      <c r="B321" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17546,12 +17580,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="94" t="inlineStr">
+      <c r="A322" s="98" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="94" t="inlineStr">
+      <c r="B322" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17576,12 +17610,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="94" t="inlineStr">
+      <c r="A323" s="98" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="94" t="inlineStr">
+      <c r="B323" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17606,12 +17640,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="94" t="inlineStr">
+      <c r="A324" s="98" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="94" t="inlineStr">
+      <c r="B324" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17636,12 +17670,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="94" t="inlineStr">
+      <c r="A325" s="98" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="94" t="inlineStr">
+      <c r="B325" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17666,12 +17700,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="94" t="inlineStr">
+      <c r="A326" s="98" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="94" t="inlineStr">
+      <c r="B326" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17696,12 +17730,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="94" t="inlineStr">
+      <c r="A327" s="98" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="94" t="inlineStr">
+      <c r="B327" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17728,12 +17762,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="94" t="inlineStr">
+      <c r="A328" s="98" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="94" t="inlineStr">
+      <c r="B328" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17760,12 +17794,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="94" t="inlineStr">
+      <c r="A329" s="98" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="94" t="inlineStr">
+      <c r="B329" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17792,12 +17826,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="94" t="inlineStr">
+      <c r="A330" s="98" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="94" t="inlineStr">
+      <c r="B330" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17824,12 +17858,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="94" t="inlineStr">
+      <c r="A331" s="98" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="94" t="inlineStr">
+      <c r="B331" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17856,12 +17890,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="94" t="inlineStr">
+      <c r="A332" s="98" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="94" t="inlineStr">
+      <c r="B332" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17888,12 +17922,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="94" t="inlineStr">
+      <c r="A333" s="98" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="94" t="inlineStr">
+      <c r="B333" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17920,12 +17954,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="94" t="inlineStr">
+      <c r="A334" s="98" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="94" t="inlineStr">
+      <c r="B334" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17952,12 +17986,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="94" t="inlineStr">
+      <c r="A335" s="98" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="94" t="inlineStr">
+      <c r="B335" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17984,12 +18018,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="94" t="inlineStr">
+      <c r="A336" s="98" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="94" t="inlineStr">
+      <c r="B336" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18016,12 +18050,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="94" t="inlineStr">
+      <c r="A337" s="98" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="94" t="inlineStr">
+      <c r="B337" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18048,12 +18082,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="94" t="inlineStr">
+      <c r="A338" s="98" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="94" t="inlineStr">
+      <c r="B338" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18080,12 +18114,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="94" t="inlineStr">
+      <c r="A339" s="98" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="94" t="inlineStr">
+      <c r="B339" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18112,12 +18146,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="94" t="inlineStr">
+      <c r="A340" s="98" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="94" t="inlineStr">
+      <c r="B340" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18144,12 +18178,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="94" t="inlineStr">
+      <c r="A341" s="98" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="94" t="inlineStr">
+      <c r="B341" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18176,12 +18210,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="94" t="inlineStr">
+      <c r="A342" s="98" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="94" t="inlineStr">
+      <c r="B342" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18208,12 +18242,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="94" t="inlineStr">
+      <c r="A343" s="98" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="94" t="inlineStr">
+      <c r="B343" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18240,12 +18274,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="94" t="inlineStr">
+      <c r="A344" s="98" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="94" t="inlineStr">
+      <c r="B344" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18272,12 +18306,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="94" t="inlineStr">
+      <c r="A345" s="98" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="94" t="inlineStr">
+      <c r="B345" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18304,12 +18338,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="94" t="inlineStr">
+      <c r="A346" s="98" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="94" t="inlineStr">
+      <c r="B346" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18336,12 +18370,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="94" t="inlineStr">
+      <c r="A347" s="98" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="94" t="inlineStr">
+      <c r="B347" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18368,12 +18402,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="94" t="inlineStr">
+      <c r="A348" s="98" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="94" t="inlineStr">
+      <c r="B348" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18400,12 +18434,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="94" t="inlineStr">
+      <c r="A349" s="98" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="94" t="inlineStr">
+      <c r="B349" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18432,12 +18466,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="94" t="inlineStr">
+      <c r="A350" s="98" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="94" t="inlineStr">
+      <c r="B350" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18464,12 +18498,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="94" t="inlineStr">
+      <c r="A351" s="98" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="94" t="inlineStr">
+      <c r="B351" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18496,12 +18530,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="94" t="inlineStr">
+      <c r="A352" s="98" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="94" t="inlineStr">
+      <c r="B352" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18527,12 +18561,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="94" t="inlineStr">
+      <c r="A353" s="98" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="94" t="inlineStr">
+      <c r="B353" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18558,12 +18592,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="94" t="inlineStr">
+      <c r="A354" s="98" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="94" t="inlineStr">
+      <c r="B354" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18589,12 +18623,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="94" t="inlineStr">
+      <c r="A355" s="98" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="94" t="inlineStr">
+      <c r="B355" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18620,12 +18654,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="94" t="inlineStr">
+      <c r="A356" s="98" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="94" t="inlineStr">
+      <c r="B356" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18651,12 +18685,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="94" t="inlineStr">
+      <c r="A357" s="98" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="94" t="inlineStr">
+      <c r="B357" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18682,12 +18716,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="94" t="inlineStr">
+      <c r="A358" s="98" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="94" t="inlineStr">
+      <c r="B358" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18713,12 +18747,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="94" t="inlineStr">
+      <c r="A359" s="98" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="94" t="inlineStr">
+      <c r="B359" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18744,12 +18778,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="94" t="inlineStr">
+      <c r="A360" s="98" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="94" t="inlineStr">
+      <c r="B360" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18775,12 +18809,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="94" t="inlineStr">
+      <c r="A361" s="98" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="94" t="inlineStr">
+      <c r="B361" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18806,12 +18840,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="94" t="inlineStr">
+      <c r="A362" s="98" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="94" t="inlineStr">
+      <c r="B362" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18838,12 +18872,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="94" t="inlineStr">
+      <c r="A363" s="98" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="94" t="inlineStr">
+      <c r="B363" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18870,12 +18904,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="94" t="inlineStr">
+      <c r="A364" s="98" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="94" t="inlineStr">
+      <c r="B364" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18902,12 +18936,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="94" t="inlineStr">
+      <c r="A365" s="98" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="94" t="inlineStr">
+      <c r="B365" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18934,12 +18968,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="94" t="inlineStr">
+      <c r="A366" s="98" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="94" t="inlineStr">
+      <c r="B366" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18966,12 +19000,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="94" t="inlineStr">
+      <c r="A367" s="98" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="94" t="inlineStr">
+      <c r="B367" s="98" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18998,12 +19032,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="94" t="inlineStr">
+      <c r="A368" s="98" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="94" t="inlineStr">
+      <c r="B368" s="98" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -19030,12 +19064,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="94" t="inlineStr">
+      <c r="A369" s="98" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="94" t="inlineStr">
+      <c r="B369" s="98" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -19062,12 +19096,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="94" t="inlineStr">
+      <c r="A370" s="98" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="94" t="inlineStr">
+      <c r="B370" s="98" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -19094,12 +19128,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="94" t="inlineStr">
+      <c r="A371" s="98" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="94" t="inlineStr">
+      <c r="B371" s="98" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -20235,7 +20269,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="94" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -20245,7 +20279,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="94" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20257,7 +20291,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="94" t="inlineStr">
+      <c r="A3" s="98" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -20267,7 +20301,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="94" t="inlineStr">
+      <c r="C3" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20279,7 +20313,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="94" t="inlineStr">
+      <c r="A4" s="98" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -20289,7 +20323,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20301,7 +20335,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="94" t="inlineStr">
+      <c r="A5" s="98" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -20311,7 +20345,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="94" t="inlineStr">
+      <c r="C5" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20323,7 +20357,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="94" t="inlineStr">
+      <c r="A6" s="98" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20333,7 +20367,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20345,7 +20379,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="94" t="inlineStr">
+      <c r="A7" s="98" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20355,7 +20389,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="94" t="inlineStr">
+      <c r="C7" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20367,7 +20401,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="94" t="inlineStr">
+      <c r="A8" s="98" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20377,7 +20411,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20389,7 +20423,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="94" t="inlineStr">
+      <c r="A9" s="98" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20399,7 +20433,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="94" t="inlineStr">
+      <c r="C9" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20411,7 +20445,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="94" t="inlineStr">
+      <c r="A10" s="98" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20421,7 +20455,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20433,7 +20467,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="94" t="inlineStr">
+      <c r="A11" s="98" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20443,7 +20477,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="94" t="inlineStr">
+      <c r="C11" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20455,7 +20489,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="94" t="inlineStr">
+      <c r="A12" s="98" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20465,7 +20499,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20477,7 +20511,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="94" t="inlineStr">
+      <c r="A13" s="98" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20487,7 +20521,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="94" t="inlineStr">
+      <c r="C13" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20629,53 +20663,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="94" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="94" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="94" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="94" t="inlineStr">
+      <c r="D2" s="98" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="94" t="inlineStr">
+      <c r="E2" s="98" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="94" t="inlineStr">
+      <c r="F2" s="98" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="94" t="inlineStr">
+      <c r="G2" s="98" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="94" t="inlineStr">
+      <c r="H2" s="98" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="94" t="inlineStr">
+      <c r="I2" s="98" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="94" t="n"/>
-      <c r="K2" s="94" t="inlineStr">
+      <c r="J2" s="98" t="n"/>
+      <c r="K2" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20712,45 +20746,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="94" t="inlineStr">
+      <c r="A3" s="98" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="94" t="inlineStr">
+      <c r="B3" s="98" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="94" t="inlineStr">
+      <c r="C3" s="98" t="inlineStr">
         <is>
           <t>main_idle_20261013044809.png</t>
         </is>
       </c>
-      <c r="D3" s="94" t="n"/>
-      <c r="E3" s="94" t="n"/>
-      <c r="F3" s="94" t="n">
+      <c r="D3" s="98" t="n"/>
+      <c r="E3" s="98" t="n"/>
+      <c r="F3" s="98" t="n">
         <v>0.179</v>
       </c>
-      <c r="G3" s="94" t="n">
+      <c r="G3" s="98" t="n">
         <v>0.23</v>
       </c>
-      <c r="H3" s="94" t="inlineStr">
+      <c r="H3" s="98" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="94" t="inlineStr">
+      <c r="I3" s="98" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="94" t="inlineStr">
+      <c r="J3" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="94" t="inlineStr">
+      <c r="K3" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20787,45 +20821,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="94" t="inlineStr">
+      <c r="A4" s="98" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="94" t="inlineStr">
+      <c r="B4" s="98" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="98" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="94" t="n"/>
-      <c r="E4" s="94" t="n"/>
-      <c r="F4" s="94" t="inlineStr">
+      <c r="D4" s="98" t="n"/>
+      <c r="E4" s="98" t="n"/>
+      <c r="F4" s="98" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="94" t="inlineStr">
+      <c r="G4" s="98" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="94" t="inlineStr">
+      <c r="H4" s="98" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="94" t="inlineStr">
+      <c r="I4" s="98" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="94" t="n"/>
-      <c r="K4" s="94" t="inlineStr">
+      <c r="J4" s="98" t="n"/>
+      <c r="K4" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20862,45 +20896,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="94" t="inlineStr">
+      <c r="A5" s="98" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="94" t="inlineStr">
+      <c r="B5" s="98" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="94" t="inlineStr">
+      <c r="C5" s="98" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="94" t="n"/>
-      <c r="E5" s="94" t="n"/>
-      <c r="F5" s="94" t="inlineStr">
+      <c r="D5" s="98" t="n"/>
+      <c r="E5" s="98" t="n"/>
+      <c r="F5" s="98" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="94" t="inlineStr">
+      <c r="G5" s="98" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="94" t="inlineStr">
+      <c r="H5" s="98" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="94" t="inlineStr">
+      <c r="I5" s="98" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="94" t="n"/>
-      <c r="K5" s="94" t="inlineStr">
+      <c r="J5" s="98" t="n"/>
+      <c r="K5" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20937,45 +20971,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="94" t="inlineStr">
+      <c r="A6" s="98" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="94" t="inlineStr">
+      <c r="B6" s="98" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="98" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="94" t="n"/>
-      <c r="E6" s="94" t="n"/>
-      <c r="F6" s="94" t="inlineStr">
+      <c r="D6" s="98" t="n"/>
+      <c r="E6" s="98" t="n"/>
+      <c r="F6" s="98" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="94" t="inlineStr">
+      <c r="G6" s="98" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="94" t="inlineStr">
+      <c r="H6" s="98" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="94" t="inlineStr">
+      <c r="I6" s="98" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="94" t="n"/>
-      <c r="K6" s="94" t="inlineStr">
+      <c r="J6" s="98" t="n"/>
+      <c r="K6" s="98" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -21097,12 +21131,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="94" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B2" s="94" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21141,12 +21175,12 @@
       <c r="J2" s="46" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="94" t="inlineStr">
+      <c r="A3" s="98" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B3" s="94" t="inlineStr">
+      <c r="B3" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21185,12 +21219,12 @@
       <c r="J3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="94" t="inlineStr">
+      <c r="A4" s="98" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B4" s="94" t="inlineStr">
+      <c r="B4" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21229,12 +21263,12 @@
       <c r="J4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="94" t="inlineStr">
+      <c r="A5" s="98" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B5" s="94" t="inlineStr">
+      <c r="B5" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21273,12 +21307,12 @@
       <c r="J5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="94" t="inlineStr">
+      <c r="A6" s="98" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B6" s="94" t="inlineStr">
+      <c r="B6" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21317,12 +21351,12 @@
       <c r="J6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="94" t="inlineStr">
+      <c r="A7" s="98" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B7" s="94" t="inlineStr">
+      <c r="B7" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21361,12 +21395,12 @@
       <c r="J7" s="46" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="94" t="inlineStr">
+      <c r="A8" s="98" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B8" s="94" t="inlineStr">
+      <c r="B8" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21405,12 +21439,12 @@
       <c r="J8" s="46" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="94" t="inlineStr">
+      <c r="A9" s="98" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B9" s="94" t="inlineStr">
+      <c r="B9" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21449,12 +21483,12 @@
       <c r="J9" s="46" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="94" t="inlineStr">
+      <c r="A10" s="98" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B10" s="94" t="inlineStr">
+      <c r="B10" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21493,12 +21527,12 @@
       <c r="J10" s="46" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="94" t="inlineStr">
+      <c r="A11" s="98" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B11" s="94" t="inlineStr">
+      <c r="B11" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21537,12 +21571,12 @@
       <c r="J11" s="46" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="94" t="inlineStr">
+      <c r="A12" s="98" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B12" s="94" t="inlineStr">
+      <c r="B12" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21581,12 +21615,12 @@
       <c r="J12" s="46" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="94" t="inlineStr">
+      <c r="A13" s="98" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B13" s="94" t="inlineStr">
+      <c r="B13" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21644,12 +21678,12 @@
       <c r="J13" s="46" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="94" t="inlineStr">
+      <c r="A14" s="98" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B14" s="94" t="inlineStr">
+      <c r="B14" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21707,12 +21741,12 @@
       <c r="J14" s="46" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="94" t="inlineStr">
+      <c r="A15" s="98" t="inlineStr">
         <is>
           <t>趣味</t>
         </is>
       </c>
-      <c r="B15" s="94" t="inlineStr">
+      <c r="B15" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21773,12 +21807,12 @@
       <c r="J15" s="46" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="94" t="inlineStr">
+      <c r="A16" s="98" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B16" s="94" t="inlineStr">
+      <c r="B16" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21838,12 +21872,12 @@
       <c r="J16" s="46" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="94" t="inlineStr">
+      <c r="A17" s="98" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B17" s="94" t="inlineStr">
+      <c r="B17" s="98" t="inlineStr">
         <is>
           <t>共通</t>
         </is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -546,6 +546,18 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1260,7 +1272,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="101" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1270,31 +1282,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="98" t="n">
+      <c r="C2" s="101" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="98" t="n">
+      <c r="D2" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="98" t="n">
+      <c r="E2" s="101" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="98" t="n">
+      <c r="F2" s="101" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="98" t="n">
+      <c r="G2" s="101" t="n">
         <v>0.957</v>
       </c>
-      <c r="H2" s="98" t="n">
+      <c r="H2" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="98" t="n">
+      <c r="I2" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="98" t="n">
+      <c r="J2" s="101" t="n">
         <v>0.864</v>
       </c>
-      <c r="K2" s="98" t="n">
+      <c r="K2" s="101" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1304,7 +1316,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="98" t="inlineStr">
+      <c r="A3" s="101" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1314,31 +1326,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="98" t="n">
+      <c r="C3" s="101" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="98" t="n">
+      <c r="D3" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="98" t="n">
+      <c r="E3" s="101" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="98" t="n">
+      <c r="F3" s="101" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="98" t="n">
+      <c r="G3" s="101" t="n">
         <v>0.929</v>
       </c>
-      <c r="H3" s="98" t="n">
+      <c r="H3" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="98" t="n">
+      <c r="I3" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="98" t="n">
+      <c r="J3" s="101" t="n">
         <v>0.753</v>
       </c>
-      <c r="K3" s="98" t="n">
+      <c r="K3" s="101" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1348,7 +1360,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="98" t="inlineStr">
+      <c r="A4" s="101" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1358,31 +1370,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="98" t="n">
+      <c r="C4" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="98" t="n">
+      <c r="D4" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="98" t="n">
+      <c r="E4" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="98" t="n">
+      <c r="F4" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="98" t="n">
+      <c r="G4" s="101" t="n">
         <v>0.92</v>
       </c>
-      <c r="H4" s="98" t="n">
+      <c r="H4" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="98" t="n">
+      <c r="I4" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="98" t="n">
+      <c r="J4" s="101" t="n">
         <v>0.884</v>
       </c>
-      <c r="K4" s="98" t="n">
+      <c r="K4" s="101" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1454,7 +1466,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="101" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1464,10 +1476,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="98" t="n">
+      <c r="C2" s="101" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="98" t="n">
+      <c r="D2" s="101" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1477,7 +1489,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="98" t="inlineStr">
+      <c r="A3" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1487,16 +1499,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="98" t="n">
+      <c r="C3" s="101" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="98" t="n">
+      <c r="D3" s="101" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="98" t="inlineStr">
+      <c r="A4" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1506,16 +1518,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="98" t="n">
+      <c r="C4" s="101" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="98" t="n">
+      <c r="D4" s="101" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="98" t="inlineStr">
+      <c r="A5" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1525,16 +1537,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="98" t="n">
+      <c r="C5" s="101" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="98" t="n">
+      <c r="D5" s="101" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="98" t="inlineStr">
+      <c r="A6" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1544,16 +1556,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="98" t="n">
+      <c r="C6" s="101" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="98" t="n">
+      <c r="D6" s="101" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="98" t="inlineStr">
+      <c r="A7" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1563,10 +1575,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="98" t="n">
+      <c r="C7" s="101" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="98" t="n">
+      <c r="D7" s="101" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1626,17 +1638,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="101" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="101" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1648,17 +1660,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="98" t="inlineStr">
+      <c r="A3" s="101" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="98" t="inlineStr">
+      <c r="B3" s="101" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="98" t="inlineStr">
+      <c r="C3" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1666,17 +1678,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="98" t="inlineStr">
+      <c r="A4" s="101" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="98" t="inlineStr">
+      <c r="B4" s="101" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="98" t="inlineStr">
+      <c r="C4" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1688,17 +1700,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="98" t="inlineStr">
+      <c r="A5" s="101" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="98" t="inlineStr">
+      <c r="B5" s="101" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="98" t="inlineStr">
+      <c r="C5" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1710,17 +1722,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="98" t="inlineStr">
+      <c r="A6" s="101" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="98" t="inlineStr">
+      <c r="B6" s="101" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="98" t="inlineStr">
+      <c r="C6" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1728,17 +1740,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="98" t="inlineStr">
+      <c r="A7" s="101" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="98" t="inlineStr">
+      <c r="B7" s="101" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="98" t="inlineStr">
+      <c r="C7" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1746,17 +1758,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="98" t="inlineStr">
+      <c r="A8" s="101" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="98" t="inlineStr">
+      <c r="B8" s="101" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="98" t="inlineStr">
+      <c r="C8" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1768,17 +1780,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="98" t="inlineStr">
+      <c r="A9" s="101" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="98" t="inlineStr">
+      <c r="B9" s="101" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="98" t="inlineStr">
+      <c r="C9" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1790,17 +1802,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="98" t="inlineStr">
+      <c r="A10" s="101" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="98" t="inlineStr">
+      <c r="B10" s="101" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="98" t="inlineStr">
+      <c r="C10" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1812,17 +1824,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="98" t="inlineStr">
+      <c r="A11" s="101" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="98" t="inlineStr">
+      <c r="B11" s="101" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="98" t="inlineStr">
+      <c r="C11" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1830,17 +1842,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="98" t="inlineStr">
+      <c r="A12" s="101" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="98" t="inlineStr">
+      <c r="B12" s="101" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="98" t="inlineStr">
+      <c r="C12" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1848,17 +1860,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="98" t="inlineStr">
+      <c r="A13" s="101" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="98" t="inlineStr">
+      <c r="B13" s="101" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="98" t="inlineStr">
+      <c r="C13" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1870,17 +1882,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="98" t="inlineStr">
+      <c r="A14" s="101" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="98" t="inlineStr">
+      <c r="B14" s="101" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="98" t="inlineStr">
+      <c r="C14" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1892,17 +1904,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="98" t="inlineStr">
+      <c r="A15" s="101" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="98" t="inlineStr">
+      <c r="B15" s="101" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="98" t="inlineStr">
+      <c r="C15" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1914,17 +1926,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="98" t="inlineStr">
+      <c r="A16" s="101" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="98" t="inlineStr">
+      <c r="B16" s="101" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="98" t="inlineStr">
+      <c r="C16" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1936,17 +1948,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="98" t="inlineStr">
+      <c r="A17" s="101" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="98" t="inlineStr">
+      <c r="B17" s="101" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="98" t="inlineStr">
+      <c r="C17" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1958,17 +1970,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="98" t="inlineStr">
+      <c r="A18" s="101" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="98" t="inlineStr">
+      <c r="B18" s="101" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="98" t="inlineStr">
+      <c r="C18" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1980,17 +1992,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="98" t="inlineStr">
+      <c r="A19" s="101" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="98" t="inlineStr">
+      <c r="B19" s="101" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="98" t="inlineStr">
+      <c r="C19" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1998,17 +2010,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="98" t="inlineStr">
+      <c r="A20" s="101" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="98" t="inlineStr">
+      <c r="B20" s="101" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="98" t="inlineStr">
+      <c r="C20" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2016,17 +2028,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="98" t="inlineStr">
+      <c r="A21" s="101" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="98" t="inlineStr">
+      <c r="B21" s="101" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="98" t="inlineStr">
+      <c r="C21" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2038,17 +2050,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="98" t="inlineStr">
+      <c r="A22" s="101" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="98" t="inlineStr">
+      <c r="B22" s="101" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="98" t="inlineStr">
+      <c r="C22" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2060,17 +2072,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="98" t="inlineStr">
+      <c r="A23" s="101" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="98" t="inlineStr">
+      <c r="B23" s="101" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="98" t="inlineStr">
+      <c r="C23" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2082,17 +2094,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="98" t="inlineStr">
+      <c r="A24" s="101" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="98" t="inlineStr">
+      <c r="B24" s="101" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="98" t="inlineStr">
+      <c r="C24" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2104,17 +2116,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="98" t="inlineStr">
+      <c r="A25" s="101" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="98" t="inlineStr">
+      <c r="B25" s="101" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="98" t="inlineStr">
+      <c r="C25" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2122,17 +2134,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="98" t="inlineStr">
+      <c r="A26" s="101" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="98" t="inlineStr">
+      <c r="B26" s="101" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="98" t="inlineStr">
+      <c r="C26" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2140,17 +2152,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="98" t="inlineStr">
+      <c r="A27" s="101" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="98" t="inlineStr">
+      <c r="B27" s="101" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="98" t="inlineStr">
+      <c r="C27" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2162,17 +2174,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="98" t="inlineStr">
+      <c r="A28" s="101" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="98" t="inlineStr">
+      <c r="B28" s="101" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="98" t="inlineStr">
+      <c r="C28" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2184,17 +2196,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="98" t="inlineStr">
+      <c r="A29" s="101" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="98" t="inlineStr">
+      <c r="B29" s="101" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="98" t="inlineStr">
+      <c r="C29" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2206,17 +2218,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="98" t="inlineStr">
+      <c r="A30" s="101" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="98" t="inlineStr">
+      <c r="B30" s="101" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="98" t="inlineStr">
+      <c r="C30" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2224,17 +2236,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="98" t="inlineStr">
+      <c r="A31" s="101" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="98" t="inlineStr">
+      <c r="B31" s="101" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="98" t="inlineStr">
+      <c r="C31" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2246,17 +2258,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="98" t="inlineStr">
+      <c r="A32" s="101" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="98" t="inlineStr">
+      <c r="B32" s="101" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="98" t="inlineStr">
+      <c r="C32" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2264,17 +2276,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="98" t="inlineStr">
+      <c r="A33" s="101" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="98" t="inlineStr">
+      <c r="B33" s="101" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="98" t="inlineStr">
+      <c r="C33" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2282,17 +2294,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="98" t="inlineStr">
+      <c r="A34" s="101" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="98" t="inlineStr">
+      <c r="B34" s="101" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="98" t="inlineStr">
+      <c r="C34" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2300,17 +2312,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="98" t="inlineStr">
+      <c r="A35" s="101" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="98" t="inlineStr">
+      <c r="B35" s="101" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="98" t="inlineStr">
+      <c r="C35" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2318,17 +2330,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="98" t="inlineStr">
+      <c r="A36" s="101" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="98" t="inlineStr">
+      <c r="B36" s="101" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="98" t="inlineStr">
+      <c r="C36" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2336,17 +2348,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="98" t="inlineStr">
+      <c r="A37" s="101" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="98" t="inlineStr">
+      <c r="B37" s="101" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="98" t="inlineStr">
+      <c r="C37" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2354,17 +2366,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="98" t="inlineStr">
+      <c r="A38" s="101" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="98" t="inlineStr">
+      <c r="B38" s="101" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="98" t="inlineStr">
+      <c r="C38" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2372,17 +2384,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="98" t="inlineStr">
+      <c r="A39" s="101" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="98" t="inlineStr">
+      <c r="B39" s="101" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="98" t="inlineStr">
+      <c r="C39" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2390,17 +2402,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="98" t="inlineStr">
+      <c r="A40" s="101" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="98" t="inlineStr">
+      <c r="B40" s="101" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="98" t="inlineStr">
+      <c r="C40" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2412,17 +2424,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="98" t="inlineStr">
+      <c r="A41" s="101" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="98" t="inlineStr">
+      <c r="B41" s="101" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="98" t="inlineStr">
+      <c r="C41" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2430,17 +2442,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="98" t="inlineStr">
+      <c r="A42" s="101" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="98" t="inlineStr">
+      <c r="B42" s="101" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="98" t="inlineStr">
+      <c r="C42" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2452,17 +2464,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="98" t="inlineStr">
+      <c r="A43" s="101" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="98" t="inlineStr">
+      <c r="B43" s="101" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="98" t="inlineStr">
+      <c r="C43" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2470,17 +2482,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="98" t="inlineStr">
+      <c r="A44" s="101" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="98" t="inlineStr">
+      <c r="B44" s="101" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="98" t="inlineStr">
+      <c r="C44" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2492,17 +2504,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="98" t="inlineStr">
+      <c r="A45" s="101" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="98" t="inlineStr">
+      <c r="B45" s="101" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="98" t="inlineStr">
+      <c r="C45" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2851,17 +2863,17 @@
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="97" t="inlineStr">
+      <c r="A6" s="100" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B6" s="97" t="inlineStr">
+      <c r="B6" s="100" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C6" s="97" t="inlineStr">
+      <c r="C6" s="100" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2886,49 +2898,49 @@
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
         </is>
       </c>
-      <c r="G6" s="97" t="n"/>
-      <c r="H6" s="97" t="n"/>
-      <c r="I6" s="97" t="inlineStr">
+      <c r="G6" s="100" t="n"/>
+      <c r="H6" s="100" t="n"/>
+      <c r="I6" s="100" t="inlineStr">
         <is>
           <t>atm_bt.mp3</t>
         </is>
       </c>
-      <c r="J6" s="97" t="inlineStr">
+      <c r="J6" s="100" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K6" s="97" t="n"/>
-      <c r="L6" s="97" t="n"/>
-      <c r="M6" s="97" t="inlineStr">
+      <c r="K6" s="100" t="n"/>
+      <c r="L6" s="100" t="n"/>
+      <c r="M6" s="100" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N6" s="98" t="inlineStr">
+      <c r="N6" s="101" t="inlineStr">
         <is>
           <t>ATMはどこ</t>
         </is>
       </c>
-      <c r="O6" s="98" t="n"/>
-      <c r="P6" s="98" t="inlineStr">
+      <c r="O6" s="101" t="n"/>
+      <c r="P6" s="101" t="inlineStr">
         <is>
           <t>2026-10-13 17:14</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="97" t="inlineStr">
+      <c r="A7" s="100" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B7" s="97" t="inlineStr">
+      <c r="B7" s="100" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="C7" s="100" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2953,28 +2965,28 @@
           <t>海外のカードは鳩谷郵便局のATM、日本のカードは和田家前のJAのATMをご利用ください。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G7" s="97" t="n"/>
-      <c r="H7" s="97" t="n"/>
-      <c r="I7" s="97" t="inlineStr">
+      <c r="G7" s="100" t="n"/>
+      <c r="H7" s="100" t="n"/>
+      <c r="I7" s="100" t="inlineStr">
         <is>
           <t>atm_deai.mp3</t>
         </is>
       </c>
-      <c r="J7" s="97" t="inlineStr">
+      <c r="J7" s="100" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K7" s="97" t="n"/>
-      <c r="L7" s="97" t="n"/>
-      <c r="M7" s="97" t="inlineStr">
+      <c r="K7" s="100" t="n"/>
+      <c r="L7" s="100" t="n"/>
+      <c r="M7" s="100" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N7" s="98" t="n"/>
-      <c r="O7" s="98" t="n"/>
-      <c r="P7" s="98" t="inlineStr">
+      <c r="N7" s="101" t="n"/>
+      <c r="O7" s="101" t="n"/>
+      <c r="P7" s="101" t="inlineStr">
         <is>
           <t>2026-10-13 17:15</t>
         </is>
@@ -3030,17 +3042,17 @@
       </c>
     </row>
     <row r="9" ht="58.05" customHeight="1">
-      <c r="A9" s="97" t="inlineStr">
+      <c r="A9" s="100" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B9" s="97" t="inlineStr">
+      <c r="B9" s="100" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="C9" s="100" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3060,45 +3072,45 @@
         </is>
       </c>
       <c r="F9" s="44" t="n"/>
-      <c r="G9" s="97" t="n"/>
-      <c r="H9" s="97" t="n"/>
-      <c r="I9" s="97" t="inlineStr">
+      <c r="G9" s="100" t="n"/>
+      <c r="H9" s="100" t="n"/>
+      <c r="I9" s="100" t="inlineStr">
         <is>
           <t>currency_exchange_bt.mp3</t>
         </is>
       </c>
-      <c r="J9" s="97" t="inlineStr">
+      <c r="J9" s="100" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K9" s="97" t="n"/>
-      <c r="L9" s="97" t="n"/>
-      <c r="M9" s="97" t="inlineStr">
+      <c r="K9" s="100" t="n"/>
+      <c r="L9" s="100" t="n"/>
+      <c r="M9" s="100" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N9" s="98" t="n"/>
-      <c r="O9" s="98" t="n"/>
-      <c r="P9" s="98" t="inlineStr">
+      <c r="N9" s="101" t="n"/>
+      <c r="O9" s="101" t="n"/>
+      <c r="P9" s="101" t="inlineStr">
         <is>
           <t>2026-10-13 17:18</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58.05" customHeight="1">
-      <c r="A10" s="97" t="inlineStr">
+      <c r="A10" s="100" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B10" s="97" t="inlineStr">
+      <c r="B10" s="100" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C10" s="97" t="inlineStr">
+      <c r="C10" s="100" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3118,45 +3130,45 @@
         </is>
       </c>
       <c r="F10" s="44" t="n"/>
-      <c r="G10" s="97" t="n"/>
-      <c r="H10" s="97" t="n"/>
-      <c r="I10" s="97" t="inlineStr">
+      <c r="G10" s="100" t="n"/>
+      <c r="H10" s="100" t="n"/>
+      <c r="I10" s="100" t="inlineStr">
         <is>
           <t>currency_exchange_deai.mp3</t>
         </is>
       </c>
-      <c r="J10" s="97" t="inlineStr">
+      <c r="J10" s="100" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K10" s="97" t="n"/>
-      <c r="L10" s="97" t="n"/>
-      <c r="M10" s="97" t="inlineStr">
+      <c r="K10" s="100" t="n"/>
+      <c r="L10" s="100" t="n"/>
+      <c r="M10" s="100" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N10" s="98" t="n"/>
-      <c r="O10" s="98" t="n"/>
-      <c r="P10" s="98" t="inlineStr">
+      <c r="N10" s="101" t="n"/>
+      <c r="O10" s="101" t="n"/>
+      <c r="P10" s="101" t="inlineStr">
         <is>
           <t>2026-10-13 17:19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58.05" customHeight="1">
-      <c r="A11" s="97" t="inlineStr">
+      <c r="A11" s="100" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B11" s="97" t="inlineStr">
+      <c r="B11" s="100" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="100" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3177,49 +3189,49 @@
         </is>
       </c>
       <c r="F11" s="44" t="n"/>
-      <c r="G11" s="97" t="n"/>
-      <c r="H11" s="97" t="n"/>
-      <c r="I11" s="97" t="inlineStr">
+      <c r="G11" s="100" t="n"/>
+      <c r="H11" s="100" t="n"/>
+      <c r="I11" s="100" t="inlineStr">
         <is>
           <t>luggage_bt.mp3</t>
         </is>
       </c>
-      <c r="J11" s="97" t="inlineStr">
+      <c r="J11" s="100" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K11" s="97" t="n"/>
-      <c r="L11" s="97" t="n"/>
-      <c r="M11" s="97" t="inlineStr">
+      <c r="K11" s="100" t="n"/>
+      <c r="L11" s="100" t="n"/>
+      <c r="M11" s="100" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N11" s="98" t="inlineStr">
+      <c r="N11" s="101" t="inlineStr">
         <is>
           <t>荷物を預けたい</t>
         </is>
       </c>
-      <c r="O11" s="98" t="n"/>
-      <c r="P11" s="98" t="inlineStr">
+      <c r="O11" s="101" t="n"/>
+      <c r="P11" s="101" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58.05" customHeight="1">
-      <c r="A12" s="97" t="inlineStr">
+      <c r="A12" s="100" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B12" s="97" t="inlineStr">
+      <c r="B12" s="100" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C12" s="97" t="inlineStr">
+      <c r="C12" s="100" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3240,28 +3252,28 @@
         </is>
       </c>
       <c r="F12" s="44" t="n"/>
-      <c r="G12" s="97" t="n"/>
-      <c r="H12" s="97" t="n"/>
-      <c r="I12" s="97" t="inlineStr">
+      <c r="G12" s="100" t="n"/>
+      <c r="H12" s="100" t="n"/>
+      <c r="I12" s="100" t="inlineStr">
         <is>
           <t>luggage_deai.mp3</t>
         </is>
       </c>
-      <c r="J12" s="97" t="inlineStr">
+      <c r="J12" s="100" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K12" s="97" t="n"/>
-      <c r="L12" s="97" t="n"/>
-      <c r="M12" s="97" t="inlineStr">
+      <c r="K12" s="100" t="n"/>
+      <c r="L12" s="100" t="n"/>
+      <c r="M12" s="100" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N12" s="98" t="n"/>
-      <c r="O12" s="98" t="n"/>
-      <c r="P12" s="98" t="inlineStr">
+      <c r="N12" s="101" t="n"/>
+      <c r="O12" s="101" t="n"/>
+      <c r="P12" s="101" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
@@ -3324,17 +3336,17 @@
       </c>
     </row>
     <row r="14" ht="58.05" customHeight="1">
-      <c r="A14" s="97" t="inlineStr">
+      <c r="A14" s="100" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B14" s="97" t="inlineStr">
+      <c r="B14" s="100" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C14" s="97" t="inlineStr">
+      <c r="C14" s="100" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3354,45 +3366,45 @@
         </is>
       </c>
       <c r="F14" s="44" t="n"/>
-      <c r="G14" s="97" t="n"/>
-      <c r="H14" s="97" t="n"/>
-      <c r="I14" s="97" t="inlineStr">
+      <c r="G14" s="100" t="n"/>
+      <c r="H14" s="100" t="n"/>
+      <c r="I14" s="100" t="inlineStr">
         <is>
           <t>stamp_bt.mp3</t>
         </is>
       </c>
-      <c r="J14" s="97" t="inlineStr">
+      <c r="J14" s="100" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K14" s="97" t="n"/>
-      <c r="L14" s="97" t="n"/>
-      <c r="M14" s="97" t="inlineStr">
+      <c r="K14" s="100" t="n"/>
+      <c r="L14" s="100" t="n"/>
+      <c r="M14" s="100" t="inlineStr">
         <is>
           <t>stamp</t>
         </is>
       </c>
-      <c r="N14" s="98" t="n"/>
-      <c r="O14" s="98" t="n"/>
-      <c r="P14" s="98" t="inlineStr">
+      <c r="N14" s="101" t="n"/>
+      <c r="O14" s="101" t="n"/>
+      <c r="P14" s="101" t="inlineStr">
         <is>
           <t>2026-10-13 17:22</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58.05" customHeight="1">
-      <c r="A15" s="97" t="inlineStr">
+      <c r="A15" s="100" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B15" s="97" t="inlineStr">
+      <c r="B15" s="100" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C15" s="97" t="inlineStr">
+      <c r="C15" s="100" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3412,28 +3424,28 @@
         </is>
       </c>
       <c r="F15" s="44" t="n"/>
-      <c r="G15" s="97" t="n"/>
-      <c r="H15" s="97" t="n"/>
-      <c r="I15" s="97" t="inlineStr">
+      <c r="G15" s="100" t="n"/>
+      <c r="H15" s="100" t="n"/>
+      <c r="I15" s="100" t="inlineStr">
         <is>
           <t>stamp_deai.mp3</t>
         </is>
       </c>
-      <c r="J15" s="97" t="inlineStr">
+      <c r="J15" s="100" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K15" s="97" t="n"/>
-      <c r="L15" s="97" t="n"/>
-      <c r="M15" s="97" t="inlineStr">
+      <c r="K15" s="100" t="n"/>
+      <c r="L15" s="100" t="n"/>
+      <c r="M15" s="100" t="inlineStr">
         <is>
           <t>stamp</t>
         </is>
       </c>
-      <c r="N15" s="98" t="n"/>
-      <c r="O15" s="98" t="n"/>
-      <c r="P15" s="98" t="inlineStr">
+      <c r="N15" s="101" t="n"/>
+      <c r="O15" s="101" t="n"/>
+      <c r="P15" s="101" t="inlineStr">
         <is>
           <t>2026-10-13 17:23</t>
         </is>
@@ -3553,17 +3565,17 @@
       </c>
     </row>
     <row r="18" ht="58.05" customHeight="1">
-      <c r="A18" s="97" t="inlineStr">
+      <c r="A18" s="100" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B18" s="97" t="inlineStr">
+      <c r="B18" s="100" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C18" s="97" t="inlineStr">
+      <c r="C18" s="100" t="inlineStr">
         <is>
           <t>sightseeing</t>
         </is>
@@ -3588,32 +3600,32 @@
           <t>展望台へは、自家用車で行くことはできません。歩いておよそ15分、またはシャトルバスでお越しいただけます。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G18" s="97" t="n"/>
-      <c r="H18" s="97" t="n"/>
-      <c r="I18" s="97" t="inlineStr">
+      <c r="G18" s="100" t="n"/>
+      <c r="H18" s="100" t="n"/>
+      <c r="I18" s="100" t="inlineStr">
         <is>
           <t>observatory_access_bt.mp3</t>
         </is>
       </c>
-      <c r="J18" s="97" t="inlineStr">
+      <c r="J18" s="100" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K18" s="97" t="n"/>
-      <c r="L18" s="97" t="n"/>
-      <c r="M18" s="97" t="inlineStr">
+      <c r="K18" s="100" t="n"/>
+      <c r="L18" s="100" t="n"/>
+      <c r="M18" s="100" t="inlineStr">
         <is>
           <t>observatory_access</t>
         </is>
       </c>
-      <c r="N18" s="98" t="inlineStr">
+      <c r="N18" s="101" t="inlineStr">
         <is>
           <t>展望台への行き方</t>
         </is>
       </c>
-      <c r="O18" s="98" t="n"/>
-      <c r="P18" s="98" t="inlineStr">
+      <c r="O18" s="101" t="n"/>
+      <c r="P18" s="101" t="inlineStr">
         <is>
           <t>2026-10-13 17:26</t>
         </is>
@@ -3741,57 +3753,65 @@
       </c>
     </row>
     <row r="21" ht="66" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="104" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="104" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="104" t="inlineStr">
         <is>
           <t>sightseeing</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="44" t="inlineStr">
         <is>
           <t>白水湖
-滝 行き
 白水
-滝 どうやって
-白水湖 行き方</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
+白水湖 行き方
+白水湖 アクセス
+白水の滝 車で
+滝へ どうやって</t>
+        </is>
+      </c>
+      <c r="E21" s="44" t="inlineStr">
+        <is>
+          <t>白水の滝と白水湖へは、自家用車で飲み行くことができますが、概ね11月から6月までは道路が冬期閉鎖となるため行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
+        </is>
+      </c>
+      <c r="F21" s="44" t="n"/>
+      <c r="G21" s="104" t="n"/>
+      <c r="H21" s="104" t="inlineStr">
         <is>
           <t>https://shirakawa-going.jp/</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="104" t="inlineStr">
         <is>
           <t>waterfall_lake.mp3</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J21" s="104" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K21" s="11" t="n"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="14" t="inlineStr">
+      <c r="K21" s="104" t="n"/>
+      <c r="L21" s="104" t="n"/>
+      <c r="M21" s="104" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
+        </is>
+      </c>
+      <c r="N21" s="105" t="n"/>
+      <c r="O21" s="105" t="n"/>
+      <c r="P21" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:30</t>
         </is>
       </c>
     </row>
@@ -4992,17 +5012,17 @@
       </c>
     </row>
     <row r="43" ht="249.6" customHeight="1">
-      <c r="A43" s="97" t="inlineStr">
+      <c r="A43" s="100" t="inlineStr">
         <is>
           <t>guesthouse_access_deai</t>
         </is>
       </c>
-      <c r="B43" s="97" t="inlineStr">
+      <c r="B43" s="100" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C43" s="97" t="inlineStr">
+      <c r="C43" s="100" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -5036,30 +5056,30 @@
           <t>その建物は鳩谷八幡神社方面にあります。国道は交通量が多いため、川沿いの道をおすすめしております。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G43" s="97" t="inlineStr">
+      <c r="G43" s="100" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H43" s="97" t="n"/>
-      <c r="I43" s="97" t="inlineStr">
+      <c r="H43" s="100" t="n"/>
+      <c r="I43" s="100" t="inlineStr">
         <is>
           <t>guesthouse_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J43" s="97" t="inlineStr">
+      <c r="J43" s="100" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K43" s="97" t="n"/>
-      <c r="L43" s="97" t="n"/>
-      <c r="M43" s="97" t="inlineStr">
+      <c r="K43" s="100" t="n"/>
+      <c r="L43" s="100" t="n"/>
+      <c r="M43" s="100" t="inlineStr">
         <is>
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="98" t="n"/>
+      <c r="N43" s="101" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -6248,17 +6268,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="98" t="inlineStr">
+      <c r="A66" s="101" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="98" t="inlineStr">
+      <c r="B66" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="98" t="inlineStr">
+      <c r="C66" s="101" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -6288,26 +6308,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="98" t="inlineStr">
+      <c r="G66" s="101" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="98" t="n"/>
-      <c r="I66" s="98" t="inlineStr">
+      <c r="H66" s="101" t="n"/>
+      <c r="I66" s="101" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="98" t="inlineStr">
+      <c r="J66" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="98" t="n"/>
-      <c r="L66" s="98" t="n"/>
-      <c r="M66" s="98" t="n"/>
-      <c r="N66" s="98" t="n"/>
+      <c r="K66" s="101" t="n"/>
+      <c r="L66" s="101" t="n"/>
+      <c r="M66" s="101" t="n"/>
+      <c r="N66" s="101" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -7516,12 +7536,12 @@
       </c>
     </row>
     <row r="22" ht="64.8" customHeight="1">
-      <c r="A22" s="98" t="inlineStr">
+      <c r="A22" s="101" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B22" s="98" t="inlineStr">
+      <c r="B22" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7552,12 +7572,12 @@
       </c>
     </row>
     <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="98" t="inlineStr">
+      <c r="A23" s="101" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B23" s="98" t="inlineStr">
+      <c r="B23" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7588,12 +7608,12 @@
       </c>
     </row>
     <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="98" t="inlineStr">
+      <c r="A24" s="101" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B24" s="98" t="inlineStr">
+      <c r="B24" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7624,12 +7644,12 @@
       </c>
     </row>
     <row r="25" ht="81" customHeight="1">
-      <c r="A25" s="98" t="inlineStr">
+      <c r="A25" s="101" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B25" s="98" t="inlineStr">
+      <c r="B25" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7696,12 +7716,12 @@
       </c>
     </row>
     <row r="27" ht="64.8" customHeight="1">
-      <c r="A27" s="95" t="inlineStr">
+      <c r="A27" s="102" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B27" s="95" t="inlineStr">
+      <c r="B27" s="102" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7732,12 +7752,12 @@
       </c>
     </row>
     <row r="28" ht="64.8" customHeight="1">
-      <c r="A28" s="95" t="inlineStr">
+      <c r="A28" s="102" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B28" s="95" t="inlineStr">
+      <c r="B28" s="102" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7768,12 +7788,12 @@
       </c>
     </row>
     <row r="29" ht="64.8" customHeight="1">
-      <c r="A29" s="95" t="inlineStr">
+      <c r="A29" s="102" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B29" s="95" t="inlineStr">
+      <c r="B29" s="102" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7804,12 +7824,12 @@
       </c>
     </row>
     <row r="30" ht="81" customHeight="1">
-      <c r="A30" s="95" t="inlineStr">
+      <c r="A30" s="102" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B30" s="95" t="inlineStr">
+      <c r="B30" s="102" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7840,12 +7860,12 @@
       </c>
     </row>
     <row r="31" ht="64.8" customHeight="1">
-      <c r="A31" s="96" t="inlineStr">
+      <c r="A31" s="103" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B31" s="96" t="inlineStr">
+      <c r="B31" s="103" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8037,12 +8057,12 @@
       </c>
     </row>
     <row r="37" ht="64.8" customHeight="1">
-      <c r="A37" s="95" t="inlineStr">
+      <c r="A37" s="102" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B37" s="95" t="inlineStr">
+      <c r="B37" s="102" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8073,12 +8093,12 @@
       </c>
     </row>
     <row r="38" ht="64.8" customHeight="1">
-      <c r="A38" s="95" t="inlineStr">
+      <c r="A38" s="102" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B38" s="95" t="inlineStr">
+      <c r="B38" s="102" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8109,12 +8129,12 @@
       </c>
     </row>
     <row r="39" ht="64.8" customHeight="1">
-      <c r="A39" s="95" t="inlineStr">
+      <c r="A39" s="102" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B39" s="95" t="inlineStr">
+      <c r="B39" s="102" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8145,12 +8165,12 @@
       </c>
     </row>
     <row r="40" ht="113.4" customHeight="1">
-      <c r="A40" s="95" t="inlineStr">
+      <c r="A40" s="102" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B40" s="95" t="inlineStr">
+      <c r="B40" s="102" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8181,12 +8201,12 @@
       </c>
     </row>
     <row r="41" ht="97.2" customHeight="1">
-      <c r="A41" s="96" t="inlineStr">
+      <c r="A41" s="103" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B41" s="96" t="inlineStr">
+      <c r="B41" s="103" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8217,12 +8237,12 @@
       </c>
     </row>
     <row r="42" ht="64.8" customHeight="1">
-      <c r="A42" s="98" t="inlineStr">
+      <c r="A42" s="101" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B42" s="98" t="inlineStr">
+      <c r="B42" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8253,12 +8273,12 @@
       </c>
     </row>
     <row r="43" ht="64.8" customHeight="1">
-      <c r="A43" s="98" t="inlineStr">
+      <c r="A43" s="101" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B43" s="98" t="inlineStr">
+      <c r="B43" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8289,12 +8309,12 @@
       </c>
     </row>
     <row r="44" ht="81" customHeight="1">
-      <c r="A44" s="98" t="inlineStr">
+      <c r="A44" s="101" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B44" s="98" t="inlineStr">
+      <c r="B44" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8325,12 +8345,12 @@
       </c>
     </row>
     <row r="45" ht="64.8" customHeight="1">
-      <c r="A45" s="98" t="inlineStr">
+      <c r="A45" s="101" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B45" s="98" t="inlineStr">
+      <c r="B45" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8397,12 +8417,12 @@
       </c>
     </row>
     <row r="47" ht="81" customHeight="1">
-      <c r="A47" s="95" t="inlineStr">
+      <c r="A47" s="102" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B47" s="95" t="inlineStr">
+      <c r="B47" s="102" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8433,12 +8453,12 @@
       </c>
     </row>
     <row r="48" ht="64.8" customHeight="1">
-      <c r="A48" s="95" t="inlineStr">
+      <c r="A48" s="102" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B48" s="95" t="inlineStr">
+      <c r="B48" s="102" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8469,12 +8489,12 @@
       </c>
     </row>
     <row r="49" ht="64.8" customHeight="1">
-      <c r="A49" s="95" t="inlineStr">
+      <c r="A49" s="102" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B49" s="95" t="inlineStr">
+      <c r="B49" s="102" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8505,12 +8525,12 @@
       </c>
     </row>
     <row r="50" ht="64.8" customHeight="1">
-      <c r="A50" s="95" t="inlineStr">
+      <c r="A50" s="102" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B50" s="95" t="inlineStr">
+      <c r="B50" s="102" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8541,12 +8561,12 @@
       </c>
     </row>
     <row r="51" ht="48.6" customHeight="1">
-      <c r="A51" s="96" t="inlineStr">
+      <c r="A51" s="103" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B51" s="96" t="inlineStr">
+      <c r="B51" s="103" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8577,12 +8597,12 @@
       </c>
     </row>
     <row r="52" ht="48.6" customHeight="1">
-      <c r="A52" s="98" t="inlineStr">
+      <c r="A52" s="101" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B52" s="98" t="inlineStr">
+      <c r="B52" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8613,12 +8633,12 @@
       </c>
     </row>
     <row r="53" ht="97.2" customHeight="1">
-      <c r="A53" s="98" t="inlineStr">
+      <c r="A53" s="101" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B53" s="98" t="inlineStr">
+      <c r="B53" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8649,12 +8669,12 @@
       </c>
     </row>
     <row r="54" ht="97.2" customHeight="1">
-      <c r="A54" s="98" t="inlineStr">
+      <c r="A54" s="101" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B54" s="98" t="inlineStr">
+      <c r="B54" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8685,12 +8705,12 @@
       </c>
     </row>
     <row r="55" ht="97.2" customHeight="1">
-      <c r="A55" s="98" t="inlineStr">
+      <c r="A55" s="101" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B55" s="98" t="inlineStr">
+      <c r="B55" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8921,12 +8941,12 @@
       </c>
     </row>
     <row r="62" ht="81" customHeight="1">
-      <c r="A62" s="98" t="inlineStr">
+      <c r="A62" s="101" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B62" s="98" t="inlineStr">
+      <c r="B62" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8957,12 +8977,12 @@
       </c>
     </row>
     <row r="63" ht="97.2" customHeight="1">
-      <c r="A63" s="98" t="inlineStr">
+      <c r="A63" s="101" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B63" s="98" t="inlineStr">
+      <c r="B63" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8993,12 +9013,12 @@
       </c>
     </row>
     <row r="64" ht="97.2" customHeight="1">
-      <c r="A64" s="98" t="inlineStr">
+      <c r="A64" s="101" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B64" s="98" t="inlineStr">
+      <c r="B64" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -9029,12 +9049,12 @@
       </c>
     </row>
     <row r="65" ht="97.2" customHeight="1">
-      <c r="A65" s="98" t="inlineStr">
+      <c r="A65" s="101" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B65" s="98" t="inlineStr">
+      <c r="B65" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -9101,12 +9121,12 @@
       </c>
     </row>
     <row r="67" ht="81" customHeight="1">
-      <c r="A67" s="95" t="inlineStr">
+      <c r="A67" s="102" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B67" s="95" t="inlineStr">
+      <c r="B67" s="102" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -9137,12 +9157,12 @@
       </c>
     </row>
     <row r="68" ht="97.2" customHeight="1">
-      <c r="A68" s="95" t="inlineStr">
+      <c r="A68" s="102" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B68" s="95" t="inlineStr">
+      <c r="B68" s="102" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -9173,12 +9193,12 @@
       </c>
     </row>
     <row r="69" ht="97.2" customHeight="1">
-      <c r="A69" s="95" t="inlineStr">
+      <c r="A69" s="102" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B69" s="95" t="inlineStr">
+      <c r="B69" s="102" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -9209,12 +9229,12 @@
       </c>
     </row>
     <row r="70" ht="97.2" customHeight="1">
-      <c r="A70" s="95" t="inlineStr">
+      <c r="A70" s="102" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B70" s="95" t="inlineStr">
+      <c r="B70" s="102" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -9245,12 +9265,12 @@
       </c>
     </row>
     <row r="71" ht="81" customHeight="1">
-      <c r="A71" s="96" t="inlineStr">
+      <c r="A71" s="103" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B71" s="96" t="inlineStr">
+      <c r="B71" s="103" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -9611,12 +9631,12 @@
       </c>
     </row>
     <row r="82" ht="145.8" customHeight="1">
-      <c r="A82" s="98" t="inlineStr">
+      <c r="A82" s="101" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B82" s="98" t="inlineStr">
+      <c r="B82" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -9648,12 +9668,12 @@
       </c>
     </row>
     <row r="83" ht="145.8" customHeight="1">
-      <c r="A83" s="98" t="inlineStr">
+      <c r="A83" s="101" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B83" s="98" t="inlineStr">
+      <c r="B83" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -9685,12 +9705,12 @@
       </c>
     </row>
     <row r="84" ht="162" customHeight="1">
-      <c r="A84" s="98" t="inlineStr">
+      <c r="A84" s="101" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B84" s="98" t="inlineStr">
+      <c r="B84" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -9722,12 +9742,12 @@
       </c>
     </row>
     <row r="85" ht="145.8" customHeight="1">
-      <c r="A85" s="98" t="inlineStr">
+      <c r="A85" s="101" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B85" s="98" t="inlineStr">
+      <c r="B85" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -10141,32 +10161,36 @@
       </c>
     </row>
     <row r="97" ht="97.2" customHeight="1">
-      <c r="A97" s="27" t="inlineStr">
+      <c r="A97" s="106" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="B97" s="27" t="inlineStr">
+      <c r="B97" s="106" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="C97" s="28" t="inlineStr">
-        <is>
-          <t>Shiramizu
-waterfall
-falls
-Shiramizu Lake
-lake get
-waterfall how</t>
-        </is>
-      </c>
-      <c r="D97" s="28" t="inlineStr">
-        <is>
-          <t>Shiramizu Falls and Shiramizu Lake can only be reached by private car. Please note that the road may be closed or restricted due to heavy rain. For details, please see SHIRAKAWA-Going.</t>
-        </is>
-      </c>
-      <c r="E97" s="27" t="n"/>
+      <c r="C97" s="73" t="inlineStr">
+        <is>
+          <t>Hakuizu Lake
+Hakuizu waterfall access
+how to get to Hakuizu
+Hakuizu Lake driving
+Hakuizu waterfall car
+can I drive to the waterfall</t>
+        </is>
+      </c>
+      <c r="D97" s="73" t="inlineStr">
+        <is>
+          <t>You can drive to Hakuizu Waterfall and Hakuizu Lake by private vehicle. However, the road is closed during winter from approximately November to June, so access is not possible during this period. Please note that traffic restrictions may also occur due to heavy rain. For detailed information, please visit Shirakawa-Going.</t>
+        </is>
+      </c>
+      <c r="E97" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 白水の滝と白水湖へは、自家用車で飲み行くことができますが、概ね11月から6月までは道路が冬期閉鎖となるため行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
+        </is>
+      </c>
       <c r="F97" s="29" t="inlineStr">
         <is>
           <t>白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
@@ -10174,32 +10198,36 @@
       </c>
     </row>
     <row r="98" ht="97.2" customHeight="1">
-      <c r="A98" s="27" t="inlineStr">
+      <c r="A98" s="106" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="B98" s="27" t="inlineStr">
+      <c r="B98" s="106" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="C98" s="28" t="inlineStr">
-        <is>
-          <t>Shiramizu
-cascada
-catarata
-lago Shiramizu
-cascada llegar
-lago llegar</t>
-        </is>
-      </c>
-      <c r="D98" s="28" t="inlineStr">
-        <is>
-          <t>A la cascada Shiramizu y al lago Shiramizu solo se puede llegar en vehículo propio. Tenga en cuenta también que puede haber restricciones de tráfico por lluvias intensas. Para más información, consulte SHIRAKAWA-Going.</t>
-        </is>
-      </c>
-      <c r="E98" s="27" t="n"/>
+      <c r="C98" s="73" t="inlineStr">
+        <is>
+          <t>Lago Hakuizu
+Cascada Hakuizu
+cómo llegar Hakuizu
+Hakuizu en coche
+acceso Hakuizu
+carretera Hakuizu</t>
+        </is>
+      </c>
+      <c r="D98" s="73" t="inlineStr">
+        <is>
+          <t>Puede acceder a la Cascada Hakuizu y al Lago Hakuizu en automóvil privado. Sin embargo, la carretera está cerrada durante el invierno aproximadamente desde noviembre hasta junio, por lo que el acceso no es posible durante este período. Tenga en cuenta que también puede haber restricciones de tráfico debido a fuertes lluvias. Para información detallada, visite Shirakawa-Going.</t>
+        </is>
+      </c>
+      <c r="E98" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 白水の滝と白水湖へは、自家用車で飲み行くことができますが、概ね11月から6月までは道路が冬期閉鎖となるため行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
+        </is>
+      </c>
       <c r="F98" s="29" t="inlineStr">
         <is>
           <t>白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
@@ -10207,32 +10235,36 @@
       </c>
     </row>
     <row r="99" ht="97.2" customHeight="1">
-      <c r="A99" s="27" t="inlineStr">
+      <c r="A99" s="106" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="B99" s="27" t="inlineStr">
+      <c r="B99" s="106" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="C99" s="28" t="inlineStr">
-        <is>
-          <t>lac shiramizu
-cascade
-shiramizu
-chute eau
-aller lac
-cascade aller</t>
-        </is>
-      </c>
-      <c r="D99" s="28" t="inlineStr">
-        <is>
-          <t>Les chutes de Shiramizu et le lac Shiramizu ne sont accessibles qu'en voiture particulière. Attention, la circulation peut être restreinte en cas de fortes pluies. Pour plus de détails, veuillez consulter SHIRAKAWA-Going.</t>
-        </is>
-      </c>
-      <c r="E99" s="27" t="n"/>
+      <c r="C99" s="73" t="inlineStr">
+        <is>
+          <t>Lac Hakuizu
+Cascade Hakuizu
+comment aller Hakuizu
+Hakuizu en voiture
+accès Hakuizu
+route Hakuizu</t>
+        </is>
+      </c>
+      <c r="D99" s="73" t="inlineStr">
+        <is>
+          <t>Vous pouvez accéder à la Cascade Hakuizu et au Lac Hakuizu en voiture particulière. Cependant, la route est fermée pendant l'hiver, approximativement de novembre à juin, donc l'accès n'est pas possible pendant cette période. Veuillez noter que des restrictions de circulation peuvent également survenir en raison de fortes pluies. Pour plus d'informations, consultez le site Shirakawa-Going.</t>
+        </is>
+      </c>
+      <c r="E99" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 白水の滝と白水湖へは、自家用車で飲み行くことができますが、概ね11月から6月までは道路が冬期閉鎖となるため行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
+        </is>
+      </c>
       <c r="F99" s="29" t="inlineStr">
         <is>
           <t>白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
@@ -10240,32 +10272,36 @@
       </c>
     </row>
     <row r="100" ht="97.2" customHeight="1">
-      <c r="A100" s="27" t="inlineStr">
+      <c r="A100" s="106" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="B100" s="27" t="inlineStr">
+      <c r="B100" s="106" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="C100" s="28" t="inlineStr">
-        <is>
-          <t>시라미즈 호수
-시라미즈 폭포
-시라미즈
-폭포 가는
-폭포 어떻게
-호수 가는</t>
-        </is>
-      </c>
-      <c r="D100" s="28" t="inlineStr">
-        <is>
-          <t>시라미즈 폭포와 시라미즈 호수는 자가용이 아니면 가실 수 없습니다. 또한 폭우로 통행이 제한되는 경우가 있으니 주의해 주세요. 자세한 내용은 시라카와 고잉을 확인해 주세요.</t>
-        </is>
-      </c>
-      <c r="E100" s="27" t="n"/>
+      <c r="C100" s="73" t="inlineStr">
+        <is>
+          <t>하쿠이즈 호수
+하쿠이즈 폭포
+하쿠이즈 가는 길
+하쿠이즈 자동차
+하쿠이즈 드라이브
+폭포 접근</t>
+        </is>
+      </c>
+      <c r="D100" s="73" t="inlineStr">
+        <is>
+          <t>하쿠이즈 폭포와 하쿠이즈 호수는 개인 차량으로 방문할 수 있습니다. 다만, 11월부터 6월까지는 도로가 겨울철 폐쇄되어 통행이 불가능합니다. 또한 집중호우로 인해 통행이 제한될 수 있으니 주의하시기 바랍니다. 자세한 정보는 Shirakawa-Going을 참고하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="E100" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 白水の滝と白水湖へは、自家用車で飲み行くことができますが、概ね11月から6月までは道路が冬期閉鎖となるため行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
+        </is>
+      </c>
       <c r="F100" s="29" t="inlineStr">
         <is>
           <t>白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
@@ -10273,31 +10309,36 @@
       </c>
     </row>
     <row r="101" ht="81" customHeight="1">
-      <c r="A101" s="30" t="inlineStr">
+      <c r="A101" s="107" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="B101" s="30" t="inlineStr">
+      <c r="B101" s="107" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C101" s="31" t="inlineStr">
+      <c r="C101" s="75" t="inlineStr">
         <is>
           <t>白水湖
 白水瀑布
-瀑布 怎么去
-白水
-白水湖 怎么走</t>
-        </is>
-      </c>
-      <c r="D101" s="31" t="inlineStr">
-        <is>
-          <t>白水瀑布和白水湖只能自驾前往。另外，因暴雨有时会实施通行限制，请注意。详情请查看SHIRAKAWA-Going。</t>
-        </is>
-      </c>
-      <c r="E101" s="30" t="n"/>
+白水湖怎么去
+白水湖交通
+白水瀑布自驾
+开车去白水</t>
+        </is>
+      </c>
+      <c r="D101" s="75" t="inlineStr">
+        <is>
+          <t>您可以驾驶私家车前往白水瀑布和白水湖。但是，从大约十一月至六月期间，道路实行冬季封闭，无法通行。请注意，由于暴雨可能会实施交通管制。有关详细信息，请访问Shirakawa-Going网站。</t>
+        </is>
+      </c>
+      <c r="E101" s="75" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 白水の滝と白水湖へは、自家用車で飲み行くことができますが、概ね11月から6月までは道路が冬期閉鎖となるため行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
+        </is>
+      </c>
       <c r="F101" s="32" t="inlineStr">
         <is>
           <t>白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。</t>
@@ -16965,12 +17006,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="98" t="inlineStr">
+      <c r="A302" s="101" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="98" t="inlineStr">
+      <c r="B302" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -16996,12 +17037,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="98" t="inlineStr">
+      <c r="A303" s="101" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="98" t="inlineStr">
+      <c r="B303" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17027,12 +17068,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="98" t="inlineStr">
+      <c r="A304" s="101" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="98" t="inlineStr">
+      <c r="B304" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17058,12 +17099,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="98" t="inlineStr">
+      <c r="A305" s="101" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="98" t="inlineStr">
+      <c r="B305" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17089,12 +17130,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="98" t="inlineStr">
+      <c r="A306" s="101" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="98" t="inlineStr">
+      <c r="B306" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17120,12 +17161,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="98" t="inlineStr">
+      <c r="A307" s="101" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="98" t="inlineStr">
+      <c r="B307" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17151,12 +17192,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="98" t="inlineStr">
+      <c r="A308" s="101" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="98" t="inlineStr">
+      <c r="B308" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17182,12 +17223,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="98" t="inlineStr">
+      <c r="A309" s="101" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="98" t="inlineStr">
+      <c r="B309" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17213,12 +17254,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="98" t="inlineStr">
+      <c r="A310" s="101" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="98" t="inlineStr">
+      <c r="B310" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17244,12 +17285,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="98" t="inlineStr">
+      <c r="A311" s="101" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="98" t="inlineStr">
+      <c r="B311" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17275,12 +17316,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="98" t="inlineStr">
+      <c r="A312" s="101" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="98" t="inlineStr">
+      <c r="B312" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17305,12 +17346,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="98" t="inlineStr">
+      <c r="A313" s="101" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="98" t="inlineStr">
+      <c r="B313" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17335,12 +17376,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="98" t="inlineStr">
+      <c r="A314" s="101" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="98" t="inlineStr">
+      <c r="B314" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17365,12 +17406,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="98" t="inlineStr">
+      <c r="A315" s="101" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="98" t="inlineStr">
+      <c r="B315" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17395,12 +17436,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="98" t="inlineStr">
+      <c r="A316" s="101" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="98" t="inlineStr">
+      <c r="B316" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17425,12 +17466,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="98" t="inlineStr">
+      <c r="A317" s="101" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="98" t="inlineStr">
+      <c r="B317" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17456,12 +17497,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="98" t="inlineStr">
+      <c r="A318" s="101" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="98" t="inlineStr">
+      <c r="B318" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17487,12 +17528,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="98" t="inlineStr">
+      <c r="A319" s="101" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="98" t="inlineStr">
+      <c r="B319" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17518,12 +17559,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="98" t="inlineStr">
+      <c r="A320" s="101" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="98" t="inlineStr">
+      <c r="B320" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17549,12 +17590,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="98" t="inlineStr">
+      <c r="A321" s="101" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="98" t="inlineStr">
+      <c r="B321" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17580,12 +17621,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="98" t="inlineStr">
+      <c r="A322" s="101" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="98" t="inlineStr">
+      <c r="B322" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17610,12 +17651,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="98" t="inlineStr">
+      <c r="A323" s="101" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="98" t="inlineStr">
+      <c r="B323" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17640,12 +17681,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="98" t="inlineStr">
+      <c r="A324" s="101" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="98" t="inlineStr">
+      <c r="B324" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17670,12 +17711,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="98" t="inlineStr">
+      <c r="A325" s="101" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="98" t="inlineStr">
+      <c r="B325" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17700,12 +17741,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="98" t="inlineStr">
+      <c r="A326" s="101" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="98" t="inlineStr">
+      <c r="B326" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17730,12 +17771,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="98" t="inlineStr">
+      <c r="A327" s="101" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="98" t="inlineStr">
+      <c r="B327" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17762,12 +17803,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="98" t="inlineStr">
+      <c r="A328" s="101" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="98" t="inlineStr">
+      <c r="B328" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17794,12 +17835,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="98" t="inlineStr">
+      <c r="A329" s="101" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="98" t="inlineStr">
+      <c r="B329" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17826,12 +17867,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="98" t="inlineStr">
+      <c r="A330" s="101" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="98" t="inlineStr">
+      <c r="B330" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17858,12 +17899,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="98" t="inlineStr">
+      <c r="A331" s="101" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="98" t="inlineStr">
+      <c r="B331" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17890,12 +17931,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="98" t="inlineStr">
+      <c r="A332" s="101" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="98" t="inlineStr">
+      <c r="B332" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17922,12 +17963,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="98" t="inlineStr">
+      <c r="A333" s="101" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="98" t="inlineStr">
+      <c r="B333" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17954,12 +17995,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="98" t="inlineStr">
+      <c r="A334" s="101" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="98" t="inlineStr">
+      <c r="B334" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17986,12 +18027,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="98" t="inlineStr">
+      <c r="A335" s="101" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="98" t="inlineStr">
+      <c r="B335" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18018,12 +18059,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="98" t="inlineStr">
+      <c r="A336" s="101" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="98" t="inlineStr">
+      <c r="B336" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18050,12 +18091,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="98" t="inlineStr">
+      <c r="A337" s="101" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="98" t="inlineStr">
+      <c r="B337" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18082,12 +18123,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="98" t="inlineStr">
+      <c r="A338" s="101" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="98" t="inlineStr">
+      <c r="B338" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18114,12 +18155,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="98" t="inlineStr">
+      <c r="A339" s="101" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="98" t="inlineStr">
+      <c r="B339" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18146,12 +18187,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="98" t="inlineStr">
+      <c r="A340" s="101" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="98" t="inlineStr">
+      <c r="B340" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18178,12 +18219,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="98" t="inlineStr">
+      <c r="A341" s="101" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="98" t="inlineStr">
+      <c r="B341" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18210,12 +18251,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="98" t="inlineStr">
+      <c r="A342" s="101" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="98" t="inlineStr">
+      <c r="B342" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18242,12 +18283,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="98" t="inlineStr">
+      <c r="A343" s="101" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="98" t="inlineStr">
+      <c r="B343" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18274,12 +18315,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="98" t="inlineStr">
+      <c r="A344" s="101" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="98" t="inlineStr">
+      <c r="B344" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18306,12 +18347,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="98" t="inlineStr">
+      <c r="A345" s="101" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="98" t="inlineStr">
+      <c r="B345" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18338,12 +18379,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="98" t="inlineStr">
+      <c r="A346" s="101" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="98" t="inlineStr">
+      <c r="B346" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18370,12 +18411,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="98" t="inlineStr">
+      <c r="A347" s="101" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="98" t="inlineStr">
+      <c r="B347" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18402,12 +18443,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="98" t="inlineStr">
+      <c r="A348" s="101" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="98" t="inlineStr">
+      <c r="B348" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18434,12 +18475,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="98" t="inlineStr">
+      <c r="A349" s="101" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="98" t="inlineStr">
+      <c r="B349" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18466,12 +18507,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="98" t="inlineStr">
+      <c r="A350" s="101" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="98" t="inlineStr">
+      <c r="B350" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18498,12 +18539,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="98" t="inlineStr">
+      <c r="A351" s="101" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="98" t="inlineStr">
+      <c r="B351" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18530,12 +18571,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="98" t="inlineStr">
+      <c r="A352" s="101" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="98" t="inlineStr">
+      <c r="B352" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18561,12 +18602,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="98" t="inlineStr">
+      <c r="A353" s="101" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="98" t="inlineStr">
+      <c r="B353" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18592,12 +18633,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="98" t="inlineStr">
+      <c r="A354" s="101" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="98" t="inlineStr">
+      <c r="B354" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18623,12 +18664,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="98" t="inlineStr">
+      <c r="A355" s="101" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="98" t="inlineStr">
+      <c r="B355" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18654,12 +18695,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="98" t="inlineStr">
+      <c r="A356" s="101" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="98" t="inlineStr">
+      <c r="B356" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18685,12 +18726,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="98" t="inlineStr">
+      <c r="A357" s="101" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="98" t="inlineStr">
+      <c r="B357" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18716,12 +18757,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="98" t="inlineStr">
+      <c r="A358" s="101" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="98" t="inlineStr">
+      <c r="B358" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18747,12 +18788,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="98" t="inlineStr">
+      <c r="A359" s="101" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="98" t="inlineStr">
+      <c r="B359" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18778,12 +18819,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="98" t="inlineStr">
+      <c r="A360" s="101" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="98" t="inlineStr">
+      <c r="B360" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18809,12 +18850,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="98" t="inlineStr">
+      <c r="A361" s="101" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="98" t="inlineStr">
+      <c r="B361" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18840,12 +18881,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="98" t="inlineStr">
+      <c r="A362" s="101" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="98" t="inlineStr">
+      <c r="B362" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18872,12 +18913,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="98" t="inlineStr">
+      <c r="A363" s="101" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="98" t="inlineStr">
+      <c r="B363" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18904,12 +18945,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="98" t="inlineStr">
+      <c r="A364" s="101" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="98" t="inlineStr">
+      <c r="B364" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18936,12 +18977,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="98" t="inlineStr">
+      <c r="A365" s="101" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="98" t="inlineStr">
+      <c r="B365" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18968,12 +19009,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="98" t="inlineStr">
+      <c r="A366" s="101" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="98" t="inlineStr">
+      <c r="B366" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -19000,12 +19041,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="98" t="inlineStr">
+      <c r="A367" s="101" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="98" t="inlineStr">
+      <c r="B367" s="101" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -19032,12 +19073,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="98" t="inlineStr">
+      <c r="A368" s="101" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="98" t="inlineStr">
+      <c r="B368" s="101" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -19064,12 +19105,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="98" t="inlineStr">
+      <c r="A369" s="101" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="98" t="inlineStr">
+      <c r="B369" s="101" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -19096,12 +19137,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="98" t="inlineStr">
+      <c r="A370" s="101" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="98" t="inlineStr">
+      <c r="B370" s="101" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -19128,12 +19169,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="98" t="inlineStr">
+      <c r="A371" s="101" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="98" t="inlineStr">
+      <c r="B371" s="101" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -20269,7 +20310,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="101" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -20279,7 +20320,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20291,7 +20332,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="98" t="inlineStr">
+      <c r="A3" s="101" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -20301,7 +20342,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="98" t="inlineStr">
+      <c r="C3" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20313,7 +20354,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="98" t="inlineStr">
+      <c r="A4" s="101" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -20323,7 +20364,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="98" t="inlineStr">
+      <c r="C4" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20335,7 +20376,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="98" t="inlineStr">
+      <c r="A5" s="101" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -20345,7 +20386,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="98" t="inlineStr">
+      <c r="C5" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20357,7 +20398,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="98" t="inlineStr">
+      <c r="A6" s="101" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20367,7 +20408,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="98" t="inlineStr">
+      <c r="C6" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20379,7 +20420,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="98" t="inlineStr">
+      <c r="A7" s="101" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20389,7 +20430,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="98" t="inlineStr">
+      <c r="C7" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20401,7 +20442,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="98" t="inlineStr">
+      <c r="A8" s="101" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20411,7 +20452,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="98" t="inlineStr">
+      <c r="C8" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20423,7 +20464,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="98" t="inlineStr">
+      <c r="A9" s="101" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20433,7 +20474,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="98" t="inlineStr">
+      <c r="C9" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20445,7 +20486,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="98" t="inlineStr">
+      <c r="A10" s="101" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20455,7 +20496,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="98" t="inlineStr">
+      <c r="C10" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20467,7 +20508,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="98" t="inlineStr">
+      <c r="A11" s="101" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20477,7 +20518,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="98" t="inlineStr">
+      <c r="C11" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20489,7 +20530,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="98" t="inlineStr">
+      <c r="A12" s="101" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20499,7 +20540,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="98" t="inlineStr">
+      <c r="C12" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20511,7 +20552,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="98" t="inlineStr">
+      <c r="A13" s="101" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20521,7 +20562,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="98" t="inlineStr">
+      <c r="C13" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20663,53 +20704,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="101" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="101" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="98" t="inlineStr">
+      <c r="C2" s="101" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="98" t="inlineStr">
+      <c r="D2" s="101" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="98" t="inlineStr">
+      <c r="E2" s="101" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="98" t="inlineStr">
+      <c r="F2" s="101" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="98" t="inlineStr">
+      <c r="G2" s="101" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="98" t="inlineStr">
+      <c r="H2" s="101" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="98" t="inlineStr">
+      <c r="I2" s="101" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="98" t="n"/>
-      <c r="K2" s="98" t="inlineStr">
+      <c r="J2" s="101" t="n"/>
+      <c r="K2" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20746,45 +20787,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="98" t="inlineStr">
+      <c r="A3" s="101" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="98" t="inlineStr">
+      <c r="B3" s="101" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="98" t="inlineStr">
+      <c r="C3" s="101" t="inlineStr">
         <is>
           <t>main_idle_20261013044809.png</t>
         </is>
       </c>
-      <c r="D3" s="98" t="n"/>
-      <c r="E3" s="98" t="n"/>
-      <c r="F3" s="98" t="n">
+      <c r="D3" s="101" t="n"/>
+      <c r="E3" s="101" t="n"/>
+      <c r="F3" s="101" t="n">
         <v>0.179</v>
       </c>
-      <c r="G3" s="98" t="n">
+      <c r="G3" s="101" t="n">
         <v>0.23</v>
       </c>
-      <c r="H3" s="98" t="inlineStr">
+      <c r="H3" s="101" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="98" t="inlineStr">
+      <c r="I3" s="101" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="98" t="inlineStr">
+      <c r="J3" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="98" t="inlineStr">
+      <c r="K3" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20821,45 +20862,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="98" t="inlineStr">
+      <c r="A4" s="101" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="98" t="inlineStr">
+      <c r="B4" s="101" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="98" t="inlineStr">
+      <c r="C4" s="101" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="98" t="n"/>
-      <c r="E4" s="98" t="n"/>
-      <c r="F4" s="98" t="inlineStr">
+      <c r="D4" s="101" t="n"/>
+      <c r="E4" s="101" t="n"/>
+      <c r="F4" s="101" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="98" t="inlineStr">
+      <c r="G4" s="101" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="98" t="inlineStr">
+      <c r="H4" s="101" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="98" t="inlineStr">
+      <c r="I4" s="101" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="98" t="n"/>
-      <c r="K4" s="98" t="inlineStr">
+      <c r="J4" s="101" t="n"/>
+      <c r="K4" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20896,45 +20937,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="98" t="inlineStr">
+      <c r="A5" s="101" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="98" t="inlineStr">
+      <c r="B5" s="101" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="98" t="inlineStr">
+      <c r="C5" s="101" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="98" t="n"/>
-      <c r="E5" s="98" t="n"/>
-      <c r="F5" s="98" t="inlineStr">
+      <c r="D5" s="101" t="n"/>
+      <c r="E5" s="101" t="n"/>
+      <c r="F5" s="101" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="98" t="inlineStr">
+      <c r="G5" s="101" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="98" t="inlineStr">
+      <c r="H5" s="101" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="98" t="inlineStr">
+      <c r="I5" s="101" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="98" t="n"/>
-      <c r="K5" s="98" t="inlineStr">
+      <c r="J5" s="101" t="n"/>
+      <c r="K5" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20971,45 +21012,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="98" t="inlineStr">
+      <c r="A6" s="101" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="98" t="inlineStr">
+      <c r="B6" s="101" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="98" t="inlineStr">
+      <c r="C6" s="101" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="98" t="n"/>
-      <c r="E6" s="98" t="n"/>
-      <c r="F6" s="98" t="inlineStr">
+      <c r="D6" s="101" t="n"/>
+      <c r="E6" s="101" t="n"/>
+      <c r="F6" s="101" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="98" t="inlineStr">
+      <c r="G6" s="101" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="98" t="inlineStr">
+      <c r="H6" s="101" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="98" t="inlineStr">
+      <c r="I6" s="101" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="98" t="n"/>
-      <c r="K6" s="98" t="inlineStr">
+      <c r="J6" s="101" t="n"/>
+      <c r="K6" s="101" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -21131,12 +21172,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="101" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21175,12 +21216,12 @@
       <c r="J2" s="46" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="98" t="inlineStr">
+      <c r="A3" s="101" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B3" s="98" t="inlineStr">
+      <c r="B3" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21219,12 +21260,12 @@
       <c r="J3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="98" t="inlineStr">
+      <c r="A4" s="101" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B4" s="98" t="inlineStr">
+      <c r="B4" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21263,12 +21304,12 @@
       <c r="J4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="98" t="inlineStr">
+      <c r="A5" s="101" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B5" s="98" t="inlineStr">
+      <c r="B5" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21307,12 +21348,12 @@
       <c r="J5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="98" t="inlineStr">
+      <c r="A6" s="101" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B6" s="98" t="inlineStr">
+      <c r="B6" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21351,12 +21392,12 @@
       <c r="J6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="98" t="inlineStr">
+      <c r="A7" s="101" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B7" s="98" t="inlineStr">
+      <c r="B7" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21395,12 +21436,12 @@
       <c r="J7" s="46" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="98" t="inlineStr">
+      <c r="A8" s="101" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B8" s="98" t="inlineStr">
+      <c r="B8" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21439,12 +21480,12 @@
       <c r="J8" s="46" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="98" t="inlineStr">
+      <c r="A9" s="101" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B9" s="98" t="inlineStr">
+      <c r="B9" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21483,12 +21524,12 @@
       <c r="J9" s="46" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="98" t="inlineStr">
+      <c r="A10" s="101" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B10" s="98" t="inlineStr">
+      <c r="B10" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21527,12 +21568,12 @@
       <c r="J10" s="46" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="98" t="inlineStr">
+      <c r="A11" s="101" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B11" s="98" t="inlineStr">
+      <c r="B11" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21571,12 +21612,12 @@
       <c r="J11" s="46" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="98" t="inlineStr">
+      <c r="A12" s="101" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B12" s="98" t="inlineStr">
+      <c r="B12" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21615,12 +21656,12 @@
       <c r="J12" s="46" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="98" t="inlineStr">
+      <c r="A13" s="101" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B13" s="98" t="inlineStr">
+      <c r="B13" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21678,12 +21719,12 @@
       <c r="J13" s="46" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="98" t="inlineStr">
+      <c r="A14" s="101" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B14" s="98" t="inlineStr">
+      <c r="B14" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21741,12 +21782,12 @@
       <c r="J14" s="46" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="98" t="inlineStr">
+      <c r="A15" s="101" t="inlineStr">
         <is>
           <t>趣味</t>
         </is>
       </c>
-      <c r="B15" s="98" t="inlineStr">
+      <c r="B15" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21807,12 +21848,12 @@
       <c r="J15" s="46" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="98" t="inlineStr">
+      <c r="A16" s="101" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B16" s="98" t="inlineStr">
+      <c r="B16" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21872,12 +21913,12 @@
       <c r="J16" s="46" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="98" t="inlineStr">
+      <c r="A17" s="101" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B17" s="98" t="inlineStr">
+      <c r="B17" s="101" t="inlineStr">
         <is>
           <t>共通</t>
         </is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -570,6 +570,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1272,7 +1281,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="101" t="inlineStr">
+      <c r="A2" s="105" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1282,31 +1291,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="101" t="n">
+      <c r="C2" s="105" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="101" t="n">
+      <c r="D2" s="105" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="101" t="n">
+      <c r="E2" s="105" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="101" t="n">
+      <c r="F2" s="105" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="101" t="n">
+      <c r="G2" s="105" t="n">
         <v>0.957</v>
       </c>
-      <c r="H2" s="101" t="n">
+      <c r="H2" s="105" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="101" t="n">
+      <c r="I2" s="105" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="101" t="n">
+      <c r="J2" s="105" t="n">
         <v>0.864</v>
       </c>
-      <c r="K2" s="101" t="n">
+      <c r="K2" s="105" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1316,7 +1325,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="101" t="inlineStr">
+      <c r="A3" s="105" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1326,31 +1335,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="101" t="n">
+      <c r="C3" s="105" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="101" t="n">
+      <c r="D3" s="105" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="101" t="n">
+      <c r="E3" s="105" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="101" t="n">
+      <c r="F3" s="105" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="101" t="n">
+      <c r="G3" s="105" t="n">
         <v>0.929</v>
       </c>
-      <c r="H3" s="101" t="n">
+      <c r="H3" s="105" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="101" t="n">
+      <c r="I3" s="105" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="101" t="n">
+      <c r="J3" s="105" t="n">
         <v>0.753</v>
       </c>
-      <c r="K3" s="101" t="n">
+      <c r="K3" s="105" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1360,7 +1369,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="101" t="inlineStr">
+      <c r="A4" s="105" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1370,31 +1379,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="101" t="n">
+      <c r="C4" s="105" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="101" t="n">
+      <c r="D4" s="105" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="101" t="n">
+      <c r="E4" s="105" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="101" t="n">
+      <c r="F4" s="105" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="101" t="n">
+      <c r="G4" s="105" t="n">
         <v>0.92</v>
       </c>
-      <c r="H4" s="101" t="n">
+      <c r="H4" s="105" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="101" t="n">
+      <c r="I4" s="105" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="101" t="n">
+      <c r="J4" s="105" t="n">
         <v>0.884</v>
       </c>
-      <c r="K4" s="101" t="n">
+      <c r="K4" s="105" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1466,7 +1475,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="101" t="inlineStr">
+      <c r="A2" s="105" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1476,10 +1485,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="101" t="n">
+      <c r="C2" s="105" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="101" t="n">
+      <c r="D2" s="105" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1489,7 +1498,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="101" t="inlineStr">
+      <c r="A3" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1499,16 +1508,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="101" t="n">
+      <c r="C3" s="105" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="101" t="n">
+      <c r="D3" s="105" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="101" t="inlineStr">
+      <c r="A4" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1518,16 +1527,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="101" t="n">
+      <c r="C4" s="105" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="101" t="n">
+      <c r="D4" s="105" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="101" t="inlineStr">
+      <c r="A5" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1537,16 +1546,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="101" t="n">
+      <c r="C5" s="105" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="101" t="n">
+      <c r="D5" s="105" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="101" t="inlineStr">
+      <c r="A6" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1556,16 +1565,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="101" t="n">
+      <c r="C6" s="105" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="101" t="n">
+      <c r="D6" s="105" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="101" t="inlineStr">
+      <c r="A7" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1575,10 +1584,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="101" t="n">
+      <c r="C7" s="105" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="101" t="n">
+      <c r="D7" s="105" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1638,17 +1647,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="101" t="inlineStr">
+      <c r="A2" s="105" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="101" t="inlineStr">
+      <c r="B2" s="105" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="101" t="inlineStr">
+      <c r="C2" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1660,17 +1669,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="101" t="inlineStr">
+      <c r="A3" s="105" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="101" t="inlineStr">
+      <c r="B3" s="105" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="101" t="inlineStr">
+      <c r="C3" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1678,17 +1687,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="101" t="inlineStr">
+      <c r="A4" s="105" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="101" t="inlineStr">
+      <c r="B4" s="105" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="101" t="inlineStr">
+      <c r="C4" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1700,17 +1709,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="101" t="inlineStr">
+      <c r="A5" s="105" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="101" t="inlineStr">
+      <c r="B5" s="105" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="101" t="inlineStr">
+      <c r="C5" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1722,17 +1731,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="101" t="inlineStr">
+      <c r="A6" s="105" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="101" t="inlineStr">
+      <c r="B6" s="105" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="101" t="inlineStr">
+      <c r="C6" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1740,17 +1749,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="101" t="inlineStr">
+      <c r="A7" s="105" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="101" t="inlineStr">
+      <c r="B7" s="105" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="101" t="inlineStr">
+      <c r="C7" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1758,17 +1767,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="101" t="inlineStr">
+      <c r="A8" s="105" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="101" t="inlineStr">
+      <c r="B8" s="105" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="101" t="inlineStr">
+      <c r="C8" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1780,17 +1789,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="101" t="inlineStr">
+      <c r="A9" s="105" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="101" t="inlineStr">
+      <c r="B9" s="105" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="101" t="inlineStr">
+      <c r="C9" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1802,17 +1811,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="101" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="101" t="inlineStr">
+      <c r="B10" s="105" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="101" t="inlineStr">
+      <c r="C10" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1824,17 +1833,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="101" t="inlineStr">
+      <c r="A11" s="105" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="101" t="inlineStr">
+      <c r="B11" s="105" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="101" t="inlineStr">
+      <c r="C11" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1842,17 +1851,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="101" t="inlineStr">
+      <c r="A12" s="105" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="101" t="inlineStr">
+      <c r="B12" s="105" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="101" t="inlineStr">
+      <c r="C12" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1860,17 +1869,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="101" t="inlineStr">
+      <c r="A13" s="105" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="101" t="inlineStr">
+      <c r="B13" s="105" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="101" t="inlineStr">
+      <c r="C13" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1882,17 +1891,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="101" t="inlineStr">
+      <c r="A14" s="105" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="101" t="inlineStr">
+      <c r="B14" s="105" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="101" t="inlineStr">
+      <c r="C14" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1904,17 +1913,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="101" t="inlineStr">
+      <c r="A15" s="105" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="101" t="inlineStr">
+      <c r="B15" s="105" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="101" t="inlineStr">
+      <c r="C15" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1926,17 +1935,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="101" t="inlineStr">
+      <c r="A16" s="105" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="101" t="inlineStr">
+      <c r="B16" s="105" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="101" t="inlineStr">
+      <c r="C16" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1948,17 +1957,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="101" t="inlineStr">
+      <c r="A17" s="105" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="101" t="inlineStr">
+      <c r="B17" s="105" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="101" t="inlineStr">
+      <c r="C17" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1970,17 +1979,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="101" t="inlineStr">
+      <c r="A18" s="105" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="101" t="inlineStr">
+      <c r="B18" s="105" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="101" t="inlineStr">
+      <c r="C18" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1992,17 +2001,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="101" t="inlineStr">
+      <c r="A19" s="105" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="101" t="inlineStr">
+      <c r="B19" s="105" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="101" t="inlineStr">
+      <c r="C19" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2010,17 +2019,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="101" t="inlineStr">
+      <c r="A20" s="105" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="101" t="inlineStr">
+      <c r="B20" s="105" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="101" t="inlineStr">
+      <c r="C20" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2028,17 +2037,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="101" t="inlineStr">
+      <c r="A21" s="105" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="101" t="inlineStr">
+      <c r="B21" s="105" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="101" t="inlineStr">
+      <c r="C21" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2050,17 +2059,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="101" t="inlineStr">
+      <c r="A22" s="105" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="101" t="inlineStr">
+      <c r="B22" s="105" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="101" t="inlineStr">
+      <c r="C22" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2072,17 +2081,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="101" t="inlineStr">
+      <c r="A23" s="105" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="101" t="inlineStr">
+      <c r="B23" s="105" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="101" t="inlineStr">
+      <c r="C23" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2094,17 +2103,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="101" t="inlineStr">
+      <c r="A24" s="105" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="101" t="inlineStr">
+      <c r="B24" s="105" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="101" t="inlineStr">
+      <c r="C24" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2116,17 +2125,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="101" t="inlineStr">
+      <c r="A25" s="105" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="101" t="inlineStr">
+      <c r="B25" s="105" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="101" t="inlineStr">
+      <c r="C25" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2134,17 +2143,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="101" t="inlineStr">
+      <c r="A26" s="105" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="101" t="inlineStr">
+      <c r="B26" s="105" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="101" t="inlineStr">
+      <c r="C26" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2152,17 +2161,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="101" t="inlineStr">
+      <c r="A27" s="105" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="101" t="inlineStr">
+      <c r="B27" s="105" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="101" t="inlineStr">
+      <c r="C27" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2174,17 +2183,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="101" t="inlineStr">
+      <c r="A28" s="105" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="101" t="inlineStr">
+      <c r="B28" s="105" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="101" t="inlineStr">
+      <c r="C28" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2196,17 +2205,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="101" t="inlineStr">
+      <c r="A29" s="105" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="101" t="inlineStr">
+      <c r="B29" s="105" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="101" t="inlineStr">
+      <c r="C29" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2218,17 +2227,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="101" t="inlineStr">
+      <c r="A30" s="105" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="101" t="inlineStr">
+      <c r="B30" s="105" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="101" t="inlineStr">
+      <c r="C30" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2236,17 +2245,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="101" t="inlineStr">
+      <c r="A31" s="105" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="101" t="inlineStr">
+      <c r="B31" s="105" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="101" t="inlineStr">
+      <c r="C31" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2258,17 +2267,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="101" t="inlineStr">
+      <c r="A32" s="105" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="101" t="inlineStr">
+      <c r="B32" s="105" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="101" t="inlineStr">
+      <c r="C32" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2276,17 +2285,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="101" t="inlineStr">
+      <c r="A33" s="105" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="101" t="inlineStr">
+      <c r="B33" s="105" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="101" t="inlineStr">
+      <c r="C33" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2294,17 +2303,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="101" t="inlineStr">
+      <c r="A34" s="105" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="101" t="inlineStr">
+      <c r="B34" s="105" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="101" t="inlineStr">
+      <c r="C34" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2312,17 +2321,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="101" t="inlineStr">
+      <c r="A35" s="105" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="101" t="inlineStr">
+      <c r="B35" s="105" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="101" t="inlineStr">
+      <c r="C35" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2330,17 +2339,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="101" t="inlineStr">
+      <c r="A36" s="105" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="101" t="inlineStr">
+      <c r="B36" s="105" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="101" t="inlineStr">
+      <c r="C36" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2348,17 +2357,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="101" t="inlineStr">
+      <c r="A37" s="105" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="101" t="inlineStr">
+      <c r="B37" s="105" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="101" t="inlineStr">
+      <c r="C37" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2366,17 +2375,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="101" t="inlineStr">
+      <c r="A38" s="105" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="101" t="inlineStr">
+      <c r="B38" s="105" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="101" t="inlineStr">
+      <c r="C38" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2384,17 +2393,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="101" t="inlineStr">
+      <c r="A39" s="105" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="101" t="inlineStr">
+      <c r="B39" s="105" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="101" t="inlineStr">
+      <c r="C39" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2402,17 +2411,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="101" t="inlineStr">
+      <c r="A40" s="105" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="101" t="inlineStr">
+      <c r="B40" s="105" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="101" t="inlineStr">
+      <c r="C40" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2424,17 +2433,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="101" t="inlineStr">
+      <c r="A41" s="105" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="101" t="inlineStr">
+      <c r="B41" s="105" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="101" t="inlineStr">
+      <c r="C41" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2442,17 +2451,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="101" t="inlineStr">
+      <c r="A42" s="105" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="101" t="inlineStr">
+      <c r="B42" s="105" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="101" t="inlineStr">
+      <c r="C42" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2464,17 +2473,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="101" t="inlineStr">
+      <c r="A43" s="105" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="101" t="inlineStr">
+      <c r="B43" s="105" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="101" t="inlineStr">
+      <c r="C43" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2482,17 +2491,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="101" t="inlineStr">
+      <c r="A44" s="105" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="101" t="inlineStr">
+      <c r="B44" s="105" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="101" t="inlineStr">
+      <c r="C44" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2504,17 +2513,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="101" t="inlineStr">
+      <c r="A45" s="105" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="101" t="inlineStr">
+      <c r="B45" s="105" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="101" t="inlineStr">
+      <c r="C45" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2863,17 +2872,17 @@
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="100" t="inlineStr">
+      <c r="A6" s="104" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B6" s="100" t="inlineStr">
+      <c r="B6" s="104" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C6" s="100" t="inlineStr">
+      <c r="C6" s="104" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2898,49 +2907,49 @@
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
         </is>
       </c>
-      <c r="G6" s="100" t="n"/>
-      <c r="H6" s="100" t="n"/>
-      <c r="I6" s="100" t="inlineStr">
+      <c r="G6" s="104" t="n"/>
+      <c r="H6" s="104" t="n"/>
+      <c r="I6" s="104" t="inlineStr">
         <is>
           <t>atm_bt.mp3</t>
         </is>
       </c>
-      <c r="J6" s="100" t="inlineStr">
+      <c r="J6" s="104" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K6" s="100" t="n"/>
-      <c r="L6" s="100" t="n"/>
-      <c r="M6" s="100" t="inlineStr">
+      <c r="K6" s="104" t="n"/>
+      <c r="L6" s="104" t="n"/>
+      <c r="M6" s="104" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N6" s="101" t="inlineStr">
+      <c r="N6" s="105" t="inlineStr">
         <is>
           <t>ATMはどこ</t>
         </is>
       </c>
-      <c r="O6" s="101" t="n"/>
-      <c r="P6" s="101" t="inlineStr">
+      <c r="O6" s="105" t="n"/>
+      <c r="P6" s="105" t="inlineStr">
         <is>
           <t>2026-10-13 17:14</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="100" t="inlineStr">
+      <c r="A7" s="104" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B7" s="100" t="inlineStr">
+      <c r="B7" s="104" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C7" s="100" t="inlineStr">
+      <c r="C7" s="104" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2965,28 +2974,28 @@
           <t>海外のカードは鳩谷郵便局のATM、日本のカードは和田家前のJAのATMをご利用ください。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G7" s="100" t="n"/>
-      <c r="H7" s="100" t="n"/>
-      <c r="I7" s="100" t="inlineStr">
+      <c r="G7" s="104" t="n"/>
+      <c r="H7" s="104" t="n"/>
+      <c r="I7" s="104" t="inlineStr">
         <is>
           <t>atm_deai.mp3</t>
         </is>
       </c>
-      <c r="J7" s="100" t="inlineStr">
+      <c r="J7" s="104" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K7" s="100" t="n"/>
-      <c r="L7" s="100" t="n"/>
-      <c r="M7" s="100" t="inlineStr">
+      <c r="K7" s="104" t="n"/>
+      <c r="L7" s="104" t="n"/>
+      <c r="M7" s="104" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N7" s="101" t="n"/>
-      <c r="O7" s="101" t="n"/>
-      <c r="P7" s="101" t="inlineStr">
+      <c r="N7" s="105" t="n"/>
+      <c r="O7" s="105" t="n"/>
+      <c r="P7" s="105" t="inlineStr">
         <is>
           <t>2026-10-13 17:15</t>
         </is>
@@ -3042,17 +3051,17 @@
       </c>
     </row>
     <row r="9" ht="58.05" customHeight="1">
-      <c r="A9" s="100" t="inlineStr">
+      <c r="A9" s="104" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B9" s="100" t="inlineStr">
+      <c r="B9" s="104" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C9" s="100" t="inlineStr">
+      <c r="C9" s="104" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3072,45 +3081,45 @@
         </is>
       </c>
       <c r="F9" s="44" t="n"/>
-      <c r="G9" s="100" t="n"/>
-      <c r="H9" s="100" t="n"/>
-      <c r="I9" s="100" t="inlineStr">
+      <c r="G9" s="104" t="n"/>
+      <c r="H9" s="104" t="n"/>
+      <c r="I9" s="104" t="inlineStr">
         <is>
           <t>currency_exchange_bt.mp3</t>
         </is>
       </c>
-      <c r="J9" s="100" t="inlineStr">
+      <c r="J9" s="104" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K9" s="100" t="n"/>
-      <c r="L9" s="100" t="n"/>
-      <c r="M9" s="100" t="inlineStr">
+      <c r="K9" s="104" t="n"/>
+      <c r="L9" s="104" t="n"/>
+      <c r="M9" s="104" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N9" s="101" t="n"/>
-      <c r="O9" s="101" t="n"/>
-      <c r="P9" s="101" t="inlineStr">
+      <c r="N9" s="105" t="n"/>
+      <c r="O9" s="105" t="n"/>
+      <c r="P9" s="105" t="inlineStr">
         <is>
           <t>2026-10-13 17:18</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58.05" customHeight="1">
-      <c r="A10" s="100" t="inlineStr">
+      <c r="A10" s="104" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B10" s="100" t="inlineStr">
+      <c r="B10" s="104" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C10" s="100" t="inlineStr">
+      <c r="C10" s="104" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3130,45 +3139,45 @@
         </is>
       </c>
       <c r="F10" s="44" t="n"/>
-      <c r="G10" s="100" t="n"/>
-      <c r="H10" s="100" t="n"/>
-      <c r="I10" s="100" t="inlineStr">
+      <c r="G10" s="104" t="n"/>
+      <c r="H10" s="104" t="n"/>
+      <c r="I10" s="104" t="inlineStr">
         <is>
           <t>currency_exchange_deai.mp3</t>
         </is>
       </c>
-      <c r="J10" s="100" t="inlineStr">
+      <c r="J10" s="104" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K10" s="100" t="n"/>
-      <c r="L10" s="100" t="n"/>
-      <c r="M10" s="100" t="inlineStr">
+      <c r="K10" s="104" t="n"/>
+      <c r="L10" s="104" t="n"/>
+      <c r="M10" s="104" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N10" s="101" t="n"/>
-      <c r="O10" s="101" t="n"/>
-      <c r="P10" s="101" t="inlineStr">
+      <c r="N10" s="105" t="n"/>
+      <c r="O10" s="105" t="n"/>
+      <c r="P10" s="105" t="inlineStr">
         <is>
           <t>2026-10-13 17:19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58.05" customHeight="1">
-      <c r="A11" s="100" t="inlineStr">
+      <c r="A11" s="104" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B11" s="100" t="inlineStr">
+      <c r="B11" s="104" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C11" s="100" t="inlineStr">
+      <c r="C11" s="104" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3189,49 +3198,49 @@
         </is>
       </c>
       <c r="F11" s="44" t="n"/>
-      <c r="G11" s="100" t="n"/>
-      <c r="H11" s="100" t="n"/>
-      <c r="I11" s="100" t="inlineStr">
+      <c r="G11" s="104" t="n"/>
+      <c r="H11" s="104" t="n"/>
+      <c r="I11" s="104" t="inlineStr">
         <is>
           <t>luggage_bt.mp3</t>
         </is>
       </c>
-      <c r="J11" s="100" t="inlineStr">
+      <c r="J11" s="104" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K11" s="100" t="n"/>
-      <c r="L11" s="100" t="n"/>
-      <c r="M11" s="100" t="inlineStr">
+      <c r="K11" s="104" t="n"/>
+      <c r="L11" s="104" t="n"/>
+      <c r="M11" s="104" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N11" s="101" t="inlineStr">
+      <c r="N11" s="105" t="inlineStr">
         <is>
           <t>荷物を預けたい</t>
         </is>
       </c>
-      <c r="O11" s="101" t="n"/>
-      <c r="P11" s="101" t="inlineStr">
+      <c r="O11" s="105" t="n"/>
+      <c r="P11" s="105" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58.05" customHeight="1">
-      <c r="A12" s="100" t="inlineStr">
+      <c r="A12" s="104" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B12" s="100" t="inlineStr">
+      <c r="B12" s="104" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C12" s="100" t="inlineStr">
+      <c r="C12" s="104" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3252,28 +3261,28 @@
         </is>
       </c>
       <c r="F12" s="44" t="n"/>
-      <c r="G12" s="100" t="n"/>
-      <c r="H12" s="100" t="n"/>
-      <c r="I12" s="100" t="inlineStr">
+      <c r="G12" s="104" t="n"/>
+      <c r="H12" s="104" t="n"/>
+      <c r="I12" s="104" t="inlineStr">
         <is>
           <t>luggage_deai.mp3</t>
         </is>
       </c>
-      <c r="J12" s="100" t="inlineStr">
+      <c r="J12" s="104" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K12" s="100" t="n"/>
-      <c r="L12" s="100" t="n"/>
-      <c r="M12" s="100" t="inlineStr">
+      <c r="K12" s="104" t="n"/>
+      <c r="L12" s="104" t="n"/>
+      <c r="M12" s="104" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N12" s="101" t="n"/>
-      <c r="O12" s="101" t="n"/>
-      <c r="P12" s="101" t="inlineStr">
+      <c r="N12" s="105" t="n"/>
+      <c r="O12" s="105" t="n"/>
+      <c r="P12" s="105" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
@@ -3336,17 +3345,17 @@
       </c>
     </row>
     <row r="14" ht="58.05" customHeight="1">
-      <c r="A14" s="100" t="inlineStr">
+      <c r="A14" s="104" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B14" s="100" t="inlineStr">
+      <c r="B14" s="104" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C14" s="100" t="inlineStr">
+      <c r="C14" s="104" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3366,45 +3375,45 @@
         </is>
       </c>
       <c r="F14" s="44" t="n"/>
-      <c r="G14" s="100" t="n"/>
-      <c r="H14" s="100" t="n"/>
-      <c r="I14" s="100" t="inlineStr">
+      <c r="G14" s="104" t="n"/>
+      <c r="H14" s="104" t="n"/>
+      <c r="I14" s="104" t="inlineStr">
         <is>
           <t>stamp_bt.mp3</t>
         </is>
       </c>
-      <c r="J14" s="100" t="inlineStr">
+      <c r="J14" s="104" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K14" s="100" t="n"/>
-      <c r="L14" s="100" t="n"/>
-      <c r="M14" s="100" t="inlineStr">
+      <c r="K14" s="104" t="n"/>
+      <c r="L14" s="104" t="n"/>
+      <c r="M14" s="104" t="inlineStr">
         <is>
           <t>stamp</t>
         </is>
       </c>
-      <c r="N14" s="101" t="n"/>
-      <c r="O14" s="101" t="n"/>
-      <c r="P14" s="101" t="inlineStr">
+      <c r="N14" s="105" t="n"/>
+      <c r="O14" s="105" t="n"/>
+      <c r="P14" s="105" t="inlineStr">
         <is>
           <t>2026-10-13 17:22</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58.05" customHeight="1">
-      <c r="A15" s="100" t="inlineStr">
+      <c r="A15" s="104" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B15" s="100" t="inlineStr">
+      <c r="B15" s="104" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C15" s="100" t="inlineStr">
+      <c r="C15" s="104" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3424,28 +3433,28 @@
         </is>
       </c>
       <c r="F15" s="44" t="n"/>
-      <c r="G15" s="100" t="n"/>
-      <c r="H15" s="100" t="n"/>
-      <c r="I15" s="100" t="inlineStr">
+      <c r="G15" s="104" t="n"/>
+      <c r="H15" s="104" t="n"/>
+      <c r="I15" s="104" t="inlineStr">
         <is>
           <t>stamp_deai.mp3</t>
         </is>
       </c>
-      <c r="J15" s="100" t="inlineStr">
+      <c r="J15" s="104" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K15" s="100" t="n"/>
-      <c r="L15" s="100" t="n"/>
-      <c r="M15" s="100" t="inlineStr">
+      <c r="K15" s="104" t="n"/>
+      <c r="L15" s="104" t="n"/>
+      <c r="M15" s="104" t="inlineStr">
         <is>
           <t>stamp</t>
         </is>
       </c>
-      <c r="N15" s="101" t="n"/>
-      <c r="O15" s="101" t="n"/>
-      <c r="P15" s="101" t="inlineStr">
+      <c r="N15" s="105" t="n"/>
+      <c r="O15" s="105" t="n"/>
+      <c r="P15" s="105" t="inlineStr">
         <is>
           <t>2026-10-13 17:23</t>
         </is>
@@ -3565,17 +3574,17 @@
       </c>
     </row>
     <row r="18" ht="58.05" customHeight="1">
-      <c r="A18" s="100" t="inlineStr">
+      <c r="A18" s="104" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B18" s="100" t="inlineStr">
+      <c r="B18" s="104" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C18" s="100" t="inlineStr">
+      <c r="C18" s="104" t="inlineStr">
         <is>
           <t>sightseeing</t>
         </is>
@@ -3600,49 +3609,49 @@
           <t>展望台へは、自家用車で行くことはできません。歩いておよそ15分、またはシャトルバスでお越しいただけます。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G18" s="100" t="n"/>
-      <c r="H18" s="100" t="n"/>
-      <c r="I18" s="100" t="inlineStr">
+      <c r="G18" s="104" t="n"/>
+      <c r="H18" s="104" t="n"/>
+      <c r="I18" s="104" t="inlineStr">
         <is>
           <t>observatory_access_bt.mp3</t>
         </is>
       </c>
-      <c r="J18" s="100" t="inlineStr">
+      <c r="J18" s="104" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K18" s="100" t="n"/>
-      <c r="L18" s="100" t="n"/>
-      <c r="M18" s="100" t="inlineStr">
+      <c r="K18" s="104" t="n"/>
+      <c r="L18" s="104" t="n"/>
+      <c r="M18" s="104" t="inlineStr">
         <is>
           <t>observatory_access</t>
         </is>
       </c>
-      <c r="N18" s="101" t="inlineStr">
+      <c r="N18" s="105" t="inlineStr">
         <is>
           <t>展望台への行き方</t>
         </is>
       </c>
-      <c r="O18" s="101" t="n"/>
-      <c r="P18" s="101" t="inlineStr">
+      <c r="O18" s="105" t="n"/>
+      <c r="P18" s="105" t="inlineStr">
         <is>
           <t>2026-10-13 17:26</t>
         </is>
       </c>
     </row>
     <row r="19" ht="79.2" customHeight="1">
-      <c r="A19" s="100" t="inlineStr">
+      <c r="A19" s="104" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B19" s="100" t="inlineStr">
+      <c r="B19" s="104" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C19" s="100" t="inlineStr">
+      <c r="C19" s="104" t="inlineStr">
         <is>
           <t>sightseeing</t>
         </is>
@@ -3666,28 +3675,28 @@
           <t>展望台へは、目の前の橋を渡り、大通りを左へ10分ほど進んだ池の前のバス停から、シャトルバスが出ています。遊歩道もございます。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G19" s="100" t="n"/>
-      <c r="H19" s="100" t="n"/>
-      <c r="I19" s="100" t="inlineStr">
+      <c r="G19" s="104" t="n"/>
+      <c r="H19" s="104" t="n"/>
+      <c r="I19" s="104" t="inlineStr">
         <is>
           <t>observatory_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J19" s="100" t="inlineStr">
+      <c r="J19" s="104" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K19" s="100" t="n"/>
-      <c r="L19" s="100" t="n"/>
-      <c r="M19" s="100" t="inlineStr">
+      <c r="K19" s="104" t="n"/>
+      <c r="L19" s="104" t="n"/>
+      <c r="M19" s="104" t="inlineStr">
         <is>
           <t>observatory_access</t>
         </is>
       </c>
-      <c r="N19" s="101" t="n"/>
-      <c r="O19" s="101" t="n"/>
-      <c r="P19" s="101" t="inlineStr">
+      <c r="N19" s="105" t="n"/>
+      <c r="O19" s="105" t="n"/>
+      <c r="P19" s="105" t="inlineStr">
         <is>
           <t>2026-10-13 17:27</t>
         </is>
@@ -4843,22 +4852,22 @@
       </c>
     </row>
     <row r="40" ht="66" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="108" t="inlineStr">
         <is>
           <t>festival_shrine_access_bt</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="108" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C40" s="108" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D40" s="44" t="inlineStr">
         <is>
           <t>白川八幡神社 どこ
 神社 行き方
@@ -4866,29 +4875,36 @@
 どぶろく どこ</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="11" t="n"/>
-      <c r="H40" s="11" t="n"/>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="E40" s="44" t="inlineStr">
+        <is>
+          <t>会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは約800m、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
+        </is>
+      </c>
+      <c r="F40" s="44" t="n"/>
+      <c r="G40" s="108" t="n"/>
+      <c r="H40" s="108" t="n"/>
+      <c r="I40" s="108" t="inlineStr">
         <is>
           <t>festival_shrine_access_bt.mp3</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K40" s="11" t="n"/>
-      <c r="L40" s="11" t="n"/>
-      <c r="M40" s="14" t="inlineStr">
+      <c r="J40" s="108" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K40" s="108" t="n"/>
+      <c r="L40" s="108" t="n"/>
+      <c r="M40" s="108" t="inlineStr">
         <is>
           <t>festival_shrine_access</t>
+        </is>
+      </c>
+      <c r="N40" s="109" t="n"/>
+      <c r="O40" s="109" t="n"/>
+      <c r="P40" s="109" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:30</t>
         </is>
       </c>
     </row>
@@ -5012,17 +5028,17 @@
       </c>
     </row>
     <row r="43" ht="249.6" customHeight="1">
-      <c r="A43" s="100" t="inlineStr">
+      <c r="A43" s="104" t="inlineStr">
         <is>
           <t>guesthouse_access_deai</t>
         </is>
       </c>
-      <c r="B43" s="100" t="inlineStr">
+      <c r="B43" s="104" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C43" s="100" t="inlineStr">
+      <c r="C43" s="104" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -5056,30 +5072,30 @@
           <t>その建物は鳩谷八幡神社方面にあります。国道は交通量が多いため、川沿いの道をおすすめしております。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G43" s="100" t="inlineStr">
+      <c r="G43" s="104" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H43" s="100" t="n"/>
-      <c r="I43" s="100" t="inlineStr">
+      <c r="H43" s="104" t="n"/>
+      <c r="I43" s="104" t="inlineStr">
         <is>
           <t>guesthouse_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J43" s="100" t="inlineStr">
+      <c r="J43" s="104" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K43" s="100" t="n"/>
-      <c r="L43" s="100" t="n"/>
-      <c r="M43" s="100" t="inlineStr">
+      <c r="K43" s="104" t="n"/>
+      <c r="L43" s="104" t="n"/>
+      <c r="M43" s="104" t="inlineStr">
         <is>
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="101" t="n"/>
+      <c r="N43" s="105" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -6268,17 +6284,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="101" t="inlineStr">
+      <c r="A66" s="105" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="101" t="inlineStr">
+      <c r="B66" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="101" t="inlineStr">
+      <c r="C66" s="105" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -6308,26 +6324,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="101" t="inlineStr">
+      <c r="G66" s="105" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="101" t="n"/>
-      <c r="I66" s="101" t="inlineStr">
+      <c r="H66" s="105" t="n"/>
+      <c r="I66" s="105" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="101" t="inlineStr">
+      <c r="J66" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="101" t="n"/>
-      <c r="L66" s="101" t="n"/>
-      <c r="M66" s="101" t="n"/>
-      <c r="N66" s="101" t="n"/>
+      <c r="K66" s="105" t="n"/>
+      <c r="L66" s="105" t="n"/>
+      <c r="M66" s="105" t="n"/>
+      <c r="N66" s="105" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -7536,12 +7552,12 @@
       </c>
     </row>
     <row r="22" ht="64.8" customHeight="1">
-      <c r="A22" s="101" t="inlineStr">
+      <c r="A22" s="105" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B22" s="101" t="inlineStr">
+      <c r="B22" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7572,12 +7588,12 @@
       </c>
     </row>
     <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="101" t="inlineStr">
+      <c r="A23" s="105" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B23" s="101" t="inlineStr">
+      <c r="B23" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7608,12 +7624,12 @@
       </c>
     </row>
     <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="101" t="inlineStr">
+      <c r="A24" s="105" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B24" s="101" t="inlineStr">
+      <c r="B24" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7644,12 +7660,12 @@
       </c>
     </row>
     <row r="25" ht="81" customHeight="1">
-      <c r="A25" s="101" t="inlineStr">
+      <c r="A25" s="105" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B25" s="101" t="inlineStr">
+      <c r="B25" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7716,12 +7732,12 @@
       </c>
     </row>
     <row r="27" ht="64.8" customHeight="1">
-      <c r="A27" s="102" t="inlineStr">
+      <c r="A27" s="106" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B27" s="102" t="inlineStr">
+      <c r="B27" s="106" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7752,12 +7768,12 @@
       </c>
     </row>
     <row r="28" ht="64.8" customHeight="1">
-      <c r="A28" s="102" t="inlineStr">
+      <c r="A28" s="106" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B28" s="102" t="inlineStr">
+      <c r="B28" s="106" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7788,12 +7804,12 @@
       </c>
     </row>
     <row r="29" ht="64.8" customHeight="1">
-      <c r="A29" s="102" t="inlineStr">
+      <c r="A29" s="106" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B29" s="102" t="inlineStr">
+      <c r="B29" s="106" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7824,12 +7840,12 @@
       </c>
     </row>
     <row r="30" ht="81" customHeight="1">
-      <c r="A30" s="102" t="inlineStr">
+      <c r="A30" s="106" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B30" s="102" t="inlineStr">
+      <c r="B30" s="106" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7860,12 +7876,12 @@
       </c>
     </row>
     <row r="31" ht="64.8" customHeight="1">
-      <c r="A31" s="103" t="inlineStr">
+      <c r="A31" s="107" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B31" s="103" t="inlineStr">
+      <c r="B31" s="107" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8057,12 +8073,12 @@
       </c>
     </row>
     <row r="37" ht="64.8" customHeight="1">
-      <c r="A37" s="102" t="inlineStr">
+      <c r="A37" s="106" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B37" s="102" t="inlineStr">
+      <c r="B37" s="106" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8093,12 +8109,12 @@
       </c>
     </row>
     <row r="38" ht="64.8" customHeight="1">
-      <c r="A38" s="102" t="inlineStr">
+      <c r="A38" s="106" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B38" s="102" t="inlineStr">
+      <c r="B38" s="106" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8129,12 +8145,12 @@
       </c>
     </row>
     <row r="39" ht="64.8" customHeight="1">
-      <c r="A39" s="102" t="inlineStr">
+      <c r="A39" s="106" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B39" s="102" t="inlineStr">
+      <c r="B39" s="106" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8165,12 +8181,12 @@
       </c>
     </row>
     <row r="40" ht="113.4" customHeight="1">
-      <c r="A40" s="102" t="inlineStr">
+      <c r="A40" s="106" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B40" s="102" t="inlineStr">
+      <c r="B40" s="106" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8201,12 +8217,12 @@
       </c>
     </row>
     <row r="41" ht="97.2" customHeight="1">
-      <c r="A41" s="103" t="inlineStr">
+      <c r="A41" s="107" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B41" s="103" t="inlineStr">
+      <c r="B41" s="107" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8237,12 +8253,12 @@
       </c>
     </row>
     <row r="42" ht="64.8" customHeight="1">
-      <c r="A42" s="101" t="inlineStr">
+      <c r="A42" s="105" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B42" s="101" t="inlineStr">
+      <c r="B42" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8273,12 +8289,12 @@
       </c>
     </row>
     <row r="43" ht="64.8" customHeight="1">
-      <c r="A43" s="101" t="inlineStr">
+      <c r="A43" s="105" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B43" s="101" t="inlineStr">
+      <c r="B43" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8309,12 +8325,12 @@
       </c>
     </row>
     <row r="44" ht="81" customHeight="1">
-      <c r="A44" s="101" t="inlineStr">
+      <c r="A44" s="105" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B44" s="101" t="inlineStr">
+      <c r="B44" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8345,12 +8361,12 @@
       </c>
     </row>
     <row r="45" ht="64.8" customHeight="1">
-      <c r="A45" s="101" t="inlineStr">
+      <c r="A45" s="105" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B45" s="101" t="inlineStr">
+      <c r="B45" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8417,12 +8433,12 @@
       </c>
     </row>
     <row r="47" ht="81" customHeight="1">
-      <c r="A47" s="102" t="inlineStr">
+      <c r="A47" s="106" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B47" s="102" t="inlineStr">
+      <c r="B47" s="106" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8453,12 +8469,12 @@
       </c>
     </row>
     <row r="48" ht="64.8" customHeight="1">
-      <c r="A48" s="102" t="inlineStr">
+      <c r="A48" s="106" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B48" s="102" t="inlineStr">
+      <c r="B48" s="106" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8489,12 +8505,12 @@
       </c>
     </row>
     <row r="49" ht="64.8" customHeight="1">
-      <c r="A49" s="102" t="inlineStr">
+      <c r="A49" s="106" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B49" s="102" t="inlineStr">
+      <c r="B49" s="106" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8525,12 +8541,12 @@
       </c>
     </row>
     <row r="50" ht="64.8" customHeight="1">
-      <c r="A50" s="102" t="inlineStr">
+      <c r="A50" s="106" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B50" s="102" t="inlineStr">
+      <c r="B50" s="106" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8561,12 +8577,12 @@
       </c>
     </row>
     <row r="51" ht="48.6" customHeight="1">
-      <c r="A51" s="103" t="inlineStr">
+      <c r="A51" s="107" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B51" s="103" t="inlineStr">
+      <c r="B51" s="107" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8597,12 +8613,12 @@
       </c>
     </row>
     <row r="52" ht="48.6" customHeight="1">
-      <c r="A52" s="101" t="inlineStr">
+      <c r="A52" s="105" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B52" s="101" t="inlineStr">
+      <c r="B52" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8633,12 +8649,12 @@
       </c>
     </row>
     <row r="53" ht="97.2" customHeight="1">
-      <c r="A53" s="101" t="inlineStr">
+      <c r="A53" s="105" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B53" s="101" t="inlineStr">
+      <c r="B53" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8669,12 +8685,12 @@
       </c>
     </row>
     <row r="54" ht="97.2" customHeight="1">
-      <c r="A54" s="101" t="inlineStr">
+      <c r="A54" s="105" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B54" s="101" t="inlineStr">
+      <c r="B54" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8705,12 +8721,12 @@
       </c>
     </row>
     <row r="55" ht="97.2" customHeight="1">
-      <c r="A55" s="101" t="inlineStr">
+      <c r="A55" s="105" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B55" s="101" t="inlineStr">
+      <c r="B55" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8941,12 +8957,12 @@
       </c>
     </row>
     <row r="62" ht="81" customHeight="1">
-      <c r="A62" s="101" t="inlineStr">
+      <c r="A62" s="105" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B62" s="101" t="inlineStr">
+      <c r="B62" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8977,12 +8993,12 @@
       </c>
     </row>
     <row r="63" ht="97.2" customHeight="1">
-      <c r="A63" s="101" t="inlineStr">
+      <c r="A63" s="105" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B63" s="101" t="inlineStr">
+      <c r="B63" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -9013,12 +9029,12 @@
       </c>
     </row>
     <row r="64" ht="97.2" customHeight="1">
-      <c r="A64" s="101" t="inlineStr">
+      <c r="A64" s="105" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B64" s="101" t="inlineStr">
+      <c r="B64" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -9049,12 +9065,12 @@
       </c>
     </row>
     <row r="65" ht="97.2" customHeight="1">
-      <c r="A65" s="101" t="inlineStr">
+      <c r="A65" s="105" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B65" s="101" t="inlineStr">
+      <c r="B65" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -9121,12 +9137,12 @@
       </c>
     </row>
     <row r="67" ht="81" customHeight="1">
-      <c r="A67" s="102" t="inlineStr">
+      <c r="A67" s="106" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B67" s="102" t="inlineStr">
+      <c r="B67" s="106" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -9157,12 +9173,12 @@
       </c>
     </row>
     <row r="68" ht="97.2" customHeight="1">
-      <c r="A68" s="102" t="inlineStr">
+      <c r="A68" s="106" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B68" s="102" t="inlineStr">
+      <c r="B68" s="106" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -9193,12 +9209,12 @@
       </c>
     </row>
     <row r="69" ht="97.2" customHeight="1">
-      <c r="A69" s="102" t="inlineStr">
+      <c r="A69" s="106" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B69" s="102" t="inlineStr">
+      <c r="B69" s="106" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -9229,12 +9245,12 @@
       </c>
     </row>
     <row r="70" ht="97.2" customHeight="1">
-      <c r="A70" s="102" t="inlineStr">
+      <c r="A70" s="106" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B70" s="102" t="inlineStr">
+      <c r="B70" s="106" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -9265,12 +9281,12 @@
       </c>
     </row>
     <row r="71" ht="81" customHeight="1">
-      <c r="A71" s="103" t="inlineStr">
+      <c r="A71" s="107" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B71" s="103" t="inlineStr">
+      <c r="B71" s="107" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -9631,12 +9647,12 @@
       </c>
     </row>
     <row r="82" ht="145.8" customHeight="1">
-      <c r="A82" s="101" t="inlineStr">
+      <c r="A82" s="105" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B82" s="101" t="inlineStr">
+      <c r="B82" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -9668,12 +9684,12 @@
       </c>
     </row>
     <row r="83" ht="145.8" customHeight="1">
-      <c r="A83" s="101" t="inlineStr">
+      <c r="A83" s="105" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B83" s="101" t="inlineStr">
+      <c r="B83" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -9705,12 +9721,12 @@
       </c>
     </row>
     <row r="84" ht="162" customHeight="1">
-      <c r="A84" s="101" t="inlineStr">
+      <c r="A84" s="105" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B84" s="101" t="inlineStr">
+      <c r="B84" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -9742,12 +9758,12 @@
       </c>
     </row>
     <row r="85" ht="145.8" customHeight="1">
-      <c r="A85" s="101" t="inlineStr">
+      <c r="A85" s="105" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B85" s="101" t="inlineStr">
+      <c r="B85" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -9816,12 +9832,12 @@
       </c>
     </row>
     <row r="87" ht="97.2" customHeight="1">
-      <c r="A87" s="102" t="inlineStr">
+      <c r="A87" s="106" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B87" s="102" t="inlineStr">
+      <c r="B87" s="106" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -9852,12 +9868,12 @@
       </c>
     </row>
     <row r="88" ht="97.2" customHeight="1">
-      <c r="A88" s="102" t="inlineStr">
+      <c r="A88" s="106" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B88" s="102" t="inlineStr">
+      <c r="B88" s="106" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -9888,12 +9904,12 @@
       </c>
     </row>
     <row r="89" ht="97.2" customHeight="1">
-      <c r="A89" s="102" t="inlineStr">
+      <c r="A89" s="106" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B89" s="102" t="inlineStr">
+      <c r="B89" s="106" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -9924,12 +9940,12 @@
       </c>
     </row>
     <row r="90" ht="97.2" customHeight="1">
-      <c r="A90" s="102" t="inlineStr">
+      <c r="A90" s="106" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B90" s="102" t="inlineStr">
+      <c r="B90" s="106" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -9960,12 +9976,12 @@
       </c>
     </row>
     <row r="91" ht="97.2" customHeight="1">
-      <c r="A91" s="103" t="inlineStr">
+      <c r="A91" s="107" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B91" s="103" t="inlineStr">
+      <c r="B91" s="107" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -13299,32 +13315,35 @@
       </c>
     </row>
     <row r="192" ht="97.2" customHeight="1">
-      <c r="A192" s="21" t="inlineStr">
+      <c r="A192" s="109" t="inlineStr">
         <is>
           <t>festival_shrine_access_bt</t>
         </is>
       </c>
-      <c r="B192" s="21" t="inlineStr">
+      <c r="B192" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="C192" s="22" t="inlineStr">
-        <is>
-          <t>Shirakawa Hachiman
-shrine where
-shrine get
+      <c r="C192" s="46" t="inlineStr">
+        <is>
+          <t>Shirakawa Hachiман Shrine location
+how to get to shrine
 festival venue
 doburoku where
-festival place</t>
-        </is>
-      </c>
-      <c r="D192" s="22" t="inlineStr">
-        <is>
-          <t>The venue, Shirakawa Hachiman Shrine, is at the southern end of the Ogimachi gassho-style village. From Shirakawa-go Bus Terminal, it is about a 15 to 20 minute walk south, along the main street lined with gassho-style houses.</t>
-        </is>
-      </c>
-      <c r="E192" s="21" t="n"/>
+shrine access directions</t>
+        </is>
+      </c>
+      <c r="D192" s="46" t="inlineStr">
+        <is>
+          <t>The festival venue, Shirakawa Hachiман Shrine, is located at the southern end of the Ogimachi Gassho-zukuri village. From the Shirakawa-go Bus Terminal, it is approximately eight hundred metres away. Head south along the main street lined with traditional Gassho-zukuri houses, and you will reach the shrine in approximately fifteen to twenty minutes on foot.</t>
+        </is>
+      </c>
+      <c r="E192" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは約800m、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
+        </is>
+      </c>
       <c r="F192" s="23" t="inlineStr">
         <is>
           <t>会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
@@ -13332,32 +13351,35 @@
       </c>
     </row>
     <row r="193" ht="97.2" customHeight="1">
-      <c r="A193" s="21" t="inlineStr">
+      <c r="A193" s="109" t="inlineStr">
         <is>
           <t>festival_shrine_access_bt</t>
         </is>
       </c>
-      <c r="B193" s="21" t="inlineStr">
+      <c r="B193" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="C193" s="22" t="inlineStr">
-        <is>
-          <t>Hachiman
-santuario llegar
-santuario Shirakawa
-lugar festival
-doburoku donde
-templo festival</t>
-        </is>
-      </c>
-      <c r="D193" s="22" t="inlineStr">
-        <is>
-          <t>El lugar del festival, el Santuario Hachiman de Shirakawa, está en el extremo sur de la aldea de casas gassho-zukuri de Ogimachi. Desde la Terminal de Autobuses de Shirakawa-go, está a unos 15 a 20 minutos a pie en dirección sur, por la calle principal donde se alinean las casas gassho-zukuri.</t>
-        </is>
-      </c>
-      <c r="E193" s="21" t="n"/>
+      <c r="C193" s="46" t="inlineStr">
+        <is>
+          <t>ubicación del Santuario Shirakawa Hachiман
+cómo llegar al santuario
+dónde está la plaza del festival
+dónde está el doburoku
+acceso al santuario</t>
+        </is>
+      </c>
+      <c r="D193" s="46" t="inlineStr">
+        <is>
+          <t>El Santuario Shirakawa Hachiман, lugar de la celebración, se encuentra ubicado en el extremo sur de la aldea de casas Gassho-zukuri de Ogimachi. Desde la Terminal de Autobuses de Shirakawa-go se encuentra a aproximadamente ochocientos metros. Camine hacia el sur siguiendo la calle principal donde se alinean las tradicionales casas Gassho-zukuri, y llegará al santuario en aproximadamente quince a veinte minutos a pie.</t>
+        </is>
+      </c>
+      <c r="E193" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは約800m、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
+        </is>
+      </c>
       <c r="F193" s="23" t="inlineStr">
         <is>
           <t>会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
@@ -13365,32 +13387,35 @@
       </c>
     </row>
     <row r="194" ht="97.2" customHeight="1">
-      <c r="A194" s="21" t="inlineStr">
+      <c r="A194" s="109" t="inlineStr">
         <is>
           <t>festival_shrine_access_bt</t>
         </is>
       </c>
-      <c r="B194" s="21" t="inlineStr">
+      <c r="B194" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="C194" s="22" t="inlineStr">
-        <is>
-          <t>sanctuaire shirakawa
-sanctuaire aller
-sanctuaire où
-lieu festival
-doburoku où
-hachiman</t>
-        </is>
-      </c>
-      <c r="D194" s="22" t="inlineStr">
-        <is>
-          <t>Le lieu du festival, le sanctuaire Shirakawa Hachiman, se trouve à l'extrémité sud du village aux maisons gassho d'Ogimachi. Depuis le terminal de bus de Shirakawa-go, comptez environ 15 à 20 minutes à pied vers le sud, par la rue principale bordée de maisons gassho.</t>
-        </is>
-      </c>
-      <c r="E194" s="21" t="n"/>
+      <c r="C194" s="46" t="inlineStr">
+        <is>
+          <t>localisation du Sanctuaire Shirakawa Hachiман
+comment aller au sanctuaire
+où se trouve le festival
+où est le doburoku
+accès au sanctuaire</t>
+        </is>
+      </c>
+      <c r="D194" s="46" t="inlineStr">
+        <is>
+          <t>Le Sanctuaire Shirakawa Hachiман, lieu du festival, est situé à l'extrémité sud du village de maisons Gassho-zukuri d'Ogimachi. Depuis la Gare routière de Shirakawa-go, il se trouve à environ huit cents mètres de distance. Dirigez-vous vers le sud en suivant la rue principale bordée de traditionnelles maisons Gassho-zukuri, et vous atteindrez le sanctuaire en environ quinze à vingt minutes à pied.</t>
+        </is>
+      </c>
+      <c r="E194" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは約800m、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
+        </is>
+      </c>
       <c r="F194" s="23" t="inlineStr">
         <is>
           <t>会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
@@ -13398,32 +13423,35 @@
       </c>
     </row>
     <row r="195" ht="97.2" customHeight="1">
-      <c r="A195" s="21" t="inlineStr">
+      <c r="A195" s="109" t="inlineStr">
         <is>
           <t>festival_shrine_access_bt</t>
         </is>
       </c>
-      <c r="B195" s="21" t="inlineStr">
+      <c r="B195" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="C195" s="22" t="inlineStr">
-        <is>
-          <t>시라카와 하치만 신사
-하치만 신사
-신사 가는
-신사 어떻게
-축제 장소
-도부로쿠 어디</t>
-        </is>
-      </c>
-      <c r="D195" s="22" t="inlineStr">
-        <is>
-          <t>행사장인 시라카와 하치만 신사는 오기마치 갓쇼즈쿠리 마을의 남쪽 끝에 있습니다. 시라카와고 버스터미널에서는 남쪽, 갓쇼즈쿠리 가옥이 늘어선 메인 거리 방향으로 걸어서 약 15분에서 20분 걸립니다.</t>
-        </is>
-      </c>
-      <c r="E195" s="21" t="n"/>
+      <c r="C195" s="46" t="inlineStr">
+        <is>
+          <t>시라카와 하치만신사 어디
+신사 가는 길
+축제 회장 위치
+도부로쿠 어디있어
+신사 접근 방법</t>
+        </is>
+      </c>
+      <c r="D195" s="46" t="inlineStr">
+        <is>
+          <t>축제 회장인 시라카와 하치만신사는 오기마치 갓쇼즈쿠리 마을의 남쪽 끝에 위치하고 있습니다. 시라카와고 버스터미널에서 약 팔백 미터 거리에 있습니다. 전통 갓쇼즈쿠리 가옥들이 줄지어 있는 남쪽 메인 거리를 따라 도보로 약 십오 분에서 이십 분 정도 가면 신사에 도착합니다.</t>
+        </is>
+      </c>
+      <c r="E195" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは約800m、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
+        </is>
+      </c>
       <c r="F195" s="23" t="inlineStr">
         <is>
           <t>会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
@@ -13431,31 +13459,35 @@
       </c>
     </row>
     <row r="196" ht="81" customHeight="1">
-      <c r="A196" s="24" t="inlineStr">
+      <c r="A196" s="110" t="inlineStr">
         <is>
           <t>festival_shrine_access_bt</t>
         </is>
       </c>
-      <c r="B196" s="24" t="inlineStr">
+      <c r="B196" s="110" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C196" s="25" t="inlineStr">
-        <is>
-          <t>白川八幡神社
-神社 怎么走
-节日 会场
-浊酒 哪里
-神社 在哪</t>
-        </is>
-      </c>
-      <c r="D196" s="25" t="inlineStr">
-        <is>
-          <t>会场白川八幡神社位于荻町合掌造村落的南端。从白川乡巴士总站出发，向南沿着合掌造房屋林立的主街步行约15到20分钟。</t>
-        </is>
-      </c>
-      <c r="E196" s="24" t="n"/>
+      <c r="C196" s="69" t="inlineStr">
+        <is>
+          <t>白川八幡神社在哪里
+神社怎么去
+祭典会场位置
+浊酒在哪儿
+前往神社的路线</t>
+        </is>
+      </c>
+      <c r="D196" s="69" t="inlineStr">
+        <is>
+          <t>祭典会场白川八幡神社位于荻町合掌造村落的南端。从白川乡巴士总站出发，距离约为八百米。沿着排满传统合掌造房屋的南向主街步行，约需十五分钟至二十分钟便可到达神社。</t>
+        </is>
+      </c>
+      <c r="E196" s="69" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは約800m、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
+        </is>
+      </c>
       <c r="F196" s="26" t="inlineStr">
         <is>
           <t>会場の「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 白川郷バスターミナルからは、南（合掌造りが並ぶメイン通り）へ向かって徒歩約15分〜20分です。</t>
@@ -17006,12 +17038,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="101" t="inlineStr">
+      <c r="A302" s="105" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="101" t="inlineStr">
+      <c r="B302" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17037,12 +17069,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="101" t="inlineStr">
+      <c r="A303" s="105" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="101" t="inlineStr">
+      <c r="B303" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17068,12 +17100,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="101" t="inlineStr">
+      <c r="A304" s="105" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="101" t="inlineStr">
+      <c r="B304" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17099,12 +17131,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="101" t="inlineStr">
+      <c r="A305" s="105" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="101" t="inlineStr">
+      <c r="B305" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17130,12 +17162,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="101" t="inlineStr">
+      <c r="A306" s="105" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="101" t="inlineStr">
+      <c r="B306" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17161,12 +17193,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="101" t="inlineStr">
+      <c r="A307" s="105" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="101" t="inlineStr">
+      <c r="B307" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17192,12 +17224,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="101" t="inlineStr">
+      <c r="A308" s="105" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="101" t="inlineStr">
+      <c r="B308" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17223,12 +17255,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="101" t="inlineStr">
+      <c r="A309" s="105" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="101" t="inlineStr">
+      <c r="B309" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17254,12 +17286,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="101" t="inlineStr">
+      <c r="A310" s="105" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="101" t="inlineStr">
+      <c r="B310" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17285,12 +17317,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="101" t="inlineStr">
+      <c r="A311" s="105" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="101" t="inlineStr">
+      <c r="B311" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17316,12 +17348,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="101" t="inlineStr">
+      <c r="A312" s="105" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="101" t="inlineStr">
+      <c r="B312" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17346,12 +17378,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="101" t="inlineStr">
+      <c r="A313" s="105" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="101" t="inlineStr">
+      <c r="B313" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17376,12 +17408,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="101" t="inlineStr">
+      <c r="A314" s="105" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="101" t="inlineStr">
+      <c r="B314" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17406,12 +17438,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="101" t="inlineStr">
+      <c r="A315" s="105" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="101" t="inlineStr">
+      <c r="B315" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17436,12 +17468,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="101" t="inlineStr">
+      <c r="A316" s="105" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="101" t="inlineStr">
+      <c r="B316" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17466,12 +17498,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="101" t="inlineStr">
+      <c r="A317" s="105" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="101" t="inlineStr">
+      <c r="B317" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17497,12 +17529,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="101" t="inlineStr">
+      <c r="A318" s="105" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="101" t="inlineStr">
+      <c r="B318" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17528,12 +17560,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="101" t="inlineStr">
+      <c r="A319" s="105" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="101" t="inlineStr">
+      <c r="B319" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17559,12 +17591,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="101" t="inlineStr">
+      <c r="A320" s="105" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="101" t="inlineStr">
+      <c r="B320" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17590,12 +17622,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="101" t="inlineStr">
+      <c r="A321" s="105" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="101" t="inlineStr">
+      <c r="B321" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17621,12 +17653,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="101" t="inlineStr">
+      <c r="A322" s="105" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="101" t="inlineStr">
+      <c r="B322" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17651,12 +17683,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="101" t="inlineStr">
+      <c r="A323" s="105" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="101" t="inlineStr">
+      <c r="B323" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17681,12 +17713,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="101" t="inlineStr">
+      <c r="A324" s="105" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="101" t="inlineStr">
+      <c r="B324" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17711,12 +17743,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="101" t="inlineStr">
+      <c r="A325" s="105" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="101" t="inlineStr">
+      <c r="B325" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17741,12 +17773,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="101" t="inlineStr">
+      <c r="A326" s="105" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="101" t="inlineStr">
+      <c r="B326" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17771,12 +17803,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="101" t="inlineStr">
+      <c r="A327" s="105" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="101" t="inlineStr">
+      <c r="B327" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17803,12 +17835,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="101" t="inlineStr">
+      <c r="A328" s="105" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="101" t="inlineStr">
+      <c r="B328" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17835,12 +17867,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="101" t="inlineStr">
+      <c r="A329" s="105" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="101" t="inlineStr">
+      <c r="B329" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17867,12 +17899,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="101" t="inlineStr">
+      <c r="A330" s="105" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="101" t="inlineStr">
+      <c r="B330" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17899,12 +17931,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="101" t="inlineStr">
+      <c r="A331" s="105" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="101" t="inlineStr">
+      <c r="B331" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17931,12 +17963,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="101" t="inlineStr">
+      <c r="A332" s="105" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="101" t="inlineStr">
+      <c r="B332" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17963,12 +17995,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="101" t="inlineStr">
+      <c r="A333" s="105" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="101" t="inlineStr">
+      <c r="B333" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17995,12 +18027,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="101" t="inlineStr">
+      <c r="A334" s="105" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="101" t="inlineStr">
+      <c r="B334" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18027,12 +18059,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="101" t="inlineStr">
+      <c r="A335" s="105" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="101" t="inlineStr">
+      <c r="B335" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18059,12 +18091,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="101" t="inlineStr">
+      <c r="A336" s="105" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="101" t="inlineStr">
+      <c r="B336" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18091,12 +18123,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="101" t="inlineStr">
+      <c r="A337" s="105" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="101" t="inlineStr">
+      <c r="B337" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18123,12 +18155,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="101" t="inlineStr">
+      <c r="A338" s="105" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="101" t="inlineStr">
+      <c r="B338" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18155,12 +18187,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="101" t="inlineStr">
+      <c r="A339" s="105" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="101" t="inlineStr">
+      <c r="B339" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18187,12 +18219,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="101" t="inlineStr">
+      <c r="A340" s="105" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="101" t="inlineStr">
+      <c r="B340" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18219,12 +18251,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="101" t="inlineStr">
+      <c r="A341" s="105" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="101" t="inlineStr">
+      <c r="B341" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18251,12 +18283,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="101" t="inlineStr">
+      <c r="A342" s="105" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="101" t="inlineStr">
+      <c r="B342" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18283,12 +18315,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="101" t="inlineStr">
+      <c r="A343" s="105" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="101" t="inlineStr">
+      <c r="B343" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18315,12 +18347,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="101" t="inlineStr">
+      <c r="A344" s="105" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="101" t="inlineStr">
+      <c r="B344" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18347,12 +18379,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="101" t="inlineStr">
+      <c r="A345" s="105" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="101" t="inlineStr">
+      <c r="B345" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18379,12 +18411,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="101" t="inlineStr">
+      <c r="A346" s="105" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="101" t="inlineStr">
+      <c r="B346" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18411,12 +18443,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="101" t="inlineStr">
+      <c r="A347" s="105" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="101" t="inlineStr">
+      <c r="B347" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18443,12 +18475,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="101" t="inlineStr">
+      <c r="A348" s="105" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="101" t="inlineStr">
+      <c r="B348" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18475,12 +18507,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="101" t="inlineStr">
+      <c r="A349" s="105" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="101" t="inlineStr">
+      <c r="B349" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18507,12 +18539,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="101" t="inlineStr">
+      <c r="A350" s="105" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="101" t="inlineStr">
+      <c r="B350" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18539,12 +18571,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="101" t="inlineStr">
+      <c r="A351" s="105" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="101" t="inlineStr">
+      <c r="B351" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18571,12 +18603,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="101" t="inlineStr">
+      <c r="A352" s="105" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="101" t="inlineStr">
+      <c r="B352" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18602,12 +18634,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="101" t="inlineStr">
+      <c r="A353" s="105" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="101" t="inlineStr">
+      <c r="B353" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18633,12 +18665,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="101" t="inlineStr">
+      <c r="A354" s="105" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="101" t="inlineStr">
+      <c r="B354" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18664,12 +18696,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="101" t="inlineStr">
+      <c r="A355" s="105" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="101" t="inlineStr">
+      <c r="B355" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18695,12 +18727,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="101" t="inlineStr">
+      <c r="A356" s="105" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="101" t="inlineStr">
+      <c r="B356" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18726,12 +18758,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="101" t="inlineStr">
+      <c r="A357" s="105" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="101" t="inlineStr">
+      <c r="B357" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18757,12 +18789,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="101" t="inlineStr">
+      <c r="A358" s="105" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="101" t="inlineStr">
+      <c r="B358" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18788,12 +18820,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="101" t="inlineStr">
+      <c r="A359" s="105" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="101" t="inlineStr">
+      <c r="B359" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18819,12 +18851,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="101" t="inlineStr">
+      <c r="A360" s="105" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="101" t="inlineStr">
+      <c r="B360" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18850,12 +18882,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="101" t="inlineStr">
+      <c r="A361" s="105" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="101" t="inlineStr">
+      <c r="B361" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18881,12 +18913,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="101" t="inlineStr">
+      <c r="A362" s="105" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="101" t="inlineStr">
+      <c r="B362" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18913,12 +18945,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="101" t="inlineStr">
+      <c r="A363" s="105" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="101" t="inlineStr">
+      <c r="B363" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18945,12 +18977,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="101" t="inlineStr">
+      <c r="A364" s="105" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="101" t="inlineStr">
+      <c r="B364" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18977,12 +19009,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="101" t="inlineStr">
+      <c r="A365" s="105" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="101" t="inlineStr">
+      <c r="B365" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -19009,12 +19041,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="101" t="inlineStr">
+      <c r="A366" s="105" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="101" t="inlineStr">
+      <c r="B366" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -19041,12 +19073,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="101" t="inlineStr">
+      <c r="A367" s="105" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="101" t="inlineStr">
+      <c r="B367" s="105" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -19073,12 +19105,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="101" t="inlineStr">
+      <c r="A368" s="105" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="101" t="inlineStr">
+      <c r="B368" s="105" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -19105,12 +19137,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="101" t="inlineStr">
+      <c r="A369" s="105" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="101" t="inlineStr">
+      <c r="B369" s="105" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -19137,12 +19169,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="101" t="inlineStr">
+      <c r="A370" s="105" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="101" t="inlineStr">
+      <c r="B370" s="105" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -19169,12 +19201,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="101" t="inlineStr">
+      <c r="A371" s="105" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="101" t="inlineStr">
+      <c r="B371" s="105" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -20310,7 +20342,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="101" t="inlineStr">
+      <c r="A2" s="105" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -20320,7 +20352,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="101" t="inlineStr">
+      <c r="C2" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20332,7 +20364,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="101" t="inlineStr">
+      <c r="A3" s="105" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -20342,7 +20374,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="101" t="inlineStr">
+      <c r="C3" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20354,7 +20386,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="101" t="inlineStr">
+      <c r="A4" s="105" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -20364,7 +20396,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="101" t="inlineStr">
+      <c r="C4" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20376,7 +20408,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="101" t="inlineStr">
+      <c r="A5" s="105" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -20386,7 +20418,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="101" t="inlineStr">
+      <c r="C5" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20398,7 +20430,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="101" t="inlineStr">
+      <c r="A6" s="105" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20408,7 +20440,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="101" t="inlineStr">
+      <c r="C6" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20420,7 +20452,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="101" t="inlineStr">
+      <c r="A7" s="105" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20430,7 +20462,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="101" t="inlineStr">
+      <c r="C7" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20442,7 +20474,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="101" t="inlineStr">
+      <c r="A8" s="105" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20452,7 +20484,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="101" t="inlineStr">
+      <c r="C8" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20464,7 +20496,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="101" t="inlineStr">
+      <c r="A9" s="105" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20474,7 +20506,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="101" t="inlineStr">
+      <c r="C9" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20486,7 +20518,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="101" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20496,7 +20528,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="101" t="inlineStr">
+      <c r="C10" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20508,7 +20540,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="101" t="inlineStr">
+      <c r="A11" s="105" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20518,7 +20550,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="101" t="inlineStr">
+      <c r="C11" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20530,7 +20562,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="101" t="inlineStr">
+      <c r="A12" s="105" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20540,7 +20572,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="101" t="inlineStr">
+      <c r="C12" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20552,7 +20584,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="101" t="inlineStr">
+      <c r="A13" s="105" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20562,7 +20594,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="101" t="inlineStr">
+      <c r="C13" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20704,53 +20736,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="101" t="inlineStr">
+      <c r="A2" s="105" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="101" t="inlineStr">
+      <c r="B2" s="105" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="101" t="inlineStr">
+      <c r="C2" s="105" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="101" t="inlineStr">
+      <c r="D2" s="105" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="101" t="inlineStr">
+      <c r="E2" s="105" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="101" t="inlineStr">
+      <c r="F2" s="105" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="101" t="inlineStr">
+      <c r="G2" s="105" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="101" t="inlineStr">
+      <c r="H2" s="105" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="101" t="inlineStr">
+      <c r="I2" s="105" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="101" t="n"/>
-      <c r="K2" s="101" t="inlineStr">
+      <c r="J2" s="105" t="n"/>
+      <c r="K2" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20787,45 +20819,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="101" t="inlineStr">
+      <c r="A3" s="105" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="101" t="inlineStr">
+      <c r="B3" s="105" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="101" t="inlineStr">
+      <c r="C3" s="105" t="inlineStr">
         <is>
           <t>main_idle_20261013044809.png</t>
         </is>
       </c>
-      <c r="D3" s="101" t="n"/>
-      <c r="E3" s="101" t="n"/>
-      <c r="F3" s="101" t="n">
+      <c r="D3" s="105" t="n"/>
+      <c r="E3" s="105" t="n"/>
+      <c r="F3" s="105" t="n">
         <v>0.179</v>
       </c>
-      <c r="G3" s="101" t="n">
+      <c r="G3" s="105" t="n">
         <v>0.23</v>
       </c>
-      <c r="H3" s="101" t="inlineStr">
+      <c r="H3" s="105" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="101" t="inlineStr">
+      <c r="I3" s="105" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="101" t="inlineStr">
+      <c r="J3" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="101" t="inlineStr">
+      <c r="K3" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20862,45 +20894,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="101" t="inlineStr">
+      <c r="A4" s="105" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="101" t="inlineStr">
+      <c r="B4" s="105" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="101" t="inlineStr">
+      <c r="C4" s="105" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="101" t="n"/>
-      <c r="E4" s="101" t="n"/>
-      <c r="F4" s="101" t="inlineStr">
+      <c r="D4" s="105" t="n"/>
+      <c r="E4" s="105" t="n"/>
+      <c r="F4" s="105" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="101" t="inlineStr">
+      <c r="G4" s="105" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="101" t="inlineStr">
+      <c r="H4" s="105" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="101" t="inlineStr">
+      <c r="I4" s="105" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="101" t="n"/>
-      <c r="K4" s="101" t="inlineStr">
+      <c r="J4" s="105" t="n"/>
+      <c r="K4" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20937,45 +20969,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="101" t="inlineStr">
+      <c r="A5" s="105" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="101" t="inlineStr">
+      <c r="B5" s="105" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="101" t="inlineStr">
+      <c r="C5" s="105" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="101" t="n"/>
-      <c r="E5" s="101" t="n"/>
-      <c r="F5" s="101" t="inlineStr">
+      <c r="D5" s="105" t="n"/>
+      <c r="E5" s="105" t="n"/>
+      <c r="F5" s="105" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="101" t="inlineStr">
+      <c r="G5" s="105" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="101" t="inlineStr">
+      <c r="H5" s="105" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="101" t="inlineStr">
+      <c r="I5" s="105" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="101" t="n"/>
-      <c r="K5" s="101" t="inlineStr">
+      <c r="J5" s="105" t="n"/>
+      <c r="K5" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -21012,45 +21044,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="101" t="inlineStr">
+      <c r="A6" s="105" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="101" t="inlineStr">
+      <c r="B6" s="105" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="101" t="inlineStr">
+      <c r="C6" s="105" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="101" t="n"/>
-      <c r="E6" s="101" t="n"/>
-      <c r="F6" s="101" t="inlineStr">
+      <c r="D6" s="105" t="n"/>
+      <c r="E6" s="105" t="n"/>
+      <c r="F6" s="105" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="101" t="inlineStr">
+      <c r="G6" s="105" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="101" t="inlineStr">
+      <c r="H6" s="105" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="101" t="inlineStr">
+      <c r="I6" s="105" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="101" t="n"/>
-      <c r="K6" s="101" t="inlineStr">
+      <c r="J6" s="105" t="n"/>
+      <c r="K6" s="105" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -21172,12 +21204,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="101" t="inlineStr">
+      <c r="A2" s="105" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B2" s="101" t="inlineStr">
+      <c r="B2" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21216,12 +21248,12 @@
       <c r="J2" s="46" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="101" t="inlineStr">
+      <c r="A3" s="105" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B3" s="101" t="inlineStr">
+      <c r="B3" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21260,12 +21292,12 @@
       <c r="J3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="101" t="inlineStr">
+      <c r="A4" s="105" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B4" s="101" t="inlineStr">
+      <c r="B4" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21304,12 +21336,12 @@
       <c r="J4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="101" t="inlineStr">
+      <c r="A5" s="105" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B5" s="101" t="inlineStr">
+      <c r="B5" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21348,12 +21380,12 @@
       <c r="J5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="101" t="inlineStr">
+      <c r="A6" s="105" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B6" s="101" t="inlineStr">
+      <c r="B6" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21392,12 +21424,12 @@
       <c r="J6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="101" t="inlineStr">
+      <c r="A7" s="105" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B7" s="101" t="inlineStr">
+      <c r="B7" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21436,12 +21468,12 @@
       <c r="J7" s="46" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="101" t="inlineStr">
+      <c r="A8" s="105" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B8" s="101" t="inlineStr">
+      <c r="B8" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21480,12 +21512,12 @@
       <c r="J8" s="46" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="101" t="inlineStr">
+      <c r="A9" s="105" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B9" s="101" t="inlineStr">
+      <c r="B9" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21524,12 +21556,12 @@
       <c r="J9" s="46" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="101" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B10" s="101" t="inlineStr">
+      <c r="B10" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21568,12 +21600,12 @@
       <c r="J10" s="46" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="101" t="inlineStr">
+      <c r="A11" s="105" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B11" s="101" t="inlineStr">
+      <c r="B11" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21612,12 +21644,12 @@
       <c r="J11" s="46" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="101" t="inlineStr">
+      <c r="A12" s="105" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B12" s="101" t="inlineStr">
+      <c r="B12" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21656,12 +21688,12 @@
       <c r="J12" s="46" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="101" t="inlineStr">
+      <c r="A13" s="105" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B13" s="101" t="inlineStr">
+      <c r="B13" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21719,12 +21751,12 @@
       <c r="J13" s="46" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="101" t="inlineStr">
+      <c r="A14" s="105" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B14" s="101" t="inlineStr">
+      <c r="B14" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21782,12 +21814,12 @@
       <c r="J14" s="46" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="101" t="inlineStr">
+      <c r="A15" s="105" t="inlineStr">
         <is>
           <t>趣味</t>
         </is>
       </c>
-      <c r="B15" s="101" t="inlineStr">
+      <c r="B15" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21848,12 +21880,12 @@
       <c r="J15" s="46" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="101" t="inlineStr">
+      <c r="A16" s="105" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B16" s="101" t="inlineStr">
+      <c r="B16" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21913,12 +21945,12 @@
       <c r="J16" s="46" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="101" t="inlineStr">
+      <c r="A17" s="105" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B17" s="101" t="inlineStr">
+      <c r="B17" s="105" t="inlineStr">
         <is>
           <t>共通</t>
         </is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -579,6 +579,18 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1281,7 +1293,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="109" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1291,31 +1303,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="105" t="n">
+      <c r="C2" s="109" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="105" t="n">
+      <c r="D2" s="109" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="105" t="n">
+      <c r="E2" s="109" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="105" t="n">
+      <c r="F2" s="109" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="105" t="n">
+      <c r="G2" s="109" t="n">
         <v>0.957</v>
       </c>
-      <c r="H2" s="105" t="n">
+      <c r="H2" s="109" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="105" t="n">
+      <c r="I2" s="109" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="105" t="n">
+      <c r="J2" s="109" t="n">
         <v>0.864</v>
       </c>
-      <c r="K2" s="105" t="n">
+      <c r="K2" s="109" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1325,7 +1337,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="A3" s="109" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1335,31 +1347,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="105" t="n">
+      <c r="C3" s="109" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="105" t="n">
+      <c r="D3" s="109" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="105" t="n">
+      <c r="E3" s="109" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="105" t="n">
+      <c r="F3" s="109" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="105" t="n">
+      <c r="G3" s="109" t="n">
         <v>0.929</v>
       </c>
-      <c r="H3" s="105" t="n">
+      <c r="H3" s="109" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="105" t="n">
+      <c r="I3" s="109" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="105" t="n">
+      <c r="J3" s="109" t="n">
         <v>0.753</v>
       </c>
-      <c r="K3" s="105" t="n">
+      <c r="K3" s="109" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1369,7 +1381,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="105" t="inlineStr">
+      <c r="A4" s="109" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1379,31 +1391,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="105" t="n">
+      <c r="C4" s="109" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="105" t="n">
+      <c r="D4" s="109" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="105" t="n">
+      <c r="E4" s="109" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="105" t="n">
+      <c r="F4" s="109" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="105" t="n">
+      <c r="G4" s="109" t="n">
         <v>0.92</v>
       </c>
-      <c r="H4" s="105" t="n">
+      <c r="H4" s="109" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="105" t="n">
+      <c r="I4" s="109" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="105" t="n">
+      <c r="J4" s="109" t="n">
         <v>0.884</v>
       </c>
-      <c r="K4" s="105" t="n">
+      <c r="K4" s="109" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1475,7 +1487,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="109" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1485,10 +1497,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="105" t="n">
+      <c r="C2" s="109" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="105" t="n">
+      <c r="D2" s="109" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1498,7 +1510,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="A3" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1508,16 +1520,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="105" t="n">
+      <c r="C3" s="109" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="105" t="n">
+      <c r="D3" s="109" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="105" t="inlineStr">
+      <c r="A4" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1527,16 +1539,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="105" t="n">
+      <c r="C4" s="109" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="105" t="n">
+      <c r="D4" s="109" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="105" t="inlineStr">
+      <c r="A5" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1546,16 +1558,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="105" t="n">
+      <c r="C5" s="109" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="105" t="n">
+      <c r="D5" s="109" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="105" t="inlineStr">
+      <c r="A6" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1565,16 +1577,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="105" t="n">
+      <c r="C6" s="109" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="105" t="n">
+      <c r="D6" s="109" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="105" t="inlineStr">
+      <c r="A7" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1584,10 +1596,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="105" t="n">
+      <c r="C7" s="109" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="105" t="n">
+      <c r="D7" s="109" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1647,17 +1659,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="109" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="105" t="inlineStr">
+      <c r="B2" s="109" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="105" t="inlineStr">
+      <c r="C2" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1669,17 +1681,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="A3" s="109" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="105" t="inlineStr">
+      <c r="B3" s="109" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="105" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1687,17 +1699,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="105" t="inlineStr">
+      <c r="A4" s="109" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="105" t="inlineStr">
+      <c r="B4" s="109" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="105" t="inlineStr">
+      <c r="C4" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1709,17 +1721,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="105" t="inlineStr">
+      <c r="A5" s="109" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="105" t="inlineStr">
+      <c r="B5" s="109" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="105" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1731,17 +1743,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="105" t="inlineStr">
+      <c r="A6" s="109" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="105" t="inlineStr">
+      <c r="B6" s="109" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="105" t="inlineStr">
+      <c r="C6" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1749,17 +1761,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="105" t="inlineStr">
+      <c r="A7" s="109" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="105" t="inlineStr">
+      <c r="B7" s="109" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="105" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1767,17 +1779,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="105" t="inlineStr">
+      <c r="A8" s="109" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="105" t="inlineStr">
+      <c r="B8" s="109" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="105" t="inlineStr">
+      <c r="C8" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1789,17 +1801,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="105" t="inlineStr">
+      <c r="A9" s="109" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="105" t="inlineStr">
+      <c r="B9" s="109" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="105" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1811,17 +1823,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="105" t="inlineStr">
+      <c r="A10" s="109" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="105" t="inlineStr">
+      <c r="B10" s="109" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="105" t="inlineStr">
+      <c r="C10" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1833,17 +1845,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="105" t="inlineStr">
+      <c r="A11" s="109" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="105" t="inlineStr">
+      <c r="B11" s="109" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="105" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1851,17 +1863,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="105" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="105" t="inlineStr">
+      <c r="B12" s="109" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="105" t="inlineStr">
+      <c r="C12" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1869,17 +1881,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="105" t="inlineStr">
+      <c r="A13" s="109" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="105" t="inlineStr">
+      <c r="B13" s="109" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="105" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1891,17 +1903,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="105" t="inlineStr">
+      <c r="A14" s="109" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="105" t="inlineStr">
+      <c r="B14" s="109" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="105" t="inlineStr">
+      <c r="C14" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1913,17 +1925,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="105" t="inlineStr">
+      <c r="A15" s="109" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="105" t="inlineStr">
+      <c r="B15" s="109" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="105" t="inlineStr">
+      <c r="C15" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1935,17 +1947,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="105" t="inlineStr">
+      <c r="A16" s="109" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="105" t="inlineStr">
+      <c r="B16" s="109" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="105" t="inlineStr">
+      <c r="C16" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1957,17 +1969,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="105" t="inlineStr">
+      <c r="A17" s="109" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="105" t="inlineStr">
+      <c r="B17" s="109" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="105" t="inlineStr">
+      <c r="C17" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1979,17 +1991,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="105" t="inlineStr">
+      <c r="A18" s="109" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="105" t="inlineStr">
+      <c r="B18" s="109" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="105" t="inlineStr">
+      <c r="C18" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2001,17 +2013,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="105" t="inlineStr">
+      <c r="A19" s="109" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="105" t="inlineStr">
+      <c r="B19" s="109" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="105" t="inlineStr">
+      <c r="C19" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2019,17 +2031,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="105" t="inlineStr">
+      <c r="A20" s="109" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="105" t="inlineStr">
+      <c r="B20" s="109" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="105" t="inlineStr">
+      <c r="C20" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2037,17 +2049,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="105" t="inlineStr">
+      <c r="A21" s="109" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="105" t="inlineStr">
+      <c r="B21" s="109" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="105" t="inlineStr">
+      <c r="C21" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2059,17 +2071,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="105" t="inlineStr">
+      <c r="A22" s="109" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="105" t="inlineStr">
+      <c r="B22" s="109" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="105" t="inlineStr">
+      <c r="C22" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2081,17 +2093,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="105" t="inlineStr">
+      <c r="A23" s="109" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="105" t="inlineStr">
+      <c r="B23" s="109" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="105" t="inlineStr">
+      <c r="C23" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2103,17 +2115,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="105" t="inlineStr">
+      <c r="A24" s="109" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="105" t="inlineStr">
+      <c r="B24" s="109" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="105" t="inlineStr">
+      <c r="C24" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2125,17 +2137,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="105" t="inlineStr">
+      <c r="A25" s="109" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="105" t="inlineStr">
+      <c r="B25" s="109" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="105" t="inlineStr">
+      <c r="C25" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2143,17 +2155,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="105" t="inlineStr">
+      <c r="A26" s="109" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="105" t="inlineStr">
+      <c r="B26" s="109" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="105" t="inlineStr">
+      <c r="C26" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2161,17 +2173,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="105" t="inlineStr">
+      <c r="A27" s="109" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="105" t="inlineStr">
+      <c r="B27" s="109" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="105" t="inlineStr">
+      <c r="C27" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2183,17 +2195,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="105" t="inlineStr">
+      <c r="A28" s="109" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="105" t="inlineStr">
+      <c r="B28" s="109" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="105" t="inlineStr">
+      <c r="C28" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2205,17 +2217,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="105" t="inlineStr">
+      <c r="A29" s="109" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="105" t="inlineStr">
+      <c r="B29" s="109" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="105" t="inlineStr">
+      <c r="C29" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2227,17 +2239,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="105" t="inlineStr">
+      <c r="A30" s="109" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="105" t="inlineStr">
+      <c r="B30" s="109" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="105" t="inlineStr">
+      <c r="C30" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2245,17 +2257,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="105" t="inlineStr">
+      <c r="A31" s="109" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="105" t="inlineStr">
+      <c r="B31" s="109" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="105" t="inlineStr">
+      <c r="C31" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2267,17 +2279,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="105" t="inlineStr">
+      <c r="A32" s="109" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="105" t="inlineStr">
+      <c r="B32" s="109" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="105" t="inlineStr">
+      <c r="C32" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2285,17 +2297,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="105" t="inlineStr">
+      <c r="A33" s="109" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="105" t="inlineStr">
+      <c r="B33" s="109" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="105" t="inlineStr">
+      <c r="C33" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2303,17 +2315,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="105" t="inlineStr">
+      <c r="A34" s="109" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="105" t="inlineStr">
+      <c r="B34" s="109" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="105" t="inlineStr">
+      <c r="C34" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2321,17 +2333,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="105" t="inlineStr">
+      <c r="A35" s="109" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="105" t="inlineStr">
+      <c r="B35" s="109" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="105" t="inlineStr">
+      <c r="C35" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2339,17 +2351,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="105" t="inlineStr">
+      <c r="A36" s="109" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="105" t="inlineStr">
+      <c r="B36" s="109" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="105" t="inlineStr">
+      <c r="C36" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2357,17 +2369,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="105" t="inlineStr">
+      <c r="A37" s="109" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="105" t="inlineStr">
+      <c r="B37" s="109" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="105" t="inlineStr">
+      <c r="C37" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2375,17 +2387,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="105" t="inlineStr">
+      <c r="A38" s="109" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="105" t="inlineStr">
+      <c r="B38" s="109" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="105" t="inlineStr">
+      <c r="C38" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2393,17 +2405,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="105" t="inlineStr">
+      <c r="A39" s="109" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="105" t="inlineStr">
+      <c r="B39" s="109" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="105" t="inlineStr">
+      <c r="C39" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2411,17 +2423,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="105" t="inlineStr">
+      <c r="A40" s="109" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="105" t="inlineStr">
+      <c r="B40" s="109" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="105" t="inlineStr">
+      <c r="C40" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2433,17 +2445,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="105" t="inlineStr">
+      <c r="A41" s="109" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="105" t="inlineStr">
+      <c r="B41" s="109" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="105" t="inlineStr">
+      <c r="C41" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2451,17 +2463,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="105" t="inlineStr">
+      <c r="A42" s="109" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="105" t="inlineStr">
+      <c r="B42" s="109" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="105" t="inlineStr">
+      <c r="C42" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2473,17 +2485,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="105" t="inlineStr">
+      <c r="A43" s="109" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="105" t="inlineStr">
+      <c r="B43" s="109" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="105" t="inlineStr">
+      <c r="C43" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2491,17 +2503,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="105" t="inlineStr">
+      <c r="A44" s="109" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="105" t="inlineStr">
+      <c r="B44" s="109" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="105" t="inlineStr">
+      <c r="C44" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2513,17 +2525,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="105" t="inlineStr">
+      <c r="A45" s="109" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="105" t="inlineStr">
+      <c r="B45" s="109" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="105" t="inlineStr">
+      <c r="C45" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2872,17 +2884,17 @@
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="104" t="inlineStr">
+      <c r="A6" s="108" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B6" s="104" t="inlineStr">
+      <c r="B6" s="108" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C6" s="104" t="inlineStr">
+      <c r="C6" s="108" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2907,49 +2919,49 @@
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
         </is>
       </c>
-      <c r="G6" s="104" t="n"/>
-      <c r="H6" s="104" t="n"/>
-      <c r="I6" s="104" t="inlineStr">
+      <c r="G6" s="108" t="n"/>
+      <c r="H6" s="108" t="n"/>
+      <c r="I6" s="108" t="inlineStr">
         <is>
           <t>atm_bt.mp3</t>
         </is>
       </c>
-      <c r="J6" s="104" t="inlineStr">
+      <c r="J6" s="108" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K6" s="104" t="n"/>
-      <c r="L6" s="104" t="n"/>
-      <c r="M6" s="104" t="inlineStr">
+      <c r="K6" s="108" t="n"/>
+      <c r="L6" s="108" t="n"/>
+      <c r="M6" s="108" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N6" s="105" t="inlineStr">
+      <c r="N6" s="109" t="inlineStr">
         <is>
           <t>ATMはどこ</t>
         </is>
       </c>
-      <c r="O6" s="105" t="n"/>
-      <c r="P6" s="105" t="inlineStr">
+      <c r="O6" s="109" t="n"/>
+      <c r="P6" s="109" t="inlineStr">
         <is>
           <t>2026-10-13 17:14</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="104" t="inlineStr">
+      <c r="A7" s="108" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B7" s="104" t="inlineStr">
+      <c r="B7" s="108" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C7" s="104" t="inlineStr">
+      <c r="C7" s="108" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2974,28 +2986,28 @@
           <t>海外のカードは鳩谷郵便局のATM、日本のカードは和田家前のJAのATMをご利用ください。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G7" s="104" t="n"/>
-      <c r="H7" s="104" t="n"/>
-      <c r="I7" s="104" t="inlineStr">
+      <c r="G7" s="108" t="n"/>
+      <c r="H7" s="108" t="n"/>
+      <c r="I7" s="108" t="inlineStr">
         <is>
           <t>atm_deai.mp3</t>
         </is>
       </c>
-      <c r="J7" s="104" t="inlineStr">
+      <c r="J7" s="108" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K7" s="104" t="n"/>
-      <c r="L7" s="104" t="n"/>
-      <c r="M7" s="104" t="inlineStr">
+      <c r="K7" s="108" t="n"/>
+      <c r="L7" s="108" t="n"/>
+      <c r="M7" s="108" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N7" s="105" t="n"/>
-      <c r="O7" s="105" t="n"/>
-      <c r="P7" s="105" t="inlineStr">
+      <c r="N7" s="109" t="n"/>
+      <c r="O7" s="109" t="n"/>
+      <c r="P7" s="109" t="inlineStr">
         <is>
           <t>2026-10-13 17:15</t>
         </is>
@@ -3051,17 +3063,17 @@
       </c>
     </row>
     <row r="9" ht="58.05" customHeight="1">
-      <c r="A9" s="104" t="inlineStr">
+      <c r="A9" s="108" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B9" s="104" t="inlineStr">
+      <c r="B9" s="108" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C9" s="104" t="inlineStr">
+      <c r="C9" s="108" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3081,45 +3093,45 @@
         </is>
       </c>
       <c r="F9" s="44" t="n"/>
-      <c r="G9" s="104" t="n"/>
-      <c r="H9" s="104" t="n"/>
-      <c r="I9" s="104" t="inlineStr">
+      <c r="G9" s="108" t="n"/>
+      <c r="H9" s="108" t="n"/>
+      <c r="I9" s="108" t="inlineStr">
         <is>
           <t>currency_exchange_bt.mp3</t>
         </is>
       </c>
-      <c r="J9" s="104" t="inlineStr">
+      <c r="J9" s="108" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K9" s="104" t="n"/>
-      <c r="L9" s="104" t="n"/>
-      <c r="M9" s="104" t="inlineStr">
+      <c r="K9" s="108" t="n"/>
+      <c r="L9" s="108" t="n"/>
+      <c r="M9" s="108" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N9" s="105" t="n"/>
-      <c r="O9" s="105" t="n"/>
-      <c r="P9" s="105" t="inlineStr">
+      <c r="N9" s="109" t="n"/>
+      <c r="O9" s="109" t="n"/>
+      <c r="P9" s="109" t="inlineStr">
         <is>
           <t>2026-10-13 17:18</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58.05" customHeight="1">
-      <c r="A10" s="104" t="inlineStr">
+      <c r="A10" s="108" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B10" s="104" t="inlineStr">
+      <c r="B10" s="108" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C10" s="104" t="inlineStr">
+      <c r="C10" s="108" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3139,45 +3151,45 @@
         </is>
       </c>
       <c r="F10" s="44" t="n"/>
-      <c r="G10" s="104" t="n"/>
-      <c r="H10" s="104" t="n"/>
-      <c r="I10" s="104" t="inlineStr">
+      <c r="G10" s="108" t="n"/>
+      <c r="H10" s="108" t="n"/>
+      <c r="I10" s="108" t="inlineStr">
         <is>
           <t>currency_exchange_deai.mp3</t>
         </is>
       </c>
-      <c r="J10" s="104" t="inlineStr">
+      <c r="J10" s="108" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K10" s="104" t="n"/>
-      <c r="L10" s="104" t="n"/>
-      <c r="M10" s="104" t="inlineStr">
+      <c r="K10" s="108" t="n"/>
+      <c r="L10" s="108" t="n"/>
+      <c r="M10" s="108" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N10" s="105" t="n"/>
-      <c r="O10" s="105" t="n"/>
-      <c r="P10" s="105" t="inlineStr">
+      <c r="N10" s="109" t="n"/>
+      <c r="O10" s="109" t="n"/>
+      <c r="P10" s="109" t="inlineStr">
         <is>
           <t>2026-10-13 17:19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58.05" customHeight="1">
-      <c r="A11" s="104" t="inlineStr">
+      <c r="A11" s="108" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B11" s="104" t="inlineStr">
+      <c r="B11" s="108" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C11" s="104" t="inlineStr">
+      <c r="C11" s="108" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3198,49 +3210,49 @@
         </is>
       </c>
       <c r="F11" s="44" t="n"/>
-      <c r="G11" s="104" t="n"/>
-      <c r="H11" s="104" t="n"/>
-      <c r="I11" s="104" t="inlineStr">
+      <c r="G11" s="108" t="n"/>
+      <c r="H11" s="108" t="n"/>
+      <c r="I11" s="108" t="inlineStr">
         <is>
           <t>luggage_bt.mp3</t>
         </is>
       </c>
-      <c r="J11" s="104" t="inlineStr">
+      <c r="J11" s="108" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K11" s="104" t="n"/>
-      <c r="L11" s="104" t="n"/>
-      <c r="M11" s="104" t="inlineStr">
+      <c r="K11" s="108" t="n"/>
+      <c r="L11" s="108" t="n"/>
+      <c r="M11" s="108" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N11" s="105" t="inlineStr">
+      <c r="N11" s="109" t="inlineStr">
         <is>
           <t>荷物を預けたい</t>
         </is>
       </c>
-      <c r="O11" s="105" t="n"/>
-      <c r="P11" s="105" t="inlineStr">
+      <c r="O11" s="109" t="n"/>
+      <c r="P11" s="109" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58.05" customHeight="1">
-      <c r="A12" s="104" t="inlineStr">
+      <c r="A12" s="108" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B12" s="104" t="inlineStr">
+      <c r="B12" s="108" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C12" s="104" t="inlineStr">
+      <c r="C12" s="108" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3261,28 +3273,28 @@
         </is>
       </c>
       <c r="F12" s="44" t="n"/>
-      <c r="G12" s="104" t="n"/>
-      <c r="H12" s="104" t="n"/>
-      <c r="I12" s="104" t="inlineStr">
+      <c r="G12" s="108" t="n"/>
+      <c r="H12" s="108" t="n"/>
+      <c r="I12" s="108" t="inlineStr">
         <is>
           <t>luggage_deai.mp3</t>
         </is>
       </c>
-      <c r="J12" s="104" t="inlineStr">
+      <c r="J12" s="108" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K12" s="104" t="n"/>
-      <c r="L12" s="104" t="n"/>
-      <c r="M12" s="104" t="inlineStr">
+      <c r="K12" s="108" t="n"/>
+      <c r="L12" s="108" t="n"/>
+      <c r="M12" s="108" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N12" s="105" t="n"/>
-      <c r="O12" s="105" t="n"/>
-      <c r="P12" s="105" t="inlineStr">
+      <c r="N12" s="109" t="n"/>
+      <c r="O12" s="109" t="n"/>
+      <c r="P12" s="109" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
@@ -3345,17 +3357,17 @@
       </c>
     </row>
     <row r="14" ht="58.05" customHeight="1">
-      <c r="A14" s="104" t="inlineStr">
+      <c r="A14" s="108" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B14" s="104" t="inlineStr">
+      <c r="B14" s="108" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C14" s="104" t="inlineStr">
+      <c r="C14" s="108" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3375,45 +3387,45 @@
         </is>
       </c>
       <c r="F14" s="44" t="n"/>
-      <c r="G14" s="104" t="n"/>
-      <c r="H14" s="104" t="n"/>
-      <c r="I14" s="104" t="inlineStr">
+      <c r="G14" s="108" t="n"/>
+      <c r="H14" s="108" t="n"/>
+      <c r="I14" s="108" t="inlineStr">
         <is>
           <t>stamp_bt.mp3</t>
         </is>
       </c>
-      <c r="J14" s="104" t="inlineStr">
+      <c r="J14" s="108" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K14" s="104" t="n"/>
-      <c r="L14" s="104" t="n"/>
-      <c r="M14" s="104" t="inlineStr">
+      <c r="K14" s="108" t="n"/>
+      <c r="L14" s="108" t="n"/>
+      <c r="M14" s="108" t="inlineStr">
         <is>
           <t>stamp</t>
         </is>
       </c>
-      <c r="N14" s="105" t="n"/>
-      <c r="O14" s="105" t="n"/>
-      <c r="P14" s="105" t="inlineStr">
+      <c r="N14" s="109" t="n"/>
+      <c r="O14" s="109" t="n"/>
+      <c r="P14" s="109" t="inlineStr">
         <is>
           <t>2026-10-13 17:22</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58.05" customHeight="1">
-      <c r="A15" s="104" t="inlineStr">
+      <c r="A15" s="108" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B15" s="104" t="inlineStr">
+      <c r="B15" s="108" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C15" s="104" t="inlineStr">
+      <c r="C15" s="108" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3433,28 +3445,28 @@
         </is>
       </c>
       <c r="F15" s="44" t="n"/>
-      <c r="G15" s="104" t="n"/>
-      <c r="H15" s="104" t="n"/>
-      <c r="I15" s="104" t="inlineStr">
+      <c r="G15" s="108" t="n"/>
+      <c r="H15" s="108" t="n"/>
+      <c r="I15" s="108" t="inlineStr">
         <is>
           <t>stamp_deai.mp3</t>
         </is>
       </c>
-      <c r="J15" s="104" t="inlineStr">
+      <c r="J15" s="108" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K15" s="104" t="n"/>
-      <c r="L15" s="104" t="n"/>
-      <c r="M15" s="104" t="inlineStr">
+      <c r="K15" s="108" t="n"/>
+      <c r="L15" s="108" t="n"/>
+      <c r="M15" s="108" t="inlineStr">
         <is>
           <t>stamp</t>
         </is>
       </c>
-      <c r="N15" s="105" t="n"/>
-      <c r="O15" s="105" t="n"/>
-      <c r="P15" s="105" t="inlineStr">
+      <c r="N15" s="109" t="n"/>
+      <c r="O15" s="109" t="n"/>
+      <c r="P15" s="109" t="inlineStr">
         <is>
           <t>2026-10-13 17:23</t>
         </is>
@@ -3574,17 +3586,17 @@
       </c>
     </row>
     <row r="18" ht="58.05" customHeight="1">
-      <c r="A18" s="104" t="inlineStr">
+      <c r="A18" s="108" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B18" s="104" t="inlineStr">
+      <c r="B18" s="108" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C18" s="104" t="inlineStr">
+      <c r="C18" s="108" t="inlineStr">
         <is>
           <t>sightseeing</t>
         </is>
@@ -3609,49 +3621,49 @@
           <t>展望台へは、自家用車で行くことはできません。歩いておよそ15分、またはシャトルバスでお越しいただけます。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G18" s="104" t="n"/>
-      <c r="H18" s="104" t="n"/>
-      <c r="I18" s="104" t="inlineStr">
+      <c r="G18" s="108" t="n"/>
+      <c r="H18" s="108" t="n"/>
+      <c r="I18" s="108" t="inlineStr">
         <is>
           <t>observatory_access_bt.mp3</t>
         </is>
       </c>
-      <c r="J18" s="104" t="inlineStr">
+      <c r="J18" s="108" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K18" s="104" t="n"/>
-      <c r="L18" s="104" t="n"/>
-      <c r="M18" s="104" t="inlineStr">
+      <c r="K18" s="108" t="n"/>
+      <c r="L18" s="108" t="n"/>
+      <c r="M18" s="108" t="inlineStr">
         <is>
           <t>observatory_access</t>
         </is>
       </c>
-      <c r="N18" s="105" t="inlineStr">
+      <c r="N18" s="109" t="inlineStr">
         <is>
           <t>展望台への行き方</t>
         </is>
       </c>
-      <c r="O18" s="105" t="n"/>
-      <c r="P18" s="105" t="inlineStr">
+      <c r="O18" s="109" t="n"/>
+      <c r="P18" s="109" t="inlineStr">
         <is>
           <t>2026-10-13 17:26</t>
         </is>
       </c>
     </row>
     <row r="19" ht="79.2" customHeight="1">
-      <c r="A19" s="104" t="inlineStr">
+      <c r="A19" s="108" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B19" s="104" t="inlineStr">
+      <c r="B19" s="108" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C19" s="104" t="inlineStr">
+      <c r="C19" s="108" t="inlineStr">
         <is>
           <t>sightseeing</t>
         </is>
@@ -3675,28 +3687,28 @@
           <t>展望台へは、目の前の橋を渡り、大通りを左へ10分ほど進んだ池の前のバス停から、シャトルバスが出ています。遊歩道もございます。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G19" s="104" t="n"/>
-      <c r="H19" s="104" t="n"/>
-      <c r="I19" s="104" t="inlineStr">
+      <c r="G19" s="108" t="n"/>
+      <c r="H19" s="108" t="n"/>
+      <c r="I19" s="108" t="inlineStr">
         <is>
           <t>observatory_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J19" s="104" t="inlineStr">
+      <c r="J19" s="108" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K19" s="104" t="n"/>
-      <c r="L19" s="104" t="n"/>
-      <c r="M19" s="104" t="inlineStr">
+      <c r="K19" s="108" t="n"/>
+      <c r="L19" s="108" t="n"/>
+      <c r="M19" s="108" t="inlineStr">
         <is>
           <t>observatory_access</t>
         </is>
       </c>
-      <c r="N19" s="105" t="n"/>
-      <c r="O19" s="105" t="n"/>
-      <c r="P19" s="105" t="inlineStr">
+      <c r="N19" s="109" t="n"/>
+      <c r="O19" s="109" t="n"/>
+      <c r="P19" s="109" t="inlineStr">
         <is>
           <t>2026-10-13 17:27</t>
         </is>
@@ -3762,17 +3774,17 @@
       </c>
     </row>
     <row r="21" ht="66" customHeight="1">
-      <c r="A21" s="104" t="inlineStr">
+      <c r="A21" s="108" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="B21" s="104" t="inlineStr">
+      <c r="B21" s="108" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C21" s="104" t="inlineStr">
+      <c r="C21" s="108" t="inlineStr">
         <is>
           <t>sightseeing</t>
         </is>
@@ -3793,32 +3805,32 @@
         </is>
       </c>
       <c r="F21" s="44" t="n"/>
-      <c r="G21" s="104" t="n"/>
-      <c r="H21" s="104" t="inlineStr">
+      <c r="G21" s="108" t="n"/>
+      <c r="H21" s="108" t="inlineStr">
         <is>
           <t>https://shirakawa-going.jp/</t>
         </is>
       </c>
-      <c r="I21" s="104" t="inlineStr">
+      <c r="I21" s="108" t="inlineStr">
         <is>
           <t>waterfall_lake.mp3</t>
         </is>
       </c>
-      <c r="J21" s="104" t="inlineStr">
+      <c r="J21" s="108" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K21" s="104" t="n"/>
-      <c r="L21" s="104" t="n"/>
-      <c r="M21" s="104" t="inlineStr">
+      <c r="K21" s="108" t="n"/>
+      <c r="L21" s="108" t="n"/>
+      <c r="M21" s="108" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="N21" s="105" t="n"/>
-      <c r="O21" s="105" t="n"/>
-      <c r="P21" s="105" t="inlineStr">
+      <c r="N21" s="109" t="n"/>
+      <c r="O21" s="109" t="n"/>
+      <c r="P21" s="109" t="inlineStr">
         <is>
           <t>2026-10-13 17:30</t>
         </is>
@@ -4909,22 +4921,22 @@
       </c>
     </row>
     <row r="41" ht="66" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="111" t="inlineStr">
         <is>
           <t>festival_shrine_access_deai</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B41" s="111" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C41" s="111" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" s="44" t="inlineStr">
         <is>
           <t>白川八幡神社 どこ
 神社 行き方
@@ -4932,29 +4944,36 @@
 どぶろく どこ</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="11" t="n"/>
-      <c r="I41" s="11" t="inlineStr">
+      <c r="E41" s="44" t="inlineStr">
+        <is>
+          <t>「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは約400m、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
+        </is>
+      </c>
+      <c r="F41" s="44" t="n"/>
+      <c r="G41" s="111" t="n"/>
+      <c r="H41" s="111" t="n"/>
+      <c r="I41" s="111" t="inlineStr">
         <is>
           <t>festival_shrine_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K41" s="11" t="n"/>
-      <c r="L41" s="11" t="n"/>
-      <c r="M41" s="14" t="inlineStr">
+      <c r="J41" s="111" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K41" s="111" t="n"/>
+      <c r="L41" s="111" t="n"/>
+      <c r="M41" s="111" t="inlineStr">
         <is>
           <t>festival_shrine_access</t>
+        </is>
+      </c>
+      <c r="N41" s="112" t="n"/>
+      <c r="O41" s="112" t="n"/>
+      <c r="P41" s="112" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:31</t>
         </is>
       </c>
     </row>
@@ -5028,17 +5047,17 @@
       </c>
     </row>
     <row r="43" ht="249.6" customHeight="1">
-      <c r="A43" s="104" t="inlineStr">
+      <c r="A43" s="108" t="inlineStr">
         <is>
           <t>guesthouse_access_deai</t>
         </is>
       </c>
-      <c r="B43" s="104" t="inlineStr">
+      <c r="B43" s="108" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C43" s="104" t="inlineStr">
+      <c r="C43" s="108" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -5072,30 +5091,30 @@
           <t>その建物は鳩谷八幡神社方面にあります。国道は交通量が多いため、川沿いの道をおすすめしております。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G43" s="104" t="inlineStr">
+      <c r="G43" s="108" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H43" s="104" t="n"/>
-      <c r="I43" s="104" t="inlineStr">
+      <c r="H43" s="108" t="n"/>
+      <c r="I43" s="108" t="inlineStr">
         <is>
           <t>guesthouse_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J43" s="104" t="inlineStr">
+      <c r="J43" s="108" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K43" s="104" t="n"/>
-      <c r="L43" s="104" t="n"/>
-      <c r="M43" s="104" t="inlineStr">
+      <c r="K43" s="108" t="n"/>
+      <c r="L43" s="108" t="n"/>
+      <c r="M43" s="108" t="inlineStr">
         <is>
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="105" t="n"/>
+      <c r="N43" s="109" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -6284,17 +6303,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="105" t="inlineStr">
+      <c r="A66" s="109" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="105" t="inlineStr">
+      <c r="B66" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="105" t="inlineStr">
+      <c r="C66" s="109" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -6324,26 +6343,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="105" t="inlineStr">
+      <c r="G66" s="109" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="105" t="n"/>
-      <c r="I66" s="105" t="inlineStr">
+      <c r="H66" s="109" t="n"/>
+      <c r="I66" s="109" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="105" t="inlineStr">
+      <c r="J66" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="105" t="n"/>
-      <c r="L66" s="105" t="n"/>
-      <c r="M66" s="105" t="n"/>
-      <c r="N66" s="105" t="n"/>
+      <c r="K66" s="109" t="n"/>
+      <c r="L66" s="109" t="n"/>
+      <c r="M66" s="109" t="n"/>
+      <c r="N66" s="109" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -7552,12 +7571,12 @@
       </c>
     </row>
     <row r="22" ht="64.8" customHeight="1">
-      <c r="A22" s="105" t="inlineStr">
+      <c r="A22" s="109" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B22" s="105" t="inlineStr">
+      <c r="B22" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7588,12 +7607,12 @@
       </c>
     </row>
     <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="105" t="inlineStr">
+      <c r="A23" s="109" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B23" s="105" t="inlineStr">
+      <c r="B23" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7624,12 +7643,12 @@
       </c>
     </row>
     <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="105" t="inlineStr">
+      <c r="A24" s="109" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B24" s="105" t="inlineStr">
+      <c r="B24" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7660,12 +7679,12 @@
       </c>
     </row>
     <row r="25" ht="81" customHeight="1">
-      <c r="A25" s="105" t="inlineStr">
+      <c r="A25" s="109" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B25" s="105" t="inlineStr">
+      <c r="B25" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7696,12 +7715,12 @@
       </c>
     </row>
     <row r="26" ht="64.8" customHeight="1">
-      <c r="A26" s="99" t="inlineStr">
+      <c r="A26" s="110" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B26" s="99" t="inlineStr">
+      <c r="B26" s="110" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8253,12 +8272,12 @@
       </c>
     </row>
     <row r="42" ht="64.8" customHeight="1">
-      <c r="A42" s="105" t="inlineStr">
+      <c r="A42" s="109" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B42" s="105" t="inlineStr">
+      <c r="B42" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8289,12 +8308,12 @@
       </c>
     </row>
     <row r="43" ht="64.8" customHeight="1">
-      <c r="A43" s="105" t="inlineStr">
+      <c r="A43" s="109" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B43" s="105" t="inlineStr">
+      <c r="B43" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8325,12 +8344,12 @@
       </c>
     </row>
     <row r="44" ht="81" customHeight="1">
-      <c r="A44" s="105" t="inlineStr">
+      <c r="A44" s="109" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B44" s="105" t="inlineStr">
+      <c r="B44" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8361,12 +8380,12 @@
       </c>
     </row>
     <row r="45" ht="64.8" customHeight="1">
-      <c r="A45" s="105" t="inlineStr">
+      <c r="A45" s="109" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B45" s="105" t="inlineStr">
+      <c r="B45" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8397,12 +8416,12 @@
       </c>
     </row>
     <row r="46" ht="64.8" customHeight="1">
-      <c r="A46" s="99" t="inlineStr">
+      <c r="A46" s="110" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B46" s="99" t="inlineStr">
+      <c r="B46" s="110" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8613,12 +8632,12 @@
       </c>
     </row>
     <row r="52" ht="48.6" customHeight="1">
-      <c r="A52" s="105" t="inlineStr">
+      <c r="A52" s="109" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B52" s="105" t="inlineStr">
+      <c r="B52" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8649,12 +8668,12 @@
       </c>
     </row>
     <row r="53" ht="97.2" customHeight="1">
-      <c r="A53" s="105" t="inlineStr">
+      <c r="A53" s="109" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B53" s="105" t="inlineStr">
+      <c r="B53" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8685,12 +8704,12 @@
       </c>
     </row>
     <row r="54" ht="97.2" customHeight="1">
-      <c r="A54" s="105" t="inlineStr">
+      <c r="A54" s="109" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B54" s="105" t="inlineStr">
+      <c r="B54" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8721,12 +8740,12 @@
       </c>
     </row>
     <row r="55" ht="97.2" customHeight="1">
-      <c r="A55" s="105" t="inlineStr">
+      <c r="A55" s="109" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B55" s="105" t="inlineStr">
+      <c r="B55" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8757,12 +8776,12 @@
       </c>
     </row>
     <row r="56" ht="97.2" customHeight="1">
-      <c r="A56" s="99" t="inlineStr">
+      <c r="A56" s="110" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B56" s="99" t="inlineStr">
+      <c r="B56" s="110" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8957,12 +8976,12 @@
       </c>
     </row>
     <row r="62" ht="81" customHeight="1">
-      <c r="A62" s="105" t="inlineStr">
+      <c r="A62" s="109" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B62" s="105" t="inlineStr">
+      <c r="B62" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8993,12 +9012,12 @@
       </c>
     </row>
     <row r="63" ht="97.2" customHeight="1">
-      <c r="A63" s="105" t="inlineStr">
+      <c r="A63" s="109" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B63" s="105" t="inlineStr">
+      <c r="B63" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -9029,12 +9048,12 @@
       </c>
     </row>
     <row r="64" ht="97.2" customHeight="1">
-      <c r="A64" s="105" t="inlineStr">
+      <c r="A64" s="109" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B64" s="105" t="inlineStr">
+      <c r="B64" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -9065,12 +9084,12 @@
       </c>
     </row>
     <row r="65" ht="97.2" customHeight="1">
-      <c r="A65" s="105" t="inlineStr">
+      <c r="A65" s="109" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B65" s="105" t="inlineStr">
+      <c r="B65" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -9101,12 +9120,12 @@
       </c>
     </row>
     <row r="66" ht="81" customHeight="1">
-      <c r="A66" s="99" t="inlineStr">
+      <c r="A66" s="110" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B66" s="99" t="inlineStr">
+      <c r="B66" s="110" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -9647,12 +9666,12 @@
       </c>
     </row>
     <row r="82" ht="145.8" customHeight="1">
-      <c r="A82" s="105" t="inlineStr">
+      <c r="A82" s="109" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B82" s="105" t="inlineStr">
+      <c r="B82" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -9684,12 +9703,12 @@
       </c>
     </row>
     <row r="83" ht="145.8" customHeight="1">
-      <c r="A83" s="105" t="inlineStr">
+      <c r="A83" s="109" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B83" s="105" t="inlineStr">
+      <c r="B83" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -9721,12 +9740,12 @@
       </c>
     </row>
     <row r="84" ht="162" customHeight="1">
-      <c r="A84" s="105" t="inlineStr">
+      <c r="A84" s="109" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B84" s="105" t="inlineStr">
+      <c r="B84" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -9758,12 +9777,12 @@
       </c>
     </row>
     <row r="85" ht="145.8" customHeight="1">
-      <c r="A85" s="105" t="inlineStr">
+      <c r="A85" s="109" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B85" s="105" t="inlineStr">
+      <c r="B85" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -9795,12 +9814,12 @@
       </c>
     </row>
     <row r="86" ht="145.8" customHeight="1">
-      <c r="A86" s="99" t="inlineStr">
+      <c r="A86" s="110" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B86" s="99" t="inlineStr">
+      <c r="B86" s="110" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -13495,32 +13514,35 @@
       </c>
     </row>
     <row r="197" ht="97.2" customHeight="1">
-      <c r="A197" s="27" t="inlineStr">
+      <c r="A197" s="113" t="inlineStr">
         <is>
           <t>festival_shrine_access_deai</t>
         </is>
       </c>
-      <c r="B197" s="27" t="inlineStr">
+      <c r="B197" s="113" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="C197" s="28" t="inlineStr">
-        <is>
-          <t>Shirakawa Hachiman
-shrine where
-shrine get
-festival venue
-doburoku where
-festival place</t>
-        </is>
-      </c>
-      <c r="D197" s="28" t="inlineStr">
-        <is>
-          <t>Shirakawa Hachiman Shrine is at the southern end of the Ogimachi gassho-style village. From Deai-no-Yakata, cross Deai Bridge, go out to the main street, and head right, to the south, and you will arrive there. Look for the torii gate and the large cedar trees.</t>
-        </is>
-      </c>
-      <c r="E197" s="27" t="n"/>
+      <c r="C197" s="73" t="inlineStr">
+        <is>
+          <t>Shirakawa Hachimangu Shrine location
+how to get to the shrine
+where is the festival venue
+Doburoku sake where
+Hachimangu direction from Deai</t>
+        </is>
+      </c>
+      <c r="D197" s="73" t="inlineStr">
+        <is>
+          <t>Shirakawa Hachimangu Shrine is located at the southern end of the Ogimachi gassho-zukuri village. From the Deai no Yakan building, it's about four hundred meters away. Cross the Deai Bridge, head out to the main street, and continue to the right, heading south. You'll recognize it by the torii gate and the large cedar trees.</t>
+        </is>
+      </c>
+      <c r="E197" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは約400m、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
+        </is>
+      </c>
       <c r="F197" s="29" t="inlineStr">
         <is>
           <t>「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
@@ -13528,32 +13550,35 @@
       </c>
     </row>
     <row r="198" ht="97.2" customHeight="1">
-      <c r="A198" s="27" t="inlineStr">
+      <c r="A198" s="113" t="inlineStr">
         <is>
           <t>festival_shrine_access_deai</t>
         </is>
       </c>
-      <c r="B198" s="27" t="inlineStr">
+      <c r="B198" s="113" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="C198" s="28" t="inlineStr">
-        <is>
-          <t>Hachiman
-santuario llegar
-santuario Shirakawa
-lugar festival
-doburoku donde
-templo festival</t>
-        </is>
-      </c>
-      <c r="D198" s="28" t="inlineStr">
-        <is>
-          <t>El Santuario Hachiman de Shirakawa está en el extremo sur de la aldea de casas gassho-zukuri de Ogimachi. Desde Deai-no-Yakata, cruce el Puente Deai, salga a la calle principal y siga hacia la derecha, es decir, hacia el sur, hasta llegar. Lo reconocerá por el torii y el gran cedro.</t>
-        </is>
-      </c>
-      <c r="E198" s="27" t="n"/>
+      <c r="C198" s="73" t="inlineStr">
+        <is>
+          <t>Santuario Shirakawa Hachimangu dónde
+cómo llegar al santuario
+ubicación del festival
+dónde está el Doburoku
+dirección desde Deai no Yakan</t>
+        </is>
+      </c>
+      <c r="D198" s="73" t="inlineStr">
+        <is>
+          <t>El Santuario Shirakawa Hachimangu se encuentra ubicado en el extremo sur de la aldea de casas gassho-zukuri de Ogimachi. Desde el edificio Deai no Yakan, está a aproximadamente cuatrocientos metros. Cruza el puente Deai, sal a la calle principal y continúa hacia la derecha, en dirección sur. Podrás reconocerlo por la puerta torii y los grandes árboles de cedro.</t>
+        </is>
+      </c>
+      <c r="E198" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは約400m、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
+        </is>
+      </c>
       <c r="F198" s="29" t="inlineStr">
         <is>
           <t>「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
@@ -13561,32 +13586,35 @@
       </c>
     </row>
     <row r="199" ht="97.2" customHeight="1">
-      <c r="A199" s="27" t="inlineStr">
+      <c r="A199" s="113" t="inlineStr">
         <is>
           <t>festival_shrine_access_deai</t>
         </is>
       </c>
-      <c r="B199" s="27" t="inlineStr">
+      <c r="B199" s="113" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="C199" s="28" t="inlineStr">
-        <is>
-          <t>sanctuaire shirakawa
-sanctuaire aller
-sanctuaire où
-lieu festival
-doburoku où
-hachiman</t>
-        </is>
-      </c>
-      <c r="D199" s="28" t="inlineStr">
-        <is>
-          <t>Le sanctuaire Shirakawa Hachiman se trouve à l'extrémité sud du village aux maisons gassho d'Ogimachi. Depuis le Deai-no-Yakata, traversez le pont Deai, rejoignez la rue principale et continuez vers la droite, c'est-à-dire vers le sud, pour y arriver. Le torii et le grand cèdre vous serviront de repères.</t>
-        </is>
-      </c>
-      <c r="E199" s="27" t="n"/>
+      <c r="C199" s="73" t="inlineStr">
+        <is>
+          <t>Sanctuaire Shirakawa Hachimangu localisation
+comment aller au sanctuaire
+où est le festival
+où trouver le Doburoku
+direction depuis Deai no Yakan</t>
+        </is>
+      </c>
+      <c r="D199" s="73" t="inlineStr">
+        <is>
+          <t>Le Sanctuaire Shirakawa Hachimangu est situé à l'extrémité sud du village de maisons gassho-zukuri d'Ogimachi. En partant du bâtiment Deai no Yakan, il se trouve à environ quatre cents mètres. Traversez le pont Deai, rejoignez la rue principale et continuez vers la droite en direction du sud. Vous le reconnaîtrez par le portique torii et les grands cèdres.</t>
+        </is>
+      </c>
+      <c r="E199" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは約400m、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
+        </is>
+      </c>
       <c r="F199" s="29" t="inlineStr">
         <is>
           <t>「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
@@ -13594,32 +13622,35 @@
       </c>
     </row>
     <row r="200" ht="97.2" customHeight="1">
-      <c r="A200" s="27" t="inlineStr">
+      <c r="A200" s="113" t="inlineStr">
         <is>
           <t>festival_shrine_access_deai</t>
         </is>
       </c>
-      <c r="B200" s="27" t="inlineStr">
+      <c r="B200" s="113" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="C200" s="28" t="inlineStr">
-        <is>
-          <t>시라카와 하치만 신사
-하치만 신사
-신사 가는
-신사 어떻게
-축제 장소
-도부로쿠 어디</t>
-        </is>
-      </c>
-      <c r="D200" s="28" t="inlineStr">
-        <is>
-          <t>시라카와 하치만 신사는 오기마치 갓쇼즈쿠리 마을의 남쪽 끝에 있습니다. 데아이노야카타 쪽에서는 데아이 다리를 건너 큰길로 나가서 오른쪽, 즉 남쪽으로 가시면 도착합니다. 도리이와 큰 삼나무가 표지입니다.</t>
-        </is>
-      </c>
-      <c r="E200" s="27" t="n"/>
+      <c r="C200" s="73" t="inlineStr">
+        <is>
+          <t>시라카와 하치만구 신사 위치
+신사 가는 방법
+제사 장소 어디
+도부로쿠 어디 있어
+데아이에서 하치만구 길</t>
+        </is>
+      </c>
+      <c r="D200" s="73" t="inlineStr">
+        <is>
+          <t>시라카와 하치만구 신사는 오기마치 합장조 집락의 남쪽 끝에 위치하고 있습니다. 데아이노야칸 방면에서 약사백 미터 떨어져 있습니다. 데아이 다리를 건너 대로에 나온 후 오른쪽, 즉 남쪽으로 진행하면 도착합니다. 토리이 문과 큰 삼나무가 표시입니다.</t>
+        </is>
+      </c>
+      <c r="E200" s="73" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは約400m、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
+        </is>
+      </c>
       <c r="F200" s="29" t="inlineStr">
         <is>
           <t>「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
@@ -13627,31 +13658,35 @@
       </c>
     </row>
     <row r="201" ht="81" customHeight="1">
-      <c r="A201" s="30" t="inlineStr">
+      <c r="A201" s="114" t="inlineStr">
         <is>
           <t>festival_shrine_access_deai</t>
         </is>
       </c>
-      <c r="B201" s="30" t="inlineStr">
+      <c r="B201" s="114" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C201" s="31" t="inlineStr">
-        <is>
-          <t>白川八幡神社
-神社 怎么走
-节日 会场
-浊酒 哪里
-神社 在哪</t>
-        </is>
-      </c>
-      <c r="D201" s="31" t="inlineStr">
-        <is>
-          <t>白川八幡神社位于荻町合掌造村落的南端。从Deai-no-Yakata（出会之馆）方向出发，过Deai桥走到大路后，向右（南边）前进即可到达。鸟居和高大的杉树是标志。</t>
-        </is>
-      </c>
-      <c r="E201" s="30" t="n"/>
+      <c r="C201" s="75" t="inlineStr">
+        <is>
+          <t>白川八幡神社 位置
+怎么去神社
+祭典会场在哪里
+浊酒在哪里
+从相逢馆去八幡神社</t>
+        </is>
+      </c>
+      <c r="D201" s="75" t="inlineStr">
+        <is>
+          <t>白川八幡神社位于荻町合掌造集落的南端。从相逢馆方向出发，约四百米的距离。穿过相逢桥，来到大街上，向右边，即南侧方向行进就能到达。以鸟居和大杉树为标志。</t>
+        </is>
+      </c>
+      <c r="E201" s="75" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは約400m、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
+        </is>
+      </c>
       <c r="F201" s="32" t="inlineStr">
         <is>
           <t>「白川八幡神社」は、荻町合掌造り集落の南端に位置しています。 であいの館方面からは、であい橋を渡って大通りに出て右（南側）へ進むと到着します。鳥居と大きな杉の木が目印です。</t>
@@ -17038,12 +17073,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="105" t="inlineStr">
+      <c r="A302" s="109" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="105" t="inlineStr">
+      <c r="B302" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17069,12 +17104,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="105" t="inlineStr">
+      <c r="A303" s="109" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="105" t="inlineStr">
+      <c r="B303" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17100,12 +17135,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="105" t="inlineStr">
+      <c r="A304" s="109" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="105" t="inlineStr">
+      <c r="B304" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17131,12 +17166,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="105" t="inlineStr">
+      <c r="A305" s="109" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="105" t="inlineStr">
+      <c r="B305" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17162,12 +17197,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="105" t="inlineStr">
+      <c r="A306" s="109" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="105" t="inlineStr">
+      <c r="B306" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17193,12 +17228,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="105" t="inlineStr">
+      <c r="A307" s="109" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="105" t="inlineStr">
+      <c r="B307" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17224,12 +17259,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="105" t="inlineStr">
+      <c r="A308" s="109" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="105" t="inlineStr">
+      <c r="B308" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17255,12 +17290,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="105" t="inlineStr">
+      <c r="A309" s="109" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="105" t="inlineStr">
+      <c r="B309" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17286,12 +17321,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="105" t="inlineStr">
+      <c r="A310" s="109" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="105" t="inlineStr">
+      <c r="B310" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17317,12 +17352,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="105" t="inlineStr">
+      <c r="A311" s="109" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="105" t="inlineStr">
+      <c r="B311" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17348,12 +17383,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="105" t="inlineStr">
+      <c r="A312" s="109" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="105" t="inlineStr">
+      <c r="B312" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17378,12 +17413,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="105" t="inlineStr">
+      <c r="A313" s="109" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="105" t="inlineStr">
+      <c r="B313" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17408,12 +17443,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="105" t="inlineStr">
+      <c r="A314" s="109" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="105" t="inlineStr">
+      <c r="B314" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17438,12 +17473,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="105" t="inlineStr">
+      <c r="A315" s="109" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="105" t="inlineStr">
+      <c r="B315" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17468,12 +17503,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="105" t="inlineStr">
+      <c r="A316" s="109" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="105" t="inlineStr">
+      <c r="B316" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17498,12 +17533,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="105" t="inlineStr">
+      <c r="A317" s="109" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="105" t="inlineStr">
+      <c r="B317" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17529,12 +17564,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="105" t="inlineStr">
+      <c r="A318" s="109" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="105" t="inlineStr">
+      <c r="B318" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17560,12 +17595,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="105" t="inlineStr">
+      <c r="A319" s="109" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="105" t="inlineStr">
+      <c r="B319" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17591,12 +17626,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="105" t="inlineStr">
+      <c r="A320" s="109" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="105" t="inlineStr">
+      <c r="B320" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17622,12 +17657,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="105" t="inlineStr">
+      <c r="A321" s="109" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="105" t="inlineStr">
+      <c r="B321" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17653,12 +17688,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="105" t="inlineStr">
+      <c r="A322" s="109" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="105" t="inlineStr">
+      <c r="B322" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17683,12 +17718,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="105" t="inlineStr">
+      <c r="A323" s="109" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="105" t="inlineStr">
+      <c r="B323" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17713,12 +17748,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="105" t="inlineStr">
+      <c r="A324" s="109" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="105" t="inlineStr">
+      <c r="B324" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17743,12 +17778,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="105" t="inlineStr">
+      <c r="A325" s="109" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="105" t="inlineStr">
+      <c r="B325" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17773,12 +17808,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="105" t="inlineStr">
+      <c r="A326" s="109" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="105" t="inlineStr">
+      <c r="B326" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17803,12 +17838,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="105" t="inlineStr">
+      <c r="A327" s="109" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="105" t="inlineStr">
+      <c r="B327" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17835,12 +17870,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="105" t="inlineStr">
+      <c r="A328" s="109" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="105" t="inlineStr">
+      <c r="B328" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17867,12 +17902,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="105" t="inlineStr">
+      <c r="A329" s="109" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="105" t="inlineStr">
+      <c r="B329" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17899,12 +17934,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="105" t="inlineStr">
+      <c r="A330" s="109" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="105" t="inlineStr">
+      <c r="B330" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17931,12 +17966,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="105" t="inlineStr">
+      <c r="A331" s="109" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="105" t="inlineStr">
+      <c r="B331" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17963,12 +17998,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="105" t="inlineStr">
+      <c r="A332" s="109" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="105" t="inlineStr">
+      <c r="B332" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17995,12 +18030,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="105" t="inlineStr">
+      <c r="A333" s="109" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="105" t="inlineStr">
+      <c r="B333" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18027,12 +18062,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="105" t="inlineStr">
+      <c r="A334" s="109" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="105" t="inlineStr">
+      <c r="B334" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18059,12 +18094,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="105" t="inlineStr">
+      <c r="A335" s="109" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="105" t="inlineStr">
+      <c r="B335" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18091,12 +18126,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="105" t="inlineStr">
+      <c r="A336" s="109" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="105" t="inlineStr">
+      <c r="B336" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18123,12 +18158,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="105" t="inlineStr">
+      <c r="A337" s="109" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="105" t="inlineStr">
+      <c r="B337" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18155,12 +18190,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="105" t="inlineStr">
+      <c r="A338" s="109" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="105" t="inlineStr">
+      <c r="B338" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18187,12 +18222,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="105" t="inlineStr">
+      <c r="A339" s="109" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="105" t="inlineStr">
+      <c r="B339" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18219,12 +18254,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="105" t="inlineStr">
+      <c r="A340" s="109" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="105" t="inlineStr">
+      <c r="B340" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18251,12 +18286,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="105" t="inlineStr">
+      <c r="A341" s="109" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="105" t="inlineStr">
+      <c r="B341" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18283,12 +18318,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="105" t="inlineStr">
+      <c r="A342" s="109" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="105" t="inlineStr">
+      <c r="B342" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18315,12 +18350,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="105" t="inlineStr">
+      <c r="A343" s="109" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="105" t="inlineStr">
+      <c r="B343" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18347,12 +18382,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="105" t="inlineStr">
+      <c r="A344" s="109" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="105" t="inlineStr">
+      <c r="B344" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18379,12 +18414,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="105" t="inlineStr">
+      <c r="A345" s="109" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="105" t="inlineStr">
+      <c r="B345" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18411,12 +18446,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="105" t="inlineStr">
+      <c r="A346" s="109" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="105" t="inlineStr">
+      <c r="B346" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18443,12 +18478,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="105" t="inlineStr">
+      <c r="A347" s="109" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="105" t="inlineStr">
+      <c r="B347" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18475,12 +18510,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="105" t="inlineStr">
+      <c r="A348" s="109" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="105" t="inlineStr">
+      <c r="B348" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18507,12 +18542,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="105" t="inlineStr">
+      <c r="A349" s="109" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="105" t="inlineStr">
+      <c r="B349" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18539,12 +18574,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="105" t="inlineStr">
+      <c r="A350" s="109" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="105" t="inlineStr">
+      <c r="B350" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18571,12 +18606,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="105" t="inlineStr">
+      <c r="A351" s="109" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="105" t="inlineStr">
+      <c r="B351" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18603,12 +18638,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="105" t="inlineStr">
+      <c r="A352" s="109" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="105" t="inlineStr">
+      <c r="B352" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18634,12 +18669,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="105" t="inlineStr">
+      <c r="A353" s="109" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="105" t="inlineStr">
+      <c r="B353" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18665,12 +18700,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="105" t="inlineStr">
+      <c r="A354" s="109" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="105" t="inlineStr">
+      <c r="B354" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18696,12 +18731,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="105" t="inlineStr">
+      <c r="A355" s="109" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="105" t="inlineStr">
+      <c r="B355" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18727,12 +18762,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="105" t="inlineStr">
+      <c r="A356" s="109" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="105" t="inlineStr">
+      <c r="B356" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18758,12 +18793,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="105" t="inlineStr">
+      <c r="A357" s="109" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="105" t="inlineStr">
+      <c r="B357" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18789,12 +18824,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="105" t="inlineStr">
+      <c r="A358" s="109" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="105" t="inlineStr">
+      <c r="B358" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18820,12 +18855,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="105" t="inlineStr">
+      <c r="A359" s="109" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="105" t="inlineStr">
+      <c r="B359" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18851,12 +18886,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="105" t="inlineStr">
+      <c r="A360" s="109" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="105" t="inlineStr">
+      <c r="B360" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18882,12 +18917,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="105" t="inlineStr">
+      <c r="A361" s="109" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="105" t="inlineStr">
+      <c r="B361" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18913,12 +18948,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="105" t="inlineStr">
+      <c r="A362" s="109" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="105" t="inlineStr">
+      <c r="B362" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18945,12 +18980,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="105" t="inlineStr">
+      <c r="A363" s="109" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="105" t="inlineStr">
+      <c r="B363" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18977,12 +19012,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="105" t="inlineStr">
+      <c r="A364" s="109" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="105" t="inlineStr">
+      <c r="B364" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -19009,12 +19044,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="105" t="inlineStr">
+      <c r="A365" s="109" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="105" t="inlineStr">
+      <c r="B365" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -19041,12 +19076,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="105" t="inlineStr">
+      <c r="A366" s="109" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="105" t="inlineStr">
+      <c r="B366" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -19073,12 +19108,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="105" t="inlineStr">
+      <c r="A367" s="109" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="105" t="inlineStr">
+      <c r="B367" s="109" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -19105,12 +19140,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="105" t="inlineStr">
+      <c r="A368" s="109" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="105" t="inlineStr">
+      <c r="B368" s="109" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -19137,12 +19172,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="105" t="inlineStr">
+      <c r="A369" s="109" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="105" t="inlineStr">
+      <c r="B369" s="109" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -19169,12 +19204,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="105" t="inlineStr">
+      <c r="A370" s="109" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="105" t="inlineStr">
+      <c r="B370" s="109" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -19201,12 +19236,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="105" t="inlineStr">
+      <c r="A371" s="109" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="105" t="inlineStr">
+      <c r="B371" s="109" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -20342,7 +20377,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="109" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -20352,7 +20387,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="105" t="inlineStr">
+      <c r="C2" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20364,7 +20399,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="A3" s="109" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -20374,7 +20409,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="105" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20386,7 +20421,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="105" t="inlineStr">
+      <c r="A4" s="109" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -20396,7 +20431,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="105" t="inlineStr">
+      <c r="C4" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20408,7 +20443,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="105" t="inlineStr">
+      <c r="A5" s="109" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -20418,7 +20453,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="105" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20430,7 +20465,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="105" t="inlineStr">
+      <c r="A6" s="109" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20440,7 +20475,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="105" t="inlineStr">
+      <c r="C6" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20452,7 +20487,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="105" t="inlineStr">
+      <c r="A7" s="109" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20462,7 +20497,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="105" t="inlineStr">
+      <c r="C7" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20474,7 +20509,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="105" t="inlineStr">
+      <c r="A8" s="109" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20484,7 +20519,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="105" t="inlineStr">
+      <c r="C8" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20496,7 +20531,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="105" t="inlineStr">
+      <c r="A9" s="109" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20506,7 +20541,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="105" t="inlineStr">
+      <c r="C9" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20518,7 +20553,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="105" t="inlineStr">
+      <c r="A10" s="109" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20528,7 +20563,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="105" t="inlineStr">
+      <c r="C10" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20540,7 +20575,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="105" t="inlineStr">
+      <c r="A11" s="109" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20550,7 +20585,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="105" t="inlineStr">
+      <c r="C11" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20562,7 +20597,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="105" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20572,7 +20607,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="105" t="inlineStr">
+      <c r="C12" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20584,7 +20619,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="105" t="inlineStr">
+      <c r="A13" s="109" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20594,7 +20629,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="105" t="inlineStr">
+      <c r="C13" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20736,53 +20771,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="109" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="105" t="inlineStr">
+      <c r="B2" s="109" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="105" t="inlineStr">
+      <c r="C2" s="109" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="105" t="inlineStr">
+      <c r="D2" s="109" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="105" t="inlineStr">
+      <c r="E2" s="109" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="105" t="inlineStr">
+      <c r="F2" s="109" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="105" t="inlineStr">
+      <c r="G2" s="109" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="105" t="inlineStr">
+      <c r="H2" s="109" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="105" t="inlineStr">
+      <c r="I2" s="109" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="105" t="n"/>
-      <c r="K2" s="105" t="inlineStr">
+      <c r="J2" s="109" t="n"/>
+      <c r="K2" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20819,45 +20854,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="A3" s="109" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="105" t="inlineStr">
+      <c r="B3" s="109" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="105" t="inlineStr">
+      <c r="C3" s="109" t="inlineStr">
         <is>
           <t>main_idle_20261013044809.png</t>
         </is>
       </c>
-      <c r="D3" s="105" t="n"/>
-      <c r="E3" s="105" t="n"/>
-      <c r="F3" s="105" t="n">
+      <c r="D3" s="109" t="n"/>
+      <c r="E3" s="109" t="n"/>
+      <c r="F3" s="109" t="n">
         <v>0.179</v>
       </c>
-      <c r="G3" s="105" t="n">
+      <c r="G3" s="109" t="n">
         <v>0.23</v>
       </c>
-      <c r="H3" s="105" t="inlineStr">
+      <c r="H3" s="109" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="105" t="inlineStr">
+      <c r="I3" s="109" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="105" t="inlineStr">
+      <c r="J3" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="105" t="inlineStr">
+      <c r="K3" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20894,45 +20929,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="105" t="inlineStr">
+      <c r="A4" s="109" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="105" t="inlineStr">
+      <c r="B4" s="109" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="105" t="inlineStr">
+      <c r="C4" s="109" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="105" t="n"/>
-      <c r="E4" s="105" t="n"/>
-      <c r="F4" s="105" t="inlineStr">
+      <c r="D4" s="109" t="n"/>
+      <c r="E4" s="109" t="n"/>
+      <c r="F4" s="109" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="105" t="inlineStr">
+      <c r="G4" s="109" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="105" t="inlineStr">
+      <c r="H4" s="109" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="105" t="inlineStr">
+      <c r="I4" s="109" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="105" t="n"/>
-      <c r="K4" s="105" t="inlineStr">
+      <c r="J4" s="109" t="n"/>
+      <c r="K4" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20969,45 +21004,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="105" t="inlineStr">
+      <c r="A5" s="109" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="105" t="inlineStr">
+      <c r="B5" s="109" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="105" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="105" t="n"/>
-      <c r="E5" s="105" t="n"/>
-      <c r="F5" s="105" t="inlineStr">
+      <c r="D5" s="109" t="n"/>
+      <c r="E5" s="109" t="n"/>
+      <c r="F5" s="109" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="105" t="inlineStr">
+      <c r="G5" s="109" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="105" t="inlineStr">
+      <c r="H5" s="109" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="105" t="inlineStr">
+      <c r="I5" s="109" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="105" t="n"/>
-      <c r="K5" s="105" t="inlineStr">
+      <c r="J5" s="109" t="n"/>
+      <c r="K5" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -21044,45 +21079,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="105" t="inlineStr">
+      <c r="A6" s="109" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="105" t="inlineStr">
+      <c r="B6" s="109" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="105" t="inlineStr">
+      <c r="C6" s="109" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="105" t="n"/>
-      <c r="E6" s="105" t="n"/>
-      <c r="F6" s="105" t="inlineStr">
+      <c r="D6" s="109" t="n"/>
+      <c r="E6" s="109" t="n"/>
+      <c r="F6" s="109" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="105" t="inlineStr">
+      <c r="G6" s="109" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="105" t="inlineStr">
+      <c r="H6" s="109" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="105" t="inlineStr">
+      <c r="I6" s="109" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="105" t="n"/>
-      <c r="K6" s="105" t="inlineStr">
+      <c r="J6" s="109" t="n"/>
+      <c r="K6" s="109" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -21204,12 +21239,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="109" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B2" s="105" t="inlineStr">
+      <c r="B2" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21248,12 +21283,12 @@
       <c r="J2" s="46" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="A3" s="109" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B3" s="105" t="inlineStr">
+      <c r="B3" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21292,12 +21327,12 @@
       <c r="J3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="105" t="inlineStr">
+      <c r="A4" s="109" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B4" s="105" t="inlineStr">
+      <c r="B4" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21336,12 +21371,12 @@
       <c r="J4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="105" t="inlineStr">
+      <c r="A5" s="109" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B5" s="105" t="inlineStr">
+      <c r="B5" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21380,12 +21415,12 @@
       <c r="J5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="105" t="inlineStr">
+      <c r="A6" s="109" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B6" s="105" t="inlineStr">
+      <c r="B6" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21424,12 +21459,12 @@
       <c r="J6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="105" t="inlineStr">
+      <c r="A7" s="109" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B7" s="105" t="inlineStr">
+      <c r="B7" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21468,12 +21503,12 @@
       <c r="J7" s="46" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="105" t="inlineStr">
+      <c r="A8" s="109" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B8" s="105" t="inlineStr">
+      <c r="B8" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21512,12 +21547,12 @@
       <c r="J8" s="46" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="105" t="inlineStr">
+      <c r="A9" s="109" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B9" s="105" t="inlineStr">
+      <c r="B9" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21556,12 +21591,12 @@
       <c r="J9" s="46" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="105" t="inlineStr">
+      <c r="A10" s="109" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B10" s="105" t="inlineStr">
+      <c r="B10" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21600,12 +21635,12 @@
       <c r="J10" s="46" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="105" t="inlineStr">
+      <c r="A11" s="109" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B11" s="105" t="inlineStr">
+      <c r="B11" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21644,12 +21679,12 @@
       <c r="J11" s="46" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="105" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B12" s="105" t="inlineStr">
+      <c r="B12" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21688,12 +21723,12 @@
       <c r="J12" s="46" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="105" t="inlineStr">
+      <c r="A13" s="109" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B13" s="105" t="inlineStr">
+      <c r="B13" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21751,12 +21786,12 @@
       <c r="J13" s="46" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="105" t="inlineStr">
+      <c r="A14" s="109" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B14" s="105" t="inlineStr">
+      <c r="B14" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21814,12 +21849,12 @@
       <c r="J14" s="46" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="105" t="inlineStr">
+      <c r="A15" s="109" t="inlineStr">
         <is>
           <t>趣味</t>
         </is>
       </c>
-      <c r="B15" s="105" t="inlineStr">
+      <c r="B15" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21880,12 +21915,12 @@
       <c r="J15" s="46" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="105" t="inlineStr">
+      <c r="A16" s="109" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B16" s="105" t="inlineStr">
+      <c r="B16" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21945,12 +21980,12 @@
       <c r="J16" s="46" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="105" t="inlineStr">
+      <c r="A17" s="109" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B17" s="105" t="inlineStr">
+      <c r="B17" s="109" t="inlineStr">
         <is>
           <t>共通</t>
         </is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -591,6 +591,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1293,7 +1302,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="109" t="inlineStr">
+      <c r="A2" s="112" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1303,31 +1312,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="109" t="n">
+      <c r="C2" s="112" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="109" t="n">
+      <c r="D2" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="109" t="n">
+      <c r="E2" s="112" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="109" t="n">
+      <c r="F2" s="112" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="109" t="n">
+      <c r="G2" s="112" t="n">
         <v>0.957</v>
       </c>
-      <c r="H2" s="109" t="n">
+      <c r="H2" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="109" t="n">
+      <c r="I2" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="109" t="n">
+      <c r="J2" s="112" t="n">
         <v>0.864</v>
       </c>
-      <c r="K2" s="109" t="n">
+      <c r="K2" s="112" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1337,7 +1346,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="109" t="inlineStr">
+      <c r="A3" s="112" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1347,31 +1356,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="109" t="n">
+      <c r="C3" s="112" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="109" t="n">
+      <c r="D3" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="109" t="n">
+      <c r="E3" s="112" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="109" t="n">
+      <c r="F3" s="112" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="109" t="n">
+      <c r="G3" s="112" t="n">
         <v>0.929</v>
       </c>
-      <c r="H3" s="109" t="n">
+      <c r="H3" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="109" t="n">
+      <c r="I3" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="109" t="n">
+      <c r="J3" s="112" t="n">
         <v>0.753</v>
       </c>
-      <c r="K3" s="109" t="n">
+      <c r="K3" s="112" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1381,7 +1390,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="109" t="inlineStr">
+      <c r="A4" s="112" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1391,31 +1400,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="109" t="n">
+      <c r="C4" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="109" t="n">
+      <c r="D4" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="109" t="n">
+      <c r="E4" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="109" t="n">
+      <c r="F4" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="109" t="n">
+      <c r="G4" s="112" t="n">
         <v>0.92</v>
       </c>
-      <c r="H4" s="109" t="n">
+      <c r="H4" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="109" t="n">
+      <c r="I4" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="109" t="n">
+      <c r="J4" s="112" t="n">
         <v>0.884</v>
       </c>
-      <c r="K4" s="109" t="n">
+      <c r="K4" s="112" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1487,7 +1496,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="109" t="inlineStr">
+      <c r="A2" s="112" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1497,10 +1506,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="109" t="n">
+      <c r="C2" s="112" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="109" t="n">
+      <c r="D2" s="112" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1510,7 +1519,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="109" t="inlineStr">
+      <c r="A3" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1520,16 +1529,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="109" t="n">
+      <c r="C3" s="112" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="109" t="n">
+      <c r="D3" s="112" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="109" t="inlineStr">
+      <c r="A4" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1539,16 +1548,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="109" t="n">
+      <c r="C4" s="112" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="109" t="n">
+      <c r="D4" s="112" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="109" t="inlineStr">
+      <c r="A5" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1558,16 +1567,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="109" t="n">
+      <c r="C5" s="112" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="109" t="n">
+      <c r="D5" s="112" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="109" t="inlineStr">
+      <c r="A6" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1577,16 +1586,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="109" t="n">
+      <c r="C6" s="112" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="109" t="n">
+      <c r="D6" s="112" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="109" t="inlineStr">
+      <c r="A7" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1596,10 +1605,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="109" t="n">
+      <c r="C7" s="112" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="109" t="n">
+      <c r="D7" s="112" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1659,17 +1668,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="109" t="inlineStr">
+      <c r="A2" s="112" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="109" t="inlineStr">
+      <c r="B2" s="112" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="109" t="inlineStr">
+      <c r="C2" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1681,17 +1690,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="109" t="inlineStr">
+      <c r="A3" s="112" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="109" t="inlineStr">
+      <c r="B3" s="112" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="109" t="inlineStr">
+      <c r="C3" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1699,17 +1708,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="109" t="inlineStr">
+      <c r="A4" s="112" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="109" t="inlineStr">
+      <c r="B4" s="112" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="109" t="inlineStr">
+      <c r="C4" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1721,17 +1730,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="109" t="inlineStr">
+      <c r="A5" s="112" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="109" t="inlineStr">
+      <c r="B5" s="112" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="109" t="inlineStr">
+      <c r="C5" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1743,17 +1752,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="109" t="inlineStr">
+      <c r="A6" s="112" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="109" t="inlineStr">
+      <c r="B6" s="112" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="109" t="inlineStr">
+      <c r="C6" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1761,17 +1770,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="109" t="inlineStr">
+      <c r="A7" s="112" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="109" t="inlineStr">
+      <c r="B7" s="112" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="109" t="inlineStr">
+      <c r="C7" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1779,17 +1788,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="109" t="inlineStr">
+      <c r="A8" s="112" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="109" t="inlineStr">
+      <c r="B8" s="112" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="109" t="inlineStr">
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1801,17 +1810,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="109" t="inlineStr">
+      <c r="A9" s="112" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="109" t="inlineStr">
+      <c r="B9" s="112" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="109" t="inlineStr">
+      <c r="C9" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1823,17 +1832,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="109" t="inlineStr">
+      <c r="A10" s="112" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="109" t="inlineStr">
+      <c r="B10" s="112" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="109" t="inlineStr">
+      <c r="C10" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1845,17 +1854,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="109" t="inlineStr">
+      <c r="A11" s="112" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="109" t="inlineStr">
+      <c r="B11" s="112" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="109" t="inlineStr">
+      <c r="C11" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1863,17 +1872,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="109" t="inlineStr">
+      <c r="A12" s="112" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="109" t="inlineStr">
+      <c r="B12" s="112" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="109" t="inlineStr">
+      <c r="C12" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1881,17 +1890,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="109" t="inlineStr">
+      <c r="A13" s="112" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="109" t="inlineStr">
+      <c r="B13" s="112" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="109" t="inlineStr">
+      <c r="C13" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1903,17 +1912,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="109" t="inlineStr">
+      <c r="A14" s="112" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="109" t="inlineStr">
+      <c r="B14" s="112" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="109" t="inlineStr">
+      <c r="C14" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1925,17 +1934,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="109" t="inlineStr">
+      <c r="A15" s="112" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="109" t="inlineStr">
+      <c r="B15" s="112" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="109" t="inlineStr">
+      <c r="C15" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1947,17 +1956,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="109" t="inlineStr">
+      <c r="A16" s="112" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="109" t="inlineStr">
+      <c r="B16" s="112" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="109" t="inlineStr">
+      <c r="C16" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1969,17 +1978,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="109" t="inlineStr">
+      <c r="A17" s="112" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="109" t="inlineStr">
+      <c r="B17" s="112" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="109" t="inlineStr">
+      <c r="C17" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1991,17 +2000,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="109" t="inlineStr">
+      <c r="A18" s="112" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="109" t="inlineStr">
+      <c r="B18" s="112" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="109" t="inlineStr">
+      <c r="C18" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2013,17 +2022,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="109" t="inlineStr">
+      <c r="A19" s="112" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="109" t="inlineStr">
+      <c r="B19" s="112" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="109" t="inlineStr">
+      <c r="C19" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2031,17 +2040,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="109" t="inlineStr">
+      <c r="A20" s="112" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="109" t="inlineStr">
+      <c r="B20" s="112" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="109" t="inlineStr">
+      <c r="C20" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2049,17 +2058,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="109" t="inlineStr">
+      <c r="A21" s="112" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="109" t="inlineStr">
+      <c r="B21" s="112" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="109" t="inlineStr">
+      <c r="C21" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2071,17 +2080,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="109" t="inlineStr">
+      <c r="A22" s="112" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="109" t="inlineStr">
+      <c r="B22" s="112" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="109" t="inlineStr">
+      <c r="C22" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2093,17 +2102,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="109" t="inlineStr">
+      <c r="A23" s="112" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="109" t="inlineStr">
+      <c r="B23" s="112" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="109" t="inlineStr">
+      <c r="C23" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2115,17 +2124,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="109" t="inlineStr">
+      <c r="A24" s="112" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="109" t="inlineStr">
+      <c r="B24" s="112" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="109" t="inlineStr">
+      <c r="C24" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2137,17 +2146,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="109" t="inlineStr">
+      <c r="A25" s="112" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="109" t="inlineStr">
+      <c r="B25" s="112" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="109" t="inlineStr">
+      <c r="C25" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2155,17 +2164,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="109" t="inlineStr">
+      <c r="A26" s="112" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="109" t="inlineStr">
+      <c r="B26" s="112" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="109" t="inlineStr">
+      <c r="C26" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2173,17 +2182,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="109" t="inlineStr">
+      <c r="A27" s="112" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="109" t="inlineStr">
+      <c r="B27" s="112" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="109" t="inlineStr">
+      <c r="C27" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2195,17 +2204,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="109" t="inlineStr">
+      <c r="A28" s="112" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="109" t="inlineStr">
+      <c r="B28" s="112" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="109" t="inlineStr">
+      <c r="C28" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2217,17 +2226,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="109" t="inlineStr">
+      <c r="A29" s="112" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="109" t="inlineStr">
+      <c r="B29" s="112" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="109" t="inlineStr">
+      <c r="C29" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2239,17 +2248,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="109" t="inlineStr">
+      <c r="A30" s="112" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="109" t="inlineStr">
+      <c r="B30" s="112" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="109" t="inlineStr">
+      <c r="C30" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2257,17 +2266,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="109" t="inlineStr">
+      <c r="A31" s="112" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="109" t="inlineStr">
+      <c r="B31" s="112" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="109" t="inlineStr">
+      <c r="C31" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2279,17 +2288,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="109" t="inlineStr">
+      <c r="A32" s="112" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="109" t="inlineStr">
+      <c r="B32" s="112" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="109" t="inlineStr">
+      <c r="C32" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2297,17 +2306,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="109" t="inlineStr">
+      <c r="A33" s="112" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="109" t="inlineStr">
+      <c r="B33" s="112" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="109" t="inlineStr">
+      <c r="C33" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2315,17 +2324,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="109" t="inlineStr">
+      <c r="A34" s="112" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="109" t="inlineStr">
+      <c r="B34" s="112" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="109" t="inlineStr">
+      <c r="C34" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2333,17 +2342,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="109" t="inlineStr">
+      <c r="A35" s="112" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="109" t="inlineStr">
+      <c r="B35" s="112" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="109" t="inlineStr">
+      <c r="C35" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2351,17 +2360,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="109" t="inlineStr">
+      <c r="A36" s="112" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="109" t="inlineStr">
+      <c r="B36" s="112" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="109" t="inlineStr">
+      <c r="C36" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2369,17 +2378,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="109" t="inlineStr">
+      <c r="A37" s="112" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="109" t="inlineStr">
+      <c r="B37" s="112" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="109" t="inlineStr">
+      <c r="C37" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2387,17 +2396,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="109" t="inlineStr">
+      <c r="A38" s="112" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="109" t="inlineStr">
+      <c r="B38" s="112" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="109" t="inlineStr">
+      <c r="C38" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2405,17 +2414,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="109" t="inlineStr">
+      <c r="A39" s="112" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="109" t="inlineStr">
+      <c r="B39" s="112" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="109" t="inlineStr">
+      <c r="C39" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2423,17 +2432,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="109" t="inlineStr">
+      <c r="A40" s="112" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="109" t="inlineStr">
+      <c r="B40" s="112" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is>
       </c>
-      <c r="C40" s="109" t="inlineStr">
+      <c r="C40" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2445,17 +2454,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="109" t="inlineStr">
+      <c r="A41" s="112" t="inlineStr">
         <is>
           <t>当村</t>
         </is>
       </c>
-      <c r="B41" s="109" t="inlineStr">
+      <c r="B41" s="112" t="inlineStr">
         <is>
           <t>トウソン</t>
         </is>
       </c>
-      <c r="C41" s="109" t="inlineStr">
+      <c r="C41" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2463,17 +2472,17 @@
       <c r="D41" s="46" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="109" t="inlineStr">
+      <c r="A42" s="112" t="inlineStr">
         <is>
           <t>窓口机上</t>
         </is>
       </c>
-      <c r="B42" s="109" t="inlineStr">
+      <c r="B42" s="112" t="inlineStr">
         <is>
           <t>マドグチノツクエノウエ</t>
         </is>
       </c>
-      <c r="C42" s="109" t="inlineStr">
+      <c r="C42" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2485,17 +2494,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="109" t="inlineStr">
+      <c r="A43" s="112" t="inlineStr">
         <is>
           <t>拾得物</t>
         </is>
       </c>
-      <c r="B43" s="109" t="inlineStr">
+      <c r="B43" s="112" t="inlineStr">
         <is>
           <t>シュウトクブツ</t>
         </is>
       </c>
-      <c r="C43" s="109" t="inlineStr">
+      <c r="C43" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2503,17 +2512,17 @@
       <c r="D43" s="46" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="109" t="inlineStr">
+      <c r="A44" s="112" t="inlineStr">
         <is>
           <t>紙巻</t>
         </is>
       </c>
-      <c r="B44" s="109" t="inlineStr">
+      <c r="B44" s="112" t="inlineStr">
         <is>
           <t>カミマキ</t>
         </is>
       </c>
-      <c r="C44" s="109" t="inlineStr">
+      <c r="C44" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2525,17 +2534,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="109" t="inlineStr">
+      <c r="A45" s="112" t="inlineStr">
         <is>
           <t>加熱式</t>
         </is>
       </c>
-      <c r="B45" s="109" t="inlineStr">
+      <c r="B45" s="112" t="inlineStr">
         <is>
           <t>カネツシキ</t>
         </is>
       </c>
-      <c r="C45" s="109" t="inlineStr">
+      <c r="C45" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2884,17 +2893,17 @@
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="108" t="inlineStr">
+      <c r="A6" s="111" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B6" s="108" t="inlineStr">
+      <c r="B6" s="111" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C6" s="108" t="inlineStr">
+      <c r="C6" s="111" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2919,49 +2928,49 @@
           <t>海外で発行されたカードは、郵便局のATMのみご利用いただけます。この建物を出て右へ、歩いて20分ほどの場所にございます。日本で発行されたカードは、JAのATMをご利用いただけます。この建物を出て左へ、歩いて2分ほどの場所にございます。</t>
         </is>
       </c>
-      <c r="G6" s="108" t="n"/>
-      <c r="H6" s="108" t="n"/>
-      <c r="I6" s="108" t="inlineStr">
+      <c r="G6" s="111" t="n"/>
+      <c r="H6" s="111" t="n"/>
+      <c r="I6" s="111" t="inlineStr">
         <is>
           <t>atm_bt.mp3</t>
         </is>
       </c>
-      <c r="J6" s="108" t="inlineStr">
+      <c r="J6" s="111" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K6" s="108" t="n"/>
-      <c r="L6" s="108" t="n"/>
-      <c r="M6" s="108" t="inlineStr">
+      <c r="K6" s="111" t="n"/>
+      <c r="L6" s="111" t="n"/>
+      <c r="M6" s="111" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N6" s="109" t="inlineStr">
+      <c r="N6" s="112" t="inlineStr">
         <is>
           <t>ATMはどこ</t>
         </is>
       </c>
-      <c r="O6" s="109" t="n"/>
-      <c r="P6" s="109" t="inlineStr">
+      <c r="O6" s="112" t="n"/>
+      <c r="P6" s="112" t="inlineStr">
         <is>
           <t>2026-10-13 17:14</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="108" t="inlineStr">
+      <c r="A7" s="111" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B7" s="108" t="inlineStr">
+      <c r="B7" s="111" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C7" s="108" t="inlineStr">
+      <c r="C7" s="111" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -2986,28 +2995,28 @@
           <t>海外のカードは鳩谷郵便局のATM、日本のカードは和田家前のJAのATMをご利用ください。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G7" s="108" t="n"/>
-      <c r="H7" s="108" t="n"/>
-      <c r="I7" s="108" t="inlineStr">
+      <c r="G7" s="111" t="n"/>
+      <c r="H7" s="111" t="n"/>
+      <c r="I7" s="111" t="inlineStr">
         <is>
           <t>atm_deai.mp3</t>
         </is>
       </c>
-      <c r="J7" s="108" t="inlineStr">
+      <c r="J7" s="111" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K7" s="108" t="n"/>
-      <c r="L7" s="108" t="n"/>
-      <c r="M7" s="108" t="inlineStr">
+      <c r="K7" s="111" t="n"/>
+      <c r="L7" s="111" t="n"/>
+      <c r="M7" s="111" t="inlineStr">
         <is>
           <t>atm</t>
         </is>
       </c>
-      <c r="N7" s="109" t="n"/>
-      <c r="O7" s="109" t="n"/>
-      <c r="P7" s="109" t="inlineStr">
+      <c r="N7" s="112" t="n"/>
+      <c r="O7" s="112" t="n"/>
+      <c r="P7" s="112" t="inlineStr">
         <is>
           <t>2026-10-13 17:15</t>
         </is>
@@ -3063,17 +3072,17 @@
       </c>
     </row>
     <row r="9" ht="58.05" customHeight="1">
-      <c r="A9" s="108" t="inlineStr">
+      <c r="A9" s="111" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B9" s="108" t="inlineStr">
+      <c r="B9" s="111" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C9" s="108" t="inlineStr">
+      <c r="C9" s="111" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3093,45 +3102,45 @@
         </is>
       </c>
       <c r="F9" s="44" t="n"/>
-      <c r="G9" s="108" t="n"/>
-      <c r="H9" s="108" t="n"/>
-      <c r="I9" s="108" t="inlineStr">
+      <c r="G9" s="111" t="n"/>
+      <c r="H9" s="111" t="n"/>
+      <c r="I9" s="111" t="inlineStr">
         <is>
           <t>currency_exchange_bt.mp3</t>
         </is>
       </c>
-      <c r="J9" s="108" t="inlineStr">
+      <c r="J9" s="111" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K9" s="108" t="n"/>
-      <c r="L9" s="108" t="n"/>
-      <c r="M9" s="108" t="inlineStr">
+      <c r="K9" s="111" t="n"/>
+      <c r="L9" s="111" t="n"/>
+      <c r="M9" s="111" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N9" s="109" t="n"/>
-      <c r="O9" s="109" t="n"/>
-      <c r="P9" s="109" t="inlineStr">
+      <c r="N9" s="112" t="n"/>
+      <c r="O9" s="112" t="n"/>
+      <c r="P9" s="112" t="inlineStr">
         <is>
           <t>2026-10-13 17:18</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58.05" customHeight="1">
-      <c r="A10" s="108" t="inlineStr">
+      <c r="A10" s="111" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B10" s="108" t="inlineStr">
+      <c r="B10" s="111" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C10" s="108" t="inlineStr">
+      <c r="C10" s="111" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3151,45 +3160,45 @@
         </is>
       </c>
       <c r="F10" s="44" t="n"/>
-      <c r="G10" s="108" t="n"/>
-      <c r="H10" s="108" t="n"/>
-      <c r="I10" s="108" t="inlineStr">
+      <c r="G10" s="111" t="n"/>
+      <c r="H10" s="111" t="n"/>
+      <c r="I10" s="111" t="inlineStr">
         <is>
           <t>currency_exchange_deai.mp3</t>
         </is>
       </c>
-      <c r="J10" s="108" t="inlineStr">
+      <c r="J10" s="111" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K10" s="108" t="n"/>
-      <c r="L10" s="108" t="n"/>
-      <c r="M10" s="108" t="inlineStr">
+      <c r="K10" s="111" t="n"/>
+      <c r="L10" s="111" t="n"/>
+      <c r="M10" s="111" t="inlineStr">
         <is>
           <t>currency_exchange</t>
         </is>
       </c>
-      <c r="N10" s="109" t="n"/>
-      <c r="O10" s="109" t="n"/>
-      <c r="P10" s="109" t="inlineStr">
+      <c r="N10" s="112" t="n"/>
+      <c r="O10" s="112" t="n"/>
+      <c r="P10" s="112" t="inlineStr">
         <is>
           <t>2026-10-13 17:19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58.05" customHeight="1">
-      <c r="A11" s="108" t="inlineStr">
+      <c r="A11" s="111" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B11" s="108" t="inlineStr">
+      <c r="B11" s="111" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C11" s="108" t="inlineStr">
+      <c r="C11" s="111" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3210,49 +3219,49 @@
         </is>
       </c>
       <c r="F11" s="44" t="n"/>
-      <c r="G11" s="108" t="n"/>
-      <c r="H11" s="108" t="n"/>
-      <c r="I11" s="108" t="inlineStr">
+      <c r="G11" s="111" t="n"/>
+      <c r="H11" s="111" t="n"/>
+      <c r="I11" s="111" t="inlineStr">
         <is>
           <t>luggage_bt.mp3</t>
         </is>
       </c>
-      <c r="J11" s="108" t="inlineStr">
+      <c r="J11" s="111" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K11" s="108" t="n"/>
-      <c r="L11" s="108" t="n"/>
-      <c r="M11" s="108" t="inlineStr">
+      <c r="K11" s="111" t="n"/>
+      <c r="L11" s="111" t="n"/>
+      <c r="M11" s="111" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N11" s="109" t="inlineStr">
+      <c r="N11" s="112" t="inlineStr">
         <is>
           <t>荷物を預けたい</t>
         </is>
       </c>
-      <c r="O11" s="109" t="n"/>
-      <c r="P11" s="109" t="inlineStr">
+      <c r="O11" s="112" t="n"/>
+      <c r="P11" s="112" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58.05" customHeight="1">
-      <c r="A12" s="108" t="inlineStr">
+      <c r="A12" s="111" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B12" s="108" t="inlineStr">
+      <c r="B12" s="111" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C12" s="108" t="inlineStr">
+      <c r="C12" s="111" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3273,28 +3282,28 @@
         </is>
       </c>
       <c r="F12" s="44" t="n"/>
-      <c r="G12" s="108" t="n"/>
-      <c r="H12" s="108" t="n"/>
-      <c r="I12" s="108" t="inlineStr">
+      <c r="G12" s="111" t="n"/>
+      <c r="H12" s="111" t="n"/>
+      <c r="I12" s="111" t="inlineStr">
         <is>
           <t>luggage_deai.mp3</t>
         </is>
       </c>
-      <c r="J12" s="108" t="inlineStr">
+      <c r="J12" s="111" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K12" s="108" t="n"/>
-      <c r="L12" s="108" t="n"/>
-      <c r="M12" s="108" t="inlineStr">
+      <c r="K12" s="111" t="n"/>
+      <c r="L12" s="111" t="n"/>
+      <c r="M12" s="111" t="inlineStr">
         <is>
           <t>luggage</t>
         </is>
       </c>
-      <c r="N12" s="109" t="n"/>
-      <c r="O12" s="109" t="n"/>
-      <c r="P12" s="109" t="inlineStr">
+      <c r="N12" s="112" t="n"/>
+      <c r="O12" s="112" t="n"/>
+      <c r="P12" s="112" t="inlineStr">
         <is>
           <t>2026-10-13 17:21</t>
         </is>
@@ -3357,17 +3366,17 @@
       </c>
     </row>
     <row r="14" ht="58.05" customHeight="1">
-      <c r="A14" s="108" t="inlineStr">
+      <c r="A14" s="111" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B14" s="108" t="inlineStr">
+      <c r="B14" s="111" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C14" s="108" t="inlineStr">
+      <c r="C14" s="111" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3387,45 +3396,45 @@
         </is>
       </c>
       <c r="F14" s="44" t="n"/>
-      <c r="G14" s="108" t="n"/>
-      <c r="H14" s="108" t="n"/>
-      <c r="I14" s="108" t="inlineStr">
+      <c r="G14" s="111" t="n"/>
+      <c r="H14" s="111" t="n"/>
+      <c r="I14" s="111" t="inlineStr">
         <is>
           <t>stamp_bt.mp3</t>
         </is>
       </c>
-      <c r="J14" s="108" t="inlineStr">
+      <c r="J14" s="111" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K14" s="108" t="n"/>
-      <c r="L14" s="108" t="n"/>
-      <c r="M14" s="108" t="inlineStr">
+      <c r="K14" s="111" t="n"/>
+      <c r="L14" s="111" t="n"/>
+      <c r="M14" s="111" t="inlineStr">
         <is>
           <t>stamp</t>
         </is>
       </c>
-      <c r="N14" s="109" t="n"/>
-      <c r="O14" s="109" t="n"/>
-      <c r="P14" s="109" t="inlineStr">
+      <c r="N14" s="112" t="n"/>
+      <c r="O14" s="112" t="n"/>
+      <c r="P14" s="112" t="inlineStr">
         <is>
           <t>2026-10-13 17:22</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58.05" customHeight="1">
-      <c r="A15" s="108" t="inlineStr">
+      <c r="A15" s="111" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B15" s="108" t="inlineStr">
+      <c r="B15" s="111" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C15" s="108" t="inlineStr">
+      <c r="C15" s="111" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
@@ -3445,28 +3454,28 @@
         </is>
       </c>
       <c r="F15" s="44" t="n"/>
-      <c r="G15" s="108" t="n"/>
-      <c r="H15" s="108" t="n"/>
-      <c r="I15" s="108" t="inlineStr">
+      <c r="G15" s="111" t="n"/>
+      <c r="H15" s="111" t="n"/>
+      <c r="I15" s="111" t="inlineStr">
         <is>
           <t>stamp_deai.mp3</t>
         </is>
       </c>
-      <c r="J15" s="108" t="inlineStr">
+      <c r="J15" s="111" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K15" s="108" t="n"/>
-      <c r="L15" s="108" t="n"/>
-      <c r="M15" s="108" t="inlineStr">
+      <c r="K15" s="111" t="n"/>
+      <c r="L15" s="111" t="n"/>
+      <c r="M15" s="111" t="inlineStr">
         <is>
           <t>stamp</t>
         </is>
       </c>
-      <c r="N15" s="109" t="n"/>
-      <c r="O15" s="109" t="n"/>
-      <c r="P15" s="109" t="inlineStr">
+      <c r="N15" s="112" t="n"/>
+      <c r="O15" s="112" t="n"/>
+      <c r="P15" s="112" t="inlineStr">
         <is>
           <t>2026-10-13 17:23</t>
         </is>
@@ -3586,17 +3595,17 @@
       </c>
     </row>
     <row r="18" ht="58.05" customHeight="1">
-      <c r="A18" s="108" t="inlineStr">
+      <c r="A18" s="111" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B18" s="108" t="inlineStr">
+      <c r="B18" s="111" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C18" s="108" t="inlineStr">
+      <c r="C18" s="111" t="inlineStr">
         <is>
           <t>sightseeing</t>
         </is>
@@ -3621,49 +3630,49 @@
           <t>展望台へは、自家用車で行くことはできません。歩いておよそ15分、またはシャトルバスでお越しいただけます。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G18" s="108" t="n"/>
-      <c r="H18" s="108" t="n"/>
-      <c r="I18" s="108" t="inlineStr">
+      <c r="G18" s="111" t="n"/>
+      <c r="H18" s="111" t="n"/>
+      <c r="I18" s="111" t="inlineStr">
         <is>
           <t>observatory_access_bt.mp3</t>
         </is>
       </c>
-      <c r="J18" s="108" t="inlineStr">
+      <c r="J18" s="111" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K18" s="108" t="n"/>
-      <c r="L18" s="108" t="n"/>
-      <c r="M18" s="108" t="inlineStr">
+      <c r="K18" s="111" t="n"/>
+      <c r="L18" s="111" t="n"/>
+      <c r="M18" s="111" t="inlineStr">
         <is>
           <t>observatory_access</t>
         </is>
       </c>
-      <c r="N18" s="109" t="inlineStr">
+      <c r="N18" s="112" t="inlineStr">
         <is>
           <t>展望台への行き方</t>
         </is>
       </c>
-      <c r="O18" s="109" t="n"/>
-      <c r="P18" s="109" t="inlineStr">
+      <c r="O18" s="112" t="n"/>
+      <c r="P18" s="112" t="inlineStr">
         <is>
           <t>2026-10-13 17:26</t>
         </is>
       </c>
     </row>
     <row r="19" ht="79.2" customHeight="1">
-      <c r="A19" s="108" t="inlineStr">
+      <c r="A19" s="111" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B19" s="108" t="inlineStr">
+      <c r="B19" s="111" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C19" s="108" t="inlineStr">
+      <c r="C19" s="111" t="inlineStr">
         <is>
           <t>sightseeing</t>
         </is>
@@ -3687,28 +3696,28 @@
           <t>展望台へは、目の前の橋を渡り、大通りを左へ10分ほど進んだ池の前のバス停から、シャトルバスが出ています。遊歩道もございます。詳しくは画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G19" s="108" t="n"/>
-      <c r="H19" s="108" t="n"/>
-      <c r="I19" s="108" t="inlineStr">
+      <c r="G19" s="111" t="n"/>
+      <c r="H19" s="111" t="n"/>
+      <c r="I19" s="111" t="inlineStr">
         <is>
           <t>observatory_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J19" s="108" t="inlineStr">
+      <c r="J19" s="111" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K19" s="108" t="n"/>
-      <c r="L19" s="108" t="n"/>
-      <c r="M19" s="108" t="inlineStr">
+      <c r="K19" s="111" t="n"/>
+      <c r="L19" s="111" t="n"/>
+      <c r="M19" s="111" t="inlineStr">
         <is>
           <t>observatory_access</t>
         </is>
       </c>
-      <c r="N19" s="109" t="n"/>
-      <c r="O19" s="109" t="n"/>
-      <c r="P19" s="109" t="inlineStr">
+      <c r="N19" s="112" t="n"/>
+      <c r="O19" s="112" t="n"/>
+      <c r="P19" s="112" t="inlineStr">
         <is>
           <t>2026-10-13 17:27</t>
         </is>
@@ -3774,17 +3783,17 @@
       </c>
     </row>
     <row r="21" ht="66" customHeight="1">
-      <c r="A21" s="108" t="inlineStr">
+      <c r="A21" s="111" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="B21" s="108" t="inlineStr">
+      <c r="B21" s="111" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C21" s="108" t="inlineStr">
+      <c r="C21" s="111" t="inlineStr">
         <is>
           <t>sightseeing</t>
         </is>
@@ -3805,32 +3814,32 @@
         </is>
       </c>
       <c r="F21" s="44" t="n"/>
-      <c r="G21" s="108" t="n"/>
-      <c r="H21" s="108" t="inlineStr">
+      <c r="G21" s="111" t="n"/>
+      <c r="H21" s="111" t="inlineStr">
         <is>
           <t>https://shirakawa-going.jp/</t>
         </is>
       </c>
-      <c r="I21" s="108" t="inlineStr">
+      <c r="I21" s="111" t="inlineStr">
         <is>
           <t>waterfall_lake.mp3</t>
         </is>
       </c>
-      <c r="J21" s="108" t="inlineStr">
+      <c r="J21" s="111" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K21" s="108" t="n"/>
-      <c r="L21" s="108" t="n"/>
-      <c r="M21" s="108" t="inlineStr">
+      <c r="K21" s="111" t="n"/>
+      <c r="L21" s="111" t="n"/>
+      <c r="M21" s="111" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="N21" s="109" t="n"/>
-      <c r="O21" s="109" t="n"/>
-      <c r="P21" s="109" t="inlineStr">
+      <c r="N21" s="112" t="n"/>
+      <c r="O21" s="112" t="n"/>
+      <c r="P21" s="112" t="inlineStr">
         <is>
           <t>2026-10-13 17:30</t>
         </is>
@@ -4864,17 +4873,17 @@
       </c>
     </row>
     <row r="40" ht="66" customHeight="1">
-      <c r="A40" s="108" t="inlineStr">
+      <c r="A40" s="111" t="inlineStr">
         <is>
           <t>festival_shrine_access_bt</t>
         </is>
       </c>
-      <c r="B40" s="108" t="inlineStr">
+      <c r="B40" s="111" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
       </c>
-      <c r="C40" s="108" t="inlineStr">
+      <c r="C40" s="111" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -4893,28 +4902,28 @@
         </is>
       </c>
       <c r="F40" s="44" t="n"/>
-      <c r="G40" s="108" t="n"/>
-      <c r="H40" s="108" t="n"/>
-      <c r="I40" s="108" t="inlineStr">
+      <c r="G40" s="111" t="n"/>
+      <c r="H40" s="111" t="n"/>
+      <c r="I40" s="111" t="inlineStr">
         <is>
           <t>festival_shrine_access_bt.mp3</t>
         </is>
       </c>
-      <c r="J40" s="108" t="inlineStr">
+      <c r="J40" s="111" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K40" s="108" t="n"/>
-      <c r="L40" s="108" t="n"/>
-      <c r="M40" s="108" t="inlineStr">
+      <c r="K40" s="111" t="n"/>
+      <c r="L40" s="111" t="n"/>
+      <c r="M40" s="111" t="inlineStr">
         <is>
           <t>festival_shrine_access</t>
         </is>
       </c>
-      <c r="N40" s="109" t="n"/>
-      <c r="O40" s="109" t="n"/>
-      <c r="P40" s="109" t="inlineStr">
+      <c r="N40" s="112" t="n"/>
+      <c r="O40" s="112" t="n"/>
+      <c r="P40" s="112" t="inlineStr">
         <is>
           <t>2026-10-13 17:30</t>
         </is>
@@ -5047,17 +5056,17 @@
       </c>
     </row>
     <row r="43" ht="249.6" customHeight="1">
-      <c r="A43" s="108" t="inlineStr">
+      <c r="A43" s="111" t="inlineStr">
         <is>
           <t>guesthouse_access_deai</t>
         </is>
       </c>
-      <c r="B43" s="108" t="inlineStr">
+      <c r="B43" s="111" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
       </c>
-      <c r="C43" s="108" t="inlineStr">
+      <c r="C43" s="111" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -5091,30 +5100,30 @@
           <t>その建物は鳩谷八幡神社方面にあります。国道は交通量が多いため、川沿いの道をおすすめしております。詳しい道順は画面をご覧ください。</t>
         </is>
       </c>
-      <c r="G43" s="108" t="inlineStr">
+      <c r="G43" s="111" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H43" s="108" t="n"/>
-      <c r="I43" s="108" t="inlineStr">
+      <c r="H43" s="111" t="n"/>
+      <c r="I43" s="111" t="inlineStr">
         <is>
           <t>guesthouse_access_deai.mp3</t>
         </is>
       </c>
-      <c r="J43" s="108" t="inlineStr">
+      <c r="J43" s="111" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K43" s="108" t="n"/>
-      <c r="L43" s="108" t="n"/>
-      <c r="M43" s="108" t="inlineStr">
+      <c r="K43" s="111" t="n"/>
+      <c r="L43" s="111" t="n"/>
+      <c r="M43" s="111" t="inlineStr">
         <is>
           <t>guesthouse_access</t>
         </is>
       </c>
-      <c r="N43" s="109" t="n"/>
+      <c r="N43" s="112" t="n"/>
     </row>
     <row r="44" ht="79.2" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -5552,57 +5561,64 @@
       </c>
     </row>
     <row r="52" ht="66" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="115" t="inlineStr">
         <is>
           <t>gassho_facilities</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B52" s="115" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C52" s="115" t="inlineStr">
         <is>
           <t>sightseeing</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D52" s="44" t="inlineStr">
         <is>
           <t>合掌造り 見学
 見学施設
-中 入れる
 入館料
-見学 料金</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。</t>
-        </is>
-      </c>
-      <c r="F52" s="15" t="n"/>
-      <c r="G52" s="11" t="n"/>
-      <c r="H52" s="11" t="inlineStr">
+見学 料金
+見学施設 入れる</t>
+        </is>
+      </c>
+      <c r="E52" s="44" t="inlineStr">
+        <is>
+          <t>合掌造りの見学施設は、各施設おひとり大人400円、民家園のみおひとり800円となります。</t>
+        </is>
+      </c>
+      <c r="F52" s="44" t="n"/>
+      <c r="G52" s="115" t="n"/>
+      <c r="H52" s="115" t="inlineStr">
         <is>
           <t>https://shirakawa-go.gr.jp/active/</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr">
+      <c r="I52" s="115" t="inlineStr">
         <is>
           <t>gassho_facilities.mp3</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr">
+      <c r="J52" s="115" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K52" s="11" t="n"/>
-      <c r="L52" s="11" t="n"/>
-      <c r="M52" s="14" t="inlineStr">
+      <c r="K52" s="115" t="n"/>
+      <c r="L52" s="115" t="n"/>
+      <c r="M52" s="115" t="inlineStr">
         <is>
           <t>gassho_facilities</t>
+        </is>
+      </c>
+      <c r="N52" s="116" t="n"/>
+      <c r="O52" s="116" t="n"/>
+      <c r="P52" s="116" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:32</t>
         </is>
       </c>
     </row>
@@ -6303,17 +6319,17 @@
       </c>
     </row>
     <row r="66" ht="259.2" customHeight="1">
-      <c r="A66" s="109" t="inlineStr">
+      <c r="A66" s="112" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B66" s="109" t="inlineStr">
+      <c r="B66" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C66" s="109" t="inlineStr">
+      <c r="C66" s="112" t="inlineStr">
         <is>
           <t>other</t>
         </is>
@@ -6343,26 +6359,26 @@
         </is>
       </c>
       <c r="F66" s="46" t="n"/>
-      <c r="G66" s="109" t="inlineStr">
+      <c r="G66" s="112" t="inlineStr">
         <is>
           <t>guesthouse_route.jpg</t>
         </is>
       </c>
-      <c r="H66" s="109" t="n"/>
-      <c r="I66" s="109" t="inlineStr">
+      <c r="H66" s="112" t="n"/>
+      <c r="I66" s="112" t="inlineStr">
         <is>
           <t>guesthouse_access_common.mp3</t>
         </is>
       </c>
-      <c r="J66" s="109" t="inlineStr">
+      <c r="J66" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K66" s="109" t="n"/>
-      <c r="L66" s="109" t="n"/>
-      <c r="M66" s="109" t="n"/>
-      <c r="N66" s="109" t="n"/>
+      <c r="K66" s="112" t="n"/>
+      <c r="L66" s="112" t="n"/>
+      <c r="M66" s="112" t="n"/>
+      <c r="N66" s="112" t="n"/>
       <c r="O66" s="49" t="inlineStr">
         <is>
           <t>※要確認（自動作成の下書き）</t>
@@ -7571,12 +7587,12 @@
       </c>
     </row>
     <row r="22" ht="64.8" customHeight="1">
-      <c r="A22" s="109" t="inlineStr">
+      <c r="A22" s="112" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B22" s="109" t="inlineStr">
+      <c r="B22" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7607,12 +7623,12 @@
       </c>
     </row>
     <row r="23" ht="81" customHeight="1">
-      <c r="A23" s="109" t="inlineStr">
+      <c r="A23" s="112" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B23" s="109" t="inlineStr">
+      <c r="B23" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7643,12 +7659,12 @@
       </c>
     </row>
     <row r="24" ht="81" customHeight="1">
-      <c r="A24" s="109" t="inlineStr">
+      <c r="A24" s="112" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B24" s="109" t="inlineStr">
+      <c r="B24" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7679,12 +7695,12 @@
       </c>
     </row>
     <row r="25" ht="81" customHeight="1">
-      <c r="A25" s="109" t="inlineStr">
+      <c r="A25" s="112" t="inlineStr">
         <is>
           <t>atm_bt</t>
         </is>
       </c>
-      <c r="B25" s="109" t="inlineStr">
+      <c r="B25" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7751,12 +7767,12 @@
       </c>
     </row>
     <row r="27" ht="64.8" customHeight="1">
-      <c r="A27" s="106" t="inlineStr">
+      <c r="A27" s="113" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B27" s="106" t="inlineStr">
+      <c r="B27" s="113" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -7787,12 +7803,12 @@
       </c>
     </row>
     <row r="28" ht="64.8" customHeight="1">
-      <c r="A28" s="106" t="inlineStr">
+      <c r="A28" s="113" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B28" s="106" t="inlineStr">
+      <c r="B28" s="113" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -7823,12 +7839,12 @@
       </c>
     </row>
     <row r="29" ht="64.8" customHeight="1">
-      <c r="A29" s="106" t="inlineStr">
+      <c r="A29" s="113" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B29" s="106" t="inlineStr">
+      <c r="B29" s="113" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -7859,12 +7875,12 @@
       </c>
     </row>
     <row r="30" ht="81" customHeight="1">
-      <c r="A30" s="106" t="inlineStr">
+      <c r="A30" s="113" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B30" s="106" t="inlineStr">
+      <c r="B30" s="113" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -7895,12 +7911,12 @@
       </c>
     </row>
     <row r="31" ht="64.8" customHeight="1">
-      <c r="A31" s="107" t="inlineStr">
+      <c r="A31" s="114" t="inlineStr">
         <is>
           <t>atm_deai</t>
         </is>
       </c>
-      <c r="B31" s="107" t="inlineStr">
+      <c r="B31" s="114" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8092,12 +8108,12 @@
       </c>
     </row>
     <row r="37" ht="64.8" customHeight="1">
-      <c r="A37" s="106" t="inlineStr">
+      <c r="A37" s="113" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B37" s="106" t="inlineStr">
+      <c r="B37" s="113" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8128,12 +8144,12 @@
       </c>
     </row>
     <row r="38" ht="64.8" customHeight="1">
-      <c r="A38" s="106" t="inlineStr">
+      <c r="A38" s="113" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B38" s="106" t="inlineStr">
+      <c r="B38" s="113" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8164,12 +8180,12 @@
       </c>
     </row>
     <row r="39" ht="64.8" customHeight="1">
-      <c r="A39" s="106" t="inlineStr">
+      <c r="A39" s="113" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B39" s="106" t="inlineStr">
+      <c r="B39" s="113" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8200,12 +8216,12 @@
       </c>
     </row>
     <row r="40" ht="113.4" customHeight="1">
-      <c r="A40" s="106" t="inlineStr">
+      <c r="A40" s="113" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B40" s="106" t="inlineStr">
+      <c r="B40" s="113" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8236,12 +8252,12 @@
       </c>
     </row>
     <row r="41" ht="97.2" customHeight="1">
-      <c r="A41" s="107" t="inlineStr">
+      <c r="A41" s="114" t="inlineStr">
         <is>
           <t>currency_exchange_bt</t>
         </is>
       </c>
-      <c r="B41" s="107" t="inlineStr">
+      <c r="B41" s="114" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8272,12 +8288,12 @@
       </c>
     </row>
     <row r="42" ht="64.8" customHeight="1">
-      <c r="A42" s="109" t="inlineStr">
+      <c r="A42" s="112" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B42" s="109" t="inlineStr">
+      <c r="B42" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8308,12 +8324,12 @@
       </c>
     </row>
     <row r="43" ht="64.8" customHeight="1">
-      <c r="A43" s="109" t="inlineStr">
+      <c r="A43" s="112" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B43" s="109" t="inlineStr">
+      <c r="B43" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8344,12 +8360,12 @@
       </c>
     </row>
     <row r="44" ht="81" customHeight="1">
-      <c r="A44" s="109" t="inlineStr">
+      <c r="A44" s="112" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B44" s="109" t="inlineStr">
+      <c r="B44" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8380,12 +8396,12 @@
       </c>
     </row>
     <row r="45" ht="64.8" customHeight="1">
-      <c r="A45" s="109" t="inlineStr">
+      <c r="A45" s="112" t="inlineStr">
         <is>
           <t>currency_exchange_deai</t>
         </is>
       </c>
-      <c r="B45" s="109" t="inlineStr">
+      <c r="B45" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8452,12 +8468,12 @@
       </c>
     </row>
     <row r="47" ht="81" customHeight="1">
-      <c r="A47" s="106" t="inlineStr">
+      <c r="A47" s="113" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B47" s="106" t="inlineStr">
+      <c r="B47" s="113" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8488,12 +8504,12 @@
       </c>
     </row>
     <row r="48" ht="64.8" customHeight="1">
-      <c r="A48" s="106" t="inlineStr">
+      <c r="A48" s="113" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B48" s="106" t="inlineStr">
+      <c r="B48" s="113" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8524,12 +8540,12 @@
       </c>
     </row>
     <row r="49" ht="64.8" customHeight="1">
-      <c r="A49" s="106" t="inlineStr">
+      <c r="A49" s="113" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B49" s="106" t="inlineStr">
+      <c r="B49" s="113" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8560,12 +8576,12 @@
       </c>
     </row>
     <row r="50" ht="64.8" customHeight="1">
-      <c r="A50" s="106" t="inlineStr">
+      <c r="A50" s="113" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B50" s="106" t="inlineStr">
+      <c r="B50" s="113" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8596,12 +8612,12 @@
       </c>
     </row>
     <row r="51" ht="48.6" customHeight="1">
-      <c r="A51" s="107" t="inlineStr">
+      <c r="A51" s="114" t="inlineStr">
         <is>
           <t>luggage_bt</t>
         </is>
       </c>
-      <c r="B51" s="107" t="inlineStr">
+      <c r="B51" s="114" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -8632,12 +8648,12 @@
       </c>
     </row>
     <row r="52" ht="48.6" customHeight="1">
-      <c r="A52" s="109" t="inlineStr">
+      <c r="A52" s="112" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B52" s="109" t="inlineStr">
+      <c r="B52" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -8668,12 +8684,12 @@
       </c>
     </row>
     <row r="53" ht="97.2" customHeight="1">
-      <c r="A53" s="109" t="inlineStr">
+      <c r="A53" s="112" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B53" s="109" t="inlineStr">
+      <c r="B53" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -8704,12 +8720,12 @@
       </c>
     </row>
     <row r="54" ht="97.2" customHeight="1">
-      <c r="A54" s="109" t="inlineStr">
+      <c r="A54" s="112" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B54" s="109" t="inlineStr">
+      <c r="B54" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -8740,12 +8756,12 @@
       </c>
     </row>
     <row r="55" ht="97.2" customHeight="1">
-      <c r="A55" s="109" t="inlineStr">
+      <c r="A55" s="112" t="inlineStr">
         <is>
           <t>luggage_deai</t>
         </is>
       </c>
-      <c r="B55" s="109" t="inlineStr">
+      <c r="B55" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -8976,12 +8992,12 @@
       </c>
     </row>
     <row r="62" ht="81" customHeight="1">
-      <c r="A62" s="109" t="inlineStr">
+      <c r="A62" s="112" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B62" s="109" t="inlineStr">
+      <c r="B62" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -9012,12 +9028,12 @@
       </c>
     </row>
     <row r="63" ht="97.2" customHeight="1">
-      <c r="A63" s="109" t="inlineStr">
+      <c r="A63" s="112" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B63" s="109" t="inlineStr">
+      <c r="B63" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -9048,12 +9064,12 @@
       </c>
     </row>
     <row r="64" ht="97.2" customHeight="1">
-      <c r="A64" s="109" t="inlineStr">
+      <c r="A64" s="112" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B64" s="109" t="inlineStr">
+      <c r="B64" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -9084,12 +9100,12 @@
       </c>
     </row>
     <row r="65" ht="97.2" customHeight="1">
-      <c r="A65" s="109" t="inlineStr">
+      <c r="A65" s="112" t="inlineStr">
         <is>
           <t>stamp_bt</t>
         </is>
       </c>
-      <c r="B65" s="109" t="inlineStr">
+      <c r="B65" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -9156,12 +9172,12 @@
       </c>
     </row>
     <row r="67" ht="81" customHeight="1">
-      <c r="A67" s="106" t="inlineStr">
+      <c r="A67" s="113" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B67" s="106" t="inlineStr">
+      <c r="B67" s="113" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -9192,12 +9208,12 @@
       </c>
     </row>
     <row r="68" ht="97.2" customHeight="1">
-      <c r="A68" s="106" t="inlineStr">
+      <c r="A68" s="113" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B68" s="106" t="inlineStr">
+      <c r="B68" s="113" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -9228,12 +9244,12 @@
       </c>
     </row>
     <row r="69" ht="97.2" customHeight="1">
-      <c r="A69" s="106" t="inlineStr">
+      <c r="A69" s="113" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B69" s="106" t="inlineStr">
+      <c r="B69" s="113" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -9264,12 +9280,12 @@
       </c>
     </row>
     <row r="70" ht="97.2" customHeight="1">
-      <c r="A70" s="106" t="inlineStr">
+      <c r="A70" s="113" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B70" s="106" t="inlineStr">
+      <c r="B70" s="113" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -9300,12 +9316,12 @@
       </c>
     </row>
     <row r="71" ht="81" customHeight="1">
-      <c r="A71" s="107" t="inlineStr">
+      <c r="A71" s="114" t="inlineStr">
         <is>
           <t>stamp_deai</t>
         </is>
       </c>
-      <c r="B71" s="107" t="inlineStr">
+      <c r="B71" s="114" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -9666,12 +9682,12 @@
       </c>
     </row>
     <row r="82" ht="145.8" customHeight="1">
-      <c r="A82" s="109" t="inlineStr">
+      <c r="A82" s="112" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B82" s="109" t="inlineStr">
+      <c r="B82" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -9703,12 +9719,12 @@
       </c>
     </row>
     <row r="83" ht="145.8" customHeight="1">
-      <c r="A83" s="109" t="inlineStr">
+      <c r="A83" s="112" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B83" s="109" t="inlineStr">
+      <c r="B83" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -9740,12 +9756,12 @@
       </c>
     </row>
     <row r="84" ht="162" customHeight="1">
-      <c r="A84" s="109" t="inlineStr">
+      <c r="A84" s="112" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B84" s="109" t="inlineStr">
+      <c r="B84" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -9777,12 +9793,12 @@
       </c>
     </row>
     <row r="85" ht="145.8" customHeight="1">
-      <c r="A85" s="109" t="inlineStr">
+      <c r="A85" s="112" t="inlineStr">
         <is>
           <t>observatory_access_bt</t>
         </is>
       </c>
-      <c r="B85" s="109" t="inlineStr">
+      <c r="B85" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -9851,12 +9867,12 @@
       </c>
     </row>
     <row r="87" ht="97.2" customHeight="1">
-      <c r="A87" s="106" t="inlineStr">
+      <c r="A87" s="113" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B87" s="106" t="inlineStr">
+      <c r="B87" s="113" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -9887,12 +9903,12 @@
       </c>
     </row>
     <row r="88" ht="97.2" customHeight="1">
-      <c r="A88" s="106" t="inlineStr">
+      <c r="A88" s="113" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B88" s="106" t="inlineStr">
+      <c r="B88" s="113" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -9923,12 +9939,12 @@
       </c>
     </row>
     <row r="89" ht="97.2" customHeight="1">
-      <c r="A89" s="106" t="inlineStr">
+      <c r="A89" s="113" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B89" s="106" t="inlineStr">
+      <c r="B89" s="113" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -9959,12 +9975,12 @@
       </c>
     </row>
     <row r="90" ht="97.2" customHeight="1">
-      <c r="A90" s="106" t="inlineStr">
+      <c r="A90" s="113" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B90" s="106" t="inlineStr">
+      <c r="B90" s="113" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -9995,12 +10011,12 @@
       </c>
     </row>
     <row r="91" ht="97.2" customHeight="1">
-      <c r="A91" s="107" t="inlineStr">
+      <c r="A91" s="114" t="inlineStr">
         <is>
           <t>observatory_access_deai</t>
         </is>
       </c>
-      <c r="B91" s="107" t="inlineStr">
+      <c r="B91" s="114" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -10196,12 +10212,12 @@
       </c>
     </row>
     <row r="97" ht="97.2" customHeight="1">
-      <c r="A97" s="106" t="inlineStr">
+      <c r="A97" s="113" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="B97" s="106" t="inlineStr">
+      <c r="B97" s="113" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -10233,12 +10249,12 @@
       </c>
     </row>
     <row r="98" ht="97.2" customHeight="1">
-      <c r="A98" s="106" t="inlineStr">
+      <c r="A98" s="113" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="B98" s="106" t="inlineStr">
+      <c r="B98" s="113" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -10270,12 +10286,12 @@
       </c>
     </row>
     <row r="99" ht="97.2" customHeight="1">
-      <c r="A99" s="106" t="inlineStr">
+      <c r="A99" s="113" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="B99" s="106" t="inlineStr">
+      <c r="B99" s="113" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -10307,12 +10323,12 @@
       </c>
     </row>
     <row r="100" ht="97.2" customHeight="1">
-      <c r="A100" s="106" t="inlineStr">
+      <c r="A100" s="113" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="B100" s="106" t="inlineStr">
+      <c r="B100" s="113" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -10344,12 +10360,12 @@
       </c>
     </row>
     <row r="101" ht="81" customHeight="1">
-      <c r="A101" s="107" t="inlineStr">
+      <c r="A101" s="114" t="inlineStr">
         <is>
           <t>waterfall_lake</t>
         </is>
       </c>
-      <c r="B101" s="107" t="inlineStr">
+      <c r="B101" s="114" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -13334,12 +13350,12 @@
       </c>
     </row>
     <row r="192" ht="97.2" customHeight="1">
-      <c r="A192" s="109" t="inlineStr">
+      <c r="A192" s="112" t="inlineStr">
         <is>
           <t>festival_shrine_access_bt</t>
         </is>
       </c>
-      <c r="B192" s="109" t="inlineStr">
+      <c r="B192" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -13370,12 +13386,12 @@
       </c>
     </row>
     <row r="193" ht="97.2" customHeight="1">
-      <c r="A193" s="109" t="inlineStr">
+      <c r="A193" s="112" t="inlineStr">
         <is>
           <t>festival_shrine_access_bt</t>
         </is>
       </c>
-      <c r="B193" s="109" t="inlineStr">
+      <c r="B193" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -13406,12 +13422,12 @@
       </c>
     </row>
     <row r="194" ht="97.2" customHeight="1">
-      <c r="A194" s="109" t="inlineStr">
+      <c r="A194" s="112" t="inlineStr">
         <is>
           <t>festival_shrine_access_bt</t>
         </is>
       </c>
-      <c r="B194" s="109" t="inlineStr">
+      <c r="B194" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -13442,12 +13458,12 @@
       </c>
     </row>
     <row r="195" ht="97.2" customHeight="1">
-      <c r="A195" s="109" t="inlineStr">
+      <c r="A195" s="112" t="inlineStr">
         <is>
           <t>festival_shrine_access_bt</t>
         </is>
       </c>
-      <c r="B195" s="109" t="inlineStr">
+      <c r="B195" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -15429,32 +15445,35 @@
       </c>
     </row>
     <row r="252" ht="97.2" customHeight="1">
-      <c r="A252" s="21" t="inlineStr">
+      <c r="A252" s="116" t="inlineStr">
         <is>
           <t>gassho_facilities</t>
         </is>
       </c>
-      <c r="B252" s="21" t="inlineStr">
+      <c r="B252" s="116" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="C252" s="22" t="inlineStr">
-        <is>
-          <t>gassho house visit
-gassho inside
-visit house
-go inside
-entrance fee house
-admission house</t>
-        </is>
-      </c>
-      <c r="D252" s="22" t="inlineStr">
-        <is>
-          <t>Admission to the gassho-style houses open to visitors is 300 yen to 400 yen per person at each facility, except for Gassho-zukuri Minkaen, which is 800 yen per person.</t>
-        </is>
-      </c>
-      <c r="E252" s="21" t="n"/>
+      <c r="C252" s="46" t="inlineStr">
+        <is>
+          <t>gassho tour admission fee
+gassho village entrance price
+how much cost gassho houses
+gassho minkaen admission
+visiting gassho buildings price</t>
+        </is>
+      </c>
+      <c r="D252" s="46" t="inlineStr">
+        <is>
+          <t>The admission fee for each gassho-style house viewing facility is four hundred yen per adult. The Minkaen folk village is eight hundred yen per adult.</t>
+        </is>
+      </c>
+      <c r="E252" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 合掌造りの見学施設は、各施設おひとり大人400円、民家園のみおひとり800円となります。</t>
+        </is>
+      </c>
       <c r="F252" s="23" t="inlineStr">
         <is>
           <t>合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。</t>
@@ -15462,32 +15481,35 @@
       </c>
     </row>
     <row r="253" ht="97.2" customHeight="1">
-      <c r="A253" s="21" t="inlineStr">
+      <c r="A253" s="116" t="inlineStr">
         <is>
           <t>gassho_facilities</t>
         </is>
       </c>
-      <c r="B253" s="21" t="inlineStr">
+      <c r="B253" s="116" t="inlineStr">
         <is>
           <t>es</t>
         </is>
       </c>
-      <c r="C253" s="22" t="inlineStr">
-        <is>
-          <t>gassho visita
-casa gassho
-entrar casa
-casa precio
-museo entrada
-Minkaen</t>
-        </is>
-      </c>
-      <c r="D253" s="22" t="inlineStr">
-        <is>
-          <t>Las casas gassho-zukuri visitables cuestan de 300 a 400 yenes por persona cada una; solo el Gassho-zukuri Minkaen, un museo al aire libre, cuesta 800 yenes por persona.</t>
-        </is>
-      </c>
-      <c r="E253" s="21" t="n"/>
+      <c r="C253" s="46" t="inlineStr">
+        <is>
+          <t>gassho precio entrada
+casas gassho cuánto cuesta
+minkaen tarifa admisión
+costo visita gassho
+entrada gassho village</t>
+        </is>
+      </c>
+      <c r="D253" s="46" t="inlineStr">
+        <is>
+          <t>El precio de entrada para cada instalación de visita de casas gassho es de cuatrocientos yenes por adulto. La aldea folclórica Minkaen es de ochocientos yenes por adulto.</t>
+        </is>
+      </c>
+      <c r="E253" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 合掌造りの見学施設は、各施設おひとり大人400円、民家園のみおひとり800円となります。</t>
+        </is>
+      </c>
       <c r="F253" s="23" t="inlineStr">
         <is>
           <t>合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。</t>
@@ -15495,32 +15517,35 @@
       </c>
     </row>
     <row r="254" ht="97.2" customHeight="1">
-      <c r="A254" s="21" t="inlineStr">
+      <c r="A254" s="116" t="inlineStr">
         <is>
           <t>gassho_facilities</t>
         </is>
       </c>
-      <c r="B254" s="21" t="inlineStr">
+      <c r="B254" s="116" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="C254" s="22" t="inlineStr">
-        <is>
-          <t>maison gassho visite
-visiter gassho
-visiter intérieur
-entrer maison
-tarif maison
-gassho prix</t>
-        </is>
-      </c>
-      <c r="D254" s="22" t="inlineStr">
-        <is>
-          <t>Les maisons gassho ouvertes à la visite coûtent de 300 à 400 yens par personne chacune, sauf le Gassho-zukuri Minkaen, un musée en plein air, qui coûte 800 yens par personne.</t>
-        </is>
-      </c>
-      <c r="E254" s="21" t="n"/>
+      <c r="C254" s="46" t="inlineStr">
+        <is>
+          <t>gassho tarif entrée
+maisons gassho prix visite
+minkaen coût admission
+village gassho tarif
+gassho combien coûte</t>
+        </is>
+      </c>
+      <c r="D254" s="46" t="inlineStr">
+        <is>
+          <t>Le tarif d'entrée pour chaque installation de visite des maisons gassho est de quatre cents yens par adulte. Le village folklorique Minkaen est de huit cents yens par adulte.</t>
+        </is>
+      </c>
+      <c r="E254" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 合掌造りの見学施設は、各施設おひとり大人400円、民家園のみおひとり800円となります。</t>
+        </is>
+      </c>
       <c r="F254" s="23" t="inlineStr">
         <is>
           <t>合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。</t>
@@ -15528,32 +15553,35 @@
       </c>
     </row>
     <row r="255" ht="97.2" customHeight="1">
-      <c r="A255" s="21" t="inlineStr">
+      <c r="A255" s="116" t="inlineStr">
         <is>
           <t>gassho_facilities</t>
         </is>
       </c>
-      <c r="B255" s="21" t="inlineStr">
+      <c r="B255" s="116" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="C255" s="22" t="inlineStr">
-        <is>
-          <t>갓쇼즈쿠리 관람
-관람 시설
-안에 들어가
-입관료
-관람 요금
-갓쇼 내부</t>
-        </is>
-      </c>
-      <c r="D255" s="22" t="inlineStr">
-        <is>
-          <t>갓쇼즈쿠리 관람 시설은 각 시설 1인당 300엔에서 400엔이며, 갓쇼즈쿠리 민카엔만 1인당 800엔입니다.</t>
-        </is>
-      </c>
-      <c r="E255" s="21" t="n"/>
+      <c r="C255" s="46" t="inlineStr">
+        <is>
+          <t>갓쇼조쿠리 관광 입장료
+갓쇼조쿠리 집 입장료
+민카엔 가격
+갓쇼조쿠리 보다 료금
+갓쇼 민가 방문 비용</t>
+        </is>
+      </c>
+      <c r="D255" s="46" t="inlineStr">
+        <is>
+          <t>갓쇼조쿠리 관광 시설 각각의 입장료는 성인 한 명당 사백 엔입니다. 민카엔은 성인 한 명당 팔백 엔입니다.</t>
+        </is>
+      </c>
+      <c r="E255" s="46" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 合掌造りの見学施設は、各施設おひとり大人400円、民家園のみおひとり800円となります。</t>
+        </is>
+      </c>
       <c r="F255" s="23" t="inlineStr">
         <is>
           <t>合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。</t>
@@ -15561,32 +15589,35 @@
       </c>
     </row>
     <row r="256" ht="97.2" customHeight="1">
-      <c r="A256" s="24" t="inlineStr">
+      <c r="A256" s="117" t="inlineStr">
         <is>
           <t>gassho_facilities</t>
         </is>
       </c>
-      <c r="B256" s="24" t="inlineStr">
+      <c r="B256" s="117" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
       </c>
-      <c r="C256" s="25" t="inlineStr">
-        <is>
-          <t>合掌造 参观
-参观 设施
-进去 参观
-合掌屋 门票
-参观 费用
-里面 参观</t>
-        </is>
-      </c>
-      <c r="D256" s="25" t="inlineStr">
-        <is>
-          <t>合掌造参观设施的门票为每处每人300日元至400日元，只有合掌造民家园（露天博物馆）为每人800日元。</t>
-        </is>
-      </c>
-      <c r="E256" s="24" t="n"/>
+      <c r="C256" s="69" t="inlineStr">
+        <is>
+          <t>合掌造 参观 门票
+合掌造房屋 入场费
+民家园 多少钱
+参观合掌村 价格
+合掌建筑 参观费用</t>
+        </is>
+      </c>
+      <c r="D256" s="69" t="inlineStr">
+        <is>
+          <t>合掌造房屋各个参观设施的成人门票价格为每人四百日元。民家园的门票价格为每人八百日元。</t>
+        </is>
+      </c>
+      <c r="E256" s="69" t="inlineStr">
+        <is>
+          <t>自動翻訳（要確認）｜日本語原文: 合掌造りの見学施設は、各施設おひとり大人400円、民家園のみおひとり800円となります。</t>
+        </is>
+      </c>
       <c r="F256" s="26" t="inlineStr">
         <is>
           <t>合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。</t>
@@ -17073,12 +17104,12 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="109" t="inlineStr">
+      <c r="A302" s="112" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B302" s="109" t="inlineStr">
+      <c r="B302" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17104,12 +17135,12 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="109" t="inlineStr">
+      <c r="A303" s="112" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B303" s="109" t="inlineStr">
+      <c r="B303" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17135,12 +17166,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="109" t="inlineStr">
+      <c r="A304" s="112" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B304" s="109" t="inlineStr">
+      <c r="B304" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17166,12 +17197,12 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="109" t="inlineStr">
+      <c r="A305" s="112" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B305" s="109" t="inlineStr">
+      <c r="B305" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17197,12 +17228,12 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="109" t="inlineStr">
+      <c r="A306" s="112" t="inlineStr">
         <is>
           <t>accessible_parking_common</t>
         </is>
       </c>
-      <c r="B306" s="109" t="inlineStr">
+      <c r="B306" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17228,12 +17259,12 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="109" t="inlineStr">
+      <c r="A307" s="112" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B307" s="109" t="inlineStr">
+      <c r="B307" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17259,12 +17290,12 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="109" t="inlineStr">
+      <c r="A308" s="112" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B308" s="109" t="inlineStr">
+      <c r="B308" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17290,12 +17321,12 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="109" t="inlineStr">
+      <c r="A309" s="112" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B309" s="109" t="inlineStr">
+      <c r="B309" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17321,12 +17352,12 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="109" t="inlineStr">
+      <c r="A310" s="112" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B310" s="109" t="inlineStr">
+      <c r="B310" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17352,12 +17383,12 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="109" t="inlineStr">
+      <c r="A311" s="112" t="inlineStr">
         <is>
           <t>atm_common</t>
         </is>
       </c>
-      <c r="B311" s="109" t="inlineStr">
+      <c r="B311" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17383,12 +17414,12 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="109" t="inlineStr">
+      <c r="A312" s="112" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B312" s="109" t="inlineStr">
+      <c r="B312" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17413,12 +17444,12 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="109" t="inlineStr">
+      <c r="A313" s="112" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B313" s="109" t="inlineStr">
+      <c r="B313" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17443,12 +17474,12 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="109" t="inlineStr">
+      <c r="A314" s="112" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B314" s="109" t="inlineStr">
+      <c r="B314" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17473,12 +17504,12 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="109" t="inlineStr">
+      <c r="A315" s="112" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B315" s="109" t="inlineStr">
+      <c r="B315" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17503,12 +17534,12 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="109" t="inlineStr">
+      <c r="A316" s="112" t="inlineStr">
         <is>
           <t>bus_return_common</t>
         </is>
       </c>
-      <c r="B316" s="109" t="inlineStr">
+      <c r="B316" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17533,12 +17564,12 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="109" t="inlineStr">
+      <c r="A317" s="112" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B317" s="109" t="inlineStr">
+      <c r="B317" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17564,12 +17595,12 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="109" t="inlineStr">
+      <c r="A318" s="112" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B318" s="109" t="inlineStr">
+      <c r="B318" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17595,12 +17626,12 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="109" t="inlineStr">
+      <c r="A319" s="112" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B319" s="109" t="inlineStr">
+      <c r="B319" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17626,12 +17657,12 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="109" t="inlineStr">
+      <c r="A320" s="112" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B320" s="109" t="inlineStr">
+      <c r="B320" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17657,12 +17688,12 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="109" t="inlineStr">
+      <c r="A321" s="112" t="inlineStr">
         <is>
           <t>currency_exchange_common</t>
         </is>
       </c>
-      <c r="B321" s="109" t="inlineStr">
+      <c r="B321" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17688,12 +17719,12 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="109" t="inlineStr">
+      <c r="A322" s="112" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B322" s="109" t="inlineStr">
+      <c r="B322" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17718,12 +17749,12 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="109" t="inlineStr">
+      <c r="A323" s="112" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B323" s="109" t="inlineStr">
+      <c r="B323" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17748,12 +17779,12 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="109" t="inlineStr">
+      <c r="A324" s="112" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B324" s="109" t="inlineStr">
+      <c r="B324" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17778,12 +17809,12 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="109" t="inlineStr">
+      <c r="A325" s="112" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B325" s="109" t="inlineStr">
+      <c r="B325" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17808,12 +17839,12 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="109" t="inlineStr">
+      <c r="A326" s="112" t="inlineStr">
         <is>
           <t>festival_shrine_access_common</t>
         </is>
       </c>
-      <c r="B326" s="109" t="inlineStr">
+      <c r="B326" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17838,12 +17869,12 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="109" t="inlineStr">
+      <c r="A327" s="112" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B327" s="109" t="inlineStr">
+      <c r="B327" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -17870,12 +17901,12 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="109" t="inlineStr">
+      <c r="A328" s="112" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B328" s="109" t="inlineStr">
+      <c r="B328" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -17902,12 +17933,12 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="109" t="inlineStr">
+      <c r="A329" s="112" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B329" s="109" t="inlineStr">
+      <c r="B329" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -17934,12 +17965,12 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="109" t="inlineStr">
+      <c r="A330" s="112" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B330" s="109" t="inlineStr">
+      <c r="B330" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -17966,12 +17997,12 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="109" t="inlineStr">
+      <c r="A331" s="112" t="inlineStr">
         <is>
           <t>guesthouse_access_common</t>
         </is>
       </c>
-      <c r="B331" s="109" t="inlineStr">
+      <c r="B331" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -17998,12 +18029,12 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="109" t="inlineStr">
+      <c r="A332" s="112" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B332" s="109" t="inlineStr">
+      <c r="B332" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18030,12 +18061,12 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="109" t="inlineStr">
+      <c r="A333" s="112" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B333" s="109" t="inlineStr">
+      <c r="B333" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18062,12 +18093,12 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="109" t="inlineStr">
+      <c r="A334" s="112" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B334" s="109" t="inlineStr">
+      <c r="B334" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18094,12 +18125,12 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="109" t="inlineStr">
+      <c r="A335" s="112" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B335" s="109" t="inlineStr">
+      <c r="B335" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18126,12 +18157,12 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="109" t="inlineStr">
+      <c r="A336" s="112" t="inlineStr">
         <is>
           <t>lost_item_common</t>
         </is>
       </c>
-      <c r="B336" s="109" t="inlineStr">
+      <c r="B336" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18158,12 +18189,12 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="109" t="inlineStr">
+      <c r="A337" s="112" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B337" s="109" t="inlineStr">
+      <c r="B337" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18190,12 +18221,12 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="109" t="inlineStr">
+      <c r="A338" s="112" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B338" s="109" t="inlineStr">
+      <c r="B338" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18222,12 +18253,12 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="109" t="inlineStr">
+      <c r="A339" s="112" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B339" s="109" t="inlineStr">
+      <c r="B339" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18254,12 +18285,12 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="109" t="inlineStr">
+      <c r="A340" s="112" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B340" s="109" t="inlineStr">
+      <c r="B340" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18286,12 +18317,12 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="109" t="inlineStr">
+      <c r="A341" s="112" t="inlineStr">
         <is>
           <t>luggage_common</t>
         </is>
       </c>
-      <c r="B341" s="109" t="inlineStr">
+      <c r="B341" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18318,12 +18349,12 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="109" t="inlineStr">
+      <c r="A342" s="112" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B342" s="109" t="inlineStr">
+      <c r="B342" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18350,12 +18381,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="109" t="inlineStr">
+      <c r="A343" s="112" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B343" s="109" t="inlineStr">
+      <c r="B343" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18382,12 +18413,12 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="109" t="inlineStr">
+      <c r="A344" s="112" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B344" s="109" t="inlineStr">
+      <c r="B344" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18414,12 +18445,12 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="109" t="inlineStr">
+      <c r="A345" s="112" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B345" s="109" t="inlineStr">
+      <c r="B345" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18446,12 +18477,12 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="109" t="inlineStr">
+      <c r="A346" s="112" t="inlineStr">
         <is>
           <t>mountain_names_common</t>
         </is>
       </c>
-      <c r="B346" s="109" t="inlineStr">
+      <c r="B346" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18478,12 +18509,12 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="109" t="inlineStr">
+      <c r="A347" s="112" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B347" s="109" t="inlineStr">
+      <c r="B347" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18510,12 +18541,12 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="109" t="inlineStr">
+      <c r="A348" s="112" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B348" s="109" t="inlineStr">
+      <c r="B348" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18542,12 +18573,12 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="109" t="inlineStr">
+      <c r="A349" s="112" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B349" s="109" t="inlineStr">
+      <c r="B349" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18574,12 +18605,12 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="109" t="inlineStr">
+      <c r="A350" s="112" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B350" s="109" t="inlineStr">
+      <c r="B350" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18606,12 +18637,12 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="109" t="inlineStr">
+      <c r="A351" s="112" t="inlineStr">
         <is>
           <t>observatory_access_common</t>
         </is>
       </c>
-      <c r="B351" s="109" t="inlineStr">
+      <c r="B351" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18638,12 +18669,12 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="109" t="inlineStr">
+      <c r="A352" s="112" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B352" s="109" t="inlineStr">
+      <c r="B352" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18669,12 +18700,12 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="109" t="inlineStr">
+      <c r="A353" s="112" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B353" s="109" t="inlineStr">
+      <c r="B353" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18700,12 +18731,12 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="109" t="inlineStr">
+      <c r="A354" s="112" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B354" s="109" t="inlineStr">
+      <c r="B354" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18731,12 +18762,12 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="109" t="inlineStr">
+      <c r="A355" s="112" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B355" s="109" t="inlineStr">
+      <c r="B355" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18762,12 +18793,12 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="109" t="inlineStr">
+      <c r="A356" s="112" t="inlineStr">
         <is>
           <t>snow_play_common</t>
         </is>
       </c>
-      <c r="B356" s="109" t="inlineStr">
+      <c r="B356" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18793,12 +18824,12 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="109" t="inlineStr">
+      <c r="A357" s="112" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B357" s="109" t="inlineStr">
+      <c r="B357" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18824,12 +18855,12 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="109" t="inlineStr">
+      <c r="A358" s="112" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B358" s="109" t="inlineStr">
+      <c r="B358" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -18855,12 +18886,12 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="109" t="inlineStr">
+      <c r="A359" s="112" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B359" s="109" t="inlineStr">
+      <c r="B359" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -18886,12 +18917,12 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="109" t="inlineStr">
+      <c r="A360" s="112" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B360" s="109" t="inlineStr">
+      <c r="B360" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -18917,12 +18948,12 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="109" t="inlineStr">
+      <c r="A361" s="112" t="inlineStr">
         <is>
           <t>stamp_common</t>
         </is>
       </c>
-      <c r="B361" s="109" t="inlineStr">
+      <c r="B361" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -18948,12 +18979,12 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="109" t="inlineStr">
+      <c r="A362" s="112" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B362" s="109" t="inlineStr">
+      <c r="B362" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -18980,12 +19011,12 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="109" t="inlineStr">
+      <c r="A363" s="112" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B363" s="109" t="inlineStr">
+      <c r="B363" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -19012,12 +19043,12 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="109" t="inlineStr">
+      <c r="A364" s="112" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B364" s="109" t="inlineStr">
+      <c r="B364" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -19044,12 +19075,12 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="109" t="inlineStr">
+      <c r="A365" s="112" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B365" s="109" t="inlineStr">
+      <c r="B365" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -19076,12 +19107,12 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="109" t="inlineStr">
+      <c r="A366" s="112" t="inlineStr">
         <is>
           <t>terao_shuttle_common</t>
         </is>
       </c>
-      <c r="B366" s="109" t="inlineStr">
+      <c r="B366" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -19108,12 +19139,12 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="109" t="inlineStr">
+      <c r="A367" s="112" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B367" s="109" t="inlineStr">
+      <c r="B367" s="112" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -19140,12 +19171,12 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="109" t="inlineStr">
+      <c r="A368" s="112" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B368" s="109" t="inlineStr">
+      <c r="B368" s="112" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -19172,12 +19203,12 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="109" t="inlineStr">
+      <c r="A369" s="112" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B369" s="109" t="inlineStr">
+      <c r="B369" s="112" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -19204,12 +19235,12 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="109" t="inlineStr">
+      <c r="A370" s="112" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B370" s="109" t="inlineStr">
+      <c r="B370" s="112" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -19236,12 +19267,12 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="109" t="inlineStr">
+      <c r="A371" s="112" t="inlineStr">
         <is>
           <t>yuinosho_common</t>
         </is>
       </c>
-      <c r="B371" s="109" t="inlineStr">
+      <c r="B371" s="112" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -20377,7 +20408,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="109" t="inlineStr">
+      <c r="A2" s="112" t="inlineStr">
         <is>
           <t>雨・雪の日の見学</t>
         </is>
@@ -20387,7 +20418,7 @@
           <t>集落は屋外のため、雨や雪の日も見学できますが、傘や雨具が必要です。道は舗装されていない場所があり、雨の日はぬかるみます。冬は積雪があり、足もとが滑りやすくなります。</t>
         </is>
       </c>
-      <c r="C2" s="109" t="inlineStr">
+      <c r="C2" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20399,7 +20430,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="109" t="inlineStr">
+      <c r="A3" s="112" t="inlineStr">
         <is>
           <t>冬の服装と靴</t>
         </is>
@@ -20409,7 +20440,7 @@
           <t>冬は雪が積もり、路面が凍ることがあります。滑りにくい靴と、防寒の用意をおすすめします。</t>
         </is>
       </c>
-      <c r="C3" s="109" t="inlineStr">
+      <c r="C3" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20421,7 +20452,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="109" t="inlineStr">
+      <c r="A4" s="112" t="inlineStr">
         <is>
           <t>集落の歩き方</t>
         </is>
@@ -20431,7 +20462,7 @@
           <t>集落は平坦で、端から端まで歩いて回れる広さです。住民の方が生活している場所なので、私有地には入らないでください。</t>
         </is>
       </c>
-      <c r="C4" s="109" t="inlineStr">
+      <c r="C4" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20443,7 +20474,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="109" t="inlineStr">
+      <c r="A5" s="112" t="inlineStr">
         <is>
           <t>【質問回答集より】見どころ・観光</t>
         </is>
@@ -20453,7 +20484,7 @@
           <t>入村料をお支払いいただく必要はありませんが、駐車料金の一部は合掌集落の保全に役立てられています。また合掌集落内の見学施設に入るときには、それぞれの入館料をその場でお支払いいただきます。施設はそれぞれ個別に営業しており、フリーパスのようなチケットはございません。　とても小さな集落ですので、歩いてお回りいただけます。お食事を入れても2時間から3時間で全体をご覧いただけます。目のマークが付いている場所が見学施設です。　白水の滝と白水湖へは、自家用車でないと行くことができません。また、大雨により通行制限されている場合がありますのでご注意ください。詳しくはシラカワ・ゴーイングをご覧ください。　合掌造りの見学施設は、各施設おひとり300円から400円、民家園のみおひとり800円となります。　展望台へは、歩きと有料シャトルバスの2通りがあります。シャトルバスは和田家のすいれん池前の乗り場から出ています。歩く場合は、和田家の先から登る遊歩道でおよそ20分です。　白川郷から見える主な山は、三方岩岳、野谷荘司山、猪臥山などです。展望台からは白山も少しご覧いただけます。</t>
         </is>
       </c>
-      <c r="C5" s="109" t="inlineStr">
+      <c r="C5" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20465,7 +20496,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="109" t="inlineStr">
+      <c r="A6" s="112" t="inlineStr">
         <is>
           <t>【質問回答集より】交通・バス</t>
         </is>
@@ -20475,7 +20506,7 @@
           <t>展望台行きのシャトルバスは、和田家のすいれん池前の乗り場から出ています。料金は片道300円で、降りるときに現金でお支払いください。小学生は半額、幼児は座席を使わない場合は無料、障害者手帳をお持ちの方は半額です。ペットはご乗車いただけません。上りは午前9時から11時40分まで、午後は1時20分から3時40分まで。下りは午前9時10分から12時10分まで、午後は1時30分から4時10分まで。いずれも20分間隔で運行しています。　村内のタクシー会社は一社のみで、シャトルバスの運行をしているため、通常はご利用いただけません。タクシー会社に直接電話していただき、予約が取れた場合のみ利用可能です。村内の移動は路線バスをご利用ください。　バスの時刻表は、案内所前の掲示またはバス会社の窓口でご確認いただけます。詳しくは係員にお尋ねください。　村内は小さなエリアですので、観光用の周遊バスはございません。徒歩でのご見学をお楽しみください。なお、展望台へのシャトルバスはございます。　寺尾駐車場行きのシャトルバスは、時刻を定めず随時運行しております。往路で降車された場所でお待ちください。</t>
         </is>
       </c>
-      <c r="C6" s="109" t="inlineStr">
+      <c r="C6" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20487,7 +20518,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="109" t="inlineStr">
+      <c r="A7" s="112" t="inlineStr">
         <is>
           <t>【質問回答集より】施設・設備</t>
         </is>
@@ -20497,7 +20528,7 @@
           <t>駐車場の利用料金は、出庫時に精算機でお支払いください。なお、駐車券はありません。一万円札など現金はもちろんクレジットカード、QRコード決済、交通系ICカードもご利用いただけます。　お手洗いのご案内は、村内マップをご覧ください。車椅子でご利用いただけるトイレは村内に5か所ございます。　海外で発行されたカードは、郵便局のATMのみご利用いただけます。日本で発行されたカードは、JAのATMをご利用いただけます。JAのATMは和田家前、展望台行きシャトルバス乗り場の向かいにございます。　外貨の両替は、白川郷バスターミナルにある両替機をご利用ください。紙幣のみの対応です。コインロッカーでお使いになる小銭への両替は、各案内所の窓口で承ります。　コインロッカーは白川郷バスターミナルにございます。せせらぎ公園駐車場やであいの館の周辺にはございません。バスターミナルのロッカーが満杯の場合は、窓口にお声がけください。　記念スタンプは、白川郷バスターミナルとであいの館の窓口机上にご用意しております。切手は白川郷バスターミナルの窓口で取り扱っております。御朱印の取扱いはございません。　高速バスは白川郷バスターミナルから発車します。ご予約済みの便、または当日券でご乗車ください。当日券はバスターミナルの窓口でお求めいただけます。</t>
         </is>
       </c>
-      <c r="C7" s="109" t="inlineStr">
+      <c r="C7" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20509,7 +20540,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="109" t="inlineStr">
+      <c r="A8" s="112" t="inlineStr">
         <is>
           <t>【質問回答集より】食事</t>
         </is>
@@ -20519,7 +20550,7 @@
           <t>ハラール対応のお食事はご用意がございません。ベジタリアンの方には、お肉を使わない朴葉味噌、岩魚料理、豆腐料理がございます。　郷土料理は朴葉味噌定食です。飛騨牛や山菜、岩魚、ニジマス、石豆腐のお料理もございます。　村内の食事施設をご案内しております。団体様は早めのご予約が必要です。多くの店舗が不定休となっておりますので、事前にご確認ください。詳しい一覧は画面のリンクをご覧ください。</t>
         </is>
       </c>
-      <c r="C8" s="109" t="inlineStr">
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20531,7 +20562,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="109" t="inlineStr">
+      <c r="A9" s="112" t="inlineStr">
         <is>
           <t>【質問回答集より】季節・天候</t>
         </is>
@@ -20541,7 +20572,7 @@
           <t>毎年の気温により変動いたしますので、必ずご自身でご確認ください。桜は例年4月15日頃に開花を迎えます。紅葉は例年10月末から11月初旬が見ごろです。　近年の傾向では、毎年12月初旬に初雪が観測されます。当村は豪雪地帯のため、12月下旬から2月下旬は雪の積もった状態が続きます。お出かけ前に天気予報をご確認ください。　雪の降る時季は、必ずスタッドレスタイヤをご装着のうえお越しください。路面は大変滑りやすくなっております。</t>
         </is>
       </c>
-      <c r="C9" s="109" t="inlineStr">
+      <c r="C9" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20553,7 +20584,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="109" t="inlineStr">
+      <c r="A10" s="112" t="inlineStr">
         <is>
           <t>【質問回答集より】車椅子・バリアフリー</t>
         </is>
@@ -20563,7 +20594,7 @@
           <t>車椅子は、白川郷バスターミナルに2台、せせらぎ公園駐車場に2台ご用意しております。先着順となりますので、各案内所にお声がけください。せせらぎ公園駐車場での貸出は、午前9時30分から午後3時30分までです。11月から3月末までの冬期間は、安全のため貸出を行っておりません。なお、村内は砂利道や段差が多く、整備された観光施設ではございませんので、ご移動にはお気をつけください。　身体障害者用の駐車スペースは、白川郷バスターミナルに2台、せせらぎ公園駐車場に5台ございます。ご利用時間は午前8時から午後5時まで、駐車料金は1台2000円で、障がい者割引はございません。台数が少ないため、満車の場合はお断りすることがございます。</t>
         </is>
       </c>
-      <c r="C10" s="109" t="inlineStr">
+      <c r="C10" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20575,7 +20606,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="109" t="inlineStr">
+      <c r="A11" s="112" t="inlineStr">
         <is>
           <t>【質問回答集より】見学のマナー・注意</t>
         </is>
@@ -20585,7 +20616,7 @@
           <t>クマの出没にご注意ください。もしクマに出会ってしまったら、背中を見せずゆっくりと後退しましょう。 もし襲われてしまった際には地面に伏せて頭を守りましょう。　火を使わない電子たばこ・加熱式たばこであっても、歩行喫煙や所定場所以外での使用は禁止されています。加熱式たばこは、荻町多目的集会施設、荻町公園、バスターミナル、せせらぎ公園駐車場の各喫煙所をご利用ください。　集落は住民の方が生活されている場所です。私有地に立ち入っての撮影や、住民の方を無断で撮影することは禁止です。生活されている場所ですので大きな声を出したり騒いだりするのはお止め下さい。静かに観光をお願いします。　合掌造り集落は火災に非常に弱いため、歩行中を含め指定場所以外での喫煙は厳禁です。紙巻たばこは「白川郷バスターミナル」「せせらぎ公園駐車場」の喫煙所をご利用ください。「荻町公園」「荻町多目的集会施設」の喫煙所は加熱式たばこ専用です。　白川村にはゴミ箱を設置しておりません。お持ち帰りへのご協力をお願いいたします。　自転車で集落内へお越しいただくことは可能ですが、歩いている方が多いため、おすすめはしておりません。押して歩いていただくか、駐輪してからのご見学をお願いいたします。　山の中や田畑には立ち入らないでください。道に迷ったり、けがをされる危険がございます。ご散策は集落内の道と、展望台までの遊歩道をご利用ください。　ペットとご一緒に集落内をお回りいただけます。ただし店内はペット不可のお店が大半です。こびきは抱っこであれば入店いただけます。今藤商店はご同伴いただけます。その他のお店は各店舗にご確認ください。なお展望台行きのシャトルバスはご乗車いただけません。　川は流れが速く水深もあるため大変危険です。川にはお入りにならないでください。　世界遺産集落は住民の方が生活されています。そのため、集落内にご宿泊の方以外のご見学は、8時から17時の時間帯でお願いしております。村営駐車場の営業時間も8時から17時です。ライトアップなどのイベント開催日は除きます。　集落内は道路以外が私有地で、住民の方が生活されています。雪遊びができる場所はございませんので、私有地に入って遊んだり騒いだりしないでください。</t>
         </is>
       </c>
-      <c r="C11" s="109" t="inlineStr">
+      <c r="C11" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20597,7 +20628,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="109" t="inlineStr">
+      <c r="A12" s="112" t="inlineStr">
         <is>
           <t>【質問回答集より】その他</t>
         </is>
@@ -20607,7 +20638,7 @@
           <t>当日にご予約いただける宿をお探しの際は、直接お電話をお願いいたします。民宿などは当日のご予約を承っておりません。　どぶろくの振る舞いは、白川八幡神社の境内にて15時30分頃から17時頃まで行われます。どぶろくをいただくには、まず境内の受付で「奉納（初穂料）」を納めて専用の赤い記念盃（杯）をお受け取りください。その盃を持って列に並ぶと、神社で醸造された特製のどぶろくが注がれます。おかわりも可能ですが、境内限定での飲食となっており、持ち帰りはできません。　境内で振る舞われるどぶろくは神様へのお供えのお下がりであるため、水筒やペットボトル等に入れての持ち帰りは固く禁じられています。祭り期間中は、境内の受付で2000円を志納すると徳利を1本いただけます。お土産用のどぶろく（瓶詰め）は、村内の酒屋や土産品店でご購入いただけます。また、どぶろくはアルコール度数の高いお酒ですので飲みすぎにはご注意ください。お車や自転車を運転される方の飲酒は絶対におやめください。　未成年の方はどぶろくをお召し上がりいただけません。お子様連れでもお祭りはご覧いただけます。　白川郷の「どぶろく祭」は、五穀豊穣・家内安全・里の平和を祈願して毎年秋に開催される伝統的な神事です。白川八幡神社では10月14日と15日の2日間にわたって行われます。その後、2日間ごとに鳩谷八幡神社、飯島八幡神社と続きます。日中の華やかな「村回り行列（神幸祭）」や、境内での「どぶろくの振る舞い」、夕方以降に奉納される「獅子舞」や「民謡・白川郷春駒」など、見どころが豊富にあります。　神社の境内の舞台・拝殿前では、伝統の郷土芸能が奉納されます。勇壮な「白川連獅子（獅子舞）」や、県重要無形民俗文化財に指定されている民謡「春駒（はるこま）」の踊りなどが披露されます。昼の部のどぶろく振る舞いと同時に始まり、一度休憩を挟んだ後、19時頃からの夜の部でも獅子舞、民謡が披露されます。　両日ともおおむね以下の流れで進行します。 ・08:00～ 神事（本殿） ・09:00～ 村回り行列出発（神橋〜集落内を練り歩き） ・15:00～ 行列が神社に還御 ・15:30～17:00 どぶろくの振る舞い（境内） ・15:30～ 郷土芸能（獅子舞、民謡など）の奉納開始 ・19:00～ 夜の獅子舞・民謡奉納 進行状況や天候によって時間が前後する場合がありますので、時間に余裕をもってお越しください。　白川八幡神社は、荻町合掌造り集落の南端にございます。鳥居と大きな杉の木が目印です。白川郷バスターミナルからは、メイン通りを南へ徒歩15分から20分ほどです。　そちらの宿は鳩谷八幡神社の方面にございます。国道156号線を進み、川を渡る橋を左に曲がって川沿いを進む道をおすすめしております。　バス車内でのお忘れ物は、バス会社にお尋ねください。村内での落とし物は、拾得物の届け出があればお知らせできます。お名前、落とされた物の詳細、ご連絡先をご記入のうえメールをお願いいたします。貴重品は警察にもお電話をお願いいたします。　結の庄は道の駅白川郷の裏手、3.1キロメートル先にあり、歩くとおよそ30分から40分かかります。国道は交通量が多いため、川沿いの道をおすすめしております。送迎は午後2時30分から始まります。</t>
         </is>
       </c>
-      <c r="C12" s="109" t="inlineStr">
+      <c r="C12" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20619,7 +20650,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="109" t="inlineStr">
+      <c r="A13" s="112" t="inlineStr">
         <is>
           <t>【質問回答集より】案内所によって答えが違うこと</t>
         </is>
@@ -20629,7 +20660,7 @@
           <t>次の話題は、バスターミナルとであいの館で答えが違います: ATMはどこ、すみれ荘、スタンプ、両替、寺尾駐車場、展望台への行き方、山名前、帰りバス、白川八幡神社どこ、結の庄、荷物を預けたい、落とし物、障害者駐車場、雪遊び。これらは、いまいる案内所の資料に書かれている内容だけを使って答えてください。資料に無い案内所の情報を持ち出さないでください。</t>
         </is>
       </c>
-      <c r="C13" s="109" t="inlineStr">
+      <c r="C13" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20771,53 +20802,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="109" t="inlineStr">
+      <c r="A2" s="112" t="inlineStr">
         <is>
           <t>ナビ</t>
         </is>
       </c>
-      <c r="B2" s="109" t="inlineStr">
+      <c r="B2" s="112" t="inlineStr">
         <is>
           <t>navi</t>
         </is>
       </c>
-      <c r="C2" s="109" t="inlineStr">
+      <c r="C2" s="112" t="inlineStr">
         <is>
           <t>idle.png</t>
         </is>
       </c>
-      <c r="D2" s="109" t="inlineStr">
+      <c r="D2" s="112" t="inlineStr">
         <is>
           <t>listening.png</t>
         </is>
       </c>
-      <c r="E2" s="109" t="inlineStr">
+      <c r="E2" s="112" t="inlineStr">
         <is>
           <t>talking.png</t>
         </is>
       </c>
-      <c r="F2" s="109" t="inlineStr">
+      <c r="F2" s="112" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="G2" s="109" t="inlineStr">
+      <c r="G2" s="112" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="H2" s="109" t="inlineStr">
+      <c r="H2" s="112" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" s="109" t="inlineStr">
+      <c r="I2" s="112" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="109" t="n"/>
-      <c r="K2" s="109" t="inlineStr">
+      <c r="J2" s="112" t="n"/>
+      <c r="K2" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20854,45 +20885,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="109" t="inlineStr">
+      <c r="A3" s="112" t="inlineStr">
         <is>
           <t>ゆい</t>
         </is>
       </c>
-      <c r="B3" s="109" t="inlineStr">
+      <c r="B3" s="112" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C3" s="109" t="inlineStr">
+      <c r="C3" s="112" t="inlineStr">
         <is>
           <t>main_idle_20261013044809.png</t>
         </is>
       </c>
-      <c r="D3" s="109" t="n"/>
-      <c r="E3" s="109" t="n"/>
-      <c r="F3" s="109" t="n">
+      <c r="D3" s="112" t="n"/>
+      <c r="E3" s="112" t="n"/>
+      <c r="F3" s="112" t="n">
         <v>0.179</v>
       </c>
-      <c r="G3" s="109" t="n">
+      <c r="G3" s="112" t="n">
         <v>0.23</v>
       </c>
-      <c r="H3" s="109" t="inlineStr">
+      <c r="H3" s="112" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="109" t="inlineStr">
+      <c r="I3" s="112" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="109" t="inlineStr">
+      <c r="J3" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="109" t="inlineStr">
+      <c r="K3" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -20929,45 +20960,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="109" t="inlineStr">
+      <c r="A4" s="112" t="inlineStr">
         <is>
           <t>がっしょくん</t>
         </is>
       </c>
-      <c r="B4" s="109" t="inlineStr">
+      <c r="B4" s="112" t="inlineStr">
         <is>
           <t>yuru</t>
         </is>
       </c>
-      <c r="C4" s="109" t="inlineStr">
+      <c r="C4" s="112" t="inlineStr">
         <is>
           <t>yuru.png</t>
         </is>
       </c>
-      <c r="D4" s="109" t="n"/>
-      <c r="E4" s="109" t="n"/>
-      <c r="F4" s="109" t="inlineStr">
+      <c r="D4" s="112" t="n"/>
+      <c r="E4" s="112" t="n"/>
+      <c r="F4" s="112" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G4" s="109" t="inlineStr">
+      <c r="G4" s="112" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H4" s="109" t="inlineStr">
+      <c r="H4" s="112" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I4" s="109" t="inlineStr">
+      <c r="I4" s="112" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J4" s="109" t="n"/>
-      <c r="K4" s="109" t="inlineStr">
+      <c r="J4" s="112" t="n"/>
+      <c r="K4" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -21004,45 +21035,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="109" t="inlineStr">
+      <c r="A5" s="112" t="inlineStr">
         <is>
           <t>やねくん</t>
         </is>
       </c>
-      <c r="B5" s="109" t="inlineStr">
+      <c r="B5" s="112" t="inlineStr">
         <is>
           <t>yane</t>
         </is>
       </c>
-      <c r="C5" s="109" t="inlineStr">
+      <c r="C5" s="112" t="inlineStr">
         <is>
           <t>2.png</t>
         </is>
       </c>
-      <c r="D5" s="109" t="n"/>
-      <c r="E5" s="109" t="n"/>
-      <c r="F5" s="109" t="inlineStr">
+      <c r="D5" s="112" t="n"/>
+      <c r="E5" s="112" t="n"/>
+      <c r="F5" s="112" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G5" s="109" t="inlineStr">
+      <c r="G5" s="112" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H5" s="109" t="inlineStr">
+      <c r="H5" s="112" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" s="109" t="inlineStr">
+      <c r="I5" s="112" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J5" s="109" t="n"/>
-      <c r="K5" s="109" t="inlineStr">
+      <c r="J5" s="112" t="n"/>
+      <c r="K5" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -21079,45 +21110,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="109" t="inlineStr">
+      <c r="A6" s="112" t="inlineStr">
         <is>
           <t>ごうちゃん</t>
         </is>
       </c>
-      <c r="B6" s="109" t="inlineStr">
+      <c r="B6" s="112" t="inlineStr">
         <is>
           <t>gou</t>
         </is>
       </c>
-      <c r="C6" s="109" t="inlineStr">
+      <c r="C6" s="112" t="inlineStr">
         <is>
           <t>4.png</t>
         </is>
       </c>
-      <c r="D6" s="109" t="n"/>
-      <c r="E6" s="109" t="n"/>
-      <c r="F6" s="109" t="inlineStr">
+      <c r="D6" s="112" t="n"/>
+      <c r="E6" s="112" t="n"/>
+      <c r="F6" s="112" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="G6" s="109" t="inlineStr">
+      <c r="G6" s="112" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H6" s="109" t="inlineStr">
+      <c r="H6" s="112" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="I6" s="109" t="inlineStr">
+      <c r="I6" s="112" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="J6" s="109" t="n"/>
-      <c r="K6" s="109" t="inlineStr">
+      <c r="J6" s="112" t="n"/>
+      <c r="K6" s="112" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -21239,12 +21270,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="109" t="inlineStr">
+      <c r="A2" s="112" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B2" s="109" t="inlineStr">
+      <c r="B2" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21283,12 +21314,12 @@
       <c r="J2" s="46" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="109" t="inlineStr">
+      <c r="A3" s="112" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B3" s="109" t="inlineStr">
+      <c r="B3" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21327,12 +21358,12 @@
       <c r="J3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="109" t="inlineStr">
+      <c r="A4" s="112" t="inlineStr">
         <is>
           <t>あいさつ</t>
         </is>
       </c>
-      <c r="B4" s="109" t="inlineStr">
+      <c r="B4" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21371,12 +21402,12 @@
       <c r="J4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="109" t="inlineStr">
+      <c r="A5" s="112" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B5" s="109" t="inlineStr">
+      <c r="B5" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21415,12 +21446,12 @@
       <c r="J5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="109" t="inlineStr">
+      <c r="A6" s="112" t="inlineStr">
         <is>
           <t>お礼</t>
         </is>
       </c>
-      <c r="B6" s="109" t="inlineStr">
+      <c r="B6" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21459,12 +21490,12 @@
       <c r="J6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="109" t="inlineStr">
+      <c r="A7" s="112" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B7" s="109" t="inlineStr">
+      <c r="B7" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21503,12 +21534,12 @@
       <c r="J7" s="46" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="109" t="inlineStr">
+      <c r="A8" s="112" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B8" s="109" t="inlineStr">
+      <c r="B8" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21547,12 +21578,12 @@
       <c r="J8" s="46" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="109" t="inlineStr">
+      <c r="A9" s="112" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B9" s="109" t="inlineStr">
+      <c r="B9" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21591,12 +21622,12 @@
       <c r="J9" s="46" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="109" t="inlineStr">
+      <c r="A10" s="112" t="inlineStr">
         <is>
           <t>元気</t>
         </is>
       </c>
-      <c r="B10" s="109" t="inlineStr">
+      <c r="B10" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21635,12 +21666,12 @@
       <c r="J10" s="46" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="109" t="inlineStr">
+      <c r="A11" s="112" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B11" s="109" t="inlineStr">
+      <c r="B11" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21679,12 +21710,12 @@
       <c r="J11" s="46" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="109" t="inlineStr">
+      <c r="A12" s="112" t="inlineStr">
         <is>
           <t>さようなら</t>
         </is>
       </c>
-      <c r="B12" s="109" t="inlineStr">
+      <c r="B12" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21723,12 +21754,12 @@
       <c r="J12" s="46" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="109" t="inlineStr">
+      <c r="A13" s="112" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B13" s="109" t="inlineStr">
+      <c r="B13" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21786,12 +21817,12 @@
       <c r="J13" s="46" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="109" t="inlineStr">
+      <c r="A14" s="112" t="inlineStr">
         <is>
           <t>好きな食べ物</t>
         </is>
       </c>
-      <c r="B14" s="109" t="inlineStr">
+      <c r="B14" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21849,12 +21880,12 @@
       <c r="J14" s="46" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="109" t="inlineStr">
+      <c r="A15" s="112" t="inlineStr">
         <is>
           <t>趣味</t>
         </is>
       </c>
-      <c r="B15" s="109" t="inlineStr">
+      <c r="B15" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21915,12 +21946,12 @@
       <c r="J15" s="46" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="109" t="inlineStr">
+      <c r="A16" s="112" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B16" s="109" t="inlineStr">
+      <c r="B16" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
@@ -21980,12 +22011,12 @@
       <c r="J16" s="46" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="109" t="inlineStr">
+      <c r="A17" s="112" t="inlineStr">
         <is>
           <t>ほめられた</t>
         </is>
       </c>
-      <c r="B17" s="109" t="inlineStr">
+      <c r="B17" s="112" t="inlineStr">
         <is>
           <t>共通</t>
         </is>

--- a/tools/faq_master.xlsx
+++ b/tools/faq_master.xlsx
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -600,6 +600,18 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1302,7 +1314,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="112" t="inlineStr">
+      <c r="A2" s="116" t="inlineStr">
         <is>
           <t>バスターミナル</t>
         </is>
@@ -1312,31 +1324,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C2" s="112" t="n">
+      <c r="C2" s="116" t="n">
         <v>0.09</v>
       </c>
-      <c r="D2" s="112" t="n">
+      <c r="D2" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="112" t="n">
+      <c r="E2" s="116" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" s="112" t="n">
+      <c r="F2" s="116" t="n">
         <v>0.1</v>
       </c>
-      <c r="G2" s="112" t="n">
+      <c r="G2" s="116" t="n">
         <v>0.957</v>
       </c>
-      <c r="H2" s="112" t="n">
+      <c r="H2" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="112" t="n">
+      <c r="I2" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="112" t="n">
+      <c r="J2" s="116" t="n">
         <v>0.864</v>
       </c>
-      <c r="K2" s="112" t="n">
+      <c r="K2" s="116" t="n">
         <v>1.1</v>
       </c>
       <c r="L2" s="46" t="inlineStr">
@@ -1346,7 +1358,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="112" t="inlineStr">
+      <c r="A3" s="116" t="inlineStr">
         <is>
           <t>であいの館</t>
         </is>
@@ -1356,31 +1368,31 @@
           <t>stage,faq,talk,languages</t>
         </is>
       </c>
-      <c r="C3" s="112" t="n">
+      <c r="C3" s="116" t="n">
         <v>0.066</v>
       </c>
-      <c r="D3" s="112" t="n">
+      <c r="D3" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="112" t="n">
+      <c r="E3" s="116" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="112" t="n">
+      <c r="F3" s="116" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="112" t="n">
+      <c r="G3" s="116" t="n">
         <v>0.929</v>
       </c>
-      <c r="H3" s="112" t="n">
+      <c r="H3" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="112" t="n">
+      <c r="I3" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="112" t="n">
+      <c r="J3" s="116" t="n">
         <v>0.753</v>
       </c>
-      <c r="K3" s="112" t="n">
+      <c r="K3" s="116" t="n">
         <v>1.1</v>
       </c>
       <c r="L3" s="46" t="inlineStr">
@@ -1390,7 +1402,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="112" t="inlineStr">
+      <c r="A4" s="116" t="inlineStr">
         <is>
           <t>観光客</t>
         </is>
@@ -1400,31 +1412,31 @@
           <t>stage,faq,typed,talk,languages</t>
         </is>
       </c>
-      <c r="C4" s="112" t="n">
+      <c r="C4" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="112" t="n">
+      <c r="D4" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="112" t="n">
+      <c r="E4" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="112" t="n">
+      <c r="F4" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="112" t="n">
+      <c r="G4" s="116" t="n">
         <v>0.92</v>
       </c>
-      <c r="H4" s="112" t="n">
+      <c r="H4" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="112" t="n">
+      <c r="I4" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="112" t="n">
+      <c r="J4" s="116" t="n">
         <v>0.884</v>
       </c>
-      <c r="K4" s="112" t="n">
+      <c r="K4" s="116" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -1496,7 +1508,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="112" t="inlineStr">
+      <c r="A2" s="116" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
@@ -1506,10 +1518,10 @@
           <t>Google 日本語, Microsoft Nanami, Microsoft Ayumi, Microsoft Haruka, Kyoko, O-ren</t>
         </is>
       </c>
-      <c r="C2" s="112" t="n">
+      <c r="C2" s="116" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="112" t="n">
+      <c r="D2" s="116" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="46" t="inlineStr">
@@ -1519,7 +1531,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="112" t="inlineStr">
+      <c r="A3" s="116" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -1529,16 +1541,16 @@
           <t>Google US English, Microsoft Aria, Microsoft Jenny, Microsoft Michelle, Microsoft Zira, Samantha</t>
         </is>
       </c>
-      <c r="C3" s="112" t="n">
+      <c r="C3" s="116" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="112" t="n">
+      <c r="D3" s="116" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="46" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="112" t="inlineStr">
+      <c r="A4" s="116" t="inlineStr">
         <is>
           <t>zh</t>
         </is>
@@ -1548,16 +1560,16 @@
           <t>Google 普通话, Microsoft Xiaoxiao, Microsoft Xiaoyi, Microsoft Huihui, Tingting, Ting-Ting</t>
         </is>
       </c>
-      <c r="C4" s="112" t="n">
+      <c r="C4" s="116" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="112" t="n">
+      <c r="D4" s="116" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="46" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="112" t="inlineStr">
+      <c r="A5" s="116" t="inlineStr">
         <is>
           <t>ko</t>
         </is>
@@ -1567,16 +1579,16 @@
           <t>Google 한국의, Microsoft SunHi, Microsoft Heami, Yuna</t>
         </is>
       </c>
-      <c r="C5" s="112" t="n">
+      <c r="C5" s="116" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="112" t="n">
+      <c r="D5" s="116" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="46" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="112" t="inlineStr">
+      <c r="A6" s="116" t="inlineStr">
         <is>
           <t>es</t>
         </is>
@@ -1586,16 +1598,16 @@
           <t>Google español, Microsoft Elvira, Microsoft Helena, Microsoft Laura, Mónica, Monica, Paulina</t>
         </is>
       </c>
-      <c r="C6" s="112" t="n">
+      <c r="C6" s="116" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="112" t="n">
+      <c r="D6" s="116" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="46" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="112" t="inlineStr">
+      <c r="A7" s="116" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
@@ -1605,10 +1617,10 @@
           <t>Google français, Microsoft Denise, Microsoft Vivienne, Microsoft Hortense, Amélie, Amelie, Audrey</t>
         </is>
       </c>
-      <c r="C7" s="112" t="n">
+      <c r="C7" s="116" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="112" t="n">
+      <c r="D7" s="116" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="46" t="inlineStr"/>
@@ -1668,17 +1680,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="112" t="inlineStr">
+      <c r="A2" s="116" t="inlineStr">
         <is>
           <t>白川郷</t>
         </is>
       </c>
-      <c r="B2" s="112" t="inlineStr">
+      <c r="B2" s="116" t="inlineStr">
         <is>
           <t>シラカワゴウ</t>
         </is>
       </c>
-      <c r="C2" s="112" t="inlineStr">
+      <c r="C2" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1690,17 +1702,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="112" t="inlineStr">
+      <c r="A3" s="116" t="inlineStr">
         <is>
           <t>白川村</t>
         </is>
       </c>
-      <c r="B3" s="112" t="inlineStr">
+      <c r="B3" s="116" t="inlineStr">
         <is>
           <t>シラカワムラ</t>
         </is>
       </c>
-      <c r="C3" s="112" t="inlineStr">
+      <c r="C3" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1708,17 +1720,17 @@
       <c r="D3" s="46" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="112" t="inlineStr">
+      <c r="A4" s="116" t="inlineStr">
         <is>
           <t>荻町</t>
         </is>
       </c>
-      <c r="B4" s="112" t="inlineStr">
+      <c r="B4" s="116" t="inlineStr">
         <is>
           <t>オギマチ</t>
         </is>
       </c>
-      <c r="C4" s="112" t="inlineStr">
+      <c r="C4" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1730,17 +1742,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="112" t="inlineStr">
+      <c r="A5" s="116" t="inlineStr">
         <is>
           <t>鳩谷</t>
         </is>
       </c>
-      <c r="B5" s="112" t="inlineStr">
+      <c r="B5" s="116" t="inlineStr">
         <is>
           <t>ハトガヤ</t>
         </is>
       </c>
-      <c r="C5" s="112" t="inlineStr">
+      <c r="C5" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1752,17 +1764,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="112" t="inlineStr">
+      <c r="A6" s="116" t="inlineStr">
         <is>
           <t>飯島</t>
         </is>
       </c>
-      <c r="B6" s="112" t="inlineStr">
+      <c r="B6" s="116" t="inlineStr">
         <is>
           <t>イイジマ</t>
         </is>
       </c>
-      <c r="C6" s="112" t="inlineStr">
+      <c r="C6" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1770,17 +1782,17 @@
       <c r="D6" s="46" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="112" t="inlineStr">
+      <c r="A7" s="116" t="inlineStr">
         <is>
           <t>寺尾</t>
         </is>
       </c>
-      <c r="B7" s="112" t="inlineStr">
+      <c r="B7" s="116" t="inlineStr">
         <is>
           <t>テラオ</t>
         </is>
       </c>
-      <c r="C7" s="112" t="inlineStr">
+      <c r="C7" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1788,17 +1800,17 @@
       <c r="D7" s="46" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="112" t="inlineStr">
+      <c r="A8" s="116" t="inlineStr">
         <is>
           <t>和田家</t>
         </is>
       </c>
-      <c r="B8" s="112" t="inlineStr">
+      <c r="B8" s="116" t="inlineStr">
         <is>
           <t>ワダケ</t>
         </is>
       </c>
-      <c r="C8" s="112" t="inlineStr">
+      <c r="C8" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1810,17 +1822,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="112" t="inlineStr">
+      <c r="A9" s="116" t="inlineStr">
         <is>
           <t>城山</t>
         </is>
       </c>
-      <c r="B9" s="112" t="inlineStr">
+      <c r="B9" s="116" t="inlineStr">
         <is>
           <t>シロヤマ</t>
         </is>
       </c>
-      <c r="C9" s="112" t="inlineStr">
+      <c r="C9" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1832,17 +1844,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="112" t="inlineStr">
+      <c r="A10" s="116" t="inlineStr">
         <is>
           <t>白山</t>
         </is>
       </c>
-      <c r="B10" s="112" t="inlineStr">
+      <c r="B10" s="116" t="inlineStr">
         <is>
           <t>ハクサン</t>
         </is>
       </c>
-      <c r="C10" s="112" t="inlineStr">
+      <c r="C10" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1854,17 +1866,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="112" t="inlineStr">
+      <c r="A11" s="116" t="inlineStr">
         <is>
           <t>庄川</t>
         </is>
       </c>
-      <c r="B11" s="112" t="inlineStr">
+      <c r="B11" s="116" t="inlineStr">
         <is>
           <t>ショウガワ</t>
         </is>
       </c>
-      <c r="C11" s="112" t="inlineStr">
+      <c r="C11" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1872,17 +1884,17 @@
       <c r="D11" s="46" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="112" t="inlineStr">
+      <c r="A12" s="116" t="inlineStr">
         <is>
           <t>白水湖</t>
         </is>
       </c>
-      <c r="B12" s="112" t="inlineStr">
+      <c r="B12" s="116" t="inlineStr">
         <is>
           <t>シラミズコ</t>
         </is>
       </c>
-      <c r="C12" s="112" t="inlineStr">
+      <c r="C12" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1890,17 +1902,17 @@
       <c r="D12" s="46" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="112" t="inlineStr">
+      <c r="A13" s="116" t="inlineStr">
         <is>
           <t>白水園</t>
         </is>
       </c>
-      <c r="B13" s="112" t="inlineStr">
+      <c r="B13" s="116" t="inlineStr">
         <is>
           <t>シラミズエン</t>
         </is>
       </c>
-      <c r="C13" s="112" t="inlineStr">
+      <c r="C13" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1912,17 +1924,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="112" t="inlineStr">
+      <c r="A14" s="116" t="inlineStr">
         <is>
           <t>三方岩岳</t>
         </is>
       </c>
-      <c r="B14" s="112" t="inlineStr">
+      <c r="B14" s="116" t="inlineStr">
         <is>
           <t>サンボウイワダケ</t>
         </is>
       </c>
-      <c r="C14" s="112" t="inlineStr">
+      <c r="C14" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1934,17 +1946,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="112" t="inlineStr">
+      <c r="A15" s="116" t="inlineStr">
         <is>
           <t>野谷荘司山</t>
         </is>
       </c>
-      <c r="B15" s="112" t="inlineStr">
+      <c r="B15" s="116" t="inlineStr">
         <is>
           <t>ノダニショウジヤマ</t>
         </is>
       </c>
-      <c r="C15" s="112" t="inlineStr">
+      <c r="C15" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1956,17 +1968,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="112" t="inlineStr">
+      <c r="A16" s="116" t="inlineStr">
         <is>
           <t>猪臥山</t>
         </is>
       </c>
-      <c r="B16" s="112" t="inlineStr">
+      <c r="B16" s="116" t="inlineStr">
         <is>
           <t>イブシヤマ</t>
         </is>
       </c>
-      <c r="C16" s="112" t="inlineStr">
+      <c r="C16" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1978,17 +1990,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="112" t="inlineStr">
+      <c r="A17" s="116" t="inlineStr">
         <is>
           <t>民家園</t>
         </is>
       </c>
-      <c r="B17" s="112" t="inlineStr">
+      <c r="B17" s="116" t="inlineStr">
         <is>
           <t>ミンカエン</t>
         </is>
       </c>
-      <c r="C17" s="112" t="inlineStr">
+      <c r="C17" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2000,17 +2012,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="112" t="inlineStr">
+      <c r="A18" s="116" t="inlineStr">
         <is>
           <t>白川八幡神社</t>
         </is>
       </c>
-      <c r="B18" s="112" t="inlineStr">
+      <c r="B18" s="116" t="inlineStr">
         <is>
           <t>シラカワハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C18" s="112" t="inlineStr">
+      <c r="C18" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2022,17 +2034,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="112" t="inlineStr">
+      <c r="A19" s="116" t="inlineStr">
         <is>
           <t>鳩谷八幡神社</t>
         </is>
       </c>
-      <c r="B19" s="112" t="inlineStr">
+      <c r="B19" s="116" t="inlineStr">
         <is>
           <t>ハトガヤハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C19" s="112" t="inlineStr">
+      <c r="C19" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2040,17 +2052,17 @@
       <c r="D19" s="46" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="112" t="inlineStr">
+      <c r="A20" s="116" t="inlineStr">
         <is>
           <t>飯島八幡神社</t>
         </is>
       </c>
-      <c r="B20" s="112" t="inlineStr">
+      <c r="B20" s="116" t="inlineStr">
         <is>
           <t>イイジマハチマンジンジャ</t>
         </is>
       </c>
-      <c r="C20" s="112" t="inlineStr">
+      <c r="C20" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2058,17 +2070,17 @@
       <c r="D20" s="46" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="112" t="inlineStr">
+      <c r="A21" s="116" t="inlineStr">
         <is>
           <t>今藤商店</t>
         </is>
       </c>
-      <c r="B21" s="112" t="inlineStr">
+      <c r="B21" s="116" t="inlineStr">
         <is>
           <t>イマトウショウテン</t>
         </is>
       </c>
-      <c r="C21" s="112" t="inlineStr">
+      <c r="C21" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2080,17 +2092,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="112" t="inlineStr">
+      <c r="A22" s="116" t="inlineStr">
         <is>
           <t>朴葉味噌</t>
         </is>
       </c>
-      <c r="B22" s="112" t="inlineStr">
+      <c r="B22" s="116" t="inlineStr">
         <is>
           <t>ホウバミソ</t>
         </is>
       </c>
-      <c r="C22" s="112" t="inlineStr">
+      <c r="C22" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2102,17 +2114,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="112" t="inlineStr">
+      <c r="A23" s="116" t="inlineStr">
         <is>
           <t>岩魚</t>
         </is>
       </c>
-      <c r="B23" s="112" t="inlineStr">
+      <c r="B23" s="116" t="inlineStr">
         <is>
           <t>イワナ</t>
         </is>
       </c>
-      <c r="C23" s="112" t="inlineStr">
+      <c r="C23" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2124,17 +2136,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="112" t="inlineStr">
+      <c r="A24" s="116" t="inlineStr">
         <is>
           <t>飛騨牛</t>
         </is>
       </c>
-      <c r="B24" s="112" t="inlineStr">
+      <c r="B24" s="116" t="inlineStr">
         <is>
           <t>ヒダギュウ</t>
         </is>
       </c>
-      <c r="C24" s="112" t="inlineStr">
+      <c r="C24" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2146,17 +2158,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="112" t="inlineStr">
+      <c r="A25" s="116" t="inlineStr">
         <is>
           <t>石豆腐</t>
         </is>
       </c>
-      <c r="B25" s="112" t="inlineStr">
+      <c r="B25" s="116" t="inlineStr">
         <is>
           <t>イシドウフ</t>
         </is>
       </c>
-      <c r="C25" s="112" t="inlineStr">
+      <c r="C25" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2164,17 +2176,17 @@
       <c r="D25" s="46" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="112" t="inlineStr">
+      <c r="A26" s="116" t="inlineStr">
         <is>
           <t>合掌造り</t>
         </is>
       </c>
-      <c r="B26" s="112" t="inlineStr">
+      <c r="B26" s="116" t="inlineStr">
         <is>
           <t>ガッショウヅクリ</t>
         </is>
       </c>
-      <c r="C26" s="112" t="inlineStr">
+      <c r="C26" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2182,17 +2194,17 @@
       <c r="D26" s="46" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="112" t="inlineStr">
+      <c r="A27" s="116" t="inlineStr">
         <is>
           <t>春駒（はるこま）</t>
         </is>
       </c>
-      <c r="B27" s="112" t="inlineStr">
+      <c r="B27" s="116" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C27" s="112" t="inlineStr">
+      <c r="C27" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2204,17 +2216,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="112" t="inlineStr">
+      <c r="A28" s="116" t="inlineStr">
         <is>
           <t>春駒</t>
         </is>
       </c>
-      <c r="B28" s="112" t="inlineStr">
+      <c r="B28" s="116" t="inlineStr">
         <is>
           <t>ハルコマ</t>
         </is>
       </c>
-      <c r="C28" s="112" t="inlineStr">
+      <c r="C28" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2226,17 +2238,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="112" t="inlineStr">
+      <c r="A29" s="116" t="inlineStr">
         <is>
           <t>白川連獅子</t>
         </is>
       </c>
-      <c r="B29" s="112" t="inlineStr">
+      <c r="B29" s="116" t="inlineStr">
         <is>
           <t>シラカワレンジシ</t>
         </is>
       </c>
-      <c r="C29" s="112" t="inlineStr">
+      <c r="C29" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2248,17 +2260,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="112" t="inlineStr">
+      <c r="A30" s="116" t="inlineStr">
         <is>
           <t>獅子舞</t>
         </is>
       </c>
-      <c r="B30" s="112" t="inlineStr">
+      <c r="B30" s="116" t="inlineStr">
         <is>
           <t>シシマイ</t>
         </is>
       </c>
-      <c r="C30" s="112" t="inlineStr">
+      <c r="C30" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2266,17 +2278,17 @@
       <c r="D30" s="46" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="112" t="inlineStr">
+      <c r="A31" s="116" t="inlineStr">
         <is>
           <t>神幸祭</t>
         </is>
       </c>
-      <c r="B31" s="112" t="inlineStr">
+      <c r="B31" s="116" t="inlineStr">
         <is>
           <t>シンコウサイ</t>
         </is>
       </c>
-      <c r="C31" s="112" t="inlineStr">
+      <c r="C31" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2288,17 +2300,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="112" t="inlineStr">
+      <c r="A32" s="116" t="inlineStr">
         <is>
           <t>還御</t>
         </is>
       </c>
-      <c r="B32" s="112" t="inlineStr">
+      <c r="B32" s="116" t="inlineStr">
         <is>
           <t>カンギョ</t>
         </is>
       </c>
-      <c r="C32" s="112" t="inlineStr">
+      <c r="C32" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2306,17 +2318,17 @@
       <c r="D32" s="46" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="112" t="inlineStr">
+      <c r="A33" s="116" t="inlineStr">
         <is>
           <t>初穂料</t>
         </is>
       </c>
-      <c r="B33" s="112" t="inlineStr">
+      <c r="B33" s="116" t="inlineStr">
         <is>
           <t>ハツホリョウ</t>
         </is>
       </c>
-      <c r="C33" s="112" t="inlineStr">
+      <c r="C33" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2324,17 +2336,17 @@
       <c r="D33" s="46" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="112" t="inlineStr">
+      <c r="A34" s="116" t="inlineStr">
         <is>
           <t>記念盃</t>
         </is>
       </c>
-      <c r="B34" s="112" t="inlineStr">
+      <c r="B34" s="116" t="inlineStr">
         <is>
           <t>キネンハイ</t>
         </is>
       </c>
-      <c r="C34" s="112" t="inlineStr">
+      <c r="C34" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2342,17 +2354,17 @@
       <c r="D34" s="46" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="112" t="inlineStr">
+      <c r="A35" s="116" t="inlineStr">
         <is>
           <t>志納</t>
         </is>
       </c>
-      <c r="B35" s="112" t="inlineStr">
+      <c r="B35" s="116" t="inlineStr">
         <is>
           <t>シノウ</t>
         </is>
       </c>
-      <c r="C35" s="112" t="inlineStr">
+      <c r="C35" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2360,17 +2372,17 @@
       <c r="D35" s="46" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="112" t="inlineStr">
+      <c r="A36" s="116" t="inlineStr">
         <is>
           <t>徳利</t>
         </is>
       </c>
-      <c r="B36" s="112" t="inlineStr">
+      <c r="B36" s="116" t="inlineStr">
         <is>
           <t>トックリ</t>
         </is>
       </c>
-      <c r="C36" s="112" t="inlineStr">
+      <c r="C36" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2378,17 +2390,17 @@
       <c r="D36" s="46" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="112" t="inlineStr">
+      <c r="A37" s="116" t="inlineStr">
         <is>
           <t>五穀豊穣</t>
         </is>
       </c>
-      <c r="B37" s="112" t="inlineStr">
+      <c r="B37" s="116" t="inlineStr">
         <is>
           <t>ゴコクホウジョウ</t>
         </is>
       </c>
-      <c r="C37" s="112" t="inlineStr">
+      <c r="C37" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2396,17 +2408,17 @@
       <c r="D37" s="46" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="112" t="inlineStr">
+      <c r="A38" s="116" t="inlineStr">
         <is>
           <t>郷土芸能</t>
         </is>
       </c>
-      <c r="B38" s="112" t="inlineStr">
+      <c r="B38" s="116" t="inlineStr">
         <is>
           <t>キョウドゲイノウ</t>
         </is>
       </c>
-      <c r="C38" s="112" t="inlineStr">
+      <c r="C38" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2414,17 +2426,17 @@
       <c r="D38" s="46" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="112" t="inlineStr">
+      <c r="A39" s="116" t="inlineStr">
         <is>
           <t>入村料</t>
         </is>
       </c>
-      <c r="B39" s="112" t="inlineStr">
+      <c r="B39" s="116" t="inlineStr">
         <is>
           <t>ニュウソンリョウ</t>
         </is>
       </c>
-      <c r="C39" s="112" t="inlineStr">
+      <c r="C39" s="116" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2432,17 +2444,17 @@
       <c r="D39" s="46" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="112" t="inlineStr">
+      <c r="A40" s="116" t="inlineStr">
         <is>
           <t>村内</t>
         </is>
       </c>
-      <c r="B40" s="112" t="inlineStr">
+      <c r="B40" s="116" t="inlineStr">
         <is>
           <t>ソンナイ</t>
         </is